--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12585" windowHeight="9120"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12585" windowHeight="7275"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="148">
   <si>
     <t/>
   </si>
@@ -89,6 +89,27 @@
     <t>Address</t>
   </si>
   <si>
+    <t>Alameda County</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>Closure Permanent</t>
+  </si>
+  <si>
+    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>Los Angeles County</t>
+  </si>
+  <si>
+    <t>Assembled Financial Technology, LLC</t>
+  </si>
+  <si>
+    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
+  </si>
+  <si>
     <t>San Diego County</t>
   </si>
   <si>
@@ -98,39 +119,57 @@
     <t>Layoff Permanent</t>
   </si>
   <si>
+    <t>2620 Commerce Way, Suite A/B  Vista CA 92081</t>
+  </si>
+  <si>
     <t>6225 Nancy Ridge Dr.  San Diego CA 92121</t>
   </si>
   <si>
-    <t>2620 Commerce Way, Suite A/B  Vista CA 92081</t>
-  </si>
-  <si>
-    <t>Alameda County</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>Closure Permanent</t>
-  </si>
-  <si>
-    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
-  </si>
-  <si>
-    <t>Los Angeles County</t>
-  </si>
-  <si>
-    <t>Assembled Financial Technology, LLC</t>
-  </si>
-  <si>
-    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
-  </si>
-  <si>
     <t>Cue Health</t>
   </si>
   <si>
     <t>9877 Waples St.  San Diego CA 92121</t>
   </si>
   <si>
+    <t>PAE Shared Services LLC dba Amentum</t>
+  </si>
+  <si>
+    <t>San Clemente Island  Los Angeles CA 90731</t>
+  </si>
+  <si>
+    <t>Naval Base Point Loma 4045 Hancock St  San Diego CA 92110</t>
+  </si>
+  <si>
+    <t>San Mateo County</t>
+  </si>
+  <si>
+    <t>Tesla, Inc.</t>
+  </si>
+  <si>
+    <t>3055 Clearview Way  San Mateo CA 94402</t>
+  </si>
+  <si>
+    <t>NAS North Island  San Diego CA 92135</t>
+  </si>
+  <si>
+    <t>DailyLook, Inc.</t>
+  </si>
+  <si>
+    <t>2445 E. 12th Street, Unit B  Los Angeles CA 90021</t>
+  </si>
+  <si>
+    <t>Heron Therapeutics, Inc.</t>
+  </si>
+  <si>
+    <t>4242 Campus Point Court, Suite 200  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>ABM Industry Groups, LLC dba Meta</t>
+  </si>
+  <si>
+    <t>1 Hacker Way  Menlo Park CA 94025</t>
+  </si>
+  <si>
     <t>Santa Clara County</t>
   </si>
   <si>
@@ -140,48 +179,54 @@
     <t>1100 Page Mill Road  Palo Alto CA 94304</t>
   </si>
   <si>
-    <t>PAE Shared Services LLC dba Amentum</t>
-  </si>
-  <si>
-    <t>NAS North Island  San Diego CA 92135</t>
-  </si>
-  <si>
-    <t>Naval Base Point Loma 4045 Hancock St  San Diego CA 92110</t>
-  </si>
-  <si>
-    <t>San Mateo County</t>
-  </si>
-  <si>
-    <t>Tesla, Inc.</t>
-  </si>
-  <si>
-    <t>3055 Clearview Way  San Mateo CA 94402</t>
-  </si>
-  <si>
-    <t>San Clemente Island  Los Angeles CA 90731</t>
-  </si>
-  <si>
-    <t>DailyLook, Inc.</t>
-  </si>
-  <si>
-    <t>2445 E. 12th Street, Unit B  Los Angeles CA 90021</t>
-  </si>
-  <si>
-    <t>Heron Therapeutics, Inc.</t>
-  </si>
-  <si>
-    <t>4242 Campus Point Court, Suite 200  San Diego CA 92121</t>
-  </si>
-  <si>
-    <t>ABM Industry Groups, LLC dba Meta</t>
-  </si>
-  <si>
-    <t>1 Hacker Way  Menlo Park CA 94025</t>
+    <t>Kern County</t>
   </si>
   <si>
     <t>JSL Transport, LLC</t>
   </si>
   <si>
+    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>PACT Pharma</t>
+  </si>
+  <si>
+    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
+  </si>
+  <si>
+    <t>901 Page Avenue  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>R.A. Phillips Industries, Inc.</t>
+  </si>
+  <si>
+    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>47700 Kato Road  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>10371 Culver Blvd.  Culver City CA 90232</t>
+  </si>
+  <si>
+    <t>47400 Kato Road  Fremotn CA 94538</t>
+  </si>
+  <si>
+    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
+  </si>
+  <si>
     <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
   </si>
   <si>
@@ -191,49 +236,13 @@
     <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
   </si>
   <si>
-    <t>47400 Kato Road  Fremotn CA 94538</t>
-  </si>
-  <si>
-    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>Orange County</t>
-  </si>
-  <si>
-    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
-  </si>
-  <si>
-    <t>47700 Kato Road  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>10371 Culver Blvd.  Culver City CA 90232</t>
-  </si>
-  <si>
-    <t>901 Page Avenue  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>R.A. Phillips Industries, Inc.</t>
-  </si>
-  <si>
-    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>Kern County</t>
-  </si>
-  <si>
-    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>PACT Pharma</t>
-  </si>
-  <si>
-    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
+    <t>14250 Arminta Street  Panorama City CA 91402</t>
+  </si>
+  <si>
+    <t>621 Ruberta, Unit 2  Glendale CA 91201</t>
+  </si>
+  <si>
+    <t>7300 Medical Center Drive  West Hills CA 91307</t>
   </si>
   <si>
     <t>Stanislaus County</t>
@@ -242,18 +251,27 @@
     <t>4301 N. Star Way  Modesto CA 95356</t>
   </si>
   <si>
-    <t>14250 Arminta Street  Panorama City CA 91402</t>
-  </si>
-  <si>
-    <t>621 Ruberta, Unit 2  Glendale CA 91201</t>
-  </si>
-  <si>
-    <t>7300 Medical Center Drive  West Hills CA 91307</t>
-  </si>
-  <si>
     <t>First Student</t>
   </si>
   <si>
+    <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
+  </si>
+  <si>
+    <t>Riverside County</t>
+  </si>
+  <si>
+    <t>Scotts Temecula Operations LLC</t>
+  </si>
+  <si>
+    <t>42375 Remington Avenue  Temecula CA 92590</t>
+  </si>
+  <si>
+    <t>11233 San Fernando Road  San Fernando CA 91340</t>
+  </si>
+  <si>
+    <t>1600 Lincoln Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
     <t>5950 S. St. Andrews Pl.  Los Angeles CA 90047</t>
   </si>
   <si>
@@ -263,24 +281,6 @@
     <t>3825 Fabian Way  Palo Alto CA 94303</t>
   </si>
   <si>
-    <t>Riverside County</t>
-  </si>
-  <si>
-    <t>Scotts Temecula Operations LLC</t>
-  </si>
-  <si>
-    <t>42375 Remington Avenue  Temecula CA 92590</t>
-  </si>
-  <si>
-    <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
-  </si>
-  <si>
-    <t>11233 San Fernando Road  San Fernando CA 91340</t>
-  </si>
-  <si>
-    <t>1600 Lincoln Ave.  Pasadena CA 91103</t>
-  </si>
-  <si>
     <t>Voxpro Group, LLC</t>
   </si>
   <si>
@@ -293,6 +293,12 @@
     <t>38 Technology Drive, Suite 100  Irvine CA 92618</t>
   </si>
   <si>
+    <t>Anheuser-Busch, LLC</t>
+  </si>
+  <si>
+    <t>8380 Pardee Drive  Oakland CA 94621</t>
+  </si>
+  <si>
     <t>San Bernardino County</t>
   </si>
   <si>
@@ -302,10 +308,10 @@
     <t>14613 Bar Harbor Road  Fontana CA 92336</t>
   </si>
   <si>
-    <t>Anheuser-Busch, LLC</t>
-  </si>
-  <si>
-    <t>8380 Pardee Drive  Oakland CA 94621</t>
+    <t>Adverum Biotechnologies, Inc.</t>
+  </si>
+  <si>
+    <t>900 Saginaw Drive  Redwood City CA 94063</t>
   </si>
   <si>
     <t>ADP, Inc.</t>
@@ -320,15 +326,9 @@
     <t>2535 Camino Del Rio South Suite 250  San Diego CA 92108</t>
   </si>
   <si>
-    <t>Adverum Biotechnologies, Inc.</t>
-  </si>
-  <si>
     <t>100 Cardinal Way  Redwood City CA 94063</t>
   </si>
   <si>
-    <t>900 Saginaw Drive  Redwood City CA 94063</t>
-  </si>
-  <si>
     <t>Freshly, Inc.</t>
   </si>
   <si>
@@ -350,36 +350,72 @@
     <t>3615 Foothill Rd.  Carpinteria CA 93013</t>
   </si>
   <si>
+    <t>Solano County</t>
+  </si>
+  <si>
+    <t>North Bay Health</t>
+  </si>
+  <si>
+    <t>4500 Business Center Dr.  Fairfield CA 94534</t>
+  </si>
+  <si>
+    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
+  </si>
+  <si>
     <t>Ventura County</t>
   </si>
   <si>
     <t>Pennymac</t>
   </si>
   <si>
+    <t>3043 Townsgate Road  Thousand Oaks CA 91361</t>
+  </si>
+  <si>
     <t>112 Lakeview Canyon Road  Thousand Oaks CA 91362</t>
   </si>
   <si>
-    <t>Solano County</t>
-  </si>
-  <si>
-    <t>North Bay Health</t>
-  </si>
-  <si>
     <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
   </si>
   <si>
-    <t>4500 Business Center Dr.  Fairfield CA 94534</t>
-  </si>
-  <si>
-    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
-  </si>
-  <si>
-    <t>3043 Townsgate Road  Thousand Oaks CA 91361</t>
-  </si>
-  <si>
     <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
   </si>
   <si>
+    <t>OnePointOne Inc.</t>
+  </si>
+  <si>
+    <t>1185 Campbell Avenue  San Jose CA 95126</t>
+  </si>
+  <si>
+    <t>Data Aire Inc.</t>
+  </si>
+  <si>
+    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
+  </si>
+  <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Restoration Hardware Inc.</t>
+  </si>
+  <si>
+    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
+  </si>
+  <si>
+    <t>Gardena Honda</t>
+  </si>
+  <si>
+    <t>15515 South Western Avenue  Gardena CA 90249</t>
+  </si>
+  <si>
+    <t>San Francisco County</t>
+  </si>
+  <si>
+    <t>Tonal Systems, Inc.</t>
+  </si>
+  <si>
+    <t>617 Bryant Street  San Francisco CA 94107</t>
+  </si>
+  <si>
     <t>Urbn Leaf dba Uprooted Inc.</t>
   </si>
   <si>
@@ -395,46 +431,46 @@
     <t>151 Oyster Point Blvd. #400  South San Francisco CA 94080</t>
   </si>
   <si>
-    <t>Data Aire Inc.</t>
-  </si>
-  <si>
-    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
-  </si>
-  <si>
-    <t>San Joaquin County</t>
-  </si>
-  <si>
-    <t>Restoration Hardware Inc.</t>
-  </si>
-  <si>
-    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
-  </si>
-  <si>
-    <t>OnePointOne Inc.</t>
-  </si>
-  <si>
-    <t>1185 Campbell Avenue  San Jose CA 95126</t>
-  </si>
-  <si>
-    <t>Gardena Honda</t>
-  </si>
-  <si>
-    <t>15515 South Western Avenue  Gardena CA 90249</t>
-  </si>
-  <si>
-    <t>San Francisco County</t>
-  </si>
-  <si>
-    <t>Tonal Systems, Inc.</t>
-  </si>
-  <si>
-    <t>617 Bryant Street  San Francisco CA 94107</t>
-  </si>
-  <si>
     <t>Amy&amp;rsquo;s Kitchen, Inc.</t>
   </si>
   <si>
     <t>1885 Las Plumas Avenue  San Jose CA 95133</t>
+  </si>
+  <si>
+    <t>Rise Baking Company dba Brill, Inc.</t>
+  </si>
+  <si>
+    <t>2111 W. Valley Blvd.  Colton CA 92324</t>
+  </si>
+  <si>
+    <t>Schneider Electric</t>
+  </si>
+  <si>
+    <t>1660 Scenic Avenue  Costa Mesa CA 92626</t>
+  </si>
+  <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Adventist Health</t>
+  </si>
+  <si>
+    <t>1 Adventist Health Way  Roseville CA 95661</t>
+  </si>
+  <si>
+    <t>Imperfect Foods, Inc.</t>
+  </si>
+  <si>
+    <t>1616 Donner Ave  San Francisco CA 94124</t>
+  </si>
+  <si>
+    <t>Invitae Corporation</t>
+  </si>
+  <si>
+    <t>5 Technology Drive  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>1400 16th Street  San Francisco CA 94103</t>
   </si>
   <si>
     <t xml:space="preserve"> Employees Affected</t>
@@ -463,7 +499,7 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 7/25/2022
+ End Date: 7/27/2022
 </t>
   </si>
   <si>
@@ -1302,26 +1338,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
+    <col min="11" max="11" width="7" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="48" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -1341,9 +1377,9 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="39" customHeight="1">
+    <row r="2" spans="1:18" ht="37.5" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -1432,14 +1468,14 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>44735</v>
+        <v>44727</v>
       </c>
       <c r="C5" s="26">
         <v>44750</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="2">
-        <v>44796</v>
+        <v>44897</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>10</v>
@@ -1451,7 +1487,7 @@
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="30">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L5" s="27"/>
       <c r="M5" s="31" t="s">
@@ -1461,20 +1497,20 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="C6" s="33">
         <v>44750</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="4">
-        <v>44796</v>
+        <v>44794</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" s="29"/>
       <c r="H6" s="27"/>
@@ -1483,71 +1519,71 @@
       </c>
       <c r="J6" s="27"/>
       <c r="K6" s="35">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="L6" s="27"/>
       <c r="M6" s="36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>44727</v>
+        <v>44735</v>
       </c>
       <c r="C7" s="26">
         <v>44750</v>
       </c>
       <c r="D7" s="27"/>
       <c r="E7" s="2">
-        <v>44897</v>
+        <v>44796</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7" s="27"/>
       <c r="K7" s="30">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="L7" s="27"/>
       <c r="M7" s="31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N7" s="32"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4">
-        <v>44736</v>
+        <v>44735</v>
       </c>
       <c r="C8" s="33">
         <v>44750</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="4">
-        <v>44794</v>
+        <v>44796</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="27"/>
       <c r="I8" s="34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J8" s="27"/>
       <c r="K8" s="35">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="36" t="s">
@@ -1557,7 +1593,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>44735</v>
@@ -1575,7 +1611,7 @@
       <c r="G9" s="29"/>
       <c r="H9" s="27"/>
       <c r="I9" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="30">
@@ -1589,39 +1625,39 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>44739</v>
+        <v>44727</v>
       </c>
       <c r="C10" s="33">
         <v>44753</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="4">
-        <v>44799</v>
+        <v>44784</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="27"/>
       <c r="I10" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J10" s="27"/>
       <c r="K10" s="35">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N10" s="32"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
         <v>44727</v>
@@ -1634,39 +1670,39 @@
         <v>44784</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="27"/>
       <c r="I11" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J11" s="27"/>
       <c r="K11" s="30">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="L11" s="27"/>
       <c r="M11" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4">
-        <v>44727</v>
+        <v>44741</v>
       </c>
       <c r="C12" s="33">
         <v>44753</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="4">
-        <v>44784</v>
+        <v>44800</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="29"/>
       <c r="H12" s="27"/>
@@ -1675,7 +1711,7 @@
       </c>
       <c r="J12" s="27"/>
       <c r="K12" s="35">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="L12" s="27"/>
       <c r="M12" s="36" t="s">
@@ -1685,145 +1721,145 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>44741</v>
+        <v>44727</v>
       </c>
       <c r="C13" s="26">
         <v>44753</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="2">
-        <v>44800</v>
+        <v>44784</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G13" s="29"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J13" s="27"/>
       <c r="K13" s="30">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="L13" s="27"/>
       <c r="M13" s="31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>44727</v>
+        <v>44739</v>
       </c>
       <c r="C14" s="33">
         <v>44753</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="4">
-        <v>44784</v>
+        <v>44799</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G14" s="29"/>
       <c r="H14" s="27"/>
       <c r="I14" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J14" s="27"/>
       <c r="K14" s="35">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L14" s="27"/>
       <c r="M14" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N14" s="32"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>44739</v>
+        <v>44741</v>
       </c>
       <c r="C15" s="26">
         <v>44753</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="2">
-        <v>44799</v>
+        <v>44801</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="27"/>
       <c r="I15" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J15" s="27"/>
       <c r="K15" s="30">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L15" s="27"/>
       <c r="M15" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N15" s="32"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B16" s="4">
-        <v>44741</v>
+        <v>44743</v>
       </c>
       <c r="C16" s="33">
         <v>44753</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="4">
-        <v>44801</v>
+        <v>44766</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="29"/>
       <c r="H16" s="27"/>
       <c r="I16" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J16" s="27"/>
       <c r="K16" s="35">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="L16" s="27"/>
       <c r="M16" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N16" s="32"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C17" s="26">
         <v>44753</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="2">
-        <v>44766</v>
+        <v>44799</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>37</v>
@@ -1831,11 +1867,11 @@
       <c r="G17" s="29"/>
       <c r="H17" s="27"/>
       <c r="I17" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J17" s="27"/>
       <c r="K17" s="30">
-        <v>368</v>
+        <v>62</v>
       </c>
       <c r="L17" s="27"/>
       <c r="M17" s="31" t="s">
@@ -1845,7 +1881,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B18" s="4">
         <v>44743</v>
@@ -1858,71 +1894,71 @@
         <v>44804</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" s="29"/>
       <c r="H18" s="27"/>
       <c r="I18" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J18" s="27"/>
       <c r="K18" s="35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="27"/>
       <c r="M18" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N18" s="32"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
-        <v>44743</v>
+        <v>44742</v>
       </c>
       <c r="C19" s="26">
         <v>44754</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="2">
-        <v>44804</v>
+        <v>44802</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G19" s="29"/>
       <c r="H19" s="27"/>
       <c r="I19" s="28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" s="27"/>
       <c r="K19" s="30">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="L19" s="27"/>
       <c r="M19" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N19" s="32"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B20" s="4">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C20" s="33">
         <v>44754</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="4">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G20" s="29"/>
       <c r="H20" s="27"/>
@@ -1931,17 +1967,17 @@
       </c>
       <c r="J20" s="27"/>
       <c r="K20" s="35">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L20" s="27"/>
       <c r="M20" s="36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N20" s="32"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
         <v>44739</v>
@@ -1954,58 +1990,58 @@
         <v>44800</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G21" s="29"/>
       <c r="H21" s="27"/>
       <c r="I21" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J21" s="27"/>
       <c r="K21" s="30">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L21" s="27"/>
       <c r="M21" s="31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N21" s="32"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B22" s="4">
-        <v>44743</v>
+        <v>44732</v>
       </c>
       <c r="C22" s="33">
         <v>44754</v>
       </c>
       <c r="D22" s="27"/>
       <c r="E22" s="4">
-        <v>44804</v>
+        <v>44926</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G22" s="29"/>
       <c r="H22" s="27"/>
       <c r="I22" s="34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J22" s="27"/>
       <c r="K22" s="35">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="L22" s="27"/>
       <c r="M22" s="36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N22" s="32"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2">
         <v>44739</v>
@@ -2018,12 +2054,12 @@
         <v>44800</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" s="29"/>
       <c r="H23" s="27"/>
       <c r="I23" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J23" s="27"/>
       <c r="K23" s="30">
@@ -2031,13 +2067,13 @@
       </c>
       <c r="L23" s="27"/>
       <c r="M23" s="31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N23" s="32"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B24" s="4">
         <v>44743</v>
@@ -2050,12 +2086,12 @@
         <v>44804</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" s="29"/>
       <c r="H24" s="27"/>
       <c r="I24" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J24" s="27"/>
       <c r="K24" s="35">
@@ -2063,13 +2099,13 @@
       </c>
       <c r="L24" s="27"/>
       <c r="M24" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N24" s="32"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2">
         <v>44739</v>
@@ -2082,80 +2118,80 @@
         <v>44800</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" s="29"/>
       <c r="H25" s="27"/>
       <c r="I25" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J25" s="27"/>
       <c r="K25" s="30">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L25" s="27"/>
       <c r="M25" s="31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B26" s="4">
-        <v>44732</v>
+        <v>44739</v>
       </c>
       <c r="C26" s="33">
         <v>44754</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="4">
-        <v>44926</v>
+        <v>44800</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G26" s="29"/>
       <c r="H26" s="27"/>
       <c r="I26" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="35">
-        <v>211</v>
+        <v>1</v>
       </c>
       <c r="L26" s="27"/>
       <c r="M26" s="36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N26" s="32"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C27" s="26">
         <v>44754</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="2">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="27"/>
       <c r="I27" s="28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J27" s="27"/>
       <c r="K27" s="30">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="L27" s="27"/>
       <c r="M27" s="31" t="s">
@@ -2165,20 +2201,20 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B28" s="4">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="C28" s="33">
         <v>44754</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="4">
-        <v>44802</v>
+        <v>44804</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G28" s="29"/>
       <c r="H28" s="27"/>
@@ -2187,30 +2223,30 @@
       </c>
       <c r="J28" s="27"/>
       <c r="K28" s="35">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="L28" s="27"/>
       <c r="M28" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N28" s="32"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C29" s="26">
         <v>44754</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="2">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G29" s="29"/>
       <c r="H29" s="27"/>
@@ -2219,17 +2255,17 @@
       </c>
       <c r="J29" s="27"/>
       <c r="K29" s="30">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="L29" s="27"/>
       <c r="M29" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4">
         <v>44743</v>
@@ -2242,16 +2278,16 @@
         <v>44804</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="27"/>
       <c r="I30" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J30" s="27"/>
       <c r="K30" s="35">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L30" s="27"/>
       <c r="M30" s="36" t="s">
@@ -2261,7 +2297,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2">
         <v>44743</v>
@@ -2274,26 +2310,26 @@
         <v>44804</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G31" s="29"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="30">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L31" s="27"/>
       <c r="M31" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N31" s="32"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B32" s="4">
         <v>44743</v>
@@ -2306,26 +2342,26 @@
         <v>44804</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G32" s="29"/>
       <c r="H32" s="27"/>
       <c r="I32" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="35">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="L32" s="27"/>
       <c r="M32" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2">
         <v>44743</v>
@@ -2338,26 +2374,26 @@
         <v>44804</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="27"/>
       <c r="M33" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N33" s="32"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B34" s="4">
         <v>44743</v>
@@ -2370,16 +2406,16 @@
         <v>44804</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="29"/>
       <c r="H34" s="27"/>
       <c r="I34" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="35">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L34" s="27"/>
       <c r="M34" s="36" t="s">
@@ -2389,7 +2425,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2">
         <v>44743</v>
@@ -2407,11 +2443,11 @@
       <c r="G35" s="29"/>
       <c r="H35" s="27"/>
       <c r="I35" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="30">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="L35" s="27"/>
       <c r="M35" s="31" t="s">
@@ -2421,81 +2457,81 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B36" s="4">
-        <v>44748</v>
+        <v>44753</v>
       </c>
       <c r="C36" s="33">
         <v>44756</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="4">
-        <v>44809</v>
+        <v>44813</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G36" s="29"/>
       <c r="H36" s="27"/>
       <c r="I36" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="35">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="L36" s="27"/>
       <c r="M36" s="36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N36" s="32"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
-        <v>44753</v>
+        <v>44743</v>
       </c>
       <c r="C37" s="26">
         <v>44756</v>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="2">
-        <v>44813</v>
+        <v>44799</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G37" s="29"/>
       <c r="H37" s="27"/>
       <c r="I37" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J37" s="27"/>
       <c r="K37" s="30">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="L37" s="27"/>
       <c r="M37" s="31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N37" s="32"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B38" s="4">
-        <v>44743</v>
+        <v>44747</v>
       </c>
       <c r="C38" s="33">
         <v>44756</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="4">
-        <v>44799</v>
+        <v>44788</v>
       </c>
       <c r="F38" s="34" t="s">
         <v>63</v>
@@ -2503,21 +2539,21 @@
       <c r="G38" s="29"/>
       <c r="H38" s="27"/>
       <c r="I38" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J38" s="27"/>
       <c r="K38" s="35">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="L38" s="27"/>
       <c r="M38" s="36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N38" s="32"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2">
         <v>44743</v>
@@ -2535,43 +2571,43 @@
       <c r="G39" s="29"/>
       <c r="H39" s="27"/>
       <c r="I39" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J39" s="27"/>
       <c r="K39" s="30">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="L39" s="27"/>
       <c r="M39" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N39" s="32"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B40" s="4">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="C40" s="33">
         <v>44756</v>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="4">
-        <v>44788</v>
+        <v>44809</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G40" s="29"/>
       <c r="H40" s="27"/>
       <c r="I40" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J40" s="27"/>
       <c r="K40" s="35">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="L40" s="27"/>
       <c r="M40" s="36" t="s">
@@ -2581,7 +2617,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B41" s="2">
         <v>44749</v>
@@ -2599,7 +2635,7 @@
       <c r="G41" s="29"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J41" s="27"/>
       <c r="K41" s="30">
@@ -2613,7 +2649,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="4">
         <v>44749</v>
@@ -2631,7 +2667,7 @@
       <c r="G42" s="29"/>
       <c r="H42" s="27"/>
       <c r="I42" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J42" s="27"/>
       <c r="K42" s="35">
@@ -2645,49 +2681,49 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2">
-        <v>44753</v>
+        <v>44749</v>
       </c>
       <c r="C43" s="26">
         <v>44760</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="2">
-        <v>44804</v>
+        <v>44813</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G43" s="29"/>
       <c r="H43" s="27"/>
       <c r="I43" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J43" s="27"/>
       <c r="K43" s="30">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="L43" s="27"/>
       <c r="M43" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N43" s="32"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="B44" s="4">
-        <v>44749</v>
+        <v>44753</v>
       </c>
       <c r="C44" s="33">
         <v>44760</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="4">
-        <v>44813</v>
+        <v>44804</v>
       </c>
       <c r="F44" s="34" t="s">
         <v>80</v>
@@ -2695,11 +2731,11 @@
       <c r="G44" s="29"/>
       <c r="H44" s="27"/>
       <c r="I44" s="34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J44" s="27"/>
       <c r="K44" s="35">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L44" s="27"/>
       <c r="M44" s="36" t="s">
@@ -2709,17 +2745,17 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B45" s="2">
-        <v>44754</v>
+        <v>44749</v>
       </c>
       <c r="C45" s="26">
         <v>44761</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="2">
-        <v>44820</v>
+        <v>44749</v>
       </c>
       <c r="F45" s="28" t="s">
         <v>82</v>
@@ -2727,11 +2763,11 @@
       <c r="G45" s="29"/>
       <c r="H45" s="27"/>
       <c r="I45" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J45" s="27"/>
       <c r="K45" s="30">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L45" s="27"/>
       <c r="M45" s="31" t="s">
@@ -2744,14 +2780,14 @@
         <v>9</v>
       </c>
       <c r="B46" s="4">
-        <v>44755</v>
+        <v>44754</v>
       </c>
       <c r="C46" s="33">
         <v>44761</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="4">
-        <v>44806</v>
+        <v>44820</v>
       </c>
       <c r="F46" s="34" t="s">
         <v>84</v>
@@ -2759,11 +2795,11 @@
       <c r="G46" s="29"/>
       <c r="H46" s="27"/>
       <c r="I46" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J46" s="27"/>
       <c r="K46" s="35">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="L46" s="27"/>
       <c r="M46" s="36" t="s">
@@ -2773,17 +2809,17 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B47" s="2">
-        <v>44749</v>
+        <v>44755</v>
       </c>
       <c r="C47" s="26">
         <v>44761</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="2">
-        <v>44749</v>
+        <v>44806</v>
       </c>
       <c r="F47" s="28" t="s">
         <v>86</v>
@@ -2791,11 +2827,11 @@
       <c r="G47" s="29"/>
       <c r="H47" s="27"/>
       <c r="I47" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J47" s="27"/>
       <c r="K47" s="30">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L47" s="27"/>
       <c r="M47" s="31" t="s">
@@ -2805,7 +2841,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B48" s="4">
         <v>44749</v>
@@ -2818,16 +2854,16 @@
         <v>44749</v>
       </c>
       <c r="F48" s="34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G48" s="29"/>
       <c r="H48" s="27"/>
       <c r="I48" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J48" s="27"/>
       <c r="K48" s="35">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="L48" s="27"/>
       <c r="M48" s="36" t="s">
@@ -2837,7 +2873,7 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2">
         <v>44754</v>
@@ -2855,7 +2891,7 @@
       <c r="G49" s="29"/>
       <c r="H49" s="27"/>
       <c r="I49" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J49" s="27"/>
       <c r="K49" s="30">
@@ -2869,7 +2905,7 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B50" s="4">
         <v>44692</v>
@@ -2887,7 +2923,7 @@
       <c r="G50" s="29"/>
       <c r="H50" s="27"/>
       <c r="I50" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J50" s="27"/>
       <c r="K50" s="35">
@@ -2919,7 +2955,7 @@
       <c r="G51" s="29"/>
       <c r="H51" s="27"/>
       <c r="I51" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J51" s="27"/>
       <c r="K51" s="30">
@@ -2936,14 +2972,14 @@
         <v>96</v>
       </c>
       <c r="B52" s="4">
-        <v>44700</v>
+        <v>44753</v>
       </c>
       <c r="C52" s="33">
         <v>44763</v>
       </c>
       <c r="D52" s="27"/>
       <c r="E52" s="4">
-        <v>44760</v>
+        <v>44795</v>
       </c>
       <c r="F52" s="34" t="s">
         <v>97</v>
@@ -2951,11 +2987,11 @@
       <c r="G52" s="29"/>
       <c r="H52" s="27"/>
       <c r="I52" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J52" s="27"/>
       <c r="K52" s="35">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L52" s="27"/>
       <c r="M52" s="36" t="s">
@@ -2965,7 +3001,7 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B53" s="2">
         <v>44753</v>
@@ -2978,48 +3014,48 @@
         <v>44795</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G53" s="29"/>
       <c r="H53" s="27"/>
       <c r="I53" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J53" s="27"/>
       <c r="K53" s="30">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="L53" s="27"/>
       <c r="M53" s="31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N53" s="32"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B54" s="4">
-        <v>44753</v>
+        <v>44700</v>
       </c>
       <c r="C54" s="33">
         <v>44763</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="4">
-        <v>44795</v>
+        <v>44760</v>
       </c>
       <c r="F54" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G54" s="29"/>
       <c r="H54" s="27"/>
       <c r="I54" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J54" s="27"/>
       <c r="K54" s="35">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L54" s="27"/>
       <c r="M54" s="36" t="s">
@@ -3029,29 +3065,29 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2">
-        <v>44753</v>
+        <v>44700</v>
       </c>
       <c r="C55" s="26">
         <v>44763</v>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="2">
-        <v>44795</v>
+        <v>44760</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G55" s="29"/>
       <c r="H55" s="27"/>
       <c r="I55" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J55" s="27"/>
       <c r="K55" s="30">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="L55" s="27"/>
       <c r="M55" s="31" t="s">
@@ -3064,14 +3100,14 @@
         <v>96</v>
       </c>
       <c r="B56" s="4">
-        <v>44700</v>
+        <v>44753</v>
       </c>
       <c r="C56" s="33">
         <v>44763</v>
       </c>
       <c r="D56" s="27"/>
       <c r="E56" s="4">
-        <v>44760</v>
+        <v>44795</v>
       </c>
       <c r="F56" s="34" t="s">
         <v>97</v>
@@ -3079,11 +3115,11 @@
       <c r="G56" s="29"/>
       <c r="H56" s="27"/>
       <c r="I56" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J56" s="27"/>
       <c r="K56" s="35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L56" s="27"/>
       <c r="M56" s="36" t="s">
@@ -3093,7 +3129,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B57" s="2">
         <v>44753</v>
@@ -3106,12 +3142,12 @@
         <v>44795</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="27"/>
       <c r="I57" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J57" s="27"/>
       <c r="K57" s="30">
@@ -3125,7 +3161,7 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B58" s="4">
         <v>44756</v>
@@ -3135,7 +3171,7 @@
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="4">
-        <v>44816</v>
+        <v>44818</v>
       </c>
       <c r="F58" s="34" t="s">
         <v>106</v>
@@ -3147,7 +3183,7 @@
       </c>
       <c r="J58" s="27"/>
       <c r="K58" s="35">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="L58" s="27"/>
       <c r="M58" s="36" t="s">
@@ -3157,17 +3193,17 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B59" s="2">
-        <v>44755</v>
+        <v>44762</v>
       </c>
       <c r="C59" s="26">
         <v>44764</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="2">
-        <v>44755</v>
+        <v>44837</v>
       </c>
       <c r="F59" s="28" t="s">
         <v>108</v>
@@ -3175,21 +3211,21 @@
       <c r="G59" s="29"/>
       <c r="H59" s="27"/>
       <c r="I59" s="28" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="J59" s="27"/>
       <c r="K59" s="30">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="L59" s="27"/>
       <c r="M59" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N59" s="32"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B60" s="4">
         <v>44762</v>
@@ -3199,7 +3235,7 @@
       </c>
       <c r="D60" s="27"/>
       <c r="E60" s="4">
-        <v>44837</v>
+        <v>44835</v>
       </c>
       <c r="F60" s="34" t="s">
         <v>111</v>
@@ -3207,11 +3243,11 @@
       <c r="G60" s="29"/>
       <c r="H60" s="27"/>
       <c r="I60" s="34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J60" s="27"/>
       <c r="K60" s="35">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="L60" s="27"/>
       <c r="M60" s="36" t="s">
@@ -3221,20 +3257,20 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="B61" s="2">
-        <v>44762</v>
+        <v>44757</v>
       </c>
       <c r="C61" s="26">
         <v>44764</v>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="2">
-        <v>44835</v>
+        <v>44819</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G61" s="29"/>
       <c r="H61" s="27"/>
@@ -3243,27 +3279,27 @@
       </c>
       <c r="J61" s="27"/>
       <c r="K61" s="30">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="L61" s="27"/>
       <c r="M61" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N61" s="32"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="B62" s="4">
-        <v>44756</v>
+        <v>44755</v>
       </c>
       <c r="C62" s="33">
         <v>44764</v>
       </c>
       <c r="D62" s="27"/>
       <c r="E62" s="4">
-        <v>44818</v>
+        <v>44816</v>
       </c>
       <c r="F62" s="34" t="s">
         <v>116</v>
@@ -3271,11 +3307,11 @@
       <c r="G62" s="29"/>
       <c r="H62" s="27"/>
       <c r="I62" s="34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" s="27"/>
       <c r="K62" s="35">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="L62" s="27"/>
       <c r="M62" s="36" t="s">
@@ -3285,17 +3321,17 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B63" s="2">
-        <v>44757</v>
+        <v>44756</v>
       </c>
       <c r="C63" s="26">
         <v>44764</v>
       </c>
       <c r="D63" s="27"/>
       <c r="E63" s="2">
-        <v>44819</v>
+        <v>44816</v>
       </c>
       <c r="F63" s="28" t="s">
         <v>118</v>
@@ -3303,11 +3339,11 @@
       <c r="G63" s="29"/>
       <c r="H63" s="27"/>
       <c r="I63" s="28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J63" s="27"/>
       <c r="K63" s="30">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="L63" s="27"/>
       <c r="M63" s="31" t="s">
@@ -3317,7 +3353,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="B64" s="4">
         <v>44755</v>
@@ -3327,19 +3363,19 @@
       </c>
       <c r="D64" s="27"/>
       <c r="E64" s="4">
-        <v>44816</v>
+        <v>44755</v>
       </c>
       <c r="F64" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G64" s="29"/>
       <c r="H64" s="27"/>
       <c r="I64" s="34" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="J64" s="27"/>
       <c r="K64" s="35">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L64" s="27"/>
       <c r="M64" s="36" t="s">
@@ -3349,7 +3385,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B65" s="2">
         <v>44761</v>
@@ -3367,7 +3403,7 @@
       <c r="G65" s="29"/>
       <c r="H65" s="27"/>
       <c r="I65" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J65" s="27"/>
       <c r="K65" s="30">
@@ -3379,72 +3415,264 @@
       </c>
       <c r="N65" s="32"/>
     </row>
-    <row r="66" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A66" s="24" t="s">
+    <row r="66" spans="1:14">
+      <c r="A66" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="4">
+        <v>44763</v>
+      </c>
+      <c r="C66" s="33">
+        <v>44768</v>
+      </c>
+      <c r="D66" s="27"/>
+      <c r="E66" s="4">
+        <v>44834</v>
+      </c>
+      <c r="F66" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="29"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="27"/>
+      <c r="K66" s="35">
+        <v>78</v>
+      </c>
+      <c r="L66" s="27"/>
+      <c r="M66" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="N66" s="32"/>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="2">
+        <v>44767</v>
+      </c>
+      <c r="C67" s="26">
+        <v>44768</v>
+      </c>
+      <c r="D67" s="27"/>
+      <c r="E67" s="2">
+        <v>44827</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="G67" s="29"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="27"/>
+      <c r="K67" s="30">
+        <v>9</v>
+      </c>
+      <c r="L67" s="27"/>
+      <c r="M67" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="N67" s="32"/>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="4">
+        <v>44764</v>
+      </c>
+      <c r="C68" s="33">
+        <v>44768</v>
+      </c>
+      <c r="D68" s="27"/>
+      <c r="E68" s="4">
+        <v>44761</v>
+      </c>
+      <c r="F68" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G68" s="29"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="27"/>
+      <c r="K68" s="35">
+        <v>52</v>
+      </c>
+      <c r="L68" s="27"/>
+      <c r="M68" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="N68" s="32"/>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="2">
+        <v>44760</v>
+      </c>
+      <c r="C69" s="26">
+        <v>44769</v>
+      </c>
+      <c r="D69" s="27"/>
+      <c r="E69" s="2">
+        <v>44820</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" s="29"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="27"/>
+      <c r="K69" s="30">
+        <v>50</v>
+      </c>
+      <c r="L69" s="27"/>
+      <c r="M69" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="N69" s="32"/>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="4">
+        <v>44760</v>
+      </c>
+      <c r="C70" s="33">
+        <v>44769</v>
+      </c>
+      <c r="D70" s="27"/>
+      <c r="E70" s="4">
+        <v>44822</v>
+      </c>
+      <c r="F70" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G70" s="29"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="27"/>
+      <c r="K70" s="35">
+        <v>48</v>
+      </c>
+      <c r="L70" s="27"/>
+      <c r="M70" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="B66" s="25"/>
-      <c r="C66" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="D66" s="22"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="I66" s="23"/>
-      <c r="J66" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="K66" s="23"/>
-      <c r="L66" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="M66" s="23"/>
-      <c r="N66" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" s="9" customFormat="1">
-      <c r="A67" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="16">
-        <v>4139</v>
-      </c>
-      <c r="D67" s="17"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="7">
-        <v>39</v>
-      </c>
-      <c r="G67" s="7">
+      <c r="N70" s="32"/>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="2">
+        <v>44760</v>
+      </c>
+      <c r="C71" s="26">
+        <v>44769</v>
+      </c>
+      <c r="D71" s="27"/>
+      <c r="E71" s="2">
+        <v>44822</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="G71" s="29"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="27"/>
+      <c r="K71" s="30">
+        <v>736</v>
+      </c>
+      <c r="L71" s="27"/>
+      <c r="M71" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="N71" s="32"/>
+    </row>
+    <row r="72" spans="1:14" ht="30.75" customHeight="1">
+      <c r="A72" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" s="25"/>
+      <c r="C72" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="22"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H72" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="I72" s="23"/>
+      <c r="J72" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="K72" s="23"/>
+      <c r="L72" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="M72" s="23"/>
+      <c r="N72" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" s="9" customFormat="1">
+      <c r="A73" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="20"/>
+      <c r="C73" s="16">
+        <v>5112</v>
+      </c>
+      <c r="D73" s="17"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="7">
+        <v>45</v>
+      </c>
+      <c r="G73" s="7">
         <v>0</v>
       </c>
-      <c r="H67" s="16">
+      <c r="H73" s="16">
         <v>1</v>
       </c>
-      <c r="I67" s="18"/>
-      <c r="J67" s="16">
+      <c r="I73" s="18"/>
+      <c r="J73" s="16">
         <v>21</v>
       </c>
-      <c r="K67" s="18"/>
-      <c r="L67" s="16">
+      <c r="K73" s="18"/>
+      <c r="L73" s="16">
         <v>0</v>
       </c>
-      <c r="M67" s="18"/>
-      <c r="N67" s="8">
+      <c r="M73" s="18"/>
+      <c r="N73" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="327">
+  <mergeCells count="357">
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:J3"/>
@@ -3762,16 +3990,46 @@
     <mergeCell ref="I64:J64"/>
     <mergeCell ref="K64:L64"/>
     <mergeCell ref="M64:N64"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="M69:N69"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15480" windowHeight="9105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14685" windowHeight="7440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="181">
   <si>
     <t/>
   </si>
@@ -89,6 +89,27 @@
     <t>Address</t>
   </si>
   <si>
+    <t>Alameda County</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>Closure Permanent</t>
+  </si>
+  <si>
+    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>Los Angeles County</t>
+  </si>
+  <si>
+    <t>Assembled Financial Technology, LLC</t>
+  </si>
+  <si>
+    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
+  </si>
+  <si>
     <t>San Diego County</t>
   </si>
   <si>
@@ -104,31 +125,19 @@
     <t>Cue Health Inc.</t>
   </si>
   <si>
+    <t>2620 Commerce Way, Suite A/B  Vista CA 92081</t>
+  </si>
+  <si>
     <t>6225 Nancy Ridge Dr.  San Diego CA 92121</t>
   </si>
   <si>
-    <t>2620 Commerce Way, Suite A/B  Vista CA 92081</t>
-  </si>
-  <si>
-    <t>Alameda County</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>Closure Permanent</t>
-  </si>
-  <si>
-    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
-  </si>
-  <si>
-    <t>Los Angeles County</t>
-  </si>
-  <si>
-    <t>Assembled Financial Technology, LLC</t>
-  </si>
-  <si>
-    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
+    <t>PAE Shared Services LLC dba Amentum</t>
+  </si>
+  <si>
+    <t>San Clemente Island  Los Angeles CA 90731</t>
+  </si>
+  <si>
+    <t>NAS North Island  San Diego CA 92135</t>
   </si>
   <si>
     <t>DailyLook, Inc.</t>
@@ -152,9 +161,6 @@
     <t>1 Hacker Way  Menlo Park CA 94025</t>
   </si>
   <si>
-    <t>PAE Shared Services LLC dba Amentum</t>
-  </si>
-  <si>
     <t>Naval Base Point Loma 4045 Hancock St  San Diego CA 92110</t>
   </si>
   <si>
@@ -164,12 +170,6 @@
     <t>3055 Clearview Way  San Mateo CA 94402</t>
   </si>
   <si>
-    <t>NAS North Island  San Diego CA 92135</t>
-  </si>
-  <si>
-    <t>San Clemente Island  Los Angeles CA 90731</t>
-  </si>
-  <si>
     <t>Santa Clara County</t>
   </si>
   <si>
@@ -182,60 +182,60 @@
     <t>47400 Kato Road  Fremotn CA 94538</t>
   </si>
   <si>
+    <t>Kern County</t>
+  </si>
+  <si>
+    <t>JSL Transport, LLC</t>
+  </si>
+  <si>
+    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>PACT Pharma</t>
+  </si>
+  <si>
+    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
     <t>Orange County</t>
   </si>
   <si>
-    <t>JSL Transport, LLC</t>
+    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
+  </si>
+  <si>
+    <t>901 Page Avenue  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>R.A. Phillips Industries, Inc.</t>
+  </si>
+  <si>
+    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>47700 Kato Road  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>10371 Culver Blvd.  Culver City CA 90232</t>
+  </si>
+  <si>
+    <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Sacramento County</t>
+  </si>
+  <si>
+    <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
   </si>
   <si>
     <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
   </si>
   <si>
-    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
-  </si>
-  <si>
-    <t>47700 Kato Road  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>10371 Culver Blvd.  Culver City CA 90232</t>
-  </si>
-  <si>
-    <t>901 Page Avenue  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>R.A. Phillips Industries, Inc.</t>
-  </si>
-  <si>
-    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>Kern County</t>
-  </si>
-  <si>
-    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>PACT Pharma</t>
-  </si>
-  <si>
-    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
-  </si>
-  <si>
-    <t>Sacramento County</t>
-  </si>
-  <si>
-    <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
-  </si>
-  <si>
     <t>14250 Arminta Street  Panorama City CA 91402</t>
   </si>
   <si>
@@ -254,6 +254,9 @@
     <t>First Student</t>
   </si>
   <si>
+    <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
+  </si>
+  <si>
     <t>11233 San Fernando Road  San Fernando CA 91340</t>
   </si>
   <si>
@@ -269,9 +272,6 @@
     <t>42375 Remington Avenue  Temecula CA 92590</t>
   </si>
   <si>
-    <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
-  </si>
-  <si>
     <t>5950 S. St. Andrews Pl.  Los Angeles CA 90047</t>
   </si>
   <si>
@@ -293,21 +293,21 @@
     <t>38 Technology Drive, Suite 100  Irvine CA 92618</t>
   </si>
   <si>
+    <t>San Bernardino County</t>
+  </si>
+  <si>
+    <t>Performance Team</t>
+  </si>
+  <si>
+    <t>14613 Bar Harbor Road  Fontana CA 92336</t>
+  </si>
+  <si>
     <t>Anheuser-Busch, LLC</t>
   </si>
   <si>
     <t>8380 Pardee Drive  Oakland CA 94621</t>
   </si>
   <si>
-    <t>San Bernardino County</t>
-  </si>
-  <si>
-    <t>Performance Team</t>
-  </si>
-  <si>
-    <t>14613 Bar Harbor Road  Fontana CA 92336</t>
-  </si>
-  <si>
     <t>ADP, Inc.</t>
   </si>
   <si>
@@ -365,27 +365,36 @@
     <t>North Bay Health</t>
   </si>
   <si>
+    <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
+  </si>
+  <si>
+    <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
+  </si>
+  <si>
+    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
+  </si>
+  <si>
+    <t>3043 Townsgate Road  Thousand Oaks CA 91361</t>
+  </si>
+  <si>
     <t>4500 Business Center Dr.  Fairfield CA 94534</t>
   </si>
   <si>
-    <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
-  </si>
-  <si>
-    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
-  </si>
-  <si>
-    <t>3043 Townsgate Road  Thousand Oaks CA 91361</t>
-  </si>
-  <si>
-    <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
-  </si>
-  <si>
     <t>Data Aire Inc.</t>
   </si>
   <si>
     <t>230 W. Blueridge Avenue  Orange CA 92865</t>
   </si>
   <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Restoration Hardware Inc.</t>
+  </si>
+  <si>
+    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
+  </si>
+  <si>
     <t>Gardena Honda</t>
   </si>
   <si>
@@ -407,15 +416,6 @@
     <t>1185 Campbell Avenue  San Jose CA 95126</t>
   </si>
   <si>
-    <t>San Joaquin County</t>
-  </si>
-  <si>
-    <t>Restoration Hardware Inc.</t>
-  </si>
-  <si>
-    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
-  </si>
-  <si>
     <t>Urbn Leaf dba Uprooted Inc.</t>
   </si>
   <si>
@@ -437,40 +437,58 @@
     <t>1885 Las Plumas Avenue  San Jose CA 95133</t>
   </si>
   <si>
+    <t>Rise Baking Company dba Brill, Inc.</t>
+  </si>
+  <si>
+    <t>2111 W. Valley Blvd.  Colton CA 92324</t>
+  </si>
+  <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Adventist Health</t>
+  </si>
+  <si>
+    <t>1 Adventist Health Way  Roseville CA 95661</t>
+  </si>
+  <si>
     <t>Schneider Electric</t>
   </si>
   <si>
     <t>1660 Scenic Avenue  Costa Mesa CA 92626</t>
   </si>
   <si>
-    <t>Placer County</t>
-  </si>
-  <si>
-    <t>Adventist Health</t>
-  </si>
-  <si>
-    <t>1 Adventist Health Way  Roseville CA 95661</t>
-  </si>
-  <si>
-    <t>Rise Baking Company dba Brill, Inc.</t>
-  </si>
-  <si>
-    <t>2111 W. Valley Blvd.  Colton CA 92324</t>
+    <t>Imperfect Foods, Inc.</t>
+  </si>
+  <si>
+    <t>1616 Donner Ave  San Francisco CA 94124</t>
   </si>
   <si>
     <t>Invitae Corporation</t>
   </si>
   <si>
+    <t>5 Technology Drive  Irvine CA 92618</t>
+  </si>
+  <si>
     <t>1400 16th Street  San Francisco CA 94103</t>
   </si>
   <si>
-    <t>5 Technology Drive  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>Imperfect Foods, Inc.</t>
-  </si>
-  <si>
-    <t>1616 Donner Ave  San Francisco CA 94124</t>
+    <t>RingCentral, Inc.</t>
+  </si>
+  <si>
+    <t>20 Davis Drive  Belmont CA 94002</t>
+  </si>
+  <si>
+    <t>Owens Corning</t>
+  </si>
+  <si>
+    <t>960 Central Expy  Santa Clara CA 95050</t>
+  </si>
+  <si>
+    <t>Zymergen Inc.</t>
+  </si>
+  <si>
+    <t>5980 Horton Street, Suite 105  Emeryville CA 94608</t>
   </si>
   <si>
     <t>Inland SoCal United Way</t>
@@ -479,24 +497,6 @@
     <t>1835 Chicago Avenue B  Riverside CA 92507</t>
   </si>
   <si>
-    <t>RingCentral, Inc.</t>
-  </si>
-  <si>
-    <t>20 Davis Drive  Belmont CA 94002</t>
-  </si>
-  <si>
-    <t>Owens Corning</t>
-  </si>
-  <si>
-    <t>960 Central Expy  Santa Clara CA 95050</t>
-  </si>
-  <si>
-    <t>Zymergen Inc.</t>
-  </si>
-  <si>
-    <t>5980 Horton Street, Suite 105  Emeryville CA 94608</t>
-  </si>
-  <si>
     <t>Alza Corporation</t>
   </si>
   <si>
@@ -515,6 +515,63 @@
     <t>3400 Bridge Parkway  Redwood City CA 94065</t>
   </si>
   <si>
+    <t>Brinker International Payroll Company, L.P.</t>
+  </si>
+  <si>
+    <t>189 The Grove Dr.  Los Angeles CA 90036</t>
+  </si>
+  <si>
+    <t>Tulare County</t>
+  </si>
+  <si>
+    <t>Plaza Palace, Inc. dba Palace Food Depot</t>
+  </si>
+  <si>
+    <t>d:115 S. West Street  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>Robinhood Markets, Inc.</t>
+  </si>
+  <si>
+    <t>85 Willow Road  Menlo Park CA 94025</t>
+  </si>
+  <si>
+    <t>Rivian Automotive, LLC</t>
+  </si>
+  <si>
+    <t>9750 Irvine Boulevard  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>14192 Franklin Avenue  Tustin CA 92780</t>
+  </si>
+  <si>
+    <t>1751 Kettering Street  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>119 Waterworks Way  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>The Lafayette Hotel, Swim Club &amp; Bungalows</t>
+  </si>
+  <si>
+    <t>Layoff Temporary</t>
+  </si>
+  <si>
+    <t>2223 El Cajon Blvd  San Diego CA 92104</t>
+  </si>
+  <si>
+    <t>630 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>607 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>14600 Myford Road  Irvine CA 92606</t>
+  </si>
+  <si>
+    <t>850 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -537,18 +594,17 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>WARN Summary</t>
+  </si>
+  <si>
+    <t>Report Summary</t>
   </si>
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 8/3/2022
-</t>
-  </si>
-  <si>
-    <t>WARN Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report Summary </t>
+ End Date: 8/8/2022</t>
   </si>
 </sst>
 </file>
@@ -616,6 +672,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFDCDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFDCDCDC"/>
       </patternFill>
@@ -623,18 +691,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFDCDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -976,6 +1032,18 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -983,22 +1051,10 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1016,19 +1072,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1064,34 +1120,34 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1380,26 +1436,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="2.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" customWidth="1"/>
-    <col min="11" max="11" width="5.140625" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" customWidth="1"/>
-    <col min="13" max="13" width="5.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="3" max="3" width="2.140625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.28515625" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="48" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -1419,9 +1473,9 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="38.25" customHeight="1">
+    <row r="2" spans="1:18" ht="39" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -1442,17 +1496,17 @@
       <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="42" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="43"/>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="42" t="s">
@@ -1474,17 +1528,17 @@
       <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:18" ht="24.75">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="37" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="38"/>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="37" t="s">
@@ -1510,14 +1564,14 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>44735</v>
+        <v>44727</v>
       </c>
       <c r="C5" s="26">
         <v>44750</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="2">
-        <v>44796</v>
+        <v>44897</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>10</v>
@@ -1529,7 +1583,7 @@
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="30">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="L5" s="27"/>
       <c r="M5" s="31" t="s">
@@ -1539,20 +1593,20 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="C6" s="33">
         <v>44750</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="4">
-        <v>44796</v>
+        <v>44794</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="29"/>
       <c r="H6" s="27"/>
@@ -1561,17 +1615,17 @@
       </c>
       <c r="J6" s="27"/>
       <c r="K6" s="35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L6" s="27"/>
       <c r="M6" s="36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>44735</v>
@@ -1584,20 +1638,20 @@
         <v>44796</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J7" s="27"/>
       <c r="K7" s="30">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="L7" s="27"/>
       <c r="M7" s="31" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N7" s="32"/>
     </row>
@@ -1606,17 +1660,17 @@
         <v>16</v>
       </c>
       <c r="B8" s="4">
-        <v>44727</v>
+        <v>44735</v>
       </c>
       <c r="C8" s="33">
         <v>44750</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="4">
-        <v>44897</v>
+        <v>44796</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="27"/>
@@ -1625,30 +1679,30 @@
       </c>
       <c r="J8" s="27"/>
       <c r="K8" s="35">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="36" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N8" s="32"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
-        <v>44736</v>
+        <v>44735</v>
       </c>
       <c r="C9" s="26">
         <v>44750</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="2">
-        <v>44794</v>
+        <v>44796</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="27"/>
@@ -1657,7 +1711,7 @@
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="30">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L9" s="27"/>
       <c r="M9" s="31" t="s">
@@ -1667,17 +1721,17 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>44739</v>
+        <v>44727</v>
       </c>
       <c r="C10" s="33">
         <v>44753</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="4">
-        <v>44799</v>
+        <v>44784</v>
       </c>
       <c r="F10" s="34" t="s">
         <v>23</v>
@@ -1685,11 +1739,11 @@
       <c r="G10" s="29"/>
       <c r="H10" s="27"/>
       <c r="I10" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J10" s="27"/>
       <c r="K10" s="35">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="36" t="s">
@@ -1699,116 +1753,116 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>44741</v>
+        <v>44727</v>
       </c>
       <c r="C11" s="26">
         <v>44753</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="2">
-        <v>44801</v>
+        <v>44784</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="27"/>
       <c r="I11" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J11" s="27"/>
       <c r="K11" s="30">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L11" s="27"/>
       <c r="M11" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C12" s="33">
         <v>44753</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="4">
-        <v>44766</v>
+        <v>44799</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12" s="29"/>
       <c r="H12" s="27"/>
       <c r="I12" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J12" s="27"/>
       <c r="K12" s="35">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="L12" s="27"/>
       <c r="M12" s="36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N12" s="32"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>44727</v>
+        <v>44741</v>
       </c>
       <c r="C13" s="26">
         <v>44753</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="2">
-        <v>44784</v>
+        <v>44801</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G13" s="29"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J13" s="27"/>
       <c r="K13" s="30">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L13" s="27"/>
       <c r="M13" s="31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4">
-        <v>44741</v>
+        <v>44743</v>
       </c>
       <c r="C14" s="33">
         <v>44753</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="4">
-        <v>44800</v>
+        <v>44766</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" s="29"/>
       <c r="H14" s="27"/>
@@ -1817,17 +1871,17 @@
       </c>
       <c r="J14" s="27"/>
       <c r="K14" s="35">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="L14" s="27"/>
       <c r="M14" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="32"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
         <v>44727</v>
@@ -1840,39 +1894,39 @@
         <v>44784</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="27"/>
       <c r="I15" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J15" s="27"/>
       <c r="K15" s="30">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="L15" s="27"/>
       <c r="M15" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N15" s="32"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4">
-        <v>44727</v>
+        <v>44741</v>
       </c>
       <c r="C16" s="33">
         <v>44753</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="4">
-        <v>44784</v>
+        <v>44800</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G16" s="29"/>
       <c r="H16" s="27"/>
@@ -1881,7 +1935,7 @@
       </c>
       <c r="J16" s="27"/>
       <c r="K16" s="35">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="L16" s="27"/>
       <c r="M16" s="36" t="s">
@@ -1909,7 +1963,7 @@
       <c r="G17" s="29"/>
       <c r="H17" s="27"/>
       <c r="I17" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J17" s="27"/>
       <c r="K17" s="30">
@@ -1923,7 +1977,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4">
         <v>44739</v>
@@ -1936,12 +1990,12 @@
         <v>44800</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G18" s="29"/>
       <c r="H18" s="27"/>
       <c r="I18" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J18" s="27"/>
       <c r="K18" s="35">
@@ -1973,11 +2027,11 @@
       <c r="G19" s="29"/>
       <c r="H19" s="27"/>
       <c r="I19" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J19" s="27"/>
       <c r="K19" s="30">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L19" s="27"/>
       <c r="M19" s="31" t="s">
@@ -1987,52 +2041,52 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B20" s="4">
-        <v>44739</v>
+        <v>44742</v>
       </c>
       <c r="C20" s="33">
         <v>44754</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="4">
-        <v>44800</v>
+        <v>44802</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G20" s="29"/>
       <c r="H20" s="27"/>
       <c r="I20" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J20" s="27"/>
       <c r="K20" s="35">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="L20" s="27"/>
       <c r="M20" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N20" s="32"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C21" s="26">
         <v>44754</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="2">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" s="29"/>
       <c r="H21" s="27"/>
@@ -2041,17 +2095,17 @@
       </c>
       <c r="J21" s="27"/>
       <c r="K21" s="30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L21" s="27"/>
       <c r="M21" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N21" s="32"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B22" s="4">
         <v>44739</v>
@@ -2064,26 +2118,26 @@
         <v>44800</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" s="29"/>
       <c r="H22" s="27"/>
       <c r="I22" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J22" s="27"/>
       <c r="K22" s="35">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="L22" s="27"/>
       <c r="M22" s="36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N22" s="32"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2">
         <v>44743</v>
@@ -2101,21 +2155,21 @@
       <c r="G23" s="29"/>
       <c r="H23" s="27"/>
       <c r="I23" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J23" s="27"/>
       <c r="K23" s="30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L23" s="27"/>
       <c r="M23" s="31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N23" s="32"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B24" s="4">
         <v>44739</v>
@@ -2128,12 +2182,12 @@
         <v>44800</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" s="29"/>
       <c r="H24" s="27"/>
       <c r="I24" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J24" s="27"/>
       <c r="K24" s="35">
@@ -2141,13 +2195,13 @@
       </c>
       <c r="L24" s="27"/>
       <c r="M24" s="36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N24" s="32"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2">
         <v>44732</v>
@@ -2160,12 +2214,12 @@
         <v>44926</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" s="29"/>
       <c r="H25" s="27"/>
       <c r="I25" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J25" s="27"/>
       <c r="K25" s="30">
@@ -2173,13 +2227,13 @@
       </c>
       <c r="L25" s="27"/>
       <c r="M25" s="31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B26" s="4">
         <v>44739</v>
@@ -2192,26 +2246,26 @@
         <v>44800</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="29"/>
       <c r="H26" s="27"/>
       <c r="I26" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L26" s="27"/>
       <c r="M26" s="36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N26" s="32"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B27" s="2">
         <v>44743</v>
@@ -2229,34 +2283,34 @@
       <c r="G27" s="29"/>
       <c r="H27" s="27"/>
       <c r="I27" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J27" s="27"/>
       <c r="K27" s="30">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L27" s="27"/>
       <c r="M27" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N27" s="32"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B28" s="4">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="C28" s="33">
         <v>44754</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="4">
-        <v>44802</v>
+        <v>44804</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G28" s="29"/>
       <c r="H28" s="27"/>
@@ -2265,7 +2319,7 @@
       </c>
       <c r="J28" s="27"/>
       <c r="K28" s="35">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="L28" s="27"/>
       <c r="M28" s="36" t="s">
@@ -2275,7 +2329,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2">
         <v>44743</v>
@@ -2293,21 +2347,21 @@
       <c r="G29" s="29"/>
       <c r="H29" s="27"/>
       <c r="I29" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J29" s="27"/>
       <c r="K29" s="30">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L29" s="27"/>
       <c r="M29" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B30" s="4">
         <v>44743</v>
@@ -2325,11 +2379,11 @@
       <c r="G30" s="29"/>
       <c r="H30" s="27"/>
       <c r="I30" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J30" s="27"/>
       <c r="K30" s="35">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L30" s="27"/>
       <c r="M30" s="36" t="s">
@@ -2339,7 +2393,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2">
         <v>44743</v>
@@ -2357,7 +2411,7 @@
       <c r="G31" s="29"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="30">
@@ -2371,7 +2425,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B32" s="4">
         <v>44743</v>
@@ -2389,7 +2443,7 @@
       <c r="G32" s="29"/>
       <c r="H32" s="27"/>
       <c r="I32" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="35">
@@ -2403,7 +2457,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2">
         <v>44743</v>
@@ -2421,7 +2475,7 @@
       <c r="G33" s="29"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="30">
@@ -2453,7 +2507,7 @@
       <c r="G34" s="29"/>
       <c r="H34" s="27"/>
       <c r="I34" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="35">
@@ -2467,7 +2521,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2">
         <v>44743</v>
@@ -2485,11 +2539,11 @@
       <c r="G35" s="29"/>
       <c r="H35" s="27"/>
       <c r="I35" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="30">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="L35" s="27"/>
       <c r="M35" s="31" t="s">
@@ -2499,17 +2553,17 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B36" s="4">
-        <v>44747</v>
+        <v>44743</v>
       </c>
       <c r="C36" s="33">
         <v>44756</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="4">
-        <v>44788</v>
+        <v>44799</v>
       </c>
       <c r="F36" s="34" t="s">
         <v>63</v>
@@ -2517,11 +2571,11 @@
       <c r="G36" s="29"/>
       <c r="H36" s="27"/>
       <c r="I36" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="35">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L36" s="27"/>
       <c r="M36" s="36" t="s">
@@ -2531,61 +2585,61 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
-        <v>44753</v>
+        <v>44747</v>
       </c>
       <c r="C37" s="26">
         <v>44756</v>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="2">
-        <v>44813</v>
+        <v>44788</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G37" s="29"/>
       <c r="H37" s="27"/>
       <c r="I37" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J37" s="27"/>
       <c r="K37" s="30">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L37" s="27"/>
       <c r="M37" s="31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N37" s="32"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B38" s="4">
-        <v>44743</v>
+        <v>44753</v>
       </c>
       <c r="C38" s="33">
         <v>44756</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="4">
-        <v>44799</v>
+        <v>44813</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G38" s="29"/>
       <c r="H38" s="27"/>
       <c r="I38" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J38" s="27"/>
       <c r="K38" s="35">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="L38" s="27"/>
       <c r="M38" s="36" t="s">
@@ -2595,7 +2649,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2">
         <v>44743</v>
@@ -2613,7 +2667,7 @@
       <c r="G39" s="29"/>
       <c r="H39" s="27"/>
       <c r="I39" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J39" s="27"/>
       <c r="K39" s="30">
@@ -2645,7 +2699,7 @@
       <c r="G40" s="29"/>
       <c r="H40" s="27"/>
       <c r="I40" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J40" s="27"/>
       <c r="K40" s="35">
@@ -2659,7 +2713,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="2">
         <v>44749</v>
@@ -2677,7 +2731,7 @@
       <c r="G41" s="29"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J41" s="27"/>
       <c r="K41" s="30">
@@ -2691,7 +2745,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B42" s="4">
         <v>44749</v>
@@ -2709,7 +2763,7 @@
       <c r="G42" s="29"/>
       <c r="H42" s="27"/>
       <c r="I42" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J42" s="27"/>
       <c r="K42" s="35">
@@ -2723,49 +2777,49 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>44749</v>
+        <v>44753</v>
       </c>
       <c r="C43" s="26">
         <v>44760</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="2">
-        <v>44813</v>
+        <v>44804</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43" s="29"/>
       <c r="H43" s="27"/>
       <c r="I43" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J43" s="27"/>
       <c r="K43" s="30">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L43" s="27"/>
       <c r="M43" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N43" s="32"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="B44" s="4">
-        <v>44753</v>
+        <v>44749</v>
       </c>
       <c r="C44" s="33">
         <v>44760</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="4">
-        <v>44804</v>
+        <v>44813</v>
       </c>
       <c r="F44" s="34" t="s">
         <v>80</v>
@@ -2773,11 +2827,11 @@
       <c r="G44" s="29"/>
       <c r="H44" s="27"/>
       <c r="I44" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J44" s="27"/>
       <c r="K44" s="35">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="L44" s="27"/>
       <c r="M44" s="36" t="s">
@@ -2787,7 +2841,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2">
         <v>44754</v>
@@ -2805,7 +2859,7 @@
       <c r="G45" s="29"/>
       <c r="H45" s="27"/>
       <c r="I45" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J45" s="27"/>
       <c r="K45" s="30">
@@ -2819,7 +2873,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B46" s="4">
         <v>44755</v>
@@ -2837,7 +2891,7 @@
       <c r="G46" s="29"/>
       <c r="H46" s="27"/>
       <c r="I46" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J46" s="27"/>
       <c r="K46" s="35">
@@ -2851,7 +2905,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2">
         <v>44749</v>
@@ -2869,7 +2923,7 @@
       <c r="G47" s="29"/>
       <c r="H47" s="27"/>
       <c r="I47" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J47" s="27"/>
       <c r="K47" s="30">
@@ -2883,7 +2937,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B48" s="4">
         <v>44749</v>
@@ -2901,7 +2955,7 @@
       <c r="G48" s="29"/>
       <c r="H48" s="27"/>
       <c r="I48" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J48" s="27"/>
       <c r="K48" s="35">
@@ -2915,7 +2969,7 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2">
         <v>44754</v>
@@ -2933,7 +2987,7 @@
       <c r="G49" s="29"/>
       <c r="H49" s="27"/>
       <c r="I49" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J49" s="27"/>
       <c r="K49" s="30">
@@ -2947,7 +3001,7 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B50" s="4">
         <v>44692</v>
@@ -2965,7 +3019,7 @@
       <c r="G50" s="29"/>
       <c r="H50" s="27"/>
       <c r="I50" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J50" s="27"/>
       <c r="K50" s="35">
@@ -2997,7 +3051,7 @@
       <c r="G51" s="29"/>
       <c r="H51" s="27"/>
       <c r="I51" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J51" s="27"/>
       <c r="K51" s="30">
@@ -3029,7 +3083,7 @@
       <c r="G52" s="29"/>
       <c r="H52" s="27"/>
       <c r="I52" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J52" s="27"/>
       <c r="K52" s="35">
@@ -3061,11 +3115,11 @@
       <c r="G53" s="29"/>
       <c r="H53" s="27"/>
       <c r="I53" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J53" s="27"/>
       <c r="K53" s="30">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L53" s="27"/>
       <c r="M53" s="31" t="s">
@@ -3093,7 +3147,7 @@
       <c r="G54" s="29"/>
       <c r="H54" s="27"/>
       <c r="I54" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J54" s="27"/>
       <c r="K54" s="35">
@@ -3125,7 +3179,7 @@
       <c r="G55" s="29"/>
       <c r="H55" s="27"/>
       <c r="I55" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J55" s="27"/>
       <c r="K55" s="30">
@@ -3157,7 +3211,7 @@
       <c r="G56" s="29"/>
       <c r="H56" s="27"/>
       <c r="I56" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J56" s="27"/>
       <c r="K56" s="35">
@@ -3189,11 +3243,11 @@
       <c r="G57" s="29"/>
       <c r="H57" s="27"/>
       <c r="I57" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J57" s="27"/>
       <c r="K57" s="30">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L57" s="27"/>
       <c r="M57" s="31" t="s">
@@ -3203,7 +3257,7 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B58" s="4">
         <v>44762</v>
@@ -3221,7 +3275,7 @@
       <c r="G58" s="29"/>
       <c r="H58" s="27"/>
       <c r="I58" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J58" s="27"/>
       <c r="K58" s="35">
@@ -3235,20 +3289,20 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="B59" s="2">
-        <v>44757</v>
+        <v>44762</v>
       </c>
       <c r="C59" s="26">
         <v>44764</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="2">
-        <v>44819</v>
+        <v>44835</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G59" s="29"/>
       <c r="H59" s="27"/>
@@ -3257,27 +3311,27 @@
       </c>
       <c r="J59" s="27"/>
       <c r="K59" s="30">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="L59" s="27"/>
       <c r="M59" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N59" s="32"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="B60" s="4">
-        <v>44755</v>
+        <v>44757</v>
       </c>
       <c r="C60" s="33">
         <v>44764</v>
       </c>
       <c r="D60" s="27"/>
       <c r="E60" s="4">
-        <v>44816</v>
+        <v>44819</v>
       </c>
       <c r="F60" s="34" t="s">
         <v>111</v>
@@ -3289,7 +3343,7 @@
       </c>
       <c r="J60" s="27"/>
       <c r="K60" s="35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L60" s="27"/>
       <c r="M60" s="36" t="s">
@@ -3299,20 +3353,20 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2">
-        <v>44756</v>
+        <v>44755</v>
       </c>
       <c r="C61" s="26">
         <v>44764</v>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="2">
-        <v>44818</v>
+        <v>44816</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G61" s="29"/>
       <c r="H61" s="27"/>
@@ -3321,27 +3375,27 @@
       </c>
       <c r="J61" s="27"/>
       <c r="K61" s="30">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="L61" s="27"/>
       <c r="M61" s="31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N61" s="32"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="B62" s="4">
-        <v>44762</v>
+        <v>44756</v>
       </c>
       <c r="C62" s="33">
         <v>44764</v>
       </c>
       <c r="D62" s="27"/>
       <c r="E62" s="4">
-        <v>44835</v>
+        <v>44818</v>
       </c>
       <c r="F62" s="34" t="s">
         <v>116</v>
@@ -3353,7 +3407,7 @@
       </c>
       <c r="J62" s="27"/>
       <c r="K62" s="35">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="L62" s="27"/>
       <c r="M62" s="36" t="s">
@@ -3363,7 +3417,7 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B63" s="2">
         <v>44756</v>
@@ -3381,7 +3435,7 @@
       <c r="G63" s="29"/>
       <c r="H63" s="27"/>
       <c r="I63" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J63" s="27"/>
       <c r="K63" s="30">
@@ -3395,7 +3449,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B64" s="4">
         <v>44755</v>
@@ -3445,7 +3499,7 @@
       <c r="G65" s="29"/>
       <c r="H65" s="27"/>
       <c r="I65" s="28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J65" s="27"/>
       <c r="K65" s="30">
@@ -3459,17 +3513,17 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B66" s="4">
-        <v>44767</v>
+        <v>44763</v>
       </c>
       <c r="C66" s="33">
         <v>44768</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="4">
-        <v>44827</v>
+        <v>44834</v>
       </c>
       <c r="F66" s="34" t="s">
         <v>125</v>
@@ -3477,11 +3531,11 @@
       <c r="G66" s="29"/>
       <c r="H66" s="27"/>
       <c r="I66" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J66" s="27"/>
       <c r="K66" s="35">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="L66" s="27"/>
       <c r="M66" s="36" t="s">
@@ -3509,7 +3563,7 @@
       <c r="G67" s="29"/>
       <c r="H67" s="27"/>
       <c r="I67" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J67" s="27"/>
       <c r="K67" s="30">
@@ -3523,17 +3577,17 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="B68" s="4">
-        <v>44763</v>
+        <v>44767</v>
       </c>
       <c r="C68" s="33">
         <v>44768</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="4">
-        <v>44834</v>
+        <v>44827</v>
       </c>
       <c r="F68" s="34" t="s">
         <v>130</v>
@@ -3541,11 +3595,11 @@
       <c r="G68" s="29"/>
       <c r="H68" s="27"/>
       <c r="I68" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J68" s="27"/>
       <c r="K68" s="35">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="L68" s="27"/>
       <c r="M68" s="36" t="s">
@@ -3555,7 +3609,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B69" s="2">
         <v>44760</v>
@@ -3565,7 +3619,7 @@
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="2">
-        <v>44822</v>
+        <v>44820</v>
       </c>
       <c r="F69" s="28" t="s">
         <v>132</v>
@@ -3573,11 +3627,11 @@
       <c r="G69" s="29"/>
       <c r="H69" s="27"/>
       <c r="I69" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J69" s="27"/>
       <c r="K69" s="30">
-        <v>736</v>
+        <v>50</v>
       </c>
       <c r="L69" s="27"/>
       <c r="M69" s="31" t="s">
@@ -3587,7 +3641,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B70" s="4">
         <v>44760</v>
@@ -3600,12 +3654,12 @@
         <v>44822</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G70" s="29"/>
       <c r="H70" s="27"/>
       <c r="I70" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J70" s="27"/>
       <c r="K70" s="35">
@@ -3613,13 +3667,13 @@
       </c>
       <c r="L70" s="27"/>
       <c r="M70" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N70" s="32"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B71" s="2">
         <v>44760</v>
@@ -3629,19 +3683,19 @@
       </c>
       <c r="D71" s="27"/>
       <c r="E71" s="2">
-        <v>44820</v>
+        <v>44822</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G71" s="29"/>
       <c r="H71" s="27"/>
       <c r="I71" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J71" s="27"/>
       <c r="K71" s="30">
-        <v>50</v>
+        <v>736</v>
       </c>
       <c r="L71" s="27"/>
       <c r="M71" s="31" t="s">
@@ -3651,17 +3705,17 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="B72" s="4">
-        <v>44769</v>
+        <v>44762</v>
       </c>
       <c r="C72" s="33">
         <v>44770</v>
       </c>
       <c r="D72" s="27"/>
       <c r="E72" s="4">
-        <v>44837</v>
+        <v>44822</v>
       </c>
       <c r="F72" s="34" t="s">
         <v>137</v>
@@ -3669,11 +3723,11 @@
       <c r="G72" s="29"/>
       <c r="H72" s="27"/>
       <c r="I72" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J72" s="27"/>
       <c r="K72" s="35">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="L72" s="27"/>
       <c r="M72" s="36" t="s">
@@ -3683,7 +3737,7 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B73" s="2">
         <v>44762</v>
@@ -3696,12 +3750,12 @@
         <v>44829</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G73" s="29"/>
       <c r="H73" s="27"/>
       <c r="I73" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J73" s="27"/>
       <c r="K73" s="30">
@@ -3709,7 +3763,7 @@
       </c>
       <c r="L73" s="27"/>
       <c r="M73" s="31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N73" s="32"/>
     </row>
@@ -3728,12 +3782,12 @@
         <v>44865</v>
       </c>
       <c r="F74" s="34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G74" s="29"/>
       <c r="H74" s="27"/>
       <c r="I74" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J74" s="27"/>
       <c r="K74" s="35">
@@ -3741,55 +3795,55 @@
       </c>
       <c r="L74" s="27"/>
       <c r="M74" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N74" s="32"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B75" s="2">
-        <v>44762</v>
+        <v>44768</v>
       </c>
       <c r="C75" s="26">
         <v>44770</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="2">
-        <v>44822</v>
+        <v>44830</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G75" s="29"/>
       <c r="H75" s="27"/>
       <c r="I75" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J75" s="27"/>
       <c r="K75" s="30">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="L75" s="27"/>
       <c r="M75" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N75" s="32"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B76" s="4">
-        <v>44768</v>
+        <v>44769</v>
       </c>
       <c r="C76" s="33">
         <v>44770</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="4">
-        <v>44830</v>
+        <v>44837</v>
       </c>
       <c r="F76" s="34" t="s">
         <v>143</v>
@@ -3797,11 +3851,11 @@
       <c r="G76" s="29"/>
       <c r="H76" s="27"/>
       <c r="I76" s="34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J76" s="27"/>
       <c r="K76" s="35">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="L76" s="27"/>
       <c r="M76" s="36" t="s">
@@ -3829,7 +3883,7 @@
       <c r="G77" s="29"/>
       <c r="H77" s="27"/>
       <c r="I77" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J77" s="27"/>
       <c r="K77" s="30">
@@ -3843,7 +3897,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B78" s="4">
         <v>44774</v>
@@ -3861,7 +3915,7 @@
       <c r="G78" s="29"/>
       <c r="H78" s="27"/>
       <c r="I78" s="34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J78" s="27"/>
       <c r="K78" s="35">
@@ -3875,7 +3929,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B79" s="2">
         <v>44774</v>
@@ -3893,7 +3947,7 @@
       <c r="G79" s="29"/>
       <c r="H79" s="27"/>
       <c r="I79" s="28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J79" s="27"/>
       <c r="K79" s="30">
@@ -3905,72 +3959,456 @@
       </c>
       <c r="N79" s="32"/>
     </row>
-    <row r="80" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A80" s="24" t="s">
+    <row r="80" spans="1:14">
+      <c r="A80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="4">
+        <v>44767</v>
+      </c>
+      <c r="C80" s="33">
+        <v>44778</v>
+      </c>
+      <c r="D80" s="27"/>
+      <c r="E80" s="4">
+        <v>44834</v>
+      </c>
+      <c r="F80" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G80" s="29"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="J80" s="27"/>
+      <c r="K80" s="35">
+        <v>133</v>
+      </c>
+      <c r="L80" s="27"/>
+      <c r="M80" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="N80" s="32"/>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="2">
+        <v>44770</v>
+      </c>
+      <c r="C81" s="26">
+        <v>44778</v>
+      </c>
+      <c r="D81" s="27"/>
+      <c r="E81" s="2">
+        <v>44835</v>
+      </c>
+      <c r="F81" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="G81" s="29"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J81" s="27"/>
+      <c r="K81" s="30">
+        <v>68</v>
+      </c>
+      <c r="L81" s="27"/>
+      <c r="M81" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="N81" s="32"/>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="4">
+        <v>44775</v>
+      </c>
+      <c r="C82" s="33">
+        <v>44778</v>
+      </c>
+      <c r="D82" s="27"/>
+      <c r="E82" s="4">
+        <v>44835</v>
+      </c>
+      <c r="F82" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="G82" s="29"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="27"/>
+      <c r="K82" s="35">
+        <v>146</v>
+      </c>
+      <c r="L82" s="27"/>
+      <c r="M82" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="N82" s="32"/>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B83" s="2">
+        <v>44769</v>
+      </c>
+      <c r="C83" s="26">
+        <v>44781</v>
+      </c>
+      <c r="D83" s="27"/>
+      <c r="E83" s="2">
+        <v>44841</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G83" s="29"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="27"/>
+      <c r="K83" s="30">
+        <v>2</v>
+      </c>
+      <c r="L83" s="27"/>
+      <c r="M83" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="N83" s="32"/>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B84" s="4">
+        <v>44769</v>
+      </c>
+      <c r="C84" s="33">
+        <v>44781</v>
+      </c>
+      <c r="D84" s="27"/>
+      <c r="E84" s="4">
+        <v>44841</v>
+      </c>
+      <c r="F84" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G84" s="29"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="27"/>
+      <c r="K84" s="35">
+        <v>21</v>
+      </c>
+      <c r="L84" s="27"/>
+      <c r="M84" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="N84" s="32"/>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B85" s="2">
+        <v>44769</v>
+      </c>
+      <c r="C85" s="26">
+        <v>44781</v>
+      </c>
+      <c r="D85" s="27"/>
+      <c r="E85" s="2">
+        <v>44841</v>
+      </c>
+      <c r="F85" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G85" s="29"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="27"/>
+      <c r="K85" s="30">
+        <v>9</v>
+      </c>
+      <c r="L85" s="27"/>
+      <c r="M85" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="D80" s="22"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="I80" s="23"/>
-      <c r="J80" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="K80" s="23"/>
-      <c r="L80" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="M80" s="23"/>
-      <c r="N80" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" s="9" customFormat="1">
-      <c r="A81" s="19" t="s">
+      <c r="N85" s="32"/>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="4">
+        <v>44769</v>
+      </c>
+      <c r="C86" s="33">
+        <v>44781</v>
+      </c>
+      <c r="D86" s="27"/>
+      <c r="E86" s="4">
+        <v>44841</v>
+      </c>
+      <c r="F86" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="B81" s="20"/>
-      <c r="C81" s="16">
-        <v>5764</v>
-      </c>
-      <c r="D81" s="17"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="7">
-        <v>51</v>
-      </c>
-      <c r="G81" s="7">
+      <c r="G86" s="29"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="27"/>
+      <c r="K86" s="35">
+        <v>25</v>
+      </c>
+      <c r="L86" s="27"/>
+      <c r="M86" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="N86" s="32"/>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" s="2">
+        <v>44774</v>
+      </c>
+      <c r="C87" s="26">
+        <v>44781</v>
+      </c>
+      <c r="D87" s="27"/>
+      <c r="E87" s="2">
+        <v>44836</v>
+      </c>
+      <c r="F87" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="G87" s="29"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J87" s="27"/>
+      <c r="K87" s="30">
+        <v>73</v>
+      </c>
+      <c r="L87" s="27"/>
+      <c r="M87" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="N87" s="32"/>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B88" s="4">
+        <v>44769</v>
+      </c>
+      <c r="C88" s="33">
+        <v>44781</v>
+      </c>
+      <c r="D88" s="27"/>
+      <c r="E88" s="4">
+        <v>44841</v>
+      </c>
+      <c r="F88" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G88" s="29"/>
+      <c r="H88" s="27"/>
+      <c r="I88" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="27"/>
+      <c r="K88" s="35">
+        <v>77</v>
+      </c>
+      <c r="L88" s="27"/>
+      <c r="M88" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="N88" s="32"/>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" s="2">
+        <v>44769</v>
+      </c>
+      <c r="C89" s="26">
+        <v>44781</v>
+      </c>
+      <c r="D89" s="27"/>
+      <c r="E89" s="2">
+        <v>44841</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G89" s="29"/>
+      <c r="H89" s="27"/>
+      <c r="I89" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="27"/>
+      <c r="K89" s="30">
+        <v>111</v>
+      </c>
+      <c r="L89" s="27"/>
+      <c r="M89" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="N89" s="32"/>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B90" s="4">
+        <v>44769</v>
+      </c>
+      <c r="C90" s="33">
+        <v>44781</v>
+      </c>
+      <c r="D90" s="27"/>
+      <c r="E90" s="4">
+        <v>44841</v>
+      </c>
+      <c r="F90" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G90" s="29"/>
+      <c r="H90" s="27"/>
+      <c r="I90" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="27"/>
+      <c r="K90" s="35">
+        <v>86</v>
+      </c>
+      <c r="L90" s="27"/>
+      <c r="M90" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="N90" s="32"/>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="2">
+        <v>44769</v>
+      </c>
+      <c r="C91" s="26">
+        <v>44781</v>
+      </c>
+      <c r="D91" s="27"/>
+      <c r="E91" s="2">
+        <v>44841</v>
+      </c>
+      <c r="F91" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G91" s="29"/>
+      <c r="H91" s="27"/>
+      <c r="I91" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="27"/>
+      <c r="K91" s="30">
+        <v>20</v>
+      </c>
+      <c r="L91" s="27"/>
+      <c r="M91" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="N91" s="32"/>
+    </row>
+    <row r="92" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A92" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" s="25"/>
+      <c r="C92" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D92" s="22"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I92" s="23"/>
+      <c r="J92" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="K92" s="23"/>
+      <c r="L92" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="M92" s="23"/>
+      <c r="N92" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="13" customFormat="1">
+      <c r="A93" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="20"/>
+      <c r="C93" s="16">
+        <v>6535</v>
+      </c>
+      <c r="D93" s="17"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="11">
+        <v>60</v>
+      </c>
+      <c r="G93" s="11">
+        <v>1</v>
+      </c>
+      <c r="H93" s="16">
+        <v>1</v>
+      </c>
+      <c r="I93" s="18"/>
+      <c r="J93" s="16">
+        <v>25</v>
+      </c>
+      <c r="K93" s="18"/>
+      <c r="L93" s="16">
         <v>0</v>
       </c>
-      <c r="H81" s="16">
-        <v>1</v>
-      </c>
-      <c r="I81" s="18"/>
-      <c r="J81" s="16">
-        <v>23</v>
-      </c>
-      <c r="K81" s="18"/>
-      <c r="L81" s="16">
+      <c r="M93" s="18"/>
+      <c r="N93" s="12">
         <v>0</v>
       </c>
-      <c r="M81" s="18"/>
-      <c r="N81" s="8">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="397">
+  <mergeCells count="457">
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:J3"/>
@@ -4358,16 +4796,76 @@
     <mergeCell ref="I78:J78"/>
     <mergeCell ref="K78:L78"/>
     <mergeCell ref="M78:N78"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="L81:M81"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="M91:N91"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="L93:M93"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="A92:B92"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="9210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
   <si>
     <t/>
   </si>
@@ -131,6 +131,15 @@
     <t>6225 Nancy Ridge Dr.  San Diego CA 92121</t>
   </si>
   <si>
+    <t>Santa Clara County</t>
+  </si>
+  <si>
+    <t>AppLovin Corporation</t>
+  </si>
+  <si>
+    <t>1100 Page Mill Road  Palo Alto CA 94304</t>
+  </si>
+  <si>
     <t>PAE Shared Services LLC dba Amentum</t>
   </si>
   <si>
@@ -149,15 +158,6 @@
     <t>San Clemente Island  Los Angeles CA 90731</t>
   </si>
   <si>
-    <t>Santa Clara County</t>
-  </si>
-  <si>
-    <t>AppLovin Corporation</t>
-  </si>
-  <si>
-    <t>1100 Page Mill Road  Palo Alto CA 94304</t>
-  </si>
-  <si>
     <t>DailyLook, Inc.</t>
   </si>
   <si>
@@ -179,6 +179,24 @@
     <t>NAS North Island  San Diego CA 92135</t>
   </si>
   <si>
+    <t>JSL Transport, LLC</t>
+  </si>
+  <si>
+    <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Sacramento County</t>
+  </si>
+  <si>
+    <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
+  </si>
+  <si>
     <t>901 Page Avenue  Fremont CA 94538</t>
   </si>
   <si>
@@ -191,9 +209,6 @@
     <t>Kern County</t>
   </si>
   <si>
-    <t>JSL Transport, LLC</t>
-  </si>
-  <si>
     <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
   </si>
   <si>
@@ -203,19 +218,7 @@
     <t>2 Corporate Dr.  South San Francisco CA 94080</t>
   </si>
   <si>
-    <t>Orange County</t>
-  </si>
-  <si>
-    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
-  </si>
-  <si>
-    <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
-  </si>
-  <si>
-    <t>Sacramento County</t>
-  </si>
-  <si>
-    <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
+    <t>47400 Kato Road  Fremotn CA 94538</t>
   </si>
   <si>
     <t>45500 Fremont Blvd.  Fremont CA 94538</t>
@@ -224,9 +227,6 @@
     <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
   </si>
   <si>
-    <t>47400 Kato Road  Fremotn CA 94538</t>
-  </si>
-  <si>
     <t>45201 Fremont Blvd.  Fremont CA 94538</t>
   </si>
   <si>
@@ -251,6 +251,18 @@
     <t>7300 Medical Center Drive  West Hills CA 91307</t>
   </si>
   <si>
+    <t>First Student</t>
+  </si>
+  <si>
+    <t>5950 S. St. Andrews Pl.  Los Angeles CA 90047</t>
+  </si>
+  <si>
+    <t>Maxar Space LLC</t>
+  </si>
+  <si>
+    <t>3825 Fabian Way  Palo Alto CA 94303</t>
+  </si>
+  <si>
     <t>Riverside County</t>
   </si>
   <si>
@@ -260,39 +272,27 @@
     <t>42375 Remington Avenue  Temecula CA 92590</t>
   </si>
   <si>
-    <t>First Student</t>
-  </si>
-  <si>
     <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
   </si>
   <si>
-    <t>5950 S. St. Andrews Pl.  Los Angeles CA 90047</t>
-  </si>
-  <si>
-    <t>Maxar Space LLC</t>
-  </si>
-  <si>
-    <t>3825 Fabian Way  Palo Alto CA 94303</t>
-  </si>
-  <si>
     <t>11233 San Fernando Road  San Fernando CA 91340</t>
   </si>
   <si>
     <t>1600 Lincoln Ave.  Pasadena CA 91103</t>
   </si>
   <si>
+    <t>Voxpro Group, LLC</t>
+  </si>
+  <si>
+    <t>255 Parkshore Drive  Folsom CA 95630</t>
+  </si>
+  <si>
     <t>Texana Bank</t>
   </si>
   <si>
     <t>38 Technology Drive, Suite 100  Irvine CA 92618</t>
   </si>
   <si>
-    <t>Voxpro Group, LLC</t>
-  </si>
-  <si>
-    <t>255 Parkshore Drive  Folsom CA 95630</t>
-  </si>
-  <si>
     <t>Anheuser-Busch, LLC</t>
   </si>
   <si>
@@ -359,18 +359,18 @@
     <t>4500 Business Center Dr.  Fairfield CA 94534</t>
   </si>
   <si>
+    <t>Ventura County</t>
+  </si>
+  <si>
+    <t>Pennymac</t>
+  </si>
+  <si>
+    <t>112 Lakeview Canyon Road  Thousand Oaks CA 91362</t>
+  </si>
+  <si>
     <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
   </si>
   <si>
-    <t>Ventura County</t>
-  </si>
-  <si>
-    <t>Pennymac</t>
-  </si>
-  <si>
-    <t>112 Lakeview Canyon Road  Thousand Oaks CA 91362</t>
-  </si>
-  <si>
     <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
   </si>
   <si>
@@ -395,6 +395,12 @@
     <t>151 Oyster Point Blvd. #400  South San Francisco CA 94080</t>
   </si>
   <si>
+    <t>Data Aire Inc.</t>
+  </si>
+  <si>
+    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
+  </si>
+  <si>
     <t>Gardena Honda</t>
   </si>
   <si>
@@ -410,12 +416,6 @@
     <t>617 Bryant Street  San Francisco CA 94107</t>
   </si>
   <si>
-    <t>Data Aire Inc.</t>
-  </si>
-  <si>
-    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
-  </si>
-  <si>
     <t>San Joaquin County</t>
   </si>
   <si>
@@ -437,18 +437,18 @@
     <t>1885 Las Plumas Avenue  San Jose CA 95133</t>
   </si>
   <si>
+    <t>Schneider Electric</t>
+  </si>
+  <si>
+    <t>1660 Scenic Avenue  Costa Mesa CA 92626</t>
+  </si>
+  <si>
     <t>Rise Baking Company dba Brill, Inc.</t>
   </si>
   <si>
     <t>2111 W. Valley Blvd.  Colton CA 92324</t>
   </si>
   <si>
-    <t>Schneider Electric</t>
-  </si>
-  <si>
-    <t>1660 Scenic Avenue  Costa Mesa CA 92626</t>
-  </si>
-  <si>
     <t>Placer County</t>
   </si>
   <si>
@@ -473,6 +473,18 @@
     <t>1400 16th Street  San Francisco CA 94103</t>
   </si>
   <si>
+    <t>Zymergen Inc.</t>
+  </si>
+  <si>
+    <t>5980 Horton Street, Suite 105  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>Inland SoCal United Way</t>
+  </si>
+  <si>
+    <t>1835 Chicago Avenue B  Riverside CA 92507</t>
+  </si>
+  <si>
     <t>RingCentral, Inc.</t>
   </si>
   <si>
@@ -485,18 +497,6 @@
     <t>960 Central Expy  Santa Clara CA 95050</t>
   </si>
   <si>
-    <t>Inland SoCal United Way</t>
-  </si>
-  <si>
-    <t>1835 Chicago Avenue B  Riverside CA 92507</t>
-  </si>
-  <si>
-    <t>Zymergen Inc.</t>
-  </si>
-  <si>
-    <t>5980 Horton Street, Suite 105  Emeryville CA 94608</t>
-  </si>
-  <si>
     <t>Alza Corporation</t>
   </si>
   <si>
@@ -539,13 +539,16 @@
     <t>Rivian Automotive, LLC</t>
   </si>
   <si>
+    <t>14600 Myford Road  Irvine CA 92606</t>
+  </si>
+  <si>
+    <t>850 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
     <t>630 Hansen Way  Palo Alto CA 94304</t>
   </si>
   <si>
-    <t>14600 Myford Road  Irvine CA 92606</t>
-  </si>
-  <si>
-    <t>850 Hansen Way  Palo Alto CA 94304</t>
+    <t>9750 Irvine Boulevard  Irvine CA 92618</t>
   </si>
   <si>
     <t>119 Waterworks Way  Irvine CA 92618</t>
@@ -560,9 +563,6 @@
     <t>2223 El Cajon Blvd  San Diego CA 92104</t>
   </si>
   <si>
-    <t>9750 Irvine Boulevard  Irvine CA 92618</t>
-  </si>
-  <si>
     <t>14192 Franklin Avenue  Tustin CA 92780</t>
   </si>
   <si>
@@ -578,18 +578,24 @@
     <t>3000 Upas St.  San Diego CA 92104</t>
   </si>
   <si>
+    <t>470 S. Coast Hwy 101  Encinitas CA 92024</t>
+  </si>
+  <si>
     <t>3725 Greenwood St.  San Diego CA 92110</t>
   </si>
   <si>
-    <t>470 S. Coast Hwy 101  Encinitas CA 92024</t>
-  </si>
-  <si>
     <t>549 S. Anaheim Blvd.  Anaheim CA 92805</t>
   </si>
   <si>
     <t>3612 Kurtz St.  San Dieg CA 92110</t>
   </si>
   <si>
+    <t>Hubbell Power Systems</t>
+  </si>
+  <si>
+    <t>500 S. Dupont Ave  Ontario CA 91761</t>
+  </si>
+  <si>
     <t>San Francisco Housing Authority</t>
   </si>
   <si>
@@ -599,12 +605,6 @@
     <t>1654 Sunnydale Avenue  San Francisco CA 94134</t>
   </si>
   <si>
-    <t>Hubbell Power Systems</t>
-  </si>
-  <si>
-    <t>500 S. Dupont Ave  Ontario CA 91761</t>
-  </si>
-  <si>
     <t>Godspeed Logistics LLC</t>
   </si>
   <si>
@@ -659,21 +659,21 @@
     <t>2000 Maritime Street #100  Oakland CA 94607</t>
   </si>
   <si>
+    <t>21243 S Avalon Blvd  Carson CA 90745</t>
+  </si>
+  <si>
+    <t>Teva Parental Medicines, Inc.</t>
+  </si>
+  <si>
+    <t>19 Hughes  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>175 Commerce Circle  Sacramento CA 95815</t>
+  </si>
+  <si>
     <t>12910 Mulberry Drive  Whittier CA 90602</t>
   </si>
   <si>
-    <t>21243 S Avalon Blvd  Carson CA 90745</t>
-  </si>
-  <si>
-    <t>Teva Parental Medicines, Inc.</t>
-  </si>
-  <si>
-    <t>19 Hughes  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>175 Commerce Circle  Sacramento CA 95815</t>
-  </si>
-  <si>
     <t>3939 Market Street  San Diego CA 92102</t>
   </si>
   <si>
@@ -719,6 +719,12 @@
     <t>3979 Freedom Circle  Santa Clara CA 95054</t>
   </si>
   <si>
+    <t>Silgan Containers</t>
+  </si>
+  <si>
+    <t>567 S. Riverside Drive  Modesto CA 95354</t>
+  </si>
+  <si>
     <t>Fresno County</t>
   </si>
   <si>
@@ -728,12 +734,6 @@
     <t>2715 Fresno Street  Fresno CA 93721</t>
   </si>
   <si>
-    <t>Silgan Containers</t>
-  </si>
-  <si>
-    <t>567 S. Riverside Drive  Modesto CA 95354</t>
-  </si>
-  <si>
     <t>430 Doherty Avenue  Modesto CA 95354</t>
   </si>
   <si>
@@ -752,6 +752,36 @@
     <t>2 Corporate Dr., South  South San Francisco CA 94080</t>
   </si>
   <si>
+    <t>Cal-Multi, LLC</t>
+  </si>
+  <si>
+    <t>7720 Kenamar Court Ste A  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Santa Teresita, Inc.</t>
+  </si>
+  <si>
+    <t>819 Buena Vista St  Duarte CA 91010</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC and NBCUniversal Production Services, LLC</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1440  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>Dacor</t>
+  </si>
+  <si>
+    <t>14425 Clark Avenue  City of Industry CA 91745</t>
+  </si>
+  <si>
+    <t>Mechanics Bank</t>
+  </si>
+  <si>
+    <t>2100 South Blosser Road  Santa Maria CA 93458</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -774,15 +804,15 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>WARN Summary</t>
   </si>
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 8/24/2022
+ End Date: 8/31/2022
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">WARN Summary </t>
   </si>
   <si>
     <t>Report Summary</t>
@@ -1195,7 +1225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1251,10 +1281,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1292,9 +1318,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1336,6 +1360,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1617,26 +1644,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R129"/>
+  <dimension ref="A1:R135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="2.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="6.140625" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="2.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1651,96 +1678,96 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-    </row>
-    <row r="2" spans="1:18" ht="38.25" customHeight="1">
-      <c r="A2" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+    </row>
+    <row r="2" spans="1:18" ht="37.5" customHeight="1">
+      <c r="A2" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="37" t="s">
+      <c r="G3" s="37"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="37" t="s">
+      <c r="J3" s="36"/>
+      <c r="K3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="38"/>
-      <c r="M3" s="40" t="s">
+      <c r="L3" s="36"/>
+      <c r="M3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="41"/>
+      <c r="N3" s="39"/>
     </row>
     <row r="4" spans="1:18" ht="24.75">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="43" t="s">
+      <c r="D4" s="43"/>
+      <c r="E4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="46"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44" t="s">
+      <c r="G4" s="44"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="45"/>
-      <c r="K4" s="44" t="s">
+      <c r="J4" s="43"/>
+      <c r="K4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="47" t="s">
+      <c r="L4" s="43"/>
+      <c r="M4" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="48"/>
+      <c r="N4" s="46"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
@@ -1904,20 +1931,20 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="11" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B10" s="12">
-        <v>44727</v>
+        <v>44739</v>
       </c>
       <c r="C10" s="13">
         <v>44753</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="12">
-        <v>44784</v>
+        <v>44799</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="5"/>
@@ -1926,27 +1953,27 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="15">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" s="10"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>44741</v>
+        <v>44727</v>
       </c>
       <c r="C11" s="4">
         <v>44753</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="3">
-        <v>44800</v>
+        <v>44784</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>26</v>
@@ -1954,11 +1981,11 @@
       <c r="G11" s="7"/>
       <c r="H11" s="5"/>
       <c r="I11" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="8">
-        <v>229</v>
+        <v>25</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="9" t="s">
@@ -1968,52 +1995,52 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="11" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B12" s="12">
-        <v>44727</v>
+        <v>44741</v>
       </c>
       <c r="C12" s="13">
         <v>44753</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="12">
-        <v>44784</v>
+        <v>44800</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="5"/>
       <c r="I12" s="14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="15">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>44739</v>
+        <v>44727</v>
       </c>
       <c r="C13" s="4">
         <v>44753</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3">
-        <v>44799</v>
+        <v>44784</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="5"/>
@@ -2022,7 +2049,7 @@
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="8">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="9" t="s">
@@ -2096,7 +2123,7 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16" s="12">
         <v>44743</v>
@@ -2141,7 +2168,7 @@
         <v>44784</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="5"/>
@@ -2160,71 +2187,71 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" s="12">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C18" s="13">
         <v>44754</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="12">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="5"/>
       <c r="I18" s="14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="15">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3">
-        <v>44732</v>
+        <v>44743</v>
       </c>
       <c r="C19" s="4">
         <v>44754</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="3">
-        <v>44926</v>
+        <v>44804</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="5"/>
       <c r="I19" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="8">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N19" s="10"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="12">
         <v>44743</v>
@@ -2237,7 +2264,7 @@
         <v>44804</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="5"/>
@@ -2246,7 +2273,7 @@
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="16" t="s">
@@ -2256,20 +2283,20 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B21" s="3">
-        <v>44742</v>
+        <v>44739</v>
       </c>
       <c r="C21" s="4">
         <v>44754</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="3">
-        <v>44802</v>
+        <v>44800</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="5"/>
@@ -2278,49 +2305,49 @@
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="8">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N21" s="10"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="11" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B22" s="12">
-        <v>44743</v>
+        <v>44732</v>
       </c>
       <c r="C22" s="13">
         <v>44754</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="12">
-        <v>44804</v>
+        <v>44926</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="5"/>
       <c r="I22" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="15">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="10"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B23" s="3">
         <v>44743</v>
@@ -2333,7 +2360,7 @@
         <v>44804</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="5"/>
@@ -2342,7 +2369,7 @@
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="9" t="s">
@@ -2352,29 +2379,29 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="11" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B24" s="12">
-        <v>44743</v>
+        <v>44742</v>
       </c>
       <c r="C24" s="13">
         <v>44754</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="12">
-        <v>44804</v>
+        <v>44802</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="5"/>
       <c r="I24" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="15">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="16" t="s">
@@ -2397,7 +2424,7 @@
         <v>44800</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="5"/>
@@ -2406,7 +2433,7 @@
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="8">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="9" t="s">
@@ -2416,29 +2443,29 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="11" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B26" s="12">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C26" s="13">
         <v>44754</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="12">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="5"/>
       <c r="I26" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="15">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="16" t="s">
@@ -2448,29 +2475,29 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C27" s="4">
         <v>44754</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="3">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="5"/>
       <c r="I27" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="9" t="s">
@@ -2493,7 +2520,7 @@
         <v>44800</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="5"/>
@@ -2525,7 +2552,7 @@
         <v>44800</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="5"/>
@@ -2557,7 +2584,7 @@
         <v>44804</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="5"/>
@@ -2589,7 +2616,7 @@
         <v>44804</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="5"/>
@@ -2621,7 +2648,7 @@
         <v>44804</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="5"/>
@@ -2653,7 +2680,7 @@
         <v>44804</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="5"/>
@@ -2685,7 +2712,7 @@
         <v>44804</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="5"/>
@@ -2704,20 +2731,20 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="B35" s="3">
-        <v>44753</v>
+        <v>44743</v>
       </c>
       <c r="C35" s="4">
         <v>44756</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="3">
-        <v>44813</v>
+        <v>44799</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="5"/>
@@ -2726,30 +2753,30 @@
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="8">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N35" s="10"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B36" s="12">
-        <v>44743</v>
+        <v>44748</v>
       </c>
       <c r="C36" s="13">
         <v>44756</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="12">
-        <v>44799</v>
+        <v>44809</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="5"/>
@@ -2758,30 +2785,30 @@
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="15">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N36" s="10"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="B37" s="3">
-        <v>44743</v>
+        <v>44753</v>
       </c>
       <c r="C37" s="4">
         <v>44756</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="3">
-        <v>44799</v>
+        <v>44813</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="5"/>
@@ -2790,30 +2817,30 @@
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="8">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N37" s="10"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B38" s="12">
-        <v>44748</v>
+        <v>44743</v>
       </c>
       <c r="C38" s="13">
         <v>44756</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="12">
-        <v>44809</v>
+        <v>44799</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="5"/>
@@ -2822,7 +2849,7 @@
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="15">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="16" t="s">
@@ -2845,7 +2872,7 @@
         <v>44799</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="5"/>
@@ -2877,7 +2904,7 @@
         <v>44788</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="5"/>
@@ -2896,7 +2923,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3">
         <v>44749</v>
@@ -2906,7 +2933,7 @@
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="3">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>73</v>
@@ -2918,7 +2945,7 @@
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="8">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="9" t="s">
@@ -2928,7 +2955,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B42" s="12">
         <v>44749</v>
@@ -2938,7 +2965,7 @@
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="12">
-        <v>44810</v>
+        <v>44809</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>75</v>
@@ -2950,7 +2977,7 @@
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="15">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="16" t="s">
@@ -3024,7 +3051,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B45" s="3">
         <v>44749</v>
@@ -3120,7 +3147,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B48" s="12">
         <v>44749</v>
@@ -3280,20 +3307,20 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B53" s="3">
-        <v>44753</v>
+        <v>44700</v>
       </c>
       <c r="C53" s="4">
         <v>44763</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="3">
-        <v>44795</v>
+        <v>44760</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="5"/>
@@ -3302,30 +3329,30 @@
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N53" s="10"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B54" s="12">
-        <v>44700</v>
+        <v>44753</v>
       </c>
       <c r="C54" s="13">
         <v>44763</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="12">
-        <v>44760</v>
+        <v>44795</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="5"/>
@@ -3334,7 +3361,7 @@
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="15">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="16" t="s">
@@ -3408,7 +3435,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="3">
         <v>44700</v>
@@ -3421,7 +3448,7 @@
         <v>44760</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="5"/>
@@ -3472,7 +3499,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B59" s="3">
         <v>44755</v>
@@ -3504,17 +3531,17 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="11" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B60" s="12">
-        <v>44757</v>
+        <v>44762</v>
       </c>
       <c r="C60" s="13">
         <v>44764</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="12">
-        <v>44819</v>
+        <v>44837</v>
       </c>
       <c r="F60" s="14" t="s">
         <v>111</v>
@@ -3526,7 +3553,7 @@
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="15">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="16" t="s">
@@ -3536,49 +3563,49 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="2" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B61" s="3">
-        <v>44755</v>
+        <v>44757</v>
       </c>
       <c r="C61" s="4">
         <v>44764</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="3">
-        <v>44816</v>
+        <v>44819</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="5"/>
       <c r="I61" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N61" s="10"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="11" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="B62" s="12">
-        <v>44762</v>
+        <v>44755</v>
       </c>
       <c r="C62" s="13">
         <v>44764</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="12">
-        <v>44837</v>
+        <v>44816</v>
       </c>
       <c r="F62" s="14" t="s">
         <v>116</v>
@@ -3586,11 +3613,11 @@
       <c r="G62" s="7"/>
       <c r="H62" s="5"/>
       <c r="I62" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="16" t="s">
@@ -3632,7 +3659,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B64" s="12">
         <v>44756</v>
@@ -3664,7 +3691,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B65" s="3">
         <v>44761</v>
@@ -3696,17 +3723,17 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="11" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="B66" s="12">
-        <v>44763</v>
+        <v>44767</v>
       </c>
       <c r="C66" s="13">
         <v>44768</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="12">
-        <v>44834</v>
+        <v>44827</v>
       </c>
       <c r="F66" s="14" t="s">
         <v>125</v>
@@ -3718,7 +3745,7 @@
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="15">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="16" t="s">
@@ -3728,17 +3755,17 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B67" s="3">
-        <v>44767</v>
+        <v>44763</v>
       </c>
       <c r="C67" s="4">
         <v>44768</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="3">
-        <v>44827</v>
+        <v>44834</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>127</v>
@@ -3750,7 +3777,7 @@
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="8">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="9" t="s">
@@ -3792,7 +3819,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B69" s="3">
         <v>44760</v>
@@ -3824,7 +3851,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B70" s="12">
         <v>44760</v>
@@ -3856,7 +3883,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B71" s="3">
         <v>44760</v>
@@ -3888,17 +3915,17 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="11" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B72" s="12">
-        <v>44762</v>
+        <v>44768</v>
       </c>
       <c r="C72" s="13">
         <v>44770</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="12">
-        <v>44829</v>
+        <v>44830</v>
       </c>
       <c r="F72" s="14" t="s">
         <v>137</v>
@@ -3910,7 +3937,7 @@
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="15">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="16" t="s">
@@ -3920,17 +3947,17 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B73" s="3">
-        <v>44770</v>
+        <v>44769</v>
       </c>
       <c r="C73" s="4">
         <v>44770</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="3">
-        <v>44865</v>
+        <v>44837</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>139</v>
@@ -3938,11 +3965,11 @@
       <c r="G73" s="7"/>
       <c r="H73" s="5"/>
       <c r="I73" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="8">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="9" t="s">
@@ -3952,7 +3979,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B74" s="12">
         <v>44762</v>
@@ -3962,10 +3989,10 @@
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="12">
-        <v>44822</v>
+        <v>44829</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="5"/>
@@ -3978,58 +4005,58 @@
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N74" s="10"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="2" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B75" s="3">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="C75" s="4">
         <v>44770</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="3">
-        <v>44837</v>
+        <v>44865</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="5"/>
       <c r="I75" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J75" s="5"/>
       <c r="K75" s="8">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N75" s="10"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B76" s="12">
-        <v>44768</v>
+        <v>44762</v>
       </c>
       <c r="C76" s="13">
         <v>44770</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="12">
-        <v>44830</v>
+        <v>44822</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="5"/>
@@ -4038,11 +4065,11 @@
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="15">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N76" s="10"/>
     </row>
@@ -4080,7 +4107,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B78" s="12">
         <v>44774</v>
@@ -4112,7 +4139,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B79" s="3">
         <v>44774</v>
@@ -4208,7 +4235,7 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B82" s="12">
         <v>44775</v>
@@ -4240,7 +4267,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B83" s="3">
         <v>44769</v>
@@ -4262,7 +4289,7 @@
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="8">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="9" t="s">
@@ -4272,7 +4299,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B84" s="12">
         <v>44769</v>
@@ -4294,7 +4321,7 @@
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="15">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="16" t="s">
@@ -4304,7 +4331,7 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B85" s="3">
         <v>44769</v>
@@ -4326,7 +4353,7 @@
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="8">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="9" t="s">
@@ -4336,7 +4363,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B86" s="12">
         <v>44769</v>
@@ -4358,7 +4385,7 @@
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="15">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="16" t="s">
@@ -4368,61 +4395,61 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="2" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B87" s="3">
-        <v>44774</v>
+        <v>44769</v>
       </c>
       <c r="C87" s="4">
         <v>44781</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="3">
-        <v>44836</v>
+        <v>44841</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="5"/>
       <c r="I87" s="6" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="8">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N87" s="10"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="11" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B88" s="12">
-        <v>44769</v>
+        <v>44774</v>
       </c>
       <c r="C88" s="13">
         <v>44781</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="12">
-        <v>44841</v>
+        <v>44836</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="5"/>
       <c r="I88" s="14" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="15">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="16" t="s">
@@ -4432,7 +4459,7 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B89" s="3">
         <v>44769</v>
@@ -4464,7 +4491,7 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B90" s="12">
         <v>44769</v>
@@ -4496,7 +4523,7 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B91" s="3">
         <v>44769</v>
@@ -4582,7 +4609,7 @@
       </c>
       <c r="J93" s="5"/>
       <c r="K93" s="8">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="9" t="s">
@@ -4614,7 +4641,7 @@
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="15">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="16" t="s">
@@ -4624,7 +4651,7 @@
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B95" s="3">
         <v>44782</v>
@@ -4688,17 +4715,17 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="B97" s="3">
-        <v>44771</v>
+        <v>44778</v>
       </c>
       <c r="C97" s="4">
         <v>44783</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="3">
-        <v>44834</v>
+        <v>44839</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>176</v>
@@ -4706,11 +4733,11 @@
       <c r="G97" s="7"/>
       <c r="H97" s="5"/>
       <c r="I97" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="8">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="9" t="s">
@@ -4720,7 +4747,7 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B98" s="12">
         <v>44771</v>
@@ -4733,7 +4760,7 @@
         <v>44834</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="5"/>
@@ -4742,39 +4769,39 @@
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="15">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N98" s="10"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B99" s="3">
-        <v>44778</v>
+        <v>44771</v>
       </c>
       <c r="C99" s="4">
         <v>44783</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3">
-        <v>44839</v>
+        <v>44834</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="5"/>
       <c r="I99" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="8">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="9" t="s">
@@ -4816,7 +4843,7 @@
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B101" s="3">
         <v>44771</v>
@@ -4829,7 +4856,7 @@
         <v>44834</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="5"/>
@@ -4848,7 +4875,7 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B102" s="12">
         <v>44777</v>
@@ -4880,7 +4907,7 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B103" s="3">
         <v>44781</v>
@@ -4944,7 +4971,7 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B105" s="3">
         <v>44781</v>
@@ -4976,7 +5003,7 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B106" s="12">
         <v>44781</v>
@@ -5008,7 +5035,7 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B107" s="3">
         <v>44781</v>
@@ -5072,7 +5099,7 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B109" s="3">
         <v>44784</v>
@@ -5154,11 +5181,11 @@
       <c r="G111" s="7"/>
       <c r="H111" s="5"/>
       <c r="I111" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="8">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="9" t="s">
@@ -5168,20 +5195,20 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="11" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B112" s="12">
-        <v>44782</v>
+        <v>44642</v>
       </c>
       <c r="C112" s="13">
         <v>44789</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="12">
-        <v>44842</v>
+        <v>44726</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="5"/>
@@ -5190,30 +5217,30 @@
       </c>
       <c r="J112" s="5"/>
       <c r="K112" s="15">
-        <v>33</v>
+        <v>305</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N112" s="10"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B113" s="3">
-        <v>44642</v>
+        <v>44782</v>
       </c>
       <c r="C113" s="4">
         <v>44789</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3">
-        <v>44726</v>
+        <v>44842</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="5"/>
@@ -5222,7 +5249,7 @@
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="8">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="9" t="s">
@@ -5232,7 +5259,7 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="11" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B114" s="12">
         <v>44782</v>
@@ -5250,11 +5277,11 @@
       <c r="G114" s="7"/>
       <c r="H114" s="5"/>
       <c r="I114" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J114" s="5"/>
       <c r="K114" s="15">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="16" t="s">
@@ -5296,7 +5323,7 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B116" s="12">
         <v>44781</v>
@@ -5328,7 +5355,7 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B117" s="3">
         <v>44781</v>
@@ -5424,7 +5451,7 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B120" s="12">
         <v>44788</v>
@@ -5456,7 +5483,7 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B121" s="3">
         <v>44781</v>
@@ -5488,7 +5515,7 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B122" s="12">
         <v>44785</v>
@@ -5520,49 +5547,49 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="2" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="B123" s="3">
-        <v>44776</v>
+        <v>44771</v>
       </c>
       <c r="C123" s="4">
         <v>44791</v>
       </c>
       <c r="D123" s="5"/>
       <c r="E123" s="3">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="5"/>
       <c r="I123" s="6" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="8">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N123" s="10"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="11" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="B124" s="12">
-        <v>44771</v>
+        <v>44776</v>
       </c>
       <c r="C124" s="13">
         <v>44791</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="12">
-        <v>44837</v>
+        <v>44834</v>
       </c>
       <c r="F124" s="14" t="s">
         <v>222</v>
@@ -5570,11 +5597,11 @@
       <c r="G124" s="7"/>
       <c r="H124" s="5"/>
       <c r="I124" s="14" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="15">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="16" t="s">
@@ -5597,12 +5624,12 @@
         <v>44844</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="5"/>
       <c r="I125" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="8">
@@ -5648,7 +5675,7 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B127" s="3">
         <v>44792</v>
@@ -5678,82 +5705,304 @@
       </c>
       <c r="N127" s="10"/>
     </row>
-    <row r="128" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A128" s="27" t="s">
+    <row r="128" spans="1:14">
+      <c r="A128" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B128" s="12">
+        <v>44798</v>
+      </c>
+      <c r="C128" s="13">
+        <v>44799</v>
+      </c>
+      <c r="D128" s="5"/>
+      <c r="E128" s="12">
+        <v>44858</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J128" s="5"/>
+      <c r="K128" s="15">
+        <v>80</v>
+      </c>
+      <c r="L128" s="5"/>
+      <c r="M128" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="N128" s="10"/>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="3">
+        <v>44799</v>
+      </c>
+      <c r="C129" s="4">
+        <v>44799</v>
+      </c>
+      <c r="D129" s="5"/>
+      <c r="E129" s="3">
+        <v>44865</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G129" s="7"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J129" s="5"/>
+      <c r="K129" s="8">
+        <v>100</v>
+      </c>
+      <c r="L129" s="5"/>
+      <c r="M129" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="N129" s="10"/>
+    </row>
+    <row r="130" spans="1:14">
+      <c r="A130" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B130" s="12">
+        <v>44802</v>
+      </c>
+      <c r="C130" s="13">
+        <v>44802</v>
+      </c>
+      <c r="D130" s="5"/>
+      <c r="E130" s="12">
+        <v>44865</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G130" s="7"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J130" s="5"/>
+      <c r="K130" s="15">
+        <v>96</v>
+      </c>
+      <c r="L130" s="5"/>
+      <c r="M130" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="N130" s="10"/>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B131" s="3">
+        <v>44799</v>
+      </c>
+      <c r="C131" s="4">
+        <v>44802</v>
+      </c>
+      <c r="D131" s="5"/>
+      <c r="E131" s="3">
+        <v>44859</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G131" s="7"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J131" s="5"/>
+      <c r="K131" s="8">
+        <v>37</v>
+      </c>
+      <c r="L131" s="5"/>
+      <c r="M131" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="N131" s="10"/>
+    </row>
+    <row r="132" spans="1:14">
+      <c r="A132" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132" s="12">
+        <v>44799</v>
+      </c>
+      <c r="C132" s="13">
+        <v>44804</v>
+      </c>
+      <c r="D132" s="5"/>
+      <c r="E132" s="12">
+        <v>44862</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G132" s="7"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J132" s="5"/>
+      <c r="K132" s="15">
+        <v>91</v>
+      </c>
+      <c r="L132" s="5"/>
+      <c r="M132" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="N132" s="10"/>
+    </row>
+    <row r="133" spans="1:14">
+      <c r="A133" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B133" s="3">
+        <v>44798</v>
+      </c>
+      <c r="C133" s="4">
+        <v>44804</v>
+      </c>
+      <c r="D133" s="5"/>
+      <c r="E133" s="3">
+        <v>44837</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G133" s="7"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J133" s="5"/>
+      <c r="K133" s="8">
+        <v>56</v>
+      </c>
+      <c r="L133" s="5"/>
+      <c r="M133" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N133" s="10"/>
+    </row>
+    <row r="134" spans="1:14" ht="30" customHeight="1">
+      <c r="A134" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B134" s="26"/>
+      <c r="C134" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="B128" s="28"/>
-      <c r="C128" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="D128" s="30"/>
-      <c r="E128" s="31"/>
-      <c r="F128" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="G128" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="H128" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="I128" s="31"/>
-      <c r="J128" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="K128" s="31"/>
-      <c r="L128" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="M128" s="31"/>
-      <c r="N128" s="33" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" s="26" customFormat="1">
-      <c r="A129" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="B129" s="22"/>
-      <c r="C129" s="23">
-        <v>9388</v>
-      </c>
-      <c r="D129" s="17"/>
-      <c r="E129" s="18"/>
-      <c r="F129" s="24">
-        <v>72</v>
-      </c>
-      <c r="G129" s="24">
+      <c r="D134" s="28"/>
+      <c r="E134" s="29"/>
+      <c r="F134" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="G134" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="H134" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="I134" s="29"/>
+      <c r="J134" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="K134" s="29"/>
+      <c r="L134" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="M134" s="29"/>
+      <c r="N134" s="31" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" s="24" customFormat="1">
+      <c r="A135" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B135" s="20"/>
+      <c r="C135" s="21">
+        <v>9848</v>
+      </c>
+      <c r="D135" s="17"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="22">
+        <v>76</v>
+      </c>
+      <c r="G135" s="22">
         <v>3</v>
       </c>
-      <c r="H129" s="23">
+      <c r="H135" s="21">
         <v>1</v>
       </c>
-      <c r="I129" s="18"/>
-      <c r="J129" s="23">
-        <v>46</v>
-      </c>
-      <c r="K129" s="18"/>
-      <c r="L129" s="23">
+      <c r="I135" s="18"/>
+      <c r="J135" s="21">
+        <v>48</v>
+      </c>
+      <c r="K135" s="18"/>
+      <c r="L135" s="21">
         <v>1</v>
       </c>
-      <c r="M129" s="18"/>
-      <c r="N129" s="25">
+      <c r="M135" s="18"/>
+      <c r="N135" s="23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="637">
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="H129:I129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="L129:M129"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="H128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="L128:M128"/>
-    <mergeCell ref="A128:B128"/>
+  <mergeCells count="667">
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="H135:I135"/>
+    <mergeCell ref="J135:K135"/>
+    <mergeCell ref="L135:M135"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="J134:K134"/>
+    <mergeCell ref="L134:M134"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="M133:N133"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="M132:N132"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="M131:N131"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="K130:L130"/>
+    <mergeCell ref="M130:N130"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
     <mergeCell ref="C127:D127"/>
     <mergeCell ref="F127:H127"/>
     <mergeCell ref="I127:J127"/>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="260">
   <si>
     <t/>
   </si>
@@ -89,6 +89,27 @@
     <t>Address</t>
   </si>
   <si>
+    <t>Alameda County</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>Closure Permanent</t>
+  </si>
+  <si>
+    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>Los Angeles County</t>
+  </si>
+  <si>
+    <t>Assembled Financial Technology, LLC</t>
+  </si>
+  <si>
+    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
+  </si>
+  <si>
     <t>San Diego County</t>
   </si>
   <si>
@@ -98,37 +119,43 @@
     <t>Layoff Permanent</t>
   </si>
   <si>
+    <t>6225 Nancy Ridge Dr.  San Diego CA 92121</t>
+  </si>
+  <si>
     <t>2620 Commerce Way, Suite A/B  Vista CA 92081</t>
   </si>
   <si>
-    <t>Alameda County</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>Closure Permanent</t>
-  </si>
-  <si>
-    <t>7999 Gateway Blvd #320  Newark CA 94560</t>
-  </si>
-  <si>
-    <t>Los Angeles County</t>
-  </si>
-  <si>
-    <t>Assembled Financial Technology, LLC</t>
-  </si>
-  <si>
-    <t>9000 Sunset Boulevard, Suite 1010  West Hollywood CA 90069</t>
-  </si>
-  <si>
     <t>Cue Health</t>
   </si>
   <si>
     <t>9877 Waples St.  San Diego CA 92121</t>
   </si>
   <si>
-    <t>6225 Nancy Ridge Dr.  San Diego CA 92121</t>
+    <t>PAE Shared Services LLC dba Amentum</t>
+  </si>
+  <si>
+    <t>San Clemente Island  Los Angeles CA 90731</t>
+  </si>
+  <si>
+    <t>DailyLook, Inc.</t>
+  </si>
+  <si>
+    <t>2445 E. 12th Street, Unit B  Los Angeles CA 90021</t>
+  </si>
+  <si>
+    <t>San Mateo County</t>
+  </si>
+  <si>
+    <t>Tesla, Inc.</t>
+  </si>
+  <si>
+    <t>3055 Clearview Way  San Mateo CA 94402</t>
+  </si>
+  <si>
+    <t>ABM Industry Groups, LLC dba Meta</t>
+  </si>
+  <si>
+    <t>1 Hacker Way  Menlo Park CA 94025</t>
   </si>
   <si>
     <t>Santa Clara County</t>
@@ -140,28 +167,10 @@
     <t>1100 Page Mill Road  Palo Alto CA 94304</t>
   </si>
   <si>
-    <t>PAE Shared Services LLC dba Amentum</t>
-  </si>
-  <si>
     <t>Naval Base Point Loma 4045 Hancock St  San Diego CA 92110</t>
   </si>
   <si>
-    <t>San Mateo County</t>
-  </si>
-  <si>
-    <t>Tesla, Inc.</t>
-  </si>
-  <si>
-    <t>3055 Clearview Way  San Mateo CA 94402</t>
-  </si>
-  <si>
-    <t>San Clemente Island  Los Angeles CA 90731</t>
-  </si>
-  <si>
-    <t>DailyLook, Inc.</t>
-  </si>
-  <si>
-    <t>2445 E. 12th Street, Unit B  Los Angeles CA 90021</t>
+    <t>NAS North Island  San Diego CA 92135</t>
   </si>
   <si>
     <t>Heron Therapeutics, Inc.</t>
@@ -170,70 +179,67 @@
     <t>4242 Campus Point Court, Suite 200  San Diego CA 92121</t>
   </si>
   <si>
-    <t>ABM Industry Groups, LLC dba Meta</t>
-  </si>
-  <si>
-    <t>1 Hacker Way  Menlo Park CA 94025</t>
-  </si>
-  <si>
-    <t>NAS North Island  San Diego CA 92135</t>
+    <t>901 Page Avenue  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>47700 Kato Road  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>47400 Kato Road  Fremotn CA 94538</t>
+  </si>
+  <si>
+    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>Kern County</t>
   </si>
   <si>
     <t>JSL Transport, LLC</t>
   </si>
   <si>
+    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>R.A. Phillips Industries, Inc.</t>
+  </si>
+  <si>
+    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>10371 Culver Blvd.  Culver City CA 90232</t>
+  </si>
+  <si>
     <t>430 S. Cataract Avenue  San Dimas CA 91773</t>
   </si>
   <si>
+    <t>PACT Pharma</t>
+  </si>
+  <si>
+    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
+  </si>
+  <si>
+    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
+  </si>
+  <si>
     <t>Sacramento County</t>
   </si>
   <si>
     <t>2315 Stockton Blvd.  Sacramento CA 95817</t>
   </si>
   <si>
-    <t>Orange County</t>
-  </si>
-  <si>
-    <t>7231 Garden Grove Blvd. Suite K  Garden Grove CA 92841</t>
-  </si>
-  <si>
-    <t>901 Page Avenue  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>R.A. Phillips Industries, Inc.</t>
-  </si>
-  <si>
-    <t>12070 Burke St  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>Kern County</t>
-  </si>
-  <si>
-    <t>3000 Sillect Avenue  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>PACT Pharma</t>
-  </si>
-  <si>
-    <t>2 Corporate Dr.  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>47400 Kato Road  Fremotn CA 94538</t>
-  </si>
-  <si>
-    <t>45500 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>2700 Medical Center Road  Mission Viejo CA 92691</t>
-  </si>
-  <si>
-    <t>45201 Fremont Blvd.  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>47700 Kato Road  Fremont CA 94538</t>
-  </si>
-  <si>
-    <t>10371 Culver Blvd.  Culver City CA 90232</t>
+    <t>14250 Arminta Street  Panorama City CA 91402</t>
+  </si>
+  <si>
+    <t>7300 Medical Center Drive  West Hills CA 91307</t>
   </si>
   <si>
     <t>Stanislaus County</t>
@@ -242,21 +248,21 @@
     <t>4301 N. Star Way  Modesto CA 95356</t>
   </si>
   <si>
-    <t>14250 Arminta Street  Panorama City CA 91402</t>
-  </si>
-  <si>
     <t>621 Ruberta, Unit 2  Glendale CA 91201</t>
   </si>
   <si>
-    <t>7300 Medical Center Drive  West Hills CA 91307</t>
-  </si>
-  <si>
     <t>First Student</t>
   </si>
   <si>
+    <t>1600 Lincoln Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
     <t>5950 S. St. Andrews Pl.  Los Angeles CA 90047</t>
   </si>
   <si>
+    <t>11233 San Fernando Road  San Fernando CA 91340</t>
+  </si>
+  <si>
     <t>Maxar Space LLC</t>
   </si>
   <si>
@@ -275,10 +281,10 @@
     <t>14800 South Avalon Blvd.  Gardena CA 90248</t>
   </si>
   <si>
-    <t>11233 San Fernando Road  San Fernando CA 91340</t>
-  </si>
-  <si>
-    <t>1600 Lincoln Ave.  Pasadena CA 91103</t>
+    <t>Texana Bank</t>
+  </si>
+  <si>
+    <t>38 Technology Drive, Suite 100  Irvine CA 92618</t>
   </si>
   <si>
     <t>Voxpro Group, LLC</t>
@@ -287,12 +293,6 @@
     <t>255 Parkshore Drive  Folsom CA 95630</t>
   </si>
   <si>
-    <t>Texana Bank</t>
-  </si>
-  <si>
-    <t>38 Technology Drive, Suite 100  Irvine CA 92618</t>
-  </si>
-  <si>
     <t>Anheuser-Busch, LLC</t>
   </si>
   <si>
@@ -308,16 +308,19 @@
     <t>14613 Bar Harbor Road  Fontana CA 92336</t>
   </si>
   <si>
+    <t>ADP, Inc.</t>
+  </si>
+  <si>
+    <t>4125 Hopyard Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
     <t>Adverum Biotechnologies, Inc.</t>
   </si>
   <si>
     <t>900 Saginaw Drive  Redwood City CA 94063</t>
   </si>
   <si>
-    <t>ADP, Inc.</t>
-  </si>
-  <si>
-    <t>4125 Hopyard Road  Pleasanton CA 94588</t>
+    <t>100 Cardinal Way  Redwood City CA 94063</t>
   </si>
   <si>
     <t>Life Cycle Engineering</t>
@@ -326,9 +329,6 @@
     <t>2535 Camino Del Rio South Suite 250  San Diego CA 92108</t>
   </si>
   <si>
-    <t>100 Cardinal Way  Redwood City CA 94063</t>
-  </si>
-  <si>
     <t>Freshly, Inc.</t>
   </si>
   <si>
@@ -356,6 +356,15 @@
     <t>North Bay Health</t>
   </si>
   <si>
+    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
+  </si>
+  <si>
+    <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
+  </si>
+  <si>
+    <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
+  </si>
+  <si>
     <t>4500 Business Center Dr.  Fairfield CA 94534</t>
   </si>
   <si>
@@ -368,37 +377,52 @@
     <t>112 Lakeview Canyon Road  Thousand Oaks CA 91362</t>
   </si>
   <si>
-    <t>1200 B Gale Wilson Blvd.  Fairfield CA 94533</t>
-  </si>
-  <si>
-    <t>2458 Hilborn Rd.  Fairfield CA 94534</t>
-  </si>
-  <si>
-    <t>1000 Nut Tree Road  Vacaville CA 95687</t>
-  </si>
-  <si>
     <t>3043 Townsgate Road  Thousand Oaks CA 91361</t>
   </si>
   <si>
+    <t>CytomX Therapeutics Inc.</t>
+  </si>
+  <si>
+    <t>Layoff Not known at this time</t>
+  </si>
+  <si>
+    <t>151 Oyster Point Blvd. #400  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Data Aire Inc.</t>
+  </si>
+  <si>
+    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
+  </si>
+  <si>
     <t>Urbn Leaf dba Uprooted Inc.</t>
   </si>
   <si>
     <t>658 East San Ysidro Blvd.  San Ysidro CA 92173</t>
   </si>
   <si>
-    <t>CytomX Therapeutics Inc.</t>
-  </si>
-  <si>
-    <t>Layoff Not known at this time</t>
-  </si>
-  <si>
-    <t>151 Oyster Point Blvd. #400  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>Data Aire Inc.</t>
-  </si>
-  <si>
-    <t>230 W. Blueridge Avenue  Orange CA 92865</t>
+    <t>San Francisco County</t>
+  </si>
+  <si>
+    <t>Tonal Systems, Inc.</t>
+  </si>
+  <si>
+    <t>617 Bryant Street  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Restoration Hardware Inc.</t>
+  </si>
+  <si>
+    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
+  </si>
+  <si>
+    <t>OnePointOne Inc.</t>
+  </si>
+  <si>
+    <t>1185 Campbell Avenue  San Jose CA 95126</t>
   </si>
   <si>
     <t>Gardena Honda</t>
@@ -407,36 +431,21 @@
     <t>15515 South Western Avenue  Gardena CA 90249</t>
   </si>
   <si>
-    <t>San Francisco County</t>
-  </si>
-  <si>
-    <t>Tonal Systems, Inc.</t>
-  </si>
-  <si>
-    <t>617 Bryant Street  San Francisco CA 94107</t>
-  </si>
-  <si>
-    <t>San Joaquin County</t>
-  </si>
-  <si>
-    <t>Restoration Hardware Inc.</t>
-  </si>
-  <si>
-    <t>2900 N. MacArthur Drive  Tracy CA 95376</t>
-  </si>
-  <si>
-    <t>OnePointOne Inc.</t>
-  </si>
-  <si>
-    <t>1185 Campbell Avenue  San Jose CA 95126</t>
-  </si>
-  <si>
     <t>Amy&amp;rsquo;s Kitchen, Inc.</t>
   </si>
   <si>
     <t>1885 Las Plumas Avenue  San Jose CA 95133</t>
   </si>
   <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Adventist Health</t>
+  </si>
+  <si>
+    <t>1 Adventist Health Way  Roseville CA 95661</t>
+  </si>
+  <si>
     <t>Schneider Electric</t>
   </si>
   <si>
@@ -449,15 +458,6 @@
     <t>2111 W. Valley Blvd.  Colton CA 92324</t>
   </si>
   <si>
-    <t>Placer County</t>
-  </si>
-  <si>
-    <t>Adventist Health</t>
-  </si>
-  <si>
-    <t>1 Adventist Health Way  Roseville CA 95661</t>
-  </si>
-  <si>
     <t>Invitae Corporation</t>
   </si>
   <si>
@@ -479,22 +479,28 @@
     <t>5980 Horton Street, Suite 105  Emeryville CA 94608</t>
   </si>
   <si>
+    <t>RingCentral, Inc.</t>
+  </si>
+  <si>
+    <t>20 Davis Drive  Belmont CA 94002</t>
+  </si>
+  <si>
+    <t>Owens Corning</t>
+  </si>
+  <si>
+    <t>960 Central Expy  Santa Clara CA 95050</t>
+  </si>
+  <si>
     <t>Inland SoCal United Way</t>
   </si>
   <si>
     <t>1835 Chicago Avenue B  Riverside CA 92507</t>
   </si>
   <si>
-    <t>RingCentral, Inc.</t>
-  </si>
-  <si>
-    <t>20 Davis Drive  Belmont CA 94002</t>
-  </si>
-  <si>
-    <t>Owens Corning</t>
-  </si>
-  <si>
-    <t>960 Central Expy  Santa Clara CA 95050</t>
+    <t>Bayview Hunters Point</t>
+  </si>
+  <si>
+    <t>1625 Carroll Ave San Francisco  San Francisco CA 94124</t>
   </si>
   <si>
     <t>Alza Corporation</t>
@@ -503,12 +509,6 @@
     <t>700 Eubanks Drive  Vacaville CA 95688</t>
   </si>
   <si>
-    <t>Bayview Hunters Point</t>
-  </si>
-  <si>
-    <t>1625 Carroll Ave San Francisco  San Francisco CA 94124</t>
-  </si>
-  <si>
     <t>Talis Biomedical Corporation</t>
   </si>
   <si>
@@ -521,6 +521,12 @@
     <t>189 The Grove Dr.  Los Angeles CA 90036</t>
   </si>
   <si>
+    <t>Robinhood Markets, Inc.</t>
+  </si>
+  <si>
+    <t>85 Willow Road  Menlo Park CA 94025</t>
+  </si>
+  <si>
     <t>Tulare County</t>
   </si>
   <si>
@@ -530,30 +536,33 @@
     <t>d:115 S. West Street  Tulare CA 93274</t>
   </si>
   <si>
-    <t>Robinhood Markets, Inc.</t>
-  </si>
-  <si>
-    <t>85 Willow Road  Menlo Park CA 94025</t>
-  </si>
-  <si>
     <t>Rivian Automotive, LLC</t>
   </si>
   <si>
+    <t>607 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>630 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>850 Hansen Way  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>119 Waterworks Way  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>14192 Franklin Avenue  Tustin CA 92780</t>
+  </si>
+  <si>
     <t>14600 Myford Road  Irvine CA 92606</t>
   </si>
   <si>
-    <t>850 Hansen Way  Palo Alto CA 94304</t>
-  </si>
-  <si>
-    <t>630 Hansen Way  Palo Alto CA 94304</t>
+    <t>1751 Kettering Street  Irvine CA 92614</t>
   </si>
   <si>
     <t>9750 Irvine Boulevard  Irvine CA 92618</t>
   </si>
   <si>
-    <t>119 Waterworks Way  Irvine CA 92618</t>
-  </si>
-  <si>
     <t>The Lafayette Hotel, Swim Club &amp; Bungalows</t>
   </si>
   <si>
@@ -563,31 +572,34 @@
     <t>2223 El Cajon Blvd  San Diego CA 92104</t>
   </si>
   <si>
-    <t>14192 Franklin Avenue  Tustin CA 92780</t>
-  </si>
-  <si>
-    <t>1751 Kettering Street  Irvine CA 92614</t>
-  </si>
-  <si>
-    <t>607 Hansen Way  Palo Alto CA 94304</t>
-  </si>
-  <si>
     <t>Modern Times Drinks, Inc.</t>
   </si>
   <si>
+    <t>549 S. Anaheim Blvd.  Anaheim CA 92805</t>
+  </si>
+  <si>
+    <t>3725 Greenwood St.  San Diego CA 92110</t>
+  </si>
+  <si>
+    <t>3612 Kurtz St.  San Dieg CA 92110</t>
+  </si>
+  <si>
     <t>3000 Upas St.  San Diego CA 92104</t>
   </si>
   <si>
     <t>470 S. Coast Hwy 101  Encinitas CA 92024</t>
   </si>
   <si>
-    <t>3725 Greenwood St.  San Diego CA 92110</t>
-  </si>
-  <si>
-    <t>549 S. Anaheim Blvd.  Anaheim CA 92805</t>
-  </si>
-  <si>
-    <t>3612 Kurtz St.  San Dieg CA 92110</t>
+    <t>Godspeed Logistics LLC</t>
+  </si>
+  <si>
+    <t>4187 Temple City Blvd.  Rosemead CA 91770</t>
+  </si>
+  <si>
+    <t>Safran Cabin Galleys US, Inc.</t>
+  </si>
+  <si>
+    <t>17311 Nichols Lane  Huntington Beach CA 92647</t>
   </si>
   <si>
     <t>Hubbell Power Systems</t>
@@ -605,34 +617,34 @@
     <t>1654 Sunnydale Avenue  San Francisco CA 94134</t>
   </si>
   <si>
-    <t>Godspeed Logistics LLC</t>
-  </si>
-  <si>
-    <t>4187 Temple City Blvd.  Rosemead CA 91770</t>
-  </si>
-  <si>
     <t>1095 Connecticut St.  San Francisco CA 94107</t>
   </si>
   <si>
-    <t>Safran Cabin Galleys US, Inc.</t>
-  </si>
-  <si>
-    <t>17311 Nichols Lane  Huntington Beach CA 92647</t>
-  </si>
-  <si>
     <t>HCI, LLC</t>
   </si>
   <si>
+    <t>5924 Fremont Street  Riverside CA 92504</t>
+  </si>
+  <si>
     <t>6830 Airport Drive Suite A  Riverside CA 92504</t>
   </si>
   <si>
+    <t>6807 Airport Drive  Riverside CA 92504</t>
+  </si>
+  <si>
     <t>11080 Cherry Avenue  Fontana CA 92337</t>
   </si>
   <si>
-    <t>6807 Airport Drive  Riverside CA 92504</t>
-  </si>
-  <si>
-    <t>5924 Fremont Street  Riverside CA 92504</t>
+    <t>Fasnap Corporation</t>
+  </si>
+  <si>
+    <t>1320 N. Jefferson St.  Anaheim CA 92807</t>
+  </si>
+  <si>
+    <t>Wallboard Tool Co., Inc.</t>
+  </si>
+  <si>
+    <t>1697 Seabright Ave  Long Beach CA 90813</t>
   </si>
   <si>
     <t>Tempo Automation, Inc.</t>
@@ -641,60 +653,63 @@
     <t>2460 Alameda St.  San Francisco CA 94103</t>
   </si>
   <si>
-    <t>Wallboard Tool Co., Inc.</t>
-  </si>
-  <si>
-    <t>1697 Seabright Ave  Long Beach CA 90813</t>
-  </si>
-  <si>
-    <t>Fasnap Corporation</t>
-  </si>
-  <si>
-    <t>1320 N. Jefferson St.  Anaheim CA 92807</t>
-  </si>
-  <si>
     <t>Shift Technologies Inc.</t>
   </si>
   <si>
+    <t>12910 Mulberry Drive  Whittier CA 90602</t>
+  </si>
+  <si>
     <t>2000 Maritime Street #100  Oakland CA 94607</t>
   </si>
   <si>
+    <t>Teva Parental Medicines, Inc.</t>
+  </si>
+  <si>
+    <t>19 Hughes  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>175 Commerce Circle  Sacramento CA 95815</t>
+  </si>
+  <si>
+    <t>3939 Market Street  San Diego CA 92102</t>
+  </si>
+  <si>
     <t>21243 S Avalon Blvd  Carson CA 90745</t>
   </si>
   <si>
-    <t>Teva Parental Medicines, Inc.</t>
-  </si>
-  <si>
-    <t>19 Hughes  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>175 Commerce Circle  Sacramento CA 95815</t>
-  </si>
-  <si>
-    <t>12910 Mulberry Drive  Whittier CA 90602</t>
-  </si>
-  <si>
-    <t>3939 Market Street  San Diego CA 92102</t>
+    <t>Amador County</t>
+  </si>
+  <si>
+    <t>Timber Products Company</t>
+  </si>
+  <si>
+    <t>11610 Ampine Fibreform Road  Sutter Creek CA 95685</t>
   </si>
   <si>
     <t>Atara Biotherapeutics</t>
   </si>
   <si>
+    <t>611 Gateway Blvd #900  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Malwarebytes</t>
+  </si>
+  <si>
+    <t>3979 Freedom Circle  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Avanir Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>30 Enterprise, Suite 200  Aliso Viejo CA 92656</t>
+  </si>
+  <si>
     <t>2380 Conejo Spectrum St, Suite 200  Thousand Oaks CA 91320</t>
   </si>
   <si>
     <t>1280 Rancho Conejo Blvd.  Thousand Oaks CA 91320</t>
   </si>
   <si>
-    <t>Amador County</t>
-  </si>
-  <si>
-    <t>Timber Products Company</t>
-  </si>
-  <si>
-    <t>11610 Ampine Fibreform Road  Sutter Creek CA 95685</t>
-  </si>
-  <si>
     <t>Marin County</t>
   </si>
   <si>
@@ -704,19 +719,13 @@
     <t>111 McInnis Parkway  San Rafael CA 94903</t>
   </si>
   <si>
-    <t>Avanir Pharmaceuticals, Inc.</t>
-  </si>
-  <si>
-    <t>30 Enterprise, Suite 200  Aliso Viejo CA 92656</t>
-  </si>
-  <si>
-    <t>611 Gateway Blvd #900  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>Malwarebytes</t>
-  </si>
-  <si>
-    <t>3979 Freedom Circle  Santa Clara CA 95054</t>
+    <t>Fresno County</t>
+  </si>
+  <si>
+    <t>Promenade Care Center LLC</t>
+  </si>
+  <si>
+    <t>2715 Fresno Street  Fresno CA 93721</t>
   </si>
   <si>
     <t>Silgan Containers</t>
@@ -725,15 +734,6 @@
     <t>567 S. Riverside Drive  Modesto CA 95354</t>
   </si>
   <si>
-    <t>Fresno County</t>
-  </si>
-  <si>
-    <t>Promenade Care Center LLC</t>
-  </si>
-  <si>
-    <t>2715 Fresno Street  Fresno CA 93721</t>
-  </si>
-  <si>
     <t>430 Doherty Avenue  Modesto CA 95354</t>
   </si>
   <si>
@@ -782,6 +782,33 @@
     <t>2100 South Blosser Road  Santa Maria CA 93458</t>
   </si>
   <si>
+    <t>Snap, Inc. wholly owned subsidiary of PSA Risk Management Services Inc.</t>
+  </si>
+  <si>
+    <t>3000 31st Street  Santa Monica CA 90405</t>
+  </si>
+  <si>
+    <t>Infineon Technologies Americas Corp.</t>
+  </si>
+  <si>
+    <t>41915 Business Park Drive  Temecula CA 92590</t>
+  </si>
+  <si>
+    <t>Snap Inc., subsidiary of PSA Risk Management Services</t>
+  </si>
+  <si>
+    <t>395 Page Mill Road, 3rd Floor  Palo Alto CA 94306</t>
+  </si>
+  <si>
+    <t>Elwyn California</t>
+  </si>
+  <si>
+    <t>18325 Mt. Baldy Circle  Fountain Valley CA 92708</t>
+  </si>
+  <si>
+    <t>875 Howard St, 6th Floor  San Francisco CA 94109</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -809,9 +836,9 @@
     <t>WARN Summary</t>
   </si>
   <si>
-    <t xml:space="preserve"> Filter By Date: Received Date
+    <t xml:space="preserve">  Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 8/31/2022
+ End Date: 9/5/2022
 </t>
   </si>
   <si>
@@ -883,6 +910,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFDCDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFDCDCDC"/>
       </patternFill>
@@ -890,18 +929,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFDCDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1225,7 +1252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1281,6 +1308,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1297,72 +1373,26 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1644,26 +1674,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R135"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="5" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" customWidth="1"/>
-    <col min="13" max="13" width="7" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1678,110 +1708,110 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:18" ht="37.5" customHeight="1">
-      <c r="A2" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
+      <c r="A2" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="34" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="35" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="35" t="s">
+      <c r="J3" s="25"/>
+      <c r="K3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="36"/>
-      <c r="M3" s="38" t="s">
+      <c r="L3" s="25"/>
+      <c r="M3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="39"/>
+      <c r="N3" s="28"/>
     </row>
     <row r="4" spans="1:18" ht="24.75">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="41" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="44"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="42" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="43"/>
-      <c r="K4" s="42" t="s">
+      <c r="J4" s="32"/>
+      <c r="K4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="43"/>
-      <c r="M4" s="45" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="46"/>
+      <c r="N4" s="35"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>44735</v>
+        <v>44727</v>
       </c>
       <c r="C5" s="4">
         <v>44750</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="3">
-        <v>44796</v>
+        <v>44897</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>10</v>
@@ -1793,7 +1823,7 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="8">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="9" t="s">
@@ -1806,14 +1836,14 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>44727</v>
+        <v>44736</v>
       </c>
       <c r="C6" s="13">
         <v>44750</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="12">
-        <v>44897</v>
+        <v>44794</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>14</v>
@@ -1821,43 +1851,43 @@
       <c r="G6" s="7"/>
       <c r="H6" s="5"/>
       <c r="I6" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="15">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N6" s="10"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>44736</v>
+        <v>44735</v>
       </c>
       <c r="C7" s="4">
         <v>44750</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="3">
-        <v>44794</v>
+        <v>44796</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="5"/>
       <c r="I7" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="9" t="s">
@@ -1867,7 +1897,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B8" s="12">
         <v>44735</v>
@@ -1880,26 +1910,26 @@
         <v>44796</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="5"/>
       <c r="I8" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="15">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N8" s="10"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3">
         <v>44735</v>
@@ -1912,16 +1942,16 @@
         <v>44796</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="5"/>
       <c r="I9" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="9" t="s">
@@ -1931,71 +1961,71 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B10" s="12">
-        <v>44739</v>
+        <v>44727</v>
       </c>
       <c r="C10" s="13">
         <v>44753</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="12">
-        <v>44799</v>
+        <v>44784</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="5"/>
       <c r="I10" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="15">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N10" s="10"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
-        <v>44727</v>
+        <v>44739</v>
       </c>
       <c r="C11" s="4">
         <v>44753</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="3">
-        <v>44784</v>
+        <v>44799</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="5"/>
       <c r="I11" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="8">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N11" s="10"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12">
         <v>44741</v>
@@ -2008,12 +2038,12 @@
         <v>44800</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="5"/>
       <c r="I12" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="15">
@@ -2021,35 +2051,35 @@
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>44727</v>
+        <v>44743</v>
       </c>
       <c r="C13" s="4">
         <v>44753</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3">
-        <v>44784</v>
+        <v>44766</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="5"/>
       <c r="I13" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="8">
-        <v>37</v>
+        <v>368</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="9" t="s">
@@ -2059,7 +2089,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12">
         <v>44739</v>
@@ -2072,48 +2102,48 @@
         <v>44799</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="5"/>
       <c r="I14" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="15">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>44741</v>
+        <v>44727</v>
       </c>
       <c r="C15" s="4">
         <v>44753</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="3">
-        <v>44801</v>
+        <v>44784</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="5"/>
       <c r="I15" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="8">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="9" t="s">
@@ -2123,61 +2153,61 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="11" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B16" s="12">
-        <v>44743</v>
+        <v>44727</v>
       </c>
       <c r="C16" s="13">
         <v>44753</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="12">
-        <v>44766</v>
+        <v>44784</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="5"/>
       <c r="I16" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="15">
-        <v>368</v>
+        <v>68</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N16" s="10"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>44727</v>
+        <v>44741</v>
       </c>
       <c r="C17" s="4">
         <v>44753</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="3">
-        <v>44784</v>
+        <v>44801</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="5"/>
       <c r="I17" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="8">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="9" t="s">
@@ -2187,103 +2217,103 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B18" s="12">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C18" s="13">
         <v>44754</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="12">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="5"/>
       <c r="I18" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="15">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B19" s="3">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C19" s="4">
         <v>44754</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="3">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="5"/>
       <c r="I19" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="8">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N19" s="10"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="11" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B20" s="12">
-        <v>44743</v>
+        <v>44739</v>
       </c>
       <c r="C20" s="13">
         <v>44754</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="12">
-        <v>44804</v>
+        <v>44800</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="5"/>
       <c r="I20" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21" s="3">
         <v>44739</v>
@@ -2296,58 +2326,58 @@
         <v>44800</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="5"/>
       <c r="I21" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N21" s="10"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B22" s="12">
-        <v>44732</v>
+        <v>44739</v>
       </c>
       <c r="C22" s="13">
         <v>44754</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="12">
-        <v>44926</v>
+        <v>44800</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="5"/>
       <c r="I22" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="15">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N22" s="10"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B23" s="3">
         <v>44743</v>
@@ -2360,12 +2390,12 @@
         <v>44804</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="5"/>
       <c r="I23" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="8">
@@ -2373,39 +2403,39 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N23" s="10"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="11" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B24" s="12">
-        <v>44742</v>
+        <v>44732</v>
       </c>
       <c r="C24" s="13">
         <v>44754</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="12">
-        <v>44802</v>
+        <v>44926</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="5"/>
       <c r="I24" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="15">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N24" s="10"/>
     </row>
@@ -2414,17 +2444,17 @@
         <v>13</v>
       </c>
       <c r="B25" s="3">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C25" s="4">
         <v>44754</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="3">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="5"/>
@@ -2433,11 +2463,11 @@
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N25" s="10"/>
     </row>
@@ -2446,17 +2476,17 @@
         <v>13</v>
       </c>
       <c r="B26" s="12">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C26" s="13">
         <v>44754</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="12">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="5"/>
@@ -2465,62 +2495,62 @@
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="15">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N26" s="10"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3">
-        <v>44743</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="4">
         <v>44754</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="3">
-        <v>44804</v>
+        <v>44802</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="5"/>
       <c r="I27" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="8">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="11" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B28" s="12">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C28" s="13">
         <v>44754</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="12">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="5"/>
@@ -2529,30 +2559,30 @@
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="15">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B29" s="3">
-        <v>44739</v>
+        <v>44743</v>
       </c>
       <c r="C29" s="4">
         <v>44754</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="3">
-        <v>44800</v>
+        <v>44804</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="5"/>
@@ -2561,17 +2591,17 @@
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N29" s="10"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="11" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B30" s="12">
         <v>44743</v>
@@ -2584,16 +2614,16 @@
         <v>44804</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="5"/>
       <c r="I30" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="15">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="16" t="s">
@@ -2603,7 +2633,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B31" s="3">
         <v>44743</v>
@@ -2616,26 +2646,26 @@
         <v>44804</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="5"/>
       <c r="I31" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="8">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N31" s="10"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B32" s="12">
         <v>44743</v>
@@ -2648,26 +2678,26 @@
         <v>44804</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="5"/>
       <c r="I32" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="15">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N32" s="10"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="B33" s="3">
         <v>44743</v>
@@ -2680,16 +2710,16 @@
         <v>44804</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="5"/>
       <c r="I33" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="8">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="9" t="s">
@@ -2699,7 +2729,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B34" s="12">
         <v>44743</v>
@@ -2712,16 +2742,16 @@
         <v>44804</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="5"/>
       <c r="I34" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="16" t="s">
@@ -2731,17 +2761,17 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B35" s="3">
-        <v>44743</v>
+        <v>44747</v>
       </c>
       <c r="C35" s="4">
         <v>44756</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="3">
-        <v>44799</v>
+        <v>44788</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>63</v>
@@ -2749,11 +2779,11 @@
       <c r="G35" s="7"/>
       <c r="H35" s="5"/>
       <c r="I35" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="8">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="9" t="s">
@@ -2763,125 +2793,125 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B36" s="12">
-        <v>44748</v>
+        <v>44743</v>
       </c>
       <c r="C36" s="13">
         <v>44756</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="12">
-        <v>44809</v>
+        <v>44799</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="5"/>
       <c r="I36" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="15">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N36" s="10"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B37" s="3">
-        <v>44753</v>
+        <v>44743</v>
       </c>
       <c r="C37" s="4">
         <v>44756</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="3">
-        <v>44813</v>
+        <v>44799</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="5"/>
       <c r="I37" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="8">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N37" s="10"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="11" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B38" s="12">
-        <v>44743</v>
+        <v>44748</v>
       </c>
       <c r="C38" s="13">
         <v>44756</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="12">
-        <v>44799</v>
+        <v>44809</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="5"/>
       <c r="I38" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="15">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N38" s="10"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B39" s="3">
-        <v>44743</v>
+        <v>44753</v>
       </c>
       <c r="C39" s="4">
         <v>44756</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="3">
-        <v>44799</v>
+        <v>44813</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="5"/>
       <c r="I39" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="8">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="9" t="s">
@@ -2891,17 +2921,17 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B40" s="12">
-        <v>44747</v>
+        <v>44743</v>
       </c>
       <c r="C40" s="13">
         <v>44756</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="12">
-        <v>44788</v>
+        <v>44799</v>
       </c>
       <c r="F40" s="14" t="s">
         <v>63</v>
@@ -2909,11 +2939,11 @@
       <c r="G40" s="7"/>
       <c r="H40" s="5"/>
       <c r="I40" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="15">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="16" t="s">
@@ -2923,7 +2953,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3">
         <v>44749</v>
@@ -2933,7 +2963,7 @@
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="3">
-        <v>44810</v>
+        <v>44809</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>73</v>
@@ -2941,11 +2971,11 @@
       <c r="G41" s="7"/>
       <c r="H41" s="5"/>
       <c r="I41" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="8">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="9" t="s">
@@ -2955,7 +2985,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="11" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B42" s="12">
         <v>44749</v>
@@ -2965,7 +2995,7 @@
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="12">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>75</v>
@@ -2973,11 +3003,11 @@
       <c r="G42" s="7"/>
       <c r="H42" s="5"/>
       <c r="I42" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="15">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="16" t="s">
@@ -2987,7 +3017,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B43" s="3">
         <v>44749</v>
@@ -3005,7 +3035,7 @@
       <c r="G43" s="7"/>
       <c r="H43" s="5"/>
       <c r="I43" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="8">
@@ -3037,7 +3067,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="5"/>
       <c r="I44" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="15">
@@ -3051,17 +3081,17 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B45" s="3">
-        <v>44749</v>
+        <v>44754</v>
       </c>
       <c r="C45" s="4">
         <v>44761</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="3">
-        <v>44749</v>
+        <v>44820</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>82</v>
@@ -3069,11 +3099,11 @@
       <c r="G45" s="7"/>
       <c r="H45" s="5"/>
       <c r="I45" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="8">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="9" t="s">
@@ -3083,17 +3113,17 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="11" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B46" s="12">
-        <v>44754</v>
+        <v>44749</v>
       </c>
       <c r="C46" s="13">
         <v>44761</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="12">
-        <v>44820</v>
+        <v>44749</v>
       </c>
       <c r="F46" s="14" t="s">
         <v>84</v>
@@ -3101,11 +3131,11 @@
       <c r="G46" s="7"/>
       <c r="H46" s="5"/>
       <c r="I46" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="15">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="16" t="s">
@@ -3115,61 +3145,61 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B47" s="3">
-        <v>44755</v>
+        <v>44749</v>
       </c>
       <c r="C47" s="4">
         <v>44761</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="3">
-        <v>44806</v>
+        <v>44749</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="5"/>
       <c r="I47" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="8">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N47" s="10"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="11" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B48" s="12">
-        <v>44749</v>
+        <v>44755</v>
       </c>
       <c r="C48" s="13">
         <v>44761</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="12">
-        <v>44749</v>
+        <v>44806</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="5"/>
       <c r="I48" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="15">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="16" t="s">
@@ -3179,7 +3209,7 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B49" s="3">
         <v>44754</v>
@@ -3197,7 +3227,7 @@
       <c r="G49" s="7"/>
       <c r="H49" s="5"/>
       <c r="I49" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="8">
@@ -3211,7 +3241,7 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B50" s="12">
         <v>44692</v>
@@ -3229,7 +3259,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="5"/>
       <c r="I50" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="15">
@@ -3261,7 +3291,7 @@
       <c r="G51" s="7"/>
       <c r="H51" s="5"/>
       <c r="I51" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="8">
@@ -3293,11 +3323,11 @@
       <c r="G52" s="7"/>
       <c r="H52" s="5"/>
       <c r="I52" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="15">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="16" t="s">
@@ -3307,33 +3337,33 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B53" s="3">
-        <v>44700</v>
+        <v>44753</v>
       </c>
       <c r="C53" s="4">
         <v>44763</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="3">
-        <v>44760</v>
+        <v>44795</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="5"/>
       <c r="I53" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N53" s="10"/>
     </row>
@@ -3357,15 +3387,15 @@
       <c r="G54" s="7"/>
       <c r="H54" s="5"/>
       <c r="I54" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="15">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N54" s="10"/>
     </row>
@@ -3389,43 +3419,43 @@
       <c r="G55" s="7"/>
       <c r="H55" s="5"/>
       <c r="I55" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="8">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N55" s="10"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B56" s="12">
-        <v>44753</v>
+        <v>44700</v>
       </c>
       <c r="C56" s="13">
         <v>44763</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="12">
-        <v>44795</v>
+        <v>44760</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="5"/>
       <c r="I56" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="15">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="16" t="s">
@@ -3435,7 +3465,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B57" s="3">
         <v>44700</v>
@@ -3448,12 +3478,12 @@
         <v>44760</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="5"/>
       <c r="I57" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="8">
@@ -3467,17 +3497,17 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="11" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B58" s="12">
-        <v>44756</v>
+        <v>44755</v>
       </c>
       <c r="C58" s="13">
         <v>44764</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="12">
-        <v>44816</v>
+        <v>44755</v>
       </c>
       <c r="F58" s="14" t="s">
         <v>106</v>
@@ -3485,43 +3515,43 @@
       <c r="G58" s="7"/>
       <c r="H58" s="5"/>
       <c r="I58" s="14" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="15">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N58" s="10"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="2" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B59" s="3">
-        <v>44755</v>
+        <v>44762</v>
       </c>
       <c r="C59" s="4">
         <v>44764</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="3">
-        <v>44755</v>
+        <v>44837</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="5"/>
       <c r="I59" s="6" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="8">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="9" t="s">
@@ -3531,17 +3561,17 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B60" s="12">
-        <v>44762</v>
+        <v>44756</v>
       </c>
       <c r="C60" s="13">
         <v>44764</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="12">
-        <v>44837</v>
+        <v>44816</v>
       </c>
       <c r="F60" s="14" t="s">
         <v>111</v>
@@ -3549,11 +3579,11 @@
       <c r="G60" s="7"/>
       <c r="H60" s="5"/>
       <c r="I60" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="15">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="16" t="s">
@@ -3563,81 +3593,81 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="2" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B61" s="3">
-        <v>44757</v>
+        <v>44755</v>
       </c>
       <c r="C61" s="4">
         <v>44764</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="3">
-        <v>44819</v>
+        <v>44816</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="5"/>
       <c r="I61" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="8">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N61" s="10"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B62" s="12">
-        <v>44755</v>
+        <v>44762</v>
       </c>
       <c r="C62" s="13">
         <v>44764</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="12">
-        <v>44816</v>
+        <v>44835</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="5"/>
       <c r="I62" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="15">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N62" s="10"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="2" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="B63" s="3">
-        <v>44762</v>
+        <v>44756</v>
       </c>
       <c r="C63" s="4">
         <v>44764</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3">
-        <v>44835</v>
+        <v>44818</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>119</v>
@@ -3649,7 +3679,7 @@
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="8">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="9" t="s">
@@ -3659,17 +3689,17 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B64" s="12">
-        <v>44756</v>
+        <v>44757</v>
       </c>
       <c r="C64" s="13">
         <v>44764</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="12">
-        <v>44818</v>
+        <v>44819</v>
       </c>
       <c r="F64" s="14" t="s">
         <v>121</v>
@@ -3677,11 +3707,11 @@
       <c r="G64" s="7"/>
       <c r="H64" s="5"/>
       <c r="I64" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="15">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="16" t="s">
@@ -3691,7 +3721,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B65" s="3">
         <v>44761</v>
@@ -3709,7 +3739,7 @@
       <c r="G65" s="7"/>
       <c r="H65" s="5"/>
       <c r="I65" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="8">
@@ -3723,81 +3753,81 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="11" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="B66" s="12">
-        <v>44767</v>
+        <v>44764</v>
       </c>
       <c r="C66" s="13">
         <v>44768</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="12">
-        <v>44827</v>
+        <v>44761</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="5"/>
       <c r="I66" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="15">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N66" s="10"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B67" s="3">
-        <v>44763</v>
+        <v>44767</v>
       </c>
       <c r="C67" s="4">
         <v>44768</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="3">
-        <v>44834</v>
+        <v>44827</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="5"/>
       <c r="I67" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="8">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N67" s="10"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="11" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B68" s="12">
-        <v>44764</v>
+        <v>44763</v>
       </c>
       <c r="C68" s="13">
         <v>44768</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="12">
-        <v>44761</v>
+        <v>44834</v>
       </c>
       <c r="F68" s="14" t="s">
         <v>130</v>
@@ -3805,11 +3835,11 @@
       <c r="G68" s="7"/>
       <c r="H68" s="5"/>
       <c r="I68" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="15">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="16" t="s">
@@ -3819,7 +3849,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B69" s="3">
         <v>44760</v>
@@ -3837,7 +3867,7 @@
       <c r="G69" s="7"/>
       <c r="H69" s="5"/>
       <c r="I69" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="8">
@@ -3851,7 +3881,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B70" s="12">
         <v>44760</v>
@@ -3869,7 +3899,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="5"/>
       <c r="I70" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="15">
@@ -3883,7 +3913,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B71" s="3">
         <v>44760</v>
@@ -3901,7 +3931,7 @@
       <c r="G71" s="7"/>
       <c r="H71" s="5"/>
       <c r="I71" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="8">
@@ -3915,7 +3945,7 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B72" s="12">
         <v>44768</v>
@@ -3933,7 +3963,7 @@
       <c r="G72" s="7"/>
       <c r="H72" s="5"/>
       <c r="I72" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="15">
@@ -3947,17 +3977,17 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="2" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B73" s="3">
-        <v>44769</v>
+        <v>44762</v>
       </c>
       <c r="C73" s="4">
         <v>44770</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="3">
-        <v>44837</v>
+        <v>44822</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>139</v>
@@ -3965,11 +3995,11 @@
       <c r="G73" s="7"/>
       <c r="H73" s="5"/>
       <c r="I73" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="8">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="9" t="s">
@@ -3979,7 +4009,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" s="12">
         <v>44762</v>
@@ -3992,12 +4022,12 @@
         <v>44829</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="5"/>
       <c r="I74" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J74" s="5"/>
       <c r="K74" s="15">
@@ -4005,13 +4035,13 @@
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N74" s="10"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B75" s="3">
         <v>44770</v>
@@ -4024,12 +4054,12 @@
         <v>44865</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="5"/>
       <c r="I75" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J75" s="5"/>
       <c r="K75" s="8">
@@ -4037,45 +4067,45 @@
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N75" s="10"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="11" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B76" s="12">
-        <v>44762</v>
+        <v>44769</v>
       </c>
       <c r="C76" s="13">
         <v>44770</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="12">
-        <v>44822</v>
+        <v>44837</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="5"/>
       <c r="I76" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="15">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N76" s="10"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B77" s="3">
         <v>44774</v>
@@ -4085,7 +4115,7 @@
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="3">
-        <v>44841</v>
+        <v>44834</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>145</v>
@@ -4097,7 +4127,7 @@
       </c>
       <c r="J77" s="5"/>
       <c r="K77" s="8">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="9" t="s">
@@ -4107,7 +4137,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="11" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B78" s="12">
         <v>44774</v>
@@ -4117,7 +4147,7 @@
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="12">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="F78" s="14" t="s">
         <v>147</v>
@@ -4125,11 +4155,11 @@
       <c r="G78" s="7"/>
       <c r="H78" s="5"/>
       <c r="I78" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J78" s="5"/>
       <c r="K78" s="15">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="16" t="s">
@@ -4139,7 +4169,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" s="3">
         <v>44774</v>
@@ -4157,7 +4187,7 @@
       <c r="G79" s="7"/>
       <c r="H79" s="5"/>
       <c r="I79" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J79" s="5"/>
       <c r="K79" s="8">
@@ -4171,7 +4201,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B80" s="12">
         <v>44767</v>
@@ -4189,7 +4219,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="5"/>
       <c r="I80" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="15">
@@ -4203,10 +4233,10 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="B81" s="3">
-        <v>44770</v>
+        <v>44775</v>
       </c>
       <c r="C81" s="4">
         <v>44778</v>
@@ -4216,29 +4246,29 @@
         <v>44835</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="5"/>
       <c r="I81" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J81" s="5"/>
       <c r="K81" s="8">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N81" s="10"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="11" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="B82" s="12">
-        <v>44775</v>
+        <v>44770</v>
       </c>
       <c r="C82" s="13">
         <v>44778</v>
@@ -4257,7 +4287,7 @@
       </c>
       <c r="J82" s="5"/>
       <c r="K82" s="15">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="16" t="s">
@@ -4267,7 +4297,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B83" s="3">
         <v>44769</v>
@@ -4285,11 +4315,11 @@
       <c r="G83" s="7"/>
       <c r="H83" s="5"/>
       <c r="I83" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="8">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="9" t="s">
@@ -4299,7 +4329,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B84" s="12">
         <v>44769</v>
@@ -4317,11 +4347,11 @@
       <c r="G84" s="7"/>
       <c r="H84" s="5"/>
       <c r="I84" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="15">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="16" t="s">
@@ -4331,7 +4361,7 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B85" s="3">
         <v>44769</v>
@@ -4349,11 +4379,11 @@
       <c r="G85" s="7"/>
       <c r="H85" s="5"/>
       <c r="I85" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="8">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="9" t="s">
@@ -4363,7 +4393,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B86" s="12">
         <v>44769</v>
@@ -4381,11 +4411,11 @@
       <c r="G86" s="7"/>
       <c r="H86" s="5"/>
       <c r="I86" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="15">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="16" t="s">
@@ -4395,7 +4425,7 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B87" s="3">
         <v>44769</v>
@@ -4413,11 +4443,11 @@
       <c r="G87" s="7"/>
       <c r="H87" s="5"/>
       <c r="I87" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="9" t="s">
@@ -4427,39 +4457,39 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="11" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B88" s="12">
-        <v>44774</v>
+        <v>44769</v>
       </c>
       <c r="C88" s="13">
         <v>44781</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="12">
-        <v>44836</v>
+        <v>44841</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="5"/>
       <c r="I88" s="14" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="15">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N88" s="10"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B89" s="3">
         <v>44769</v>
@@ -4477,21 +4507,21 @@
       <c r="G89" s="7"/>
       <c r="H89" s="5"/>
       <c r="I89" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J89" s="5"/>
       <c r="K89" s="8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N89" s="10"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B90" s="12">
         <v>44769</v>
@@ -4509,43 +4539,43 @@
       <c r="G90" s="7"/>
       <c r="H90" s="5"/>
       <c r="I90" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J90" s="5"/>
       <c r="K90" s="15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N90" s="10"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B91" s="3">
-        <v>44769</v>
+        <v>44774</v>
       </c>
       <c r="C91" s="4">
         <v>44781</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="3">
-        <v>44841</v>
+        <v>44836</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="5"/>
       <c r="I91" s="6" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="8">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="9" t="s">
@@ -4555,7 +4585,7 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="11" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B92" s="12">
         <v>44782</v>
@@ -4573,11 +4603,11 @@
       <c r="G92" s="7"/>
       <c r="H92" s="5"/>
       <c r="I92" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="15">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="16" t="s">
@@ -4587,7 +4617,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B93" s="3">
         <v>44782</v>
@@ -4605,11 +4635,11 @@
       <c r="G93" s="7"/>
       <c r="H93" s="5"/>
       <c r="I93" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J93" s="5"/>
       <c r="K93" s="8">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="9" t="s">
@@ -4619,7 +4649,7 @@
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B94" s="12">
         <v>44782</v>
@@ -4637,11 +4667,11 @@
       <c r="G94" s="7"/>
       <c r="H94" s="5"/>
       <c r="I94" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="15">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="16" t="s">
@@ -4651,7 +4681,7 @@
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B95" s="3">
         <v>44782</v>
@@ -4669,11 +4699,11 @@
       <c r="G95" s="7"/>
       <c r="H95" s="5"/>
       <c r="I95" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J95" s="5"/>
       <c r="K95" s="8">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="9" t="s">
@@ -4683,7 +4713,7 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B96" s="12">
         <v>44782</v>
@@ -4701,11 +4731,11 @@
       <c r="G96" s="7"/>
       <c r="H96" s="5"/>
       <c r="I96" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="16" t="s">
@@ -4715,17 +4745,17 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="2" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B97" s="3">
-        <v>44778</v>
+        <v>44776</v>
       </c>
       <c r="C97" s="4">
         <v>44783</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="3">
-        <v>44839</v>
+        <v>44838</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>176</v>
@@ -4733,11 +4763,11 @@
       <c r="G97" s="7"/>
       <c r="H97" s="5"/>
       <c r="I97" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="8">
-        <v>193</v>
+        <v>64</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="9" t="s">
@@ -4747,17 +4777,17 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="11" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="B98" s="12">
-        <v>44771</v>
+        <v>44777</v>
       </c>
       <c r="C98" s="13">
         <v>44783</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="12">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="F98" s="14" t="s">
         <v>178</v>
@@ -4769,7 +4799,7 @@
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="15">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="16" t="s">
@@ -4779,20 +4809,20 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="2" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="B99" s="3">
-        <v>44771</v>
+        <v>44778</v>
       </c>
       <c r="C99" s="4">
         <v>44783</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3">
-        <v>44834</v>
+        <v>44839</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="5"/>
@@ -4801,49 +4831,49 @@
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="8">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N99" s="10"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B100" s="12">
-        <v>44776</v>
+        <v>44771</v>
       </c>
       <c r="C100" s="13">
         <v>44783</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="12">
-        <v>44838</v>
+        <v>44834</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="5"/>
       <c r="I100" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="15">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N100" s="10"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B101" s="3">
         <v>44771</v>
@@ -4856,48 +4886,48 @@
         <v>44834</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="5"/>
       <c r="I101" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N101" s="10"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="11" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="B102" s="12">
-        <v>44777</v>
+        <v>44771</v>
       </c>
       <c r="C102" s="13">
         <v>44783</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="12">
-        <v>44841</v>
+        <v>44834</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="5"/>
       <c r="I102" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J102" s="5"/>
       <c r="K102" s="15">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="16" t="s">
@@ -4907,7 +4937,7 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B103" s="3">
         <v>44781</v>
@@ -4925,11 +4955,11 @@
       <c r="G103" s="7"/>
       <c r="H103" s="5"/>
       <c r="I103" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="8">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="9" t="s">
@@ -4939,7 +4969,7 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B104" s="12">
         <v>44781</v>
@@ -4957,11 +4987,11 @@
       <c r="G104" s="7"/>
       <c r="H104" s="5"/>
       <c r="I104" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J104" s="5"/>
       <c r="K104" s="15">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="16" t="s">
@@ -4971,7 +5001,7 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B105" s="3">
         <v>44781</v>
@@ -4989,7 +5019,7 @@
       <c r="G105" s="7"/>
       <c r="H105" s="5"/>
       <c r="I105" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="8">
@@ -5003,7 +5033,7 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="11" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B106" s="12">
         <v>44781</v>
@@ -5021,11 +5051,11 @@
       <c r="G106" s="7"/>
       <c r="H106" s="5"/>
       <c r="I106" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J106" s="5"/>
       <c r="K106" s="15">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="16" t="s">
@@ -5035,17 +5065,17 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="2" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="B107" s="3">
-        <v>44781</v>
+        <v>44784</v>
       </c>
       <c r="C107" s="4">
         <v>44788</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3">
-        <v>44792</v>
+        <v>44865</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>191</v>
@@ -5057,7 +5087,7 @@
       </c>
       <c r="J107" s="5"/>
       <c r="K107" s="8">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="9" t="s">
@@ -5067,7 +5097,7 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B108" s="12">
         <v>44774</v>
@@ -5085,7 +5115,7 @@
       <c r="G108" s="7"/>
       <c r="H108" s="5"/>
       <c r="I108" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="15">
@@ -5099,17 +5129,17 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="2" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="B109" s="3">
-        <v>44784</v>
+        <v>44781</v>
       </c>
       <c r="C109" s="4">
         <v>44788</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="3">
-        <v>44865</v>
+        <v>44792</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>195</v>
@@ -5117,11 +5147,11 @@
       <c r="G109" s="7"/>
       <c r="H109" s="5"/>
       <c r="I109" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J109" s="5"/>
       <c r="K109" s="8">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="L109" s="5"/>
       <c r="M109" s="9" t="s">
@@ -5149,11 +5179,11 @@
       <c r="G110" s="7"/>
       <c r="H110" s="5"/>
       <c r="I110" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J110" s="5"/>
       <c r="K110" s="15">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="16" t="s">
@@ -5163,7 +5193,7 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B111" s="3">
         <v>44782</v>
@@ -5181,11 +5211,11 @@
       <c r="G111" s="7"/>
       <c r="H111" s="5"/>
       <c r="I111" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="8">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="9" t="s">
@@ -5195,7 +5225,7 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B112" s="12">
         <v>44642</v>
@@ -5213,7 +5243,7 @@
       <c r="G112" s="7"/>
       <c r="H112" s="5"/>
       <c r="I112" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J112" s="5"/>
       <c r="K112" s="15">
@@ -5227,7 +5257,7 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B113" s="3">
         <v>44782</v>
@@ -5245,7 +5275,7 @@
       <c r="G113" s="7"/>
       <c r="H113" s="5"/>
       <c r="I113" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="8">
@@ -5259,7 +5289,7 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B114" s="12">
         <v>44782</v>
@@ -5281,7 +5311,7 @@
       </c>
       <c r="J114" s="5"/>
       <c r="K114" s="15">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="16" t="s">
@@ -5291,7 +5321,7 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B115" s="3">
         <v>44782</v>
@@ -5309,11 +5339,11 @@
       <c r="G115" s="7"/>
       <c r="H115" s="5"/>
       <c r="I115" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="8">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="9" t="s">
@@ -5323,20 +5353,20 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="11" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="B116" s="12">
-        <v>44781</v>
+        <v>44788</v>
       </c>
       <c r="C116" s="13">
         <v>44790</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="12">
-        <v>44841</v>
+        <v>44783</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="5"/>
@@ -5345,17 +5375,17 @@
       </c>
       <c r="J116" s="5"/>
       <c r="K116" s="15">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N116" s="10"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="2" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="B117" s="3">
         <v>44781</v>
@@ -5368,58 +5398,58 @@
         <v>44841</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="5"/>
       <c r="I117" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N117" s="10"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="11" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="B118" s="12">
-        <v>44788</v>
+        <v>44785</v>
       </c>
       <c r="C118" s="13">
         <v>44790</v>
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="12">
-        <v>44783</v>
+        <v>44788</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="5"/>
       <c r="I118" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="15">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N118" s="10"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="2" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
       <c r="B119" s="3">
         <v>44788</v>
@@ -5437,11 +5467,11 @@
       <c r="G119" s="7"/>
       <c r="H119" s="5"/>
       <c r="I119" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="8">
-        <v>578</v>
+        <v>16</v>
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="9" t="s">
@@ -5451,39 +5481,39 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="11" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B120" s="12">
-        <v>44788</v>
+        <v>44781</v>
       </c>
       <c r="C120" s="13">
         <v>44790</v>
       </c>
       <c r="D120" s="5"/>
       <c r="E120" s="12">
-        <v>44848</v>
+        <v>44841</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="5"/>
       <c r="I120" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J120" s="5"/>
       <c r="K120" s="15">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N120" s="10"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="2" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="B121" s="3">
         <v>44781</v>
@@ -5496,36 +5526,36 @@
         <v>44841</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="5"/>
       <c r="I121" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N121" s="10"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="11" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="B122" s="12">
-        <v>44785</v>
+        <v>44788</v>
       </c>
       <c r="C122" s="13">
         <v>44790</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="12">
-        <v>44788</v>
+        <v>44848</v>
       </c>
       <c r="F122" s="14" t="s">
         <v>217</v>
@@ -5537,7 +5567,7 @@
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="15">
-        <v>47</v>
+        <v>578</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="16" t="s">
@@ -5547,49 +5577,49 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="2" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="B123" s="3">
-        <v>44771</v>
+        <v>44776</v>
       </c>
       <c r="C123" s="4">
         <v>44791</v>
       </c>
       <c r="D123" s="5"/>
       <c r="E123" s="3">
-        <v>44837</v>
+        <v>44834</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="5"/>
       <c r="I123" s="6" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="8">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N123" s="10"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="11" t="s">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c r="B124" s="12">
-        <v>44776</v>
+        <v>44771</v>
       </c>
       <c r="C124" s="13">
         <v>44791</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="12">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="F124" s="14" t="s">
         <v>222</v>
@@ -5597,11 +5627,11 @@
       <c r="G124" s="7"/>
       <c r="H124" s="5"/>
       <c r="I124" s="14" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="15">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="16" t="s">
@@ -5611,7 +5641,7 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B125" s="3">
         <v>44784</v>
@@ -5624,12 +5654,12 @@
         <v>44844</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="5"/>
       <c r="I125" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="8">
@@ -5675,7 +5705,7 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B127" s="3">
         <v>44792</v>
@@ -5693,7 +5723,7 @@
       <c r="G127" s="7"/>
       <c r="H127" s="5"/>
       <c r="I127" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="8">
@@ -5707,7 +5737,7 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B128" s="12">
         <v>44798</v>
@@ -5725,7 +5755,7 @@
       <c r="G128" s="7"/>
       <c r="H128" s="5"/>
       <c r="I128" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="15">
@@ -5739,7 +5769,7 @@
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B129" s="3">
         <v>44799</v>
@@ -5757,7 +5787,7 @@
       <c r="G129" s="7"/>
       <c r="H129" s="5"/>
       <c r="I129" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J129" s="5"/>
       <c r="K129" s="8">
@@ -5771,7 +5801,7 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B130" s="12">
         <v>44802</v>
@@ -5789,7 +5819,7 @@
       <c r="G130" s="7"/>
       <c r="H130" s="5"/>
       <c r="I130" s="14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J130" s="5"/>
       <c r="K130" s="15">
@@ -5803,7 +5833,7 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B131" s="3">
         <v>44799</v>
@@ -5821,7 +5851,7 @@
       <c r="G131" s="7"/>
       <c r="H131" s="5"/>
       <c r="I131" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="8">
@@ -5835,7 +5865,7 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B132" s="12">
         <v>44799</v>
@@ -5853,7 +5883,7 @@
       <c r="G132" s="7"/>
       <c r="H132" s="5"/>
       <c r="I132" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="15">
@@ -5885,7 +5915,7 @@
       <c r="G133" s="7"/>
       <c r="H133" s="5"/>
       <c r="I133" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="8">
@@ -5897,82 +5927,267 @@
       </c>
       <c r="N133" s="10"/>
     </row>
-    <row r="134" spans="1:14" ht="30" customHeight="1">
-      <c r="A134" s="25" t="s">
+    <row r="134" spans="1:14">
+      <c r="A134" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B134" s="12">
+        <v>44804</v>
+      </c>
+      <c r="C134" s="13">
+        <v>44805</v>
+      </c>
+      <c r="D134" s="5"/>
+      <c r="E134" s="12">
+        <v>44805</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="5"/>
+      <c r="K134" s="15">
+        <v>401</v>
+      </c>
+      <c r="L134" s="5"/>
+      <c r="M134" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N134" s="10"/>
+    </row>
+    <row r="135" spans="1:14">
+      <c r="A135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B135" s="3">
+        <v>44804</v>
+      </c>
+      <c r="C135" s="4">
+        <v>44805</v>
+      </c>
+      <c r="D135" s="5"/>
+      <c r="E135" s="3">
+        <v>44866</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G135" s="7"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J135" s="5"/>
+      <c r="K135" s="8">
+        <v>375</v>
+      </c>
+      <c r="L135" s="5"/>
+      <c r="M135" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="N135" s="10"/>
+    </row>
+    <row r="136" spans="1:14">
+      <c r="A136" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B136" s="12">
+        <v>44804</v>
+      </c>
+      <c r="C136" s="13">
+        <v>44806</v>
+      </c>
+      <c r="D136" s="5"/>
+      <c r="E136" s="12">
+        <v>44805</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="G136" s="7"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="5"/>
+      <c r="K136" s="15">
+        <v>44</v>
+      </c>
+      <c r="L136" s="5"/>
+      <c r="M136" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="N136" s="10"/>
+    </row>
+    <row r="137" spans="1:14">
+      <c r="A137" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B137" s="3">
+        <v>44805</v>
+      </c>
+      <c r="C137" s="4">
+        <v>44806</v>
+      </c>
+      <c r="D137" s="5"/>
+      <c r="E137" s="3">
+        <v>44834</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="G137" s="7"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="5"/>
+      <c r="K137" s="8">
+        <v>51</v>
+      </c>
+      <c r="L137" s="5"/>
+      <c r="M137" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="N137" s="10"/>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="A138" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B138" s="12">
+        <v>44804</v>
+      </c>
+      <c r="C138" s="13">
+        <v>44806</v>
+      </c>
+      <c r="D138" s="5"/>
+      <c r="E138" s="12">
+        <v>44805</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G138" s="7"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="5"/>
+      <c r="K138" s="15">
+        <v>40</v>
+      </c>
+      <c r="L138" s="5"/>
+      <c r="M138" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="N138" s="10"/>
+    </row>
+    <row r="139" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A139" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B139" s="43"/>
+      <c r="C139" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="D139" s="45"/>
+      <c r="E139" s="46"/>
+      <c r="F139" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="26"/>
-      <c r="C134" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="D134" s="28"/>
-      <c r="E134" s="29"/>
-      <c r="F134" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="G134" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="H134" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="I134" s="29"/>
-      <c r="J134" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="K134" s="29"/>
-      <c r="L134" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="M134" s="29"/>
-      <c r="N134" s="31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" s="24" customFormat="1">
-      <c r="A135" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B135" s="20"/>
-      <c r="C135" s="21">
-        <v>9848</v>
-      </c>
-      <c r="D135" s="17"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="22">
-        <v>76</v>
-      </c>
-      <c r="G135" s="22">
+      <c r="G139" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="H139" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="I139" s="46"/>
+      <c r="J139" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="K139" s="46"/>
+      <c r="L139" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="M139" s="46"/>
+      <c r="N139" s="48" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" s="41" customFormat="1">
+      <c r="A140" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B140" s="37"/>
+      <c r="C140" s="38">
+        <v>10759</v>
+      </c>
+      <c r="D140" s="17"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="39">
+        <v>80</v>
+      </c>
+      <c r="G140" s="39">
         <v>3</v>
       </c>
-      <c r="H135" s="21">
+      <c r="H140" s="38">
         <v>1</v>
       </c>
-      <c r="I135" s="18"/>
-      <c r="J135" s="21">
-        <v>48</v>
-      </c>
-      <c r="K135" s="18"/>
-      <c r="L135" s="21">
+      <c r="I140" s="18"/>
+      <c r="J140" s="38">
+        <v>49</v>
+      </c>
+      <c r="K140" s="18"/>
+      <c r="L140" s="38">
         <v>1</v>
       </c>
-      <c r="M135" s="18"/>
-      <c r="N135" s="23">
+      <c r="M140" s="18"/>
+      <c r="N140" s="40">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="667">
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="H135:I135"/>
-    <mergeCell ref="J135:K135"/>
-    <mergeCell ref="L135:M135"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="J134:K134"/>
-    <mergeCell ref="L134:M134"/>
-    <mergeCell ref="A134:B134"/>
+  <mergeCells count="692">
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="H140:I140"/>
+    <mergeCell ref="J140:K140"/>
+    <mergeCell ref="L140:M140"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="H139:I139"/>
+    <mergeCell ref="J139:K139"/>
+    <mergeCell ref="L139:M139"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="M137:N137"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="M136:N136"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="M135:N135"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="M134:N134"/>
     <mergeCell ref="C133:D133"/>
     <mergeCell ref="F133:H133"/>
     <mergeCell ref="I133:J133"/>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\WEBSITE MANAGMENT\Worker Adjustment and Retraining Notification (WARN)\2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15096" windowHeight="9372"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15090" windowHeight="9375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="287">
   <si>
     <t/>
   </si>
@@ -839,6 +839,57 @@
     <t>2900 E. Airport Drive  Ontario CA 91761</t>
   </si>
   <si>
+    <t>GoodRx, Inc.</t>
+  </si>
+  <si>
+    <t>2701 Olympic Blvd.  Santa Monica CA 90404</t>
+  </si>
+  <si>
+    <t>San Benito County</t>
+  </si>
+  <si>
+    <t>Triple B Corporation at Jardines Farming and Harvesting Operations</t>
+  </si>
+  <si>
+    <t>1681 San Justo Rd.  San Juan Bautista CA 95045</t>
+  </si>
+  <si>
+    <t>Syncreon</t>
+  </si>
+  <si>
+    <t>19200 S. Western Avenue  Torrance CA 90501</t>
+  </si>
+  <si>
+    <t>Eko Devices, Inc.</t>
+  </si>
+  <si>
+    <t>30800 Santana St.  Hayward CA 94541</t>
+  </si>
+  <si>
+    <t>Sierra Monitor Corporation</t>
+  </si>
+  <si>
+    <t>1991 Tarob Ct.  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>Fresh Ideas Flower Company</t>
+  </si>
+  <si>
+    <t>1302 9th St  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Temple-Culberson Enterprises LLC</t>
+  </si>
+  <si>
+    <t>9350 Rayo Ave.  South Gate CA 90280</t>
+  </si>
+  <si>
+    <t>Clairemont Healthcare &amp; Wellness Centre, LLC dba Abby Gardens Healthcare Center</t>
+  </si>
+  <si>
+    <t>8060 Frost Street  San Diego CA 92123</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -865,7 +916,7 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 9/7/2022
+ End Date: 9/12/2022
 </t>
   </si>
   <si>
@@ -963,7 +1014,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1278,11 +1329,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -1295,9 +1372,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1323,6 +1397,12 @@
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1704,130 +1784,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R146"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:R154"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="2.109375" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" customWidth="1"/>
-    <col min="12" max="12" width="6.109375" customWidth="1"/>
-    <col min="13" max="13" width="7.5546875" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" ht="37.5" customHeight="1">
-      <c r="A2" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
+      <c r="A1" s="49" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="39" customHeight="1">
+      <c r="A2" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="44"/>
+      <c r="E3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="42" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="42" t="s">
+      <c r="J3" s="44"/>
+      <c r="K3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="43"/>
-      <c r="M3" s="45" t="s">
+      <c r="L3" s="44"/>
+      <c r="M3" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="46"/>
-    </row>
-    <row r="4" spans="1:18" ht="24.6">
-      <c r="A4" s="14" t="s">
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="1:18" ht="24.75">
+      <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="39"/>
+      <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="37" t="s">
+      <c r="G4" s="40"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="37" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="38"/>
-      <c r="M4" s="40" t="s">
+      <c r="L4" s="39"/>
+      <c r="M4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="41"/>
+      <c r="N4" s="42"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -1836,30 +1916,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <v>44750</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="28"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="34" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="35">
+      <c r="J5" s="28"/>
+      <c r="K5" s="36">
         <v>2</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="36" t="s">
+      <c r="L5" s="28"/>
+      <c r="M5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="32"/>
+      <c r="N5" s="33"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -1868,30 +1948,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>44750</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="28"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="27"/>
-      <c r="K6" s="30">
+      <c r="J6" s="28"/>
+      <c r="K6" s="31">
         <v>13</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="31" t="s">
+      <c r="L6" s="28"/>
+      <c r="M6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="32"/>
+      <c r="N6" s="33"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -1900,30 +1980,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="34">
         <v>44750</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="28"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="35">
+      <c r="G7" s="30"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="28"/>
+      <c r="K7" s="36">
         <v>9</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="36" t="s">
+      <c r="L7" s="28"/>
+      <c r="M7" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="32"/>
+      <c r="N7" s="33"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -1932,30 +2012,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>44750</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="30">
+      <c r="G8" s="30"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="28"/>
+      <c r="K8" s="31">
         <v>123</v>
       </c>
-      <c r="L8" s="27"/>
-      <c r="M8" s="31" t="s">
+      <c r="L8" s="28"/>
+      <c r="M8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="32"/>
+      <c r="N8" s="33"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -1964,30 +2044,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>44750</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="35">
+      <c r="G9" s="30"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="28"/>
+      <c r="K9" s="36">
         <v>37</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="36" t="s">
+      <c r="L9" s="28"/>
+      <c r="M9" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="32"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -1996,30 +2076,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>44753</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="27"/>
-      <c r="K10" s="30">
+      <c r="G10" s="30"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="28"/>
+      <c r="K10" s="31">
         <v>37</v>
       </c>
-      <c r="L10" s="27"/>
-      <c r="M10" s="31" t="s">
+      <c r="L10" s="28"/>
+      <c r="M10" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="32"/>
+      <c r="N10" s="33"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2028,30 +2108,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <v>44753</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="35">
+      <c r="G11" s="30"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="28"/>
+      <c r="K11" s="36">
         <v>80</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="36" t="s">
+      <c r="L11" s="28"/>
+      <c r="M11" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="32"/>
+      <c r="N11" s="33"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2060,30 +2140,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>44753</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28" t="s">
+      <c r="G12" s="30"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="27"/>
-      <c r="K12" s="30">
+      <c r="J12" s="28"/>
+      <c r="K12" s="31">
         <v>229</v>
       </c>
-      <c r="L12" s="27"/>
-      <c r="M12" s="31" t="s">
+      <c r="L12" s="28"/>
+      <c r="M12" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="32"/>
+      <c r="N12" s="33"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2092,30 +2172,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <v>44753</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="35">
+      <c r="G13" s="30"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="28"/>
+      <c r="K13" s="36">
         <v>368</v>
       </c>
-      <c r="L13" s="27"/>
-      <c r="M13" s="36" t="s">
+      <c r="L13" s="28"/>
+      <c r="M13" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="32"/>
+      <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2124,30 +2204,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <v>44753</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="27"/>
-      <c r="K14" s="30">
+      <c r="G14" s="30"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="28"/>
+      <c r="K14" s="31">
         <v>62</v>
       </c>
-      <c r="L14" s="27"/>
-      <c r="M14" s="31" t="s">
+      <c r="L14" s="28"/>
+      <c r="M14" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="32"/>
+      <c r="N14" s="33"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2156,30 +2236,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <v>44753</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="35">
+      <c r="G15" s="30"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="28"/>
+      <c r="K15" s="36">
         <v>25</v>
       </c>
-      <c r="L15" s="27"/>
-      <c r="M15" s="36" t="s">
+      <c r="L15" s="28"/>
+      <c r="M15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="32"/>
+      <c r="N15" s="33"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2188,30 +2268,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <v>44753</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="28"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="30">
+      <c r="G16" s="30"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="28"/>
+      <c r="K16" s="31">
         <v>68</v>
       </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="31" t="s">
+      <c r="L16" s="28"/>
+      <c r="M16" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="32"/>
+      <c r="N16" s="33"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2220,30 +2300,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <v>44753</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="35">
+      <c r="G17" s="30"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="36">
         <v>77</v>
       </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="36" t="s">
+      <c r="L17" s="28"/>
+      <c r="M17" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="32"/>
+      <c r="N17" s="33"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2252,30 +2332,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <v>44754</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="27"/>
-      <c r="K18" s="30">
+      <c r="G18" s="30"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="28"/>
+      <c r="K18" s="31">
         <v>20</v>
       </c>
-      <c r="L18" s="27"/>
-      <c r="M18" s="31" t="s">
+      <c r="L18" s="28"/>
+      <c r="M18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="32"/>
+      <c r="N18" s="33"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2284,30 +2364,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <v>44754</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="27"/>
-      <c r="K19" s="35">
+      <c r="G19" s="30"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="28"/>
+      <c r="K19" s="36">
         <v>5</v>
       </c>
-      <c r="L19" s="27"/>
-      <c r="M19" s="36" t="s">
+      <c r="L19" s="28"/>
+      <c r="M19" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="32"/>
+      <c r="N19" s="33"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2316,30 +2396,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <v>44754</v>
       </c>
-      <c r="D20" s="27"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="30">
+      <c r="G20" s="30"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="28"/>
+      <c r="K20" s="31">
         <v>2</v>
       </c>
-      <c r="L20" s="27"/>
-      <c r="M20" s="31" t="s">
+      <c r="L20" s="28"/>
+      <c r="M20" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="32"/>
+      <c r="N20" s="33"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2348,30 +2428,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>44754</v>
       </c>
-      <c r="D21" s="27"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="35">
+      <c r="G21" s="30"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="28"/>
+      <c r="K21" s="36">
         <v>1</v>
       </c>
-      <c r="L21" s="27"/>
-      <c r="M21" s="36" t="s">
+      <c r="L21" s="28"/>
+      <c r="M21" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="32"/>
+      <c r="N21" s="33"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2380,30 +2460,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <v>44754</v>
       </c>
-      <c r="D22" s="27"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="27"/>
-      <c r="K22" s="30">
+      <c r="G22" s="30"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="28"/>
+      <c r="K22" s="31">
         <v>41</v>
       </c>
-      <c r="L22" s="27"/>
-      <c r="M22" s="31" t="s">
+      <c r="L22" s="28"/>
+      <c r="M22" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="32"/>
+      <c r="N22" s="33"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2412,30 +2492,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="34">
         <v>44754</v>
       </c>
-      <c r="D23" s="27"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="34" t="s">
+      <c r="G23" s="30"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="35">
+      <c r="J23" s="28"/>
+      <c r="K23" s="36">
         <v>4</v>
       </c>
-      <c r="L23" s="27"/>
-      <c r="M23" s="36" t="s">
+      <c r="L23" s="28"/>
+      <c r="M23" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="32"/>
+      <c r="N23" s="33"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2444,30 +2524,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>44754</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="27"/>
-      <c r="K24" s="30">
+      <c r="G24" s="30"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="28"/>
+      <c r="K24" s="31">
         <v>211</v>
       </c>
-      <c r="L24" s="27"/>
-      <c r="M24" s="31" t="s">
+      <c r="L24" s="28"/>
+      <c r="M24" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="32"/>
+      <c r="N24" s="33"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2476,30 +2556,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>44754</v>
       </c>
-      <c r="D25" s="27"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="34" t="s">
+      <c r="G25" s="30"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="27"/>
-      <c r="K25" s="35">
+      <c r="J25" s="28"/>
+      <c r="K25" s="36">
         <v>10</v>
       </c>
-      <c r="L25" s="27"/>
-      <c r="M25" s="36" t="s">
+      <c r="L25" s="28"/>
+      <c r="M25" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="32"/>
+      <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2508,30 +2588,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <v>44754</v>
       </c>
-      <c r="D26" s="27"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="28" t="s">
+      <c r="G26" s="30"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="27"/>
-      <c r="K26" s="30">
+      <c r="J26" s="28"/>
+      <c r="K26" s="31">
         <v>1</v>
       </c>
-      <c r="L26" s="27"/>
-      <c r="M26" s="31" t="s">
+      <c r="L26" s="28"/>
+      <c r="M26" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="32"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2540,30 +2620,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>44754</v>
       </c>
-      <c r="D27" s="27"/>
+      <c r="D27" s="28"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="34" t="s">
+      <c r="F27" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="29"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="27"/>
-      <c r="K27" s="35">
+      <c r="G27" s="30"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="28"/>
+      <c r="K27" s="36">
         <v>94</v>
       </c>
-      <c r="L27" s="27"/>
-      <c r="M27" s="36" t="s">
+      <c r="L27" s="28"/>
+      <c r="M27" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="32"/>
+      <c r="N27" s="33"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2572,30 +2652,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <v>44754</v>
       </c>
-      <c r="D28" s="27"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28" t="s">
+      <c r="G28" s="30"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="27"/>
-      <c r="K28" s="30">
+      <c r="J28" s="28"/>
+      <c r="K28" s="31">
         <v>9</v>
       </c>
-      <c r="L28" s="27"/>
-      <c r="M28" s="31" t="s">
+      <c r="L28" s="28"/>
+      <c r="M28" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="32"/>
+      <c r="N28" s="33"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2604,30 +2684,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="34">
         <v>44754</v>
       </c>
-      <c r="D29" s="27"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="34" t="s">
+      <c r="G29" s="30"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="27"/>
-      <c r="K29" s="35">
+      <c r="J29" s="28"/>
+      <c r="K29" s="36">
         <v>6</v>
       </c>
-      <c r="L29" s="27"/>
-      <c r="M29" s="36" t="s">
+      <c r="L29" s="28"/>
+      <c r="M29" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="32"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2636,30 +2716,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <v>44754</v>
       </c>
-      <c r="D30" s="27"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="28" t="s">
+      <c r="G30" s="30"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="27"/>
-      <c r="K30" s="30">
-        <v>18</v>
-      </c>
-      <c r="L30" s="27"/>
-      <c r="M30" s="31" t="s">
+      <c r="J30" s="28"/>
+      <c r="K30" s="31">
+        <v>18</v>
+      </c>
+      <c r="L30" s="28"/>
+      <c r="M30" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="32"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2668,30 +2748,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>44755</v>
       </c>
-      <c r="D31" s="27"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="29"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="34" t="s">
+      <c r="G31" s="30"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="27"/>
-      <c r="K31" s="35">
+      <c r="J31" s="28"/>
+      <c r="K31" s="36">
         <v>76</v>
       </c>
-      <c r="L31" s="27"/>
-      <c r="M31" s="36" t="s">
+      <c r="L31" s="28"/>
+      <c r="M31" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="32"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -2700,30 +2780,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="27">
         <v>44755</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28" t="s">
+      <c r="G32" s="30"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="27"/>
-      <c r="K32" s="30">
+      <c r="J32" s="28"/>
+      <c r="K32" s="31">
         <v>1</v>
       </c>
-      <c r="L32" s="27"/>
-      <c r="M32" s="31" t="s">
+      <c r="L32" s="28"/>
+      <c r="M32" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="32"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -2732,30 +2812,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>44755</v>
       </c>
-      <c r="D33" s="27"/>
+      <c r="D33" s="28"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="34" t="s">
+      <c r="F33" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="34" t="s">
+      <c r="G33" s="30"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="35">
+      <c r="J33" s="28"/>
+      <c r="K33" s="36">
         <v>27</v>
       </c>
-      <c r="L33" s="27"/>
-      <c r="M33" s="36" t="s">
+      <c r="L33" s="28"/>
+      <c r="M33" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="32"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -2764,30 +2844,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <v>44755</v>
       </c>
-      <c r="D34" s="27"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="29"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28" t="s">
+      <c r="G34" s="30"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="30">
+      <c r="J34" s="28"/>
+      <c r="K34" s="31">
         <v>2</v>
       </c>
-      <c r="L34" s="27"/>
-      <c r="M34" s="31" t="s">
+      <c r="L34" s="28"/>
+      <c r="M34" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="32"/>
+      <c r="N34" s="33"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -2796,30 +2876,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>44756</v>
       </c>
-      <c r="D35" s="27"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="34" t="s">
+      <c r="F35" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="29"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="35">
+      <c r="G35" s="30"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="28"/>
+      <c r="K35" s="36">
         <v>54</v>
       </c>
-      <c r="L35" s="27"/>
-      <c r="M35" s="36" t="s">
+      <c r="L35" s="28"/>
+      <c r="M35" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="32"/>
+      <c r="N35" s="33"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -2828,30 +2908,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="27">
         <v>44756</v>
       </c>
-      <c r="D36" s="27"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="29"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="27"/>
-      <c r="K36" s="30">
+      <c r="G36" s="30"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="28"/>
+      <c r="K36" s="31">
         <v>105</v>
       </c>
-      <c r="L36" s="27"/>
-      <c r="M36" s="31" t="s">
+      <c r="L36" s="28"/>
+      <c r="M36" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="32"/>
+      <c r="N36" s="33"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -2860,30 +2940,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="34">
         <v>44756</v>
       </c>
-      <c r="D37" s="27"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="34" t="s">
+      <c r="F37" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="29"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="27"/>
-      <c r="K37" s="35">
+      <c r="G37" s="30"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="28"/>
+      <c r="K37" s="36">
         <v>71</v>
       </c>
-      <c r="L37" s="27"/>
-      <c r="M37" s="36" t="s">
+      <c r="L37" s="28"/>
+      <c r="M37" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="32"/>
+      <c r="N37" s="33"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -2892,30 +2972,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="27">
         <v>44756</v>
       </c>
-      <c r="D38" s="27"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="29"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="27"/>
-      <c r="K38" s="30">
+      <c r="G38" s="30"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="28"/>
+      <c r="K38" s="31">
         <v>125</v>
       </c>
-      <c r="L38" s="27"/>
-      <c r="M38" s="31" t="s">
+      <c r="L38" s="28"/>
+      <c r="M38" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="32"/>
+      <c r="N38" s="33"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -2924,30 +3004,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>44756</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="27"/>
-      <c r="K39" s="35">
+      <c r="G39" s="30"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="28"/>
+      <c r="K39" s="36">
         <v>55</v>
       </c>
-      <c r="L39" s="27"/>
-      <c r="M39" s="36" t="s">
+      <c r="L39" s="28"/>
+      <c r="M39" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="32"/>
+      <c r="N39" s="33"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -2956,30 +3036,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="27">
         <v>44756</v>
       </c>
-      <c r="D40" s="27"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="29"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="27"/>
-      <c r="K40" s="30">
+      <c r="G40" s="30"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="28"/>
+      <c r="K40" s="31">
         <v>176</v>
       </c>
-      <c r="L40" s="27"/>
-      <c r="M40" s="31" t="s">
+      <c r="L40" s="28"/>
+      <c r="M40" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="32"/>
+      <c r="N40" s="33"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -2988,30 +3068,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>44757</v>
       </c>
-      <c r="D41" s="27"/>
+      <c r="D41" s="28"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="34" t="s">
+      <c r="F41" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="29"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="27"/>
-      <c r="K41" s="35">
+      <c r="G41" s="30"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="28"/>
+      <c r="K41" s="36">
         <v>58</v>
       </c>
-      <c r="L41" s="27"/>
-      <c r="M41" s="36" t="s">
+      <c r="L41" s="28"/>
+      <c r="M41" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="32"/>
+      <c r="N41" s="33"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3020,30 +3100,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <v>44757</v>
       </c>
-      <c r="D42" s="27"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="29"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="27"/>
-      <c r="K42" s="30">
+      <c r="G42" s="30"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="28"/>
+      <c r="K42" s="31">
         <v>180</v>
       </c>
-      <c r="L42" s="27"/>
-      <c r="M42" s="31" t="s">
+      <c r="L42" s="28"/>
+      <c r="M42" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="32"/>
+      <c r="N42" s="33"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3052,30 +3132,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="34">
         <v>44760</v>
       </c>
-      <c r="D43" s="27"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="34" t="s">
+      <c r="F43" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="29"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="34" t="s">
+      <c r="G43" s="30"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="27"/>
-      <c r="K43" s="35">
+      <c r="J43" s="28"/>
+      <c r="K43" s="36">
         <v>142</v>
       </c>
-      <c r="L43" s="27"/>
-      <c r="M43" s="36" t="s">
+      <c r="L43" s="28"/>
+      <c r="M43" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="32"/>
+      <c r="N43" s="33"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3084,30 +3164,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <v>44760</v>
       </c>
-      <c r="D44" s="27"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="28" t="s">
+      <c r="F44" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="29"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="28" t="s">
+      <c r="G44" s="30"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="27"/>
-      <c r="K44" s="30">
+      <c r="J44" s="28"/>
+      <c r="K44" s="31">
         <v>153</v>
       </c>
-      <c r="L44" s="27"/>
-      <c r="M44" s="31" t="s">
+      <c r="L44" s="28"/>
+      <c r="M44" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="32"/>
+      <c r="N44" s="33"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3116,30 +3196,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>44761</v>
       </c>
-      <c r="D45" s="27"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="34" t="s">
+      <c r="F45" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="29"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="27"/>
-      <c r="K45" s="35">
+      <c r="G45" s="30"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="28"/>
+      <c r="K45" s="36">
         <v>12</v>
       </c>
-      <c r="L45" s="27"/>
-      <c r="M45" s="36" t="s">
+      <c r="L45" s="28"/>
+      <c r="M45" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="32"/>
+      <c r="N45" s="33"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3148,30 +3228,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <v>44761</v>
       </c>
-      <c r="D46" s="27"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="28" t="s">
+      <c r="F46" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="29"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="27"/>
-      <c r="K46" s="30">
+      <c r="G46" s="30"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="28"/>
+      <c r="K46" s="31">
         <v>27</v>
       </c>
-      <c r="L46" s="27"/>
-      <c r="M46" s="31" t="s">
+      <c r="L46" s="28"/>
+      <c r="M46" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="32"/>
+      <c r="N46" s="33"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3180,30 +3260,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="34">
         <v>44761</v>
       </c>
-      <c r="D47" s="27"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="34" t="s">
+      <c r="F47" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="29"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="27"/>
-      <c r="K47" s="35">
+      <c r="G47" s="30"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="28"/>
+      <c r="K47" s="36">
         <v>51</v>
       </c>
-      <c r="L47" s="27"/>
-      <c r="M47" s="36" t="s">
+      <c r="L47" s="28"/>
+      <c r="M47" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="32"/>
+      <c r="N47" s="33"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3212,30 +3292,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="26">
+      <c r="C48" s="27">
         <v>44761</v>
       </c>
-      <c r="D48" s="27"/>
+      <c r="D48" s="28"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="29"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="27"/>
-      <c r="K48" s="30">
+      <c r="G48" s="30"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="28"/>
+      <c r="K48" s="31">
         <v>69</v>
       </c>
-      <c r="L48" s="27"/>
-      <c r="M48" s="31" t="s">
+      <c r="L48" s="28"/>
+      <c r="M48" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="32"/>
+      <c r="N48" s="33"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3244,30 +3324,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="34">
         <v>44762</v>
       </c>
-      <c r="D49" s="27"/>
+      <c r="D49" s="28"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="34" t="s">
+      <c r="F49" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="29"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="34" t="s">
+      <c r="G49" s="30"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="27"/>
-      <c r="K49" s="35">
+      <c r="J49" s="28"/>
+      <c r="K49" s="36">
         <v>104</v>
       </c>
-      <c r="L49" s="27"/>
-      <c r="M49" s="36" t="s">
+      <c r="L49" s="28"/>
+      <c r="M49" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="32"/>
+      <c r="N49" s="33"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3276,30 +3356,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="27">
         <v>44762</v>
       </c>
-      <c r="D50" s="27"/>
+      <c r="D50" s="28"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="29"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="27"/>
-      <c r="K50" s="30">
+      <c r="G50" s="30"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="31">
         <v>19</v>
       </c>
-      <c r="L50" s="27"/>
-      <c r="M50" s="31" t="s">
+      <c r="L50" s="28"/>
+      <c r="M50" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="32"/>
+      <c r="N50" s="33"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3308,30 +3388,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>44762</v>
       </c>
-      <c r="D51" s="27"/>
+      <c r="D51" s="28"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="34" t="s">
+      <c r="F51" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="29"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="34" t="s">
+      <c r="G51" s="30"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="27"/>
-      <c r="K51" s="35">
+      <c r="J51" s="28"/>
+      <c r="K51" s="36">
         <v>80</v>
       </c>
-      <c r="L51" s="27"/>
-      <c r="M51" s="36" t="s">
+      <c r="L51" s="28"/>
+      <c r="M51" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="32"/>
+      <c r="N51" s="33"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3340,30 +3420,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="27">
         <v>44763</v>
       </c>
-      <c r="D52" s="27"/>
+      <c r="D52" s="28"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="28" t="s">
+      <c r="F52" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="29"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="27"/>
-      <c r="K52" s="30">
+      <c r="G52" s="30"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="28"/>
+      <c r="K52" s="31">
         <v>99</v>
       </c>
-      <c r="L52" s="27"/>
-      <c r="M52" s="31" t="s">
+      <c r="L52" s="28"/>
+      <c r="M52" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="32"/>
+      <c r="N52" s="33"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3372,30 +3452,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>44763</v>
       </c>
-      <c r="D53" s="27"/>
+      <c r="D53" s="28"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="34" t="s">
+      <c r="F53" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="29"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="27"/>
-      <c r="K53" s="35">
+      <c r="G53" s="30"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="28"/>
+      <c r="K53" s="36">
         <v>60</v>
       </c>
-      <c r="L53" s="27"/>
-      <c r="M53" s="36" t="s">
+      <c r="L53" s="28"/>
+      <c r="M53" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="32"/>
+      <c r="N53" s="33"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3404,30 +3484,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <v>44763</v>
       </c>
-      <c r="D54" s="27"/>
+      <c r="D54" s="28"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="F54" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="29"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="27"/>
-      <c r="K54" s="30">
+      <c r="G54" s="30"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="28"/>
+      <c r="K54" s="31">
         <v>4</v>
       </c>
-      <c r="L54" s="27"/>
-      <c r="M54" s="31" t="s">
+      <c r="L54" s="28"/>
+      <c r="M54" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="32"/>
+      <c r="N54" s="33"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3436,30 +3516,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="33">
+      <c r="C55" s="34">
         <v>44763</v>
       </c>
-      <c r="D55" s="27"/>
+      <c r="D55" s="28"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="34" t="s">
+      <c r="F55" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="29"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="27"/>
-      <c r="K55" s="35">
+      <c r="G55" s="30"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="28"/>
+      <c r="K55" s="36">
         <v>26</v>
       </c>
-      <c r="L55" s="27"/>
-      <c r="M55" s="36" t="s">
+      <c r="L55" s="28"/>
+      <c r="M55" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="32"/>
+      <c r="N55" s="33"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3468,30 +3548,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="27">
         <v>44763</v>
       </c>
-      <c r="D56" s="27"/>
+      <c r="D56" s="28"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="28" t="s">
+      <c r="F56" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="29"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="27"/>
-      <c r="K56" s="30">
+      <c r="G56" s="30"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="28"/>
+      <c r="K56" s="31">
         <v>30</v>
       </c>
-      <c r="L56" s="27"/>
-      <c r="M56" s="31" t="s">
+      <c r="L56" s="28"/>
+      <c r="M56" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="32"/>
+      <c r="N56" s="33"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3500,30 +3580,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>44763</v>
       </c>
-      <c r="D57" s="27"/>
+      <c r="D57" s="28"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="34" t="s">
+      <c r="F57" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="29"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="27"/>
-      <c r="K57" s="35">
+      <c r="G57" s="30"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="28"/>
+      <c r="K57" s="36">
         <v>2</v>
       </c>
-      <c r="L57" s="27"/>
-      <c r="M57" s="36" t="s">
+      <c r="L57" s="28"/>
+      <c r="M57" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="32"/>
+      <c r="N57" s="33"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3532,30 +3612,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <v>44764</v>
       </c>
-      <c r="D58" s="27"/>
+      <c r="D58" s="28"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="29"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="28" t="s">
+      <c r="G58" s="30"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="27"/>
-      <c r="K58" s="30">
+      <c r="J58" s="28"/>
+      <c r="K58" s="31">
         <v>66</v>
       </c>
-      <c r="L58" s="27"/>
-      <c r="M58" s="31" t="s">
+      <c r="L58" s="28"/>
+      <c r="M58" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="32"/>
+      <c r="N58" s="33"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3564,30 +3644,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>44764</v>
       </c>
-      <c r="D59" s="27"/>
+      <c r="D59" s="28"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="34" t="s">
+      <c r="F59" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="29"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="34" t="s">
+      <c r="G59" s="30"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="27"/>
-      <c r="K59" s="35">
+      <c r="J59" s="28"/>
+      <c r="K59" s="36">
         <v>85</v>
       </c>
-      <c r="L59" s="27"/>
-      <c r="M59" s="36" t="s">
+      <c r="L59" s="28"/>
+      <c r="M59" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="32"/>
+      <c r="N59" s="33"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3596,30 +3676,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="26">
+      <c r="C60" s="27">
         <v>44764</v>
       </c>
-      <c r="D60" s="27"/>
+      <c r="D60" s="28"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="28" t="s">
+      <c r="F60" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="29"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="27"/>
-      <c r="K60" s="30">
+      <c r="G60" s="30"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="28"/>
+      <c r="K60" s="31">
         <v>58</v>
       </c>
-      <c r="L60" s="27"/>
-      <c r="M60" s="31" t="s">
+      <c r="L60" s="28"/>
+      <c r="M60" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="32"/>
+      <c r="N60" s="33"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3628,30 +3708,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="33">
+      <c r="C61" s="34">
         <v>44764</v>
       </c>
-      <c r="D61" s="27"/>
+      <c r="D61" s="28"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="34" t="s">
+      <c r="F61" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="29"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="27"/>
-      <c r="K61" s="35">
+      <c r="G61" s="30"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="28"/>
+      <c r="K61" s="36">
         <v>80</v>
       </c>
-      <c r="L61" s="27"/>
-      <c r="M61" s="36" t="s">
+      <c r="L61" s="28"/>
+      <c r="M61" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="32"/>
+      <c r="N61" s="33"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3660,30 +3740,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="26">
+      <c r="C62" s="27">
         <v>44764</v>
       </c>
-      <c r="D62" s="27"/>
+      <c r="D62" s="28"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="28" t="s">
+      <c r="F62" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="29"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="27"/>
-      <c r="K62" s="30">
+      <c r="G62" s="30"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="28"/>
+      <c r="K62" s="31">
         <v>55</v>
       </c>
-      <c r="L62" s="27"/>
-      <c r="M62" s="31" t="s">
+      <c r="L62" s="28"/>
+      <c r="M62" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="32"/>
+      <c r="N62" s="33"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -3692,30 +3772,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>44764</v>
       </c>
-      <c r="D63" s="27"/>
+      <c r="D63" s="28"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="34" t="s">
+      <c r="F63" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="29"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="34" t="s">
+      <c r="G63" s="30"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="27"/>
-      <c r="K63" s="35">
+      <c r="J63" s="28"/>
+      <c r="K63" s="36">
         <v>14</v>
       </c>
-      <c r="L63" s="27"/>
-      <c r="M63" s="36" t="s">
+      <c r="L63" s="28"/>
+      <c r="M63" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="32"/>
+      <c r="N63" s="33"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -3724,30 +3804,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="26">
+      <c r="C64" s="27">
         <v>44764</v>
       </c>
-      <c r="D64" s="27"/>
+      <c r="D64" s="28"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="F64" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="29"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="28" t="s">
+      <c r="G64" s="30"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="27"/>
-      <c r="K64" s="30">
+      <c r="J64" s="28"/>
+      <c r="K64" s="31">
         <v>90</v>
       </c>
-      <c r="L64" s="27"/>
-      <c r="M64" s="31" t="s">
+      <c r="L64" s="28"/>
+      <c r="M64" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="32"/>
+      <c r="N64" s="33"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -3756,30 +3836,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>44767</v>
       </c>
-      <c r="D65" s="27"/>
+      <c r="D65" s="28"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="34" t="s">
+      <c r="F65" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="29"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="34" t="s">
+      <c r="G65" s="30"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="27"/>
-      <c r="K65" s="35">
+      <c r="J65" s="28"/>
+      <c r="K65" s="36">
         <v>331</v>
       </c>
-      <c r="L65" s="27"/>
-      <c r="M65" s="36" t="s">
+      <c r="L65" s="28"/>
+      <c r="M65" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="32"/>
+      <c r="N65" s="33"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -3788,30 +3868,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="26">
+      <c r="C66" s="27">
         <v>44768</v>
       </c>
-      <c r="D66" s="27"/>
+      <c r="D66" s="28"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="28" t="s">
+      <c r="F66" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="29"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="27"/>
-      <c r="K66" s="30">
+      <c r="G66" s="30"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="28"/>
+      <c r="K66" s="31">
         <v>52</v>
       </c>
-      <c r="L66" s="27"/>
-      <c r="M66" s="31" t="s">
+      <c r="L66" s="28"/>
+      <c r="M66" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="32"/>
+      <c r="N66" s="33"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -3820,30 +3900,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="33">
+      <c r="C67" s="34">
         <v>44768</v>
       </c>
-      <c r="D67" s="27"/>
+      <c r="D67" s="28"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="34" t="s">
+      <c r="F67" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="29"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="27"/>
-      <c r="K67" s="35">
+      <c r="G67" s="30"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="28"/>
+      <c r="K67" s="36">
         <v>9</v>
       </c>
-      <c r="L67" s="27"/>
-      <c r="M67" s="36" t="s">
+      <c r="L67" s="28"/>
+      <c r="M67" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="32"/>
+      <c r="N67" s="33"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -3852,30 +3932,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="26">
+      <c r="C68" s="27">
         <v>44768</v>
       </c>
-      <c r="D68" s="27"/>
+      <c r="D68" s="28"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="29"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="27"/>
-      <c r="K68" s="30">
+      <c r="G68" s="30"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="28"/>
+      <c r="K68" s="31">
         <v>78</v>
       </c>
-      <c r="L68" s="27"/>
-      <c r="M68" s="31" t="s">
+      <c r="L68" s="28"/>
+      <c r="M68" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="32"/>
+      <c r="N68" s="33"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -3884,30 +3964,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>44769</v>
       </c>
-      <c r="D69" s="27"/>
+      <c r="D69" s="28"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="34" t="s">
+      <c r="F69" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="29"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="27"/>
-      <c r="K69" s="35">
+      <c r="G69" s="30"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="28"/>
+      <c r="K69" s="36">
         <v>48</v>
       </c>
-      <c r="L69" s="27"/>
-      <c r="M69" s="36" t="s">
+      <c r="L69" s="28"/>
+      <c r="M69" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="32"/>
+      <c r="N69" s="33"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -3916,30 +3996,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="26">
+      <c r="C70" s="27">
         <v>44769</v>
       </c>
-      <c r="D70" s="27"/>
+      <c r="D70" s="28"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="29"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="27"/>
-      <c r="K70" s="30">
+      <c r="G70" s="30"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="28"/>
+      <c r="K70" s="31">
         <v>50</v>
       </c>
-      <c r="L70" s="27"/>
-      <c r="M70" s="31" t="s">
+      <c r="L70" s="28"/>
+      <c r="M70" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="32"/>
+      <c r="N70" s="33"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -3948,30 +4028,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="34">
         <v>44769</v>
       </c>
-      <c r="D71" s="27"/>
+      <c r="D71" s="28"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="34" t="s">
+      <c r="F71" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="29"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="27"/>
-      <c r="K71" s="35">
+      <c r="G71" s="30"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="28"/>
+      <c r="K71" s="36">
         <v>736</v>
       </c>
-      <c r="L71" s="27"/>
-      <c r="M71" s="36" t="s">
+      <c r="L71" s="28"/>
+      <c r="M71" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="32"/>
+      <c r="N71" s="33"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -3980,30 +4060,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="26">
+      <c r="C72" s="27">
         <v>44770</v>
       </c>
-      <c r="D72" s="27"/>
+      <c r="D72" s="28"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="28" t="s">
+      <c r="F72" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="29"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="27"/>
-      <c r="K72" s="30">
+      <c r="G72" s="30"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="28"/>
+      <c r="K72" s="31">
         <v>74</v>
       </c>
-      <c r="L72" s="27"/>
-      <c r="M72" s="31" t="s">
+      <c r="L72" s="28"/>
+      <c r="M72" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="32"/>
+      <c r="N72" s="33"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4012,30 +4092,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="33">
+      <c r="C73" s="34">
         <v>44770</v>
       </c>
-      <c r="D73" s="27"/>
+      <c r="D73" s="28"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="34" t="s">
+      <c r="F73" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="29"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="27"/>
-      <c r="K73" s="35">
+      <c r="G73" s="30"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="28"/>
+      <c r="K73" s="36">
         <v>25</v>
       </c>
-      <c r="L73" s="27"/>
-      <c r="M73" s="36" t="s">
+      <c r="L73" s="28"/>
+      <c r="M73" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="32"/>
+      <c r="N73" s="33"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4044,30 +4124,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="26">
+      <c r="C74" s="27">
         <v>44770</v>
       </c>
-      <c r="D74" s="27"/>
+      <c r="D74" s="28"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="28" t="s">
+      <c r="F74" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="29"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="27"/>
-      <c r="K74" s="30">
+      <c r="G74" s="30"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="28"/>
+      <c r="K74" s="31">
         <v>25</v>
       </c>
-      <c r="L74" s="27"/>
-      <c r="M74" s="31" t="s">
+      <c r="L74" s="28"/>
+      <c r="M74" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="32"/>
+      <c r="N74" s="33"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4076,30 +4156,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="33">
+      <c r="C75" s="34">
         <v>44770</v>
       </c>
-      <c r="D75" s="27"/>
+      <c r="D75" s="28"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="34" t="s">
+      <c r="F75" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="29"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="34" t="s">
+      <c r="G75" s="30"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="27"/>
-      <c r="K75" s="35">
+      <c r="J75" s="28"/>
+      <c r="K75" s="36">
         <v>225</v>
       </c>
-      <c r="L75" s="27"/>
-      <c r="M75" s="36" t="s">
+      <c r="L75" s="28"/>
+      <c r="M75" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="32"/>
+      <c r="N75" s="33"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4108,30 +4188,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="26">
+      <c r="C76" s="27">
         <v>44770</v>
       </c>
-      <c r="D76" s="27"/>
+      <c r="D76" s="28"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="28" t="s">
+      <c r="F76" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="29"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="27"/>
-      <c r="K76" s="30">
+      <c r="G76" s="30"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="28"/>
+      <c r="K76" s="31">
         <v>136</v>
       </c>
-      <c r="L76" s="27"/>
-      <c r="M76" s="31" t="s">
+      <c r="L76" s="28"/>
+      <c r="M76" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="32"/>
+      <c r="N76" s="33"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4140,30 +4220,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="33">
+      <c r="C77" s="34">
         <v>44774</v>
       </c>
-      <c r="D77" s="27"/>
+      <c r="D77" s="28"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="34" t="s">
+      <c r="F77" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="29"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="34" t="s">
+      <c r="G77" s="30"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="27"/>
-      <c r="K77" s="35">
+      <c r="J77" s="28"/>
+      <c r="K77" s="36">
         <v>82</v>
       </c>
-      <c r="L77" s="27"/>
-      <c r="M77" s="36" t="s">
+      <c r="L77" s="28"/>
+      <c r="M77" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="32"/>
+      <c r="N77" s="33"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4172,30 +4252,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="26">
+      <c r="C78" s="27">
         <v>44774</v>
       </c>
-      <c r="D78" s="27"/>
+      <c r="D78" s="28"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="28" t="s">
+      <c r="F78" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="29"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="27"/>
-      <c r="K78" s="30">
+      <c r="G78" s="30"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="28"/>
+      <c r="K78" s="31">
         <v>28</v>
       </c>
-      <c r="L78" s="27"/>
-      <c r="M78" s="31" t="s">
+      <c r="L78" s="28"/>
+      <c r="M78" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="32"/>
+      <c r="N78" s="33"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4204,30 +4284,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="33">
+      <c r="C79" s="34">
         <v>44776</v>
       </c>
-      <c r="D79" s="27"/>
+      <c r="D79" s="28"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="34" t="s">
+      <c r="F79" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="29"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="27"/>
-      <c r="K79" s="35">
+      <c r="G79" s="30"/>
+      <c r="H79" s="28"/>
+      <c r="I79" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="28"/>
+      <c r="K79" s="36">
         <v>57</v>
       </c>
-      <c r="L79" s="27"/>
-      <c r="M79" s="36" t="s">
+      <c r="L79" s="28"/>
+      <c r="M79" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="32"/>
+      <c r="N79" s="33"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4236,30 +4316,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="26">
+      <c r="C80" s="27">
         <v>44778</v>
       </c>
-      <c r="D80" s="27"/>
+      <c r="D80" s="28"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="28" t="s">
+      <c r="F80" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="29"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="28" t="s">
+      <c r="G80" s="30"/>
+      <c r="H80" s="28"/>
+      <c r="I80" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="27"/>
-      <c r="K80" s="30">
+      <c r="J80" s="28"/>
+      <c r="K80" s="31">
         <v>133</v>
       </c>
-      <c r="L80" s="27"/>
-      <c r="M80" s="31" t="s">
+      <c r="L80" s="28"/>
+      <c r="M80" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="32"/>
+      <c r="N80" s="33"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4268,30 +4348,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="33">
+      <c r="C81" s="34">
         <v>44778</v>
       </c>
-      <c r="D81" s="27"/>
+      <c r="D81" s="28"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="34" t="s">
+      <c r="F81" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="29"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="27"/>
-      <c r="K81" s="35">
+      <c r="G81" s="30"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="28"/>
+      <c r="K81" s="36">
         <v>146</v>
       </c>
-      <c r="L81" s="27"/>
-      <c r="M81" s="36" t="s">
+      <c r="L81" s="28"/>
+      <c r="M81" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="32"/>
+      <c r="N81" s="33"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4300,30 +4380,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="26">
+      <c r="C82" s="27">
         <v>44778</v>
       </c>
-      <c r="D82" s="27"/>
+      <c r="D82" s="28"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="28" t="s">
+      <c r="F82" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="29"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="28" t="s">
+      <c r="G82" s="30"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="27"/>
-      <c r="K82" s="30">
+      <c r="J82" s="28"/>
+      <c r="K82" s="31">
         <v>68</v>
       </c>
-      <c r="L82" s="27"/>
-      <c r="M82" s="31" t="s">
+      <c r="L82" s="28"/>
+      <c r="M82" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="32"/>
+      <c r="N82" s="33"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4332,30 +4412,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="33">
+      <c r="C83" s="34">
         <v>44781</v>
       </c>
-      <c r="D83" s="27"/>
+      <c r="D83" s="28"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="34" t="s">
+      <c r="F83" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="29"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="27"/>
-      <c r="K83" s="35">
+      <c r="G83" s="30"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="28"/>
+      <c r="K83" s="36">
         <v>111</v>
       </c>
-      <c r="L83" s="27"/>
-      <c r="M83" s="36" t="s">
+      <c r="L83" s="28"/>
+      <c r="M83" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="32"/>
+      <c r="N83" s="33"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4364,30 +4444,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="26">
+      <c r="C84" s="27">
         <v>44781</v>
       </c>
-      <c r="D84" s="27"/>
+      <c r="D84" s="28"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="28" t="s">
+      <c r="F84" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="29"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="27"/>
-      <c r="K84" s="30">
+      <c r="G84" s="30"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="28"/>
+      <c r="K84" s="31">
         <v>77</v>
       </c>
-      <c r="L84" s="27"/>
-      <c r="M84" s="31" t="s">
+      <c r="L84" s="28"/>
+      <c r="M84" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="32"/>
+      <c r="N84" s="33"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4396,30 +4476,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="33">
+      <c r="C85" s="34">
         <v>44781</v>
       </c>
-      <c r="D85" s="27"/>
+      <c r="D85" s="28"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="34" t="s">
+      <c r="F85" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="29"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="27"/>
-      <c r="K85" s="35">
+      <c r="G85" s="30"/>
+      <c r="H85" s="28"/>
+      <c r="I85" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="28"/>
+      <c r="K85" s="36">
         <v>20</v>
       </c>
-      <c r="L85" s="27"/>
-      <c r="M85" s="36" t="s">
+      <c r="L85" s="28"/>
+      <c r="M85" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="32"/>
+      <c r="N85" s="33"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4428,30 +4508,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="26">
+      <c r="C86" s="27">
         <v>44781</v>
       </c>
-      <c r="D86" s="27"/>
+      <c r="D86" s="28"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="28" t="s">
+      <c r="F86" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="29"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="27"/>
-      <c r="K86" s="30">
+      <c r="G86" s="30"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="28"/>
+      <c r="K86" s="31">
         <v>25</v>
       </c>
-      <c r="L86" s="27"/>
-      <c r="M86" s="31" t="s">
+      <c r="L86" s="28"/>
+      <c r="M86" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="32"/>
+      <c r="N86" s="33"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4460,30 +4540,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="33">
+      <c r="C87" s="34">
         <v>44781</v>
       </c>
-      <c r="D87" s="27"/>
+      <c r="D87" s="28"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="34" t="s">
+      <c r="F87" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="29"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="27"/>
-      <c r="K87" s="35">
+      <c r="G87" s="30"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="28"/>
+      <c r="K87" s="36">
         <v>21</v>
       </c>
-      <c r="L87" s="27"/>
-      <c r="M87" s="36" t="s">
+      <c r="L87" s="28"/>
+      <c r="M87" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="32"/>
+      <c r="N87" s="33"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4492,30 +4572,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="26">
+      <c r="C88" s="27">
         <v>44781</v>
       </c>
-      <c r="D88" s="27"/>
+      <c r="D88" s="28"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="28" t="s">
+      <c r="F88" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="29"/>
-      <c r="H88" s="27"/>
-      <c r="I88" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="27"/>
-      <c r="K88" s="30">
+      <c r="G88" s="30"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="28"/>
+      <c r="K88" s="31">
         <v>86</v>
       </c>
-      <c r="L88" s="27"/>
-      <c r="M88" s="31" t="s">
+      <c r="L88" s="28"/>
+      <c r="M88" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="32"/>
+      <c r="N88" s="33"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4524,30 +4604,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="33">
+      <c r="C89" s="34">
         <v>44781</v>
       </c>
-      <c r="D89" s="27"/>
+      <c r="D89" s="28"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="34" t="s">
+      <c r="F89" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="29"/>
-      <c r="H89" s="27"/>
-      <c r="I89" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="27"/>
-      <c r="K89" s="35">
+      <c r="G89" s="30"/>
+      <c r="H89" s="28"/>
+      <c r="I89" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="28"/>
+      <c r="K89" s="36">
         <v>9</v>
       </c>
-      <c r="L89" s="27"/>
-      <c r="M89" s="36" t="s">
+      <c r="L89" s="28"/>
+      <c r="M89" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="32"/>
+      <c r="N89" s="33"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4556,30 +4636,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="26">
+      <c r="C90" s="27">
         <v>44781</v>
       </c>
-      <c r="D90" s="27"/>
+      <c r="D90" s="28"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="28" t="s">
+      <c r="F90" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="29"/>
-      <c r="H90" s="27"/>
-      <c r="I90" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="27"/>
-      <c r="K90" s="30">
+      <c r="G90" s="30"/>
+      <c r="H90" s="28"/>
+      <c r="I90" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="28"/>
+      <c r="K90" s="31">
         <v>2</v>
       </c>
-      <c r="L90" s="27"/>
-      <c r="M90" s="31" t="s">
+      <c r="L90" s="28"/>
+      <c r="M90" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="32"/>
+      <c r="N90" s="33"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4588,30 +4668,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="33">
+      <c r="C91" s="34">
         <v>44781</v>
       </c>
-      <c r="D91" s="27"/>
+      <c r="D91" s="28"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="34" t="s">
+      <c r="F91" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="29"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="34" t="s">
+      <c r="G91" s="30"/>
+      <c r="H91" s="28"/>
+      <c r="I91" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="27"/>
-      <c r="K91" s="35">
+      <c r="J91" s="28"/>
+      <c r="K91" s="36">
         <v>73</v>
       </c>
-      <c r="L91" s="27"/>
-      <c r="M91" s="36" t="s">
+      <c r="L91" s="28"/>
+      <c r="M91" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="32"/>
+      <c r="N91" s="33"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4620,30 +4700,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="26">
+      <c r="C92" s="27">
         <v>44782</v>
       </c>
-      <c r="D92" s="27"/>
+      <c r="D92" s="28"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="28" t="s">
+      <c r="F92" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="29"/>
-      <c r="H92" s="27"/>
-      <c r="I92" s="28" t="s">
+      <c r="G92" s="30"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="27"/>
-      <c r="K92" s="30">
+      <c r="J92" s="28"/>
+      <c r="K92" s="31">
         <v>33</v>
       </c>
-      <c r="L92" s="27"/>
-      <c r="M92" s="31" t="s">
+      <c r="L92" s="28"/>
+      <c r="M92" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="32"/>
+      <c r="N92" s="33"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4652,30 +4732,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="33">
+      <c r="C93" s="34">
         <v>44782</v>
       </c>
-      <c r="D93" s="27"/>
+      <c r="D93" s="28"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="34" t="s">
+      <c r="F93" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="29"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="34" t="s">
+      <c r="G93" s="30"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="27"/>
-      <c r="K93" s="35">
+      <c r="J93" s="28"/>
+      <c r="K93" s="36">
         <v>57</v>
       </c>
-      <c r="L93" s="27"/>
-      <c r="M93" s="36" t="s">
+      <c r="L93" s="28"/>
+      <c r="M93" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="32"/>
+      <c r="N93" s="33"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -4684,30 +4764,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="26">
+      <c r="C94" s="27">
         <v>44782</v>
       </c>
-      <c r="D94" s="27"/>
+      <c r="D94" s="28"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="28" t="s">
+      <c r="F94" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="29"/>
-      <c r="H94" s="27"/>
-      <c r="I94" s="28" t="s">
+      <c r="G94" s="30"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="27"/>
-      <c r="K94" s="30">
+      <c r="J94" s="28"/>
+      <c r="K94" s="31">
         <v>16</v>
       </c>
-      <c r="L94" s="27"/>
-      <c r="M94" s="31" t="s">
+      <c r="L94" s="28"/>
+      <c r="M94" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="32"/>
+      <c r="N94" s="33"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -4716,30 +4796,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="33">
+      <c r="C95" s="34">
         <v>44782</v>
       </c>
-      <c r="D95" s="27"/>
+      <c r="D95" s="28"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="34" t="s">
+      <c r="F95" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="29"/>
-      <c r="H95" s="27"/>
-      <c r="I95" s="34" t="s">
+      <c r="G95" s="30"/>
+      <c r="H95" s="28"/>
+      <c r="I95" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="27"/>
-      <c r="K95" s="35">
+      <c r="J95" s="28"/>
+      <c r="K95" s="36">
         <v>3</v>
       </c>
-      <c r="L95" s="27"/>
-      <c r="M95" s="36" t="s">
+      <c r="L95" s="28"/>
+      <c r="M95" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="32"/>
+      <c r="N95" s="33"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -4748,30 +4828,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="26">
+      <c r="C96" s="27">
         <v>44782</v>
       </c>
-      <c r="D96" s="27"/>
+      <c r="D96" s="28"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="28" t="s">
+      <c r="F96" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="29"/>
-      <c r="H96" s="27"/>
-      <c r="I96" s="28" t="s">
+      <c r="G96" s="30"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="27"/>
-      <c r="K96" s="30">
+      <c r="J96" s="28"/>
+      <c r="K96" s="31">
         <v>15</v>
       </c>
-      <c r="L96" s="27"/>
-      <c r="M96" s="31" t="s">
+      <c r="L96" s="28"/>
+      <c r="M96" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="32"/>
+      <c r="N96" s="33"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -4780,30 +4860,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="33">
+      <c r="C97" s="34">
         <v>44783</v>
       </c>
-      <c r="D97" s="27"/>
+      <c r="D97" s="28"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="34" t="s">
+      <c r="F97" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="29"/>
-      <c r="H97" s="27"/>
-      <c r="I97" s="34" t="s">
+      <c r="G97" s="30"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="27"/>
-      <c r="K97" s="35">
+      <c r="J97" s="28"/>
+      <c r="K97" s="36">
         <v>64</v>
       </c>
-      <c r="L97" s="27"/>
-      <c r="M97" s="36" t="s">
+      <c r="L97" s="28"/>
+      <c r="M97" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="32"/>
+      <c r="N97" s="33"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -4812,30 +4892,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="26">
+      <c r="C98" s="27">
         <v>44783</v>
       </c>
-      <c r="D98" s="27"/>
+      <c r="D98" s="28"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="28" t="s">
+      <c r="F98" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="29"/>
-      <c r="H98" s="27"/>
-      <c r="I98" s="28" t="s">
+      <c r="G98" s="30"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="27"/>
-      <c r="K98" s="30">
+      <c r="J98" s="28"/>
+      <c r="K98" s="31">
         <v>100</v>
       </c>
-      <c r="L98" s="27"/>
-      <c r="M98" s="31" t="s">
+      <c r="L98" s="28"/>
+      <c r="M98" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="32"/>
+      <c r="N98" s="33"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -4844,30 +4924,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="33">
+      <c r="C99" s="34">
         <v>44783</v>
       </c>
-      <c r="D99" s="27"/>
+      <c r="D99" s="28"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="34" t="s">
+      <c r="F99" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="29"/>
-      <c r="H99" s="27"/>
-      <c r="I99" s="34" t="s">
+      <c r="G99" s="30"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="27"/>
-      <c r="K99" s="35">
+      <c r="J99" s="28"/>
+      <c r="K99" s="36">
         <v>193</v>
       </c>
-      <c r="L99" s="27"/>
-      <c r="M99" s="36" t="s">
+      <c r="L99" s="28"/>
+      <c r="M99" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="32"/>
+      <c r="N99" s="33"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -4876,30 +4956,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="26">
+      <c r="C100" s="27">
         <v>44783</v>
       </c>
-      <c r="D100" s="27"/>
+      <c r="D100" s="28"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="28" t="s">
+      <c r="F100" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="29"/>
-      <c r="H100" s="27"/>
-      <c r="I100" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="27"/>
-      <c r="K100" s="30">
+      <c r="G100" s="30"/>
+      <c r="H100" s="28"/>
+      <c r="I100" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="28"/>
+      <c r="K100" s="31">
         <v>15</v>
       </c>
-      <c r="L100" s="27"/>
-      <c r="M100" s="31" t="s">
+      <c r="L100" s="28"/>
+      <c r="M100" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="32"/>
+      <c r="N100" s="33"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -4908,30 +4988,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="33">
+      <c r="C101" s="34">
         <v>44783</v>
       </c>
-      <c r="D101" s="27"/>
+      <c r="D101" s="28"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="34" t="s">
+      <c r="F101" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="29"/>
-      <c r="H101" s="27"/>
-      <c r="I101" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="27"/>
-      <c r="K101" s="35">
+      <c r="G101" s="30"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="28"/>
+      <c r="K101" s="36">
         <v>65</v>
       </c>
-      <c r="L101" s="27"/>
-      <c r="M101" s="36" t="s">
+      <c r="L101" s="28"/>
+      <c r="M101" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="32"/>
+      <c r="N101" s="33"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -4940,30 +5020,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="26">
+      <c r="C102" s="27">
         <v>44783</v>
       </c>
-      <c r="D102" s="27"/>
+      <c r="D102" s="28"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="28" t="s">
+      <c r="F102" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="29"/>
-      <c r="H102" s="27"/>
-      <c r="I102" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="27"/>
-      <c r="K102" s="30">
+      <c r="G102" s="30"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="28"/>
+      <c r="K102" s="31">
         <v>66</v>
       </c>
-      <c r="L102" s="27"/>
-      <c r="M102" s="31" t="s">
+      <c r="L102" s="28"/>
+      <c r="M102" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="32"/>
+      <c r="N102" s="33"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -4972,30 +5052,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="33">
+      <c r="C103" s="34">
         <v>44784</v>
       </c>
-      <c r="D103" s="27"/>
+      <c r="D103" s="28"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="34" t="s">
+      <c r="F103" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="29"/>
-      <c r="H103" s="27"/>
-      <c r="I103" s="34" t="s">
+      <c r="G103" s="30"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="27"/>
-      <c r="K103" s="35">
+      <c r="J103" s="28"/>
+      <c r="K103" s="36">
         <v>111</v>
       </c>
-      <c r="L103" s="27"/>
-      <c r="M103" s="36" t="s">
+      <c r="L103" s="28"/>
+      <c r="M103" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="32"/>
+      <c r="N103" s="33"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5004,30 +5084,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="26">
+      <c r="C104" s="27">
         <v>44784</v>
       </c>
-      <c r="D104" s="27"/>
+      <c r="D104" s="28"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="28" t="s">
+      <c r="F104" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="29"/>
-      <c r="H104" s="27"/>
-      <c r="I104" s="28" t="s">
+      <c r="G104" s="30"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="27"/>
-      <c r="K104" s="30">
+      <c r="J104" s="28"/>
+      <c r="K104" s="31">
         <v>30</v>
       </c>
-      <c r="L104" s="27"/>
-      <c r="M104" s="31" t="s">
+      <c r="L104" s="28"/>
+      <c r="M104" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="32"/>
+      <c r="N104" s="33"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5036,30 +5116,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="33">
+      <c r="C105" s="34">
         <v>44784</v>
       </c>
-      <c r="D105" s="27"/>
+      <c r="D105" s="28"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="34" t="s">
+      <c r="F105" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="29"/>
-      <c r="H105" s="27"/>
-      <c r="I105" s="34" t="s">
+      <c r="G105" s="30"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="27"/>
-      <c r="K105" s="35">
+      <c r="J105" s="28"/>
+      <c r="K105" s="36">
         <v>31</v>
       </c>
-      <c r="L105" s="27"/>
-      <c r="M105" s="36" t="s">
+      <c r="L105" s="28"/>
+      <c r="M105" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="32"/>
+      <c r="N105" s="33"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5068,30 +5148,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="26">
+      <c r="C106" s="27">
         <v>44784</v>
       </c>
-      <c r="D106" s="27"/>
+      <c r="D106" s="28"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="28" t="s">
+      <c r="F106" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="29"/>
-      <c r="H106" s="27"/>
-      <c r="I106" s="28" t="s">
+      <c r="G106" s="30"/>
+      <c r="H106" s="28"/>
+      <c r="I106" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="27"/>
-      <c r="K106" s="30">
+      <c r="J106" s="28"/>
+      <c r="K106" s="31">
         <v>109</v>
       </c>
-      <c r="L106" s="27"/>
-      <c r="M106" s="31" t="s">
+      <c r="L106" s="28"/>
+      <c r="M106" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="32"/>
+      <c r="N106" s="33"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5100,30 +5180,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="33">
+      <c r="C107" s="34">
         <v>44788</v>
       </c>
-      <c r="D107" s="27"/>
+      <c r="D107" s="28"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="34" t="s">
+      <c r="F107" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="29"/>
-      <c r="H107" s="27"/>
-      <c r="I107" s="34" t="s">
+      <c r="G107" s="30"/>
+      <c r="H107" s="28"/>
+      <c r="I107" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="27"/>
-      <c r="K107" s="35">
+      <c r="J107" s="28"/>
+      <c r="K107" s="36">
         <v>5</v>
       </c>
-      <c r="L107" s="27"/>
-      <c r="M107" s="36" t="s">
+      <c r="L107" s="28"/>
+      <c r="M107" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="32"/>
+      <c r="N107" s="33"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5132,30 +5212,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="26">
+      <c r="C108" s="27">
         <v>44788</v>
       </c>
-      <c r="D108" s="27"/>
+      <c r="D108" s="28"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="28" t="s">
+      <c r="F108" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="29"/>
-      <c r="H108" s="27"/>
-      <c r="I108" s="28" t="s">
+      <c r="G108" s="30"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="27"/>
-      <c r="K108" s="30">
+      <c r="J108" s="28"/>
+      <c r="K108" s="31">
         <v>100</v>
       </c>
-      <c r="L108" s="27"/>
-      <c r="M108" s="31" t="s">
+      <c r="L108" s="28"/>
+      <c r="M108" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="32"/>
+      <c r="N108" s="33"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5164,30 +5244,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="33">
+      <c r="C109" s="34">
         <v>44788</v>
       </c>
-      <c r="D109" s="27"/>
+      <c r="D109" s="28"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="34" t="s">
+      <c r="F109" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="29"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="27"/>
-      <c r="K109" s="35">
+      <c r="G109" s="30"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="28"/>
+      <c r="K109" s="36">
         <v>54</v>
       </c>
-      <c r="L109" s="27"/>
-      <c r="M109" s="36" t="s">
+      <c r="L109" s="28"/>
+      <c r="M109" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="32"/>
+      <c r="N109" s="33"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5196,30 +5276,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="26">
+      <c r="C110" s="27">
         <v>44789</v>
       </c>
-      <c r="D110" s="27"/>
+      <c r="D110" s="28"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="28" t="s">
+      <c r="F110" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="29"/>
-      <c r="H110" s="27"/>
-      <c r="I110" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="27"/>
-      <c r="K110" s="30">
+      <c r="G110" s="30"/>
+      <c r="H110" s="28"/>
+      <c r="I110" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="28"/>
+      <c r="K110" s="31">
         <v>77</v>
       </c>
-      <c r="L110" s="27"/>
-      <c r="M110" s="31" t="s">
+      <c r="L110" s="28"/>
+      <c r="M110" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="32"/>
+      <c r="N110" s="33"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5228,30 +5308,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="33">
+      <c r="C111" s="34">
         <v>44789</v>
       </c>
-      <c r="D111" s="27"/>
+      <c r="D111" s="28"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="34" t="s">
+      <c r="F111" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="29"/>
-      <c r="H111" s="27"/>
-      <c r="I111" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="27"/>
-      <c r="K111" s="35">
+      <c r="G111" s="30"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="28"/>
+      <c r="K111" s="36">
         <v>52</v>
       </c>
-      <c r="L111" s="27"/>
-      <c r="M111" s="36" t="s">
+      <c r="L111" s="28"/>
+      <c r="M111" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="32"/>
+      <c r="N111" s="33"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5260,30 +5340,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="26">
+      <c r="C112" s="27">
         <v>44789</v>
       </c>
-      <c r="D112" s="27"/>
+      <c r="D112" s="28"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="28" t="s">
+      <c r="F112" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="29"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="28" t="s">
+      <c r="G112" s="30"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="27"/>
-      <c r="K112" s="30">
+      <c r="J112" s="28"/>
+      <c r="K112" s="31">
         <v>305</v>
       </c>
-      <c r="L112" s="27"/>
-      <c r="M112" s="31" t="s">
+      <c r="L112" s="28"/>
+      <c r="M112" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="32"/>
+      <c r="N112" s="33"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5292,30 +5372,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="33">
+      <c r="C113" s="34">
         <v>44789</v>
       </c>
-      <c r="D113" s="27"/>
+      <c r="D113" s="28"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="34" t="s">
+      <c r="F113" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="29"/>
-      <c r="H113" s="27"/>
-      <c r="I113" s="34" t="s">
+      <c r="G113" s="30"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="27"/>
-      <c r="K113" s="35">
+      <c r="J113" s="28"/>
+      <c r="K113" s="36">
         <v>81</v>
       </c>
-      <c r="L113" s="27"/>
-      <c r="M113" s="36" t="s">
+      <c r="L113" s="28"/>
+      <c r="M113" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="32"/>
+      <c r="N113" s="33"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5324,30 +5404,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="26">
+      <c r="C114" s="27">
         <v>44789</v>
       </c>
-      <c r="D114" s="27"/>
+      <c r="D114" s="28"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="28" t="s">
+      <c r="F114" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="29"/>
-      <c r="H114" s="27"/>
-      <c r="I114" s="28" t="s">
+      <c r="G114" s="30"/>
+      <c r="H114" s="28"/>
+      <c r="I114" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="27"/>
-      <c r="K114" s="30">
+      <c r="J114" s="28"/>
+      <c r="K114" s="31">
         <v>53</v>
       </c>
-      <c r="L114" s="27"/>
-      <c r="M114" s="31" t="s">
+      <c r="L114" s="28"/>
+      <c r="M114" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="32"/>
+      <c r="N114" s="33"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5356,30 +5436,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="33">
+      <c r="C115" s="34">
         <v>44789</v>
       </c>
-      <c r="D115" s="27"/>
+      <c r="D115" s="28"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="34" t="s">
+      <c r="F115" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="29"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="34" t="s">
+      <c r="G115" s="30"/>
+      <c r="H115" s="28"/>
+      <c r="I115" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="27"/>
-      <c r="K115" s="35">
+      <c r="J115" s="28"/>
+      <c r="K115" s="36">
         <v>33</v>
       </c>
-      <c r="L115" s="27"/>
-      <c r="M115" s="36" t="s">
+      <c r="L115" s="28"/>
+      <c r="M115" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="32"/>
+      <c r="N115" s="33"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5388,30 +5468,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="26">
+      <c r="C116" s="27">
         <v>44790</v>
       </c>
-      <c r="D116" s="27"/>
+      <c r="D116" s="28"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="28" t="s">
+      <c r="F116" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="29"/>
-      <c r="H116" s="27"/>
-      <c r="I116" s="28" t="s">
+      <c r="G116" s="30"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="27"/>
-      <c r="K116" s="30">
+      <c r="J116" s="28"/>
+      <c r="K116" s="31">
         <v>145</v>
       </c>
-      <c r="L116" s="27"/>
-      <c r="M116" s="31" t="s">
+      <c r="L116" s="28"/>
+      <c r="M116" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="32"/>
+      <c r="N116" s="33"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5420,30 +5500,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="33">
+      <c r="C117" s="34">
         <v>44790</v>
       </c>
-      <c r="D117" s="27"/>
+      <c r="D117" s="28"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="34" t="s">
+      <c r="F117" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="29"/>
-      <c r="H117" s="27"/>
-      <c r="I117" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="27"/>
-      <c r="K117" s="35">
+      <c r="G117" s="30"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="28"/>
+      <c r="K117" s="36">
         <v>14</v>
       </c>
-      <c r="L117" s="27"/>
-      <c r="M117" s="36" t="s">
+      <c r="L117" s="28"/>
+      <c r="M117" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="32"/>
+      <c r="N117" s="33"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5452,30 +5532,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="26">
+      <c r="C118" s="27">
         <v>44790</v>
       </c>
-      <c r="D118" s="27"/>
+      <c r="D118" s="28"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="28" t="s">
+      <c r="F118" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="29"/>
-      <c r="H118" s="27"/>
-      <c r="I118" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="27"/>
-      <c r="K118" s="30">
+      <c r="G118" s="30"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="28"/>
+      <c r="K118" s="31">
         <v>47</v>
       </c>
-      <c r="L118" s="27"/>
-      <c r="M118" s="31" t="s">
+      <c r="L118" s="28"/>
+      <c r="M118" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="32"/>
+      <c r="N118" s="33"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5484,30 +5564,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="33">
+      <c r="C119" s="34">
         <v>44790</v>
       </c>
-      <c r="D119" s="27"/>
+      <c r="D119" s="28"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="34" t="s">
+      <c r="F119" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="29"/>
-      <c r="H119" s="27"/>
-      <c r="I119" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="27"/>
-      <c r="K119" s="35">
+      <c r="G119" s="30"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="28"/>
+      <c r="K119" s="36">
         <v>16</v>
       </c>
-      <c r="L119" s="27"/>
-      <c r="M119" s="36" t="s">
+      <c r="L119" s="28"/>
+      <c r="M119" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="32"/>
+      <c r="N119" s="33"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5516,30 +5596,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="26">
+      <c r="C120" s="27">
         <v>44790</v>
       </c>
-      <c r="D120" s="27"/>
+      <c r="D120" s="28"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="28" t="s">
+      <c r="F120" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="29"/>
-      <c r="H120" s="27"/>
-      <c r="I120" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="27"/>
-      <c r="K120" s="30">
+      <c r="G120" s="30"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="28"/>
+      <c r="K120" s="31">
         <v>55</v>
       </c>
-      <c r="L120" s="27"/>
-      <c r="M120" s="31" t="s">
+      <c r="L120" s="28"/>
+      <c r="M120" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="32"/>
+      <c r="N120" s="33"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5548,30 +5628,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="33">
+      <c r="C121" s="34">
         <v>44790</v>
       </c>
-      <c r="D121" s="27"/>
+      <c r="D121" s="28"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="34" t="s">
+      <c r="F121" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="29"/>
-      <c r="H121" s="27"/>
-      <c r="I121" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="27"/>
-      <c r="K121" s="35">
+      <c r="G121" s="30"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="28"/>
+      <c r="K121" s="36">
         <v>8</v>
       </c>
-      <c r="L121" s="27"/>
-      <c r="M121" s="36" t="s">
+      <c r="L121" s="28"/>
+      <c r="M121" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="32"/>
+      <c r="N121" s="33"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5580,30 +5660,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="26">
+      <c r="C122" s="27">
         <v>44790</v>
       </c>
-      <c r="D122" s="27"/>
+      <c r="D122" s="28"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="28" t="s">
+      <c r="F122" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="29"/>
-      <c r="H122" s="27"/>
-      <c r="I122" s="28" t="s">
+      <c r="G122" s="30"/>
+      <c r="H122" s="28"/>
+      <c r="I122" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="27"/>
-      <c r="K122" s="30">
+      <c r="J122" s="28"/>
+      <c r="K122" s="31">
         <v>578</v>
       </c>
-      <c r="L122" s="27"/>
-      <c r="M122" s="31" t="s">
+      <c r="L122" s="28"/>
+      <c r="M122" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="32"/>
+      <c r="N122" s="33"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5612,30 +5692,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="33">
+      <c r="C123" s="34">
         <v>44791</v>
       </c>
-      <c r="D123" s="27"/>
+      <c r="D123" s="28"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="34" t="s">
+      <c r="F123" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="29"/>
-      <c r="H123" s="27"/>
-      <c r="I123" s="34" t="s">
+      <c r="G123" s="30"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="27"/>
-      <c r="K123" s="35">
+      <c r="J123" s="28"/>
+      <c r="K123" s="36">
         <v>111</v>
       </c>
-      <c r="L123" s="27"/>
-      <c r="M123" s="36" t="s">
+      <c r="L123" s="28"/>
+      <c r="M123" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="32"/>
+      <c r="N123" s="33"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5644,30 +5724,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="26">
+      <c r="C124" s="27">
         <v>44791</v>
       </c>
-      <c r="D124" s="27"/>
+      <c r="D124" s="28"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="28" t="s">
+      <c r="F124" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="29"/>
-      <c r="H124" s="27"/>
-      <c r="I124" s="28" t="s">
+      <c r="G124" s="30"/>
+      <c r="H124" s="28"/>
+      <c r="I124" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="27"/>
-      <c r="K124" s="30">
+      <c r="J124" s="28"/>
+      <c r="K124" s="31">
         <v>51</v>
       </c>
-      <c r="L124" s="27"/>
-      <c r="M124" s="31" t="s">
+      <c r="L124" s="28"/>
+      <c r="M124" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="32"/>
+      <c r="N124" s="33"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5676,30 +5756,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="33">
+      <c r="C125" s="34">
         <v>44791</v>
       </c>
-      <c r="D125" s="27"/>
+      <c r="D125" s="28"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="34" t="s">
+      <c r="F125" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="29"/>
-      <c r="H125" s="27"/>
-      <c r="I125" s="34" t="s">
+      <c r="G125" s="30"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="27"/>
-      <c r="K125" s="35">
+      <c r="J125" s="28"/>
+      <c r="K125" s="36">
         <v>35</v>
       </c>
-      <c r="L125" s="27"/>
-      <c r="M125" s="36" t="s">
+      <c r="L125" s="28"/>
+      <c r="M125" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="32"/>
+      <c r="N125" s="33"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -5708,30 +5788,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="26">
+      <c r="C126" s="27">
         <v>44792</v>
       </c>
-      <c r="D126" s="27"/>
+      <c r="D126" s="28"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="28" t="s">
+      <c r="F126" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="29"/>
-      <c r="H126" s="27"/>
-      <c r="I126" s="28" t="s">
+      <c r="G126" s="30"/>
+      <c r="H126" s="28"/>
+      <c r="I126" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="27"/>
-      <c r="K126" s="30">
+      <c r="J126" s="28"/>
+      <c r="K126" s="31">
         <v>74</v>
       </c>
-      <c r="L126" s="27"/>
-      <c r="M126" s="31" t="s">
+      <c r="L126" s="28"/>
+      <c r="M126" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="32"/>
+      <c r="N126" s="33"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -5740,30 +5820,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="33">
+      <c r="C127" s="34">
         <v>44795</v>
       </c>
-      <c r="D127" s="27"/>
+      <c r="D127" s="28"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="34" t="s">
+      <c r="F127" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="29"/>
-      <c r="H127" s="27"/>
-      <c r="I127" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="27"/>
-      <c r="K127" s="35">
+      <c r="G127" s="30"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="28"/>
+      <c r="K127" s="36">
         <v>51</v>
       </c>
-      <c r="L127" s="27"/>
-      <c r="M127" s="36" t="s">
+      <c r="L127" s="28"/>
+      <c r="M127" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="32"/>
+      <c r="N127" s="33"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -5772,30 +5852,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="26">
+      <c r="C128" s="27">
         <v>44799</v>
       </c>
-      <c r="D128" s="27"/>
+      <c r="D128" s="28"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="28" t="s">
+      <c r="F128" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="29"/>
-      <c r="H128" s="27"/>
-      <c r="I128" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="27"/>
-      <c r="K128" s="30">
+      <c r="G128" s="30"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="28"/>
+      <c r="K128" s="31">
         <v>80</v>
       </c>
-      <c r="L128" s="27"/>
-      <c r="M128" s="31" t="s">
+      <c r="L128" s="28"/>
+      <c r="M128" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="32"/>
+      <c r="N128" s="33"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -5804,30 +5884,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="33">
+      <c r="C129" s="34">
         <v>44799</v>
       </c>
-      <c r="D129" s="27"/>
+      <c r="D129" s="28"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="34" t="s">
+      <c r="F129" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="29"/>
-      <c r="H129" s="27"/>
-      <c r="I129" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="27"/>
-      <c r="K129" s="35">
+      <c r="G129" s="30"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="28"/>
+      <c r="K129" s="36">
         <v>100</v>
       </c>
-      <c r="L129" s="27"/>
-      <c r="M129" s="36" t="s">
+      <c r="L129" s="28"/>
+      <c r="M129" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="32"/>
+      <c r="N129" s="33"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -5836,30 +5916,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="26">
+      <c r="C130" s="27">
         <v>44802</v>
       </c>
-      <c r="D130" s="27"/>
+      <c r="D130" s="28"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="28" t="s">
+      <c r="F130" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="29"/>
-      <c r="H130" s="27"/>
-      <c r="I130" s="28" t="s">
+      <c r="G130" s="30"/>
+      <c r="H130" s="28"/>
+      <c r="I130" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="27"/>
-      <c r="K130" s="30">
+      <c r="J130" s="28"/>
+      <c r="K130" s="31">
         <v>96</v>
       </c>
-      <c r="L130" s="27"/>
-      <c r="M130" s="31" t="s">
+      <c r="L130" s="28"/>
+      <c r="M130" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="32"/>
+      <c r="N130" s="33"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -5868,30 +5948,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="33">
+      <c r="C131" s="34">
         <v>44802</v>
       </c>
-      <c r="D131" s="27"/>
+      <c r="D131" s="28"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="34" t="s">
+      <c r="F131" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="29"/>
-      <c r="H131" s="27"/>
-      <c r="I131" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="27"/>
-      <c r="K131" s="35">
+      <c r="G131" s="30"/>
+      <c r="H131" s="28"/>
+      <c r="I131" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="28"/>
+      <c r="K131" s="36">
         <v>37</v>
       </c>
-      <c r="L131" s="27"/>
-      <c r="M131" s="36" t="s">
+      <c r="L131" s="28"/>
+      <c r="M131" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="32"/>
+      <c r="N131" s="33"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -5900,30 +5980,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="26">
+      <c r="C132" s="27">
         <v>44804</v>
       </c>
-      <c r="D132" s="27"/>
+      <c r="D132" s="28"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="28" t="s">
+      <c r="F132" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="29"/>
-      <c r="H132" s="27"/>
-      <c r="I132" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="27"/>
-      <c r="K132" s="30">
+      <c r="G132" s="30"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="28"/>
+      <c r="K132" s="31">
         <v>91</v>
       </c>
-      <c r="L132" s="27"/>
-      <c r="M132" s="31" t="s">
+      <c r="L132" s="28"/>
+      <c r="M132" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="32"/>
+      <c r="N132" s="33"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -5932,30 +6012,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="33">
+      <c r="C133" s="34">
         <v>44804</v>
       </c>
-      <c r="D133" s="27"/>
+      <c r="D133" s="28"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="34" t="s">
+      <c r="F133" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="29"/>
-      <c r="H133" s="27"/>
-      <c r="I133" s="34" t="s">
+      <c r="G133" s="30"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="27"/>
-      <c r="K133" s="35">
+      <c r="J133" s="28"/>
+      <c r="K133" s="36">
         <v>56</v>
       </c>
-      <c r="L133" s="27"/>
-      <c r="M133" s="36" t="s">
+      <c r="L133" s="28"/>
+      <c r="M133" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="32"/>
+      <c r="N133" s="33"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -5964,30 +6044,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="26">
+      <c r="C134" s="27">
         <v>44805</v>
       </c>
-      <c r="D134" s="27"/>
+      <c r="D134" s="28"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="28" t="s">
+      <c r="F134" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="29"/>
-      <c r="H134" s="27"/>
-      <c r="I134" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="27"/>
-      <c r="K134" s="30">
+      <c r="G134" s="30"/>
+      <c r="H134" s="28"/>
+      <c r="I134" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="28"/>
+      <c r="K134" s="31">
         <v>401</v>
       </c>
-      <c r="L134" s="27"/>
-      <c r="M134" s="31" t="s">
+      <c r="L134" s="28"/>
+      <c r="M134" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="32"/>
+      <c r="N134" s="33"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -5996,30 +6076,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="33">
+      <c r="C135" s="34">
         <v>44805</v>
       </c>
-      <c r="D135" s="27"/>
+      <c r="D135" s="28"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="34" t="s">
+      <c r="F135" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="29"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="34" t="s">
+      <c r="G135" s="30"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="27"/>
-      <c r="K135" s="35">
+      <c r="J135" s="28"/>
+      <c r="K135" s="36">
         <v>375</v>
       </c>
-      <c r="L135" s="27"/>
-      <c r="M135" s="36" t="s">
+      <c r="L135" s="28"/>
+      <c r="M135" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="32"/>
+      <c r="N135" s="33"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6028,30 +6108,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="26">
+      <c r="C136" s="27">
         <v>44806</v>
       </c>
-      <c r="D136" s="27"/>
+      <c r="D136" s="28"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="28" t="s">
+      <c r="F136" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="29"/>
-      <c r="H136" s="27"/>
-      <c r="I136" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="27"/>
-      <c r="K136" s="30">
+      <c r="G136" s="30"/>
+      <c r="H136" s="28"/>
+      <c r="I136" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="28"/>
+      <c r="K136" s="31">
         <v>44</v>
       </c>
-      <c r="L136" s="27"/>
-      <c r="M136" s="31" t="s">
+      <c r="L136" s="28"/>
+      <c r="M136" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="32"/>
+      <c r="N136" s="33"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6060,30 +6140,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="33">
+      <c r="C137" s="34">
         <v>44806</v>
       </c>
-      <c r="D137" s="27"/>
+      <c r="D137" s="28"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="34" t="s">
+      <c r="F137" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="29"/>
-      <c r="H137" s="27"/>
-      <c r="I137" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="27"/>
-      <c r="K137" s="35">
+      <c r="G137" s="30"/>
+      <c r="H137" s="28"/>
+      <c r="I137" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="28"/>
+      <c r="K137" s="36">
         <v>51</v>
       </c>
-      <c r="L137" s="27"/>
-      <c r="M137" s="36" t="s">
+      <c r="L137" s="28"/>
+      <c r="M137" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="32"/>
+      <c r="N137" s="33"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6092,30 +6172,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="26">
+      <c r="C138" s="27">
         <v>44806</v>
       </c>
-      <c r="D138" s="27"/>
+      <c r="D138" s="28"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="28" t="s">
+      <c r="F138" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="29"/>
-      <c r="H138" s="27"/>
-      <c r="I138" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="27"/>
-      <c r="K138" s="30">
+      <c r="G138" s="30"/>
+      <c r="H138" s="28"/>
+      <c r="I138" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="28"/>
+      <c r="K138" s="31">
         <v>40</v>
       </c>
-      <c r="L138" s="27"/>
-      <c r="M138" s="31" t="s">
+      <c r="L138" s="28"/>
+      <c r="M138" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="32"/>
+      <c r="N138" s="33"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6124,30 +6204,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="33">
+      <c r="C139" s="34">
         <v>44810</v>
       </c>
-      <c r="D139" s="27"/>
+      <c r="D139" s="28"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="34" t="s">
+      <c r="F139" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="29"/>
-      <c r="H139" s="27"/>
-      <c r="I139" s="34" t="s">
+      <c r="G139" s="30"/>
+      <c r="H139" s="28"/>
+      <c r="I139" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="27"/>
-      <c r="K139" s="35">
+      <c r="J139" s="28"/>
+      <c r="K139" s="36">
         <v>9</v>
       </c>
-      <c r="L139" s="27"/>
-      <c r="M139" s="36" t="s">
+      <c r="L139" s="28"/>
+      <c r="M139" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="32"/>
+      <c r="N139" s="33"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6156,30 +6236,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="26">
+      <c r="C140" s="27">
         <v>44810</v>
       </c>
-      <c r="D140" s="27"/>
+      <c r="D140" s="28"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="28" t="s">
+      <c r="F140" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="29"/>
-      <c r="H140" s="27"/>
-      <c r="I140" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="27"/>
-      <c r="K140" s="30">
+      <c r="G140" s="30"/>
+      <c r="H140" s="28"/>
+      <c r="I140" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="28"/>
+      <c r="K140" s="31">
         <v>17</v>
       </c>
-      <c r="L140" s="27"/>
-      <c r="M140" s="31" t="s">
+      <c r="L140" s="28"/>
+      <c r="M140" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="32"/>
+      <c r="N140" s="33"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6188,30 +6268,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="33">
+      <c r="C141" s="34">
         <v>44810</v>
       </c>
-      <c r="D141" s="27"/>
+      <c r="D141" s="28"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="34" t="s">
+      <c r="F141" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="29"/>
-      <c r="H141" s="27"/>
-      <c r="I141" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="27"/>
-      <c r="K141" s="35">
+      <c r="G141" s="30"/>
+      <c r="H141" s="28"/>
+      <c r="I141" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="28"/>
+      <c r="K141" s="36">
         <v>5</v>
       </c>
-      <c r="L141" s="27"/>
-      <c r="M141" s="36" t="s">
+      <c r="L141" s="28"/>
+      <c r="M141" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="32"/>
+      <c r="N141" s="33"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6220,30 +6300,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="26">
+      <c r="C142" s="27">
         <v>44810</v>
       </c>
-      <c r="D142" s="27"/>
+      <c r="D142" s="28"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="28" t="s">
+      <c r="F142" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="29"/>
-      <c r="H142" s="27"/>
-      <c r="I142" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="27"/>
-      <c r="K142" s="30">
+      <c r="G142" s="30"/>
+      <c r="H142" s="28"/>
+      <c r="I142" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="28"/>
+      <c r="K142" s="31">
         <v>45</v>
       </c>
-      <c r="L142" s="27"/>
-      <c r="M142" s="31" t="s">
+      <c r="L142" s="28"/>
+      <c r="M142" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="32"/>
+      <c r="N142" s="33"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6252,30 +6332,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="33">
+      <c r="C143" s="34">
         <v>44811</v>
       </c>
-      <c r="D143" s="27"/>
+      <c r="D143" s="28"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="34" t="s">
+      <c r="F143" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="29"/>
-      <c r="H143" s="27"/>
-      <c r="I143" s="34" t="s">
+      <c r="G143" s="30"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="27"/>
-      <c r="K143" s="35">
+      <c r="J143" s="28"/>
+      <c r="K143" s="36">
         <v>132</v>
       </c>
-      <c r="L143" s="27"/>
-      <c r="M143" s="36" t="s">
+      <c r="L143" s="28"/>
+      <c r="M143" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="32"/>
+      <c r="N143" s="33"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6284,97 +6364,353 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="26">
+      <c r="C144" s="27">
         <v>44811</v>
       </c>
-      <c r="D144" s="27"/>
+      <c r="D144" s="28"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="28" t="s">
+      <c r="F144" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="29"/>
-      <c r="H144" s="27"/>
-      <c r="I144" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="27"/>
-      <c r="K144" s="30">
+      <c r="G144" s="30"/>
+      <c r="H144" s="28"/>
+      <c r="I144" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="28"/>
+      <c r="K144" s="31">
         <v>66</v>
       </c>
-      <c r="L144" s="27"/>
-      <c r="M144" s="31" t="s">
+      <c r="L144" s="28"/>
+      <c r="M144" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="32"/>
-    </row>
-    <row r="145" spans="1:14" ht="30" customHeight="1">
-      <c r="A145" s="24" t="s">
+      <c r="N144" s="33"/>
+    </row>
+    <row r="145" spans="1:14">
+      <c r="A145" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B145" s="2">
+        <v>44804</v>
+      </c>
+      <c r="C145" s="34">
+        <v>44812</v>
+      </c>
+      <c r="D145" s="28"/>
+      <c r="E145" s="2">
+        <v>44864</v>
+      </c>
+      <c r="F145" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="G145" s="30"/>
+      <c r="H145" s="28"/>
+      <c r="I145" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="28"/>
+      <c r="K145" s="36">
+        <v>69</v>
+      </c>
+      <c r="L145" s="28"/>
+      <c r="M145" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="N145" s="33"/>
+    </row>
+    <row r="146" spans="1:14">
+      <c r="A146" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B146" s="4">
+        <v>44812</v>
+      </c>
+      <c r="C146" s="27">
+        <v>44812</v>
+      </c>
+      <c r="D146" s="28"/>
+      <c r="E146" s="4">
+        <v>44876</v>
+      </c>
+      <c r="F146" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="G146" s="30"/>
+      <c r="H146" s="28"/>
+      <c r="I146" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J146" s="28"/>
+      <c r="K146" s="31">
+        <v>48</v>
+      </c>
+      <c r="L146" s="28"/>
+      <c r="M146" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="N146" s="33"/>
+    </row>
+    <row r="147" spans="1:14">
+      <c r="A147" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B147" s="2">
+        <v>44810</v>
+      </c>
+      <c r="C147" s="34">
+        <v>44812</v>
+      </c>
+      <c r="D147" s="28"/>
+      <c r="E147" s="2">
+        <v>44876</v>
+      </c>
+      <c r="F147" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="G147" s="30"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J147" s="28"/>
+      <c r="K147" s="36">
+        <v>33</v>
+      </c>
+      <c r="L147" s="28"/>
+      <c r="M147" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="N147" s="33"/>
+    </row>
+    <row r="148" spans="1:14">
+      <c r="A148" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="4">
+        <v>44778</v>
+      </c>
+      <c r="C148" s="27">
+        <v>44813</v>
+      </c>
+      <c r="D148" s="28"/>
+      <c r="E148" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F148" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="G148" s="30"/>
+      <c r="H148" s="28"/>
+      <c r="I148" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J148" s="28"/>
+      <c r="K148" s="31">
+        <v>5</v>
+      </c>
+      <c r="L148" s="28"/>
+      <c r="M148" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="N148" s="33"/>
+    </row>
+    <row r="149" spans="1:14">
+      <c r="A149" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B149" s="2">
+        <v>44811</v>
+      </c>
+      <c r="C149" s="34">
+        <v>44813</v>
+      </c>
+      <c r="D149" s="28"/>
+      <c r="E149" s="2">
+        <v>45046</v>
+      </c>
+      <c r="F149" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="G149" s="30"/>
+      <c r="H149" s="28"/>
+      <c r="I149" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J149" s="28"/>
+      <c r="K149" s="36">
+        <v>26</v>
+      </c>
+      <c r="L149" s="28"/>
+      <c r="M149" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="B145" s="25"/>
-      <c r="C145" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="D145" s="22"/>
-      <c r="E145" s="23"/>
-      <c r="F145" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="H145" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="I145" s="23"/>
-      <c r="J145" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="K145" s="23"/>
-      <c r="L145" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="M145" s="23"/>
-      <c r="N145" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" s="9" customFormat="1">
-      <c r="A146" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="B146" s="20"/>
-      <c r="C146" s="16">
-        <v>11033</v>
-      </c>
-      <c r="D146" s="17"/>
-      <c r="E146" s="18"/>
-      <c r="F146" s="7">
-        <v>84</v>
-      </c>
-      <c r="G146" s="7">
+      <c r="N149" s="33"/>
+    </row>
+    <row r="150" spans="1:14">
+      <c r="A150" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B150" s="4">
+        <v>44810</v>
+      </c>
+      <c r="C150" s="27">
+        <v>44813</v>
+      </c>
+      <c r="D150" s="28"/>
+      <c r="E150" s="4">
+        <v>44870</v>
+      </c>
+      <c r="F150" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="G150" s="30"/>
+      <c r="H150" s="28"/>
+      <c r="I150" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="28"/>
+      <c r="K150" s="31">
+        <v>13</v>
+      </c>
+      <c r="L150" s="28"/>
+      <c r="M150" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="N150" s="33"/>
+    </row>
+    <row r="151" spans="1:14">
+      <c r="A151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151" s="2">
+        <v>44812</v>
+      </c>
+      <c r="C151" s="34">
+        <v>44816</v>
+      </c>
+      <c r="D151" s="28"/>
+      <c r="E151" s="2">
+        <v>44873</v>
+      </c>
+      <c r="F151" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="G151" s="30"/>
+      <c r="H151" s="28"/>
+      <c r="I151" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J151" s="28"/>
+      <c r="K151" s="36">
+        <v>50</v>
+      </c>
+      <c r="L151" s="28"/>
+      <c r="M151" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="N151" s="33"/>
+    </row>
+    <row r="152" spans="1:14">
+      <c r="A152" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B152" s="4">
+        <v>44791</v>
+      </c>
+      <c r="C152" s="27">
+        <v>44816</v>
+      </c>
+      <c r="D152" s="28"/>
+      <c r="E152" s="4">
+        <v>44856</v>
+      </c>
+      <c r="F152" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="G152" s="30"/>
+      <c r="H152" s="28"/>
+      <c r="I152" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J152" s="28"/>
+      <c r="K152" s="31">
+        <v>104</v>
+      </c>
+      <c r="L152" s="28"/>
+      <c r="M152" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="N152" s="33"/>
+    </row>
+    <row r="153" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A153" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="B153" s="26"/>
+      <c r="C153" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="D153" s="23"/>
+      <c r="E153" s="24"/>
+      <c r="F153" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="H153" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="I153" s="24"/>
+      <c r="J153" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="K153" s="24"/>
+      <c r="L153" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="M153" s="24"/>
+      <c r="N153" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" s="8" customFormat="1">
+      <c r="A154" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B154" s="21"/>
+      <c r="C154" s="17">
+        <v>11381</v>
+      </c>
+      <c r="D154" s="18"/>
+      <c r="E154" s="19"/>
+      <c r="F154" s="6">
+        <v>86</v>
+      </c>
+      <c r="G154" s="15">
         <v>3</v>
       </c>
-      <c r="H146" s="16">
+      <c r="H154" s="17">
         <v>1</v>
       </c>
-      <c r="I146" s="18"/>
-      <c r="J146" s="16">
-        <v>51</v>
-      </c>
-      <c r="K146" s="18"/>
-      <c r="L146" s="16">
+      <c r="I154" s="19"/>
+      <c r="J154" s="17">
+        <v>57</v>
+      </c>
+      <c r="K154" s="19"/>
+      <c r="L154" s="17">
         <v>1</v>
       </c>
-      <c r="M146" s="18"/>
-      <c r="N146" s="8">
+      <c r="M154" s="19"/>
+      <c r="N154" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="722">
+  <mergeCells count="762">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="C4:D4"/>
@@ -7087,16 +7423,56 @@
     <mergeCell ref="I143:J143"/>
     <mergeCell ref="K143:L143"/>
     <mergeCell ref="M143:N143"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="H146:I146"/>
-    <mergeCell ref="J146:K146"/>
-    <mergeCell ref="L146:M146"/>
-    <mergeCell ref="A146:B146"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="H145:I145"/>
-    <mergeCell ref="J145:K145"/>
-    <mergeCell ref="L145:M145"/>
-    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="K146:L146"/>
+    <mergeCell ref="M146:N146"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="M145:N145"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="K148:L148"/>
+    <mergeCell ref="M148:N148"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="I147:J147"/>
+    <mergeCell ref="K147:L147"/>
+    <mergeCell ref="M147:N147"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="K150:L150"/>
+    <mergeCell ref="M150:N150"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="I149:J149"/>
+    <mergeCell ref="K149:L149"/>
+    <mergeCell ref="M149:N149"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="F152:H152"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="K152:L152"/>
+    <mergeCell ref="M152:N152"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="M151:N151"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="H154:I154"/>
+    <mergeCell ref="J154:K154"/>
+    <mergeCell ref="L154:M154"/>
+    <mergeCell ref="A154:B154"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="H153:I153"/>
+    <mergeCell ref="J153:K153"/>
+    <mergeCell ref="L153:M153"/>
+    <mergeCell ref="A153:B153"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\WEBSITE MANAGMENT\Worker Adjustment and Retraining Notification (WARN)\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15090" windowHeight="9375"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15096" windowHeight="9372"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="297">
   <si>
     <t/>
   </si>
@@ -890,6 +890,36 @@
     <t>8060 Frost Street  San Diego CA 92123</t>
   </si>
   <si>
+    <t>USRA at ARC</t>
+  </si>
+  <si>
+    <t>Bristol-Myers Squibb</t>
+  </si>
+  <si>
+    <t>10628 Science Center Drive Suite 200 San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>3580 Carmel Mountain Road  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>AbbVie Inc.</t>
+  </si>
+  <si>
+    <t>2525 Dupont Drive  Irvine CA 92612</t>
+  </si>
+  <si>
+    <t>Mouser Electronics</t>
+  </si>
+  <si>
+    <t>1810 Gillespie Way  El Cajon CA 92020</t>
+  </si>
+  <si>
+    <t>Marriott Resorts Hospitality Corporation and Marriott Ownership Resorts, Inc.</t>
+  </si>
+  <si>
+    <t>2620 Jones Street  San Francisco CA 94133</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -914,9 +944,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve"> Filter By Date: Received Date
+    <t xml:space="preserve">  Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 9/12/2022
+ End Date: 9/14/2022
 </t>
   </si>
   <si>
@@ -992,13 +1022,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFDCDCDC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFDCDCDC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1014,7 +1044,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1329,37 +1359,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA9A9A9"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9A9A9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9A9A9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA9A9A9"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9A9A9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -1373,18 +1377,24 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1399,11 +1409,74 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1420,89 +1493,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1784,130 +1791,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R154"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R175"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="3" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="3" max="3" width="2.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
+      <c r="A1" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="39" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="A2" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="43" t="s">
+      <c r="J3" s="18"/>
+      <c r="K3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="44"/>
-      <c r="M3" s="46" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="47"/>
-    </row>
-    <row r="4" spans="1:18" ht="24.75">
-      <c r="A4" s="13" t="s">
+      <c r="N3" s="21"/>
+    </row>
+    <row r="4" spans="1:18" ht="24.6">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="38" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="38" t="s">
+      <c r="J4" s="32"/>
+      <c r="K4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="41" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="42"/>
+      <c r="N4" s="35"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -1916,30 +1923,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="24">
         <v>44750</v>
       </c>
-      <c r="D5" s="28"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="35" t="s">
+      <c r="G5" s="27"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="36">
+      <c r="J5" s="25"/>
+      <c r="K5" s="28">
         <v>2</v>
       </c>
-      <c r="L5" s="28"/>
-      <c r="M5" s="37" t="s">
+      <c r="L5" s="25"/>
+      <c r="M5" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="33"/>
+      <c r="N5" s="30"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -1948,30 +1955,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="36">
         <v>44750</v>
       </c>
-      <c r="D6" s="28"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29" t="s">
+      <c r="G6" s="27"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="31">
+      <c r="J6" s="25"/>
+      <c r="K6" s="38">
         <v>13</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="32" t="s">
+      <c r="L6" s="25"/>
+      <c r="M6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="33"/>
+      <c r="N6" s="30"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -1980,30 +1987,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="24">
         <v>44750</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="36">
+      <c r="G7" s="27"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="28">
         <v>9</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="37" t="s">
+      <c r="L7" s="25"/>
+      <c r="M7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="33"/>
+      <c r="N7" s="30"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -2012,30 +2019,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="36">
         <v>44750</v>
       </c>
-      <c r="D8" s="28"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="31">
+      <c r="G8" s="27"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="38">
         <v>123</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="32" t="s">
+      <c r="L8" s="25"/>
+      <c r="M8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="33"/>
+      <c r="N8" s="30"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -2044,30 +2051,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="24">
         <v>44750</v>
       </c>
-      <c r="D9" s="28"/>
+      <c r="D9" s="25"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="36">
+      <c r="G9" s="27"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="28">
         <v>37</v>
       </c>
-      <c r="L9" s="28"/>
-      <c r="M9" s="37" t="s">
+      <c r="L9" s="25"/>
+      <c r="M9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="33"/>
+      <c r="N9" s="30"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -2076,30 +2083,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="36">
         <v>44753</v>
       </c>
-      <c r="D10" s="28"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="31">
+      <c r="G10" s="27"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="38">
         <v>37</v>
       </c>
-      <c r="L10" s="28"/>
-      <c r="M10" s="32" t="s">
+      <c r="L10" s="25"/>
+      <c r="M10" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="33"/>
+      <c r="N10" s="30"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2108,30 +2115,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="24">
         <v>44753</v>
       </c>
-      <c r="D11" s="28"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="36">
+      <c r="G11" s="27"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="28">
         <v>80</v>
       </c>
-      <c r="L11" s="28"/>
-      <c r="M11" s="37" t="s">
+      <c r="L11" s="25"/>
+      <c r="M11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="33"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2140,30 +2147,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="36">
         <v>44753</v>
       </c>
-      <c r="D12" s="28"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="29" t="s">
+      <c r="G12" s="27"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="28"/>
-      <c r="K12" s="31">
+      <c r="J12" s="25"/>
+      <c r="K12" s="38">
         <v>229</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="32" t="s">
+      <c r="L12" s="25"/>
+      <c r="M12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="33"/>
+      <c r="N12" s="30"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2172,30 +2179,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="24">
         <v>44753</v>
       </c>
-      <c r="D13" s="28"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="36">
+      <c r="G13" s="27"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="25"/>
+      <c r="K13" s="28">
         <v>368</v>
       </c>
-      <c r="L13" s="28"/>
-      <c r="M13" s="37" t="s">
+      <c r="L13" s="25"/>
+      <c r="M13" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="33"/>
+      <c r="N13" s="30"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2204,30 +2211,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="36">
         <v>44753</v>
       </c>
-      <c r="D14" s="28"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="31">
+      <c r="G14" s="27"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="25"/>
+      <c r="K14" s="38">
         <v>62</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="32" t="s">
+      <c r="L14" s="25"/>
+      <c r="M14" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="33"/>
+      <c r="N14" s="30"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2236,30 +2243,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="24">
         <v>44753</v>
       </c>
-      <c r="D15" s="28"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="36">
+      <c r="G15" s="27"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="25"/>
+      <c r="K15" s="28">
         <v>25</v>
       </c>
-      <c r="L15" s="28"/>
-      <c r="M15" s="37" t="s">
+      <c r="L15" s="25"/>
+      <c r="M15" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="33"/>
+      <c r="N15" s="30"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2268,30 +2275,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="36">
         <v>44753</v>
       </c>
-      <c r="D16" s="28"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="31">
+      <c r="G16" s="27"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="25"/>
+      <c r="K16" s="38">
         <v>68</v>
       </c>
-      <c r="L16" s="28"/>
-      <c r="M16" s="32" t="s">
+      <c r="L16" s="25"/>
+      <c r="M16" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="33"/>
+      <c r="N16" s="30"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2300,30 +2307,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="24">
         <v>44753</v>
       </c>
-      <c r="D17" s="28"/>
+      <c r="D17" s="25"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="36">
+      <c r="G17" s="27"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="25"/>
+      <c r="K17" s="28">
         <v>77</v>
       </c>
-      <c r="L17" s="28"/>
-      <c r="M17" s="37" t="s">
+      <c r="L17" s="25"/>
+      <c r="M17" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="33"/>
+      <c r="N17" s="30"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2332,30 +2339,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="36">
         <v>44754</v>
       </c>
-      <c r="D18" s="28"/>
+      <c r="D18" s="25"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="31">
+      <c r="G18" s="27"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="25"/>
+      <c r="K18" s="38">
         <v>20</v>
       </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="32" t="s">
+      <c r="L18" s="25"/>
+      <c r="M18" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="33"/>
+      <c r="N18" s="30"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2364,30 +2371,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="24">
         <v>44754</v>
       </c>
-      <c r="D19" s="28"/>
+      <c r="D19" s="25"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="30"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="36">
+      <c r="G19" s="27"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="25"/>
+      <c r="K19" s="28">
         <v>5</v>
       </c>
-      <c r="L19" s="28"/>
-      <c r="M19" s="37" t="s">
+      <c r="L19" s="25"/>
+      <c r="M19" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="33"/>
+      <c r="N19" s="30"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2396,30 +2403,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="36">
         <v>44754</v>
       </c>
-      <c r="D20" s="28"/>
+      <c r="D20" s="25"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="31">
+      <c r="G20" s="27"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="25"/>
+      <c r="K20" s="38">
         <v>2</v>
       </c>
-      <c r="L20" s="28"/>
-      <c r="M20" s="32" t="s">
+      <c r="L20" s="25"/>
+      <c r="M20" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="33"/>
+      <c r="N20" s="30"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2428,30 +2435,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="24">
         <v>44754</v>
       </c>
-      <c r="D21" s="28"/>
+      <c r="D21" s="25"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="36">
+      <c r="G21" s="27"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="25"/>
+      <c r="K21" s="28">
         <v>1</v>
       </c>
-      <c r="L21" s="28"/>
-      <c r="M21" s="37" t="s">
+      <c r="L21" s="25"/>
+      <c r="M21" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="33"/>
+      <c r="N21" s="30"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2460,30 +2467,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="36">
         <v>44754</v>
       </c>
-      <c r="D22" s="28"/>
+      <c r="D22" s="25"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="31">
+      <c r="G22" s="27"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="38">
         <v>41</v>
       </c>
-      <c r="L22" s="28"/>
-      <c r="M22" s="32" t="s">
+      <c r="L22" s="25"/>
+      <c r="M22" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="33"/>
+      <c r="N22" s="30"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2492,30 +2499,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="24">
         <v>44754</v>
       </c>
-      <c r="D23" s="28"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="35" t="s">
+      <c r="G23" s="27"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="36">
+      <c r="J23" s="25"/>
+      <c r="K23" s="28">
         <v>4</v>
       </c>
-      <c r="L23" s="28"/>
-      <c r="M23" s="37" t="s">
+      <c r="L23" s="25"/>
+      <c r="M23" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="33"/>
+      <c r="N23" s="30"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2524,30 +2531,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="36">
         <v>44754</v>
       </c>
-      <c r="D24" s="28"/>
+      <c r="D24" s="25"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="31">
+      <c r="G24" s="27"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="38">
         <v>211</v>
       </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="32" t="s">
+      <c r="L24" s="25"/>
+      <c r="M24" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="33"/>
+      <c r="N24" s="30"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2556,30 +2563,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="24">
         <v>44754</v>
       </c>
-      <c r="D25" s="28"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="35" t="s">
+      <c r="G25" s="27"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="36">
+      <c r="J25" s="25"/>
+      <c r="K25" s="28">
         <v>10</v>
       </c>
-      <c r="L25" s="28"/>
-      <c r="M25" s="37" t="s">
+      <c r="L25" s="25"/>
+      <c r="M25" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="33"/>
+      <c r="N25" s="30"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2588,30 +2595,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="36">
         <v>44754</v>
       </c>
-      <c r="D26" s="28"/>
+      <c r="D26" s="25"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29" t="s">
+      <c r="G26" s="27"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="31">
+      <c r="J26" s="25"/>
+      <c r="K26" s="38">
         <v>1</v>
       </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="32" t="s">
+      <c r="L26" s="25"/>
+      <c r="M26" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="33"/>
+      <c r="N26" s="30"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2620,30 +2627,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="24">
         <v>44754</v>
       </c>
-      <c r="D27" s="28"/>
+      <c r="D27" s="25"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="30"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="36">
+      <c r="G27" s="27"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="28">
         <v>94</v>
       </c>
-      <c r="L27" s="28"/>
-      <c r="M27" s="37" t="s">
+      <c r="L27" s="25"/>
+      <c r="M27" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="33"/>
+      <c r="N27" s="30"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2652,30 +2659,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="36">
         <v>44754</v>
       </c>
-      <c r="D28" s="28"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29" t="s">
+      <c r="G28" s="27"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="31">
+      <c r="J28" s="25"/>
+      <c r="K28" s="38">
         <v>9</v>
       </c>
-      <c r="L28" s="28"/>
-      <c r="M28" s="32" t="s">
+      <c r="L28" s="25"/>
+      <c r="M28" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="33"/>
+      <c r="N28" s="30"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2684,30 +2691,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="24">
         <v>44754</v>
       </c>
-      <c r="D29" s="28"/>
+      <c r="D29" s="25"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="30"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="35" t="s">
+      <c r="G29" s="27"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="36">
+      <c r="J29" s="25"/>
+      <c r="K29" s="28">
         <v>6</v>
       </c>
-      <c r="L29" s="28"/>
-      <c r="M29" s="37" t="s">
+      <c r="L29" s="25"/>
+      <c r="M29" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="33"/>
+      <c r="N29" s="30"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2716,30 +2723,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="36">
         <v>44754</v>
       </c>
-      <c r="D30" s="28"/>
+      <c r="D30" s="25"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29" t="s">
+      <c r="G30" s="27"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="31">
-        <v>18</v>
-      </c>
-      <c r="L30" s="28"/>
-      <c r="M30" s="32" t="s">
+      <c r="J30" s="25"/>
+      <c r="K30" s="38">
+        <v>18</v>
+      </c>
+      <c r="L30" s="25"/>
+      <c r="M30" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="33"/>
+      <c r="N30" s="30"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2748,30 +2755,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="24">
         <v>44755</v>
       </c>
-      <c r="D31" s="28"/>
+      <c r="D31" s="25"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="30"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="35" t="s">
+      <c r="G31" s="27"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="28"/>
-      <c r="K31" s="36">
+      <c r="J31" s="25"/>
+      <c r="K31" s="28">
         <v>76</v>
       </c>
-      <c r="L31" s="28"/>
-      <c r="M31" s="37" t="s">
+      <c r="L31" s="25"/>
+      <c r="M31" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="33"/>
+      <c r="N31" s="30"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -2780,30 +2787,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="36">
         <v>44755</v>
       </c>
-      <c r="D32" s="28"/>
+      <c r="D32" s="25"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="30"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29" t="s">
+      <c r="G32" s="27"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="28"/>
-      <c r="K32" s="31">
+      <c r="J32" s="25"/>
+      <c r="K32" s="38">
         <v>1</v>
       </c>
-      <c r="L32" s="28"/>
-      <c r="M32" s="32" t="s">
+      <c r="L32" s="25"/>
+      <c r="M32" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="33"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -2812,30 +2819,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="24">
         <v>44755</v>
       </c>
-      <c r="D33" s="28"/>
+      <c r="D33" s="25"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="35" t="s">
+      <c r="G33" s="27"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="28"/>
-      <c r="K33" s="36">
+      <c r="J33" s="25"/>
+      <c r="K33" s="28">
         <v>27</v>
       </c>
-      <c r="L33" s="28"/>
-      <c r="M33" s="37" t="s">
+      <c r="L33" s="25"/>
+      <c r="M33" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="33"/>
+      <c r="N33" s="30"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -2844,30 +2851,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="36">
         <v>44755</v>
       </c>
-      <c r="D34" s="28"/>
+      <c r="D34" s="25"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="30"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29" t="s">
+      <c r="G34" s="27"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="31">
+      <c r="J34" s="25"/>
+      <c r="K34" s="38">
         <v>2</v>
       </c>
-      <c r="L34" s="28"/>
-      <c r="M34" s="32" t="s">
+      <c r="L34" s="25"/>
+      <c r="M34" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="33"/>
+      <c r="N34" s="30"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -2876,30 +2883,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="24">
         <v>44756</v>
       </c>
-      <c r="D35" s="28"/>
+      <c r="D35" s="25"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="30"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="28"/>
-      <c r="K35" s="36">
+      <c r="G35" s="27"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="25"/>
+      <c r="K35" s="28">
         <v>54</v>
       </c>
-      <c r="L35" s="28"/>
-      <c r="M35" s="37" t="s">
+      <c r="L35" s="25"/>
+      <c r="M35" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="33"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -2908,30 +2915,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="36">
         <v>44756</v>
       </c>
-      <c r="D36" s="28"/>
+      <c r="D36" s="25"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="30"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="28"/>
-      <c r="K36" s="31">
+      <c r="G36" s="27"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="25"/>
+      <c r="K36" s="38">
         <v>105</v>
       </c>
-      <c r="L36" s="28"/>
-      <c r="M36" s="32" t="s">
+      <c r="L36" s="25"/>
+      <c r="M36" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="33"/>
+      <c r="N36" s="30"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -2940,30 +2947,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="24">
         <v>44756</v>
       </c>
-      <c r="D37" s="28"/>
+      <c r="D37" s="25"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="F37" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="30"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="28"/>
-      <c r="K37" s="36">
+      <c r="G37" s="27"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="25"/>
+      <c r="K37" s="28">
         <v>71</v>
       </c>
-      <c r="L37" s="28"/>
-      <c r="M37" s="37" t="s">
+      <c r="L37" s="25"/>
+      <c r="M37" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="33"/>
+      <c r="N37" s="30"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -2972,30 +2979,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="36">
         <v>44756</v>
       </c>
-      <c r="D38" s="28"/>
+      <c r="D38" s="25"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="30"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="28"/>
-      <c r="K38" s="31">
+      <c r="G38" s="27"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="25"/>
+      <c r="K38" s="38">
         <v>125</v>
       </c>
-      <c r="L38" s="28"/>
-      <c r="M38" s="32" t="s">
+      <c r="L38" s="25"/>
+      <c r="M38" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="33"/>
+      <c r="N38" s="30"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -3004,30 +3011,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="24">
         <v>44756</v>
       </c>
-      <c r="D39" s="28"/>
+      <c r="D39" s="25"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="F39" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="36">
+      <c r="G39" s="27"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="25"/>
+      <c r="K39" s="28">
         <v>55</v>
       </c>
-      <c r="L39" s="28"/>
-      <c r="M39" s="37" t="s">
+      <c r="L39" s="25"/>
+      <c r="M39" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="33"/>
+      <c r="N39" s="30"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -3036,30 +3043,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="36">
         <v>44756</v>
       </c>
-      <c r="D40" s="28"/>
+      <c r="D40" s="25"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="28"/>
-      <c r="K40" s="31">
+      <c r="G40" s="27"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="25"/>
+      <c r="K40" s="38">
         <v>176</v>
       </c>
-      <c r="L40" s="28"/>
-      <c r="M40" s="32" t="s">
+      <c r="L40" s="25"/>
+      <c r="M40" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="33"/>
+      <c r="N40" s="30"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -3068,30 +3075,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="24">
         <v>44757</v>
       </c>
-      <c r="D41" s="28"/>
+      <c r="D41" s="25"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="35" t="s">
+      <c r="F41" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="28"/>
-      <c r="K41" s="36">
+      <c r="G41" s="27"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="25"/>
+      <c r="K41" s="28">
         <v>58</v>
       </c>
-      <c r="L41" s="28"/>
-      <c r="M41" s="37" t="s">
+      <c r="L41" s="25"/>
+      <c r="M41" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="33"/>
+      <c r="N41" s="30"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3100,30 +3107,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="36">
         <v>44757</v>
       </c>
-      <c r="D42" s="28"/>
+      <c r="D42" s="25"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="30"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="28"/>
-      <c r="K42" s="31">
+      <c r="G42" s="27"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="25"/>
+      <c r="K42" s="38">
         <v>180</v>
       </c>
-      <c r="L42" s="28"/>
-      <c r="M42" s="32" t="s">
+      <c r="L42" s="25"/>
+      <c r="M42" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="33"/>
+      <c r="N42" s="30"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3132,30 +3139,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="24">
         <v>44760</v>
       </c>
-      <c r="D43" s="28"/>
+      <c r="D43" s="25"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="35" t="s">
+      <c r="F43" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="30"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="35" t="s">
+      <c r="G43" s="27"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="28"/>
-      <c r="K43" s="36">
+      <c r="J43" s="25"/>
+      <c r="K43" s="28">
         <v>142</v>
       </c>
-      <c r="L43" s="28"/>
-      <c r="M43" s="37" t="s">
+      <c r="L43" s="25"/>
+      <c r="M43" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="33"/>
+      <c r="N43" s="30"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3164,30 +3171,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="36">
         <v>44760</v>
       </c>
-      <c r="D44" s="28"/>
+      <c r="D44" s="25"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="29" t="s">
+      <c r="F44" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="30"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="29" t="s">
+      <c r="G44" s="27"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="28"/>
-      <c r="K44" s="31">
+      <c r="J44" s="25"/>
+      <c r="K44" s="38">
         <v>153</v>
       </c>
-      <c r="L44" s="28"/>
-      <c r="M44" s="32" t="s">
+      <c r="L44" s="25"/>
+      <c r="M44" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="33"/>
+      <c r="N44" s="30"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3196,30 +3203,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="24">
         <v>44761</v>
       </c>
-      <c r="D45" s="28"/>
+      <c r="D45" s="25"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="30"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="28"/>
-      <c r="K45" s="36">
+      <c r="G45" s="27"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="25"/>
+      <c r="K45" s="28">
         <v>12</v>
       </c>
-      <c r="L45" s="28"/>
-      <c r="M45" s="37" t="s">
+      <c r="L45" s="25"/>
+      <c r="M45" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="33"/>
+      <c r="N45" s="30"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3228,30 +3235,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="36">
         <v>44761</v>
       </c>
-      <c r="D46" s="28"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="30"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="28"/>
-      <c r="K46" s="31">
+      <c r="G46" s="27"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="25"/>
+      <c r="K46" s="38">
         <v>27</v>
       </c>
-      <c r="L46" s="28"/>
-      <c r="M46" s="32" t="s">
+      <c r="L46" s="25"/>
+      <c r="M46" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="33"/>
+      <c r="N46" s="30"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3260,30 +3267,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="24">
         <v>44761</v>
       </c>
-      <c r="D47" s="28"/>
+      <c r="D47" s="25"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="30"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="28"/>
-      <c r="K47" s="36">
+      <c r="G47" s="27"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="25"/>
+      <c r="K47" s="28">
         <v>51</v>
       </c>
-      <c r="L47" s="28"/>
-      <c r="M47" s="37" t="s">
+      <c r="L47" s="25"/>
+      <c r="M47" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="33"/>
+      <c r="N47" s="30"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3292,30 +3299,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="36">
         <v>44761</v>
       </c>
-      <c r="D48" s="28"/>
+      <c r="D48" s="25"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="30"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="28"/>
-      <c r="K48" s="31">
+      <c r="G48" s="27"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="25"/>
+      <c r="K48" s="38">
         <v>69</v>
       </c>
-      <c r="L48" s="28"/>
-      <c r="M48" s="32" t="s">
+      <c r="L48" s="25"/>
+      <c r="M48" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="33"/>
+      <c r="N48" s="30"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3324,30 +3331,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="24">
         <v>44762</v>
       </c>
-      <c r="D49" s="28"/>
+      <c r="D49" s="25"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="30"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="35" t="s">
+      <c r="G49" s="27"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="28"/>
-      <c r="K49" s="36">
+      <c r="J49" s="25"/>
+      <c r="K49" s="28">
         <v>104</v>
       </c>
-      <c r="L49" s="28"/>
-      <c r="M49" s="37" t="s">
+      <c r="L49" s="25"/>
+      <c r="M49" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="33"/>
+      <c r="N49" s="30"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3356,30 +3363,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="36">
         <v>44762</v>
       </c>
-      <c r="D50" s="28"/>
+      <c r="D50" s="25"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="30"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="28"/>
-      <c r="K50" s="31">
+      <c r="G50" s="27"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="25"/>
+      <c r="K50" s="38">
         <v>19</v>
       </c>
-      <c r="L50" s="28"/>
-      <c r="M50" s="32" t="s">
+      <c r="L50" s="25"/>
+      <c r="M50" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="33"/>
+      <c r="N50" s="30"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3388,30 +3395,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="24">
         <v>44762</v>
       </c>
-      <c r="D51" s="28"/>
+      <c r="D51" s="25"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="35" t="s">
+      <c r="F51" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="30"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="35" t="s">
+      <c r="G51" s="27"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="28"/>
-      <c r="K51" s="36">
+      <c r="J51" s="25"/>
+      <c r="K51" s="28">
         <v>80</v>
       </c>
-      <c r="L51" s="28"/>
-      <c r="M51" s="37" t="s">
+      <c r="L51" s="25"/>
+      <c r="M51" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="33"/>
+      <c r="N51" s="30"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3420,30 +3427,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="36">
         <v>44763</v>
       </c>
-      <c r="D52" s="28"/>
+      <c r="D52" s="25"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="30"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="28"/>
-      <c r="K52" s="31">
+      <c r="G52" s="27"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="25"/>
+      <c r="K52" s="38">
         <v>99</v>
       </c>
-      <c r="L52" s="28"/>
-      <c r="M52" s="32" t="s">
+      <c r="L52" s="25"/>
+      <c r="M52" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="33"/>
+      <c r="N52" s="30"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3452,30 +3459,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="24">
         <v>44763</v>
       </c>
-      <c r="D53" s="28"/>
+      <c r="D53" s="25"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="30"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="28"/>
-      <c r="K53" s="36">
+      <c r="G53" s="27"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="25"/>
+      <c r="K53" s="28">
         <v>60</v>
       </c>
-      <c r="L53" s="28"/>
-      <c r="M53" s="37" t="s">
+      <c r="L53" s="25"/>
+      <c r="M53" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="33"/>
+      <c r="N53" s="30"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3484,30 +3491,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="36">
         <v>44763</v>
       </c>
-      <c r="D54" s="28"/>
+      <c r="D54" s="25"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="30"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="28"/>
-      <c r="K54" s="31">
+      <c r="G54" s="27"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="25"/>
+      <c r="K54" s="38">
         <v>4</v>
       </c>
-      <c r="L54" s="28"/>
-      <c r="M54" s="32" t="s">
+      <c r="L54" s="25"/>
+      <c r="M54" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="33"/>
+      <c r="N54" s="30"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3516,30 +3523,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="24">
         <v>44763</v>
       </c>
-      <c r="D55" s="28"/>
+      <c r="D55" s="25"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="30"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="28"/>
-      <c r="K55" s="36">
+      <c r="G55" s="27"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="25"/>
+      <c r="K55" s="28">
         <v>26</v>
       </c>
-      <c r="L55" s="28"/>
-      <c r="M55" s="37" t="s">
+      <c r="L55" s="25"/>
+      <c r="M55" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="33"/>
+      <c r="N55" s="30"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3548,30 +3555,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="36">
         <v>44763</v>
       </c>
-      <c r="D56" s="28"/>
+      <c r="D56" s="25"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="30"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="28"/>
-      <c r="K56" s="31">
+      <c r="G56" s="27"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="25"/>
+      <c r="K56" s="38">
         <v>30</v>
       </c>
-      <c r="L56" s="28"/>
-      <c r="M56" s="32" t="s">
+      <c r="L56" s="25"/>
+      <c r="M56" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="33"/>
+      <c r="N56" s="30"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3580,30 +3587,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="24">
         <v>44763</v>
       </c>
-      <c r="D57" s="28"/>
+      <c r="D57" s="25"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="30"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="28"/>
-      <c r="K57" s="36">
+      <c r="G57" s="27"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="25"/>
+      <c r="K57" s="28">
         <v>2</v>
       </c>
-      <c r="L57" s="28"/>
-      <c r="M57" s="37" t="s">
+      <c r="L57" s="25"/>
+      <c r="M57" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="33"/>
+      <c r="N57" s="30"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3612,30 +3619,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="36">
         <v>44764</v>
       </c>
-      <c r="D58" s="28"/>
+      <c r="D58" s="25"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="F58" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="30"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="29" t="s">
+      <c r="G58" s="27"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="28"/>
-      <c r="K58" s="31">
+      <c r="J58" s="25"/>
+      <c r="K58" s="38">
         <v>66</v>
       </c>
-      <c r="L58" s="28"/>
-      <c r="M58" s="32" t="s">
+      <c r="L58" s="25"/>
+      <c r="M58" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="33"/>
+      <c r="N58" s="30"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3644,30 +3651,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="24">
         <v>44764</v>
       </c>
-      <c r="D59" s="28"/>
+      <c r="D59" s="25"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="30"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="35" t="s">
+      <c r="G59" s="27"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="28"/>
-      <c r="K59" s="36">
+      <c r="J59" s="25"/>
+      <c r="K59" s="28">
         <v>85</v>
       </c>
-      <c r="L59" s="28"/>
-      <c r="M59" s="37" t="s">
+      <c r="L59" s="25"/>
+      <c r="M59" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="33"/>
+      <c r="N59" s="30"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3676,30 +3683,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="36">
         <v>44764</v>
       </c>
-      <c r="D60" s="28"/>
+      <c r="D60" s="25"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="30"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="28"/>
-      <c r="K60" s="31">
+      <c r="G60" s="27"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="25"/>
+      <c r="K60" s="38">
         <v>58</v>
       </c>
-      <c r="L60" s="28"/>
-      <c r="M60" s="32" t="s">
+      <c r="L60" s="25"/>
+      <c r="M60" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="33"/>
+      <c r="N60" s="30"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3708,30 +3715,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="24">
         <v>44764</v>
       </c>
-      <c r="D61" s="28"/>
+      <c r="D61" s="25"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="35" t="s">
+      <c r="F61" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="30"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="28"/>
-      <c r="K61" s="36">
+      <c r="G61" s="27"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="25"/>
+      <c r="K61" s="28">
         <v>80</v>
       </c>
-      <c r="L61" s="28"/>
-      <c r="M61" s="37" t="s">
+      <c r="L61" s="25"/>
+      <c r="M61" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="33"/>
+      <c r="N61" s="30"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3740,30 +3747,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="36">
         <v>44764</v>
       </c>
-      <c r="D62" s="28"/>
+      <c r="D62" s="25"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="30"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="28"/>
-      <c r="K62" s="31">
+      <c r="G62" s="27"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="25"/>
+      <c r="K62" s="38">
         <v>55</v>
       </c>
-      <c r="L62" s="28"/>
-      <c r="M62" s="32" t="s">
+      <c r="L62" s="25"/>
+      <c r="M62" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="33"/>
+      <c r="N62" s="30"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -3772,30 +3779,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="24">
         <v>44764</v>
       </c>
-      <c r="D63" s="28"/>
+      <c r="D63" s="25"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="35" t="s">
+      <c r="F63" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="30"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="35" t="s">
+      <c r="G63" s="27"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="28"/>
-      <c r="K63" s="36">
+      <c r="J63" s="25"/>
+      <c r="K63" s="28">
         <v>14</v>
       </c>
-      <c r="L63" s="28"/>
-      <c r="M63" s="37" t="s">
+      <c r="L63" s="25"/>
+      <c r="M63" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="33"/>
+      <c r="N63" s="30"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -3804,30 +3811,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="36">
         <v>44764</v>
       </c>
-      <c r="D64" s="28"/>
+      <c r="D64" s="25"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="29" t="s">
+      <c r="F64" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="30"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="29" t="s">
+      <c r="G64" s="27"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="28"/>
-      <c r="K64" s="31">
+      <c r="J64" s="25"/>
+      <c r="K64" s="38">
         <v>90</v>
       </c>
-      <c r="L64" s="28"/>
-      <c r="M64" s="32" t="s">
+      <c r="L64" s="25"/>
+      <c r="M64" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="33"/>
+      <c r="N64" s="30"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -3836,30 +3843,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="24">
         <v>44767</v>
       </c>
-      <c r="D65" s="28"/>
+      <c r="D65" s="25"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="35" t="s">
+      <c r="F65" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="30"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="35" t="s">
+      <c r="G65" s="27"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="28"/>
-      <c r="K65" s="36">
+      <c r="J65" s="25"/>
+      <c r="K65" s="28">
         <v>331</v>
       </c>
-      <c r="L65" s="28"/>
-      <c r="M65" s="37" t="s">
+      <c r="L65" s="25"/>
+      <c r="M65" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="33"/>
+      <c r="N65" s="30"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -3868,30 +3875,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="36">
         <v>44768</v>
       </c>
-      <c r="D66" s="28"/>
+      <c r="D66" s="25"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="29" t="s">
+      <c r="F66" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="30"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="28"/>
-      <c r="K66" s="31">
+      <c r="G66" s="27"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="25"/>
+      <c r="K66" s="38">
         <v>52</v>
       </c>
-      <c r="L66" s="28"/>
-      <c r="M66" s="32" t="s">
+      <c r="L66" s="25"/>
+      <c r="M66" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="33"/>
+      <c r="N66" s="30"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -3900,30 +3907,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="24">
         <v>44768</v>
       </c>
-      <c r="D67" s="28"/>
+      <c r="D67" s="25"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="30"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="28"/>
-      <c r="K67" s="36">
+      <c r="G67" s="27"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="25"/>
+      <c r="K67" s="28">
         <v>9</v>
       </c>
-      <c r="L67" s="28"/>
-      <c r="M67" s="37" t="s">
+      <c r="L67" s="25"/>
+      <c r="M67" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="33"/>
+      <c r="N67" s="30"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -3932,30 +3939,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="36">
         <v>44768</v>
       </c>
-      <c r="D68" s="28"/>
+      <c r="D68" s="25"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="30"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="28"/>
-      <c r="K68" s="31">
+      <c r="G68" s="27"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="25"/>
+      <c r="K68" s="38">
         <v>78</v>
       </c>
-      <c r="L68" s="28"/>
-      <c r="M68" s="32" t="s">
+      <c r="L68" s="25"/>
+      <c r="M68" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="33"/>
+      <c r="N68" s="30"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -3964,30 +3971,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="24">
         <v>44769</v>
       </c>
-      <c r="D69" s="28"/>
+      <c r="D69" s="25"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="35" t="s">
+      <c r="F69" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="30"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="28"/>
-      <c r="K69" s="36">
+      <c r="G69" s="27"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="25"/>
+      <c r="K69" s="28">
         <v>48</v>
       </c>
-      <c r="L69" s="28"/>
-      <c r="M69" s="37" t="s">
+      <c r="L69" s="25"/>
+      <c r="M69" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="33"/>
+      <c r="N69" s="30"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -3996,30 +4003,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="36">
         <v>44769</v>
       </c>
-      <c r="D70" s="28"/>
+      <c r="D70" s="25"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="30"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="28"/>
-      <c r="K70" s="31">
+      <c r="G70" s="27"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="25"/>
+      <c r="K70" s="38">
         <v>50</v>
       </c>
-      <c r="L70" s="28"/>
-      <c r="M70" s="32" t="s">
+      <c r="L70" s="25"/>
+      <c r="M70" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="33"/>
+      <c r="N70" s="30"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -4028,30 +4035,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="24">
         <v>44769</v>
       </c>
-      <c r="D71" s="28"/>
+      <c r="D71" s="25"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="35" t="s">
+      <c r="F71" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="30"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="28"/>
-      <c r="K71" s="36">
+      <c r="G71" s="27"/>
+      <c r="H71" s="25"/>
+      <c r="I71" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="25"/>
+      <c r="K71" s="28">
         <v>736</v>
       </c>
-      <c r="L71" s="28"/>
-      <c r="M71" s="37" t="s">
+      <c r="L71" s="25"/>
+      <c r="M71" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="33"/>
+      <c r="N71" s="30"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -4060,30 +4067,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="36">
         <v>44770</v>
       </c>
-      <c r="D72" s="28"/>
+      <c r="D72" s="25"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="30"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="28"/>
-      <c r="K72" s="31">
+      <c r="G72" s="27"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="25"/>
+      <c r="K72" s="38">
         <v>74</v>
       </c>
-      <c r="L72" s="28"/>
-      <c r="M72" s="32" t="s">
+      <c r="L72" s="25"/>
+      <c r="M72" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="33"/>
+      <c r="N72" s="30"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4092,30 +4099,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C73" s="24">
         <v>44770</v>
       </c>
-      <c r="D73" s="28"/>
+      <c r="D73" s="25"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="35" t="s">
+      <c r="F73" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="30"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="28"/>
-      <c r="K73" s="36">
+      <c r="G73" s="27"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="25"/>
+      <c r="K73" s="28">
         <v>25</v>
       </c>
-      <c r="L73" s="28"/>
-      <c r="M73" s="37" t="s">
+      <c r="L73" s="25"/>
+      <c r="M73" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="33"/>
+      <c r="N73" s="30"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4124,30 +4131,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="36">
         <v>44770</v>
       </c>
-      <c r="D74" s="28"/>
+      <c r="D74" s="25"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="30"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="28"/>
-      <c r="K74" s="31">
+      <c r="G74" s="27"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="25"/>
+      <c r="K74" s="38">
         <v>25</v>
       </c>
-      <c r="L74" s="28"/>
-      <c r="M74" s="32" t="s">
+      <c r="L74" s="25"/>
+      <c r="M74" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="33"/>
+      <c r="N74" s="30"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4156,30 +4163,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="34">
+      <c r="C75" s="24">
         <v>44770</v>
       </c>
-      <c r="D75" s="28"/>
+      <c r="D75" s="25"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="30"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="35" t="s">
+      <c r="G75" s="27"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="28"/>
-      <c r="K75" s="36">
+      <c r="J75" s="25"/>
+      <c r="K75" s="28">
         <v>225</v>
       </c>
-      <c r="L75" s="28"/>
-      <c r="M75" s="37" t="s">
+      <c r="L75" s="25"/>
+      <c r="M75" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="33"/>
+      <c r="N75" s="30"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4188,30 +4195,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="36">
         <v>44770</v>
       </c>
-      <c r="D76" s="28"/>
+      <c r="D76" s="25"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F76" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="30"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="28"/>
-      <c r="K76" s="31">
+      <c r="G76" s="27"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="25"/>
+      <c r="K76" s="38">
         <v>136</v>
       </c>
-      <c r="L76" s="28"/>
-      <c r="M76" s="32" t="s">
+      <c r="L76" s="25"/>
+      <c r="M76" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="33"/>
+      <c r="N76" s="30"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4220,30 +4227,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="34">
+      <c r="C77" s="24">
         <v>44774</v>
       </c>
-      <c r="D77" s="28"/>
+      <c r="D77" s="25"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="35" t="s">
+      <c r="F77" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="30"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="35" t="s">
+      <c r="G77" s="27"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="28"/>
-      <c r="K77" s="36">
+      <c r="J77" s="25"/>
+      <c r="K77" s="28">
         <v>82</v>
       </c>
-      <c r="L77" s="28"/>
-      <c r="M77" s="37" t="s">
+      <c r="L77" s="25"/>
+      <c r="M77" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="33"/>
+      <c r="N77" s="30"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4252,30 +4259,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="36">
         <v>44774</v>
       </c>
-      <c r="D78" s="28"/>
+      <c r="D78" s="25"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="30"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="28"/>
-      <c r="K78" s="31">
+      <c r="G78" s="27"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="25"/>
+      <c r="K78" s="38">
         <v>28</v>
       </c>
-      <c r="L78" s="28"/>
-      <c r="M78" s="32" t="s">
+      <c r="L78" s="25"/>
+      <c r="M78" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="33"/>
+      <c r="N78" s="30"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4284,30 +4291,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="34">
+      <c r="C79" s="24">
         <v>44776</v>
       </c>
-      <c r="D79" s="28"/>
+      <c r="D79" s="25"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="35" t="s">
+      <c r="F79" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="30"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="28"/>
-      <c r="K79" s="36">
+      <c r="G79" s="27"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="25"/>
+      <c r="K79" s="28">
         <v>57</v>
       </c>
-      <c r="L79" s="28"/>
-      <c r="M79" s="37" t="s">
+      <c r="L79" s="25"/>
+      <c r="M79" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="33"/>
+      <c r="N79" s="30"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4316,30 +4323,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="36">
         <v>44778</v>
       </c>
-      <c r="D80" s="28"/>
+      <c r="D80" s="25"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="29" t="s">
+      <c r="F80" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="30"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="29" t="s">
+      <c r="G80" s="27"/>
+      <c r="H80" s="25"/>
+      <c r="I80" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="28"/>
-      <c r="K80" s="31">
+      <c r="J80" s="25"/>
+      <c r="K80" s="38">
         <v>133</v>
       </c>
-      <c r="L80" s="28"/>
-      <c r="M80" s="32" t="s">
+      <c r="L80" s="25"/>
+      <c r="M80" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="33"/>
+      <c r="N80" s="30"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4348,30 +4355,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="34">
+      <c r="C81" s="24">
         <v>44778</v>
       </c>
-      <c r="D81" s="28"/>
+      <c r="D81" s="25"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="30"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="28"/>
-      <c r="K81" s="36">
+      <c r="G81" s="27"/>
+      <c r="H81" s="25"/>
+      <c r="I81" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="25"/>
+      <c r="K81" s="28">
         <v>146</v>
       </c>
-      <c r="L81" s="28"/>
-      <c r="M81" s="37" t="s">
+      <c r="L81" s="25"/>
+      <c r="M81" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="33"/>
+      <c r="N81" s="30"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4380,30 +4387,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="36">
         <v>44778</v>
       </c>
-      <c r="D82" s="28"/>
+      <c r="D82" s="25"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="30"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="29" t="s">
+      <c r="G82" s="27"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="28"/>
-      <c r="K82" s="31">
+      <c r="J82" s="25"/>
+      <c r="K82" s="38">
         <v>68</v>
       </c>
-      <c r="L82" s="28"/>
-      <c r="M82" s="32" t="s">
+      <c r="L82" s="25"/>
+      <c r="M82" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="33"/>
+      <c r="N82" s="30"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4412,30 +4419,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="34">
+      <c r="C83" s="24">
         <v>44781</v>
       </c>
-      <c r="D83" s="28"/>
+      <c r="D83" s="25"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="30"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="28"/>
-      <c r="K83" s="36">
+      <c r="G83" s="27"/>
+      <c r="H83" s="25"/>
+      <c r="I83" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="25"/>
+      <c r="K83" s="28">
         <v>111</v>
       </c>
-      <c r="L83" s="28"/>
-      <c r="M83" s="37" t="s">
+      <c r="L83" s="25"/>
+      <c r="M83" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="33"/>
+      <c r="N83" s="30"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4444,30 +4451,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="36">
         <v>44781</v>
       </c>
-      <c r="D84" s="28"/>
+      <c r="D84" s="25"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="29" t="s">
+      <c r="F84" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="30"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="28"/>
-      <c r="K84" s="31">
+      <c r="G84" s="27"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="25"/>
+      <c r="K84" s="38">
         <v>77</v>
       </c>
-      <c r="L84" s="28"/>
-      <c r="M84" s="32" t="s">
+      <c r="L84" s="25"/>
+      <c r="M84" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="33"/>
+      <c r="N84" s="30"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4476,30 +4483,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="24">
         <v>44781</v>
       </c>
-      <c r="D85" s="28"/>
+      <c r="D85" s="25"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="35" t="s">
+      <c r="F85" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="30"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="28"/>
-      <c r="K85" s="36">
+      <c r="G85" s="27"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="25"/>
+      <c r="K85" s="28">
         <v>20</v>
       </c>
-      <c r="L85" s="28"/>
-      <c r="M85" s="37" t="s">
+      <c r="L85" s="25"/>
+      <c r="M85" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="33"/>
+      <c r="N85" s="30"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4508,30 +4515,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="36">
         <v>44781</v>
       </c>
-      <c r="D86" s="28"/>
+      <c r="D86" s="25"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="29" t="s">
+      <c r="F86" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="30"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="28"/>
-      <c r="K86" s="31">
+      <c r="G86" s="27"/>
+      <c r="H86" s="25"/>
+      <c r="I86" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="25"/>
+      <c r="K86" s="38">
         <v>25</v>
       </c>
-      <c r="L86" s="28"/>
-      <c r="M86" s="32" t="s">
+      <c r="L86" s="25"/>
+      <c r="M86" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="33"/>
+      <c r="N86" s="30"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4540,30 +4547,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C87" s="24">
         <v>44781</v>
       </c>
-      <c r="D87" s="28"/>
+      <c r="D87" s="25"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="35" t="s">
+      <c r="F87" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="30"/>
-      <c r="H87" s="28"/>
-      <c r="I87" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="28"/>
-      <c r="K87" s="36">
+      <c r="G87" s="27"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="25"/>
+      <c r="K87" s="28">
         <v>21</v>
       </c>
-      <c r="L87" s="28"/>
-      <c r="M87" s="37" t="s">
+      <c r="L87" s="25"/>
+      <c r="M87" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="33"/>
+      <c r="N87" s="30"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4572,30 +4579,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="36">
         <v>44781</v>
       </c>
-      <c r="D88" s="28"/>
+      <c r="D88" s="25"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="29" t="s">
+      <c r="F88" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="30"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="28"/>
-      <c r="K88" s="31">
+      <c r="G88" s="27"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="25"/>
+      <c r="K88" s="38">
         <v>86</v>
       </c>
-      <c r="L88" s="28"/>
-      <c r="M88" s="32" t="s">
+      <c r="L88" s="25"/>
+      <c r="M88" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="33"/>
+      <c r="N88" s="30"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4604,30 +4611,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="24">
         <v>44781</v>
       </c>
-      <c r="D89" s="28"/>
+      <c r="D89" s="25"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="35" t="s">
+      <c r="F89" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="30"/>
-      <c r="H89" s="28"/>
-      <c r="I89" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="28"/>
-      <c r="K89" s="36">
+      <c r="G89" s="27"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="25"/>
+      <c r="K89" s="28">
         <v>9</v>
       </c>
-      <c r="L89" s="28"/>
-      <c r="M89" s="37" t="s">
+      <c r="L89" s="25"/>
+      <c r="M89" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="33"/>
+      <c r="N89" s="30"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4636,30 +4643,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="36">
         <v>44781</v>
       </c>
-      <c r="D90" s="28"/>
+      <c r="D90" s="25"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="29" t="s">
+      <c r="F90" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="30"/>
-      <c r="H90" s="28"/>
-      <c r="I90" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="28"/>
-      <c r="K90" s="31">
+      <c r="G90" s="27"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="25"/>
+      <c r="K90" s="38">
         <v>2</v>
       </c>
-      <c r="L90" s="28"/>
-      <c r="M90" s="32" t="s">
+      <c r="L90" s="25"/>
+      <c r="M90" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="33"/>
+      <c r="N90" s="30"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4668,30 +4675,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="24">
         <v>44781</v>
       </c>
-      <c r="D91" s="28"/>
+      <c r="D91" s="25"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="35" t="s">
+      <c r="F91" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="30"/>
-      <c r="H91" s="28"/>
-      <c r="I91" s="35" t="s">
+      <c r="G91" s="27"/>
+      <c r="H91" s="25"/>
+      <c r="I91" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="28"/>
-      <c r="K91" s="36">
+      <c r="J91" s="25"/>
+      <c r="K91" s="28">
         <v>73</v>
       </c>
-      <c r="L91" s="28"/>
-      <c r="M91" s="37" t="s">
+      <c r="L91" s="25"/>
+      <c r="M91" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="33"/>
+      <c r="N91" s="30"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4700,30 +4707,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="36">
         <v>44782</v>
       </c>
-      <c r="D92" s="28"/>
+      <c r="D92" s="25"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="30"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="29" t="s">
+      <c r="G92" s="27"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="28"/>
-      <c r="K92" s="31">
+      <c r="J92" s="25"/>
+      <c r="K92" s="38">
         <v>33</v>
       </c>
-      <c r="L92" s="28"/>
-      <c r="M92" s="32" t="s">
+      <c r="L92" s="25"/>
+      <c r="M92" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="33"/>
+      <c r="N92" s="30"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4732,30 +4739,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="34">
+      <c r="C93" s="24">
         <v>44782</v>
       </c>
-      <c r="D93" s="28"/>
+      <c r="D93" s="25"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="35" t="s">
+      <c r="F93" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="30"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="35" t="s">
+      <c r="G93" s="27"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="28"/>
-      <c r="K93" s="36">
+      <c r="J93" s="25"/>
+      <c r="K93" s="28">
         <v>57</v>
       </c>
-      <c r="L93" s="28"/>
-      <c r="M93" s="37" t="s">
+      <c r="L93" s="25"/>
+      <c r="M93" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="33"/>
+      <c r="N93" s="30"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -4764,30 +4771,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="36">
         <v>44782</v>
       </c>
-      <c r="D94" s="28"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="29" t="s">
+      <c r="F94" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="30"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29" t="s">
+      <c r="G94" s="27"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="28"/>
-      <c r="K94" s="31">
+      <c r="J94" s="25"/>
+      <c r="K94" s="38">
         <v>16</v>
       </c>
-      <c r="L94" s="28"/>
-      <c r="M94" s="32" t="s">
+      <c r="L94" s="25"/>
+      <c r="M94" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="33"/>
+      <c r="N94" s="30"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -4796,30 +4803,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="34">
+      <c r="C95" s="24">
         <v>44782</v>
       </c>
-      <c r="D95" s="28"/>
+      <c r="D95" s="25"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="35" t="s">
+      <c r="F95" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="30"/>
-      <c r="H95" s="28"/>
-      <c r="I95" s="35" t="s">
+      <c r="G95" s="27"/>
+      <c r="H95" s="25"/>
+      <c r="I95" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="28"/>
-      <c r="K95" s="36">
+      <c r="J95" s="25"/>
+      <c r="K95" s="28">
         <v>3</v>
       </c>
-      <c r="L95" s="28"/>
-      <c r="M95" s="37" t="s">
+      <c r="L95" s="25"/>
+      <c r="M95" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="33"/>
+      <c r="N95" s="30"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -4828,30 +4835,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="36">
         <v>44782</v>
       </c>
-      <c r="D96" s="28"/>
+      <c r="D96" s="25"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="29" t="s">
+      <c r="F96" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="30"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="29" t="s">
+      <c r="G96" s="27"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="28"/>
-      <c r="K96" s="31">
+      <c r="J96" s="25"/>
+      <c r="K96" s="38">
         <v>15</v>
       </c>
-      <c r="L96" s="28"/>
-      <c r="M96" s="32" t="s">
+      <c r="L96" s="25"/>
+      <c r="M96" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="33"/>
+      <c r="N96" s="30"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -4860,30 +4867,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="34">
+      <c r="C97" s="24">
         <v>44783</v>
       </c>
-      <c r="D97" s="28"/>
+      <c r="D97" s="25"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="35" t="s">
+      <c r="F97" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="30"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="35" t="s">
+      <c r="G97" s="27"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="28"/>
-      <c r="K97" s="36">
+      <c r="J97" s="25"/>
+      <c r="K97" s="28">
         <v>64</v>
       </c>
-      <c r="L97" s="28"/>
-      <c r="M97" s="37" t="s">
+      <c r="L97" s="25"/>
+      <c r="M97" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="33"/>
+      <c r="N97" s="30"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -4892,30 +4899,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="36">
         <v>44783</v>
       </c>
-      <c r="D98" s="28"/>
+      <c r="D98" s="25"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="29" t="s">
+      <c r="F98" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="30"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="29" t="s">
+      <c r="G98" s="27"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="28"/>
-      <c r="K98" s="31">
+      <c r="J98" s="25"/>
+      <c r="K98" s="38">
         <v>100</v>
       </c>
-      <c r="L98" s="28"/>
-      <c r="M98" s="32" t="s">
+      <c r="L98" s="25"/>
+      <c r="M98" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="33"/>
+      <c r="N98" s="30"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -4924,30 +4931,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="34">
+      <c r="C99" s="24">
         <v>44783</v>
       </c>
-      <c r="D99" s="28"/>
+      <c r="D99" s="25"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="35" t="s">
+      <c r="F99" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="30"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="35" t="s">
+      <c r="G99" s="27"/>
+      <c r="H99" s="25"/>
+      <c r="I99" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="28"/>
-      <c r="K99" s="36">
+      <c r="J99" s="25"/>
+      <c r="K99" s="28">
         <v>193</v>
       </c>
-      <c r="L99" s="28"/>
-      <c r="M99" s="37" t="s">
+      <c r="L99" s="25"/>
+      <c r="M99" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="33"/>
+      <c r="N99" s="30"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -4956,30 +4963,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="36">
         <v>44783</v>
       </c>
-      <c r="D100" s="28"/>
+      <c r="D100" s="25"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="29" t="s">
+      <c r="F100" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="30"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="28"/>
-      <c r="K100" s="31">
+      <c r="G100" s="27"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="25"/>
+      <c r="K100" s="38">
         <v>15</v>
       </c>
-      <c r="L100" s="28"/>
-      <c r="M100" s="32" t="s">
+      <c r="L100" s="25"/>
+      <c r="M100" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="33"/>
+      <c r="N100" s="30"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -4988,30 +4995,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="34">
+      <c r="C101" s="24">
         <v>44783</v>
       </c>
-      <c r="D101" s="28"/>
+      <c r="D101" s="25"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="35" t="s">
+      <c r="F101" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="30"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="28"/>
-      <c r="K101" s="36">
+      <c r="G101" s="27"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="25"/>
+      <c r="K101" s="28">
         <v>65</v>
       </c>
-      <c r="L101" s="28"/>
-      <c r="M101" s="37" t="s">
+      <c r="L101" s="25"/>
+      <c r="M101" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="33"/>
+      <c r="N101" s="30"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -5020,30 +5027,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="36">
         <v>44783</v>
       </c>
-      <c r="D102" s="28"/>
+      <c r="D102" s="25"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="29" t="s">
+      <c r="F102" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="30"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="28"/>
-      <c r="K102" s="31">
+      <c r="G102" s="27"/>
+      <c r="H102" s="25"/>
+      <c r="I102" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="25"/>
+      <c r="K102" s="38">
         <v>66</v>
       </c>
-      <c r="L102" s="28"/>
-      <c r="M102" s="32" t="s">
+      <c r="L102" s="25"/>
+      <c r="M102" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="33"/>
+      <c r="N102" s="30"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -5052,30 +5059,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="34">
+      <c r="C103" s="24">
         <v>44784</v>
       </c>
-      <c r="D103" s="28"/>
+      <c r="D103" s="25"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="35" t="s">
+      <c r="F103" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="30"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="35" t="s">
+      <c r="G103" s="27"/>
+      <c r="H103" s="25"/>
+      <c r="I103" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="28"/>
-      <c r="K103" s="36">
+      <c r="J103" s="25"/>
+      <c r="K103" s="28">
         <v>111</v>
       </c>
-      <c r="L103" s="28"/>
-      <c r="M103" s="37" t="s">
+      <c r="L103" s="25"/>
+      <c r="M103" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="33"/>
+      <c r="N103" s="30"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5084,30 +5091,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="36">
         <v>44784</v>
       </c>
-      <c r="D104" s="28"/>
+      <c r="D104" s="25"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="29" t="s">
+      <c r="F104" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="30"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="29" t="s">
+      <c r="G104" s="27"/>
+      <c r="H104" s="25"/>
+      <c r="I104" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="28"/>
-      <c r="K104" s="31">
+      <c r="J104" s="25"/>
+      <c r="K104" s="38">
         <v>30</v>
       </c>
-      <c r="L104" s="28"/>
-      <c r="M104" s="32" t="s">
+      <c r="L104" s="25"/>
+      <c r="M104" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="33"/>
+      <c r="N104" s="30"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5116,30 +5123,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="34">
+      <c r="C105" s="24">
         <v>44784</v>
       </c>
-      <c r="D105" s="28"/>
+      <c r="D105" s="25"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="35" t="s">
+      <c r="F105" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="30"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="35" t="s">
+      <c r="G105" s="27"/>
+      <c r="H105" s="25"/>
+      <c r="I105" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="28"/>
-      <c r="K105" s="36">
+      <c r="J105" s="25"/>
+      <c r="K105" s="28">
         <v>31</v>
       </c>
-      <c r="L105" s="28"/>
-      <c r="M105" s="37" t="s">
+      <c r="L105" s="25"/>
+      <c r="M105" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="33"/>
+      <c r="N105" s="30"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5148,30 +5155,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="36">
         <v>44784</v>
       </c>
-      <c r="D106" s="28"/>
+      <c r="D106" s="25"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="29" t="s">
+      <c r="F106" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="30"/>
-      <c r="H106" s="28"/>
-      <c r="I106" s="29" t="s">
+      <c r="G106" s="27"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="28"/>
-      <c r="K106" s="31">
+      <c r="J106" s="25"/>
+      <c r="K106" s="38">
         <v>109</v>
       </c>
-      <c r="L106" s="28"/>
-      <c r="M106" s="32" t="s">
+      <c r="L106" s="25"/>
+      <c r="M106" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="33"/>
+      <c r="N106" s="30"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5180,30 +5187,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="34">
+      <c r="C107" s="24">
         <v>44788</v>
       </c>
-      <c r="D107" s="28"/>
+      <c r="D107" s="25"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="35" t="s">
+      <c r="F107" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="30"/>
-      <c r="H107" s="28"/>
-      <c r="I107" s="35" t="s">
+      <c r="G107" s="27"/>
+      <c r="H107" s="25"/>
+      <c r="I107" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="28"/>
-      <c r="K107" s="36">
+      <c r="J107" s="25"/>
+      <c r="K107" s="28">
         <v>5</v>
       </c>
-      <c r="L107" s="28"/>
-      <c r="M107" s="37" t="s">
+      <c r="L107" s="25"/>
+      <c r="M107" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="33"/>
+      <c r="N107" s="30"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5212,30 +5219,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="36">
         <v>44788</v>
       </c>
-      <c r="D108" s="28"/>
+      <c r="D108" s="25"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="29" t="s">
+      <c r="F108" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="30"/>
-      <c r="H108" s="28"/>
-      <c r="I108" s="29" t="s">
+      <c r="G108" s="27"/>
+      <c r="H108" s="25"/>
+      <c r="I108" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="28"/>
-      <c r="K108" s="31">
+      <c r="J108" s="25"/>
+      <c r="K108" s="38">
         <v>100</v>
       </c>
-      <c r="L108" s="28"/>
-      <c r="M108" s="32" t="s">
+      <c r="L108" s="25"/>
+      <c r="M108" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="33"/>
+      <c r="N108" s="30"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5244,30 +5251,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="34">
+      <c r="C109" s="24">
         <v>44788</v>
       </c>
-      <c r="D109" s="28"/>
+      <c r="D109" s="25"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="35" t="s">
+      <c r="F109" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="30"/>
-      <c r="H109" s="28"/>
-      <c r="I109" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="28"/>
-      <c r="K109" s="36">
+      <c r="G109" s="27"/>
+      <c r="H109" s="25"/>
+      <c r="I109" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="25"/>
+      <c r="K109" s="28">
         <v>54</v>
       </c>
-      <c r="L109" s="28"/>
-      <c r="M109" s="37" t="s">
+      <c r="L109" s="25"/>
+      <c r="M109" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="33"/>
+      <c r="N109" s="30"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5276,30 +5283,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="36">
         <v>44789</v>
       </c>
-      <c r="D110" s="28"/>
+      <c r="D110" s="25"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="29" t="s">
+      <c r="F110" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="30"/>
-      <c r="H110" s="28"/>
-      <c r="I110" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="28"/>
-      <c r="K110" s="31">
+      <c r="G110" s="27"/>
+      <c r="H110" s="25"/>
+      <c r="I110" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="25"/>
+      <c r="K110" s="38">
         <v>77</v>
       </c>
-      <c r="L110" s="28"/>
-      <c r="M110" s="32" t="s">
+      <c r="L110" s="25"/>
+      <c r="M110" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="33"/>
+      <c r="N110" s="30"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5308,30 +5315,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="34">
+      <c r="C111" s="24">
         <v>44789</v>
       </c>
-      <c r="D111" s="28"/>
+      <c r="D111" s="25"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="35" t="s">
+      <c r="F111" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="30"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="28"/>
-      <c r="K111" s="36">
+      <c r="G111" s="27"/>
+      <c r="H111" s="25"/>
+      <c r="I111" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="25"/>
+      <c r="K111" s="28">
         <v>52</v>
       </c>
-      <c r="L111" s="28"/>
-      <c r="M111" s="37" t="s">
+      <c r="L111" s="25"/>
+      <c r="M111" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="33"/>
+      <c r="N111" s="30"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5340,30 +5347,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="36">
         <v>44789</v>
       </c>
-      <c r="D112" s="28"/>
+      <c r="D112" s="25"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="29" t="s">
+      <c r="F112" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="30"/>
-      <c r="H112" s="28"/>
-      <c r="I112" s="29" t="s">
+      <c r="G112" s="27"/>
+      <c r="H112" s="25"/>
+      <c r="I112" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="28"/>
-      <c r="K112" s="31">
+      <c r="J112" s="25"/>
+      <c r="K112" s="38">
         <v>305</v>
       </c>
-      <c r="L112" s="28"/>
-      <c r="M112" s="32" t="s">
+      <c r="L112" s="25"/>
+      <c r="M112" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="33"/>
+      <c r="N112" s="30"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5372,30 +5379,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="34">
+      <c r="C113" s="24">
         <v>44789</v>
       </c>
-      <c r="D113" s="28"/>
+      <c r="D113" s="25"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="35" t="s">
+      <c r="F113" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="30"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="35" t="s">
+      <c r="G113" s="27"/>
+      <c r="H113" s="25"/>
+      <c r="I113" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="28"/>
-      <c r="K113" s="36">
+      <c r="J113" s="25"/>
+      <c r="K113" s="28">
         <v>81</v>
       </c>
-      <c r="L113" s="28"/>
-      <c r="M113" s="37" t="s">
+      <c r="L113" s="25"/>
+      <c r="M113" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="33"/>
+      <c r="N113" s="30"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5404,30 +5411,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="36">
         <v>44789</v>
       </c>
-      <c r="D114" s="28"/>
+      <c r="D114" s="25"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="29" t="s">
+      <c r="F114" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="30"/>
-      <c r="H114" s="28"/>
-      <c r="I114" s="29" t="s">
+      <c r="G114" s="27"/>
+      <c r="H114" s="25"/>
+      <c r="I114" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="28"/>
-      <c r="K114" s="31">
+      <c r="J114" s="25"/>
+      <c r="K114" s="38">
         <v>53</v>
       </c>
-      <c r="L114" s="28"/>
-      <c r="M114" s="32" t="s">
+      <c r="L114" s="25"/>
+      <c r="M114" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="33"/>
+      <c r="N114" s="30"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5436,30 +5443,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="34">
+      <c r="C115" s="24">
         <v>44789</v>
       </c>
-      <c r="D115" s="28"/>
+      <c r="D115" s="25"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="35" t="s">
+      <c r="F115" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="30"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="35" t="s">
+      <c r="G115" s="27"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="28"/>
-      <c r="K115" s="36">
+      <c r="J115" s="25"/>
+      <c r="K115" s="28">
         <v>33</v>
       </c>
-      <c r="L115" s="28"/>
-      <c r="M115" s="37" t="s">
+      <c r="L115" s="25"/>
+      <c r="M115" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="33"/>
+      <c r="N115" s="30"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5468,30 +5475,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="36">
         <v>44790</v>
       </c>
-      <c r="D116" s="28"/>
+      <c r="D116" s="25"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="29" t="s">
+      <c r="F116" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="30"/>
-      <c r="H116" s="28"/>
-      <c r="I116" s="29" t="s">
+      <c r="G116" s="27"/>
+      <c r="H116" s="25"/>
+      <c r="I116" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="28"/>
-      <c r="K116" s="31">
+      <c r="J116" s="25"/>
+      <c r="K116" s="38">
         <v>145</v>
       </c>
-      <c r="L116" s="28"/>
-      <c r="M116" s="32" t="s">
+      <c r="L116" s="25"/>
+      <c r="M116" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="33"/>
+      <c r="N116" s="30"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5500,30 +5507,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="34">
+      <c r="C117" s="24">
         <v>44790</v>
       </c>
-      <c r="D117" s="28"/>
+      <c r="D117" s="25"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="35" t="s">
+      <c r="F117" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="30"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="28"/>
-      <c r="K117" s="36">
+      <c r="G117" s="27"/>
+      <c r="H117" s="25"/>
+      <c r="I117" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="25"/>
+      <c r="K117" s="28">
         <v>14</v>
       </c>
-      <c r="L117" s="28"/>
-      <c r="M117" s="37" t="s">
+      <c r="L117" s="25"/>
+      <c r="M117" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="33"/>
+      <c r="N117" s="30"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5532,30 +5539,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="36">
         <v>44790</v>
       </c>
-      <c r="D118" s="28"/>
+      <c r="D118" s="25"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="29" t="s">
+      <c r="F118" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="30"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="28"/>
-      <c r="K118" s="31">
+      <c r="G118" s="27"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="25"/>
+      <c r="K118" s="38">
         <v>47</v>
       </c>
-      <c r="L118" s="28"/>
-      <c r="M118" s="32" t="s">
+      <c r="L118" s="25"/>
+      <c r="M118" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="33"/>
+      <c r="N118" s="30"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5564,30 +5571,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="34">
+      <c r="C119" s="24">
         <v>44790</v>
       </c>
-      <c r="D119" s="28"/>
+      <c r="D119" s="25"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="35" t="s">
+      <c r="F119" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="30"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="28"/>
-      <c r="K119" s="36">
+      <c r="G119" s="27"/>
+      <c r="H119" s="25"/>
+      <c r="I119" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="25"/>
+      <c r="K119" s="28">
         <v>16</v>
       </c>
-      <c r="L119" s="28"/>
-      <c r="M119" s="37" t="s">
+      <c r="L119" s="25"/>
+      <c r="M119" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="33"/>
+      <c r="N119" s="30"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5596,30 +5603,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="36">
         <v>44790</v>
       </c>
-      <c r="D120" s="28"/>
+      <c r="D120" s="25"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="29" t="s">
+      <c r="F120" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="30"/>
-      <c r="H120" s="28"/>
-      <c r="I120" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="28"/>
-      <c r="K120" s="31">
+      <c r="G120" s="27"/>
+      <c r="H120" s="25"/>
+      <c r="I120" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="25"/>
+      <c r="K120" s="38">
         <v>55</v>
       </c>
-      <c r="L120" s="28"/>
-      <c r="M120" s="32" t="s">
+      <c r="L120" s="25"/>
+      <c r="M120" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="33"/>
+      <c r="N120" s="30"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5628,30 +5635,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="34">
+      <c r="C121" s="24">
         <v>44790</v>
       </c>
-      <c r="D121" s="28"/>
+      <c r="D121" s="25"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="35" t="s">
+      <c r="F121" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="30"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="28"/>
-      <c r="K121" s="36">
+      <c r="G121" s="27"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="25"/>
+      <c r="K121" s="28">
         <v>8</v>
       </c>
-      <c r="L121" s="28"/>
-      <c r="M121" s="37" t="s">
+      <c r="L121" s="25"/>
+      <c r="M121" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="33"/>
+      <c r="N121" s="30"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5660,30 +5667,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="36">
         <v>44790</v>
       </c>
-      <c r="D122" s="28"/>
+      <c r="D122" s="25"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="29" t="s">
+      <c r="F122" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="30"/>
-      <c r="H122" s="28"/>
-      <c r="I122" s="29" t="s">
+      <c r="G122" s="27"/>
+      <c r="H122" s="25"/>
+      <c r="I122" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="28"/>
-      <c r="K122" s="31">
+      <c r="J122" s="25"/>
+      <c r="K122" s="38">
         <v>578</v>
       </c>
-      <c r="L122" s="28"/>
-      <c r="M122" s="32" t="s">
+      <c r="L122" s="25"/>
+      <c r="M122" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="33"/>
+      <c r="N122" s="30"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5692,30 +5699,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="34">
+      <c r="C123" s="24">
         <v>44791</v>
       </c>
-      <c r="D123" s="28"/>
+      <c r="D123" s="25"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="35" t="s">
+      <c r="F123" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="30"/>
-      <c r="H123" s="28"/>
-      <c r="I123" s="35" t="s">
+      <c r="G123" s="27"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="28"/>
-      <c r="K123" s="36">
+      <c r="J123" s="25"/>
+      <c r="K123" s="28">
         <v>111</v>
       </c>
-      <c r="L123" s="28"/>
-      <c r="M123" s="37" t="s">
+      <c r="L123" s="25"/>
+      <c r="M123" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="33"/>
+      <c r="N123" s="30"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5724,30 +5731,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="36">
         <v>44791</v>
       </c>
-      <c r="D124" s="28"/>
+      <c r="D124" s="25"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="29" t="s">
+      <c r="F124" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="30"/>
-      <c r="H124" s="28"/>
-      <c r="I124" s="29" t="s">
+      <c r="G124" s="27"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="28"/>
-      <c r="K124" s="31">
+      <c r="J124" s="25"/>
+      <c r="K124" s="38">
         <v>51</v>
       </c>
-      <c r="L124" s="28"/>
-      <c r="M124" s="32" t="s">
+      <c r="L124" s="25"/>
+      <c r="M124" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="33"/>
+      <c r="N124" s="30"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5756,30 +5763,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="34">
+      <c r="C125" s="24">
         <v>44791</v>
       </c>
-      <c r="D125" s="28"/>
+      <c r="D125" s="25"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="35" t="s">
+      <c r="F125" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="30"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="35" t="s">
+      <c r="G125" s="27"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="28"/>
-      <c r="K125" s="36">
+      <c r="J125" s="25"/>
+      <c r="K125" s="28">
         <v>35</v>
       </c>
-      <c r="L125" s="28"/>
-      <c r="M125" s="37" t="s">
+      <c r="L125" s="25"/>
+      <c r="M125" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="33"/>
+      <c r="N125" s="30"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -5788,30 +5795,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="36">
         <v>44792</v>
       </c>
-      <c r="D126" s="28"/>
+      <c r="D126" s="25"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="29" t="s">
+      <c r="F126" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="30"/>
-      <c r="H126" s="28"/>
-      <c r="I126" s="29" t="s">
+      <c r="G126" s="27"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="28"/>
-      <c r="K126" s="31">
+      <c r="J126" s="25"/>
+      <c r="K126" s="38">
         <v>74</v>
       </c>
-      <c r="L126" s="28"/>
-      <c r="M126" s="32" t="s">
+      <c r="L126" s="25"/>
+      <c r="M126" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="33"/>
+      <c r="N126" s="30"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -5820,30 +5827,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="34">
+      <c r="C127" s="24">
         <v>44795</v>
       </c>
-      <c r="D127" s="28"/>
+      <c r="D127" s="25"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="35" t="s">
+      <c r="F127" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="30"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="28"/>
-      <c r="K127" s="36">
+      <c r="G127" s="27"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="25"/>
+      <c r="K127" s="28">
         <v>51</v>
       </c>
-      <c r="L127" s="28"/>
-      <c r="M127" s="37" t="s">
+      <c r="L127" s="25"/>
+      <c r="M127" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="33"/>
+      <c r="N127" s="30"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -5852,30 +5859,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="36">
         <v>44799</v>
       </c>
-      <c r="D128" s="28"/>
+      <c r="D128" s="25"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="29" t="s">
+      <c r="F128" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="30"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="28"/>
-      <c r="K128" s="31">
+      <c r="G128" s="27"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="25"/>
+      <c r="K128" s="38">
         <v>80</v>
       </c>
-      <c r="L128" s="28"/>
-      <c r="M128" s="32" t="s">
+      <c r="L128" s="25"/>
+      <c r="M128" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="33"/>
+      <c r="N128" s="30"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -5884,30 +5891,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="34">
+      <c r="C129" s="24">
         <v>44799</v>
       </c>
-      <c r="D129" s="28"/>
+      <c r="D129" s="25"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="35" t="s">
+      <c r="F129" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="30"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="28"/>
-      <c r="K129" s="36">
+      <c r="G129" s="27"/>
+      <c r="H129" s="25"/>
+      <c r="I129" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="25"/>
+      <c r="K129" s="28">
         <v>100</v>
       </c>
-      <c r="L129" s="28"/>
-      <c r="M129" s="37" t="s">
+      <c r="L129" s="25"/>
+      <c r="M129" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="33"/>
+      <c r="N129" s="30"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -5916,30 +5923,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="36">
         <v>44802</v>
       </c>
-      <c r="D130" s="28"/>
+      <c r="D130" s="25"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="29" t="s">
+      <c r="F130" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="30"/>
-      <c r="H130" s="28"/>
-      <c r="I130" s="29" t="s">
+      <c r="G130" s="27"/>
+      <c r="H130" s="25"/>
+      <c r="I130" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="28"/>
-      <c r="K130" s="31">
+      <c r="J130" s="25"/>
+      <c r="K130" s="38">
         <v>96</v>
       </c>
-      <c r="L130" s="28"/>
-      <c r="M130" s="32" t="s">
+      <c r="L130" s="25"/>
+      <c r="M130" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="33"/>
+      <c r="N130" s="30"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -5948,30 +5955,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="34">
+      <c r="C131" s="24">
         <v>44802</v>
       </c>
-      <c r="D131" s="28"/>
+      <c r="D131" s="25"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="35" t="s">
+      <c r="F131" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="30"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="28"/>
-      <c r="K131" s="36">
+      <c r="G131" s="27"/>
+      <c r="H131" s="25"/>
+      <c r="I131" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="25"/>
+      <c r="K131" s="28">
         <v>37</v>
       </c>
-      <c r="L131" s="28"/>
-      <c r="M131" s="37" t="s">
+      <c r="L131" s="25"/>
+      <c r="M131" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="33"/>
+      <c r="N131" s="30"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -5980,30 +5987,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="36">
         <v>44804</v>
       </c>
-      <c r="D132" s="28"/>
+      <c r="D132" s="25"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="29" t="s">
+      <c r="F132" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="30"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="28"/>
-      <c r="K132" s="31">
+      <c r="G132" s="27"/>
+      <c r="H132" s="25"/>
+      <c r="I132" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="25"/>
+      <c r="K132" s="38">
         <v>91</v>
       </c>
-      <c r="L132" s="28"/>
-      <c r="M132" s="32" t="s">
+      <c r="L132" s="25"/>
+      <c r="M132" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="33"/>
+      <c r="N132" s="30"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -6012,30 +6019,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="34">
+      <c r="C133" s="24">
         <v>44804</v>
       </c>
-      <c r="D133" s="28"/>
+      <c r="D133" s="25"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="35" t="s">
+      <c r="F133" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="30"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="35" t="s">
+      <c r="G133" s="27"/>
+      <c r="H133" s="25"/>
+      <c r="I133" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="28"/>
-      <c r="K133" s="36">
+      <c r="J133" s="25"/>
+      <c r="K133" s="28">
         <v>56</v>
       </c>
-      <c r="L133" s="28"/>
-      <c r="M133" s="37" t="s">
+      <c r="L133" s="25"/>
+      <c r="M133" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="33"/>
+      <c r="N133" s="30"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -6044,30 +6051,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="36">
         <v>44805</v>
       </c>
-      <c r="D134" s="28"/>
+      <c r="D134" s="25"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="29" t="s">
+      <c r="F134" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="30"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="28"/>
-      <c r="K134" s="31">
+      <c r="G134" s="27"/>
+      <c r="H134" s="25"/>
+      <c r="I134" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="25"/>
+      <c r="K134" s="38">
         <v>401</v>
       </c>
-      <c r="L134" s="28"/>
-      <c r="M134" s="32" t="s">
+      <c r="L134" s="25"/>
+      <c r="M134" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="33"/>
+      <c r="N134" s="30"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -6076,30 +6083,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="34">
+      <c r="C135" s="24">
         <v>44805</v>
       </c>
-      <c r="D135" s="28"/>
+      <c r="D135" s="25"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="35" t="s">
+      <c r="F135" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="30"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="35" t="s">
+      <c r="G135" s="27"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="28"/>
-      <c r="K135" s="36">
+      <c r="J135" s="25"/>
+      <c r="K135" s="28">
         <v>375</v>
       </c>
-      <c r="L135" s="28"/>
-      <c r="M135" s="37" t="s">
+      <c r="L135" s="25"/>
+      <c r="M135" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="33"/>
+      <c r="N135" s="30"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6108,30 +6115,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="27">
+      <c r="C136" s="36">
         <v>44806</v>
       </c>
-      <c r="D136" s="28"/>
+      <c r="D136" s="25"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="29" t="s">
+      <c r="F136" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="30"/>
-      <c r="H136" s="28"/>
-      <c r="I136" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="28"/>
-      <c r="K136" s="31">
+      <c r="G136" s="27"/>
+      <c r="H136" s="25"/>
+      <c r="I136" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="25"/>
+      <c r="K136" s="38">
         <v>44</v>
       </c>
-      <c r="L136" s="28"/>
-      <c r="M136" s="32" t="s">
+      <c r="L136" s="25"/>
+      <c r="M136" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="33"/>
+      <c r="N136" s="30"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6140,30 +6147,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="34">
+      <c r="C137" s="24">
         <v>44806</v>
       </c>
-      <c r="D137" s="28"/>
+      <c r="D137" s="25"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="35" t="s">
+      <c r="F137" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="30"/>
-      <c r="H137" s="28"/>
-      <c r="I137" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="28"/>
-      <c r="K137" s="36">
+      <c r="G137" s="27"/>
+      <c r="H137" s="25"/>
+      <c r="I137" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="25"/>
+      <c r="K137" s="28">
         <v>51</v>
       </c>
-      <c r="L137" s="28"/>
-      <c r="M137" s="37" t="s">
+      <c r="L137" s="25"/>
+      <c r="M137" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="33"/>
+      <c r="N137" s="30"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6172,30 +6179,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="27">
+      <c r="C138" s="36">
         <v>44806</v>
       </c>
-      <c r="D138" s="28"/>
+      <c r="D138" s="25"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="29" t="s">
+      <c r="F138" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="30"/>
-      <c r="H138" s="28"/>
-      <c r="I138" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="28"/>
-      <c r="K138" s="31">
+      <c r="G138" s="27"/>
+      <c r="H138" s="25"/>
+      <c r="I138" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="25"/>
+      <c r="K138" s="38">
         <v>40</v>
       </c>
-      <c r="L138" s="28"/>
-      <c r="M138" s="32" t="s">
+      <c r="L138" s="25"/>
+      <c r="M138" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="33"/>
+      <c r="N138" s="30"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6204,30 +6211,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="34">
+      <c r="C139" s="24">
         <v>44810</v>
       </c>
-      <c r="D139" s="28"/>
+      <c r="D139" s="25"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="35" t="s">
+      <c r="F139" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="30"/>
-      <c r="H139" s="28"/>
-      <c r="I139" s="35" t="s">
+      <c r="G139" s="27"/>
+      <c r="H139" s="25"/>
+      <c r="I139" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="28"/>
-      <c r="K139" s="36">
+      <c r="J139" s="25"/>
+      <c r="K139" s="28">
         <v>9</v>
       </c>
-      <c r="L139" s="28"/>
-      <c r="M139" s="37" t="s">
+      <c r="L139" s="25"/>
+      <c r="M139" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="33"/>
+      <c r="N139" s="30"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6236,30 +6243,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="27">
+      <c r="C140" s="36">
         <v>44810</v>
       </c>
-      <c r="D140" s="28"/>
+      <c r="D140" s="25"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="29" t="s">
+      <c r="F140" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="30"/>
-      <c r="H140" s="28"/>
-      <c r="I140" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="28"/>
-      <c r="K140" s="31">
+      <c r="G140" s="27"/>
+      <c r="H140" s="25"/>
+      <c r="I140" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="25"/>
+      <c r="K140" s="38">
         <v>17</v>
       </c>
-      <c r="L140" s="28"/>
-      <c r="M140" s="32" t="s">
+      <c r="L140" s="25"/>
+      <c r="M140" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="33"/>
+      <c r="N140" s="30"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6268,30 +6275,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="34">
+      <c r="C141" s="24">
         <v>44810</v>
       </c>
-      <c r="D141" s="28"/>
+      <c r="D141" s="25"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="35" t="s">
+      <c r="F141" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="30"/>
-      <c r="H141" s="28"/>
-      <c r="I141" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="28"/>
-      <c r="K141" s="36">
+      <c r="G141" s="27"/>
+      <c r="H141" s="25"/>
+      <c r="I141" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="25"/>
+      <c r="K141" s="28">
         <v>5</v>
       </c>
-      <c r="L141" s="28"/>
-      <c r="M141" s="37" t="s">
+      <c r="L141" s="25"/>
+      <c r="M141" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="33"/>
+      <c r="N141" s="30"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6300,30 +6307,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="27">
+      <c r="C142" s="36">
         <v>44810</v>
       </c>
-      <c r="D142" s="28"/>
+      <c r="D142" s="25"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="29" t="s">
+      <c r="F142" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="30"/>
-      <c r="H142" s="28"/>
-      <c r="I142" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="28"/>
-      <c r="K142" s="31">
+      <c r="G142" s="27"/>
+      <c r="H142" s="25"/>
+      <c r="I142" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="25"/>
+      <c r="K142" s="38">
         <v>45</v>
       </c>
-      <c r="L142" s="28"/>
-      <c r="M142" s="32" t="s">
+      <c r="L142" s="25"/>
+      <c r="M142" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="33"/>
+      <c r="N142" s="30"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6332,30 +6339,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="34">
+      <c r="C143" s="24">
         <v>44811</v>
       </c>
-      <c r="D143" s="28"/>
+      <c r="D143" s="25"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="35" t="s">
+      <c r="F143" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="30"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="35" t="s">
+      <c r="G143" s="27"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="28"/>
-      <c r="K143" s="36">
+      <c r="J143" s="25"/>
+      <c r="K143" s="28">
         <v>132</v>
       </c>
-      <c r="L143" s="28"/>
-      <c r="M143" s="37" t="s">
+      <c r="L143" s="25"/>
+      <c r="M143" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="33"/>
+      <c r="N143" s="30"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6364,30 +6371,30 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="27">
+      <c r="C144" s="36">
         <v>44811</v>
       </c>
-      <c r="D144" s="28"/>
+      <c r="D144" s="25"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="29" t="s">
+      <c r="F144" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="30"/>
-      <c r="H144" s="28"/>
-      <c r="I144" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="28"/>
-      <c r="K144" s="31">
+      <c r="G144" s="27"/>
+      <c r="H144" s="25"/>
+      <c r="I144" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="25"/>
+      <c r="K144" s="38">
         <v>66</v>
       </c>
-      <c r="L144" s="28"/>
-      <c r="M144" s="32" t="s">
+      <c r="L144" s="25"/>
+      <c r="M144" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="33"/>
+      <c r="N144" s="30"/>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
@@ -6396,30 +6403,30 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="34">
+      <c r="C145" s="24">
         <v>44812</v>
       </c>
-      <c r="D145" s="28"/>
+      <c r="D145" s="25"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="35" t="s">
+      <c r="F145" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="30"/>
-      <c r="H145" s="28"/>
-      <c r="I145" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J145" s="28"/>
-      <c r="K145" s="36">
+      <c r="G145" s="27"/>
+      <c r="H145" s="25"/>
+      <c r="I145" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="25"/>
+      <c r="K145" s="28">
         <v>69</v>
       </c>
-      <c r="L145" s="28"/>
-      <c r="M145" s="37" t="s">
+      <c r="L145" s="25"/>
+      <c r="M145" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="N145" s="33"/>
+      <c r="N145" s="30"/>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="3" t="s">
@@ -6428,30 +6435,30 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="27">
+      <c r="C146" s="36">
         <v>44812</v>
       </c>
-      <c r="D146" s="28"/>
+      <c r="D146" s="25"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="29" t="s">
+      <c r="F146" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="G146" s="30"/>
-      <c r="H146" s="28"/>
-      <c r="I146" s="29" t="s">
+      <c r="G146" s="27"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J146" s="28"/>
-      <c r="K146" s="31">
+      <c r="J146" s="25"/>
+      <c r="K146" s="38">
         <v>48</v>
       </c>
-      <c r="L146" s="28"/>
-      <c r="M146" s="32" t="s">
+      <c r="L146" s="25"/>
+      <c r="M146" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="N146" s="33"/>
+      <c r="N146" s="30"/>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
@@ -6460,30 +6467,30 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="34">
+      <c r="C147" s="24">
         <v>44812</v>
       </c>
-      <c r="D147" s="28"/>
+      <c r="D147" s="25"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="35" t="s">
+      <c r="F147" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="G147" s="30"/>
-      <c r="H147" s="28"/>
-      <c r="I147" s="35" t="s">
+      <c r="G147" s="27"/>
+      <c r="H147" s="25"/>
+      <c r="I147" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J147" s="28"/>
-      <c r="K147" s="36">
+      <c r="J147" s="25"/>
+      <c r="K147" s="28">
         <v>33</v>
       </c>
-      <c r="L147" s="28"/>
-      <c r="M147" s="37" t="s">
+      <c r="L147" s="25"/>
+      <c r="M147" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="N147" s="33"/>
+      <c r="N147" s="30"/>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="3" t="s">
@@ -6492,30 +6499,30 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="27">
+      <c r="C148" s="36">
         <v>44813</v>
       </c>
-      <c r="D148" s="28"/>
+      <c r="D148" s="25"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="29" t="s">
+      <c r="F148" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="G148" s="30"/>
-      <c r="H148" s="28"/>
-      <c r="I148" s="29" t="s">
+      <c r="G148" s="27"/>
+      <c r="H148" s="25"/>
+      <c r="I148" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J148" s="28"/>
-      <c r="K148" s="31">
+      <c r="J148" s="25"/>
+      <c r="K148" s="38">
         <v>5</v>
       </c>
-      <c r="L148" s="28"/>
-      <c r="M148" s="32" t="s">
+      <c r="L148" s="25"/>
+      <c r="M148" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="N148" s="33"/>
+      <c r="N148" s="30"/>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
@@ -6524,30 +6531,30 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="34">
+      <c r="C149" s="24">
         <v>44813</v>
       </c>
-      <c r="D149" s="28"/>
+      <c r="D149" s="25"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="35" t="s">
+      <c r="F149" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="G149" s="30"/>
-      <c r="H149" s="28"/>
-      <c r="I149" s="35" t="s">
+      <c r="G149" s="27"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J149" s="28"/>
-      <c r="K149" s="36">
+      <c r="J149" s="25"/>
+      <c r="K149" s="28">
         <v>26</v>
       </c>
-      <c r="L149" s="28"/>
-      <c r="M149" s="37" t="s">
+      <c r="L149" s="25"/>
+      <c r="M149" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="N149" s="33"/>
+      <c r="N149" s="30"/>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="3" t="s">
@@ -6556,30 +6563,30 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="27">
+      <c r="C150" s="36">
         <v>44813</v>
       </c>
-      <c r="D150" s="28"/>
+      <c r="D150" s="25"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="29" t="s">
+      <c r="F150" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="G150" s="30"/>
-      <c r="H150" s="28"/>
-      <c r="I150" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J150" s="28"/>
-      <c r="K150" s="31">
+      <c r="G150" s="27"/>
+      <c r="H150" s="25"/>
+      <c r="I150" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="25"/>
+      <c r="K150" s="38">
         <v>13</v>
       </c>
-      <c r="L150" s="28"/>
-      <c r="M150" s="32" t="s">
+      <c r="L150" s="25"/>
+      <c r="M150" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="N150" s="33"/>
+      <c r="N150" s="30"/>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
@@ -6588,30 +6595,30 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="34">
+      <c r="C151" s="24">
         <v>44816</v>
       </c>
-      <c r="D151" s="28"/>
+      <c r="D151" s="25"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="35" t="s">
+      <c r="F151" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="G151" s="30"/>
-      <c r="H151" s="28"/>
-      <c r="I151" s="35" t="s">
+      <c r="G151" s="27"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J151" s="28"/>
-      <c r="K151" s="36">
+      <c r="J151" s="25"/>
+      <c r="K151" s="28">
         <v>50</v>
       </c>
-      <c r="L151" s="28"/>
-      <c r="M151" s="37" t="s">
+      <c r="L151" s="25"/>
+      <c r="M151" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="N151" s="33"/>
+      <c r="N151" s="30"/>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="3" t="s">
@@ -6620,119 +6627,1604 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="27">
+      <c r="C152" s="36">
         <v>44816</v>
       </c>
-      <c r="D152" s="28"/>
+      <c r="D152" s="25"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="29" t="s">
+      <c r="F152" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="30"/>
-      <c r="H152" s="28"/>
-      <c r="I152" s="29" t="s">
+      <c r="G152" s="27"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J152" s="28"/>
-      <c r="K152" s="31">
+      <c r="J152" s="25"/>
+      <c r="K152" s="38">
         <v>104</v>
       </c>
-      <c r="L152" s="28"/>
-      <c r="M152" s="32" t="s">
+      <c r="L152" s="25"/>
+      <c r="M152" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="N152" s="33"/>
-    </row>
-    <row r="153" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A153" s="25" t="s">
+      <c r="N152" s="30"/>
+    </row>
+    <row r="153" spans="1:14">
+      <c r="A153" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B153" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C153" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D153" s="25"/>
+      <c r="E153" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F153" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G153" s="27"/>
+      <c r="H153" s="25"/>
+      <c r="I153" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="25"/>
+      <c r="K153" s="28">
+        <v>1</v>
+      </c>
+      <c r="L153" s="25"/>
+      <c r="M153" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N153" s="30"/>
+    </row>
+    <row r="154" spans="1:14">
+      <c r="A154" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B154" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C154" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D154" s="25"/>
+      <c r="E154" s="4">
+        <v>44848</v>
+      </c>
+      <c r="F154" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G154" s="27"/>
+      <c r="H154" s="25"/>
+      <c r="I154" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="25"/>
+      <c r="K154" s="38">
+        <v>2</v>
+      </c>
+      <c r="L154" s="25"/>
+      <c r="M154" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N154" s="30"/>
+    </row>
+    <row r="155" spans="1:14">
+      <c r="A155" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B155" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C155" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D155" s="25"/>
+      <c r="E155" s="2">
+        <v>45198</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G155" s="27"/>
+      <c r="H155" s="25"/>
+      <c r="I155" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="25"/>
+      <c r="K155" s="28">
+        <v>2</v>
+      </c>
+      <c r="L155" s="25"/>
+      <c r="M155" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N155" s="30"/>
+    </row>
+    <row r="156" spans="1:14">
+      <c r="A156" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B156" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C156" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D156" s="25"/>
+      <c r="E156" s="4">
+        <v>45044</v>
+      </c>
+      <c r="F156" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G156" s="27"/>
+      <c r="H156" s="25"/>
+      <c r="I156" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="25"/>
+      <c r="K156" s="38">
+        <v>5</v>
+      </c>
+      <c r="L156" s="25"/>
+      <c r="M156" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N156" s="30"/>
+    </row>
+    <row r="157" spans="1:14">
+      <c r="A157" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B157" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C157" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D157" s="25"/>
+      <c r="E157" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F157" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G157" s="27"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="25"/>
+      <c r="K157" s="28">
+        <v>2</v>
+      </c>
+      <c r="L157" s="25"/>
+      <c r="M157" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N157" s="30"/>
+    </row>
+    <row r="158" spans="1:14">
+      <c r="A158" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B158" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C158" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D158" s="25"/>
+      <c r="E158" s="4">
+        <v>45192</v>
+      </c>
+      <c r="F158" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G158" s="27"/>
+      <c r="H158" s="25"/>
+      <c r="I158" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="25"/>
+      <c r="K158" s="38">
+        <v>1</v>
+      </c>
+      <c r="L158" s="25"/>
+      <c r="M158" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N158" s="30"/>
+    </row>
+    <row r="159" spans="1:14">
+      <c r="A159" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B159" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C159" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D159" s="25"/>
+      <c r="E159" s="2">
+        <v>44957</v>
+      </c>
+      <c r="F159" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G159" s="27"/>
+      <c r="H159" s="25"/>
+      <c r="I159" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="25"/>
+      <c r="K159" s="28">
+        <v>4</v>
+      </c>
+      <c r="L159" s="25"/>
+      <c r="M159" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N159" s="30"/>
+    </row>
+    <row r="160" spans="1:14">
+      <c r="A160" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B160" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C160" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D160" s="25"/>
+      <c r="E160" s="4">
+        <v>44834</v>
+      </c>
+      <c r="F160" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G160" s="27"/>
+      <c r="H160" s="25"/>
+      <c r="I160" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="25"/>
+      <c r="K160" s="38">
+        <v>4</v>
+      </c>
+      <c r="L160" s="25"/>
+      <c r="M160" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N160" s="30"/>
+    </row>
+    <row r="161" spans="1:14">
+      <c r="A161" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B161" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C161" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D161" s="25"/>
+      <c r="E161" s="2">
+        <v>45077</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G161" s="27"/>
+      <c r="H161" s="25"/>
+      <c r="I161" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="25"/>
+      <c r="K161" s="28">
+        <v>3</v>
+      </c>
+      <c r="L161" s="25"/>
+      <c r="M161" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N161" s="30"/>
+    </row>
+    <row r="162" spans="1:14">
+      <c r="A162" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B162" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C162" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D162" s="25"/>
+      <c r="E162" s="4">
+        <v>45093</v>
+      </c>
+      <c r="F162" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G162" s="27"/>
+      <c r="H162" s="25"/>
+      <c r="I162" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="25"/>
+      <c r="K162" s="38">
+        <v>8</v>
+      </c>
+      <c r="L162" s="25"/>
+      <c r="M162" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N162" s="30"/>
+    </row>
+    <row r="163" spans="1:14">
+      <c r="A163" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B163" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C163" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D163" s="25"/>
+      <c r="E163" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F163" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G163" s="27"/>
+      <c r="H163" s="25"/>
+      <c r="I163" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="25"/>
+      <c r="K163" s="28">
+        <v>1</v>
+      </c>
+      <c r="L163" s="25"/>
+      <c r="M163" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N163" s="30"/>
+    </row>
+    <row r="164" spans="1:14">
+      <c r="A164" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B164" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C164" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D164" s="25"/>
+      <c r="E164" s="4">
+        <v>45227</v>
+      </c>
+      <c r="F164" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G164" s="27"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="25"/>
+      <c r="K164" s="38">
+        <v>2</v>
+      </c>
+      <c r="L164" s="25"/>
+      <c r="M164" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N164" s="30"/>
+    </row>
+    <row r="165" spans="1:14">
+      <c r="A165" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B165" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C165" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D165" s="25"/>
+      <c r="E165" s="2">
+        <v>45046</v>
+      </c>
+      <c r="F165" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G165" s="27"/>
+      <c r="H165" s="25"/>
+      <c r="I165" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="25"/>
+      <c r="K165" s="28">
+        <v>1</v>
+      </c>
+      <c r="L165" s="25"/>
+      <c r="M165" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N165" s="30"/>
+    </row>
+    <row r="166" spans="1:14">
+      <c r="A166" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B166" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C166" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D166" s="25"/>
+      <c r="E166" s="4">
+        <v>45092</v>
+      </c>
+      <c r="F166" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G166" s="27"/>
+      <c r="H166" s="25"/>
+      <c r="I166" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="25"/>
+      <c r="K166" s="38">
+        <v>3</v>
+      </c>
+      <c r="L166" s="25"/>
+      <c r="M166" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N166" s="30"/>
+    </row>
+    <row r="167" spans="1:14">
+      <c r="A167" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B167" s="2">
+        <v>44813</v>
+      </c>
+      <c r="C167" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D167" s="25"/>
+      <c r="E167" s="2">
+        <v>44985</v>
+      </c>
+      <c r="F167" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G167" s="27"/>
+      <c r="H167" s="25"/>
+      <c r="I167" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="25"/>
+      <c r="K167" s="28">
+        <v>1</v>
+      </c>
+      <c r="L167" s="25"/>
+      <c r="M167" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N167" s="30"/>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="A168" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B168" s="4">
+        <v>44813</v>
+      </c>
+      <c r="C168" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D168" s="25"/>
+      <c r="E168" s="4">
+        <v>45555</v>
+      </c>
+      <c r="F168" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G168" s="27"/>
+      <c r="H168" s="25"/>
+      <c r="I168" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="25"/>
+      <c r="K168" s="38">
+        <v>1</v>
+      </c>
+      <c r="L168" s="25"/>
+      <c r="M168" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="N168" s="30"/>
+    </row>
+    <row r="169" spans="1:14">
+      <c r="A169" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B169" s="2">
+        <v>44811</v>
+      </c>
+      <c r="C169" s="24">
+        <v>44817</v>
+      </c>
+      <c r="D169" s="25"/>
+      <c r="E169" s="2">
+        <v>44882</v>
+      </c>
+      <c r="F169" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="G169" s="27"/>
+      <c r="H169" s="25"/>
+      <c r="I169" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J169" s="25"/>
+      <c r="K169" s="28">
+        <v>92</v>
+      </c>
+      <c r="L169" s="25"/>
+      <c r="M169" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="N169" s="30"/>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="A170" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B170" s="4">
+        <v>44811</v>
+      </c>
+      <c r="C170" s="36">
+        <v>44817</v>
+      </c>
+      <c r="D170" s="25"/>
+      <c r="E170" s="4">
+        <v>44882</v>
+      </c>
+      <c r="F170" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="G170" s="27"/>
+      <c r="H170" s="25"/>
+      <c r="I170" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="J170" s="25"/>
+      <c r="K170" s="38">
+        <v>169</v>
+      </c>
+      <c r="L170" s="25"/>
+      <c r="M170" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="N170" s="30"/>
+    </row>
+    <row r="171" spans="1:14">
+      <c r="A171" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B171" s="2">
+        <v>44817</v>
+      </c>
+      <c r="C171" s="24">
+        <v>44818</v>
+      </c>
+      <c r="D171" s="25"/>
+      <c r="E171" s="2">
+        <v>44888</v>
+      </c>
+      <c r="F171" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="G171" s="27"/>
+      <c r="H171" s="25"/>
+      <c r="I171" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="25"/>
+      <c r="K171" s="28">
+        <v>99</v>
+      </c>
+      <c r="L171" s="25"/>
+      <c r="M171" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="N171" s="30"/>
+    </row>
+    <row r="172" spans="1:14">
+      <c r="A172" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B172" s="4">
+        <v>44817</v>
+      </c>
+      <c r="C172" s="36">
+        <v>44818</v>
+      </c>
+      <c r="D172" s="25"/>
+      <c r="E172" s="4">
+        <v>44911</v>
+      </c>
+      <c r="F172" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="G172" s="27"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="J172" s="25"/>
+      <c r="K172" s="38">
+        <v>10</v>
+      </c>
+      <c r="L172" s="25"/>
+      <c r="M172" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="N172" s="30"/>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B173" s="2">
+        <v>44817</v>
+      </c>
+      <c r="C173" s="24">
+        <v>44818</v>
+      </c>
+      <c r="D173" s="25"/>
+      <c r="E173" s="2">
+        <v>44876</v>
+      </c>
+      <c r="F173" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="G173" s="27"/>
+      <c r="H173" s="25"/>
+      <c r="I173" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="J173" s="25"/>
+      <c r="K173" s="28">
+        <v>69</v>
+      </c>
+      <c r="L173" s="25"/>
+      <c r="M173" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="N173" s="30"/>
+    </row>
+    <row r="174" spans="1:14" ht="28.5" customHeight="1">
+      <c r="A174" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="B174" s="50"/>
+      <c r="C174" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="B153" s="26"/>
-      <c r="C153" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="D153" s="23"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G153" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="H153" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="I153" s="24"/>
-      <c r="J153" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="K153" s="24"/>
-      <c r="L153" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="M153" s="24"/>
-      <c r="N153" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" s="8" customFormat="1">
-      <c r="A154" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B154" s="21"/>
-      <c r="C154" s="17">
-        <v>11381</v>
-      </c>
-      <c r="D154" s="18"/>
-      <c r="E154" s="19"/>
-      <c r="F154" s="6">
-        <v>86</v>
-      </c>
-      <c r="G154" s="15">
-        <v>3</v>
-      </c>
-      <c r="H154" s="17">
+      <c r="D174" s="46"/>
+      <c r="E174" s="47"/>
+      <c r="F174" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G174" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="H174" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="I174" s="48"/>
+      <c r="J174" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="K174" s="47"/>
+      <c r="L174" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="M174" s="47"/>
+      <c r="N174" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" s="10" customFormat="1">
+      <c r="A175" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="B175" s="44"/>
+      <c r="C175" s="40">
+        <v>11861</v>
+      </c>
+      <c r="D175" s="41"/>
+      <c r="E175" s="42"/>
+      <c r="F175" s="7">
+        <v>103</v>
+      </c>
+      <c r="G175" s="8">
+        <v>4</v>
+      </c>
+      <c r="H175" s="40">
         <v>1</v>
       </c>
-      <c r="I154" s="19"/>
-      <c r="J154" s="17">
-        <v>57</v>
-      </c>
-      <c r="K154" s="19"/>
-      <c r="L154" s="17">
+      <c r="I175" s="42"/>
+      <c r="J175" s="40">
+        <v>60</v>
+      </c>
+      <c r="K175" s="42"/>
+      <c r="L175" s="40">
         <v>1</v>
       </c>
-      <c r="M154" s="19"/>
-      <c r="N154" s="7">
+      <c r="M175" s="42"/>
+      <c r="N175" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="762">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
+  <mergeCells count="867">
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="H175:I175"/>
+    <mergeCell ref="J175:K175"/>
+    <mergeCell ref="L175:M175"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="H174:I174"/>
+    <mergeCell ref="J174:K174"/>
+    <mergeCell ref="L174:M174"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="F173:H173"/>
+    <mergeCell ref="I173:J173"/>
+    <mergeCell ref="K173:L173"/>
+    <mergeCell ref="M173:N173"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="F172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="M172:N172"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="F171:H171"/>
+    <mergeCell ref="I171:J171"/>
+    <mergeCell ref="K171:L171"/>
+    <mergeCell ref="M171:N171"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="F170:H170"/>
+    <mergeCell ref="I170:J170"/>
+    <mergeCell ref="K170:L170"/>
+    <mergeCell ref="M170:N170"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="F169:H169"/>
+    <mergeCell ref="I169:J169"/>
+    <mergeCell ref="K169:L169"/>
+    <mergeCell ref="M169:N169"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="I168:J168"/>
+    <mergeCell ref="K168:L168"/>
+    <mergeCell ref="M168:N168"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="I167:J167"/>
+    <mergeCell ref="K167:L167"/>
+    <mergeCell ref="M167:N167"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="I166:J166"/>
+    <mergeCell ref="K166:L166"/>
+    <mergeCell ref="M166:N166"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="F165:H165"/>
+    <mergeCell ref="I165:J165"/>
+    <mergeCell ref="K165:L165"/>
+    <mergeCell ref="M165:N165"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="F164:H164"/>
+    <mergeCell ref="I164:J164"/>
+    <mergeCell ref="K164:L164"/>
+    <mergeCell ref="M164:N164"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="F163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="M163:N163"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="F162:H162"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="K162:L162"/>
+    <mergeCell ref="M162:N162"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="F161:H161"/>
+    <mergeCell ref="I161:J161"/>
+    <mergeCell ref="K161:L161"/>
+    <mergeCell ref="M161:N161"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="F160:H160"/>
+    <mergeCell ref="I160:J160"/>
+    <mergeCell ref="K160:L160"/>
+    <mergeCell ref="M160:N160"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="F159:H159"/>
+    <mergeCell ref="I159:J159"/>
+    <mergeCell ref="K159:L159"/>
+    <mergeCell ref="M159:N159"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="I158:J158"/>
+    <mergeCell ref="K158:L158"/>
+    <mergeCell ref="M158:N158"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="I157:J157"/>
+    <mergeCell ref="K157:L157"/>
+    <mergeCell ref="M157:N157"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="I156:J156"/>
+    <mergeCell ref="K156:L156"/>
+    <mergeCell ref="M156:N156"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="I155:J155"/>
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="M155:N155"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="M154:N154"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F153:H153"/>
+    <mergeCell ref="I153:J153"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="M153:N153"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="F152:H152"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="K152:L152"/>
+    <mergeCell ref="M152:N152"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="M151:N151"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="K150:L150"/>
+    <mergeCell ref="M150:N150"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="I149:J149"/>
+    <mergeCell ref="K149:L149"/>
+    <mergeCell ref="M149:N149"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="K148:L148"/>
+    <mergeCell ref="M148:N148"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="I147:J147"/>
+    <mergeCell ref="K147:L147"/>
+    <mergeCell ref="M147:N147"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="K146:L146"/>
+    <mergeCell ref="M146:N146"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="M145:N145"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="F144:H144"/>
+    <mergeCell ref="I144:J144"/>
+    <mergeCell ref="K144:L144"/>
+    <mergeCell ref="M144:N144"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="F143:H143"/>
+    <mergeCell ref="I143:J143"/>
+    <mergeCell ref="K143:L143"/>
+    <mergeCell ref="M143:N143"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="I142:J142"/>
+    <mergeCell ref="K142:L142"/>
+    <mergeCell ref="M142:N142"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="I141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="M141:N141"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="F140:H140"/>
+    <mergeCell ref="I140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="M140:N140"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="F139:H139"/>
+    <mergeCell ref="I139:J139"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="M139:N139"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="M137:N137"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="M136:N136"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="M135:N135"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="M134:N134"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="M133:N133"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="M132:N132"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="M131:N131"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="K130:L130"/>
+    <mergeCell ref="M130:N130"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="M126:N126"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="I124:J124"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="M124:N124"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="I123:J123"/>
+    <mergeCell ref="K123:L123"/>
+    <mergeCell ref="M123:N123"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="M122:N122"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="I121:J121"/>
+    <mergeCell ref="K121:L121"/>
+    <mergeCell ref="M121:N121"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="I120:J120"/>
+    <mergeCell ref="K120:L120"/>
+    <mergeCell ref="M120:N120"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="I119:J119"/>
+    <mergeCell ref="K119:L119"/>
+    <mergeCell ref="M119:N119"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="I118:J118"/>
+    <mergeCell ref="K118:L118"/>
+    <mergeCell ref="M118:N118"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="M117:N117"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="F116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="F111:H111"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="I110:J110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="I109:J109"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="M109:N109"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="I106:J106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="F105:H105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:H104"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="M104:N104"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="M100:N100"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="M96:N96"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="M95:N95"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="M92:N92"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="M91:N91"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="F74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="F73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="M72:N72"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="M69:N69"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="M61:N61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:J8"/>
@@ -6743,736 +8235,28 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="M58:N58"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="M61:N61"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="F65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="M69:N69"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="M72:N72"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="M71:N71"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="F74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="M74:N74"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="F73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="M82:N82"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="M81:N81"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="M84:N84"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="M83:N83"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="M85:N85"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="M92:N92"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="M91:N91"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="M94:N94"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="M93:N93"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="M96:N96"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="M95:N95"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="M98:N98"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="M97:N97"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="M100:N100"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:H104"/>
-    <mergeCell ref="I104:J104"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="M104:N104"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="I106:J106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="M106:N106"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="F105:H105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="M105:N105"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="M108:N108"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="M107:N107"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="I110:J110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="M110:N110"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="I109:J109"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="M109:N109"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="F111:H111"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="M111:N111"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="M113:N113"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="I118:J118"/>
-    <mergeCell ref="K118:L118"/>
-    <mergeCell ref="M118:N118"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="M117:N117"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="I120:J120"/>
-    <mergeCell ref="K120:L120"/>
-    <mergeCell ref="M120:N120"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="I119:J119"/>
-    <mergeCell ref="K119:L119"/>
-    <mergeCell ref="M119:N119"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="M122:N122"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="I121:J121"/>
-    <mergeCell ref="K121:L121"/>
-    <mergeCell ref="M121:N121"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="I124:J124"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="M124:N124"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="I123:J123"/>
-    <mergeCell ref="K123:L123"/>
-    <mergeCell ref="M123:N123"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="M126:N126"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="K130:L130"/>
-    <mergeCell ref="M130:N130"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="M132:N132"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="M131:N131"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="M134:N134"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="M133:N133"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="M136:N136"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="M135:N135"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="M138:N138"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="M137:N137"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="F140:H140"/>
-    <mergeCell ref="I140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="M140:N140"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="F139:H139"/>
-    <mergeCell ref="I139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="M139:N139"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="I142:J142"/>
-    <mergeCell ref="K142:L142"/>
-    <mergeCell ref="M142:N142"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="I141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="M141:N141"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="F144:H144"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="M144:N144"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="F143:H143"/>
-    <mergeCell ref="I143:J143"/>
-    <mergeCell ref="K143:L143"/>
-    <mergeCell ref="M143:N143"/>
-    <mergeCell ref="C146:D146"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="I146:J146"/>
-    <mergeCell ref="K146:L146"/>
-    <mergeCell ref="M146:N146"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="M145:N145"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="I148:J148"/>
-    <mergeCell ref="K148:L148"/>
-    <mergeCell ref="M148:N148"/>
-    <mergeCell ref="C147:D147"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="I147:J147"/>
-    <mergeCell ref="K147:L147"/>
-    <mergeCell ref="M147:N147"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="I150:J150"/>
-    <mergeCell ref="K150:L150"/>
-    <mergeCell ref="M150:N150"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="I149:J149"/>
-    <mergeCell ref="K149:L149"/>
-    <mergeCell ref="M149:N149"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="F152:H152"/>
-    <mergeCell ref="I152:J152"/>
-    <mergeCell ref="K152:L152"/>
-    <mergeCell ref="M152:N152"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="I151:J151"/>
-    <mergeCell ref="K151:L151"/>
-    <mergeCell ref="M151:N151"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="H154:I154"/>
-    <mergeCell ref="J154:K154"/>
-    <mergeCell ref="L154:M154"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="H153:I153"/>
-    <mergeCell ref="J153:K153"/>
-    <mergeCell ref="L153:M153"/>
-    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12432"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14940" windowHeight="8292"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="347">
   <si>
     <t/>
   </si>
@@ -995,12 +995,6 @@
     <t>100 California, #1100  San Francisco CA 94111</t>
   </si>
   <si>
-    <t>Amobee</t>
-  </si>
-  <si>
-    <t>1000 Redwood Shores Pkwy, Third Floor  Redwood City CA 94065</t>
-  </si>
-  <si>
     <t>Onsemi</t>
   </si>
   <si>
@@ -1026,6 +1020,54 @@
   </si>
   <si>
     <t>1 Harrison St.  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>200 W. Pontiac Way, Bldg 5  Clovis CA 93612</t>
+  </si>
+  <si>
+    <t>Kitty Hawk Corporation Location 1</t>
+  </si>
+  <si>
+    <t>821 San Antonio Road  Palo Alto CA 94303</t>
+  </si>
+  <si>
+    <t>Kitty Hawk Corporation Location 2</t>
+  </si>
+  <si>
+    <t>4062 Fabian Way  Palo Alto CA 94303</t>
+  </si>
+  <si>
+    <t>Kitty Hawk Corporation Location 3</t>
+  </si>
+  <si>
+    <t>2639 A/B Terminal Blvd.  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Kitty Hawk Corporation Location 4</t>
+  </si>
+  <si>
+    <t>1201 San Antonio Blvd.  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Summit Funding Inc.</t>
+  </si>
+  <si>
+    <t>3900 Lennane Drive Suite 210  Sacramento CA 95834</t>
+  </si>
+  <si>
+    <t>WeDriveU, Inc.</t>
+  </si>
+  <si>
+    <t>8130 Enterprise Drive  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>Nutrition Corp, Inc. dba Fresh &amp;lsquo;N Lean</t>
+  </si>
+  <si>
+    <t>333 N. Euclid Way  Anaheim CA 92801</t>
+  </si>
+  <si>
+    <t>990 Hamilton Court  Menlo Park CA 94025</t>
   </si>
   <si>
     <t xml:space="preserve"> Employees Affected</t>
@@ -1057,11 +1099,11 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 9/21/2022
+ End Date: 9/26/2022
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Report Summary </t>
+    <t>Report Summary</t>
   </si>
 </sst>
 </file>
@@ -1129,6 +1171,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFDCDCDC"/>
       </patternFill>
@@ -1143,12 +1191,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FFDCDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1471,7 +1513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -1485,10 +1527,6 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1499,22 +1537,23 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1522,36 +1561,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1586,6 +1595,36 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1601,19 +1640,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1896,129 +1935,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R198"/>
+  <dimension ref="A1:R202"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="3" max="3" width="2.5546875" customWidth="1"/>
     <col min="4" max="4" width="6.44140625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="9" width="6.88671875" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
-    <col min="11" max="11" width="5" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="5.109375" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" customWidth="1"/>
+    <col min="13" max="13" width="7.5546875" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="39.75" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="A1" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+    </row>
+    <row r="2" spans="1:18" ht="37.5" customHeight="1">
+      <c r="A2" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="35"/>
+      <c r="E3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="24" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="25"/>
-      <c r="K3" s="24" t="s">
+      <c r="J3" s="35"/>
+      <c r="K3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="25"/>
-      <c r="M3" s="27" t="s">
+      <c r="L3" s="35"/>
+      <c r="M3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="28"/>
+      <c r="N3" s="38"/>
     </row>
     <row r="4" spans="1:18" ht="24.6">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="19" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="19" t="s">
+      <c r="J4" s="30"/>
+      <c r="K4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="22" t="s">
+      <c r="L4" s="30"/>
+      <c r="M4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="23"/>
+      <c r="N4" s="33"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -2027,30 +2067,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="25">
         <v>44750</v>
       </c>
-      <c r="D5" s="30"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="37" t="s">
+      <c r="G5" s="21"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="38">
+      <c r="J5" s="19"/>
+      <c r="K5" s="27">
         <v>2</v>
       </c>
-      <c r="L5" s="30"/>
-      <c r="M5" s="39" t="s">
+      <c r="L5" s="19"/>
+      <c r="M5" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="35"/>
+      <c r="N5" s="24"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -2059,30 +2099,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="18">
         <v>44750</v>
       </c>
-      <c r="D6" s="30"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31" t="s">
+      <c r="G6" s="21"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="33">
+      <c r="J6" s="19"/>
+      <c r="K6" s="22">
         <v>13</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="34" t="s">
+      <c r="L6" s="19"/>
+      <c r="M6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="35"/>
+      <c r="N6" s="24"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -2091,30 +2131,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="25">
         <v>44750</v>
       </c>
-      <c r="D7" s="30"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="30"/>
-      <c r="K7" s="38">
+      <c r="G7" s="21"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="27">
         <v>9</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="39" t="s">
+      <c r="L7" s="19"/>
+      <c r="M7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="35"/>
+      <c r="N7" s="24"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -2123,30 +2163,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="18">
         <v>44750</v>
       </c>
-      <c r="D8" s="30"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="30"/>
-      <c r="K8" s="33">
+      <c r="G8" s="21"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="22">
         <v>123</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="34" t="s">
+      <c r="L8" s="19"/>
+      <c r="M8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="35"/>
+      <c r="N8" s="24"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -2155,30 +2195,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="25">
         <v>44750</v>
       </c>
-      <c r="D9" s="30"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="38">
+      <c r="G9" s="21"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="27">
         <v>37</v>
       </c>
-      <c r="L9" s="30"/>
-      <c r="M9" s="39" t="s">
+      <c r="L9" s="19"/>
+      <c r="M9" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="35"/>
+      <c r="N9" s="24"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -2187,30 +2227,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="18">
         <v>44753</v>
       </c>
-      <c r="D10" s="30"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="33">
+      <c r="G10" s="21"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="19"/>
+      <c r="K10" s="22">
         <v>37</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="34" t="s">
+      <c r="L10" s="19"/>
+      <c r="M10" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="35"/>
+      <c r="N10" s="24"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2219,30 +2259,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="25">
         <v>44753</v>
       </c>
-      <c r="D11" s="30"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="30"/>
-      <c r="K11" s="38">
+      <c r="G11" s="21"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="27">
         <v>80</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="39" t="s">
+      <c r="L11" s="19"/>
+      <c r="M11" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="35"/>
+      <c r="N11" s="24"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2251,30 +2291,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="18">
         <v>44753</v>
       </c>
-      <c r="D12" s="30"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31" t="s">
+      <c r="G12" s="21"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="30"/>
-      <c r="K12" s="33">
+      <c r="J12" s="19"/>
+      <c r="K12" s="22">
         <v>229</v>
       </c>
-      <c r="L12" s="30"/>
-      <c r="M12" s="34" t="s">
+      <c r="L12" s="19"/>
+      <c r="M12" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="35"/>
+      <c r="N12" s="24"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2283,30 +2323,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="25">
         <v>44753</v>
       </c>
-      <c r="D13" s="30"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="38">
+      <c r="G13" s="21"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="K13" s="27">
         <v>368</v>
       </c>
-      <c r="L13" s="30"/>
-      <c r="M13" s="39" t="s">
+      <c r="L13" s="19"/>
+      <c r="M13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="35"/>
+      <c r="N13" s="24"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2315,30 +2355,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="18">
         <v>44753</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="30"/>
-      <c r="K14" s="33">
+      <c r="G14" s="21"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="19"/>
+      <c r="K14" s="22">
         <v>62</v>
       </c>
-      <c r="L14" s="30"/>
-      <c r="M14" s="34" t="s">
+      <c r="L14" s="19"/>
+      <c r="M14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="35"/>
+      <c r="N14" s="24"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2347,30 +2387,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="25">
         <v>44753</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="38">
+      <c r="G15" s="21"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="27">
         <v>25</v>
       </c>
-      <c r="L15" s="30"/>
-      <c r="M15" s="39" t="s">
+      <c r="L15" s="19"/>
+      <c r="M15" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="35"/>
+      <c r="N15" s="24"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2379,30 +2419,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="18">
         <v>44753</v>
       </c>
-      <c r="D16" s="30"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="33">
+      <c r="G16" s="21"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="19"/>
+      <c r="K16" s="22">
         <v>68</v>
       </c>
-      <c r="L16" s="30"/>
-      <c r="M16" s="34" t="s">
+      <c r="L16" s="19"/>
+      <c r="M16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="35"/>
+      <c r="N16" s="24"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2411,30 +2451,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="25">
         <v>44753</v>
       </c>
-      <c r="D17" s="30"/>
+      <c r="D17" s="19"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="38">
+      <c r="G17" s="21"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="19"/>
+      <c r="K17" s="27">
         <v>77</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="39" t="s">
+      <c r="L17" s="19"/>
+      <c r="M17" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="35"/>
+      <c r="N17" s="24"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2443,30 +2483,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="18">
         <v>44754</v>
       </c>
-      <c r="D18" s="30"/>
+      <c r="D18" s="19"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="33">
+      <c r="G18" s="21"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="22">
         <v>20</v>
       </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="34" t="s">
+      <c r="L18" s="19"/>
+      <c r="M18" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="35"/>
+      <c r="N18" s="24"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2475,30 +2515,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="25">
         <v>44754</v>
       </c>
-      <c r="D19" s="30"/>
+      <c r="D19" s="19"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="38">
+      <c r="G19" s="21"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="27">
         <v>5</v>
       </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="39" t="s">
+      <c r="L19" s="19"/>
+      <c r="M19" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="35"/>
+      <c r="N19" s="24"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2507,30 +2547,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="18">
         <v>44754</v>
       </c>
-      <c r="D20" s="30"/>
+      <c r="D20" s="19"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="30"/>
-      <c r="K20" s="33">
+      <c r="G20" s="21"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="22">
         <v>2</v>
       </c>
-      <c r="L20" s="30"/>
-      <c r="M20" s="34" t="s">
+      <c r="L20" s="19"/>
+      <c r="M20" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="35"/>
+      <c r="N20" s="24"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2539,30 +2579,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="25">
         <v>44754</v>
       </c>
-      <c r="D21" s="30"/>
+      <c r="D21" s="19"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="30"/>
-      <c r="K21" s="38">
+      <c r="G21" s="21"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="27">
         <v>1</v>
       </c>
-      <c r="L21" s="30"/>
-      <c r="M21" s="39" t="s">
+      <c r="L21" s="19"/>
+      <c r="M21" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="35"/>
+      <c r="N21" s="24"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2571,30 +2611,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="18">
         <v>44754</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="19"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="30"/>
-      <c r="K22" s="33">
+      <c r="G22" s="21"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="K22" s="22">
         <v>41</v>
       </c>
-      <c r="L22" s="30"/>
-      <c r="M22" s="34" t="s">
+      <c r="L22" s="19"/>
+      <c r="M22" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="35"/>
+      <c r="N22" s="24"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2603,30 +2643,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="25">
         <v>44754</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="19"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="32"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="37" t="s">
+      <c r="G23" s="21"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="30"/>
-      <c r="K23" s="38">
+      <c r="J23" s="19"/>
+      <c r="K23" s="27">
         <v>4</v>
       </c>
-      <c r="L23" s="30"/>
-      <c r="M23" s="39" t="s">
+      <c r="L23" s="19"/>
+      <c r="M23" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="35"/>
+      <c r="N23" s="24"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2635,30 +2675,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="18">
         <v>44754</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="19"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="30"/>
-      <c r="K24" s="33">
+      <c r="G24" s="21"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="22">
         <v>211</v>
       </c>
-      <c r="L24" s="30"/>
-      <c r="M24" s="34" t="s">
+      <c r="L24" s="19"/>
+      <c r="M24" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="35"/>
+      <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2667,30 +2707,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="25">
         <v>44754</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="19"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="37" t="s">
+      <c r="G25" s="21"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="30"/>
-      <c r="K25" s="38">
+      <c r="J25" s="19"/>
+      <c r="K25" s="27">
         <v>10</v>
       </c>
-      <c r="L25" s="30"/>
-      <c r="M25" s="39" t="s">
+      <c r="L25" s="19"/>
+      <c r="M25" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="35"/>
+      <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2699,30 +2739,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="18">
         <v>44754</v>
       </c>
-      <c r="D26" s="30"/>
+      <c r="D26" s="19"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="31" t="s">
+      <c r="G26" s="21"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="30"/>
-      <c r="K26" s="33">
+      <c r="J26" s="19"/>
+      <c r="K26" s="22">
         <v>1</v>
       </c>
-      <c r="L26" s="30"/>
-      <c r="M26" s="34" t="s">
+      <c r="L26" s="19"/>
+      <c r="M26" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="35"/>
+      <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2731,30 +2771,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="36">
+      <c r="C27" s="25">
         <v>44754</v>
       </c>
-      <c r="D27" s="30"/>
+      <c r="D27" s="19"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="32"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="30"/>
-      <c r="K27" s="38">
+      <c r="G27" s="21"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="19"/>
+      <c r="K27" s="27">
         <v>94</v>
       </c>
-      <c r="L27" s="30"/>
-      <c r="M27" s="39" t="s">
+      <c r="L27" s="19"/>
+      <c r="M27" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="35"/>
+      <c r="N27" s="24"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2763,30 +2803,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="18">
         <v>44754</v>
       </c>
-      <c r="D28" s="30"/>
+      <c r="D28" s="19"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="31" t="s">
+      <c r="G28" s="21"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="30"/>
-      <c r="K28" s="33">
+      <c r="J28" s="19"/>
+      <c r="K28" s="22">
         <v>9</v>
       </c>
-      <c r="L28" s="30"/>
-      <c r="M28" s="34" t="s">
+      <c r="L28" s="19"/>
+      <c r="M28" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="35"/>
+      <c r="N28" s="24"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2795,30 +2835,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="36">
+      <c r="C29" s="25">
         <v>44754</v>
       </c>
-      <c r="D29" s="30"/>
+      <c r="D29" s="19"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="32"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="37" t="s">
+      <c r="G29" s="21"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="30"/>
-      <c r="K29" s="38">
+      <c r="J29" s="19"/>
+      <c r="K29" s="27">
         <v>6</v>
       </c>
-      <c r="L29" s="30"/>
-      <c r="M29" s="39" t="s">
+      <c r="L29" s="19"/>
+      <c r="M29" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="35"/>
+      <c r="N29" s="24"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2827,30 +2867,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="18">
         <v>44754</v>
       </c>
-      <c r="D30" s="30"/>
+      <c r="D30" s="19"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="31" t="s">
+      <c r="G30" s="21"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="30"/>
-      <c r="K30" s="33">
-        <v>18</v>
-      </c>
-      <c r="L30" s="30"/>
-      <c r="M30" s="34" t="s">
+      <c r="J30" s="19"/>
+      <c r="K30" s="22">
+        <v>18</v>
+      </c>
+      <c r="L30" s="19"/>
+      <c r="M30" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="35"/>
+      <c r="N30" s="24"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2859,30 +2899,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="25">
         <v>44755</v>
       </c>
-      <c r="D31" s="30"/>
+      <c r="D31" s="19"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="32"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="37" t="s">
+      <c r="G31" s="21"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="30"/>
-      <c r="K31" s="38">
+      <c r="J31" s="19"/>
+      <c r="K31" s="27">
         <v>76</v>
       </c>
-      <c r="L31" s="30"/>
-      <c r="M31" s="39" t="s">
+      <c r="L31" s="19"/>
+      <c r="M31" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="35"/>
+      <c r="N31" s="24"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -2891,30 +2931,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="18">
         <v>44755</v>
       </c>
-      <c r="D32" s="30"/>
+      <c r="D32" s="19"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="31" t="s">
+      <c r="F32" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="31" t="s">
+      <c r="G32" s="21"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="30"/>
-      <c r="K32" s="33">
+      <c r="J32" s="19"/>
+      <c r="K32" s="22">
         <v>1</v>
       </c>
-      <c r="L32" s="30"/>
-      <c r="M32" s="34" t="s">
+      <c r="L32" s="19"/>
+      <c r="M32" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="35"/>
+      <c r="N32" s="24"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -2923,30 +2963,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="25">
         <v>44755</v>
       </c>
-      <c r="D33" s="30"/>
+      <c r="D33" s="19"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="37" t="s">
+      <c r="G33" s="21"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="30"/>
-      <c r="K33" s="38">
+      <c r="J33" s="19"/>
+      <c r="K33" s="27">
         <v>27</v>
       </c>
-      <c r="L33" s="30"/>
-      <c r="M33" s="39" t="s">
+      <c r="L33" s="19"/>
+      <c r="M33" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="35"/>
+      <c r="N33" s="24"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -2955,30 +2995,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="18">
         <v>44755</v>
       </c>
-      <c r="D34" s="30"/>
+      <c r="D34" s="19"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="31" t="s">
+      <c r="G34" s="21"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="30"/>
-      <c r="K34" s="33">
+      <c r="J34" s="19"/>
+      <c r="K34" s="22">
         <v>2</v>
       </c>
-      <c r="L34" s="30"/>
-      <c r="M34" s="34" t="s">
+      <c r="L34" s="19"/>
+      <c r="M34" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="35"/>
+      <c r="N34" s="24"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -2987,30 +3027,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="25">
         <v>44756</v>
       </c>
-      <c r="D35" s="30"/>
+      <c r="D35" s="19"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="32"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="30"/>
-      <c r="K35" s="38">
+      <c r="G35" s="21"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="19"/>
+      <c r="K35" s="27">
         <v>54</v>
       </c>
-      <c r="L35" s="30"/>
-      <c r="M35" s="39" t="s">
+      <c r="L35" s="19"/>
+      <c r="M35" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="35"/>
+      <c r="N35" s="24"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -3019,30 +3059,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="18">
         <v>44756</v>
       </c>
-      <c r="D36" s="30"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="30"/>
-      <c r="K36" s="33">
+      <c r="G36" s="21"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="19"/>
+      <c r="K36" s="22">
         <v>105</v>
       </c>
-      <c r="L36" s="30"/>
-      <c r="M36" s="34" t="s">
+      <c r="L36" s="19"/>
+      <c r="M36" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="35"/>
+      <c r="N36" s="24"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -3051,30 +3091,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="25">
         <v>44756</v>
       </c>
-      <c r="D37" s="30"/>
+      <c r="D37" s="19"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="32"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="30"/>
-      <c r="K37" s="38">
+      <c r="G37" s="21"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="19"/>
+      <c r="K37" s="27">
         <v>71</v>
       </c>
-      <c r="L37" s="30"/>
-      <c r="M37" s="39" t="s">
+      <c r="L37" s="19"/>
+      <c r="M37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="35"/>
+      <c r="N37" s="24"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -3083,30 +3123,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="18">
         <v>44756</v>
       </c>
-      <c r="D38" s="30"/>
+      <c r="D38" s="19"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="32"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="30"/>
-      <c r="K38" s="33">
+      <c r="G38" s="21"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="19"/>
+      <c r="K38" s="22">
         <v>125</v>
       </c>
-      <c r="L38" s="30"/>
-      <c r="M38" s="34" t="s">
+      <c r="L38" s="19"/>
+      <c r="M38" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="35"/>
+      <c r="N38" s="24"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -3115,30 +3155,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="25">
         <v>44756</v>
       </c>
-      <c r="D39" s="30"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="32"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="30"/>
-      <c r="K39" s="38">
+      <c r="G39" s="21"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="19"/>
+      <c r="K39" s="27">
         <v>55</v>
       </c>
-      <c r="L39" s="30"/>
-      <c r="M39" s="39" t="s">
+      <c r="L39" s="19"/>
+      <c r="M39" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="35"/>
+      <c r="N39" s="24"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -3147,30 +3187,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="18">
         <v>44756</v>
       </c>
-      <c r="D40" s="30"/>
+      <c r="D40" s="19"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="32"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="30"/>
-      <c r="K40" s="33">
+      <c r="G40" s="21"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="19"/>
+      <c r="K40" s="22">
         <v>176</v>
       </c>
-      <c r="L40" s="30"/>
-      <c r="M40" s="34" t="s">
+      <c r="L40" s="19"/>
+      <c r="M40" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="35"/>
+      <c r="N40" s="24"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -3179,30 +3219,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="25">
         <v>44757</v>
       </c>
-      <c r="D41" s="30"/>
+      <c r="D41" s="19"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="30"/>
-      <c r="K41" s="38">
+      <c r="G41" s="21"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="19"/>
+      <c r="K41" s="27">
         <v>58</v>
       </c>
-      <c r="L41" s="30"/>
-      <c r="M41" s="39" t="s">
+      <c r="L41" s="19"/>
+      <c r="M41" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="35"/>
+      <c r="N41" s="24"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3211,30 +3251,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="18">
         <v>44757</v>
       </c>
-      <c r="D42" s="30"/>
+      <c r="D42" s="19"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="31" t="s">
+      <c r="F42" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="32"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="30"/>
-      <c r="K42" s="33">
+      <c r="G42" s="21"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="19"/>
+      <c r="K42" s="22">
         <v>180</v>
       </c>
-      <c r="L42" s="30"/>
-      <c r="M42" s="34" t="s">
+      <c r="L42" s="19"/>
+      <c r="M42" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="35"/>
+      <c r="N42" s="24"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3243,30 +3283,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="25">
         <v>44760</v>
       </c>
-      <c r="D43" s="30"/>
+      <c r="D43" s="19"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="32"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="37" t="s">
+      <c r="G43" s="21"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="30"/>
-      <c r="K43" s="38">
+      <c r="J43" s="19"/>
+      <c r="K43" s="27">
         <v>142</v>
       </c>
-      <c r="L43" s="30"/>
-      <c r="M43" s="39" t="s">
+      <c r="L43" s="19"/>
+      <c r="M43" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="35"/>
+      <c r="N43" s="24"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3275,30 +3315,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="18">
         <v>44760</v>
       </c>
-      <c r="D44" s="30"/>
+      <c r="D44" s="19"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F44" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="31" t="s">
+      <c r="G44" s="21"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="30"/>
-      <c r="K44" s="33">
+      <c r="J44" s="19"/>
+      <c r="K44" s="22">
         <v>153</v>
       </c>
-      <c r="L44" s="30"/>
-      <c r="M44" s="34" t="s">
+      <c r="L44" s="19"/>
+      <c r="M44" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="35"/>
+      <c r="N44" s="24"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3307,30 +3347,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="25">
         <v>44761</v>
       </c>
-      <c r="D45" s="30"/>
+      <c r="D45" s="19"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F45" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="30"/>
-      <c r="K45" s="38">
+      <c r="G45" s="21"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="19"/>
+      <c r="K45" s="27">
         <v>12</v>
       </c>
-      <c r="L45" s="30"/>
-      <c r="M45" s="39" t="s">
+      <c r="L45" s="19"/>
+      <c r="M45" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="35"/>
+      <c r="N45" s="24"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3339,30 +3379,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="18">
         <v>44761</v>
       </c>
-      <c r="D46" s="30"/>
+      <c r="D46" s="19"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="30"/>
-      <c r="K46" s="33">
+      <c r="G46" s="21"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="19"/>
+      <c r="K46" s="22">
         <v>27</v>
       </c>
-      <c r="L46" s="30"/>
-      <c r="M46" s="34" t="s">
+      <c r="L46" s="19"/>
+      <c r="M46" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="35"/>
+      <c r="N46" s="24"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3371,30 +3411,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="25">
         <v>44761</v>
       </c>
-      <c r="D47" s="30"/>
+      <c r="D47" s="19"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="37" t="s">
+      <c r="F47" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="30"/>
-      <c r="K47" s="38">
+      <c r="G47" s="21"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="19"/>
+      <c r="K47" s="27">
         <v>51</v>
       </c>
-      <c r="L47" s="30"/>
-      <c r="M47" s="39" t="s">
+      <c r="L47" s="19"/>
+      <c r="M47" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="35"/>
+      <c r="N47" s="24"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3403,30 +3443,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="18">
         <v>44761</v>
       </c>
-      <c r="D48" s="30"/>
+      <c r="D48" s="19"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="31" t="s">
+      <c r="F48" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="32"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="30"/>
-      <c r="K48" s="33">
+      <c r="G48" s="21"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="19"/>
+      <c r="K48" s="22">
         <v>69</v>
       </c>
-      <c r="L48" s="30"/>
-      <c r="M48" s="34" t="s">
+      <c r="L48" s="19"/>
+      <c r="M48" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="35"/>
+      <c r="N48" s="24"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3435,30 +3475,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="25">
         <v>44762</v>
       </c>
-      <c r="D49" s="30"/>
+      <c r="D49" s="19"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="32"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="37" t="s">
+      <c r="G49" s="21"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="30"/>
-      <c r="K49" s="38">
+      <c r="J49" s="19"/>
+      <c r="K49" s="27">
         <v>104</v>
       </c>
-      <c r="L49" s="30"/>
-      <c r="M49" s="39" t="s">
+      <c r="L49" s="19"/>
+      <c r="M49" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="35"/>
+      <c r="N49" s="24"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3467,30 +3507,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="18">
         <v>44762</v>
       </c>
-      <c r="D50" s="30"/>
+      <c r="D50" s="19"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="30"/>
-      <c r="K50" s="33">
+      <c r="G50" s="21"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="19"/>
+      <c r="K50" s="22">
         <v>19</v>
       </c>
-      <c r="L50" s="30"/>
-      <c r="M50" s="34" t="s">
+      <c r="L50" s="19"/>
+      <c r="M50" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="35"/>
+      <c r="N50" s="24"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3499,30 +3539,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="25">
         <v>44762</v>
       </c>
-      <c r="D51" s="30"/>
+      <c r="D51" s="19"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="F51" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="32"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="37" t="s">
+      <c r="G51" s="21"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="30"/>
-      <c r="K51" s="38">
+      <c r="J51" s="19"/>
+      <c r="K51" s="27">
         <v>80</v>
       </c>
-      <c r="L51" s="30"/>
-      <c r="M51" s="39" t="s">
+      <c r="L51" s="19"/>
+      <c r="M51" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="35"/>
+      <c r="N51" s="24"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3531,30 +3571,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="18">
         <v>44763</v>
       </c>
-      <c r="D52" s="30"/>
+      <c r="D52" s="19"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="31" t="s">
+      <c r="F52" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="32"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="30"/>
-      <c r="K52" s="33">
+      <c r="G52" s="21"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="19"/>
+      <c r="K52" s="22">
         <v>99</v>
       </c>
-      <c r="L52" s="30"/>
-      <c r="M52" s="34" t="s">
+      <c r="L52" s="19"/>
+      <c r="M52" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="35"/>
+      <c r="N52" s="24"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3563,30 +3603,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="25">
         <v>44763</v>
       </c>
-      <c r="D53" s="30"/>
+      <c r="D53" s="19"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="37" t="s">
+      <c r="F53" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="30"/>
-      <c r="K53" s="38">
+      <c r="G53" s="21"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="19"/>
+      <c r="K53" s="27">
         <v>60</v>
       </c>
-      <c r="L53" s="30"/>
-      <c r="M53" s="39" t="s">
+      <c r="L53" s="19"/>
+      <c r="M53" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="35"/>
+      <c r="N53" s="24"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3595,30 +3635,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="18">
         <v>44763</v>
       </c>
-      <c r="D54" s="30"/>
+      <c r="D54" s="19"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="32"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="30"/>
-      <c r="K54" s="33">
+      <c r="G54" s="21"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="19"/>
+      <c r="K54" s="22">
         <v>4</v>
       </c>
-      <c r="L54" s="30"/>
-      <c r="M54" s="34" t="s">
+      <c r="L54" s="19"/>
+      <c r="M54" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="35"/>
+      <c r="N54" s="24"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3627,30 +3667,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="25">
         <v>44763</v>
       </c>
-      <c r="D55" s="30"/>
+      <c r="D55" s="19"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="37" t="s">
+      <c r="F55" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="30"/>
-      <c r="K55" s="38">
+      <c r="G55" s="21"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="19"/>
+      <c r="K55" s="27">
         <v>26</v>
       </c>
-      <c r="L55" s="30"/>
-      <c r="M55" s="39" t="s">
+      <c r="L55" s="19"/>
+      <c r="M55" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="35"/>
+      <c r="N55" s="24"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3659,30 +3699,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="18">
         <v>44763</v>
       </c>
-      <c r="D56" s="30"/>
+      <c r="D56" s="19"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="31" t="s">
+      <c r="F56" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="32"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="30"/>
-      <c r="K56" s="33">
+      <c r="G56" s="21"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="19"/>
+      <c r="K56" s="22">
         <v>30</v>
       </c>
-      <c r="L56" s="30"/>
-      <c r="M56" s="34" t="s">
+      <c r="L56" s="19"/>
+      <c r="M56" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="35"/>
+      <c r="N56" s="24"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3691,30 +3731,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="25">
         <v>44763</v>
       </c>
-      <c r="D57" s="30"/>
+      <c r="D57" s="19"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="F57" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="32"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="30"/>
-      <c r="K57" s="38">
+      <c r="G57" s="21"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="19"/>
+      <c r="K57" s="27">
         <v>2</v>
       </c>
-      <c r="L57" s="30"/>
-      <c r="M57" s="39" t="s">
+      <c r="L57" s="19"/>
+      <c r="M57" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="35"/>
+      <c r="N57" s="24"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3723,30 +3763,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="18">
         <v>44764</v>
       </c>
-      <c r="D58" s="30"/>
+      <c r="D58" s="19"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="31" t="s">
+      <c r="F58" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="32"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="31" t="s">
+      <c r="G58" s="21"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="30"/>
-      <c r="K58" s="33">
+      <c r="J58" s="19"/>
+      <c r="K58" s="22">
         <v>66</v>
       </c>
-      <c r="L58" s="30"/>
-      <c r="M58" s="34" t="s">
+      <c r="L58" s="19"/>
+      <c r="M58" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="35"/>
+      <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3755,30 +3795,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="25">
         <v>44764</v>
       </c>
-      <c r="D59" s="30"/>
+      <c r="D59" s="19"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="F59" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="32"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="37" t="s">
+      <c r="G59" s="21"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="30"/>
-      <c r="K59" s="38">
+      <c r="J59" s="19"/>
+      <c r="K59" s="27">
         <v>85</v>
       </c>
-      <c r="L59" s="30"/>
-      <c r="M59" s="39" t="s">
+      <c r="L59" s="19"/>
+      <c r="M59" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="35"/>
+      <c r="N59" s="24"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3787,30 +3827,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="18">
         <v>44764</v>
       </c>
-      <c r="D60" s="30"/>
+      <c r="D60" s="19"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="31" t="s">
+      <c r="F60" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="32"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="30"/>
-      <c r="K60" s="33">
+      <c r="G60" s="21"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="19"/>
+      <c r="K60" s="22">
         <v>58</v>
       </c>
-      <c r="L60" s="30"/>
-      <c r="M60" s="34" t="s">
+      <c r="L60" s="19"/>
+      <c r="M60" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="35"/>
+      <c r="N60" s="24"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3819,30 +3859,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="36">
+      <c r="C61" s="25">
         <v>44764</v>
       </c>
-      <c r="D61" s="30"/>
+      <c r="D61" s="19"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="F61" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="32"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="30"/>
-      <c r="K61" s="38">
+      <c r="G61" s="21"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="19"/>
+      <c r="K61" s="27">
         <v>80</v>
       </c>
-      <c r="L61" s="30"/>
-      <c r="M61" s="39" t="s">
+      <c r="L61" s="19"/>
+      <c r="M61" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="35"/>
+      <c r="N61" s="24"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3851,30 +3891,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="18">
         <v>44764</v>
       </c>
-      <c r="D62" s="30"/>
+      <c r="D62" s="19"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="31" t="s">
+      <c r="F62" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="32"/>
-      <c r="H62" s="30"/>
-      <c r="I62" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="30"/>
-      <c r="K62" s="33">
+      <c r="G62" s="21"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="19"/>
+      <c r="K62" s="22">
         <v>55</v>
       </c>
-      <c r="L62" s="30"/>
-      <c r="M62" s="34" t="s">
+      <c r="L62" s="19"/>
+      <c r="M62" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="35"/>
+      <c r="N62" s="24"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -3883,30 +3923,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="36">
+      <c r="C63" s="25">
         <v>44764</v>
       </c>
-      <c r="D63" s="30"/>
+      <c r="D63" s="19"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="37" t="s">
+      <c r="F63" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="32"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="37" t="s">
+      <c r="G63" s="21"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="30"/>
-      <c r="K63" s="38">
+      <c r="J63" s="19"/>
+      <c r="K63" s="27">
         <v>14</v>
       </c>
-      <c r="L63" s="30"/>
-      <c r="M63" s="39" t="s">
+      <c r="L63" s="19"/>
+      <c r="M63" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="35"/>
+      <c r="N63" s="24"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -3915,30 +3955,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="18">
         <v>44764</v>
       </c>
-      <c r="D64" s="30"/>
+      <c r="D64" s="19"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="31" t="s">
+      <c r="F64" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="32"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="31" t="s">
+      <c r="G64" s="21"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="30"/>
-      <c r="K64" s="33">
+      <c r="J64" s="19"/>
+      <c r="K64" s="22">
         <v>90</v>
       </c>
-      <c r="L64" s="30"/>
-      <c r="M64" s="34" t="s">
+      <c r="L64" s="19"/>
+      <c r="M64" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="35"/>
+      <c r="N64" s="24"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -3947,30 +3987,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="25">
         <v>44767</v>
       </c>
-      <c r="D65" s="30"/>
+      <c r="D65" s="19"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="37" t="s">
+      <c r="F65" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="37" t="s">
+      <c r="G65" s="21"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="30"/>
-      <c r="K65" s="38">
+      <c r="J65" s="19"/>
+      <c r="K65" s="27">
         <v>331</v>
       </c>
-      <c r="L65" s="30"/>
-      <c r="M65" s="39" t="s">
+      <c r="L65" s="19"/>
+      <c r="M65" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="35"/>
+      <c r="N65" s="24"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -3979,30 +4019,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="18">
         <v>44768</v>
       </c>
-      <c r="D66" s="30"/>
+      <c r="D66" s="19"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="31" t="s">
+      <c r="F66" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="32"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="30"/>
-      <c r="K66" s="33">
+      <c r="G66" s="21"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="19"/>
+      <c r="K66" s="22">
         <v>52</v>
       </c>
-      <c r="L66" s="30"/>
-      <c r="M66" s="34" t="s">
+      <c r="L66" s="19"/>
+      <c r="M66" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="35"/>
+      <c r="N66" s="24"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -4011,30 +4051,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="25">
         <v>44768</v>
       </c>
-      <c r="D67" s="30"/>
+      <c r="D67" s="19"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="F67" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="32"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="30"/>
-      <c r="K67" s="38">
+      <c r="G67" s="21"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="19"/>
+      <c r="K67" s="27">
         <v>9</v>
       </c>
-      <c r="L67" s="30"/>
-      <c r="M67" s="39" t="s">
+      <c r="L67" s="19"/>
+      <c r="M67" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="35"/>
+      <c r="N67" s="24"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -4043,30 +4083,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="18">
         <v>44768</v>
       </c>
-      <c r="D68" s="30"/>
+      <c r="D68" s="19"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="32"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="30"/>
-      <c r="K68" s="33">
+      <c r="G68" s="21"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="19"/>
+      <c r="K68" s="22">
         <v>78</v>
       </c>
-      <c r="L68" s="30"/>
-      <c r="M68" s="34" t="s">
+      <c r="L68" s="19"/>
+      <c r="M68" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="35"/>
+      <c r="N68" s="24"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -4075,30 +4115,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="25">
         <v>44769</v>
       </c>
-      <c r="D69" s="30"/>
+      <c r="D69" s="19"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="37" t="s">
+      <c r="F69" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="32"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="30"/>
-      <c r="K69" s="38">
+      <c r="G69" s="21"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="19"/>
+      <c r="K69" s="27">
         <v>48</v>
       </c>
-      <c r="L69" s="30"/>
-      <c r="M69" s="39" t="s">
+      <c r="L69" s="19"/>
+      <c r="M69" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="35"/>
+      <c r="N69" s="24"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -4107,30 +4147,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="18">
         <v>44769</v>
       </c>
-      <c r="D70" s="30"/>
+      <c r="D70" s="19"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="31" t="s">
+      <c r="F70" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="32"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="30"/>
-      <c r="K70" s="33">
+      <c r="G70" s="21"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="19"/>
+      <c r="K70" s="22">
         <v>50</v>
       </c>
-      <c r="L70" s="30"/>
-      <c r="M70" s="34" t="s">
+      <c r="L70" s="19"/>
+      <c r="M70" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="35"/>
+      <c r="N70" s="24"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -4139,30 +4179,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="36">
+      <c r="C71" s="25">
         <v>44769</v>
       </c>
-      <c r="D71" s="30"/>
+      <c r="D71" s="19"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="37" t="s">
+      <c r="F71" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="32"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="30"/>
-      <c r="K71" s="38">
+      <c r="G71" s="21"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="19"/>
+      <c r="K71" s="27">
         <v>736</v>
       </c>
-      <c r="L71" s="30"/>
-      <c r="M71" s="39" t="s">
+      <c r="L71" s="19"/>
+      <c r="M71" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="35"/>
+      <c r="N71" s="24"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -4171,30 +4211,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="18">
         <v>44770</v>
       </c>
-      <c r="D72" s="30"/>
+      <c r="D72" s="19"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="32"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="30"/>
-      <c r="K72" s="33">
+      <c r="G72" s="21"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="19"/>
+      <c r="K72" s="22">
         <v>74</v>
       </c>
-      <c r="L72" s="30"/>
-      <c r="M72" s="34" t="s">
+      <c r="L72" s="19"/>
+      <c r="M72" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="35"/>
+      <c r="N72" s="24"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4203,30 +4243,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="36">
+      <c r="C73" s="25">
         <v>44770</v>
       </c>
-      <c r="D73" s="30"/>
+      <c r="D73" s="19"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="37" t="s">
+      <c r="F73" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="32"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="30"/>
-      <c r="K73" s="38">
+      <c r="G73" s="21"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="19"/>
+      <c r="K73" s="27">
         <v>25</v>
       </c>
-      <c r="L73" s="30"/>
-      <c r="M73" s="39" t="s">
+      <c r="L73" s="19"/>
+      <c r="M73" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="35"/>
+      <c r="N73" s="24"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4235,30 +4275,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="18">
         <v>44770</v>
       </c>
-      <c r="D74" s="30"/>
+      <c r="D74" s="19"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="31" t="s">
+      <c r="F74" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="32"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="30"/>
-      <c r="K74" s="33">
+      <c r="G74" s="21"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="19"/>
+      <c r="K74" s="22">
         <v>25</v>
       </c>
-      <c r="L74" s="30"/>
-      <c r="M74" s="34" t="s">
+      <c r="L74" s="19"/>
+      <c r="M74" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="35"/>
+      <c r="N74" s="24"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4267,30 +4307,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="36">
+      <c r="C75" s="25">
         <v>44770</v>
       </c>
-      <c r="D75" s="30"/>
+      <c r="D75" s="19"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="37" t="s">
+      <c r="F75" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="32"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="37" t="s">
+      <c r="G75" s="21"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="30"/>
-      <c r="K75" s="38">
+      <c r="J75" s="19"/>
+      <c r="K75" s="27">
         <v>225</v>
       </c>
-      <c r="L75" s="30"/>
-      <c r="M75" s="39" t="s">
+      <c r="L75" s="19"/>
+      <c r="M75" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="35"/>
+      <c r="N75" s="24"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4299,30 +4339,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="18">
         <v>44770</v>
       </c>
-      <c r="D76" s="30"/>
+      <c r="D76" s="19"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="31" t="s">
+      <c r="F76" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="32"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="30"/>
-      <c r="K76" s="33">
+      <c r="G76" s="21"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="19"/>
+      <c r="K76" s="22">
         <v>136</v>
       </c>
-      <c r="L76" s="30"/>
-      <c r="M76" s="34" t="s">
+      <c r="L76" s="19"/>
+      <c r="M76" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="35"/>
+      <c r="N76" s="24"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4331,30 +4371,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="36">
+      <c r="C77" s="25">
         <v>44774</v>
       </c>
-      <c r="D77" s="30"/>
+      <c r="D77" s="19"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="37" t="s">
+      <c r="F77" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="32"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="37" t="s">
+      <c r="G77" s="21"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="30"/>
-      <c r="K77" s="38">
+      <c r="J77" s="19"/>
+      <c r="K77" s="27">
         <v>82</v>
       </c>
-      <c r="L77" s="30"/>
-      <c r="M77" s="39" t="s">
+      <c r="L77" s="19"/>
+      <c r="M77" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="35"/>
+      <c r="N77" s="24"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4363,30 +4403,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="18">
         <v>44774</v>
       </c>
-      <c r="D78" s="30"/>
+      <c r="D78" s="19"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="31" t="s">
+      <c r="F78" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="32"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="30"/>
-      <c r="K78" s="33">
+      <c r="G78" s="21"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="19"/>
+      <c r="K78" s="22">
         <v>28</v>
       </c>
-      <c r="L78" s="30"/>
-      <c r="M78" s="34" t="s">
+      <c r="L78" s="19"/>
+      <c r="M78" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="35"/>
+      <c r="N78" s="24"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4395,30 +4435,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="36">
+      <c r="C79" s="25">
         <v>44776</v>
       </c>
-      <c r="D79" s="30"/>
+      <c r="D79" s="19"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="37" t="s">
+      <c r="F79" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="32"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="30"/>
-      <c r="K79" s="38">
+      <c r="G79" s="21"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="19"/>
+      <c r="K79" s="27">
         <v>57</v>
       </c>
-      <c r="L79" s="30"/>
-      <c r="M79" s="39" t="s">
+      <c r="L79" s="19"/>
+      <c r="M79" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="35"/>
+      <c r="N79" s="24"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4427,30 +4467,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="18">
         <v>44778</v>
       </c>
-      <c r="D80" s="30"/>
+      <c r="D80" s="19"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="31" t="s">
+      <c r="F80" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="32"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="31" t="s">
+      <c r="G80" s="21"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="30"/>
-      <c r="K80" s="33">
+      <c r="J80" s="19"/>
+      <c r="K80" s="22">
         <v>133</v>
       </c>
-      <c r="L80" s="30"/>
-      <c r="M80" s="34" t="s">
+      <c r="L80" s="19"/>
+      <c r="M80" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="35"/>
+      <c r="N80" s="24"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4459,30 +4499,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="36">
+      <c r="C81" s="25">
         <v>44778</v>
       </c>
-      <c r="D81" s="30"/>
+      <c r="D81" s="19"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="37" t="s">
+      <c r="F81" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="32"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="30"/>
-      <c r="K81" s="38">
+      <c r="G81" s="21"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="19"/>
+      <c r="K81" s="27">
         <v>146</v>
       </c>
-      <c r="L81" s="30"/>
-      <c r="M81" s="39" t="s">
+      <c r="L81" s="19"/>
+      <c r="M81" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="35"/>
+      <c r="N81" s="24"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4491,30 +4531,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="18">
         <v>44778</v>
       </c>
-      <c r="D82" s="30"/>
+      <c r="D82" s="19"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="32"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="31" t="s">
+      <c r="G82" s="21"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="30"/>
-      <c r="K82" s="33">
+      <c r="J82" s="19"/>
+      <c r="K82" s="22">
         <v>68</v>
       </c>
-      <c r="L82" s="30"/>
-      <c r="M82" s="34" t="s">
+      <c r="L82" s="19"/>
+      <c r="M82" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="35"/>
+      <c r="N82" s="24"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4523,30 +4563,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="36">
+      <c r="C83" s="25">
         <v>44781</v>
       </c>
-      <c r="D83" s="30"/>
+      <c r="D83" s="19"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="37" t="s">
+      <c r="F83" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="32"/>
-      <c r="H83" s="30"/>
-      <c r="I83" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="30"/>
-      <c r="K83" s="38">
+      <c r="G83" s="21"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="19"/>
+      <c r="K83" s="27">
         <v>111</v>
       </c>
-      <c r="L83" s="30"/>
-      <c r="M83" s="39" t="s">
+      <c r="L83" s="19"/>
+      <c r="M83" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="35"/>
+      <c r="N83" s="24"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4555,30 +4595,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="18">
         <v>44781</v>
       </c>
-      <c r="D84" s="30"/>
+      <c r="D84" s="19"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="31" t="s">
+      <c r="F84" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="32"/>
-      <c r="H84" s="30"/>
-      <c r="I84" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="30"/>
-      <c r="K84" s="33">
+      <c r="G84" s="21"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="19"/>
+      <c r="K84" s="22">
         <v>77</v>
       </c>
-      <c r="L84" s="30"/>
-      <c r="M84" s="34" t="s">
+      <c r="L84" s="19"/>
+      <c r="M84" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="35"/>
+      <c r="N84" s="24"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4587,30 +4627,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="36">
+      <c r="C85" s="25">
         <v>44781</v>
       </c>
-      <c r="D85" s="30"/>
+      <c r="D85" s="19"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="37" t="s">
+      <c r="F85" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="32"/>
-      <c r="H85" s="30"/>
-      <c r="I85" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="30"/>
-      <c r="K85" s="38">
+      <c r="G85" s="21"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="19"/>
+      <c r="K85" s="27">
         <v>20</v>
       </c>
-      <c r="L85" s="30"/>
-      <c r="M85" s="39" t="s">
+      <c r="L85" s="19"/>
+      <c r="M85" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="35"/>
+      <c r="N85" s="24"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4619,30 +4659,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="18">
         <v>44781</v>
       </c>
-      <c r="D86" s="30"/>
+      <c r="D86" s="19"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="31" t="s">
+      <c r="F86" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="32"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="30"/>
-      <c r="K86" s="33">
+      <c r="G86" s="21"/>
+      <c r="H86" s="19"/>
+      <c r="I86" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="19"/>
+      <c r="K86" s="22">
         <v>25</v>
       </c>
-      <c r="L86" s="30"/>
-      <c r="M86" s="34" t="s">
+      <c r="L86" s="19"/>
+      <c r="M86" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="35"/>
+      <c r="N86" s="24"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4651,30 +4691,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="36">
+      <c r="C87" s="25">
         <v>44781</v>
       </c>
-      <c r="D87" s="30"/>
+      <c r="D87" s="19"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="37" t="s">
+      <c r="F87" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="32"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="30"/>
-      <c r="K87" s="38">
+      <c r="G87" s="21"/>
+      <c r="H87" s="19"/>
+      <c r="I87" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="19"/>
+      <c r="K87" s="27">
         <v>21</v>
       </c>
-      <c r="L87" s="30"/>
-      <c r="M87" s="39" t="s">
+      <c r="L87" s="19"/>
+      <c r="M87" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="35"/>
+      <c r="N87" s="24"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4683,30 +4723,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="18">
         <v>44781</v>
       </c>
-      <c r="D88" s="30"/>
+      <c r="D88" s="19"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="31" t="s">
+      <c r="F88" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="32"/>
-      <c r="H88" s="30"/>
-      <c r="I88" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="30"/>
-      <c r="K88" s="33">
+      <c r="G88" s="21"/>
+      <c r="H88" s="19"/>
+      <c r="I88" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="19"/>
+      <c r="K88" s="22">
         <v>86</v>
       </c>
-      <c r="L88" s="30"/>
-      <c r="M88" s="34" t="s">
+      <c r="L88" s="19"/>
+      <c r="M88" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="35"/>
+      <c r="N88" s="24"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4715,30 +4755,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="36">
+      <c r="C89" s="25">
         <v>44781</v>
       </c>
-      <c r="D89" s="30"/>
+      <c r="D89" s="19"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="37" t="s">
+      <c r="F89" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="32"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="30"/>
-      <c r="K89" s="38">
+      <c r="G89" s="21"/>
+      <c r="H89" s="19"/>
+      <c r="I89" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="19"/>
+      <c r="K89" s="27">
         <v>9</v>
       </c>
-      <c r="L89" s="30"/>
-      <c r="M89" s="39" t="s">
+      <c r="L89" s="19"/>
+      <c r="M89" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="35"/>
+      <c r="N89" s="24"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4747,30 +4787,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="18">
         <v>44781</v>
       </c>
-      <c r="D90" s="30"/>
+      <c r="D90" s="19"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="31" t="s">
+      <c r="F90" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="32"/>
-      <c r="H90" s="30"/>
-      <c r="I90" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="30"/>
-      <c r="K90" s="33">
+      <c r="G90" s="21"/>
+      <c r="H90" s="19"/>
+      <c r="I90" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="19"/>
+      <c r="K90" s="22">
         <v>2</v>
       </c>
-      <c r="L90" s="30"/>
-      <c r="M90" s="34" t="s">
+      <c r="L90" s="19"/>
+      <c r="M90" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="35"/>
+      <c r="N90" s="24"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4779,30 +4819,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="36">
+      <c r="C91" s="25">
         <v>44781</v>
       </c>
-      <c r="D91" s="30"/>
+      <c r="D91" s="19"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="37" t="s">
+      <c r="F91" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="32"/>
-      <c r="H91" s="30"/>
-      <c r="I91" s="37" t="s">
+      <c r="G91" s="21"/>
+      <c r="H91" s="19"/>
+      <c r="I91" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="30"/>
-      <c r="K91" s="38">
+      <c r="J91" s="19"/>
+      <c r="K91" s="27">
         <v>73</v>
       </c>
-      <c r="L91" s="30"/>
-      <c r="M91" s="39" t="s">
+      <c r="L91" s="19"/>
+      <c r="M91" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="35"/>
+      <c r="N91" s="24"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4811,30 +4851,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="18">
         <v>44782</v>
       </c>
-      <c r="D92" s="30"/>
+      <c r="D92" s="19"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="31" t="s">
+      <c r="F92" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="32"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="31" t="s">
+      <c r="G92" s="21"/>
+      <c r="H92" s="19"/>
+      <c r="I92" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="30"/>
-      <c r="K92" s="33">
+      <c r="J92" s="19"/>
+      <c r="K92" s="22">
         <v>33</v>
       </c>
-      <c r="L92" s="30"/>
-      <c r="M92" s="34" t="s">
+      <c r="L92" s="19"/>
+      <c r="M92" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="35"/>
+      <c r="N92" s="24"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4843,30 +4883,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="36">
+      <c r="C93" s="25">
         <v>44782</v>
       </c>
-      <c r="D93" s="30"/>
+      <c r="D93" s="19"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="37" t="s">
+      <c r="F93" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="32"/>
-      <c r="H93" s="30"/>
-      <c r="I93" s="37" t="s">
+      <c r="G93" s="21"/>
+      <c r="H93" s="19"/>
+      <c r="I93" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="30"/>
-      <c r="K93" s="38">
+      <c r="J93" s="19"/>
+      <c r="K93" s="27">
         <v>57</v>
       </c>
-      <c r="L93" s="30"/>
-      <c r="M93" s="39" t="s">
+      <c r="L93" s="19"/>
+      <c r="M93" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="35"/>
+      <c r="N93" s="24"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -4875,30 +4915,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="18">
         <v>44782</v>
       </c>
-      <c r="D94" s="30"/>
+      <c r="D94" s="19"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="31" t="s">
+      <c r="F94" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="32"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="31" t="s">
+      <c r="G94" s="21"/>
+      <c r="H94" s="19"/>
+      <c r="I94" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="30"/>
-      <c r="K94" s="33">
+      <c r="J94" s="19"/>
+      <c r="K94" s="22">
         <v>16</v>
       </c>
-      <c r="L94" s="30"/>
-      <c r="M94" s="34" t="s">
+      <c r="L94" s="19"/>
+      <c r="M94" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="35"/>
+      <c r="N94" s="24"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -4907,30 +4947,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="36">
+      <c r="C95" s="25">
         <v>44782</v>
       </c>
-      <c r="D95" s="30"/>
+      <c r="D95" s="19"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="37" t="s">
+      <c r="F95" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="32"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="37" t="s">
+      <c r="G95" s="21"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="30"/>
-      <c r="K95" s="38">
+      <c r="J95" s="19"/>
+      <c r="K95" s="27">
         <v>3</v>
       </c>
-      <c r="L95" s="30"/>
-      <c r="M95" s="39" t="s">
+      <c r="L95" s="19"/>
+      <c r="M95" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="35"/>
+      <c r="N95" s="24"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -4939,30 +4979,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="18">
         <v>44782</v>
       </c>
-      <c r="D96" s="30"/>
+      <c r="D96" s="19"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="31" t="s">
+      <c r="F96" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="32"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="31" t="s">
+      <c r="G96" s="21"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="30"/>
-      <c r="K96" s="33">
+      <c r="J96" s="19"/>
+      <c r="K96" s="22">
         <v>15</v>
       </c>
-      <c r="L96" s="30"/>
-      <c r="M96" s="34" t="s">
+      <c r="L96" s="19"/>
+      <c r="M96" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="35"/>
+      <c r="N96" s="24"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -4971,30 +5011,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="36">
+      <c r="C97" s="25">
         <v>44783</v>
       </c>
-      <c r="D97" s="30"/>
+      <c r="D97" s="19"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="37" t="s">
+      <c r="F97" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="32"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="37" t="s">
+      <c r="G97" s="21"/>
+      <c r="H97" s="19"/>
+      <c r="I97" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="30"/>
-      <c r="K97" s="38">
+      <c r="J97" s="19"/>
+      <c r="K97" s="27">
         <v>64</v>
       </c>
-      <c r="L97" s="30"/>
-      <c r="M97" s="39" t="s">
+      <c r="L97" s="19"/>
+      <c r="M97" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="35"/>
+      <c r="N97" s="24"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -5003,30 +5043,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="18">
         <v>44783</v>
       </c>
-      <c r="D98" s="30"/>
+      <c r="D98" s="19"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="31" t="s">
+      <c r="F98" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="32"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="31" t="s">
+      <c r="G98" s="21"/>
+      <c r="H98" s="19"/>
+      <c r="I98" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="30"/>
-      <c r="K98" s="33">
+      <c r="J98" s="19"/>
+      <c r="K98" s="22">
         <v>100</v>
       </c>
-      <c r="L98" s="30"/>
-      <c r="M98" s="34" t="s">
+      <c r="L98" s="19"/>
+      <c r="M98" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="35"/>
+      <c r="N98" s="24"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -5035,30 +5075,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="36">
+      <c r="C99" s="25">
         <v>44783</v>
       </c>
-      <c r="D99" s="30"/>
+      <c r="D99" s="19"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="37" t="s">
+      <c r="F99" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="32"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="37" t="s">
+      <c r="G99" s="21"/>
+      <c r="H99" s="19"/>
+      <c r="I99" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="30"/>
-      <c r="K99" s="38">
+      <c r="J99" s="19"/>
+      <c r="K99" s="27">
         <v>193</v>
       </c>
-      <c r="L99" s="30"/>
-      <c r="M99" s="39" t="s">
+      <c r="L99" s="19"/>
+      <c r="M99" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="35"/>
+      <c r="N99" s="24"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -5067,30 +5107,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="18">
         <v>44783</v>
       </c>
-      <c r="D100" s="30"/>
+      <c r="D100" s="19"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="31" t="s">
+      <c r="F100" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="32"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="30"/>
-      <c r="K100" s="33">
+      <c r="G100" s="21"/>
+      <c r="H100" s="19"/>
+      <c r="I100" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="19"/>
+      <c r="K100" s="22">
         <v>15</v>
       </c>
-      <c r="L100" s="30"/>
-      <c r="M100" s="34" t="s">
+      <c r="L100" s="19"/>
+      <c r="M100" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="35"/>
+      <c r="N100" s="24"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -5099,30 +5139,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="36">
+      <c r="C101" s="25">
         <v>44783</v>
       </c>
-      <c r="D101" s="30"/>
+      <c r="D101" s="19"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="37" t="s">
+      <c r="F101" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="32"/>
-      <c r="H101" s="30"/>
-      <c r="I101" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="30"/>
-      <c r="K101" s="38">
+      <c r="G101" s="21"/>
+      <c r="H101" s="19"/>
+      <c r="I101" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="19"/>
+      <c r="K101" s="27">
         <v>65</v>
       </c>
-      <c r="L101" s="30"/>
-      <c r="M101" s="39" t="s">
+      <c r="L101" s="19"/>
+      <c r="M101" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="35"/>
+      <c r="N101" s="24"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -5131,30 +5171,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="18">
         <v>44783</v>
       </c>
-      <c r="D102" s="30"/>
+      <c r="D102" s="19"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="31" t="s">
+      <c r="F102" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="32"/>
-      <c r="H102" s="30"/>
-      <c r="I102" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="30"/>
-      <c r="K102" s="33">
+      <c r="G102" s="21"/>
+      <c r="H102" s="19"/>
+      <c r="I102" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="19"/>
+      <c r="K102" s="22">
         <v>66</v>
       </c>
-      <c r="L102" s="30"/>
-      <c r="M102" s="34" t="s">
+      <c r="L102" s="19"/>
+      <c r="M102" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="35"/>
+      <c r="N102" s="24"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -5163,30 +5203,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="36">
+      <c r="C103" s="25">
         <v>44784</v>
       </c>
-      <c r="D103" s="30"/>
+      <c r="D103" s="19"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="37" t="s">
+      <c r="F103" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="32"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="37" t="s">
+      <c r="G103" s="21"/>
+      <c r="H103" s="19"/>
+      <c r="I103" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="30"/>
-      <c r="K103" s="38">
+      <c r="J103" s="19"/>
+      <c r="K103" s="27">
         <v>111</v>
       </c>
-      <c r="L103" s="30"/>
-      <c r="M103" s="39" t="s">
+      <c r="L103" s="19"/>
+      <c r="M103" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="35"/>
+      <c r="N103" s="24"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5195,30 +5235,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="18">
         <v>44784</v>
       </c>
-      <c r="D104" s="30"/>
+      <c r="D104" s="19"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="31" t="s">
+      <c r="F104" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="32"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="31" t="s">
+      <c r="G104" s="21"/>
+      <c r="H104" s="19"/>
+      <c r="I104" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="30"/>
-      <c r="K104" s="33">
+      <c r="J104" s="19"/>
+      <c r="K104" s="22">
         <v>30</v>
       </c>
-      <c r="L104" s="30"/>
-      <c r="M104" s="34" t="s">
+      <c r="L104" s="19"/>
+      <c r="M104" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="35"/>
+      <c r="N104" s="24"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5227,30 +5267,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="36">
+      <c r="C105" s="25">
         <v>44784</v>
       </c>
-      <c r="D105" s="30"/>
+      <c r="D105" s="19"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="37" t="s">
+      <c r="F105" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="32"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="37" t="s">
+      <c r="G105" s="21"/>
+      <c r="H105" s="19"/>
+      <c r="I105" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="30"/>
-      <c r="K105" s="38">
+      <c r="J105" s="19"/>
+      <c r="K105" s="27">
         <v>31</v>
       </c>
-      <c r="L105" s="30"/>
-      <c r="M105" s="39" t="s">
+      <c r="L105" s="19"/>
+      <c r="M105" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="35"/>
+      <c r="N105" s="24"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5259,30 +5299,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="18">
         <v>44784</v>
       </c>
-      <c r="D106" s="30"/>
+      <c r="D106" s="19"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="31" t="s">
+      <c r="F106" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="32"/>
-      <c r="H106" s="30"/>
-      <c r="I106" s="31" t="s">
+      <c r="G106" s="21"/>
+      <c r="H106" s="19"/>
+      <c r="I106" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="30"/>
-      <c r="K106" s="33">
+      <c r="J106" s="19"/>
+      <c r="K106" s="22">
         <v>109</v>
       </c>
-      <c r="L106" s="30"/>
-      <c r="M106" s="34" t="s">
+      <c r="L106" s="19"/>
+      <c r="M106" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="35"/>
+      <c r="N106" s="24"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5291,30 +5331,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="36">
+      <c r="C107" s="25">
         <v>44788</v>
       </c>
-      <c r="D107" s="30"/>
+      <c r="D107" s="19"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="37" t="s">
+      <c r="F107" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="32"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="37" t="s">
+      <c r="G107" s="21"/>
+      <c r="H107" s="19"/>
+      <c r="I107" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="30"/>
-      <c r="K107" s="38">
+      <c r="J107" s="19"/>
+      <c r="K107" s="27">
         <v>5</v>
       </c>
-      <c r="L107" s="30"/>
-      <c r="M107" s="39" t="s">
+      <c r="L107" s="19"/>
+      <c r="M107" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="35"/>
+      <c r="N107" s="24"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5323,30 +5363,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="18">
         <v>44788</v>
       </c>
-      <c r="D108" s="30"/>
+      <c r="D108" s="19"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="31" t="s">
+      <c r="F108" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="32"/>
-      <c r="H108" s="30"/>
-      <c r="I108" s="31" t="s">
+      <c r="G108" s="21"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="30"/>
-      <c r="K108" s="33">
+      <c r="J108" s="19"/>
+      <c r="K108" s="22">
         <v>100</v>
       </c>
-      <c r="L108" s="30"/>
-      <c r="M108" s="34" t="s">
+      <c r="L108" s="19"/>
+      <c r="M108" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="35"/>
+      <c r="N108" s="24"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5355,30 +5395,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="36">
+      <c r="C109" s="25">
         <v>44788</v>
       </c>
-      <c r="D109" s="30"/>
+      <c r="D109" s="19"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="37" t="s">
+      <c r="F109" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="32"/>
-      <c r="H109" s="30"/>
-      <c r="I109" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="30"/>
-      <c r="K109" s="38">
+      <c r="G109" s="21"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="19"/>
+      <c r="K109" s="27">
         <v>54</v>
       </c>
-      <c r="L109" s="30"/>
-      <c r="M109" s="39" t="s">
+      <c r="L109" s="19"/>
+      <c r="M109" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="35"/>
+      <c r="N109" s="24"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5387,30 +5427,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="18">
         <v>44789</v>
       </c>
-      <c r="D110" s="30"/>
+      <c r="D110" s="19"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="31" t="s">
+      <c r="F110" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="32"/>
-      <c r="H110" s="30"/>
-      <c r="I110" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="30"/>
-      <c r="K110" s="33">
+      <c r="G110" s="21"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="19"/>
+      <c r="K110" s="22">
         <v>77</v>
       </c>
-      <c r="L110" s="30"/>
-      <c r="M110" s="34" t="s">
+      <c r="L110" s="19"/>
+      <c r="M110" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="35"/>
+      <c r="N110" s="24"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5419,30 +5459,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="36">
+      <c r="C111" s="25">
         <v>44789</v>
       </c>
-      <c r="D111" s="30"/>
+      <c r="D111" s="19"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="37" t="s">
+      <c r="F111" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="32"/>
-      <c r="H111" s="30"/>
-      <c r="I111" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="30"/>
-      <c r="K111" s="38">
+      <c r="G111" s="21"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="19"/>
+      <c r="K111" s="27">
         <v>52</v>
       </c>
-      <c r="L111" s="30"/>
-      <c r="M111" s="39" t="s">
+      <c r="L111" s="19"/>
+      <c r="M111" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="35"/>
+      <c r="N111" s="24"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5451,30 +5491,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="18">
         <v>44789</v>
       </c>
-      <c r="D112" s="30"/>
+      <c r="D112" s="19"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="31" t="s">
+      <c r="F112" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="32"/>
-      <c r="H112" s="30"/>
-      <c r="I112" s="31" t="s">
+      <c r="G112" s="21"/>
+      <c r="H112" s="19"/>
+      <c r="I112" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="30"/>
-      <c r="K112" s="33">
+      <c r="J112" s="19"/>
+      <c r="K112" s="22">
         <v>305</v>
       </c>
-      <c r="L112" s="30"/>
-      <c r="M112" s="34" t="s">
+      <c r="L112" s="19"/>
+      <c r="M112" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="35"/>
+      <c r="N112" s="24"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5483,30 +5523,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="36">
+      <c r="C113" s="25">
         <v>44789</v>
       </c>
-      <c r="D113" s="30"/>
+      <c r="D113" s="19"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="37" t="s">
+      <c r="F113" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="32"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="37" t="s">
+      <c r="G113" s="21"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="30"/>
-      <c r="K113" s="38">
+      <c r="J113" s="19"/>
+      <c r="K113" s="27">
         <v>81</v>
       </c>
-      <c r="L113" s="30"/>
-      <c r="M113" s="39" t="s">
+      <c r="L113" s="19"/>
+      <c r="M113" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="35"/>
+      <c r="N113" s="24"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5515,30 +5555,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="18">
         <v>44789</v>
       </c>
-      <c r="D114" s="30"/>
+      <c r="D114" s="19"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="31" t="s">
+      <c r="F114" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="32"/>
-      <c r="H114" s="30"/>
-      <c r="I114" s="31" t="s">
+      <c r="G114" s="21"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="30"/>
-      <c r="K114" s="33">
+      <c r="J114" s="19"/>
+      <c r="K114" s="22">
         <v>53</v>
       </c>
-      <c r="L114" s="30"/>
-      <c r="M114" s="34" t="s">
+      <c r="L114" s="19"/>
+      <c r="M114" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="35"/>
+      <c r="N114" s="24"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5547,30 +5587,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="36">
+      <c r="C115" s="25">
         <v>44789</v>
       </c>
-      <c r="D115" s="30"/>
+      <c r="D115" s="19"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="37" t="s">
+      <c r="F115" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="32"/>
-      <c r="H115" s="30"/>
-      <c r="I115" s="37" t="s">
+      <c r="G115" s="21"/>
+      <c r="H115" s="19"/>
+      <c r="I115" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="30"/>
-      <c r="K115" s="38">
+      <c r="J115" s="19"/>
+      <c r="K115" s="27">
         <v>33</v>
       </c>
-      <c r="L115" s="30"/>
-      <c r="M115" s="39" t="s">
+      <c r="L115" s="19"/>
+      <c r="M115" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="35"/>
+      <c r="N115" s="24"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5579,30 +5619,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C116" s="18">
         <v>44790</v>
       </c>
-      <c r="D116" s="30"/>
+      <c r="D116" s="19"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="31" t="s">
+      <c r="F116" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="32"/>
-      <c r="H116" s="30"/>
-      <c r="I116" s="31" t="s">
+      <c r="G116" s="21"/>
+      <c r="H116" s="19"/>
+      <c r="I116" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="30"/>
-      <c r="K116" s="33">
+      <c r="J116" s="19"/>
+      <c r="K116" s="22">
         <v>145</v>
       </c>
-      <c r="L116" s="30"/>
-      <c r="M116" s="34" t="s">
+      <c r="L116" s="19"/>
+      <c r="M116" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="35"/>
+      <c r="N116" s="24"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5611,30 +5651,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="36">
+      <c r="C117" s="25">
         <v>44790</v>
       </c>
-      <c r="D117" s="30"/>
+      <c r="D117" s="19"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="37" t="s">
+      <c r="F117" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="32"/>
-      <c r="H117" s="30"/>
-      <c r="I117" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="30"/>
-      <c r="K117" s="38">
+      <c r="G117" s="21"/>
+      <c r="H117" s="19"/>
+      <c r="I117" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="19"/>
+      <c r="K117" s="27">
         <v>14</v>
       </c>
-      <c r="L117" s="30"/>
-      <c r="M117" s="39" t="s">
+      <c r="L117" s="19"/>
+      <c r="M117" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="35"/>
+      <c r="N117" s="24"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5643,30 +5683,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C118" s="18">
         <v>44790</v>
       </c>
-      <c r="D118" s="30"/>
+      <c r="D118" s="19"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="31" t="s">
+      <c r="F118" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="32"/>
-      <c r="H118" s="30"/>
-      <c r="I118" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="30"/>
-      <c r="K118" s="33">
+      <c r="G118" s="21"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="19"/>
+      <c r="K118" s="22">
         <v>47</v>
       </c>
-      <c r="L118" s="30"/>
-      <c r="M118" s="34" t="s">
+      <c r="L118" s="19"/>
+      <c r="M118" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="35"/>
+      <c r="N118" s="24"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5675,30 +5715,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="36">
+      <c r="C119" s="25">
         <v>44790</v>
       </c>
-      <c r="D119" s="30"/>
+      <c r="D119" s="19"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="37" t="s">
+      <c r="F119" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="32"/>
-      <c r="H119" s="30"/>
-      <c r="I119" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="30"/>
-      <c r="K119" s="38">
+      <c r="G119" s="21"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="19"/>
+      <c r="K119" s="27">
         <v>16</v>
       </c>
-      <c r="L119" s="30"/>
-      <c r="M119" s="39" t="s">
+      <c r="L119" s="19"/>
+      <c r="M119" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="35"/>
+      <c r="N119" s="24"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5707,30 +5747,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C120" s="18">
         <v>44790</v>
       </c>
-      <c r="D120" s="30"/>
+      <c r="D120" s="19"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="31" t="s">
+      <c r="F120" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="32"/>
-      <c r="H120" s="30"/>
-      <c r="I120" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="30"/>
-      <c r="K120" s="33">
+      <c r="G120" s="21"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="19"/>
+      <c r="K120" s="22">
         <v>55</v>
       </c>
-      <c r="L120" s="30"/>
-      <c r="M120" s="34" t="s">
+      <c r="L120" s="19"/>
+      <c r="M120" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="35"/>
+      <c r="N120" s="24"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5739,30 +5779,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="36">
+      <c r="C121" s="25">
         <v>44790</v>
       </c>
-      <c r="D121" s="30"/>
+      <c r="D121" s="19"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="37" t="s">
+      <c r="F121" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="32"/>
-      <c r="H121" s="30"/>
-      <c r="I121" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="30"/>
-      <c r="K121" s="38">
+      <c r="G121" s="21"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="19"/>
+      <c r="K121" s="27">
         <v>8</v>
       </c>
-      <c r="L121" s="30"/>
-      <c r="M121" s="39" t="s">
+      <c r="L121" s="19"/>
+      <c r="M121" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="35"/>
+      <c r="N121" s="24"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5771,30 +5811,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C122" s="18">
         <v>44790</v>
       </c>
-      <c r="D122" s="30"/>
+      <c r="D122" s="19"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="31" t="s">
+      <c r="F122" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="32"/>
-      <c r="H122" s="30"/>
-      <c r="I122" s="31" t="s">
+      <c r="G122" s="21"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="30"/>
-      <c r="K122" s="33">
+      <c r="J122" s="19"/>
+      <c r="K122" s="22">
         <v>578</v>
       </c>
-      <c r="L122" s="30"/>
-      <c r="M122" s="34" t="s">
+      <c r="L122" s="19"/>
+      <c r="M122" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="35"/>
+      <c r="N122" s="24"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5803,30 +5843,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="36">
+      <c r="C123" s="25">
         <v>44791</v>
       </c>
-      <c r="D123" s="30"/>
+      <c r="D123" s="19"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="37" t="s">
+      <c r="F123" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="32"/>
-      <c r="H123" s="30"/>
-      <c r="I123" s="37" t="s">
+      <c r="G123" s="21"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="30"/>
-      <c r="K123" s="38">
+      <c r="J123" s="19"/>
+      <c r="K123" s="27">
         <v>111</v>
       </c>
-      <c r="L123" s="30"/>
-      <c r="M123" s="39" t="s">
+      <c r="L123" s="19"/>
+      <c r="M123" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="35"/>
+      <c r="N123" s="24"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5835,30 +5875,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C124" s="18">
         <v>44791</v>
       </c>
-      <c r="D124" s="30"/>
+      <c r="D124" s="19"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="31" t="s">
+      <c r="F124" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="32"/>
-      <c r="H124" s="30"/>
-      <c r="I124" s="31" t="s">
+      <c r="G124" s="21"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="30"/>
-      <c r="K124" s="33">
+      <c r="J124" s="19"/>
+      <c r="K124" s="22">
         <v>51</v>
       </c>
-      <c r="L124" s="30"/>
-      <c r="M124" s="34" t="s">
+      <c r="L124" s="19"/>
+      <c r="M124" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="35"/>
+      <c r="N124" s="24"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5867,30 +5907,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="36">
+      <c r="C125" s="25">
         <v>44791</v>
       </c>
-      <c r="D125" s="30"/>
+      <c r="D125" s="19"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="37" t="s">
+      <c r="F125" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="32"/>
-      <c r="H125" s="30"/>
-      <c r="I125" s="37" t="s">
+      <c r="G125" s="21"/>
+      <c r="H125" s="19"/>
+      <c r="I125" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="30"/>
-      <c r="K125" s="38">
+      <c r="J125" s="19"/>
+      <c r="K125" s="27">
         <v>35</v>
       </c>
-      <c r="L125" s="30"/>
-      <c r="M125" s="39" t="s">
+      <c r="L125" s="19"/>
+      <c r="M125" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="35"/>
+      <c r="N125" s="24"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -5899,30 +5939,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C126" s="18">
         <v>44792</v>
       </c>
-      <c r="D126" s="30"/>
+      <c r="D126" s="19"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="31" t="s">
+      <c r="F126" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="32"/>
-      <c r="H126" s="30"/>
-      <c r="I126" s="31" t="s">
+      <c r="G126" s="21"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="30"/>
-      <c r="K126" s="33">
+      <c r="J126" s="19"/>
+      <c r="K126" s="22">
         <v>74</v>
       </c>
-      <c r="L126" s="30"/>
-      <c r="M126" s="34" t="s">
+      <c r="L126" s="19"/>
+      <c r="M126" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="35"/>
+      <c r="N126" s="24"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -5931,30 +5971,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="36">
+      <c r="C127" s="25">
         <v>44795</v>
       </c>
-      <c r="D127" s="30"/>
+      <c r="D127" s="19"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="37" t="s">
+      <c r="F127" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="32"/>
-      <c r="H127" s="30"/>
-      <c r="I127" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="30"/>
-      <c r="K127" s="38">
+      <c r="G127" s="21"/>
+      <c r="H127" s="19"/>
+      <c r="I127" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="19"/>
+      <c r="K127" s="27">
         <v>51</v>
       </c>
-      <c r="L127" s="30"/>
-      <c r="M127" s="39" t="s">
+      <c r="L127" s="19"/>
+      <c r="M127" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="35"/>
+      <c r="N127" s="24"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -5963,30 +6003,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C128" s="18">
         <v>44799</v>
       </c>
-      <c r="D128" s="30"/>
+      <c r="D128" s="19"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="31" t="s">
+      <c r="F128" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="32"/>
-      <c r="H128" s="30"/>
-      <c r="I128" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="30"/>
-      <c r="K128" s="33">
+      <c r="G128" s="21"/>
+      <c r="H128" s="19"/>
+      <c r="I128" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="19"/>
+      <c r="K128" s="22">
         <v>80</v>
       </c>
-      <c r="L128" s="30"/>
-      <c r="M128" s="34" t="s">
+      <c r="L128" s="19"/>
+      <c r="M128" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="35"/>
+      <c r="N128" s="24"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -5995,30 +6035,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="36">
+      <c r="C129" s="25">
         <v>44799</v>
       </c>
-      <c r="D129" s="30"/>
+      <c r="D129" s="19"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="37" t="s">
+      <c r="F129" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="32"/>
-      <c r="H129" s="30"/>
-      <c r="I129" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="30"/>
-      <c r="K129" s="38">
+      <c r="G129" s="21"/>
+      <c r="H129" s="19"/>
+      <c r="I129" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="19"/>
+      <c r="K129" s="27">
         <v>100</v>
       </c>
-      <c r="L129" s="30"/>
-      <c r="M129" s="39" t="s">
+      <c r="L129" s="19"/>
+      <c r="M129" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="35"/>
+      <c r="N129" s="24"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -6027,30 +6067,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="29">
+      <c r="C130" s="18">
         <v>44802</v>
       </c>
-      <c r="D130" s="30"/>
+      <c r="D130" s="19"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="31" t="s">
+      <c r="F130" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="32"/>
-      <c r="H130" s="30"/>
-      <c r="I130" s="31" t="s">
+      <c r="G130" s="21"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="30"/>
-      <c r="K130" s="33">
+      <c r="J130" s="19"/>
+      <c r="K130" s="22">
         <v>96</v>
       </c>
-      <c r="L130" s="30"/>
-      <c r="M130" s="34" t="s">
+      <c r="L130" s="19"/>
+      <c r="M130" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="35"/>
+      <c r="N130" s="24"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -6059,30 +6099,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="36">
+      <c r="C131" s="25">
         <v>44802</v>
       </c>
-      <c r="D131" s="30"/>
+      <c r="D131" s="19"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="37" t="s">
+      <c r="F131" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="32"/>
-      <c r="H131" s="30"/>
-      <c r="I131" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="30"/>
-      <c r="K131" s="38">
+      <c r="G131" s="21"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="19"/>
+      <c r="K131" s="27">
         <v>37</v>
       </c>
-      <c r="L131" s="30"/>
-      <c r="M131" s="39" t="s">
+      <c r="L131" s="19"/>
+      <c r="M131" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="35"/>
+      <c r="N131" s="24"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -6091,30 +6131,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="29">
+      <c r="C132" s="18">
         <v>44804</v>
       </c>
-      <c r="D132" s="30"/>
+      <c r="D132" s="19"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="31" t="s">
+      <c r="F132" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="32"/>
-      <c r="H132" s="30"/>
-      <c r="I132" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="30"/>
-      <c r="K132" s="33">
+      <c r="G132" s="21"/>
+      <c r="H132" s="19"/>
+      <c r="I132" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="19"/>
+      <c r="K132" s="22">
         <v>91</v>
       </c>
-      <c r="L132" s="30"/>
-      <c r="M132" s="34" t="s">
+      <c r="L132" s="19"/>
+      <c r="M132" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="35"/>
+      <c r="N132" s="24"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -6123,30 +6163,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="36">
+      <c r="C133" s="25">
         <v>44804</v>
       </c>
-      <c r="D133" s="30"/>
+      <c r="D133" s="19"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="37" t="s">
+      <c r="F133" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="32"/>
-      <c r="H133" s="30"/>
-      <c r="I133" s="37" t="s">
+      <c r="G133" s="21"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="30"/>
-      <c r="K133" s="38">
+      <c r="J133" s="19"/>
+      <c r="K133" s="27">
         <v>56</v>
       </c>
-      <c r="L133" s="30"/>
-      <c r="M133" s="39" t="s">
+      <c r="L133" s="19"/>
+      <c r="M133" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="35"/>
+      <c r="N133" s="24"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -6155,30 +6195,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="29">
+      <c r="C134" s="18">
         <v>44805</v>
       </c>
-      <c r="D134" s="30"/>
+      <c r="D134" s="19"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="31" t="s">
+      <c r="F134" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="32"/>
-      <c r="H134" s="30"/>
-      <c r="I134" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="30"/>
-      <c r="K134" s="33">
+      <c r="G134" s="21"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="19"/>
+      <c r="K134" s="22">
         <v>401</v>
       </c>
-      <c r="L134" s="30"/>
-      <c r="M134" s="34" t="s">
+      <c r="L134" s="19"/>
+      <c r="M134" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="35"/>
+      <c r="N134" s="24"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -6187,30 +6227,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="36">
+      <c r="C135" s="25">
         <v>44805</v>
       </c>
-      <c r="D135" s="30"/>
+      <c r="D135" s="19"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="37" t="s">
+      <c r="F135" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="32"/>
-      <c r="H135" s="30"/>
-      <c r="I135" s="37" t="s">
+      <c r="G135" s="21"/>
+      <c r="H135" s="19"/>
+      <c r="I135" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="30"/>
-      <c r="K135" s="38">
+      <c r="J135" s="19"/>
+      <c r="K135" s="27">
         <v>375</v>
       </c>
-      <c r="L135" s="30"/>
-      <c r="M135" s="39" t="s">
+      <c r="L135" s="19"/>
+      <c r="M135" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="35"/>
+      <c r="N135" s="24"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6219,30 +6259,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="29">
+      <c r="C136" s="18">
         <v>44806</v>
       </c>
-      <c r="D136" s="30"/>
+      <c r="D136" s="19"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="31" t="s">
+      <c r="F136" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="32"/>
-      <c r="H136" s="30"/>
-      <c r="I136" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="30"/>
-      <c r="K136" s="33">
+      <c r="G136" s="21"/>
+      <c r="H136" s="19"/>
+      <c r="I136" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="19"/>
+      <c r="K136" s="22">
         <v>44</v>
       </c>
-      <c r="L136" s="30"/>
-      <c r="M136" s="34" t="s">
+      <c r="L136" s="19"/>
+      <c r="M136" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="35"/>
+      <c r="N136" s="24"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6251,30 +6291,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="36">
+      <c r="C137" s="25">
         <v>44806</v>
       </c>
-      <c r="D137" s="30"/>
+      <c r="D137" s="19"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="37" t="s">
+      <c r="F137" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="32"/>
-      <c r="H137" s="30"/>
-      <c r="I137" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="30"/>
-      <c r="K137" s="38">
+      <c r="G137" s="21"/>
+      <c r="H137" s="19"/>
+      <c r="I137" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="19"/>
+      <c r="K137" s="27">
         <v>51</v>
       </c>
-      <c r="L137" s="30"/>
-      <c r="M137" s="39" t="s">
+      <c r="L137" s="19"/>
+      <c r="M137" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="35"/>
+      <c r="N137" s="24"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6283,30 +6323,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="29">
+      <c r="C138" s="18">
         <v>44806</v>
       </c>
-      <c r="D138" s="30"/>
+      <c r="D138" s="19"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="31" t="s">
+      <c r="F138" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="32"/>
-      <c r="H138" s="30"/>
-      <c r="I138" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="30"/>
-      <c r="K138" s="33">
+      <c r="G138" s="21"/>
+      <c r="H138" s="19"/>
+      <c r="I138" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="19"/>
+      <c r="K138" s="22">
         <v>40</v>
       </c>
-      <c r="L138" s="30"/>
-      <c r="M138" s="34" t="s">
+      <c r="L138" s="19"/>
+      <c r="M138" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="35"/>
+      <c r="N138" s="24"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6315,30 +6355,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="36">
+      <c r="C139" s="25">
         <v>44810</v>
       </c>
-      <c r="D139" s="30"/>
+      <c r="D139" s="19"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="37" t="s">
+      <c r="F139" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="32"/>
-      <c r="H139" s="30"/>
-      <c r="I139" s="37" t="s">
+      <c r="G139" s="21"/>
+      <c r="H139" s="19"/>
+      <c r="I139" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="30"/>
-      <c r="K139" s="38">
+      <c r="J139" s="19"/>
+      <c r="K139" s="27">
         <v>9</v>
       </c>
-      <c r="L139" s="30"/>
-      <c r="M139" s="39" t="s">
+      <c r="L139" s="19"/>
+      <c r="M139" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="35"/>
+      <c r="N139" s="24"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6347,30 +6387,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="29">
+      <c r="C140" s="18">
         <v>44810</v>
       </c>
-      <c r="D140" s="30"/>
+      <c r="D140" s="19"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="31" t="s">
+      <c r="F140" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="32"/>
-      <c r="H140" s="30"/>
-      <c r="I140" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="30"/>
-      <c r="K140" s="33">
+      <c r="G140" s="21"/>
+      <c r="H140" s="19"/>
+      <c r="I140" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="19"/>
+      <c r="K140" s="22">
         <v>17</v>
       </c>
-      <c r="L140" s="30"/>
-      <c r="M140" s="34" t="s">
+      <c r="L140" s="19"/>
+      <c r="M140" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="35"/>
+      <c r="N140" s="24"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6379,30 +6419,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="36">
+      <c r="C141" s="25">
         <v>44810</v>
       </c>
-      <c r="D141" s="30"/>
+      <c r="D141" s="19"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="37" t="s">
+      <c r="F141" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="32"/>
-      <c r="H141" s="30"/>
-      <c r="I141" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="30"/>
-      <c r="K141" s="38">
+      <c r="G141" s="21"/>
+      <c r="H141" s="19"/>
+      <c r="I141" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="19"/>
+      <c r="K141" s="27">
         <v>5</v>
       </c>
-      <c r="L141" s="30"/>
-      <c r="M141" s="39" t="s">
+      <c r="L141" s="19"/>
+      <c r="M141" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="35"/>
+      <c r="N141" s="24"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6411,30 +6451,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="29">
+      <c r="C142" s="18">
         <v>44810</v>
       </c>
-      <c r="D142" s="30"/>
+      <c r="D142" s="19"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="31" t="s">
+      <c r="F142" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="32"/>
-      <c r="H142" s="30"/>
-      <c r="I142" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="30"/>
-      <c r="K142" s="33">
+      <c r="G142" s="21"/>
+      <c r="H142" s="19"/>
+      <c r="I142" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="19"/>
+      <c r="K142" s="22">
         <v>45</v>
       </c>
-      <c r="L142" s="30"/>
-      <c r="M142" s="34" t="s">
+      <c r="L142" s="19"/>
+      <c r="M142" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="35"/>
+      <c r="N142" s="24"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6443,30 +6483,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="36">
+      <c r="C143" s="25">
         <v>44811</v>
       </c>
-      <c r="D143" s="30"/>
+      <c r="D143" s="19"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="37" t="s">
+      <c r="F143" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="32"/>
-      <c r="H143" s="30"/>
-      <c r="I143" s="37" t="s">
+      <c r="G143" s="21"/>
+      <c r="H143" s="19"/>
+      <c r="I143" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="30"/>
-      <c r="K143" s="38">
+      <c r="J143" s="19"/>
+      <c r="K143" s="27">
         <v>132</v>
       </c>
-      <c r="L143" s="30"/>
-      <c r="M143" s="39" t="s">
+      <c r="L143" s="19"/>
+      <c r="M143" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="35"/>
+      <c r="N143" s="24"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6475,30 +6515,30 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="29">
+      <c r="C144" s="18">
         <v>44811</v>
       </c>
-      <c r="D144" s="30"/>
+      <c r="D144" s="19"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="31" t="s">
+      <c r="F144" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="32"/>
-      <c r="H144" s="30"/>
-      <c r="I144" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="30"/>
-      <c r="K144" s="33">
+      <c r="G144" s="21"/>
+      <c r="H144" s="19"/>
+      <c r="I144" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="19"/>
+      <c r="K144" s="22">
         <v>66</v>
       </c>
-      <c r="L144" s="30"/>
-      <c r="M144" s="34" t="s">
+      <c r="L144" s="19"/>
+      <c r="M144" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="35"/>
+      <c r="N144" s="24"/>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
@@ -6507,30 +6547,30 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="36">
+      <c r="C145" s="25">
         <v>44812</v>
       </c>
-      <c r="D145" s="30"/>
+      <c r="D145" s="19"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="37" t="s">
+      <c r="F145" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="32"/>
-      <c r="H145" s="30"/>
-      <c r="I145" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J145" s="30"/>
-      <c r="K145" s="38">
+      <c r="G145" s="21"/>
+      <c r="H145" s="19"/>
+      <c r="I145" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="19"/>
+      <c r="K145" s="27">
         <v>69</v>
       </c>
-      <c r="L145" s="30"/>
-      <c r="M145" s="39" t="s">
+      <c r="L145" s="19"/>
+      <c r="M145" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="N145" s="35"/>
+      <c r="N145" s="24"/>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="3" t="s">
@@ -6539,30 +6579,30 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="29">
+      <c r="C146" s="18">
         <v>44812</v>
       </c>
-      <c r="D146" s="30"/>
+      <c r="D146" s="19"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="31" t="s">
+      <c r="F146" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="G146" s="32"/>
-      <c r="H146" s="30"/>
-      <c r="I146" s="31" t="s">
+      <c r="G146" s="21"/>
+      <c r="H146" s="19"/>
+      <c r="I146" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J146" s="30"/>
-      <c r="K146" s="33">
+      <c r="J146" s="19"/>
+      <c r="K146" s="22">
         <v>48</v>
       </c>
-      <c r="L146" s="30"/>
-      <c r="M146" s="34" t="s">
+      <c r="L146" s="19"/>
+      <c r="M146" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="N146" s="35"/>
+      <c r="N146" s="24"/>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
@@ -6571,30 +6611,30 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="36">
+      <c r="C147" s="25">
         <v>44812</v>
       </c>
-      <c r="D147" s="30"/>
+      <c r="D147" s="19"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="37" t="s">
+      <c r="F147" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="G147" s="32"/>
-      <c r="H147" s="30"/>
-      <c r="I147" s="37" t="s">
+      <c r="G147" s="21"/>
+      <c r="H147" s="19"/>
+      <c r="I147" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J147" s="30"/>
-      <c r="K147" s="38">
+      <c r="J147" s="19"/>
+      <c r="K147" s="27">
         <v>33</v>
       </c>
-      <c r="L147" s="30"/>
-      <c r="M147" s="39" t="s">
+      <c r="L147" s="19"/>
+      <c r="M147" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="N147" s="35"/>
+      <c r="N147" s="24"/>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="3" t="s">
@@ -6603,30 +6643,30 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="29">
+      <c r="C148" s="18">
         <v>44813</v>
       </c>
-      <c r="D148" s="30"/>
+      <c r="D148" s="19"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="31" t="s">
+      <c r="F148" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="G148" s="32"/>
-      <c r="H148" s="30"/>
-      <c r="I148" s="31" t="s">
+      <c r="G148" s="21"/>
+      <c r="H148" s="19"/>
+      <c r="I148" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J148" s="30"/>
-      <c r="K148" s="33">
+      <c r="J148" s="19"/>
+      <c r="K148" s="22">
         <v>5</v>
       </c>
-      <c r="L148" s="30"/>
-      <c r="M148" s="34" t="s">
+      <c r="L148" s="19"/>
+      <c r="M148" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="N148" s="35"/>
+      <c r="N148" s="24"/>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
@@ -6635,30 +6675,30 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="36">
+      <c r="C149" s="25">
         <v>44813</v>
       </c>
-      <c r="D149" s="30"/>
+      <c r="D149" s="19"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="37" t="s">
+      <c r="F149" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="G149" s="32"/>
-      <c r="H149" s="30"/>
-      <c r="I149" s="37" t="s">
+      <c r="G149" s="21"/>
+      <c r="H149" s="19"/>
+      <c r="I149" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J149" s="30"/>
-      <c r="K149" s="38">
+      <c r="J149" s="19"/>
+      <c r="K149" s="27">
         <v>26</v>
       </c>
-      <c r="L149" s="30"/>
-      <c r="M149" s="39" t="s">
+      <c r="L149" s="19"/>
+      <c r="M149" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="N149" s="35"/>
+      <c r="N149" s="24"/>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="3" t="s">
@@ -6667,30 +6707,30 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="29">
+      <c r="C150" s="18">
         <v>44813</v>
       </c>
-      <c r="D150" s="30"/>
+      <c r="D150" s="19"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="31" t="s">
+      <c r="F150" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="G150" s="32"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J150" s="30"/>
-      <c r="K150" s="33">
+      <c r="G150" s="21"/>
+      <c r="H150" s="19"/>
+      <c r="I150" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="19"/>
+      <c r="K150" s="22">
         <v>13</v>
       </c>
-      <c r="L150" s="30"/>
-      <c r="M150" s="34" t="s">
+      <c r="L150" s="19"/>
+      <c r="M150" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="N150" s="35"/>
+      <c r="N150" s="24"/>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
@@ -6699,30 +6739,30 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="36">
+      <c r="C151" s="25">
         <v>44816</v>
       </c>
-      <c r="D151" s="30"/>
+      <c r="D151" s="19"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="37" t="s">
+      <c r="F151" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="G151" s="32"/>
-      <c r="H151" s="30"/>
-      <c r="I151" s="37" t="s">
+      <c r="G151" s="21"/>
+      <c r="H151" s="19"/>
+      <c r="I151" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J151" s="30"/>
-      <c r="K151" s="38">
+      <c r="J151" s="19"/>
+      <c r="K151" s="27">
         <v>50</v>
       </c>
-      <c r="L151" s="30"/>
-      <c r="M151" s="39" t="s">
+      <c r="L151" s="19"/>
+      <c r="M151" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="N151" s="35"/>
+      <c r="N151" s="24"/>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="3" t="s">
@@ -6731,30 +6771,30 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="29">
+      <c r="C152" s="18">
         <v>44816</v>
       </c>
-      <c r="D152" s="30"/>
+      <c r="D152" s="19"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="31" t="s">
+      <c r="F152" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="32"/>
-      <c r="H152" s="30"/>
-      <c r="I152" s="31" t="s">
+      <c r="G152" s="21"/>
+      <c r="H152" s="19"/>
+      <c r="I152" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J152" s="30"/>
-      <c r="K152" s="33">
+      <c r="J152" s="19"/>
+      <c r="K152" s="22">
         <v>104</v>
       </c>
-      <c r="L152" s="30"/>
-      <c r="M152" s="34" t="s">
+      <c r="L152" s="19"/>
+      <c r="M152" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="N152" s="35"/>
+      <c r="N152" s="24"/>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="1" t="s">
@@ -6763,30 +6803,30 @@
       <c r="B153" s="2">
         <v>44813</v>
       </c>
-      <c r="C153" s="36">
+      <c r="C153" s="25">
         <v>44817</v>
       </c>
-      <c r="D153" s="30"/>
+      <c r="D153" s="19"/>
       <c r="E153" s="2">
         <v>45199</v>
       </c>
-      <c r="F153" s="37" t="s">
+      <c r="F153" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G153" s="32"/>
-      <c r="H153" s="30"/>
-      <c r="I153" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J153" s="30"/>
-      <c r="K153" s="38">
+      <c r="G153" s="21"/>
+      <c r="H153" s="19"/>
+      <c r="I153" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="19"/>
+      <c r="K153" s="27">
         <v>1</v>
       </c>
-      <c r="L153" s="30"/>
-      <c r="M153" s="39" t="s">
+      <c r="L153" s="19"/>
+      <c r="M153" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N153" s="35"/>
+      <c r="N153" s="24"/>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="3" t="s">
@@ -6795,30 +6835,30 @@
       <c r="B154" s="4">
         <v>44813</v>
       </c>
-      <c r="C154" s="29">
+      <c r="C154" s="18">
         <v>44817</v>
       </c>
-      <c r="D154" s="30"/>
+      <c r="D154" s="19"/>
       <c r="E154" s="4">
         <v>44848</v>
       </c>
-      <c r="F154" s="31" t="s">
+      <c r="F154" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G154" s="32"/>
-      <c r="H154" s="30"/>
-      <c r="I154" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J154" s="30"/>
-      <c r="K154" s="33">
+      <c r="G154" s="21"/>
+      <c r="H154" s="19"/>
+      <c r="I154" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="19"/>
+      <c r="K154" s="22">
         <v>2</v>
       </c>
-      <c r="L154" s="30"/>
-      <c r="M154" s="34" t="s">
+      <c r="L154" s="19"/>
+      <c r="M154" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N154" s="35"/>
+      <c r="N154" s="24"/>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="1" t="s">
@@ -6827,30 +6867,30 @@
       <c r="B155" s="2">
         <v>44813</v>
       </c>
-      <c r="C155" s="36">
+      <c r="C155" s="25">
         <v>44817</v>
       </c>
-      <c r="D155" s="30"/>
+      <c r="D155" s="19"/>
       <c r="E155" s="2">
         <v>45198</v>
       </c>
-      <c r="F155" s="37" t="s">
+      <c r="F155" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G155" s="32"/>
-      <c r="H155" s="30"/>
-      <c r="I155" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J155" s="30"/>
-      <c r="K155" s="38">
+      <c r="G155" s="21"/>
+      <c r="H155" s="19"/>
+      <c r="I155" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="19"/>
+      <c r="K155" s="27">
         <v>2</v>
       </c>
-      <c r="L155" s="30"/>
-      <c r="M155" s="39" t="s">
+      <c r="L155" s="19"/>
+      <c r="M155" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N155" s="35"/>
+      <c r="N155" s="24"/>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="3" t="s">
@@ -6859,30 +6899,30 @@
       <c r="B156" s="4">
         <v>44813</v>
       </c>
-      <c r="C156" s="29">
+      <c r="C156" s="18">
         <v>44817</v>
       </c>
-      <c r="D156" s="30"/>
+      <c r="D156" s="19"/>
       <c r="E156" s="4">
         <v>45044</v>
       </c>
-      <c r="F156" s="31" t="s">
+      <c r="F156" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G156" s="32"/>
-      <c r="H156" s="30"/>
-      <c r="I156" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J156" s="30"/>
-      <c r="K156" s="33">
+      <c r="G156" s="21"/>
+      <c r="H156" s="19"/>
+      <c r="I156" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="19"/>
+      <c r="K156" s="22">
         <v>5</v>
       </c>
-      <c r="L156" s="30"/>
-      <c r="M156" s="34" t="s">
+      <c r="L156" s="19"/>
+      <c r="M156" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N156" s="35"/>
+      <c r="N156" s="24"/>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="1" t="s">
@@ -6891,30 +6931,30 @@
       <c r="B157" s="2">
         <v>44813</v>
       </c>
-      <c r="C157" s="36">
+      <c r="C157" s="25">
         <v>44817</v>
       </c>
-      <c r="D157" s="30"/>
+      <c r="D157" s="19"/>
       <c r="E157" s="2">
         <v>45107</v>
       </c>
-      <c r="F157" s="37" t="s">
+      <c r="F157" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G157" s="32"/>
-      <c r="H157" s="30"/>
-      <c r="I157" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J157" s="30"/>
-      <c r="K157" s="38">
+      <c r="G157" s="21"/>
+      <c r="H157" s="19"/>
+      <c r="I157" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="19"/>
+      <c r="K157" s="27">
         <v>2</v>
       </c>
-      <c r="L157" s="30"/>
-      <c r="M157" s="39" t="s">
+      <c r="L157" s="19"/>
+      <c r="M157" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N157" s="35"/>
+      <c r="N157" s="24"/>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="3" t="s">
@@ -6923,30 +6963,30 @@
       <c r="B158" s="4">
         <v>44813</v>
       </c>
-      <c r="C158" s="29">
+      <c r="C158" s="18">
         <v>44817</v>
       </c>
-      <c r="D158" s="30"/>
+      <c r="D158" s="19"/>
       <c r="E158" s="4">
         <v>45192</v>
       </c>
-      <c r="F158" s="31" t="s">
+      <c r="F158" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G158" s="32"/>
-      <c r="H158" s="30"/>
-      <c r="I158" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" s="30"/>
-      <c r="K158" s="33">
+      <c r="G158" s="21"/>
+      <c r="H158" s="19"/>
+      <c r="I158" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="19"/>
+      <c r="K158" s="22">
         <v>1</v>
       </c>
-      <c r="L158" s="30"/>
-      <c r="M158" s="34" t="s">
+      <c r="L158" s="19"/>
+      <c r="M158" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N158" s="35"/>
+      <c r="N158" s="24"/>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="1" t="s">
@@ -6955,30 +6995,30 @@
       <c r="B159" s="2">
         <v>44813</v>
       </c>
-      <c r="C159" s="36">
+      <c r="C159" s="25">
         <v>44817</v>
       </c>
-      <c r="D159" s="30"/>
+      <c r="D159" s="19"/>
       <c r="E159" s="2">
         <v>44957</v>
       </c>
-      <c r="F159" s="37" t="s">
+      <c r="F159" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G159" s="32"/>
-      <c r="H159" s="30"/>
-      <c r="I159" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J159" s="30"/>
-      <c r="K159" s="38">
+      <c r="G159" s="21"/>
+      <c r="H159" s="19"/>
+      <c r="I159" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="19"/>
+      <c r="K159" s="27">
         <v>4</v>
       </c>
-      <c r="L159" s="30"/>
-      <c r="M159" s="39" t="s">
+      <c r="L159" s="19"/>
+      <c r="M159" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N159" s="35"/>
+      <c r="N159" s="24"/>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="3" t="s">
@@ -6987,30 +7027,30 @@
       <c r="B160" s="4">
         <v>44813</v>
       </c>
-      <c r="C160" s="29">
+      <c r="C160" s="18">
         <v>44817</v>
       </c>
-      <c r="D160" s="30"/>
+      <c r="D160" s="19"/>
       <c r="E160" s="4">
         <v>44834</v>
       </c>
-      <c r="F160" s="31" t="s">
+      <c r="F160" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G160" s="32"/>
-      <c r="H160" s="30"/>
-      <c r="I160" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J160" s="30"/>
-      <c r="K160" s="33">
+      <c r="G160" s="21"/>
+      <c r="H160" s="19"/>
+      <c r="I160" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="19"/>
+      <c r="K160" s="22">
         <v>4</v>
       </c>
-      <c r="L160" s="30"/>
-      <c r="M160" s="34" t="s">
+      <c r="L160" s="19"/>
+      <c r="M160" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N160" s="35"/>
+      <c r="N160" s="24"/>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="1" t="s">
@@ -7019,30 +7059,30 @@
       <c r="B161" s="2">
         <v>44813</v>
       </c>
-      <c r="C161" s="36">
+      <c r="C161" s="25">
         <v>44817</v>
       </c>
-      <c r="D161" s="30"/>
+      <c r="D161" s="19"/>
       <c r="E161" s="2">
         <v>45077</v>
       </c>
-      <c r="F161" s="37" t="s">
+      <c r="F161" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G161" s="32"/>
-      <c r="H161" s="30"/>
-      <c r="I161" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J161" s="30"/>
-      <c r="K161" s="38">
+      <c r="G161" s="21"/>
+      <c r="H161" s="19"/>
+      <c r="I161" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="19"/>
+      <c r="K161" s="27">
         <v>3</v>
       </c>
-      <c r="L161" s="30"/>
-      <c r="M161" s="39" t="s">
+      <c r="L161" s="19"/>
+      <c r="M161" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N161" s="35"/>
+      <c r="N161" s="24"/>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="3" t="s">
@@ -7051,30 +7091,30 @@
       <c r="B162" s="4">
         <v>44813</v>
       </c>
-      <c r="C162" s="29">
+      <c r="C162" s="18">
         <v>44817</v>
       </c>
-      <c r="D162" s="30"/>
+      <c r="D162" s="19"/>
       <c r="E162" s="4">
         <v>45093</v>
       </c>
-      <c r="F162" s="31" t="s">
+      <c r="F162" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G162" s="32"/>
-      <c r="H162" s="30"/>
-      <c r="I162" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J162" s="30"/>
-      <c r="K162" s="33">
+      <c r="G162" s="21"/>
+      <c r="H162" s="19"/>
+      <c r="I162" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="19"/>
+      <c r="K162" s="22">
         <v>8</v>
       </c>
-      <c r="L162" s="30"/>
-      <c r="M162" s="34" t="s">
+      <c r="L162" s="19"/>
+      <c r="M162" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N162" s="35"/>
+      <c r="N162" s="24"/>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="1" t="s">
@@ -7083,30 +7123,30 @@
       <c r="B163" s="2">
         <v>44813</v>
       </c>
-      <c r="C163" s="36">
+      <c r="C163" s="25">
         <v>44817</v>
       </c>
-      <c r="D163" s="30"/>
+      <c r="D163" s="19"/>
       <c r="E163" s="2">
         <v>45565</v>
       </c>
-      <c r="F163" s="37" t="s">
+      <c r="F163" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G163" s="32"/>
-      <c r="H163" s="30"/>
-      <c r="I163" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J163" s="30"/>
-      <c r="K163" s="38">
+      <c r="G163" s="21"/>
+      <c r="H163" s="19"/>
+      <c r="I163" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="19"/>
+      <c r="K163" s="27">
         <v>1</v>
       </c>
-      <c r="L163" s="30"/>
-      <c r="M163" s="39" t="s">
+      <c r="L163" s="19"/>
+      <c r="M163" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N163" s="35"/>
+      <c r="N163" s="24"/>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="3" t="s">
@@ -7115,30 +7155,30 @@
       <c r="B164" s="4">
         <v>44813</v>
       </c>
-      <c r="C164" s="29">
+      <c r="C164" s="18">
         <v>44817</v>
       </c>
-      <c r="D164" s="30"/>
+      <c r="D164" s="19"/>
       <c r="E164" s="4">
         <v>45227</v>
       </c>
-      <c r="F164" s="31" t="s">
+      <c r="F164" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G164" s="32"/>
-      <c r="H164" s="30"/>
-      <c r="I164" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J164" s="30"/>
-      <c r="K164" s="33">
+      <c r="G164" s="21"/>
+      <c r="H164" s="19"/>
+      <c r="I164" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="19"/>
+      <c r="K164" s="22">
         <v>2</v>
       </c>
-      <c r="L164" s="30"/>
-      <c r="M164" s="34" t="s">
+      <c r="L164" s="19"/>
+      <c r="M164" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N164" s="35"/>
+      <c r="N164" s="24"/>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="1" t="s">
@@ -7147,30 +7187,30 @@
       <c r="B165" s="2">
         <v>44813</v>
       </c>
-      <c r="C165" s="36">
+      <c r="C165" s="25">
         <v>44817</v>
       </c>
-      <c r="D165" s="30"/>
+      <c r="D165" s="19"/>
       <c r="E165" s="2">
         <v>45046</v>
       </c>
-      <c r="F165" s="37" t="s">
+      <c r="F165" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G165" s="32"/>
-      <c r="H165" s="30"/>
-      <c r="I165" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J165" s="30"/>
-      <c r="K165" s="38">
+      <c r="G165" s="21"/>
+      <c r="H165" s="19"/>
+      <c r="I165" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="19"/>
+      <c r="K165" s="27">
         <v>1</v>
       </c>
-      <c r="L165" s="30"/>
-      <c r="M165" s="39" t="s">
+      <c r="L165" s="19"/>
+      <c r="M165" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N165" s="35"/>
+      <c r="N165" s="24"/>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="3" t="s">
@@ -7179,30 +7219,30 @@
       <c r="B166" s="4">
         <v>44813</v>
       </c>
-      <c r="C166" s="29">
+      <c r="C166" s="18">
         <v>44817</v>
       </c>
-      <c r="D166" s="30"/>
+      <c r="D166" s="19"/>
       <c r="E166" s="4">
         <v>45092</v>
       </c>
-      <c r="F166" s="31" t="s">
+      <c r="F166" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G166" s="32"/>
-      <c r="H166" s="30"/>
-      <c r="I166" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J166" s="30"/>
-      <c r="K166" s="33">
+      <c r="G166" s="21"/>
+      <c r="H166" s="19"/>
+      <c r="I166" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="19"/>
+      <c r="K166" s="22">
         <v>3</v>
       </c>
-      <c r="L166" s="30"/>
-      <c r="M166" s="34" t="s">
+      <c r="L166" s="19"/>
+      <c r="M166" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N166" s="35"/>
+      <c r="N166" s="24"/>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="1" t="s">
@@ -7211,30 +7251,30 @@
       <c r="B167" s="2">
         <v>44813</v>
       </c>
-      <c r="C167" s="36">
+      <c r="C167" s="25">
         <v>44817</v>
       </c>
-      <c r="D167" s="30"/>
+      <c r="D167" s="19"/>
       <c r="E167" s="2">
         <v>44985</v>
       </c>
-      <c r="F167" s="37" t="s">
+      <c r="F167" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G167" s="32"/>
-      <c r="H167" s="30"/>
-      <c r="I167" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J167" s="30"/>
-      <c r="K167" s="38">
+      <c r="G167" s="21"/>
+      <c r="H167" s="19"/>
+      <c r="I167" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="19"/>
+      <c r="K167" s="27">
         <v>1</v>
       </c>
-      <c r="L167" s="30"/>
-      <c r="M167" s="39" t="s">
+      <c r="L167" s="19"/>
+      <c r="M167" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="N167" s="35"/>
+      <c r="N167" s="24"/>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="3" t="s">
@@ -7243,30 +7283,30 @@
       <c r="B168" s="4">
         <v>44813</v>
       </c>
-      <c r="C168" s="29">
+      <c r="C168" s="18">
         <v>44817</v>
       </c>
-      <c r="D168" s="30"/>
+      <c r="D168" s="19"/>
       <c r="E168" s="4">
         <v>45555</v>
       </c>
-      <c r="F168" s="31" t="s">
+      <c r="F168" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="G168" s="32"/>
-      <c r="H168" s="30"/>
-      <c r="I168" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J168" s="30"/>
-      <c r="K168" s="33">
+      <c r="G168" s="21"/>
+      <c r="H168" s="19"/>
+      <c r="I168" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="19"/>
+      <c r="K168" s="22">
         <v>1</v>
       </c>
-      <c r="L168" s="30"/>
-      <c r="M168" s="34" t="s">
+      <c r="L168" s="19"/>
+      <c r="M168" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N168" s="35"/>
+      <c r="N168" s="24"/>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="1" t="s">
@@ -7275,30 +7315,30 @@
       <c r="B169" s="2">
         <v>44811</v>
       </c>
-      <c r="C169" s="36">
+      <c r="C169" s="25">
         <v>44817</v>
       </c>
-      <c r="D169" s="30"/>
+      <c r="D169" s="19"/>
       <c r="E169" s="2">
         <v>44882</v>
       </c>
-      <c r="F169" s="37" t="s">
+      <c r="F169" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="G169" s="32"/>
-      <c r="H169" s="30"/>
-      <c r="I169" s="37" t="s">
+      <c r="G169" s="21"/>
+      <c r="H169" s="19"/>
+      <c r="I169" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J169" s="30"/>
-      <c r="K169" s="38">
+      <c r="J169" s="19"/>
+      <c r="K169" s="27">
         <v>92</v>
       </c>
-      <c r="L169" s="30"/>
-      <c r="M169" s="39" t="s">
+      <c r="L169" s="19"/>
+      <c r="M169" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="N169" s="35"/>
+      <c r="N169" s="24"/>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="3" t="s">
@@ -7307,30 +7347,30 @@
       <c r="B170" s="4">
         <v>44811</v>
       </c>
-      <c r="C170" s="29">
+      <c r="C170" s="18">
         <v>44817</v>
       </c>
-      <c r="D170" s="30"/>
+      <c r="D170" s="19"/>
       <c r="E170" s="4">
         <v>44882</v>
       </c>
-      <c r="F170" s="31" t="s">
+      <c r="F170" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="G170" s="32"/>
-      <c r="H170" s="30"/>
-      <c r="I170" s="31" t="s">
+      <c r="G170" s="21"/>
+      <c r="H170" s="19"/>
+      <c r="I170" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J170" s="30"/>
-      <c r="K170" s="33">
+      <c r="J170" s="19"/>
+      <c r="K170" s="22">
         <v>169</v>
       </c>
-      <c r="L170" s="30"/>
-      <c r="M170" s="34" t="s">
+      <c r="L170" s="19"/>
+      <c r="M170" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="N170" s="35"/>
+      <c r="N170" s="24"/>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="1" t="s">
@@ -7339,30 +7379,30 @@
       <c r="B171" s="2">
         <v>44817</v>
       </c>
-      <c r="C171" s="36">
+      <c r="C171" s="25">
         <v>44818</v>
       </c>
-      <c r="D171" s="30"/>
+      <c r="D171" s="19"/>
       <c r="E171" s="2">
         <v>44888</v>
       </c>
-      <c r="F171" s="37" t="s">
+      <c r="F171" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="G171" s="32"/>
-      <c r="H171" s="30"/>
-      <c r="I171" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J171" s="30"/>
-      <c r="K171" s="38">
+      <c r="G171" s="21"/>
+      <c r="H171" s="19"/>
+      <c r="I171" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="19"/>
+      <c r="K171" s="27">
         <v>99</v>
       </c>
-      <c r="L171" s="30"/>
-      <c r="M171" s="39" t="s">
+      <c r="L171" s="19"/>
+      <c r="M171" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="N171" s="35"/>
+      <c r="N171" s="24"/>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="3" t="s">
@@ -7371,30 +7411,30 @@
       <c r="B172" s="4">
         <v>44817</v>
       </c>
-      <c r="C172" s="29">
+      <c r="C172" s="18">
         <v>44818</v>
       </c>
-      <c r="D172" s="30"/>
+      <c r="D172" s="19"/>
       <c r="E172" s="4">
         <v>44911</v>
       </c>
-      <c r="F172" s="31" t="s">
+      <c r="F172" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G172" s="32"/>
-      <c r="H172" s="30"/>
-      <c r="I172" s="31" t="s">
+      <c r="G172" s="21"/>
+      <c r="H172" s="19"/>
+      <c r="I172" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J172" s="30"/>
-      <c r="K172" s="33">
+      <c r="J172" s="19"/>
+      <c r="K172" s="22">
         <v>10</v>
       </c>
-      <c r="L172" s="30"/>
-      <c r="M172" s="34" t="s">
+      <c r="L172" s="19"/>
+      <c r="M172" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="N172" s="35"/>
+      <c r="N172" s="24"/>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="1" t="s">
@@ -7403,30 +7443,30 @@
       <c r="B173" s="2">
         <v>44817</v>
       </c>
-      <c r="C173" s="36">
+      <c r="C173" s="25">
         <v>44818</v>
       </c>
-      <c r="D173" s="30"/>
+      <c r="D173" s="19"/>
       <c r="E173" s="2">
         <v>44876</v>
       </c>
-      <c r="F173" s="37" t="s">
+      <c r="F173" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="G173" s="32"/>
-      <c r="H173" s="30"/>
-      <c r="I173" s="37" t="s">
+      <c r="G173" s="21"/>
+      <c r="H173" s="19"/>
+      <c r="I173" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J173" s="30"/>
-      <c r="K173" s="38">
+      <c r="J173" s="19"/>
+      <c r="K173" s="27">
         <v>69</v>
       </c>
-      <c r="L173" s="30"/>
-      <c r="M173" s="39" t="s">
+      <c r="L173" s="19"/>
+      <c r="M173" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="N173" s="35"/>
+      <c r="N173" s="24"/>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="3" t="s">
@@ -7435,30 +7475,30 @@
       <c r="B174" s="4">
         <v>44810</v>
       </c>
-      <c r="C174" s="29">
+      <c r="C174" s="18">
         <v>44819</v>
       </c>
-      <c r="D174" s="30"/>
+      <c r="D174" s="19"/>
       <c r="E174" s="4">
         <v>44870</v>
       </c>
-      <c r="F174" s="31" t="s">
+      <c r="F174" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G174" s="32"/>
-      <c r="H174" s="30"/>
-      <c r="I174" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J174" s="30"/>
-      <c r="K174" s="33">
+      <c r="G174" s="21"/>
+      <c r="H174" s="19"/>
+      <c r="I174" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="19"/>
+      <c r="K174" s="22">
         <v>115</v>
       </c>
-      <c r="L174" s="30"/>
-      <c r="M174" s="34" t="s">
+      <c r="L174" s="19"/>
+      <c r="M174" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="N174" s="35"/>
+      <c r="N174" s="24"/>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="1" t="s">
@@ -7467,30 +7507,30 @@
       <c r="B175" s="2">
         <v>44806</v>
       </c>
-      <c r="C175" s="36">
+      <c r="C175" s="25">
         <v>44819</v>
       </c>
-      <c r="D175" s="30"/>
+      <c r="D175" s="19"/>
       <c r="E175" s="2">
         <v>44867</v>
       </c>
-      <c r="F175" s="37" t="s">
+      <c r="F175" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="G175" s="32"/>
-      <c r="H175" s="30"/>
-      <c r="I175" s="37" t="s">
+      <c r="G175" s="21"/>
+      <c r="H175" s="19"/>
+      <c r="I175" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J175" s="30"/>
-      <c r="K175" s="38">
+      <c r="J175" s="19"/>
+      <c r="K175" s="27">
         <v>109</v>
       </c>
-      <c r="L175" s="30"/>
-      <c r="M175" s="39" t="s">
+      <c r="L175" s="19"/>
+      <c r="M175" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="N175" s="35"/>
+      <c r="N175" s="24"/>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="3" t="s">
@@ -7499,30 +7539,30 @@
       <c r="B176" s="4">
         <v>44818</v>
       </c>
-      <c r="C176" s="29">
+      <c r="C176" s="18">
         <v>44819</v>
       </c>
-      <c r="D176" s="30"/>
+      <c r="D176" s="19"/>
       <c r="E176" s="4">
         <v>44883</v>
       </c>
-      <c r="F176" s="31" t="s">
+      <c r="F176" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G176" s="32"/>
-      <c r="H176" s="30"/>
-      <c r="I176" s="31" t="s">
+      <c r="G176" s="21"/>
+      <c r="H176" s="19"/>
+      <c r="I176" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J176" s="30"/>
-      <c r="K176" s="33">
+      <c r="J176" s="19"/>
+      <c r="K176" s="22">
         <v>113</v>
       </c>
-      <c r="L176" s="30"/>
-      <c r="M176" s="34" t="s">
+      <c r="L176" s="19"/>
+      <c r="M176" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="N176" s="35"/>
+      <c r="N176" s="24"/>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="1" t="s">
@@ -7531,30 +7571,30 @@
       <c r="B177" s="2">
         <v>44818</v>
       </c>
-      <c r="C177" s="36">
+      <c r="C177" s="25">
         <v>44819</v>
       </c>
-      <c r="D177" s="30"/>
+      <c r="D177" s="19"/>
       <c r="E177" s="2">
         <v>44872</v>
       </c>
-      <c r="F177" s="37" t="s">
+      <c r="F177" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="G177" s="32"/>
-      <c r="H177" s="30"/>
-      <c r="I177" s="37" t="s">
+      <c r="G177" s="21"/>
+      <c r="H177" s="19"/>
+      <c r="I177" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J177" s="30"/>
-      <c r="K177" s="38">
+      <c r="J177" s="19"/>
+      <c r="K177" s="27">
         <v>13</v>
       </c>
-      <c r="L177" s="30"/>
-      <c r="M177" s="39" t="s">
+      <c r="L177" s="19"/>
+      <c r="M177" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="N177" s="35"/>
+      <c r="N177" s="24"/>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="3" t="s">
@@ -7563,30 +7603,30 @@
       <c r="B178" s="4">
         <v>44818</v>
       </c>
-      <c r="C178" s="29">
+      <c r="C178" s="18">
         <v>44819</v>
       </c>
-      <c r="D178" s="30"/>
+      <c r="D178" s="19"/>
       <c r="E178" s="4">
         <v>44818</v>
       </c>
-      <c r="F178" s="31" t="s">
+      <c r="F178" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="G178" s="32"/>
-      <c r="H178" s="30"/>
-      <c r="I178" s="31" t="s">
+      <c r="G178" s="21"/>
+      <c r="H178" s="19"/>
+      <c r="I178" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J178" s="30"/>
-      <c r="K178" s="33">
+      <c r="J178" s="19"/>
+      <c r="K178" s="22">
         <v>1</v>
       </c>
-      <c r="L178" s="30"/>
-      <c r="M178" s="34" t="s">
+      <c r="L178" s="19"/>
+      <c r="M178" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="N178" s="35"/>
+      <c r="N178" s="24"/>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="1" t="s">
@@ -7595,30 +7635,30 @@
       <c r="B179" s="2">
         <v>44811</v>
       </c>
-      <c r="C179" s="36">
+      <c r="C179" s="25">
         <v>44819</v>
       </c>
-      <c r="D179" s="30"/>
+      <c r="D179" s="19"/>
       <c r="E179" s="2">
         <v>44895</v>
       </c>
-      <c r="F179" s="37" t="s">
+      <c r="F179" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="G179" s="32"/>
-      <c r="H179" s="30"/>
-      <c r="I179" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J179" s="30"/>
-      <c r="K179" s="38">
+      <c r="G179" s="21"/>
+      <c r="H179" s="19"/>
+      <c r="I179" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="19"/>
+      <c r="K179" s="27">
         <v>137</v>
       </c>
-      <c r="L179" s="30"/>
-      <c r="M179" s="39" t="s">
+      <c r="L179" s="19"/>
+      <c r="M179" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="N179" s="35"/>
+      <c r="N179" s="24"/>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="3" t="s">
@@ -7627,30 +7667,30 @@
       <c r="B180" s="4">
         <v>44812</v>
       </c>
-      <c r="C180" s="29">
+      <c r="C180" s="18">
         <v>44819</v>
       </c>
-      <c r="D180" s="30"/>
+      <c r="D180" s="19"/>
       <c r="E180" s="4">
         <v>44873</v>
       </c>
-      <c r="F180" s="31" t="s">
+      <c r="F180" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="G180" s="32"/>
-      <c r="H180" s="30"/>
-      <c r="I180" s="31" t="s">
+      <c r="G180" s="21"/>
+      <c r="H180" s="19"/>
+      <c r="I180" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J180" s="30"/>
-      <c r="K180" s="33">
+      <c r="J180" s="19"/>
+      <c r="K180" s="22">
         <v>73</v>
       </c>
-      <c r="L180" s="30"/>
-      <c r="M180" s="34" t="s">
+      <c r="L180" s="19"/>
+      <c r="M180" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="N180" s="35"/>
+      <c r="N180" s="24"/>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="1" t="s">
@@ -7659,30 +7699,30 @@
       <c r="B181" s="2">
         <v>44818</v>
       </c>
-      <c r="C181" s="36">
+      <c r="C181" s="25">
         <v>44819</v>
       </c>
-      <c r="D181" s="30"/>
+      <c r="D181" s="19"/>
       <c r="E181" s="2">
         <v>44880</v>
       </c>
-      <c r="F181" s="37" t="s">
+      <c r="F181" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="G181" s="32"/>
-      <c r="H181" s="30"/>
-      <c r="I181" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J181" s="30"/>
-      <c r="K181" s="38">
+      <c r="G181" s="21"/>
+      <c r="H181" s="19"/>
+      <c r="I181" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="19"/>
+      <c r="K181" s="27">
         <v>108</v>
       </c>
-      <c r="L181" s="30"/>
-      <c r="M181" s="39" t="s">
+      <c r="L181" s="19"/>
+      <c r="M181" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="N181" s="35"/>
+      <c r="N181" s="24"/>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="3" t="s">
@@ -7691,30 +7731,30 @@
       <c r="B182" s="4">
         <v>44812</v>
       </c>
-      <c r="C182" s="29">
+      <c r="C182" s="18">
         <v>44820</v>
       </c>
-      <c r="D182" s="30"/>
+      <c r="D182" s="19"/>
       <c r="E182" s="4">
         <v>44873</v>
       </c>
-      <c r="F182" s="31" t="s">
+      <c r="F182" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G182" s="32"/>
-      <c r="H182" s="30"/>
-      <c r="I182" s="31" t="s">
+      <c r="G182" s="21"/>
+      <c r="H182" s="19"/>
+      <c r="I182" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J182" s="30"/>
-      <c r="K182" s="33">
+      <c r="J182" s="19"/>
+      <c r="K182" s="22">
         <v>49</v>
       </c>
-      <c r="L182" s="30"/>
-      <c r="M182" s="34" t="s">
+      <c r="L182" s="19"/>
+      <c r="M182" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="N182" s="35"/>
+      <c r="N182" s="24"/>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="1" t="s">
@@ -7723,30 +7763,30 @@
       <c r="B183" s="2">
         <v>44812</v>
       </c>
-      <c r="C183" s="36">
+      <c r="C183" s="25">
         <v>44820</v>
       </c>
-      <c r="D183" s="30"/>
+      <c r="D183" s="19"/>
       <c r="E183" s="2">
         <v>44873</v>
       </c>
-      <c r="F183" s="37" t="s">
+      <c r="F183" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="G183" s="32"/>
-      <c r="H183" s="30"/>
-      <c r="I183" s="37" t="s">
+      <c r="G183" s="21"/>
+      <c r="H183" s="19"/>
+      <c r="I183" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J183" s="30"/>
-      <c r="K183" s="38">
+      <c r="J183" s="19"/>
+      <c r="K183" s="27">
         <v>49</v>
       </c>
-      <c r="L183" s="30"/>
-      <c r="M183" s="39" t="s">
+      <c r="L183" s="19"/>
+      <c r="M183" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="N183" s="35"/>
+      <c r="N183" s="24"/>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="3" t="s">
@@ -7755,30 +7795,30 @@
       <c r="B184" s="4">
         <v>44812</v>
       </c>
-      <c r="C184" s="29">
+      <c r="C184" s="18">
         <v>44820</v>
       </c>
-      <c r="D184" s="30"/>
+      <c r="D184" s="19"/>
       <c r="E184" s="4">
         <v>44873</v>
       </c>
-      <c r="F184" s="31" t="s">
+      <c r="F184" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G184" s="32"/>
-      <c r="H184" s="30"/>
-      <c r="I184" s="31" t="s">
+      <c r="G184" s="21"/>
+      <c r="H184" s="19"/>
+      <c r="I184" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J184" s="30"/>
-      <c r="K184" s="33">
+      <c r="J184" s="19"/>
+      <c r="K184" s="22">
         <v>41</v>
       </c>
-      <c r="L184" s="30"/>
-      <c r="M184" s="34" t="s">
+      <c r="L184" s="19"/>
+      <c r="M184" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="N184" s="35"/>
+      <c r="N184" s="24"/>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="1" t="s">
@@ -7787,30 +7827,30 @@
       <c r="B185" s="2">
         <v>44820</v>
       </c>
-      <c r="C185" s="36">
+      <c r="C185" s="25">
         <v>44820</v>
       </c>
-      <c r="D185" s="30"/>
+      <c r="D185" s="19"/>
       <c r="E185" s="2">
         <v>44880</v>
       </c>
-      <c r="F185" s="37" t="s">
+      <c r="F185" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="G185" s="32"/>
-      <c r="H185" s="30"/>
-      <c r="I185" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J185" s="30"/>
-      <c r="K185" s="38">
+      <c r="G185" s="21"/>
+      <c r="H185" s="19"/>
+      <c r="I185" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="19"/>
+      <c r="K185" s="27">
         <v>66</v>
       </c>
-      <c r="L185" s="30"/>
-      <c r="M185" s="39" t="s">
+      <c r="L185" s="19"/>
+      <c r="M185" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="N185" s="35"/>
+      <c r="N185" s="24"/>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="3" t="s">
@@ -7819,94 +7859,94 @@
       <c r="B186" s="4">
         <v>44823</v>
       </c>
-      <c r="C186" s="29">
+      <c r="C186" s="18">
         <v>44823</v>
       </c>
-      <c r="D186" s="30"/>
+      <c r="D186" s="19"/>
       <c r="E186" s="4">
         <v>44883</v>
       </c>
-      <c r="F186" s="31" t="s">
+      <c r="F186" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="G186" s="32"/>
-      <c r="H186" s="30"/>
-      <c r="I186" s="31" t="s">
+      <c r="G186" s="21"/>
+      <c r="H186" s="19"/>
+      <c r="I186" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J186" s="30"/>
-      <c r="K186" s="33">
+      <c r="J186" s="19"/>
+      <c r="K186" s="22">
         <v>57</v>
       </c>
-      <c r="L186" s="30"/>
-      <c r="M186" s="34" t="s">
+      <c r="L186" s="19"/>
+      <c r="M186" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="N186" s="35"/>
+      <c r="N186" s="24"/>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B187" s="2">
         <v>44823</v>
       </c>
-      <c r="C187" s="36">
+      <c r="C187" s="25">
         <v>44824</v>
       </c>
-      <c r="D187" s="30"/>
+      <c r="D187" s="19"/>
       <c r="E187" s="2">
-        <v>44883</v>
-      </c>
-      <c r="F187" s="37" t="s">
+        <v>44882</v>
+      </c>
+      <c r="F187" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="G187" s="32"/>
-      <c r="H187" s="30"/>
-      <c r="I187" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J187" s="30"/>
-      <c r="K187" s="38">
-        <v>39</v>
-      </c>
-      <c r="L187" s="30"/>
-      <c r="M187" s="39" t="s">
+      <c r="G187" s="21"/>
+      <c r="H187" s="19"/>
+      <c r="I187" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J187" s="19"/>
+      <c r="K187" s="27">
+        <v>88</v>
+      </c>
+      <c r="L187" s="19"/>
+      <c r="M187" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="N187" s="35"/>
+      <c r="N187" s="24"/>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B188" s="4">
-        <v>44823</v>
-      </c>
-      <c r="C188" s="29">
         <v>44824</v>
       </c>
-      <c r="D188" s="30"/>
+      <c r="C188" s="18">
+        <v>44824</v>
+      </c>
+      <c r="D188" s="19"/>
       <c r="E188" s="4">
-        <v>44885</v>
-      </c>
-      <c r="F188" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="G188" s="32"/>
-      <c r="H188" s="30"/>
-      <c r="I188" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J188" s="30"/>
-      <c r="K188" s="33">
-        <v>1</v>
-      </c>
-      <c r="L188" s="30"/>
-      <c r="M188" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="N188" s="35"/>
+        <v>44886</v>
+      </c>
+      <c r="F188" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="G188" s="21"/>
+      <c r="H188" s="19"/>
+      <c r="I188" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J188" s="19"/>
+      <c r="K188" s="22">
+        <v>79</v>
+      </c>
+      <c r="L188" s="19"/>
+      <c r="M188" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="N188" s="24"/>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="1" t="s">
@@ -7915,331 +7955,479 @@
       <c r="B189" s="2">
         <v>44823</v>
       </c>
-      <c r="C189" s="36">
-        <v>44824</v>
-      </c>
-      <c r="D189" s="30"/>
+      <c r="C189" s="25">
+        <v>44825</v>
+      </c>
+      <c r="D189" s="19"/>
       <c r="E189" s="2">
-        <v>44886</v>
-      </c>
-      <c r="F189" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="G189" s="32"/>
-      <c r="H189" s="30"/>
-      <c r="I189" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J189" s="30"/>
-      <c r="K189" s="38">
-        <v>1</v>
-      </c>
-      <c r="L189" s="30"/>
-      <c r="M189" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="N189" s="35"/>
+        <v>44883</v>
+      </c>
+      <c r="F189" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="G189" s="21"/>
+      <c r="H189" s="19"/>
+      <c r="I189" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="19"/>
+      <c r="K189" s="27">
+        <v>49</v>
+      </c>
+      <c r="L189" s="19"/>
+      <c r="M189" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="N189" s="24"/>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="3" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="B190" s="4">
-        <v>44823</v>
-      </c>
-      <c r="C190" s="29">
         <v>44824</v>
       </c>
-      <c r="D190" s="30"/>
+      <c r="C190" s="18">
+        <v>44825</v>
+      </c>
+      <c r="D190" s="19"/>
       <c r="E190" s="4">
-        <v>44926</v>
-      </c>
-      <c r="F190" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="G190" s="32"/>
-      <c r="H190" s="30"/>
-      <c r="I190" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J190" s="30"/>
-      <c r="K190" s="33">
-        <v>1</v>
-      </c>
-      <c r="L190" s="30"/>
-      <c r="M190" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="N190" s="35"/>
+        <v>44872</v>
+      </c>
+      <c r="F190" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="G190" s="21"/>
+      <c r="H190" s="19"/>
+      <c r="I190" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="19"/>
+      <c r="K190" s="22">
+        <v>104</v>
+      </c>
+      <c r="L190" s="19"/>
+      <c r="M190" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="N190" s="24"/>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="1" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="B191" s="2">
-        <v>44823</v>
-      </c>
-      <c r="C191" s="36">
         <v>44824</v>
       </c>
-      <c r="D191" s="30"/>
+      <c r="C191" s="25">
+        <v>44825</v>
+      </c>
+      <c r="D191" s="19"/>
       <c r="E191" s="2">
-        <v>44957</v>
-      </c>
-      <c r="F191" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="G191" s="32"/>
-      <c r="H191" s="30"/>
-      <c r="I191" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J191" s="30"/>
-      <c r="K191" s="38">
+        <v>44872</v>
+      </c>
+      <c r="F191" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="G191" s="21"/>
+      <c r="H191" s="19"/>
+      <c r="I191" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="19"/>
+      <c r="K191" s="27">
         <v>7</v>
       </c>
-      <c r="L191" s="30"/>
-      <c r="M191" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="N191" s="35"/>
+      <c r="L191" s="19"/>
+      <c r="M191" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="N191" s="24"/>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="3" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="B192" s="4">
-        <v>44823</v>
-      </c>
-      <c r="C192" s="29">
-        <v>44824</v>
-      </c>
-      <c r="D192" s="30"/>
+        <v>44826</v>
+      </c>
+      <c r="C192" s="18">
+        <v>44826</v>
+      </c>
+      <c r="D192" s="19"/>
       <c r="E192" s="4">
-        <v>44882</v>
-      </c>
-      <c r="F192" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="G192" s="32"/>
-      <c r="H192" s="30"/>
-      <c r="I192" s="31" t="s">
+        <v>44888</v>
+      </c>
+      <c r="F192" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G192" s="21"/>
+      <c r="H192" s="19"/>
+      <c r="I192" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J192" s="30"/>
-      <c r="K192" s="33">
-        <v>88</v>
-      </c>
-      <c r="L192" s="30"/>
-      <c r="M192" s="34" t="s">
-        <v>314</v>
-      </c>
-      <c r="N192" s="35"/>
+      <c r="J192" s="19"/>
+      <c r="K192" s="22">
+        <v>15</v>
+      </c>
+      <c r="L192" s="19"/>
+      <c r="M192" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="N192" s="24"/>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B193" s="2">
-        <v>44824</v>
-      </c>
-      <c r="C193" s="36">
-        <v>44824</v>
-      </c>
-      <c r="D193" s="30"/>
+        <v>44825</v>
+      </c>
+      <c r="C193" s="25">
+        <v>44826</v>
+      </c>
+      <c r="D193" s="19"/>
       <c r="E193" s="2">
-        <v>44886</v>
-      </c>
-      <c r="F193" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G193" s="32"/>
-      <c r="H193" s="30"/>
-      <c r="I193" s="37" t="s">
+        <v>44867</v>
+      </c>
+      <c r="F193" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="G193" s="21"/>
+      <c r="H193" s="19"/>
+      <c r="I193" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="J193" s="30"/>
-      <c r="K193" s="38">
-        <v>79</v>
-      </c>
-      <c r="L193" s="30"/>
-      <c r="M193" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="N193" s="35"/>
+      <c r="J193" s="19"/>
+      <c r="K193" s="27">
+        <v>18</v>
+      </c>
+      <c r="L193" s="19"/>
+      <c r="M193" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="N193" s="24"/>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B194" s="4">
-        <v>44823</v>
-      </c>
-      <c r="C194" s="29">
         <v>44825</v>
       </c>
-      <c r="D194" s="30"/>
+      <c r="C194" s="18">
+        <v>44826</v>
+      </c>
+      <c r="D194" s="19"/>
       <c r="E194" s="4">
-        <v>44883</v>
-      </c>
-      <c r="F194" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="G194" s="32"/>
-      <c r="H194" s="30"/>
-      <c r="I194" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J194" s="30"/>
-      <c r="K194" s="33">
-        <v>49</v>
-      </c>
-      <c r="L194" s="30"/>
-      <c r="M194" s="34" t="s">
-        <v>318</v>
-      </c>
-      <c r="N194" s="35"/>
+        <v>44867</v>
+      </c>
+      <c r="F194" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="G194" s="21"/>
+      <c r="H194" s="19"/>
+      <c r="I194" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J194" s="19"/>
+      <c r="K194" s="22">
+        <v>69</v>
+      </c>
+      <c r="L194" s="19"/>
+      <c r="M194" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="N194" s="24"/>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="1" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="B195" s="2">
-        <v>44824</v>
-      </c>
-      <c r="C195" s="36">
         <v>44825</v>
       </c>
-      <c r="D195" s="30"/>
+      <c r="C195" s="25">
+        <v>44826</v>
+      </c>
+      <c r="D195" s="19"/>
       <c r="E195" s="2">
-        <v>44872</v>
-      </c>
-      <c r="F195" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="G195" s="32"/>
-      <c r="H195" s="30"/>
-      <c r="I195" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J195" s="30"/>
-      <c r="K195" s="38">
-        <v>104</v>
-      </c>
-      <c r="L195" s="30"/>
-      <c r="M195" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="N195" s="35"/>
+        <v>44867</v>
+      </c>
+      <c r="F195" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G195" s="21"/>
+      <c r="H195" s="19"/>
+      <c r="I195" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J195" s="19"/>
+      <c r="K195" s="27">
+        <v>11</v>
+      </c>
+      <c r="L195" s="19"/>
+      <c r="M195" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="N195" s="24"/>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="3" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="B196" s="4">
-        <v>44824</v>
-      </c>
-      <c r="C196" s="29">
         <v>44825</v>
       </c>
-      <c r="D196" s="30"/>
+      <c r="C196" s="18">
+        <v>44826</v>
+      </c>
+      <c r="D196" s="19"/>
       <c r="E196" s="4">
-        <v>44872</v>
-      </c>
-      <c r="F196" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="G196" s="32"/>
-      <c r="H196" s="30"/>
-      <c r="I196" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J196" s="30"/>
-      <c r="K196" s="33">
-        <v>7</v>
-      </c>
-      <c r="L196" s="30"/>
-      <c r="M196" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="N196" s="35"/>
-    </row>
-    <row r="197" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A197" s="48" t="s">
+        <v>44867</v>
+      </c>
+      <c r="F196" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="G196" s="21"/>
+      <c r="H196" s="19"/>
+      <c r="I196" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J196" s="19"/>
+      <c r="K196" s="22">
+        <v>2</v>
+      </c>
+      <c r="L196" s="19"/>
+      <c r="M196" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="N196" s="24"/>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="A197" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B197" s="2">
+        <v>44827</v>
+      </c>
+      <c r="C197" s="25">
+        <v>44827</v>
+      </c>
+      <c r="D197" s="19"/>
+      <c r="E197" s="2">
+        <v>44888</v>
+      </c>
+      <c r="F197" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="G197" s="21"/>
+      <c r="H197" s="19"/>
+      <c r="I197" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="19"/>
+      <c r="K197" s="27">
+        <v>72</v>
+      </c>
+      <c r="L197" s="19"/>
+      <c r="M197" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="N197" s="24"/>
+    </row>
+    <row r="198" spans="1:14">
+      <c r="A198" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" s="4">
+        <v>44830</v>
+      </c>
+      <c r="C198" s="18">
+        <v>44830</v>
+      </c>
+      <c r="D198" s="19"/>
+      <c r="E198" s="4">
+        <v>44891</v>
+      </c>
+      <c r="F198" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G198" s="21"/>
+      <c r="H198" s="19"/>
+      <c r="I198" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="19"/>
+      <c r="K198" s="22">
+        <v>51</v>
+      </c>
+      <c r="L198" s="19"/>
+      <c r="M198" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="B197" s="49"/>
-      <c r="C197" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="D197" s="46"/>
-      <c r="E197" s="47"/>
-      <c r="F197" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="G197" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="H197" s="45" t="s">
-        <v>325</v>
-      </c>
-      <c r="I197" s="47"/>
-      <c r="J197" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="K197" s="47"/>
-      <c r="L197" s="45" t="s">
-        <v>327</v>
-      </c>
-      <c r="M197" s="47"/>
-      <c r="N197" s="12" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14" s="10" customFormat="1">
-      <c r="A198" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="B198" s="44"/>
-      <c r="C198" s="40">
-        <v>13168</v>
-      </c>
-      <c r="D198" s="41"/>
-      <c r="E198" s="42"/>
-      <c r="F198" s="7">
-        <v>115</v>
-      </c>
-      <c r="G198" s="8">
+      <c r="N198" s="24"/>
+    </row>
+    <row r="199" spans="1:14">
+      <c r="A199" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B199" s="2">
+        <v>44830</v>
+      </c>
+      <c r="C199" s="25">
+        <v>44830</v>
+      </c>
+      <c r="D199" s="19"/>
+      <c r="E199" s="2">
+        <v>44892</v>
+      </c>
+      <c r="F199" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="G199" s="21"/>
+      <c r="H199" s="19"/>
+      <c r="I199" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="19"/>
+      <c r="K199" s="27">
+        <v>353</v>
+      </c>
+      <c r="L199" s="19"/>
+      <c r="M199" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="N199" s="24"/>
+    </row>
+    <row r="200" spans="1:14">
+      <c r="A200" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B200" s="4">
+        <v>44830</v>
+      </c>
+      <c r="C200" s="18">
+        <v>44830</v>
+      </c>
+      <c r="D200" s="19"/>
+      <c r="E200" s="4">
+        <v>44891</v>
+      </c>
+      <c r="F200" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G200" s="21"/>
+      <c r="H200" s="19"/>
+      <c r="I200" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="19"/>
+      <c r="K200" s="22">
+        <v>46</v>
+      </c>
+      <c r="L200" s="19"/>
+      <c r="M200" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="N200" s="24"/>
+    </row>
+    <row r="201" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A201" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="B201" s="48"/>
+      <c r="C201" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="D201" s="45"/>
+      <c r="E201" s="46"/>
+      <c r="F201" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="H201" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I201" s="46"/>
+      <c r="J201" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="K201" s="46"/>
+      <c r="L201" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="M201" s="46"/>
+      <c r="N201" s="10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" s="8" customFormat="1">
+      <c r="A202" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="B202" s="43"/>
+      <c r="C202" s="39">
+        <v>13756</v>
+      </c>
+      <c r="D202" s="40"/>
+      <c r="E202" s="41"/>
+      <c r="F202" s="5">
+        <v>114</v>
+      </c>
+      <c r="G202" s="6">
         <v>5</v>
       </c>
-      <c r="H198" s="40">
+      <c r="H202" s="39">
         <v>1</v>
       </c>
-      <c r="I198" s="42"/>
-      <c r="J198" s="40">
-        <v>70</v>
-      </c>
-      <c r="K198" s="42"/>
-      <c r="L198" s="40">
+      <c r="I202" s="41"/>
+      <c r="J202" s="39">
+        <v>75</v>
+      </c>
+      <c r="K202" s="41"/>
+      <c r="L202" s="39">
         <v>1</v>
       </c>
-      <c r="M198" s="42"/>
-      <c r="N198" s="9">
+      <c r="M202" s="41"/>
+      <c r="N202" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="982">
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="H198:I198"/>
-    <mergeCell ref="J198:K198"/>
-    <mergeCell ref="L198:M198"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="H197:I197"/>
-    <mergeCell ref="J197:K197"/>
-    <mergeCell ref="L197:M197"/>
-    <mergeCell ref="A197:B197"/>
+  <mergeCells count="1002">
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="H202:I202"/>
+    <mergeCell ref="J202:K202"/>
+    <mergeCell ref="L202:M202"/>
+    <mergeCell ref="A202:B202"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="H201:I201"/>
+    <mergeCell ref="J201:K201"/>
+    <mergeCell ref="L201:M201"/>
+    <mergeCell ref="A201:B201"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="F200:H200"/>
+    <mergeCell ref="I200:J200"/>
+    <mergeCell ref="K200:L200"/>
+    <mergeCell ref="M200:N200"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="F199:H199"/>
+    <mergeCell ref="I199:J199"/>
+    <mergeCell ref="K199:L199"/>
+    <mergeCell ref="M199:N199"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:H198"/>
+    <mergeCell ref="I198:J198"/>
+    <mergeCell ref="K198:L198"/>
+    <mergeCell ref="M198:N198"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:H197"/>
+    <mergeCell ref="I197:J197"/>
+    <mergeCell ref="K197:L197"/>
+    <mergeCell ref="M197:N197"/>
     <mergeCell ref="C196:D196"/>
     <mergeCell ref="F196:H196"/>
     <mergeCell ref="I196:J196"/>
@@ -9190,6 +9378,8 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="I6:J6"/>
@@ -9200,8 +9390,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:J4"/>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14940" windowHeight="8292"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12432"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="358">
   <si>
     <t/>
   </si>
@@ -1070,6 +1070,39 @@
     <t>990 Hamilton Court  Menlo Park CA 94025</t>
   </si>
   <si>
+    <t>Dreyer's Grand Ice Cream, Inc.</t>
+  </si>
+  <si>
+    <t>7301 District Blvd.  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>Hallcon Corporation</t>
+  </si>
+  <si>
+    <t>1200 Mississippi Road  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>970 E. Continental Ave.  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC and NBC West, LLC</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldgs. 1440 and 1460  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>Lucas Oil Products, Inc. with subsidiaries of Mav'rick Entertainment Network, Inc.</t>
+  </si>
+  <si>
+    <t>302 N. Sheridan St.  Corona CA 92878</t>
+  </si>
+  <si>
+    <t>Amentum</t>
+  </si>
+  <si>
+    <t>Bldg. 873 Rogers Rd. NAS North Island  San Diego CA 92135</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1099,11 +1132,11 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 9/26/2022
+ End Date: 9/28/2022
 </t>
   </si>
   <si>
-    <t>Report Summary</t>
+    <t xml:space="preserve">Report Summary </t>
   </si>
 </sst>
 </file>
@@ -1527,11 +1560,12 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1543,7 +1577,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1556,10 +1589,40 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1594,36 +1657,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1935,66 +1968,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R202"/>
+  <dimension ref="A1:R208"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="2.5546875" customWidth="1"/>
-    <col min="4" max="4" width="6.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" customWidth="1"/>
-    <col min="9" max="9" width="5.88671875" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" customWidth="1"/>
-    <col min="13" max="13" width="7.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" customWidth="1"/>
+    <col min="11" max="11" width="5" customWidth="1"/>
+    <col min="12" max="12" width="5.88671875" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-    </row>
-    <row r="2" spans="1:18" ht="37.5" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+      <c r="A1" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="39.75" customHeight="1">
+      <c r="A2" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="12" t="s">
@@ -2003,30 +2036,30 @@
       <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="35"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="34" t="s">
+      <c r="G3" s="23"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="34" t="s">
+      <c r="J3" s="22"/>
+      <c r="K3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="37" t="s">
+      <c r="L3" s="22"/>
+      <c r="M3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="38"/>
+      <c r="N3" s="25"/>
     </row>
     <row r="4" spans="1:18" ht="24.6">
       <c r="A4" s="14" t="s">
@@ -2035,30 +2068,30 @@
       <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="30"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="29" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="30"/>
-      <c r="K4" s="29" t="s">
+      <c r="J4" s="17"/>
+      <c r="K4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="30"/>
-      <c r="M4" s="32" t="s">
+      <c r="L4" s="17"/>
+      <c r="M4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="33"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -2067,30 +2100,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="35">
         <v>44750</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="26" t="s">
+      <c r="G5" s="31"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="27">
+      <c r="J5" s="29"/>
+      <c r="K5" s="37">
         <v>2</v>
       </c>
-      <c r="L5" s="19"/>
-      <c r="M5" s="28" t="s">
+      <c r="L5" s="29"/>
+      <c r="M5" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="24"/>
+      <c r="N5" s="34"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -2099,30 +2132,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="28">
         <v>44750</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="20" t="s">
+      <c r="G6" s="31"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="22">
+      <c r="J6" s="29"/>
+      <c r="K6" s="32">
         <v>13</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="23" t="s">
+      <c r="L6" s="29"/>
+      <c r="M6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="24"/>
+      <c r="N6" s="34"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -2131,30 +2164,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="35">
         <v>44750</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="29"/>
+      <c r="K7" s="37">
         <v>9</v>
       </c>
-      <c r="L7" s="19"/>
-      <c r="M7" s="28" t="s">
+      <c r="L7" s="29"/>
+      <c r="M7" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="24"/>
+      <c r="N7" s="34"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -2163,30 +2196,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="28">
         <v>44750</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="22">
+      <c r="G8" s="31"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="29"/>
+      <c r="K8" s="32">
         <v>123</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="23" t="s">
+      <c r="L8" s="29"/>
+      <c r="M8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="24"/>
+      <c r="N8" s="34"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -2195,30 +2228,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="35">
         <v>44750</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="29"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="27">
+      <c r="G9" s="31"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="29"/>
+      <c r="K9" s="37">
         <v>37</v>
       </c>
-      <c r="L9" s="19"/>
-      <c r="M9" s="28" t="s">
+      <c r="L9" s="29"/>
+      <c r="M9" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="24"/>
+      <c r="N9" s="34"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -2227,30 +2260,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="28">
         <v>44753</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="22">
+      <c r="G10" s="31"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="32">
         <v>37</v>
       </c>
-      <c r="L10" s="19"/>
-      <c r="M10" s="23" t="s">
+      <c r="L10" s="29"/>
+      <c r="M10" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="24"/>
+      <c r="N10" s="34"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2259,30 +2292,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="35">
         <v>44753</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="29"/>
+      <c r="K11" s="37">
         <v>80</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="28" t="s">
+      <c r="L11" s="29"/>
+      <c r="M11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="24"/>
+      <c r="N11" s="34"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2291,30 +2324,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="28">
         <v>44753</v>
       </c>
-      <c r="D12" s="19"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="20" t="s">
+      <c r="G12" s="31"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="22">
+      <c r="J12" s="29"/>
+      <c r="K12" s="32">
         <v>229</v>
       </c>
-      <c r="L12" s="19"/>
-      <c r="M12" s="23" t="s">
+      <c r="L12" s="29"/>
+      <c r="M12" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="24"/>
+      <c r="N12" s="34"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2323,30 +2356,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="35">
         <v>44753</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="27">
+      <c r="G13" s="31"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="29"/>
+      <c r="K13" s="37">
         <v>368</v>
       </c>
-      <c r="L13" s="19"/>
-      <c r="M13" s="28" t="s">
+      <c r="L13" s="29"/>
+      <c r="M13" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="24"/>
+      <c r="N13" s="34"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2355,30 +2388,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="28">
         <v>44753</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="22">
+      <c r="G14" s="31"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="29"/>
+      <c r="K14" s="32">
         <v>62</v>
       </c>
-      <c r="L14" s="19"/>
-      <c r="M14" s="23" t="s">
+      <c r="L14" s="29"/>
+      <c r="M14" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="24"/>
+      <c r="N14" s="34"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2387,30 +2420,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="35">
         <v>44753</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="27">
+      <c r="G15" s="31"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="29"/>
+      <c r="K15" s="37">
         <v>25</v>
       </c>
-      <c r="L15" s="19"/>
-      <c r="M15" s="28" t="s">
+      <c r="L15" s="29"/>
+      <c r="M15" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="24"/>
+      <c r="N15" s="34"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2419,30 +2452,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="28">
         <v>44753</v>
       </c>
-      <c r="D16" s="19"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="22">
+      <c r="G16" s="31"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="29"/>
+      <c r="K16" s="32">
         <v>68</v>
       </c>
-      <c r="L16" s="19"/>
-      <c r="M16" s="23" t="s">
+      <c r="L16" s="29"/>
+      <c r="M16" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="24"/>
+      <c r="N16" s="34"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2451,30 +2484,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="35">
         <v>44753</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="29"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="29"/>
+      <c r="K17" s="37">
         <v>77</v>
       </c>
-      <c r="L17" s="19"/>
-      <c r="M17" s="28" t="s">
+      <c r="L17" s="29"/>
+      <c r="M17" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="24"/>
+      <c r="N17" s="34"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2483,30 +2516,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="28">
         <v>44754</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="29"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="22">
+      <c r="G18" s="31"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="29"/>
+      <c r="K18" s="32">
         <v>20</v>
       </c>
-      <c r="L18" s="19"/>
-      <c r="M18" s="23" t="s">
+      <c r="L18" s="29"/>
+      <c r="M18" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="24"/>
+      <c r="N18" s="34"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2515,30 +2548,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="35">
         <v>44754</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="27">
+      <c r="G19" s="31"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="29"/>
+      <c r="K19" s="37">
         <v>5</v>
       </c>
-      <c r="L19" s="19"/>
-      <c r="M19" s="28" t="s">
+      <c r="L19" s="29"/>
+      <c r="M19" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="24"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2547,30 +2580,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="28">
         <v>44754</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="22">
+      <c r="G20" s="31"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="29"/>
+      <c r="K20" s="32">
         <v>2</v>
       </c>
-      <c r="L20" s="19"/>
-      <c r="M20" s="23" t="s">
+      <c r="L20" s="29"/>
+      <c r="M20" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="24"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2579,30 +2612,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="35">
         <v>44754</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="27">
+      <c r="G21" s="31"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="29"/>
+      <c r="K21" s="37">
         <v>1</v>
       </c>
-      <c r="L21" s="19"/>
-      <c r="M21" s="28" t="s">
+      <c r="L21" s="29"/>
+      <c r="M21" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="24"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2611,30 +2644,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="28">
         <v>44754</v>
       </c>
-      <c r="D22" s="19"/>
+      <c r="D22" s="29"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="22">
+      <c r="G22" s="31"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="29"/>
+      <c r="K22" s="32">
         <v>41</v>
       </c>
-      <c r="L22" s="19"/>
-      <c r="M22" s="23" t="s">
+      <c r="L22" s="29"/>
+      <c r="M22" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="24"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2643,30 +2676,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="35">
         <v>44754</v>
       </c>
-      <c r="D23" s="19"/>
+      <c r="D23" s="29"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="26" t="s">
+      <c r="G23" s="31"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="27">
+      <c r="J23" s="29"/>
+      <c r="K23" s="37">
         <v>4</v>
       </c>
-      <c r="L23" s="19"/>
-      <c r="M23" s="28" t="s">
+      <c r="L23" s="29"/>
+      <c r="M23" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="24"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2675,30 +2708,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="28">
         <v>44754</v>
       </c>
-      <c r="D24" s="19"/>
+      <c r="D24" s="29"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="21"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="22">
+      <c r="G24" s="31"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="29"/>
+      <c r="K24" s="32">
         <v>211</v>
       </c>
-      <c r="L24" s="19"/>
-      <c r="M24" s="23" t="s">
+      <c r="L24" s="29"/>
+      <c r="M24" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="24"/>
+      <c r="N24" s="34"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2707,30 +2740,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="35">
         <v>44754</v>
       </c>
-      <c r="D25" s="19"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="21"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="26" t="s">
+      <c r="G25" s="31"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="27">
+      <c r="J25" s="29"/>
+      <c r="K25" s="37">
         <v>10</v>
       </c>
-      <c r="L25" s="19"/>
-      <c r="M25" s="28" t="s">
+      <c r="L25" s="29"/>
+      <c r="M25" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="24"/>
+      <c r="N25" s="34"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2739,30 +2772,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="28">
         <v>44754</v>
       </c>
-      <c r="D26" s="19"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="20" t="s">
+      <c r="G26" s="31"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="22">
+      <c r="J26" s="29"/>
+      <c r="K26" s="32">
         <v>1</v>
       </c>
-      <c r="L26" s="19"/>
-      <c r="M26" s="23" t="s">
+      <c r="L26" s="29"/>
+      <c r="M26" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="24"/>
+      <c r="N26" s="34"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2771,30 +2804,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="35">
         <v>44754</v>
       </c>
-      <c r="D27" s="19"/>
+      <c r="D27" s="29"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="F27" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="21"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="27">
+      <c r="G27" s="31"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="29"/>
+      <c r="K27" s="37">
         <v>94</v>
       </c>
-      <c r="L27" s="19"/>
-      <c r="M27" s="28" t="s">
+      <c r="L27" s="29"/>
+      <c r="M27" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="24"/>
+      <c r="N27" s="34"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2803,30 +2836,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="28">
         <v>44754</v>
       </c>
-      <c r="D28" s="19"/>
+      <c r="D28" s="29"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="21"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="20" t="s">
+      <c r="G28" s="31"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="22">
+      <c r="J28" s="29"/>
+      <c r="K28" s="32">
         <v>9</v>
       </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="23" t="s">
+      <c r="L28" s="29"/>
+      <c r="M28" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="24"/>
+      <c r="N28" s="34"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2835,30 +2868,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="35">
         <v>44754</v>
       </c>
-      <c r="D29" s="19"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="21"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="26" t="s">
+      <c r="G29" s="31"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="27">
+      <c r="J29" s="29"/>
+      <c r="K29" s="37">
         <v>6</v>
       </c>
-      <c r="L29" s="19"/>
-      <c r="M29" s="28" t="s">
+      <c r="L29" s="29"/>
+      <c r="M29" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="24"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2867,30 +2900,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="28">
         <v>44754</v>
       </c>
-      <c r="D30" s="19"/>
+      <c r="D30" s="29"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="20" t="s">
+      <c r="G30" s="31"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="22">
-        <v>18</v>
-      </c>
-      <c r="L30" s="19"/>
-      <c r="M30" s="23" t="s">
+      <c r="J30" s="29"/>
+      <c r="K30" s="32">
+        <v>18</v>
+      </c>
+      <c r="L30" s="29"/>
+      <c r="M30" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="24"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2899,30 +2932,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="35">
         <v>44755</v>
       </c>
-      <c r="D31" s="19"/>
+      <c r="D31" s="29"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="21"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="26" t="s">
+      <c r="G31" s="31"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="27">
+      <c r="J31" s="29"/>
+      <c r="K31" s="37">
         <v>76</v>
       </c>
-      <c r="L31" s="19"/>
-      <c r="M31" s="28" t="s">
+      <c r="L31" s="29"/>
+      <c r="M31" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="24"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -2931,30 +2964,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="28">
         <v>44755</v>
       </c>
-      <c r="D32" s="19"/>
+      <c r="D32" s="29"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="21"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="20" t="s">
+      <c r="G32" s="31"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="19"/>
-      <c r="K32" s="22">
+      <c r="J32" s="29"/>
+      <c r="K32" s="32">
         <v>1</v>
       </c>
-      <c r="L32" s="19"/>
-      <c r="M32" s="23" t="s">
+      <c r="L32" s="29"/>
+      <c r="M32" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="24"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -2963,30 +2996,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="35">
         <v>44755</v>
       </c>
-      <c r="D33" s="19"/>
+      <c r="D33" s="29"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="26" t="s">
+      <c r="G33" s="31"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="19"/>
-      <c r="K33" s="27">
+      <c r="J33" s="29"/>
+      <c r="K33" s="37">
         <v>27</v>
       </c>
-      <c r="L33" s="19"/>
-      <c r="M33" s="28" t="s">
+      <c r="L33" s="29"/>
+      <c r="M33" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="24"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -2995,30 +3028,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="28">
         <v>44755</v>
       </c>
-      <c r="D34" s="19"/>
+      <c r="D34" s="29"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="21"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="20" t="s">
+      <c r="G34" s="31"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="22">
+      <c r="J34" s="29"/>
+      <c r="K34" s="32">
         <v>2</v>
       </c>
-      <c r="L34" s="19"/>
-      <c r="M34" s="23" t="s">
+      <c r="L34" s="29"/>
+      <c r="M34" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="24"/>
+      <c r="N34" s="34"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -3027,30 +3060,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="35">
         <v>44756</v>
       </c>
-      <c r="D35" s="19"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="19"/>
-      <c r="K35" s="27">
+      <c r="G35" s="31"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="29"/>
+      <c r="K35" s="37">
         <v>54</v>
       </c>
-      <c r="L35" s="19"/>
-      <c r="M35" s="28" t="s">
+      <c r="L35" s="29"/>
+      <c r="M35" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="24"/>
+      <c r="N35" s="34"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -3059,30 +3092,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="28">
         <v>44756</v>
       </c>
-      <c r="D36" s="19"/>
+      <c r="D36" s="29"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="22">
+      <c r="G36" s="31"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="29"/>
+      <c r="K36" s="32">
         <v>105</v>
       </c>
-      <c r="L36" s="19"/>
-      <c r="M36" s="23" t="s">
+      <c r="L36" s="29"/>
+      <c r="M36" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="24"/>
+      <c r="N36" s="34"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -3091,30 +3124,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="35">
         <v>44756</v>
       </c>
-      <c r="D37" s="19"/>
+      <c r="D37" s="29"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="21"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="19"/>
-      <c r="K37" s="27">
+      <c r="G37" s="31"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="29"/>
+      <c r="K37" s="37">
         <v>71</v>
       </c>
-      <c r="L37" s="19"/>
-      <c r="M37" s="28" t="s">
+      <c r="L37" s="29"/>
+      <c r="M37" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="24"/>
+      <c r="N37" s="34"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -3123,30 +3156,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="28">
         <v>44756</v>
       </c>
-      <c r="D38" s="19"/>
+      <c r="D38" s="29"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="19"/>
-      <c r="K38" s="22">
+      <c r="G38" s="31"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="29"/>
+      <c r="K38" s="32">
         <v>125</v>
       </c>
-      <c r="L38" s="19"/>
-      <c r="M38" s="23" t="s">
+      <c r="L38" s="29"/>
+      <c r="M38" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="24"/>
+      <c r="N38" s="34"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -3155,30 +3188,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="35">
         <v>44756</v>
       </c>
-      <c r="D39" s="19"/>
+      <c r="D39" s="29"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="21"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="27">
+      <c r="G39" s="31"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="29"/>
+      <c r="K39" s="37">
         <v>55</v>
       </c>
-      <c r="L39" s="19"/>
-      <c r="M39" s="28" t="s">
+      <c r="L39" s="29"/>
+      <c r="M39" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="24"/>
+      <c r="N39" s="34"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -3187,30 +3220,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="28">
         <v>44756</v>
       </c>
-      <c r="D40" s="19"/>
+      <c r="D40" s="29"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="21"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="19"/>
-      <c r="K40" s="22">
+      <c r="G40" s="31"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="29"/>
+      <c r="K40" s="32">
         <v>176</v>
       </c>
-      <c r="L40" s="19"/>
-      <c r="M40" s="23" t="s">
+      <c r="L40" s="29"/>
+      <c r="M40" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="24"/>
+      <c r="N40" s="34"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -3219,30 +3252,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="35">
         <v>44757</v>
       </c>
-      <c r="D41" s="19"/>
+      <c r="D41" s="29"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="27">
+      <c r="G41" s="31"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="29"/>
+      <c r="K41" s="37">
         <v>58</v>
       </c>
-      <c r="L41" s="19"/>
-      <c r="M41" s="28" t="s">
+      <c r="L41" s="29"/>
+      <c r="M41" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="24"/>
+      <c r="N41" s="34"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3251,30 +3284,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="28">
         <v>44757</v>
       </c>
-      <c r="D42" s="19"/>
+      <c r="D42" s="29"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="22">
+      <c r="G42" s="31"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="29"/>
+      <c r="K42" s="32">
         <v>180</v>
       </c>
-      <c r="L42" s="19"/>
-      <c r="M42" s="23" t="s">
+      <c r="L42" s="29"/>
+      <c r="M42" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="24"/>
+      <c r="N42" s="34"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3283,30 +3316,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="35">
         <v>44760</v>
       </c>
-      <c r="D43" s="19"/>
+      <c r="D43" s="29"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="21"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="26" t="s">
+      <c r="G43" s="31"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="27">
+      <c r="J43" s="29"/>
+      <c r="K43" s="37">
         <v>142</v>
       </c>
-      <c r="L43" s="19"/>
-      <c r="M43" s="28" t="s">
+      <c r="L43" s="29"/>
+      <c r="M43" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="24"/>
+      <c r="N43" s="34"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3315,30 +3348,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="28">
         <v>44760</v>
       </c>
-      <c r="D44" s="19"/>
+      <c r="D44" s="29"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="21"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="20" t="s">
+      <c r="G44" s="31"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="19"/>
-      <c r="K44" s="22">
+      <c r="J44" s="29"/>
+      <c r="K44" s="32">
         <v>153</v>
       </c>
-      <c r="L44" s="19"/>
-      <c r="M44" s="23" t="s">
+      <c r="L44" s="29"/>
+      <c r="M44" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="24"/>
+      <c r="N44" s="34"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3347,30 +3380,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="35">
         <v>44761</v>
       </c>
-      <c r="D45" s="19"/>
+      <c r="D45" s="29"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="19"/>
-      <c r="K45" s="27">
+      <c r="G45" s="31"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="29"/>
+      <c r="K45" s="37">
         <v>12</v>
       </c>
-      <c r="L45" s="19"/>
-      <c r="M45" s="28" t="s">
+      <c r="L45" s="29"/>
+      <c r="M45" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="24"/>
+      <c r="N45" s="34"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3379,30 +3412,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="28">
         <v>44761</v>
       </c>
-      <c r="D46" s="19"/>
+      <c r="D46" s="29"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="19"/>
-      <c r="K46" s="22">
+      <c r="G46" s="31"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="29"/>
+      <c r="K46" s="32">
         <v>27</v>
       </c>
-      <c r="L46" s="19"/>
-      <c r="M46" s="23" t="s">
+      <c r="L46" s="29"/>
+      <c r="M46" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="24"/>
+      <c r="N46" s="34"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3411,30 +3444,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="35">
         <v>44761</v>
       </c>
-      <c r="D47" s="19"/>
+      <c r="D47" s="29"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="26" t="s">
+      <c r="F47" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="21"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="19"/>
-      <c r="K47" s="27">
+      <c r="G47" s="31"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="29"/>
+      <c r="K47" s="37">
         <v>51</v>
       </c>
-      <c r="L47" s="19"/>
-      <c r="M47" s="28" t="s">
+      <c r="L47" s="29"/>
+      <c r="M47" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="24"/>
+      <c r="N47" s="34"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3443,30 +3476,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="18">
+      <c r="C48" s="28">
         <v>44761</v>
       </c>
-      <c r="D48" s="19"/>
+      <c r="D48" s="29"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="19"/>
-      <c r="K48" s="22">
+      <c r="G48" s="31"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="29"/>
+      <c r="K48" s="32">
         <v>69</v>
       </c>
-      <c r="L48" s="19"/>
-      <c r="M48" s="23" t="s">
+      <c r="L48" s="29"/>
+      <c r="M48" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="24"/>
+      <c r="N48" s="34"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3475,30 +3508,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="35">
         <v>44762</v>
       </c>
-      <c r="D49" s="19"/>
+      <c r="D49" s="29"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="26" t="s">
+      <c r="G49" s="31"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="19"/>
-      <c r="K49" s="27">
+      <c r="J49" s="29"/>
+      <c r="K49" s="37">
         <v>104</v>
       </c>
-      <c r="L49" s="19"/>
-      <c r="M49" s="28" t="s">
+      <c r="L49" s="29"/>
+      <c r="M49" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="24"/>
+      <c r="N49" s="34"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3507,30 +3540,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="28">
         <v>44762</v>
       </c>
-      <c r="D50" s="19"/>
+      <c r="D50" s="29"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="19"/>
-      <c r="K50" s="22">
+      <c r="G50" s="31"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="29"/>
+      <c r="K50" s="32">
         <v>19</v>
       </c>
-      <c r="L50" s="19"/>
-      <c r="M50" s="23" t="s">
+      <c r="L50" s="29"/>
+      <c r="M50" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="24"/>
+      <c r="N50" s="34"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3539,30 +3572,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="35">
         <v>44762</v>
       </c>
-      <c r="D51" s="19"/>
+      <c r="D51" s="29"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="26" t="s">
+      <c r="F51" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="26" t="s">
+      <c r="G51" s="31"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="19"/>
-      <c r="K51" s="27">
+      <c r="J51" s="29"/>
+      <c r="K51" s="37">
         <v>80</v>
       </c>
-      <c r="L51" s="19"/>
-      <c r="M51" s="28" t="s">
+      <c r="L51" s="29"/>
+      <c r="M51" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="24"/>
+      <c r="N51" s="34"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3571,30 +3604,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="28">
         <v>44763</v>
       </c>
-      <c r="D52" s="19"/>
+      <c r="D52" s="29"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="19"/>
-      <c r="K52" s="22">
+      <c r="G52" s="31"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="29"/>
+      <c r="K52" s="32">
         <v>99</v>
       </c>
-      <c r="L52" s="19"/>
-      <c r="M52" s="23" t="s">
+      <c r="L52" s="29"/>
+      <c r="M52" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="24"/>
+      <c r="N52" s="34"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3603,30 +3636,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="35">
         <v>44763</v>
       </c>
-      <c r="D53" s="19"/>
+      <c r="D53" s="29"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="26" t="s">
+      <c r="F53" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="21"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="19"/>
-      <c r="K53" s="27">
+      <c r="G53" s="31"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="29"/>
+      <c r="K53" s="37">
         <v>60</v>
       </c>
-      <c r="L53" s="19"/>
-      <c r="M53" s="28" t="s">
+      <c r="L53" s="29"/>
+      <c r="M53" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="24"/>
+      <c r="N53" s="34"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3635,30 +3668,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="28">
         <v>44763</v>
       </c>
-      <c r="D54" s="19"/>
+      <c r="D54" s="29"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="19"/>
-      <c r="K54" s="22">
+      <c r="G54" s="31"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="29"/>
+      <c r="K54" s="32">
         <v>4</v>
       </c>
-      <c r="L54" s="19"/>
-      <c r="M54" s="23" t="s">
+      <c r="L54" s="29"/>
+      <c r="M54" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="24"/>
+      <c r="N54" s="34"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3667,30 +3700,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="35">
         <v>44763</v>
       </c>
-      <c r="D55" s="19"/>
+      <c r="D55" s="29"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="26" t="s">
+      <c r="F55" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="21"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="19"/>
-      <c r="K55" s="27">
+      <c r="G55" s="31"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="29"/>
+      <c r="K55" s="37">
         <v>26</v>
       </c>
-      <c r="L55" s="19"/>
-      <c r="M55" s="28" t="s">
+      <c r="L55" s="29"/>
+      <c r="M55" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="24"/>
+      <c r="N55" s="34"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3699,30 +3732,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="28">
         <v>44763</v>
       </c>
-      <c r="D56" s="19"/>
+      <c r="D56" s="29"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="21"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="19"/>
-      <c r="K56" s="22">
+      <c r="G56" s="31"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="29"/>
+      <c r="K56" s="32">
         <v>30</v>
       </c>
-      <c r="L56" s="19"/>
-      <c r="M56" s="23" t="s">
+      <c r="L56" s="29"/>
+      <c r="M56" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="24"/>
+      <c r="N56" s="34"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3731,30 +3764,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="35">
         <v>44763</v>
       </c>
-      <c r="D57" s="19"/>
+      <c r="D57" s="29"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="26" t="s">
+      <c r="F57" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="21"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="19"/>
-      <c r="K57" s="27">
+      <c r="G57" s="31"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="29"/>
+      <c r="K57" s="37">
         <v>2</v>
       </c>
-      <c r="L57" s="19"/>
-      <c r="M57" s="28" t="s">
+      <c r="L57" s="29"/>
+      <c r="M57" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="24"/>
+      <c r="N57" s="34"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3763,30 +3796,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="18">
+      <c r="C58" s="28">
         <v>44764</v>
       </c>
-      <c r="D58" s="19"/>
+      <c r="D58" s="29"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="21"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="20" t="s">
+      <c r="G58" s="31"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="19"/>
-      <c r="K58" s="22">
+      <c r="J58" s="29"/>
+      <c r="K58" s="32">
         <v>66</v>
       </c>
-      <c r="L58" s="19"/>
-      <c r="M58" s="23" t="s">
+      <c r="L58" s="29"/>
+      <c r="M58" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="24"/>
+      <c r="N58" s="34"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3795,30 +3828,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="35">
         <v>44764</v>
       </c>
-      <c r="D59" s="19"/>
+      <c r="D59" s="29"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="26" t="s">
+      <c r="F59" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="21"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="26" t="s">
+      <c r="G59" s="31"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="19"/>
-      <c r="K59" s="27">
+      <c r="J59" s="29"/>
+      <c r="K59" s="37">
         <v>85</v>
       </c>
-      <c r="L59" s="19"/>
-      <c r="M59" s="28" t="s">
+      <c r="L59" s="29"/>
+      <c r="M59" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="24"/>
+      <c r="N59" s="34"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3827,30 +3860,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="18">
+      <c r="C60" s="28">
         <v>44764</v>
       </c>
-      <c r="D60" s="19"/>
+      <c r="D60" s="29"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="21"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="22">
+      <c r="G60" s="31"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="29"/>
+      <c r="K60" s="32">
         <v>58</v>
       </c>
-      <c r="L60" s="19"/>
-      <c r="M60" s="23" t="s">
+      <c r="L60" s="29"/>
+      <c r="M60" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="24"/>
+      <c r="N60" s="34"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3859,30 +3892,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="35">
         <v>44764</v>
       </c>
-      <c r="D61" s="19"/>
+      <c r="D61" s="29"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="26" t="s">
+      <c r="F61" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="21"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="19"/>
-      <c r="K61" s="27">
+      <c r="G61" s="31"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="29"/>
+      <c r="K61" s="37">
         <v>80</v>
       </c>
-      <c r="L61" s="19"/>
-      <c r="M61" s="28" t="s">
+      <c r="L61" s="29"/>
+      <c r="M61" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="24"/>
+      <c r="N61" s="34"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3891,30 +3924,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C62" s="28">
         <v>44764</v>
       </c>
-      <c r="D62" s="19"/>
+      <c r="D62" s="29"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="21"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="19"/>
-      <c r="K62" s="22">
+      <c r="G62" s="31"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="29"/>
+      <c r="K62" s="32">
         <v>55</v>
       </c>
-      <c r="L62" s="19"/>
-      <c r="M62" s="23" t="s">
+      <c r="L62" s="29"/>
+      <c r="M62" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="24"/>
+      <c r="N62" s="34"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -3923,30 +3956,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="35">
         <v>44764</v>
       </c>
-      <c r="D63" s="19"/>
+      <c r="D63" s="29"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="26" t="s">
+      <c r="F63" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="26" t="s">
+      <c r="G63" s="31"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="19"/>
-      <c r="K63" s="27">
+      <c r="J63" s="29"/>
+      <c r="K63" s="37">
         <v>14</v>
       </c>
-      <c r="L63" s="19"/>
-      <c r="M63" s="28" t="s">
+      <c r="L63" s="29"/>
+      <c r="M63" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="24"/>
+      <c r="N63" s="34"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -3955,30 +3988,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="18">
+      <c r="C64" s="28">
         <v>44764</v>
       </c>
-      <c r="D64" s="19"/>
+      <c r="D64" s="29"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="21"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="20" t="s">
+      <c r="G64" s="31"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="19"/>
-      <c r="K64" s="22">
+      <c r="J64" s="29"/>
+      <c r="K64" s="32">
         <v>90</v>
       </c>
-      <c r="L64" s="19"/>
-      <c r="M64" s="23" t="s">
+      <c r="L64" s="29"/>
+      <c r="M64" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="24"/>
+      <c r="N64" s="34"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -3987,30 +4020,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="35">
         <v>44767</v>
       </c>
-      <c r="D65" s="19"/>
+      <c r="D65" s="29"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="26" t="s">
+      <c r="F65" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="21"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="26" t="s">
+      <c r="G65" s="31"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="19"/>
-      <c r="K65" s="27">
+      <c r="J65" s="29"/>
+      <c r="K65" s="37">
         <v>331</v>
       </c>
-      <c r="L65" s="19"/>
-      <c r="M65" s="28" t="s">
+      <c r="L65" s="29"/>
+      <c r="M65" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="24"/>
+      <c r="N65" s="34"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -4019,30 +4052,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="28">
         <v>44768</v>
       </c>
-      <c r="D66" s="19"/>
+      <c r="D66" s="29"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="20" t="s">
+      <c r="F66" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="21"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="19"/>
-      <c r="K66" s="22">
+      <c r="G66" s="31"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="29"/>
+      <c r="K66" s="32">
         <v>52</v>
       </c>
-      <c r="L66" s="19"/>
-      <c r="M66" s="23" t="s">
+      <c r="L66" s="29"/>
+      <c r="M66" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="24"/>
+      <c r="N66" s="34"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -4051,30 +4084,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="35">
         <v>44768</v>
       </c>
-      <c r="D67" s="19"/>
+      <c r="D67" s="29"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="26" t="s">
+      <c r="F67" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="21"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="19"/>
-      <c r="K67" s="27">
+      <c r="G67" s="31"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="29"/>
+      <c r="K67" s="37">
         <v>9</v>
       </c>
-      <c r="L67" s="19"/>
-      <c r="M67" s="28" t="s">
+      <c r="L67" s="29"/>
+      <c r="M67" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="24"/>
+      <c r="N67" s="34"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -4083,30 +4116,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="18">
+      <c r="C68" s="28">
         <v>44768</v>
       </c>
-      <c r="D68" s="19"/>
+      <c r="D68" s="29"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="21"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="19"/>
-      <c r="K68" s="22">
+      <c r="G68" s="31"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="29"/>
+      <c r="K68" s="32">
         <v>78</v>
       </c>
-      <c r="L68" s="19"/>
-      <c r="M68" s="23" t="s">
+      <c r="L68" s="29"/>
+      <c r="M68" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="24"/>
+      <c r="N68" s="34"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -4115,30 +4148,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="35">
         <v>44769</v>
       </c>
-      <c r="D69" s="19"/>
+      <c r="D69" s="29"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="26" t="s">
+      <c r="F69" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="21"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="19"/>
-      <c r="K69" s="27">
+      <c r="G69" s="31"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="29"/>
+      <c r="K69" s="37">
         <v>48</v>
       </c>
-      <c r="L69" s="19"/>
-      <c r="M69" s="28" t="s">
+      <c r="L69" s="29"/>
+      <c r="M69" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="24"/>
+      <c r="N69" s="34"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -4147,30 +4180,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="18">
+      <c r="C70" s="28">
         <v>44769</v>
       </c>
-      <c r="D70" s="19"/>
+      <c r="D70" s="29"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="21"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="19"/>
-      <c r="K70" s="22">
+      <c r="G70" s="31"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="29"/>
+      <c r="K70" s="32">
         <v>50</v>
       </c>
-      <c r="L70" s="19"/>
-      <c r="M70" s="23" t="s">
+      <c r="L70" s="29"/>
+      <c r="M70" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="24"/>
+      <c r="N70" s="34"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -4179,30 +4212,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="35">
         <v>44769</v>
       </c>
-      <c r="D71" s="19"/>
+      <c r="D71" s="29"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="26" t="s">
+      <c r="F71" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="21"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="19"/>
-      <c r="K71" s="27">
+      <c r="G71" s="31"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="29"/>
+      <c r="K71" s="37">
         <v>736</v>
       </c>
-      <c r="L71" s="19"/>
-      <c r="M71" s="28" t="s">
+      <c r="L71" s="29"/>
+      <c r="M71" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="24"/>
+      <c r="N71" s="34"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -4211,30 +4244,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="18">
+      <c r="C72" s="28">
         <v>44770</v>
       </c>
-      <c r="D72" s="19"/>
+      <c r="D72" s="29"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="20" t="s">
+      <c r="F72" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="21"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="19"/>
-      <c r="K72" s="22">
+      <c r="G72" s="31"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="29"/>
+      <c r="K72" s="32">
         <v>74</v>
       </c>
-      <c r="L72" s="19"/>
-      <c r="M72" s="23" t="s">
+      <c r="L72" s="29"/>
+      <c r="M72" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="24"/>
+      <c r="N72" s="34"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4243,30 +4276,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="35">
         <v>44770</v>
       </c>
-      <c r="D73" s="19"/>
+      <c r="D73" s="29"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="26" t="s">
+      <c r="F73" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="19"/>
-      <c r="K73" s="27">
+      <c r="G73" s="31"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="29"/>
+      <c r="K73" s="37">
         <v>25</v>
       </c>
-      <c r="L73" s="19"/>
-      <c r="M73" s="28" t="s">
+      <c r="L73" s="29"/>
+      <c r="M73" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="24"/>
+      <c r="N73" s="34"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4275,30 +4308,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="18">
+      <c r="C74" s="28">
         <v>44770</v>
       </c>
-      <c r="D74" s="19"/>
+      <c r="D74" s="29"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="F74" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="21"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="19"/>
-      <c r="K74" s="22">
+      <c r="G74" s="31"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="29"/>
+      <c r="K74" s="32">
         <v>25</v>
       </c>
-      <c r="L74" s="19"/>
-      <c r="M74" s="23" t="s">
+      <c r="L74" s="29"/>
+      <c r="M74" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="24"/>
+      <c r="N74" s="34"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4307,30 +4340,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="25">
+      <c r="C75" s="35">
         <v>44770</v>
       </c>
-      <c r="D75" s="19"/>
+      <c r="D75" s="29"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="26" t="s">
+      <c r="F75" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="21"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="26" t="s">
+      <c r="G75" s="31"/>
+      <c r="H75" s="29"/>
+      <c r="I75" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="19"/>
-      <c r="K75" s="27">
+      <c r="J75" s="29"/>
+      <c r="K75" s="37">
         <v>225</v>
       </c>
-      <c r="L75" s="19"/>
-      <c r="M75" s="28" t="s">
+      <c r="L75" s="29"/>
+      <c r="M75" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="24"/>
+      <c r="N75" s="34"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4339,30 +4372,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="18">
+      <c r="C76" s="28">
         <v>44770</v>
       </c>
-      <c r="D76" s="19"/>
+      <c r="D76" s="29"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="F76" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="21"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="19"/>
-      <c r="K76" s="22">
+      <c r="G76" s="31"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="29"/>
+      <c r="K76" s="32">
         <v>136</v>
       </c>
-      <c r="L76" s="19"/>
-      <c r="M76" s="23" t="s">
+      <c r="L76" s="29"/>
+      <c r="M76" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="24"/>
+      <c r="N76" s="34"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4371,30 +4404,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="25">
+      <c r="C77" s="35">
         <v>44774</v>
       </c>
-      <c r="D77" s="19"/>
+      <c r="D77" s="29"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="26" t="s">
+      <c r="F77" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="21"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="26" t="s">
+      <c r="G77" s="31"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="19"/>
-      <c r="K77" s="27">
+      <c r="J77" s="29"/>
+      <c r="K77" s="37">
         <v>82</v>
       </c>
-      <c r="L77" s="19"/>
-      <c r="M77" s="28" t="s">
+      <c r="L77" s="29"/>
+      <c r="M77" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="24"/>
+      <c r="N77" s="34"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4403,30 +4436,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="18">
+      <c r="C78" s="28">
         <v>44774</v>
       </c>
-      <c r="D78" s="19"/>
+      <c r="D78" s="29"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="20" t="s">
+      <c r="F78" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="21"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="19"/>
-      <c r="K78" s="22">
+      <c r="G78" s="31"/>
+      <c r="H78" s="29"/>
+      <c r="I78" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="29"/>
+      <c r="K78" s="32">
         <v>28</v>
       </c>
-      <c r="L78" s="19"/>
-      <c r="M78" s="23" t="s">
+      <c r="L78" s="29"/>
+      <c r="M78" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="24"/>
+      <c r="N78" s="34"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4435,30 +4468,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="25">
+      <c r="C79" s="35">
         <v>44776</v>
       </c>
-      <c r="D79" s="19"/>
+      <c r="D79" s="29"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="26" t="s">
+      <c r="F79" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="21"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="19"/>
-      <c r="K79" s="27">
+      <c r="G79" s="31"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="29"/>
+      <c r="K79" s="37">
         <v>57</v>
       </c>
-      <c r="L79" s="19"/>
-      <c r="M79" s="28" t="s">
+      <c r="L79" s="29"/>
+      <c r="M79" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="24"/>
+      <c r="N79" s="34"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4467,30 +4500,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="28">
         <v>44778</v>
       </c>
-      <c r="D80" s="19"/>
+      <c r="D80" s="29"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="F80" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="21"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="20" t="s">
+      <c r="G80" s="31"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="19"/>
-      <c r="K80" s="22">
+      <c r="J80" s="29"/>
+      <c r="K80" s="32">
         <v>133</v>
       </c>
-      <c r="L80" s="19"/>
-      <c r="M80" s="23" t="s">
+      <c r="L80" s="29"/>
+      <c r="M80" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="24"/>
+      <c r="N80" s="34"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4499,30 +4532,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="35">
         <v>44778</v>
       </c>
-      <c r="D81" s="19"/>
+      <c r="D81" s="29"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="26" t="s">
+      <c r="F81" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="21"/>
-      <c r="H81" s="19"/>
-      <c r="I81" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="19"/>
-      <c r="K81" s="27">
+      <c r="G81" s="31"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="29"/>
+      <c r="K81" s="37">
         <v>146</v>
       </c>
-      <c r="L81" s="19"/>
-      <c r="M81" s="28" t="s">
+      <c r="L81" s="29"/>
+      <c r="M81" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="24"/>
+      <c r="N81" s="34"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4531,30 +4564,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="28">
         <v>44778</v>
       </c>
-      <c r="D82" s="19"/>
+      <c r="D82" s="29"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="F82" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="21"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="20" t="s">
+      <c r="G82" s="31"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="19"/>
-      <c r="K82" s="22">
+      <c r="J82" s="29"/>
+      <c r="K82" s="32">
         <v>68</v>
       </c>
-      <c r="L82" s="19"/>
-      <c r="M82" s="23" t="s">
+      <c r="L82" s="29"/>
+      <c r="M82" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="24"/>
+      <c r="N82" s="34"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4563,30 +4596,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="25">
+      <c r="C83" s="35">
         <v>44781</v>
       </c>
-      <c r="D83" s="19"/>
+      <c r="D83" s="29"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="26" t="s">
+      <c r="F83" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="21"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="19"/>
-      <c r="K83" s="27">
+      <c r="G83" s="31"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="29"/>
+      <c r="K83" s="37">
         <v>111</v>
       </c>
-      <c r="L83" s="19"/>
-      <c r="M83" s="28" t="s">
+      <c r="L83" s="29"/>
+      <c r="M83" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="24"/>
+      <c r="N83" s="34"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4595,30 +4628,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="28">
         <v>44781</v>
       </c>
-      <c r="D84" s="19"/>
+      <c r="D84" s="29"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="20" t="s">
+      <c r="F84" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="21"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="19"/>
-      <c r="K84" s="22">
+      <c r="G84" s="31"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="29"/>
+      <c r="K84" s="32">
         <v>77</v>
       </c>
-      <c r="L84" s="19"/>
-      <c r="M84" s="23" t="s">
+      <c r="L84" s="29"/>
+      <c r="M84" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="24"/>
+      <c r="N84" s="34"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4627,30 +4660,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="25">
+      <c r="C85" s="35">
         <v>44781</v>
       </c>
-      <c r="D85" s="19"/>
+      <c r="D85" s="29"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="26" t="s">
+      <c r="F85" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="21"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="19"/>
-      <c r="K85" s="27">
+      <c r="G85" s="31"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="29"/>
+      <c r="K85" s="37">
         <v>20</v>
       </c>
-      <c r="L85" s="19"/>
-      <c r="M85" s="28" t="s">
+      <c r="L85" s="29"/>
+      <c r="M85" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="24"/>
+      <c r="N85" s="34"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4659,30 +4692,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="18">
+      <c r="C86" s="28">
         <v>44781</v>
       </c>
-      <c r="D86" s="19"/>
+      <c r="D86" s="29"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="20" t="s">
+      <c r="F86" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="21"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="19"/>
-      <c r="K86" s="22">
+      <c r="G86" s="31"/>
+      <c r="H86" s="29"/>
+      <c r="I86" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="29"/>
+      <c r="K86" s="32">
         <v>25</v>
       </c>
-      <c r="L86" s="19"/>
-      <c r="M86" s="23" t="s">
+      <c r="L86" s="29"/>
+      <c r="M86" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="24"/>
+      <c r="N86" s="34"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4691,30 +4724,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="25">
+      <c r="C87" s="35">
         <v>44781</v>
       </c>
-      <c r="D87" s="19"/>
+      <c r="D87" s="29"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="26" t="s">
+      <c r="F87" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="21"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="19"/>
-      <c r="K87" s="27">
+      <c r="G87" s="31"/>
+      <c r="H87" s="29"/>
+      <c r="I87" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="29"/>
+      <c r="K87" s="37">
         <v>21</v>
       </c>
-      <c r="L87" s="19"/>
-      <c r="M87" s="28" t="s">
+      <c r="L87" s="29"/>
+      <c r="M87" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="24"/>
+      <c r="N87" s="34"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4723,30 +4756,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="18">
+      <c r="C88" s="28">
         <v>44781</v>
       </c>
-      <c r="D88" s="19"/>
+      <c r="D88" s="29"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="20" t="s">
+      <c r="F88" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="21"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="19"/>
-      <c r="K88" s="22">
+      <c r="G88" s="31"/>
+      <c r="H88" s="29"/>
+      <c r="I88" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="29"/>
+      <c r="K88" s="32">
         <v>86</v>
       </c>
-      <c r="L88" s="19"/>
-      <c r="M88" s="23" t="s">
+      <c r="L88" s="29"/>
+      <c r="M88" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="24"/>
+      <c r="N88" s="34"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4755,30 +4788,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="25">
+      <c r="C89" s="35">
         <v>44781</v>
       </c>
-      <c r="D89" s="19"/>
+      <c r="D89" s="29"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="26" t="s">
+      <c r="F89" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="21"/>
-      <c r="H89" s="19"/>
-      <c r="I89" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="19"/>
-      <c r="K89" s="27">
+      <c r="G89" s="31"/>
+      <c r="H89" s="29"/>
+      <c r="I89" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="29"/>
+      <c r="K89" s="37">
         <v>9</v>
       </c>
-      <c r="L89" s="19"/>
-      <c r="M89" s="28" t="s">
+      <c r="L89" s="29"/>
+      <c r="M89" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="24"/>
+      <c r="N89" s="34"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4787,30 +4820,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="18">
+      <c r="C90" s="28">
         <v>44781</v>
       </c>
-      <c r="D90" s="19"/>
+      <c r="D90" s="29"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="20" t="s">
+      <c r="F90" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="21"/>
-      <c r="H90" s="19"/>
-      <c r="I90" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="19"/>
-      <c r="K90" s="22">
+      <c r="G90" s="31"/>
+      <c r="H90" s="29"/>
+      <c r="I90" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="29"/>
+      <c r="K90" s="32">
         <v>2</v>
       </c>
-      <c r="L90" s="19"/>
-      <c r="M90" s="23" t="s">
+      <c r="L90" s="29"/>
+      <c r="M90" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="24"/>
+      <c r="N90" s="34"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4819,30 +4852,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="25">
+      <c r="C91" s="35">
         <v>44781</v>
       </c>
-      <c r="D91" s="19"/>
+      <c r="D91" s="29"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="26" t="s">
+      <c r="F91" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="21"/>
-      <c r="H91" s="19"/>
-      <c r="I91" s="26" t="s">
+      <c r="G91" s="31"/>
+      <c r="H91" s="29"/>
+      <c r="I91" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="19"/>
-      <c r="K91" s="27">
+      <c r="J91" s="29"/>
+      <c r="K91" s="37">
         <v>73</v>
       </c>
-      <c r="L91" s="19"/>
-      <c r="M91" s="28" t="s">
+      <c r="L91" s="29"/>
+      <c r="M91" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="24"/>
+      <c r="N91" s="34"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4851,30 +4884,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="28">
         <v>44782</v>
       </c>
-      <c r="D92" s="19"/>
+      <c r="D92" s="29"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="20" t="s">
+      <c r="F92" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="21"/>
-      <c r="H92" s="19"/>
-      <c r="I92" s="20" t="s">
+      <c r="G92" s="31"/>
+      <c r="H92" s="29"/>
+      <c r="I92" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="19"/>
-      <c r="K92" s="22">
+      <c r="J92" s="29"/>
+      <c r="K92" s="32">
         <v>33</v>
       </c>
-      <c r="L92" s="19"/>
-      <c r="M92" s="23" t="s">
+      <c r="L92" s="29"/>
+      <c r="M92" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="24"/>
+      <c r="N92" s="34"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4883,30 +4916,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="25">
+      <c r="C93" s="35">
         <v>44782</v>
       </c>
-      <c r="D93" s="19"/>
+      <c r="D93" s="29"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="26" t="s">
+      <c r="F93" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="21"/>
-      <c r="H93" s="19"/>
-      <c r="I93" s="26" t="s">
+      <c r="G93" s="31"/>
+      <c r="H93" s="29"/>
+      <c r="I93" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="19"/>
-      <c r="K93" s="27">
+      <c r="J93" s="29"/>
+      <c r="K93" s="37">
         <v>57</v>
       </c>
-      <c r="L93" s="19"/>
-      <c r="M93" s="28" t="s">
+      <c r="L93" s="29"/>
+      <c r="M93" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="24"/>
+      <c r="N93" s="34"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -4915,30 +4948,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="18">
+      <c r="C94" s="28">
         <v>44782</v>
       </c>
-      <c r="D94" s="19"/>
+      <c r="D94" s="29"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="20" t="s">
+      <c r="F94" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="21"/>
-      <c r="H94" s="19"/>
-      <c r="I94" s="20" t="s">
+      <c r="G94" s="31"/>
+      <c r="H94" s="29"/>
+      <c r="I94" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="19"/>
-      <c r="K94" s="22">
+      <c r="J94" s="29"/>
+      <c r="K94" s="32">
         <v>16</v>
       </c>
-      <c r="L94" s="19"/>
-      <c r="M94" s="23" t="s">
+      <c r="L94" s="29"/>
+      <c r="M94" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="24"/>
+      <c r="N94" s="34"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -4947,30 +4980,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="25">
+      <c r="C95" s="35">
         <v>44782</v>
       </c>
-      <c r="D95" s="19"/>
+      <c r="D95" s="29"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="26" t="s">
+      <c r="F95" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="21"/>
-      <c r="H95" s="19"/>
-      <c r="I95" s="26" t="s">
+      <c r="G95" s="31"/>
+      <c r="H95" s="29"/>
+      <c r="I95" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="19"/>
-      <c r="K95" s="27">
+      <c r="J95" s="29"/>
+      <c r="K95" s="37">
         <v>3</v>
       </c>
-      <c r="L95" s="19"/>
-      <c r="M95" s="28" t="s">
+      <c r="L95" s="29"/>
+      <c r="M95" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="24"/>
+      <c r="N95" s="34"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -4979,30 +5012,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="28">
         <v>44782</v>
       </c>
-      <c r="D96" s="19"/>
+      <c r="D96" s="29"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="20" t="s">
+      <c r="F96" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="21"/>
-      <c r="H96" s="19"/>
-      <c r="I96" s="20" t="s">
+      <c r="G96" s="31"/>
+      <c r="H96" s="29"/>
+      <c r="I96" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="19"/>
-      <c r="K96" s="22">
+      <c r="J96" s="29"/>
+      <c r="K96" s="32">
         <v>15</v>
       </c>
-      <c r="L96" s="19"/>
-      <c r="M96" s="23" t="s">
+      <c r="L96" s="29"/>
+      <c r="M96" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="24"/>
+      <c r="N96" s="34"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -5011,30 +5044,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="35">
         <v>44783</v>
       </c>
-      <c r="D97" s="19"/>
+      <c r="D97" s="29"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="26" t="s">
+      <c r="F97" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="21"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="26" t="s">
+      <c r="G97" s="31"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="19"/>
-      <c r="K97" s="27">
+      <c r="J97" s="29"/>
+      <c r="K97" s="37">
         <v>64</v>
       </c>
-      <c r="L97" s="19"/>
-      <c r="M97" s="28" t="s">
+      <c r="L97" s="29"/>
+      <c r="M97" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="24"/>
+      <c r="N97" s="34"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -5043,30 +5076,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="18">
+      <c r="C98" s="28">
         <v>44783</v>
       </c>
-      <c r="D98" s="19"/>
+      <c r="D98" s="29"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="20" t="s">
+      <c r="F98" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="21"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="20" t="s">
+      <c r="G98" s="31"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="19"/>
-      <c r="K98" s="22">
+      <c r="J98" s="29"/>
+      <c r="K98" s="32">
         <v>100</v>
       </c>
-      <c r="L98" s="19"/>
-      <c r="M98" s="23" t="s">
+      <c r="L98" s="29"/>
+      <c r="M98" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="24"/>
+      <c r="N98" s="34"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -5075,30 +5108,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="35">
         <v>44783</v>
       </c>
-      <c r="D99" s="19"/>
+      <c r="D99" s="29"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="26" t="s">
+      <c r="F99" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="21"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="26" t="s">
+      <c r="G99" s="31"/>
+      <c r="H99" s="29"/>
+      <c r="I99" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="19"/>
-      <c r="K99" s="27">
+      <c r="J99" s="29"/>
+      <c r="K99" s="37">
         <v>193</v>
       </c>
-      <c r="L99" s="19"/>
-      <c r="M99" s="28" t="s">
+      <c r="L99" s="29"/>
+      <c r="M99" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="24"/>
+      <c r="N99" s="34"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -5107,30 +5140,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="18">
+      <c r="C100" s="28">
         <v>44783</v>
       </c>
-      <c r="D100" s="19"/>
+      <c r="D100" s="29"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="20" t="s">
+      <c r="F100" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="21"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="19"/>
-      <c r="K100" s="22">
+      <c r="G100" s="31"/>
+      <c r="H100" s="29"/>
+      <c r="I100" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="29"/>
+      <c r="K100" s="32">
         <v>15</v>
       </c>
-      <c r="L100" s="19"/>
-      <c r="M100" s="23" t="s">
+      <c r="L100" s="29"/>
+      <c r="M100" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="24"/>
+      <c r="N100" s="34"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -5139,30 +5172,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="35">
         <v>44783</v>
       </c>
-      <c r="D101" s="19"/>
+      <c r="D101" s="29"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="26" t="s">
+      <c r="F101" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="21"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="19"/>
-      <c r="K101" s="27">
+      <c r="G101" s="31"/>
+      <c r="H101" s="29"/>
+      <c r="I101" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="29"/>
+      <c r="K101" s="37">
         <v>65</v>
       </c>
-      <c r="L101" s="19"/>
-      <c r="M101" s="28" t="s">
+      <c r="L101" s="29"/>
+      <c r="M101" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="24"/>
+      <c r="N101" s="34"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -5171,30 +5204,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="18">
+      <c r="C102" s="28">
         <v>44783</v>
       </c>
-      <c r="D102" s="19"/>
+      <c r="D102" s="29"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="20" t="s">
+      <c r="F102" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="21"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="19"/>
-      <c r="K102" s="22">
+      <c r="G102" s="31"/>
+      <c r="H102" s="29"/>
+      <c r="I102" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="29"/>
+      <c r="K102" s="32">
         <v>66</v>
       </c>
-      <c r="L102" s="19"/>
-      <c r="M102" s="23" t="s">
+      <c r="L102" s="29"/>
+      <c r="M102" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="24"/>
+      <c r="N102" s="34"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -5203,30 +5236,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="25">
+      <c r="C103" s="35">
         <v>44784</v>
       </c>
-      <c r="D103" s="19"/>
+      <c r="D103" s="29"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="26" t="s">
+      <c r="F103" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="21"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="26" t="s">
+      <c r="G103" s="31"/>
+      <c r="H103" s="29"/>
+      <c r="I103" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="19"/>
-      <c r="K103" s="27">
+      <c r="J103" s="29"/>
+      <c r="K103" s="37">
         <v>111</v>
       </c>
-      <c r="L103" s="19"/>
-      <c r="M103" s="28" t="s">
+      <c r="L103" s="29"/>
+      <c r="M103" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="24"/>
+      <c r="N103" s="34"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5235,30 +5268,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="18">
+      <c r="C104" s="28">
         <v>44784</v>
       </c>
-      <c r="D104" s="19"/>
+      <c r="D104" s="29"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="20" t="s">
+      <c r="F104" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="21"/>
-      <c r="H104" s="19"/>
-      <c r="I104" s="20" t="s">
+      <c r="G104" s="31"/>
+      <c r="H104" s="29"/>
+      <c r="I104" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="19"/>
-      <c r="K104" s="22">
+      <c r="J104" s="29"/>
+      <c r="K104" s="32">
         <v>30</v>
       </c>
-      <c r="L104" s="19"/>
-      <c r="M104" s="23" t="s">
+      <c r="L104" s="29"/>
+      <c r="M104" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="24"/>
+      <c r="N104" s="34"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5267,30 +5300,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="25">
+      <c r="C105" s="35">
         <v>44784</v>
       </c>
-      <c r="D105" s="19"/>
+      <c r="D105" s="29"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="26" t="s">
+      <c r="F105" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="21"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="26" t="s">
+      <c r="G105" s="31"/>
+      <c r="H105" s="29"/>
+      <c r="I105" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="19"/>
-      <c r="K105" s="27">
+      <c r="J105" s="29"/>
+      <c r="K105" s="37">
         <v>31</v>
       </c>
-      <c r="L105" s="19"/>
-      <c r="M105" s="28" t="s">
+      <c r="L105" s="29"/>
+      <c r="M105" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="24"/>
+      <c r="N105" s="34"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5299,30 +5332,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="18">
+      <c r="C106" s="28">
         <v>44784</v>
       </c>
-      <c r="D106" s="19"/>
+      <c r="D106" s="29"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="20" t="s">
+      <c r="F106" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="21"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="20" t="s">
+      <c r="G106" s="31"/>
+      <c r="H106" s="29"/>
+      <c r="I106" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="19"/>
-      <c r="K106" s="22">
+      <c r="J106" s="29"/>
+      <c r="K106" s="32">
         <v>109</v>
       </c>
-      <c r="L106" s="19"/>
-      <c r="M106" s="23" t="s">
+      <c r="L106" s="29"/>
+      <c r="M106" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="24"/>
+      <c r="N106" s="34"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5331,30 +5364,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="25">
+      <c r="C107" s="35">
         <v>44788</v>
       </c>
-      <c r="D107" s="19"/>
+      <c r="D107" s="29"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F107" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="21"/>
-      <c r="H107" s="19"/>
-      <c r="I107" s="26" t="s">
+      <c r="G107" s="31"/>
+      <c r="H107" s="29"/>
+      <c r="I107" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="19"/>
-      <c r="K107" s="27">
+      <c r="J107" s="29"/>
+      <c r="K107" s="37">
         <v>5</v>
       </c>
-      <c r="L107" s="19"/>
-      <c r="M107" s="28" t="s">
+      <c r="L107" s="29"/>
+      <c r="M107" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="24"/>
+      <c r="N107" s="34"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5363,30 +5396,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="18">
+      <c r="C108" s="28">
         <v>44788</v>
       </c>
-      <c r="D108" s="19"/>
+      <c r="D108" s="29"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="20" t="s">
+      <c r="F108" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="21"/>
-      <c r="H108" s="19"/>
-      <c r="I108" s="20" t="s">
+      <c r="G108" s="31"/>
+      <c r="H108" s="29"/>
+      <c r="I108" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="19"/>
-      <c r="K108" s="22">
+      <c r="J108" s="29"/>
+      <c r="K108" s="32">
         <v>100</v>
       </c>
-      <c r="L108" s="19"/>
-      <c r="M108" s="23" t="s">
+      <c r="L108" s="29"/>
+      <c r="M108" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="24"/>
+      <c r="N108" s="34"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5395,30 +5428,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="25">
+      <c r="C109" s="35">
         <v>44788</v>
       </c>
-      <c r="D109" s="19"/>
+      <c r="D109" s="29"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="26" t="s">
+      <c r="F109" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="21"/>
-      <c r="H109" s="19"/>
-      <c r="I109" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="19"/>
-      <c r="K109" s="27">
+      <c r="G109" s="31"/>
+      <c r="H109" s="29"/>
+      <c r="I109" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="29"/>
+      <c r="K109" s="37">
         <v>54</v>
       </c>
-      <c r="L109" s="19"/>
-      <c r="M109" s="28" t="s">
+      <c r="L109" s="29"/>
+      <c r="M109" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="24"/>
+      <c r="N109" s="34"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5427,30 +5460,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="18">
+      <c r="C110" s="28">
         <v>44789</v>
       </c>
-      <c r="D110" s="19"/>
+      <c r="D110" s="29"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="20" t="s">
+      <c r="F110" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="21"/>
-      <c r="H110" s="19"/>
-      <c r="I110" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="19"/>
-      <c r="K110" s="22">
+      <c r="G110" s="31"/>
+      <c r="H110" s="29"/>
+      <c r="I110" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="29"/>
+      <c r="K110" s="32">
         <v>77</v>
       </c>
-      <c r="L110" s="19"/>
-      <c r="M110" s="23" t="s">
+      <c r="L110" s="29"/>
+      <c r="M110" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="24"/>
+      <c r="N110" s="34"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5459,30 +5492,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="25">
+      <c r="C111" s="35">
         <v>44789</v>
       </c>
-      <c r="D111" s="19"/>
+      <c r="D111" s="29"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="26" t="s">
+      <c r="F111" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="21"/>
-      <c r="H111" s="19"/>
-      <c r="I111" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="19"/>
-      <c r="K111" s="27">
+      <c r="G111" s="31"/>
+      <c r="H111" s="29"/>
+      <c r="I111" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="29"/>
+      <c r="K111" s="37">
         <v>52</v>
       </c>
-      <c r="L111" s="19"/>
-      <c r="M111" s="28" t="s">
+      <c r="L111" s="29"/>
+      <c r="M111" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="24"/>
+      <c r="N111" s="34"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5491,30 +5524,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="18">
+      <c r="C112" s="28">
         <v>44789</v>
       </c>
-      <c r="D112" s="19"/>
+      <c r="D112" s="29"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="20" t="s">
+      <c r="F112" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="21"/>
-      <c r="H112" s="19"/>
-      <c r="I112" s="20" t="s">
+      <c r="G112" s="31"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="19"/>
-      <c r="K112" s="22">
+      <c r="J112" s="29"/>
+      <c r="K112" s="32">
         <v>305</v>
       </c>
-      <c r="L112" s="19"/>
-      <c r="M112" s="23" t="s">
+      <c r="L112" s="29"/>
+      <c r="M112" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="24"/>
+      <c r="N112" s="34"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5523,30 +5556,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="25">
+      <c r="C113" s="35">
         <v>44789</v>
       </c>
-      <c r="D113" s="19"/>
+      <c r="D113" s="29"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="26" t="s">
+      <c r="F113" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="21"/>
-      <c r="H113" s="19"/>
-      <c r="I113" s="26" t="s">
+      <c r="G113" s="31"/>
+      <c r="H113" s="29"/>
+      <c r="I113" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="19"/>
-      <c r="K113" s="27">
+      <c r="J113" s="29"/>
+      <c r="K113" s="37">
         <v>81</v>
       </c>
-      <c r="L113" s="19"/>
-      <c r="M113" s="28" t="s">
+      <c r="L113" s="29"/>
+      <c r="M113" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="24"/>
+      <c r="N113" s="34"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5555,30 +5588,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="28">
         <v>44789</v>
       </c>
-      <c r="D114" s="19"/>
+      <c r="D114" s="29"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="20" t="s">
+      <c r="F114" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="21"/>
-      <c r="H114" s="19"/>
-      <c r="I114" s="20" t="s">
+      <c r="G114" s="31"/>
+      <c r="H114" s="29"/>
+      <c r="I114" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="19"/>
-      <c r="K114" s="22">
+      <c r="J114" s="29"/>
+      <c r="K114" s="32">
         <v>53</v>
       </c>
-      <c r="L114" s="19"/>
-      <c r="M114" s="23" t="s">
+      <c r="L114" s="29"/>
+      <c r="M114" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="24"/>
+      <c r="N114" s="34"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5587,30 +5620,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="25">
+      <c r="C115" s="35">
         <v>44789</v>
       </c>
-      <c r="D115" s="19"/>
+      <c r="D115" s="29"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="26" t="s">
+      <c r="F115" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="21"/>
-      <c r="H115" s="19"/>
-      <c r="I115" s="26" t="s">
+      <c r="G115" s="31"/>
+      <c r="H115" s="29"/>
+      <c r="I115" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="19"/>
-      <c r="K115" s="27">
+      <c r="J115" s="29"/>
+      <c r="K115" s="37">
         <v>33</v>
       </c>
-      <c r="L115" s="19"/>
-      <c r="M115" s="28" t="s">
+      <c r="L115" s="29"/>
+      <c r="M115" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="24"/>
+      <c r="N115" s="34"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5619,30 +5652,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="28">
         <v>44790</v>
       </c>
-      <c r="D116" s="19"/>
+      <c r="D116" s="29"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="20" t="s">
+      <c r="F116" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="21"/>
-      <c r="H116" s="19"/>
-      <c r="I116" s="20" t="s">
+      <c r="G116" s="31"/>
+      <c r="H116" s="29"/>
+      <c r="I116" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="19"/>
-      <c r="K116" s="22">
+      <c r="J116" s="29"/>
+      <c r="K116" s="32">
         <v>145</v>
       </c>
-      <c r="L116" s="19"/>
-      <c r="M116" s="23" t="s">
+      <c r="L116" s="29"/>
+      <c r="M116" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="24"/>
+      <c r="N116" s="34"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5651,30 +5684,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="25">
+      <c r="C117" s="35">
         <v>44790</v>
       </c>
-      <c r="D117" s="19"/>
+      <c r="D117" s="29"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="26" t="s">
+      <c r="F117" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="21"/>
-      <c r="H117" s="19"/>
-      <c r="I117" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="19"/>
-      <c r="K117" s="27">
+      <c r="G117" s="31"/>
+      <c r="H117" s="29"/>
+      <c r="I117" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="29"/>
+      <c r="K117" s="37">
         <v>14</v>
       </c>
-      <c r="L117" s="19"/>
-      <c r="M117" s="28" t="s">
+      <c r="L117" s="29"/>
+      <c r="M117" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="24"/>
+      <c r="N117" s="34"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5683,30 +5716,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="18">
+      <c r="C118" s="28">
         <v>44790</v>
       </c>
-      <c r="D118" s="19"/>
+      <c r="D118" s="29"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="20" t="s">
+      <c r="F118" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="21"/>
-      <c r="H118" s="19"/>
-      <c r="I118" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="19"/>
-      <c r="K118" s="22">
+      <c r="G118" s="31"/>
+      <c r="H118" s="29"/>
+      <c r="I118" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="29"/>
+      <c r="K118" s="32">
         <v>47</v>
       </c>
-      <c r="L118" s="19"/>
-      <c r="M118" s="23" t="s">
+      <c r="L118" s="29"/>
+      <c r="M118" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="24"/>
+      <c r="N118" s="34"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5715,30 +5748,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="25">
+      <c r="C119" s="35">
         <v>44790</v>
       </c>
-      <c r="D119" s="19"/>
+      <c r="D119" s="29"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="26" t="s">
+      <c r="F119" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="21"/>
-      <c r="H119" s="19"/>
-      <c r="I119" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="19"/>
-      <c r="K119" s="27">
+      <c r="G119" s="31"/>
+      <c r="H119" s="29"/>
+      <c r="I119" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="29"/>
+      <c r="K119" s="37">
         <v>16</v>
       </c>
-      <c r="L119" s="19"/>
-      <c r="M119" s="28" t="s">
+      <c r="L119" s="29"/>
+      <c r="M119" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="24"/>
+      <c r="N119" s="34"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5747,30 +5780,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="18">
+      <c r="C120" s="28">
         <v>44790</v>
       </c>
-      <c r="D120" s="19"/>
+      <c r="D120" s="29"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="20" t="s">
+      <c r="F120" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="21"/>
-      <c r="H120" s="19"/>
-      <c r="I120" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="19"/>
-      <c r="K120" s="22">
+      <c r="G120" s="31"/>
+      <c r="H120" s="29"/>
+      <c r="I120" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="29"/>
+      <c r="K120" s="32">
         <v>55</v>
       </c>
-      <c r="L120" s="19"/>
-      <c r="M120" s="23" t="s">
+      <c r="L120" s="29"/>
+      <c r="M120" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="24"/>
+      <c r="N120" s="34"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5779,30 +5812,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="25">
+      <c r="C121" s="35">
         <v>44790</v>
       </c>
-      <c r="D121" s="19"/>
+      <c r="D121" s="29"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F121" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="21"/>
-      <c r="H121" s="19"/>
-      <c r="I121" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="19"/>
-      <c r="K121" s="27">
+      <c r="G121" s="31"/>
+      <c r="H121" s="29"/>
+      <c r="I121" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="29"/>
+      <c r="K121" s="37">
         <v>8</v>
       </c>
-      <c r="L121" s="19"/>
-      <c r="M121" s="28" t="s">
+      <c r="L121" s="29"/>
+      <c r="M121" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="24"/>
+      <c r="N121" s="34"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5811,30 +5844,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="18">
+      <c r="C122" s="28">
         <v>44790</v>
       </c>
-      <c r="D122" s="19"/>
+      <c r="D122" s="29"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="20" t="s">
+      <c r="F122" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="21"/>
-      <c r="H122" s="19"/>
-      <c r="I122" s="20" t="s">
+      <c r="G122" s="31"/>
+      <c r="H122" s="29"/>
+      <c r="I122" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="19"/>
-      <c r="K122" s="22">
+      <c r="J122" s="29"/>
+      <c r="K122" s="32">
         <v>578</v>
       </c>
-      <c r="L122" s="19"/>
-      <c r="M122" s="23" t="s">
+      <c r="L122" s="29"/>
+      <c r="M122" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="24"/>
+      <c r="N122" s="34"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5843,30 +5876,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="25">
+      <c r="C123" s="35">
         <v>44791</v>
       </c>
-      <c r="D123" s="19"/>
+      <c r="D123" s="29"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F123" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="21"/>
-      <c r="H123" s="19"/>
-      <c r="I123" s="26" t="s">
+      <c r="G123" s="31"/>
+      <c r="H123" s="29"/>
+      <c r="I123" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="19"/>
-      <c r="K123" s="27">
+      <c r="J123" s="29"/>
+      <c r="K123" s="37">
         <v>111</v>
       </c>
-      <c r="L123" s="19"/>
-      <c r="M123" s="28" t="s">
+      <c r="L123" s="29"/>
+      <c r="M123" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="24"/>
+      <c r="N123" s="34"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5875,30 +5908,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="18">
+      <c r="C124" s="28">
         <v>44791</v>
       </c>
-      <c r="D124" s="19"/>
+      <c r="D124" s="29"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="20" t="s">
+      <c r="F124" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="21"/>
-      <c r="H124" s="19"/>
-      <c r="I124" s="20" t="s">
+      <c r="G124" s="31"/>
+      <c r="H124" s="29"/>
+      <c r="I124" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="19"/>
-      <c r="K124" s="22">
+      <c r="J124" s="29"/>
+      <c r="K124" s="32">
         <v>51</v>
       </c>
-      <c r="L124" s="19"/>
-      <c r="M124" s="23" t="s">
+      <c r="L124" s="29"/>
+      <c r="M124" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="24"/>
+      <c r="N124" s="34"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5907,30 +5940,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="25">
+      <c r="C125" s="35">
         <v>44791</v>
       </c>
-      <c r="D125" s="19"/>
+      <c r="D125" s="29"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F125" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="21"/>
-      <c r="H125" s="19"/>
-      <c r="I125" s="26" t="s">
+      <c r="G125" s="31"/>
+      <c r="H125" s="29"/>
+      <c r="I125" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="19"/>
-      <c r="K125" s="27">
+      <c r="J125" s="29"/>
+      <c r="K125" s="37">
         <v>35</v>
       </c>
-      <c r="L125" s="19"/>
-      <c r="M125" s="28" t="s">
+      <c r="L125" s="29"/>
+      <c r="M125" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="24"/>
+      <c r="N125" s="34"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -5939,30 +5972,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="18">
+      <c r="C126" s="28">
         <v>44792</v>
       </c>
-      <c r="D126" s="19"/>
+      <c r="D126" s="29"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="20" t="s">
+      <c r="F126" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="21"/>
-      <c r="H126" s="19"/>
-      <c r="I126" s="20" t="s">
+      <c r="G126" s="31"/>
+      <c r="H126" s="29"/>
+      <c r="I126" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="19"/>
-      <c r="K126" s="22">
+      <c r="J126" s="29"/>
+      <c r="K126" s="32">
         <v>74</v>
       </c>
-      <c r="L126" s="19"/>
-      <c r="M126" s="23" t="s">
+      <c r="L126" s="29"/>
+      <c r="M126" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="24"/>
+      <c r="N126" s="34"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -5971,30 +6004,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="25">
+      <c r="C127" s="35">
         <v>44795</v>
       </c>
-      <c r="D127" s="19"/>
+      <c r="D127" s="29"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F127" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="21"/>
-      <c r="H127" s="19"/>
-      <c r="I127" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="19"/>
-      <c r="K127" s="27">
+      <c r="G127" s="31"/>
+      <c r="H127" s="29"/>
+      <c r="I127" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="29"/>
+      <c r="K127" s="37">
         <v>51</v>
       </c>
-      <c r="L127" s="19"/>
-      <c r="M127" s="28" t="s">
+      <c r="L127" s="29"/>
+      <c r="M127" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="24"/>
+      <c r="N127" s="34"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -6003,30 +6036,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="18">
+      <c r="C128" s="28">
         <v>44799</v>
       </c>
-      <c r="D128" s="19"/>
+      <c r="D128" s="29"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="20" t="s">
+      <c r="F128" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="21"/>
-      <c r="H128" s="19"/>
-      <c r="I128" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="19"/>
-      <c r="K128" s="22">
+      <c r="G128" s="31"/>
+      <c r="H128" s="29"/>
+      <c r="I128" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="29"/>
+      <c r="K128" s="32">
         <v>80</v>
       </c>
-      <c r="L128" s="19"/>
-      <c r="M128" s="23" t="s">
+      <c r="L128" s="29"/>
+      <c r="M128" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="24"/>
+      <c r="N128" s="34"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -6035,30 +6068,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="25">
+      <c r="C129" s="35">
         <v>44799</v>
       </c>
-      <c r="D129" s="19"/>
+      <c r="D129" s="29"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F129" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="21"/>
-      <c r="H129" s="19"/>
-      <c r="I129" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="19"/>
-      <c r="K129" s="27">
+      <c r="G129" s="31"/>
+      <c r="H129" s="29"/>
+      <c r="I129" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="29"/>
+      <c r="K129" s="37">
         <v>100</v>
       </c>
-      <c r="L129" s="19"/>
-      <c r="M129" s="28" t="s">
+      <c r="L129" s="29"/>
+      <c r="M129" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="24"/>
+      <c r="N129" s="34"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -6067,30 +6100,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="18">
+      <c r="C130" s="28">
         <v>44802</v>
       </c>
-      <c r="D130" s="19"/>
+      <c r="D130" s="29"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="20" t="s">
+      <c r="F130" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="21"/>
-      <c r="H130" s="19"/>
-      <c r="I130" s="20" t="s">
+      <c r="G130" s="31"/>
+      <c r="H130" s="29"/>
+      <c r="I130" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="19"/>
-      <c r="K130" s="22">
+      <c r="J130" s="29"/>
+      <c r="K130" s="32">
         <v>96</v>
       </c>
-      <c r="L130" s="19"/>
-      <c r="M130" s="23" t="s">
+      <c r="L130" s="29"/>
+      <c r="M130" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="24"/>
+      <c r="N130" s="34"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -6099,30 +6132,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="25">
+      <c r="C131" s="35">
         <v>44802</v>
       </c>
-      <c r="D131" s="19"/>
+      <c r="D131" s="29"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="26" t="s">
+      <c r="F131" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="21"/>
-      <c r="H131" s="19"/>
-      <c r="I131" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="19"/>
-      <c r="K131" s="27">
+      <c r="G131" s="31"/>
+      <c r="H131" s="29"/>
+      <c r="I131" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="29"/>
+      <c r="K131" s="37">
         <v>37</v>
       </c>
-      <c r="L131" s="19"/>
-      <c r="M131" s="28" t="s">
+      <c r="L131" s="29"/>
+      <c r="M131" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="24"/>
+      <c r="N131" s="34"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -6131,30 +6164,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="18">
+      <c r="C132" s="28">
         <v>44804</v>
       </c>
-      <c r="D132" s="19"/>
+      <c r="D132" s="29"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="20" t="s">
+      <c r="F132" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="21"/>
-      <c r="H132" s="19"/>
-      <c r="I132" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="19"/>
-      <c r="K132" s="22">
+      <c r="G132" s="31"/>
+      <c r="H132" s="29"/>
+      <c r="I132" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="29"/>
+      <c r="K132" s="32">
         <v>91</v>
       </c>
-      <c r="L132" s="19"/>
-      <c r="M132" s="23" t="s">
+      <c r="L132" s="29"/>
+      <c r="M132" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="24"/>
+      <c r="N132" s="34"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -6163,30 +6196,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="25">
+      <c r="C133" s="35">
         <v>44804</v>
       </c>
-      <c r="D133" s="19"/>
+      <c r="D133" s="29"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="26" t="s">
+      <c r="F133" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="21"/>
-      <c r="H133" s="19"/>
-      <c r="I133" s="26" t="s">
+      <c r="G133" s="31"/>
+      <c r="H133" s="29"/>
+      <c r="I133" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="19"/>
-      <c r="K133" s="27">
+      <c r="J133" s="29"/>
+      <c r="K133" s="37">
         <v>56</v>
       </c>
-      <c r="L133" s="19"/>
-      <c r="M133" s="28" t="s">
+      <c r="L133" s="29"/>
+      <c r="M133" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="24"/>
+      <c r="N133" s="34"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -6195,30 +6228,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="18">
+      <c r="C134" s="28">
         <v>44805</v>
       </c>
-      <c r="D134" s="19"/>
+      <c r="D134" s="29"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="20" t="s">
+      <c r="F134" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="21"/>
-      <c r="H134" s="19"/>
-      <c r="I134" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="19"/>
-      <c r="K134" s="22">
+      <c r="G134" s="31"/>
+      <c r="H134" s="29"/>
+      <c r="I134" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="29"/>
+      <c r="K134" s="32">
         <v>401</v>
       </c>
-      <c r="L134" s="19"/>
-      <c r="M134" s="23" t="s">
+      <c r="L134" s="29"/>
+      <c r="M134" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="24"/>
+      <c r="N134" s="34"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -6227,30 +6260,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="25">
+      <c r="C135" s="35">
         <v>44805</v>
       </c>
-      <c r="D135" s="19"/>
+      <c r="D135" s="29"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="26" t="s">
+      <c r="F135" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="21"/>
-      <c r="H135" s="19"/>
-      <c r="I135" s="26" t="s">
+      <c r="G135" s="31"/>
+      <c r="H135" s="29"/>
+      <c r="I135" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="19"/>
-      <c r="K135" s="27">
+      <c r="J135" s="29"/>
+      <c r="K135" s="37">
         <v>375</v>
       </c>
-      <c r="L135" s="19"/>
-      <c r="M135" s="28" t="s">
+      <c r="L135" s="29"/>
+      <c r="M135" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="24"/>
+      <c r="N135" s="34"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6259,30 +6292,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="18">
+      <c r="C136" s="28">
         <v>44806</v>
       </c>
-      <c r="D136" s="19"/>
+      <c r="D136" s="29"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="20" t="s">
+      <c r="F136" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="21"/>
-      <c r="H136" s="19"/>
-      <c r="I136" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="19"/>
-      <c r="K136" s="22">
+      <c r="G136" s="31"/>
+      <c r="H136" s="29"/>
+      <c r="I136" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="29"/>
+      <c r="K136" s="32">
         <v>44</v>
       </c>
-      <c r="L136" s="19"/>
-      <c r="M136" s="23" t="s">
+      <c r="L136" s="29"/>
+      <c r="M136" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="24"/>
+      <c r="N136" s="34"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6291,30 +6324,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="25">
+      <c r="C137" s="35">
         <v>44806</v>
       </c>
-      <c r="D137" s="19"/>
+      <c r="D137" s="29"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="26" t="s">
+      <c r="F137" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="21"/>
-      <c r="H137" s="19"/>
-      <c r="I137" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="19"/>
-      <c r="K137" s="27">
+      <c r="G137" s="31"/>
+      <c r="H137" s="29"/>
+      <c r="I137" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="29"/>
+      <c r="K137" s="37">
         <v>51</v>
       </c>
-      <c r="L137" s="19"/>
-      <c r="M137" s="28" t="s">
+      <c r="L137" s="29"/>
+      <c r="M137" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="24"/>
+      <c r="N137" s="34"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6323,30 +6356,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="18">
+      <c r="C138" s="28">
         <v>44806</v>
       </c>
-      <c r="D138" s="19"/>
+      <c r="D138" s="29"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="20" t="s">
+      <c r="F138" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="21"/>
-      <c r="H138" s="19"/>
-      <c r="I138" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="19"/>
-      <c r="K138" s="22">
+      <c r="G138" s="31"/>
+      <c r="H138" s="29"/>
+      <c r="I138" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="29"/>
+      <c r="K138" s="32">
         <v>40</v>
       </c>
-      <c r="L138" s="19"/>
-      <c r="M138" s="23" t="s">
+      <c r="L138" s="29"/>
+      <c r="M138" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="24"/>
+      <c r="N138" s="34"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6355,30 +6388,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="25">
+      <c r="C139" s="35">
         <v>44810</v>
       </c>
-      <c r="D139" s="19"/>
+      <c r="D139" s="29"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="26" t="s">
+      <c r="F139" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="21"/>
-      <c r="H139" s="19"/>
-      <c r="I139" s="26" t="s">
+      <c r="G139" s="31"/>
+      <c r="H139" s="29"/>
+      <c r="I139" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="19"/>
-      <c r="K139" s="27">
+      <c r="J139" s="29"/>
+      <c r="K139" s="37">
         <v>9</v>
       </c>
-      <c r="L139" s="19"/>
-      <c r="M139" s="28" t="s">
+      <c r="L139" s="29"/>
+      <c r="M139" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="24"/>
+      <c r="N139" s="34"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6387,30 +6420,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="18">
+      <c r="C140" s="28">
         <v>44810</v>
       </c>
-      <c r="D140" s="19"/>
+      <c r="D140" s="29"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="20" t="s">
+      <c r="F140" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="21"/>
-      <c r="H140" s="19"/>
-      <c r="I140" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="19"/>
-      <c r="K140" s="22">
+      <c r="G140" s="31"/>
+      <c r="H140" s="29"/>
+      <c r="I140" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="29"/>
+      <c r="K140" s="32">
         <v>17</v>
       </c>
-      <c r="L140" s="19"/>
-      <c r="M140" s="23" t="s">
+      <c r="L140" s="29"/>
+      <c r="M140" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="24"/>
+      <c r="N140" s="34"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6419,30 +6452,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="25">
+      <c r="C141" s="35">
         <v>44810</v>
       </c>
-      <c r="D141" s="19"/>
+      <c r="D141" s="29"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="26" t="s">
+      <c r="F141" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="21"/>
-      <c r="H141" s="19"/>
-      <c r="I141" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="19"/>
-      <c r="K141" s="27">
+      <c r="G141" s="31"/>
+      <c r="H141" s="29"/>
+      <c r="I141" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="29"/>
+      <c r="K141" s="37">
         <v>5</v>
       </c>
-      <c r="L141" s="19"/>
-      <c r="M141" s="28" t="s">
+      <c r="L141" s="29"/>
+      <c r="M141" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="24"/>
+      <c r="N141" s="34"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6451,30 +6484,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="18">
+      <c r="C142" s="28">
         <v>44810</v>
       </c>
-      <c r="D142" s="19"/>
+      <c r="D142" s="29"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="20" t="s">
+      <c r="F142" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="21"/>
-      <c r="H142" s="19"/>
-      <c r="I142" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="19"/>
-      <c r="K142" s="22">
+      <c r="G142" s="31"/>
+      <c r="H142" s="29"/>
+      <c r="I142" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="29"/>
+      <c r="K142" s="32">
         <v>45</v>
       </c>
-      <c r="L142" s="19"/>
-      <c r="M142" s="23" t="s">
+      <c r="L142" s="29"/>
+      <c r="M142" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="24"/>
+      <c r="N142" s="34"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6483,30 +6516,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="25">
+      <c r="C143" s="35">
         <v>44811</v>
       </c>
-      <c r="D143" s="19"/>
+      <c r="D143" s="29"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="26" t="s">
+      <c r="F143" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="21"/>
-      <c r="H143" s="19"/>
-      <c r="I143" s="26" t="s">
+      <c r="G143" s="31"/>
+      <c r="H143" s="29"/>
+      <c r="I143" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="19"/>
-      <c r="K143" s="27">
+      <c r="J143" s="29"/>
+      <c r="K143" s="37">
         <v>132</v>
       </c>
-      <c r="L143" s="19"/>
-      <c r="M143" s="28" t="s">
+      <c r="L143" s="29"/>
+      <c r="M143" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="24"/>
+      <c r="N143" s="34"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6515,30 +6548,30 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="18">
+      <c r="C144" s="28">
         <v>44811</v>
       </c>
-      <c r="D144" s="19"/>
+      <c r="D144" s="29"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="20" t="s">
+      <c r="F144" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="21"/>
-      <c r="H144" s="19"/>
-      <c r="I144" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="19"/>
-      <c r="K144" s="22">
+      <c r="G144" s="31"/>
+      <c r="H144" s="29"/>
+      <c r="I144" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="29"/>
+      <c r="K144" s="32">
         <v>66</v>
       </c>
-      <c r="L144" s="19"/>
-      <c r="M144" s="23" t="s">
+      <c r="L144" s="29"/>
+      <c r="M144" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="24"/>
+      <c r="N144" s="34"/>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
@@ -6547,30 +6580,30 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="25">
+      <c r="C145" s="35">
         <v>44812</v>
       </c>
-      <c r="D145" s="19"/>
+      <c r="D145" s="29"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="26" t="s">
+      <c r="F145" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="21"/>
-      <c r="H145" s="19"/>
-      <c r="I145" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J145" s="19"/>
-      <c r="K145" s="27">
+      <c r="G145" s="31"/>
+      <c r="H145" s="29"/>
+      <c r="I145" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="29"/>
+      <c r="K145" s="37">
         <v>69</v>
       </c>
-      <c r="L145" s="19"/>
-      <c r="M145" s="28" t="s">
+      <c r="L145" s="29"/>
+      <c r="M145" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="N145" s="24"/>
+      <c r="N145" s="34"/>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="3" t="s">
@@ -6579,30 +6612,30 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="18">
+      <c r="C146" s="28">
         <v>44812</v>
       </c>
-      <c r="D146" s="19"/>
+      <c r="D146" s="29"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="20" t="s">
+      <c r="F146" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="G146" s="21"/>
-      <c r="H146" s="19"/>
-      <c r="I146" s="20" t="s">
+      <c r="G146" s="31"/>
+      <c r="H146" s="29"/>
+      <c r="I146" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J146" s="19"/>
-      <c r="K146" s="22">
+      <c r="J146" s="29"/>
+      <c r="K146" s="32">
         <v>48</v>
       </c>
-      <c r="L146" s="19"/>
-      <c r="M146" s="23" t="s">
+      <c r="L146" s="29"/>
+      <c r="M146" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="N146" s="24"/>
+      <c r="N146" s="34"/>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
@@ -6611,30 +6644,30 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="25">
+      <c r="C147" s="35">
         <v>44812</v>
       </c>
-      <c r="D147" s="19"/>
+      <c r="D147" s="29"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="26" t="s">
+      <c r="F147" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="G147" s="21"/>
-      <c r="H147" s="19"/>
-      <c r="I147" s="26" t="s">
+      <c r="G147" s="31"/>
+      <c r="H147" s="29"/>
+      <c r="I147" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J147" s="19"/>
-      <c r="K147" s="27">
+      <c r="J147" s="29"/>
+      <c r="K147" s="37">
         <v>33</v>
       </c>
-      <c r="L147" s="19"/>
-      <c r="M147" s="28" t="s">
+      <c r="L147" s="29"/>
+      <c r="M147" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="N147" s="24"/>
+      <c r="N147" s="34"/>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="3" t="s">
@@ -6643,30 +6676,30 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="18">
+      <c r="C148" s="28">
         <v>44813</v>
       </c>
-      <c r="D148" s="19"/>
+      <c r="D148" s="29"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="20" t="s">
+      <c r="F148" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="G148" s="21"/>
-      <c r="H148" s="19"/>
-      <c r="I148" s="20" t="s">
+      <c r="G148" s="31"/>
+      <c r="H148" s="29"/>
+      <c r="I148" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J148" s="19"/>
-      <c r="K148" s="22">
+      <c r="J148" s="29"/>
+      <c r="K148" s="32">
         <v>5</v>
       </c>
-      <c r="L148" s="19"/>
-      <c r="M148" s="23" t="s">
+      <c r="L148" s="29"/>
+      <c r="M148" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="N148" s="24"/>
+      <c r="N148" s="34"/>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
@@ -6675,30 +6708,30 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="25">
+      <c r="C149" s="35">
         <v>44813</v>
       </c>
-      <c r="D149" s="19"/>
+      <c r="D149" s="29"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="26" t="s">
+      <c r="F149" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="G149" s="21"/>
-      <c r="H149" s="19"/>
-      <c r="I149" s="26" t="s">
+      <c r="G149" s="31"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J149" s="19"/>
-      <c r="K149" s="27">
+      <c r="J149" s="29"/>
+      <c r="K149" s="37">
         <v>26</v>
       </c>
-      <c r="L149" s="19"/>
-      <c r="M149" s="28" t="s">
+      <c r="L149" s="29"/>
+      <c r="M149" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="N149" s="24"/>
+      <c r="N149" s="34"/>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="3" t="s">
@@ -6707,30 +6740,30 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="18">
+      <c r="C150" s="28">
         <v>44813</v>
       </c>
-      <c r="D150" s="19"/>
+      <c r="D150" s="29"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="20" t="s">
+      <c r="F150" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="G150" s="21"/>
-      <c r="H150" s="19"/>
-      <c r="I150" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J150" s="19"/>
-      <c r="K150" s="22">
+      <c r="G150" s="31"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="29"/>
+      <c r="K150" s="32">
         <v>13</v>
       </c>
-      <c r="L150" s="19"/>
-      <c r="M150" s="23" t="s">
+      <c r="L150" s="29"/>
+      <c r="M150" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="N150" s="24"/>
+      <c r="N150" s="34"/>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
@@ -6739,30 +6772,30 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="25">
+      <c r="C151" s="35">
         <v>44816</v>
       </c>
-      <c r="D151" s="19"/>
+      <c r="D151" s="29"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="26" t="s">
+      <c r="F151" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="G151" s="21"/>
-      <c r="H151" s="19"/>
-      <c r="I151" s="26" t="s">
+      <c r="G151" s="31"/>
+      <c r="H151" s="29"/>
+      <c r="I151" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J151" s="19"/>
-      <c r="K151" s="27">
+      <c r="J151" s="29"/>
+      <c r="K151" s="37">
         <v>50</v>
       </c>
-      <c r="L151" s="19"/>
-      <c r="M151" s="28" t="s">
+      <c r="L151" s="29"/>
+      <c r="M151" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="N151" s="24"/>
+      <c r="N151" s="34"/>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="3" t="s">
@@ -6771,30 +6804,30 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="18">
+      <c r="C152" s="28">
         <v>44816</v>
       </c>
-      <c r="D152" s="19"/>
+      <c r="D152" s="29"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="20" t="s">
+      <c r="F152" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="21"/>
-      <c r="H152" s="19"/>
-      <c r="I152" s="20" t="s">
+      <c r="G152" s="31"/>
+      <c r="H152" s="29"/>
+      <c r="I152" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J152" s="19"/>
-      <c r="K152" s="22">
+      <c r="J152" s="29"/>
+      <c r="K152" s="32">
         <v>104</v>
       </c>
-      <c r="L152" s="19"/>
-      <c r="M152" s="23" t="s">
+      <c r="L152" s="29"/>
+      <c r="M152" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="N152" s="24"/>
+      <c r="N152" s="34"/>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="1" t="s">
@@ -6803,30 +6836,30 @@
       <c r="B153" s="2">
         <v>44813</v>
       </c>
-      <c r="C153" s="25">
+      <c r="C153" s="35">
         <v>44817</v>
       </c>
-      <c r="D153" s="19"/>
+      <c r="D153" s="29"/>
       <c r="E153" s="2">
         <v>45199</v>
       </c>
-      <c r="F153" s="26" t="s">
+      <c r="F153" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G153" s="21"/>
-      <c r="H153" s="19"/>
-      <c r="I153" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J153" s="19"/>
-      <c r="K153" s="27">
+      <c r="G153" s="31"/>
+      <c r="H153" s="29"/>
+      <c r="I153" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="29"/>
+      <c r="K153" s="37">
         <v>1</v>
       </c>
-      <c r="L153" s="19"/>
-      <c r="M153" s="28" t="s">
+      <c r="L153" s="29"/>
+      <c r="M153" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N153" s="24"/>
+      <c r="N153" s="34"/>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="3" t="s">
@@ -6835,30 +6868,30 @@
       <c r="B154" s="4">
         <v>44813</v>
       </c>
-      <c r="C154" s="18">
+      <c r="C154" s="28">
         <v>44817</v>
       </c>
-      <c r="D154" s="19"/>
+      <c r="D154" s="29"/>
       <c r="E154" s="4">
         <v>44848</v>
       </c>
-      <c r="F154" s="20" t="s">
+      <c r="F154" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G154" s="21"/>
-      <c r="H154" s="19"/>
-      <c r="I154" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J154" s="19"/>
-      <c r="K154" s="22">
+      <c r="G154" s="31"/>
+      <c r="H154" s="29"/>
+      <c r="I154" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="29"/>
+      <c r="K154" s="32">
         <v>2</v>
       </c>
-      <c r="L154" s="19"/>
-      <c r="M154" s="23" t="s">
+      <c r="L154" s="29"/>
+      <c r="M154" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N154" s="24"/>
+      <c r="N154" s="34"/>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="1" t="s">
@@ -6867,30 +6900,30 @@
       <c r="B155" s="2">
         <v>44813</v>
       </c>
-      <c r="C155" s="25">
+      <c r="C155" s="35">
         <v>44817</v>
       </c>
-      <c r="D155" s="19"/>
+      <c r="D155" s="29"/>
       <c r="E155" s="2">
         <v>45198</v>
       </c>
-      <c r="F155" s="26" t="s">
+      <c r="F155" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G155" s="21"/>
-      <c r="H155" s="19"/>
-      <c r="I155" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J155" s="19"/>
-      <c r="K155" s="27">
+      <c r="G155" s="31"/>
+      <c r="H155" s="29"/>
+      <c r="I155" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="29"/>
+      <c r="K155" s="37">
         <v>2</v>
       </c>
-      <c r="L155" s="19"/>
-      <c r="M155" s="28" t="s">
+      <c r="L155" s="29"/>
+      <c r="M155" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N155" s="24"/>
+      <c r="N155" s="34"/>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="3" t="s">
@@ -6899,30 +6932,30 @@
       <c r="B156" s="4">
         <v>44813</v>
       </c>
-      <c r="C156" s="18">
+      <c r="C156" s="28">
         <v>44817</v>
       </c>
-      <c r="D156" s="19"/>
+      <c r="D156" s="29"/>
       <c r="E156" s="4">
         <v>45044</v>
       </c>
-      <c r="F156" s="20" t="s">
+      <c r="F156" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G156" s="21"/>
-      <c r="H156" s="19"/>
-      <c r="I156" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J156" s="19"/>
-      <c r="K156" s="22">
+      <c r="G156" s="31"/>
+      <c r="H156" s="29"/>
+      <c r="I156" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="29"/>
+      <c r="K156" s="32">
         <v>5</v>
       </c>
-      <c r="L156" s="19"/>
-      <c r="M156" s="23" t="s">
+      <c r="L156" s="29"/>
+      <c r="M156" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N156" s="24"/>
+      <c r="N156" s="34"/>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="1" t="s">
@@ -6931,30 +6964,30 @@
       <c r="B157" s="2">
         <v>44813</v>
       </c>
-      <c r="C157" s="25">
+      <c r="C157" s="35">
         <v>44817</v>
       </c>
-      <c r="D157" s="19"/>
+      <c r="D157" s="29"/>
       <c r="E157" s="2">
         <v>45107</v>
       </c>
-      <c r="F157" s="26" t="s">
+      <c r="F157" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G157" s="21"/>
-      <c r="H157" s="19"/>
-      <c r="I157" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J157" s="19"/>
-      <c r="K157" s="27">
+      <c r="G157" s="31"/>
+      <c r="H157" s="29"/>
+      <c r="I157" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="29"/>
+      <c r="K157" s="37">
         <v>2</v>
       </c>
-      <c r="L157" s="19"/>
-      <c r="M157" s="28" t="s">
+      <c r="L157" s="29"/>
+      <c r="M157" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N157" s="24"/>
+      <c r="N157" s="34"/>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="3" t="s">
@@ -6963,30 +6996,30 @@
       <c r="B158" s="4">
         <v>44813</v>
       </c>
-      <c r="C158" s="18">
+      <c r="C158" s="28">
         <v>44817</v>
       </c>
-      <c r="D158" s="19"/>
+      <c r="D158" s="29"/>
       <c r="E158" s="4">
         <v>45192</v>
       </c>
-      <c r="F158" s="20" t="s">
+      <c r="F158" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G158" s="21"/>
-      <c r="H158" s="19"/>
-      <c r="I158" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" s="19"/>
-      <c r="K158" s="22">
+      <c r="G158" s="31"/>
+      <c r="H158" s="29"/>
+      <c r="I158" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="29"/>
+      <c r="K158" s="32">
         <v>1</v>
       </c>
-      <c r="L158" s="19"/>
-      <c r="M158" s="23" t="s">
+      <c r="L158" s="29"/>
+      <c r="M158" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N158" s="24"/>
+      <c r="N158" s="34"/>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="1" t="s">
@@ -6995,30 +7028,30 @@
       <c r="B159" s="2">
         <v>44813</v>
       </c>
-      <c r="C159" s="25">
+      <c r="C159" s="35">
         <v>44817</v>
       </c>
-      <c r="D159" s="19"/>
+      <c r="D159" s="29"/>
       <c r="E159" s="2">
         <v>44957</v>
       </c>
-      <c r="F159" s="26" t="s">
+      <c r="F159" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G159" s="21"/>
-      <c r="H159" s="19"/>
-      <c r="I159" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J159" s="19"/>
-      <c r="K159" s="27">
+      <c r="G159" s="31"/>
+      <c r="H159" s="29"/>
+      <c r="I159" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="29"/>
+      <c r="K159" s="37">
         <v>4</v>
       </c>
-      <c r="L159" s="19"/>
-      <c r="M159" s="28" t="s">
+      <c r="L159" s="29"/>
+      <c r="M159" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N159" s="24"/>
+      <c r="N159" s="34"/>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="3" t="s">
@@ -7027,30 +7060,30 @@
       <c r="B160" s="4">
         <v>44813</v>
       </c>
-      <c r="C160" s="18">
+      <c r="C160" s="28">
         <v>44817</v>
       </c>
-      <c r="D160" s="19"/>
+      <c r="D160" s="29"/>
       <c r="E160" s="4">
         <v>44834</v>
       </c>
-      <c r="F160" s="20" t="s">
+      <c r="F160" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G160" s="21"/>
-      <c r="H160" s="19"/>
-      <c r="I160" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J160" s="19"/>
-      <c r="K160" s="22">
+      <c r="G160" s="31"/>
+      <c r="H160" s="29"/>
+      <c r="I160" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="29"/>
+      <c r="K160" s="32">
         <v>4</v>
       </c>
-      <c r="L160" s="19"/>
-      <c r="M160" s="23" t="s">
+      <c r="L160" s="29"/>
+      <c r="M160" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N160" s="24"/>
+      <c r="N160" s="34"/>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="1" t="s">
@@ -7059,30 +7092,30 @@
       <c r="B161" s="2">
         <v>44813</v>
       </c>
-      <c r="C161" s="25">
+      <c r="C161" s="35">
         <v>44817</v>
       </c>
-      <c r="D161" s="19"/>
+      <c r="D161" s="29"/>
       <c r="E161" s="2">
         <v>45077</v>
       </c>
-      <c r="F161" s="26" t="s">
+      <c r="F161" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G161" s="21"/>
-      <c r="H161" s="19"/>
-      <c r="I161" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J161" s="19"/>
-      <c r="K161" s="27">
+      <c r="G161" s="31"/>
+      <c r="H161" s="29"/>
+      <c r="I161" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="29"/>
+      <c r="K161" s="37">
         <v>3</v>
       </c>
-      <c r="L161" s="19"/>
-      <c r="M161" s="28" t="s">
+      <c r="L161" s="29"/>
+      <c r="M161" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N161" s="24"/>
+      <c r="N161" s="34"/>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="3" t="s">
@@ -7091,30 +7124,30 @@
       <c r="B162" s="4">
         <v>44813</v>
       </c>
-      <c r="C162" s="18">
+      <c r="C162" s="28">
         <v>44817</v>
       </c>
-      <c r="D162" s="19"/>
+      <c r="D162" s="29"/>
       <c r="E162" s="4">
         <v>45093</v>
       </c>
-      <c r="F162" s="20" t="s">
+      <c r="F162" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G162" s="21"/>
-      <c r="H162" s="19"/>
-      <c r="I162" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J162" s="19"/>
-      <c r="K162" s="22">
+      <c r="G162" s="31"/>
+      <c r="H162" s="29"/>
+      <c r="I162" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="29"/>
+      <c r="K162" s="32">
         <v>8</v>
       </c>
-      <c r="L162" s="19"/>
-      <c r="M162" s="23" t="s">
+      <c r="L162" s="29"/>
+      <c r="M162" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N162" s="24"/>
+      <c r="N162" s="34"/>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="1" t="s">
@@ -7123,30 +7156,30 @@
       <c r="B163" s="2">
         <v>44813</v>
       </c>
-      <c r="C163" s="25">
+      <c r="C163" s="35">
         <v>44817</v>
       </c>
-      <c r="D163" s="19"/>
+      <c r="D163" s="29"/>
       <c r="E163" s="2">
         <v>45565</v>
       </c>
-      <c r="F163" s="26" t="s">
+      <c r="F163" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G163" s="21"/>
-      <c r="H163" s="19"/>
-      <c r="I163" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J163" s="19"/>
-      <c r="K163" s="27">
+      <c r="G163" s="31"/>
+      <c r="H163" s="29"/>
+      <c r="I163" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="29"/>
+      <c r="K163" s="37">
         <v>1</v>
       </c>
-      <c r="L163" s="19"/>
-      <c r="M163" s="28" t="s">
+      <c r="L163" s="29"/>
+      <c r="M163" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N163" s="24"/>
+      <c r="N163" s="34"/>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="3" t="s">
@@ -7155,30 +7188,30 @@
       <c r="B164" s="4">
         <v>44813</v>
       </c>
-      <c r="C164" s="18">
+      <c r="C164" s="28">
         <v>44817</v>
       </c>
-      <c r="D164" s="19"/>
+      <c r="D164" s="29"/>
       <c r="E164" s="4">
         <v>45227</v>
       </c>
-      <c r="F164" s="20" t="s">
+      <c r="F164" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G164" s="21"/>
-      <c r="H164" s="19"/>
-      <c r="I164" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J164" s="19"/>
-      <c r="K164" s="22">
+      <c r="G164" s="31"/>
+      <c r="H164" s="29"/>
+      <c r="I164" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="29"/>
+      <c r="K164" s="32">
         <v>2</v>
       </c>
-      <c r="L164" s="19"/>
-      <c r="M164" s="23" t="s">
+      <c r="L164" s="29"/>
+      <c r="M164" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N164" s="24"/>
+      <c r="N164" s="34"/>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="1" t="s">
@@ -7187,30 +7220,30 @@
       <c r="B165" s="2">
         <v>44813</v>
       </c>
-      <c r="C165" s="25">
+      <c r="C165" s="35">
         <v>44817</v>
       </c>
-      <c r="D165" s="19"/>
+      <c r="D165" s="29"/>
       <c r="E165" s="2">
         <v>45046</v>
       </c>
-      <c r="F165" s="26" t="s">
+      <c r="F165" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G165" s="21"/>
-      <c r="H165" s="19"/>
-      <c r="I165" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J165" s="19"/>
-      <c r="K165" s="27">
+      <c r="G165" s="31"/>
+      <c r="H165" s="29"/>
+      <c r="I165" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="29"/>
+      <c r="K165" s="37">
         <v>1</v>
       </c>
-      <c r="L165" s="19"/>
-      <c r="M165" s="28" t="s">
+      <c r="L165" s="29"/>
+      <c r="M165" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N165" s="24"/>
+      <c r="N165" s="34"/>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="3" t="s">
@@ -7219,30 +7252,30 @@
       <c r="B166" s="4">
         <v>44813</v>
       </c>
-      <c r="C166" s="18">
+      <c r="C166" s="28">
         <v>44817</v>
       </c>
-      <c r="D166" s="19"/>
+      <c r="D166" s="29"/>
       <c r="E166" s="4">
         <v>45092</v>
       </c>
-      <c r="F166" s="20" t="s">
+      <c r="F166" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G166" s="21"/>
-      <c r="H166" s="19"/>
-      <c r="I166" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J166" s="19"/>
-      <c r="K166" s="22">
+      <c r="G166" s="31"/>
+      <c r="H166" s="29"/>
+      <c r="I166" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="29"/>
+      <c r="K166" s="32">
         <v>3</v>
       </c>
-      <c r="L166" s="19"/>
-      <c r="M166" s="23" t="s">
+      <c r="L166" s="29"/>
+      <c r="M166" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N166" s="24"/>
+      <c r="N166" s="34"/>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="1" t="s">
@@ -7251,30 +7284,30 @@
       <c r="B167" s="2">
         <v>44813</v>
       </c>
-      <c r="C167" s="25">
+      <c r="C167" s="35">
         <v>44817</v>
       </c>
-      <c r="D167" s="19"/>
+      <c r="D167" s="29"/>
       <c r="E167" s="2">
         <v>44985</v>
       </c>
-      <c r="F167" s="26" t="s">
+      <c r="F167" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="G167" s="21"/>
-      <c r="H167" s="19"/>
-      <c r="I167" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J167" s="19"/>
-      <c r="K167" s="27">
+      <c r="G167" s="31"/>
+      <c r="H167" s="29"/>
+      <c r="I167" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="29"/>
+      <c r="K167" s="37">
         <v>1</v>
       </c>
-      <c r="L167" s="19"/>
-      <c r="M167" s="28" t="s">
+      <c r="L167" s="29"/>
+      <c r="M167" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N167" s="24"/>
+      <c r="N167" s="34"/>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="3" t="s">
@@ -7283,30 +7316,30 @@
       <c r="B168" s="4">
         <v>44813</v>
       </c>
-      <c r="C168" s="18">
+      <c r="C168" s="28">
         <v>44817</v>
       </c>
-      <c r="D168" s="19"/>
+      <c r="D168" s="29"/>
       <c r="E168" s="4">
         <v>45555</v>
       </c>
-      <c r="F168" s="20" t="s">
+      <c r="F168" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G168" s="21"/>
-      <c r="H168" s="19"/>
-      <c r="I168" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J168" s="19"/>
-      <c r="K168" s="22">
+      <c r="G168" s="31"/>
+      <c r="H168" s="29"/>
+      <c r="I168" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="29"/>
+      <c r="K168" s="32">
         <v>1</v>
       </c>
-      <c r="L168" s="19"/>
-      <c r="M168" s="23" t="s">
+      <c r="L168" s="29"/>
+      <c r="M168" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="N168" s="24"/>
+      <c r="N168" s="34"/>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="1" t="s">
@@ -7315,30 +7348,30 @@
       <c r="B169" s="2">
         <v>44811</v>
       </c>
-      <c r="C169" s="25">
+      <c r="C169" s="35">
         <v>44817</v>
       </c>
-      <c r="D169" s="19"/>
+      <c r="D169" s="29"/>
       <c r="E169" s="2">
         <v>44882</v>
       </c>
-      <c r="F169" s="26" t="s">
+      <c r="F169" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="G169" s="21"/>
-      <c r="H169" s="19"/>
-      <c r="I169" s="26" t="s">
+      <c r="G169" s="31"/>
+      <c r="H169" s="29"/>
+      <c r="I169" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J169" s="19"/>
-      <c r="K169" s="27">
+      <c r="J169" s="29"/>
+      <c r="K169" s="37">
         <v>92</v>
       </c>
-      <c r="L169" s="19"/>
-      <c r="M169" s="28" t="s">
+      <c r="L169" s="29"/>
+      <c r="M169" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="N169" s="24"/>
+      <c r="N169" s="34"/>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="3" t="s">
@@ -7347,30 +7380,30 @@
       <c r="B170" s="4">
         <v>44811</v>
       </c>
-      <c r="C170" s="18">
+      <c r="C170" s="28">
         <v>44817</v>
       </c>
-      <c r="D170" s="19"/>
+      <c r="D170" s="29"/>
       <c r="E170" s="4">
         <v>44882</v>
       </c>
-      <c r="F170" s="20" t="s">
+      <c r="F170" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="G170" s="21"/>
-      <c r="H170" s="19"/>
-      <c r="I170" s="20" t="s">
+      <c r="G170" s="31"/>
+      <c r="H170" s="29"/>
+      <c r="I170" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J170" s="19"/>
-      <c r="K170" s="22">
+      <c r="J170" s="29"/>
+      <c r="K170" s="32">
         <v>169</v>
       </c>
-      <c r="L170" s="19"/>
-      <c r="M170" s="23" t="s">
+      <c r="L170" s="29"/>
+      <c r="M170" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="N170" s="24"/>
+      <c r="N170" s="34"/>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="1" t="s">
@@ -7379,30 +7412,30 @@
       <c r="B171" s="2">
         <v>44817</v>
       </c>
-      <c r="C171" s="25">
+      <c r="C171" s="35">
         <v>44818</v>
       </c>
-      <c r="D171" s="19"/>
+      <c r="D171" s="29"/>
       <c r="E171" s="2">
         <v>44888</v>
       </c>
-      <c r="F171" s="26" t="s">
+      <c r="F171" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="G171" s="21"/>
-      <c r="H171" s="19"/>
-      <c r="I171" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J171" s="19"/>
-      <c r="K171" s="27">
+      <c r="G171" s="31"/>
+      <c r="H171" s="29"/>
+      <c r="I171" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="29"/>
+      <c r="K171" s="37">
         <v>99</v>
       </c>
-      <c r="L171" s="19"/>
-      <c r="M171" s="28" t="s">
+      <c r="L171" s="29"/>
+      <c r="M171" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="N171" s="24"/>
+      <c r="N171" s="34"/>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="3" t="s">
@@ -7411,30 +7444,30 @@
       <c r="B172" s="4">
         <v>44817</v>
       </c>
-      <c r="C172" s="18">
+      <c r="C172" s="28">
         <v>44818</v>
       </c>
-      <c r="D172" s="19"/>
+      <c r="D172" s="29"/>
       <c r="E172" s="4">
         <v>44911</v>
       </c>
-      <c r="F172" s="20" t="s">
+      <c r="F172" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="G172" s="21"/>
-      <c r="H172" s="19"/>
-      <c r="I172" s="20" t="s">
+      <c r="G172" s="31"/>
+      <c r="H172" s="29"/>
+      <c r="I172" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J172" s="19"/>
-      <c r="K172" s="22">
+      <c r="J172" s="29"/>
+      <c r="K172" s="32">
         <v>10</v>
       </c>
-      <c r="L172" s="19"/>
-      <c r="M172" s="23" t="s">
+      <c r="L172" s="29"/>
+      <c r="M172" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="N172" s="24"/>
+      <c r="N172" s="34"/>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="1" t="s">
@@ -7443,30 +7476,30 @@
       <c r="B173" s="2">
         <v>44817</v>
       </c>
-      <c r="C173" s="25">
+      <c r="C173" s="35">
         <v>44818</v>
       </c>
-      <c r="D173" s="19"/>
+      <c r="D173" s="29"/>
       <c r="E173" s="2">
         <v>44876</v>
       </c>
-      <c r="F173" s="26" t="s">
+      <c r="F173" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="G173" s="21"/>
-      <c r="H173" s="19"/>
-      <c r="I173" s="26" t="s">
+      <c r="G173" s="31"/>
+      <c r="H173" s="29"/>
+      <c r="I173" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="J173" s="19"/>
-      <c r="K173" s="27">
+      <c r="J173" s="29"/>
+      <c r="K173" s="37">
         <v>69</v>
       </c>
-      <c r="L173" s="19"/>
-      <c r="M173" s="28" t="s">
+      <c r="L173" s="29"/>
+      <c r="M173" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="N173" s="24"/>
+      <c r="N173" s="34"/>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="3" t="s">
@@ -7475,30 +7508,30 @@
       <c r="B174" s="4">
         <v>44810</v>
       </c>
-      <c r="C174" s="18">
+      <c r="C174" s="28">
         <v>44819</v>
       </c>
-      <c r="D174" s="19"/>
+      <c r="D174" s="29"/>
       <c r="E174" s="4">
         <v>44870</v>
       </c>
-      <c r="F174" s="20" t="s">
+      <c r="F174" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="G174" s="21"/>
-      <c r="H174" s="19"/>
-      <c r="I174" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J174" s="19"/>
-      <c r="K174" s="22">
+      <c r="G174" s="31"/>
+      <c r="H174" s="29"/>
+      <c r="I174" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="29"/>
+      <c r="K174" s="32">
         <v>115</v>
       </c>
-      <c r="L174" s="19"/>
-      <c r="M174" s="23" t="s">
+      <c r="L174" s="29"/>
+      <c r="M174" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="N174" s="24"/>
+      <c r="N174" s="34"/>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="1" t="s">
@@ -7507,30 +7540,30 @@
       <c r="B175" s="2">
         <v>44806</v>
       </c>
-      <c r="C175" s="25">
+      <c r="C175" s="35">
         <v>44819</v>
       </c>
-      <c r="D175" s="19"/>
+      <c r="D175" s="29"/>
       <c r="E175" s="2">
         <v>44867</v>
       </c>
-      <c r="F175" s="26" t="s">
+      <c r="F175" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="G175" s="21"/>
-      <c r="H175" s="19"/>
-      <c r="I175" s="26" t="s">
+      <c r="G175" s="31"/>
+      <c r="H175" s="29"/>
+      <c r="I175" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J175" s="19"/>
-      <c r="K175" s="27">
+      <c r="J175" s="29"/>
+      <c r="K175" s="37">
         <v>109</v>
       </c>
-      <c r="L175" s="19"/>
-      <c r="M175" s="28" t="s">
+      <c r="L175" s="29"/>
+      <c r="M175" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="N175" s="24"/>
+      <c r="N175" s="34"/>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="3" t="s">
@@ -7539,30 +7572,30 @@
       <c r="B176" s="4">
         <v>44818</v>
       </c>
-      <c r="C176" s="18">
+      <c r="C176" s="28">
         <v>44819</v>
       </c>
-      <c r="D176" s="19"/>
+      <c r="D176" s="29"/>
       <c r="E176" s="4">
         <v>44883</v>
       </c>
-      <c r="F176" s="20" t="s">
+      <c r="F176" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="G176" s="21"/>
-      <c r="H176" s="19"/>
-      <c r="I176" s="20" t="s">
+      <c r="G176" s="31"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J176" s="19"/>
-      <c r="K176" s="22">
+      <c r="J176" s="29"/>
+      <c r="K176" s="32">
         <v>113</v>
       </c>
-      <c r="L176" s="19"/>
-      <c r="M176" s="23" t="s">
+      <c r="L176" s="29"/>
+      <c r="M176" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="N176" s="24"/>
+      <c r="N176" s="34"/>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="1" t="s">
@@ -7571,30 +7604,30 @@
       <c r="B177" s="2">
         <v>44818</v>
       </c>
-      <c r="C177" s="25">
+      <c r="C177" s="35">
         <v>44819</v>
       </c>
-      <c r="D177" s="19"/>
+      <c r="D177" s="29"/>
       <c r="E177" s="2">
         <v>44872</v>
       </c>
-      <c r="F177" s="26" t="s">
+      <c r="F177" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="G177" s="21"/>
-      <c r="H177" s="19"/>
-      <c r="I177" s="26" t="s">
+      <c r="G177" s="31"/>
+      <c r="H177" s="29"/>
+      <c r="I177" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="J177" s="19"/>
-      <c r="K177" s="27">
+      <c r="J177" s="29"/>
+      <c r="K177" s="37">
         <v>13</v>
       </c>
-      <c r="L177" s="19"/>
-      <c r="M177" s="28" t="s">
+      <c r="L177" s="29"/>
+      <c r="M177" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="N177" s="24"/>
+      <c r="N177" s="34"/>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="3" t="s">
@@ -7603,30 +7636,30 @@
       <c r="B178" s="4">
         <v>44818</v>
       </c>
-      <c r="C178" s="18">
+      <c r="C178" s="28">
         <v>44819</v>
       </c>
-      <c r="D178" s="19"/>
+      <c r="D178" s="29"/>
       <c r="E178" s="4">
         <v>44818</v>
       </c>
-      <c r="F178" s="20" t="s">
+      <c r="F178" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="G178" s="21"/>
-      <c r="H178" s="19"/>
-      <c r="I178" s="20" t="s">
+      <c r="G178" s="31"/>
+      <c r="H178" s="29"/>
+      <c r="I178" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J178" s="19"/>
-      <c r="K178" s="22">
+      <c r="J178" s="29"/>
+      <c r="K178" s="32">
         <v>1</v>
       </c>
-      <c r="L178" s="19"/>
-      <c r="M178" s="23" t="s">
+      <c r="L178" s="29"/>
+      <c r="M178" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="N178" s="24"/>
+      <c r="N178" s="34"/>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="1" t="s">
@@ -7635,30 +7668,30 @@
       <c r="B179" s="2">
         <v>44811</v>
       </c>
-      <c r="C179" s="25">
+      <c r="C179" s="35">
         <v>44819</v>
       </c>
-      <c r="D179" s="19"/>
+      <c r="D179" s="29"/>
       <c r="E179" s="2">
         <v>44895</v>
       </c>
-      <c r="F179" s="26" t="s">
+      <c r="F179" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="G179" s="21"/>
-      <c r="H179" s="19"/>
-      <c r="I179" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J179" s="19"/>
-      <c r="K179" s="27">
+      <c r="G179" s="31"/>
+      <c r="H179" s="29"/>
+      <c r="I179" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="29"/>
+      <c r="K179" s="37">
         <v>137</v>
       </c>
-      <c r="L179" s="19"/>
-      <c r="M179" s="28" t="s">
+      <c r="L179" s="29"/>
+      <c r="M179" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="N179" s="24"/>
+      <c r="N179" s="34"/>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="3" t="s">
@@ -7667,30 +7700,30 @@
       <c r="B180" s="4">
         <v>44812</v>
       </c>
-      <c r="C180" s="18">
+      <c r="C180" s="28">
         <v>44819</v>
       </c>
-      <c r="D180" s="19"/>
+      <c r="D180" s="29"/>
       <c r="E180" s="4">
         <v>44873</v>
       </c>
-      <c r="F180" s="20" t="s">
+      <c r="F180" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="G180" s="21"/>
-      <c r="H180" s="19"/>
-      <c r="I180" s="20" t="s">
+      <c r="G180" s="31"/>
+      <c r="H180" s="29"/>
+      <c r="I180" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J180" s="19"/>
-      <c r="K180" s="22">
+      <c r="J180" s="29"/>
+      <c r="K180" s="32">
         <v>73</v>
       </c>
-      <c r="L180" s="19"/>
-      <c r="M180" s="23" t="s">
+      <c r="L180" s="29"/>
+      <c r="M180" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="N180" s="24"/>
+      <c r="N180" s="34"/>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="1" t="s">
@@ -7699,30 +7732,30 @@
       <c r="B181" s="2">
         <v>44818</v>
       </c>
-      <c r="C181" s="25">
+      <c r="C181" s="35">
         <v>44819</v>
       </c>
-      <c r="D181" s="19"/>
+      <c r="D181" s="29"/>
       <c r="E181" s="2">
         <v>44880</v>
       </c>
-      <c r="F181" s="26" t="s">
+      <c r="F181" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="G181" s="21"/>
-      <c r="H181" s="19"/>
-      <c r="I181" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J181" s="19"/>
-      <c r="K181" s="27">
+      <c r="G181" s="31"/>
+      <c r="H181" s="29"/>
+      <c r="I181" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="29"/>
+      <c r="K181" s="37">
         <v>108</v>
       </c>
-      <c r="L181" s="19"/>
-      <c r="M181" s="28" t="s">
+      <c r="L181" s="29"/>
+      <c r="M181" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="N181" s="24"/>
+      <c r="N181" s="34"/>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="3" t="s">
@@ -7731,30 +7764,30 @@
       <c r="B182" s="4">
         <v>44812</v>
       </c>
-      <c r="C182" s="18">
+      <c r="C182" s="28">
         <v>44820</v>
       </c>
-      <c r="D182" s="19"/>
+      <c r="D182" s="29"/>
       <c r="E182" s="4">
         <v>44873</v>
       </c>
-      <c r="F182" s="20" t="s">
+      <c r="F182" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="G182" s="21"/>
-      <c r="H182" s="19"/>
-      <c r="I182" s="20" t="s">
+      <c r="G182" s="31"/>
+      <c r="H182" s="29"/>
+      <c r="I182" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J182" s="19"/>
-      <c r="K182" s="22">
+      <c r="J182" s="29"/>
+      <c r="K182" s="32">
         <v>49</v>
       </c>
-      <c r="L182" s="19"/>
-      <c r="M182" s="23" t="s">
+      <c r="L182" s="29"/>
+      <c r="M182" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="N182" s="24"/>
+      <c r="N182" s="34"/>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="1" t="s">
@@ -7763,30 +7796,30 @@
       <c r="B183" s="2">
         <v>44812</v>
       </c>
-      <c r="C183" s="25">
+      <c r="C183" s="35">
         <v>44820</v>
       </c>
-      <c r="D183" s="19"/>
+      <c r="D183" s="29"/>
       <c r="E183" s="2">
         <v>44873</v>
       </c>
-      <c r="F183" s="26" t="s">
+      <c r="F183" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="G183" s="21"/>
-      <c r="H183" s="19"/>
-      <c r="I183" s="26" t="s">
+      <c r="G183" s="31"/>
+      <c r="H183" s="29"/>
+      <c r="I183" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J183" s="19"/>
-      <c r="K183" s="27">
+      <c r="J183" s="29"/>
+      <c r="K183" s="37">
         <v>49</v>
       </c>
-      <c r="L183" s="19"/>
-      <c r="M183" s="28" t="s">
+      <c r="L183" s="29"/>
+      <c r="M183" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="N183" s="24"/>
+      <c r="N183" s="34"/>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="3" t="s">
@@ -7795,30 +7828,30 @@
       <c r="B184" s="4">
         <v>44812</v>
       </c>
-      <c r="C184" s="18">
+      <c r="C184" s="28">
         <v>44820</v>
       </c>
-      <c r="D184" s="19"/>
+      <c r="D184" s="29"/>
       <c r="E184" s="4">
         <v>44873</v>
       </c>
-      <c r="F184" s="20" t="s">
+      <c r="F184" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="G184" s="21"/>
-      <c r="H184" s="19"/>
-      <c r="I184" s="20" t="s">
+      <c r="G184" s="31"/>
+      <c r="H184" s="29"/>
+      <c r="I184" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J184" s="19"/>
-      <c r="K184" s="22">
+      <c r="J184" s="29"/>
+      <c r="K184" s="32">
         <v>41</v>
       </c>
-      <c r="L184" s="19"/>
-      <c r="M184" s="23" t="s">
+      <c r="L184" s="29"/>
+      <c r="M184" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="N184" s="24"/>
+      <c r="N184" s="34"/>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="1" t="s">
@@ -7827,30 +7860,30 @@
       <c r="B185" s="2">
         <v>44820</v>
       </c>
-      <c r="C185" s="25">
+      <c r="C185" s="35">
         <v>44820</v>
       </c>
-      <c r="D185" s="19"/>
+      <c r="D185" s="29"/>
       <c r="E185" s="2">
         <v>44880</v>
       </c>
-      <c r="F185" s="26" t="s">
+      <c r="F185" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="G185" s="21"/>
-      <c r="H185" s="19"/>
-      <c r="I185" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J185" s="19"/>
-      <c r="K185" s="27">
+      <c r="G185" s="31"/>
+      <c r="H185" s="29"/>
+      <c r="I185" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="29"/>
+      <c r="K185" s="37">
         <v>66</v>
       </c>
-      <c r="L185" s="19"/>
-      <c r="M185" s="28" t="s">
+      <c r="L185" s="29"/>
+      <c r="M185" s="38" t="s">
         <v>308</v>
       </c>
-      <c r="N185" s="24"/>
+      <c r="N185" s="34"/>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="3" t="s">
@@ -7859,30 +7892,30 @@
       <c r="B186" s="4">
         <v>44823</v>
       </c>
-      <c r="C186" s="18">
+      <c r="C186" s="28">
         <v>44823</v>
       </c>
-      <c r="D186" s="19"/>
+      <c r="D186" s="29"/>
       <c r="E186" s="4">
         <v>44883</v>
       </c>
-      <c r="F186" s="20" t="s">
+      <c r="F186" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="G186" s="21"/>
-      <c r="H186" s="19"/>
-      <c r="I186" s="20" t="s">
+      <c r="G186" s="31"/>
+      <c r="H186" s="29"/>
+      <c r="I186" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J186" s="19"/>
-      <c r="K186" s="22">
+      <c r="J186" s="29"/>
+      <c r="K186" s="32">
         <v>57</v>
       </c>
-      <c r="L186" s="19"/>
-      <c r="M186" s="23" t="s">
+      <c r="L186" s="29"/>
+      <c r="M186" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="N186" s="24"/>
+      <c r="N186" s="34"/>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="1" t="s">
@@ -7891,30 +7924,30 @@
       <c r="B187" s="2">
         <v>44823</v>
       </c>
-      <c r="C187" s="25">
+      <c r="C187" s="35">
         <v>44824</v>
       </c>
-      <c r="D187" s="19"/>
+      <c r="D187" s="29"/>
       <c r="E187" s="2">
         <v>44882</v>
       </c>
-      <c r="F187" s="26" t="s">
+      <c r="F187" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="G187" s="21"/>
-      <c r="H187" s="19"/>
-      <c r="I187" s="26" t="s">
+      <c r="G187" s="31"/>
+      <c r="H187" s="29"/>
+      <c r="I187" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J187" s="19"/>
-      <c r="K187" s="27">
+      <c r="J187" s="29"/>
+      <c r="K187" s="37">
         <v>88</v>
       </c>
-      <c r="L187" s="19"/>
-      <c r="M187" s="28" t="s">
+      <c r="L187" s="29"/>
+      <c r="M187" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="N187" s="24"/>
+      <c r="N187" s="34"/>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="3" t="s">
@@ -7923,30 +7956,30 @@
       <c r="B188" s="4">
         <v>44824</v>
       </c>
-      <c r="C188" s="18">
+      <c r="C188" s="28">
         <v>44824</v>
       </c>
-      <c r="D188" s="19"/>
+      <c r="D188" s="29"/>
       <c r="E188" s="4">
         <v>44886</v>
       </c>
-      <c r="F188" s="20" t="s">
+      <c r="F188" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="G188" s="21"/>
-      <c r="H188" s="19"/>
-      <c r="I188" s="20" t="s">
+      <c r="G188" s="31"/>
+      <c r="H188" s="29"/>
+      <c r="I188" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J188" s="19"/>
-      <c r="K188" s="22">
+      <c r="J188" s="29"/>
+      <c r="K188" s="32">
         <v>79</v>
       </c>
-      <c r="L188" s="19"/>
-      <c r="M188" s="23" t="s">
+      <c r="L188" s="29"/>
+      <c r="M188" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="N188" s="24"/>
+      <c r="N188" s="34"/>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="1" t="s">
@@ -7955,30 +7988,30 @@
       <c r="B189" s="2">
         <v>44823</v>
       </c>
-      <c r="C189" s="25">
+      <c r="C189" s="35">
         <v>44825</v>
       </c>
-      <c r="D189" s="19"/>
+      <c r="D189" s="29"/>
       <c r="E189" s="2">
         <v>44883</v>
       </c>
-      <c r="F189" s="26" t="s">
+      <c r="F189" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="G189" s="21"/>
-      <c r="H189" s="19"/>
-      <c r="I189" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J189" s="19"/>
-      <c r="K189" s="27">
+      <c r="G189" s="31"/>
+      <c r="H189" s="29"/>
+      <c r="I189" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="29"/>
+      <c r="K189" s="37">
         <v>49</v>
       </c>
-      <c r="L189" s="19"/>
-      <c r="M189" s="28" t="s">
+      <c r="L189" s="29"/>
+      <c r="M189" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="N189" s="24"/>
+      <c r="N189" s="34"/>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="3" t="s">
@@ -7987,30 +8020,30 @@
       <c r="B190" s="4">
         <v>44824</v>
       </c>
-      <c r="C190" s="18">
+      <c r="C190" s="28">
         <v>44825</v>
       </c>
-      <c r="D190" s="19"/>
+      <c r="D190" s="29"/>
       <c r="E190" s="4">
         <v>44872</v>
       </c>
-      <c r="F190" s="20" t="s">
+      <c r="F190" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="G190" s="21"/>
-      <c r="H190" s="19"/>
-      <c r="I190" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J190" s="19"/>
-      <c r="K190" s="22">
+      <c r="G190" s="31"/>
+      <c r="H190" s="29"/>
+      <c r="I190" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="29"/>
+      <c r="K190" s="32">
         <v>104</v>
       </c>
-      <c r="L190" s="19"/>
-      <c r="M190" s="23" t="s">
+      <c r="L190" s="29"/>
+      <c r="M190" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="N190" s="24"/>
+      <c r="N190" s="34"/>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="1" t="s">
@@ -8019,30 +8052,30 @@
       <c r="B191" s="2">
         <v>44824</v>
       </c>
-      <c r="C191" s="25">
+      <c r="C191" s="35">
         <v>44825</v>
       </c>
-      <c r="D191" s="19"/>
+      <c r="D191" s="29"/>
       <c r="E191" s="2">
         <v>44872</v>
       </c>
-      <c r="F191" s="26" t="s">
+      <c r="F191" s="36" t="s">
         <v>317</v>
       </c>
-      <c r="G191" s="21"/>
-      <c r="H191" s="19"/>
-      <c r="I191" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J191" s="19"/>
-      <c r="K191" s="27">
+      <c r="G191" s="31"/>
+      <c r="H191" s="29"/>
+      <c r="I191" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="29"/>
+      <c r="K191" s="37">
         <v>7</v>
       </c>
-      <c r="L191" s="19"/>
-      <c r="M191" s="28" t="s">
+      <c r="L191" s="29"/>
+      <c r="M191" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="N191" s="24"/>
+      <c r="N191" s="34"/>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="3" t="s">
@@ -8051,30 +8084,30 @@
       <c r="B192" s="4">
         <v>44826</v>
       </c>
-      <c r="C192" s="18">
+      <c r="C192" s="28">
         <v>44826</v>
       </c>
-      <c r="D192" s="19"/>
+      <c r="D192" s="29"/>
       <c r="E192" s="4">
         <v>44888</v>
       </c>
-      <c r="F192" s="20" t="s">
+      <c r="F192" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="G192" s="21"/>
-      <c r="H192" s="19"/>
-      <c r="I192" s="20" t="s">
+      <c r="G192" s="31"/>
+      <c r="H192" s="29"/>
+      <c r="I192" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J192" s="19"/>
-      <c r="K192" s="22">
+      <c r="J192" s="29"/>
+      <c r="K192" s="32">
         <v>15</v>
       </c>
-      <c r="L192" s="19"/>
-      <c r="M192" s="23" t="s">
+      <c r="L192" s="29"/>
+      <c r="M192" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="N192" s="24"/>
+      <c r="N192" s="34"/>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="1" t="s">
@@ -8083,30 +8116,30 @@
       <c r="B193" s="2">
         <v>44825</v>
       </c>
-      <c r="C193" s="25">
+      <c r="C193" s="35">
         <v>44826</v>
       </c>
-      <c r="D193" s="19"/>
+      <c r="D193" s="29"/>
       <c r="E193" s="2">
         <v>44867</v>
       </c>
-      <c r="F193" s="26" t="s">
+      <c r="F193" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="G193" s="21"/>
-      <c r="H193" s="19"/>
-      <c r="I193" s="26" t="s">
+      <c r="G193" s="31"/>
+      <c r="H193" s="29"/>
+      <c r="I193" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J193" s="19"/>
-      <c r="K193" s="27">
-        <v>18</v>
-      </c>
-      <c r="L193" s="19"/>
-      <c r="M193" s="28" t="s">
+      <c r="J193" s="29"/>
+      <c r="K193" s="37">
+        <v>18</v>
+      </c>
+      <c r="L193" s="29"/>
+      <c r="M193" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="N193" s="24"/>
+      <c r="N193" s="34"/>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="3" t="s">
@@ -8115,30 +8148,30 @@
       <c r="B194" s="4">
         <v>44825</v>
       </c>
-      <c r="C194" s="18">
+      <c r="C194" s="28">
         <v>44826</v>
       </c>
-      <c r="D194" s="19"/>
+      <c r="D194" s="29"/>
       <c r="E194" s="4">
         <v>44867</v>
       </c>
-      <c r="F194" s="20" t="s">
+      <c r="F194" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="G194" s="21"/>
-      <c r="H194" s="19"/>
-      <c r="I194" s="20" t="s">
+      <c r="G194" s="31"/>
+      <c r="H194" s="29"/>
+      <c r="I194" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J194" s="19"/>
-      <c r="K194" s="22">
+      <c r="J194" s="29"/>
+      <c r="K194" s="32">
         <v>69</v>
       </c>
-      <c r="L194" s="19"/>
-      <c r="M194" s="23" t="s">
+      <c r="L194" s="29"/>
+      <c r="M194" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="N194" s="24"/>
+      <c r="N194" s="34"/>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="1" t="s">
@@ -8147,30 +8180,30 @@
       <c r="B195" s="2">
         <v>44825</v>
       </c>
-      <c r="C195" s="25">
+      <c r="C195" s="35">
         <v>44826</v>
       </c>
-      <c r="D195" s="19"/>
+      <c r="D195" s="29"/>
       <c r="E195" s="2">
         <v>44867</v>
       </c>
-      <c r="F195" s="26" t="s">
+      <c r="F195" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="G195" s="21"/>
-      <c r="H195" s="19"/>
-      <c r="I195" s="26" t="s">
+      <c r="G195" s="31"/>
+      <c r="H195" s="29"/>
+      <c r="I195" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J195" s="19"/>
-      <c r="K195" s="27">
+      <c r="J195" s="29"/>
+      <c r="K195" s="37">
         <v>11</v>
       </c>
-      <c r="L195" s="19"/>
-      <c r="M195" s="28" t="s">
+      <c r="L195" s="29"/>
+      <c r="M195" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="N195" s="24"/>
+      <c r="N195" s="34"/>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="3" t="s">
@@ -8179,30 +8212,30 @@
       <c r="B196" s="4">
         <v>44825</v>
       </c>
-      <c r="C196" s="18">
+      <c r="C196" s="28">
         <v>44826</v>
       </c>
-      <c r="D196" s="19"/>
+      <c r="D196" s="29"/>
       <c r="E196" s="4">
         <v>44867</v>
       </c>
-      <c r="F196" s="20" t="s">
+      <c r="F196" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="G196" s="21"/>
-      <c r="H196" s="19"/>
-      <c r="I196" s="20" t="s">
+      <c r="G196" s="31"/>
+      <c r="H196" s="29"/>
+      <c r="I196" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J196" s="19"/>
-      <c r="K196" s="22">
+      <c r="J196" s="29"/>
+      <c r="K196" s="32">
         <v>2</v>
       </c>
-      <c r="L196" s="19"/>
-      <c r="M196" s="23" t="s">
+      <c r="L196" s="29"/>
+      <c r="M196" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="N196" s="24"/>
+      <c r="N196" s="34"/>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="1" t="s">
@@ -8211,30 +8244,30 @@
       <c r="B197" s="2">
         <v>44827</v>
       </c>
-      <c r="C197" s="25">
+      <c r="C197" s="35">
         <v>44827</v>
       </c>
-      <c r="D197" s="19"/>
+      <c r="D197" s="29"/>
       <c r="E197" s="2">
         <v>44888</v>
       </c>
-      <c r="F197" s="26" t="s">
+      <c r="F197" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="G197" s="21"/>
-      <c r="H197" s="19"/>
-      <c r="I197" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J197" s="19"/>
-      <c r="K197" s="27">
+      <c r="G197" s="31"/>
+      <c r="H197" s="29"/>
+      <c r="I197" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="29"/>
+      <c r="K197" s="37">
         <v>72</v>
       </c>
-      <c r="L197" s="19"/>
-      <c r="M197" s="28" t="s">
+      <c r="L197" s="29"/>
+      <c r="M197" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="N197" s="24"/>
+      <c r="N197" s="34"/>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="3" t="s">
@@ -8243,30 +8276,30 @@
       <c r="B198" s="4">
         <v>44830</v>
       </c>
-      <c r="C198" s="18">
+      <c r="C198" s="28">
         <v>44830</v>
       </c>
-      <c r="D198" s="19"/>
+      <c r="D198" s="29"/>
       <c r="E198" s="4">
         <v>44891</v>
       </c>
-      <c r="F198" s="20" t="s">
+      <c r="F198" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="G198" s="21"/>
-      <c r="H198" s="19"/>
-      <c r="I198" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J198" s="19"/>
-      <c r="K198" s="22">
+      <c r="G198" s="31"/>
+      <c r="H198" s="29"/>
+      <c r="I198" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="29"/>
+      <c r="K198" s="32">
         <v>51</v>
       </c>
-      <c r="L198" s="19"/>
-      <c r="M198" s="23" t="s">
+      <c r="L198" s="29"/>
+      <c r="M198" s="33" t="s">
         <v>332</v>
       </c>
-      <c r="N198" s="24"/>
+      <c r="N198" s="34"/>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="1" t="s">
@@ -8275,30 +8308,30 @@
       <c r="B199" s="2">
         <v>44830</v>
       </c>
-      <c r="C199" s="25">
+      <c r="C199" s="35">
         <v>44830</v>
       </c>
-      <c r="D199" s="19"/>
+      <c r="D199" s="29"/>
       <c r="E199" s="2">
         <v>44892</v>
       </c>
-      <c r="F199" s="26" t="s">
+      <c r="F199" s="36" t="s">
         <v>333</v>
       </c>
-      <c r="G199" s="21"/>
-      <c r="H199" s="19"/>
-      <c r="I199" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J199" s="19"/>
-      <c r="K199" s="27">
+      <c r="G199" s="31"/>
+      <c r="H199" s="29"/>
+      <c r="I199" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="29"/>
+      <c r="K199" s="37">
         <v>353</v>
       </c>
-      <c r="L199" s="19"/>
-      <c r="M199" s="28" t="s">
+      <c r="L199" s="29"/>
+      <c r="M199" s="38" t="s">
         <v>334</v>
       </c>
-      <c r="N199" s="24"/>
+      <c r="N199" s="34"/>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="3" t="s">
@@ -8307,107 +8340,329 @@
       <c r="B200" s="4">
         <v>44830</v>
       </c>
-      <c r="C200" s="18">
+      <c r="C200" s="28">
         <v>44830</v>
       </c>
-      <c r="D200" s="19"/>
+      <c r="D200" s="29"/>
       <c r="E200" s="4">
         <v>44891</v>
       </c>
-      <c r="F200" s="20" t="s">
+      <c r="F200" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="G200" s="21"/>
-      <c r="H200" s="19"/>
-      <c r="I200" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J200" s="19"/>
-      <c r="K200" s="22">
+      <c r="G200" s="31"/>
+      <c r="H200" s="29"/>
+      <c r="I200" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="29"/>
+      <c r="K200" s="32">
         <v>46</v>
       </c>
-      <c r="L200" s="19"/>
-      <c r="M200" s="23" t="s">
+      <c r="L200" s="29"/>
+      <c r="M200" s="33" t="s">
         <v>335</v>
       </c>
-      <c r="N200" s="24"/>
-    </row>
-    <row r="201" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A201" s="47" t="s">
+      <c r="N200" s="34"/>
+    </row>
+    <row r="201" spans="1:14">
+      <c r="A201" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B201" s="2">
+        <v>44825</v>
+      </c>
+      <c r="C201" s="35">
+        <v>44831</v>
+      </c>
+      <c r="D201" s="29"/>
+      <c r="E201" s="2">
+        <v>44888</v>
+      </c>
+      <c r="F201" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G201" s="31"/>
+      <c r="H201" s="29"/>
+      <c r="I201" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="J201" s="29"/>
+      <c r="K201" s="37">
+        <v>905</v>
+      </c>
+      <c r="L201" s="29"/>
+      <c r="M201" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="N201" s="34"/>
+    </row>
+    <row r="202" spans="1:14">
+      <c r="A202" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B202" s="4">
+        <v>44830</v>
+      </c>
+      <c r="C202" s="28">
+        <v>44831</v>
+      </c>
+      <c r="D202" s="29"/>
+      <c r="E202" s="4">
+        <v>44890</v>
+      </c>
+      <c r="F202" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="G202" s="31"/>
+      <c r="H202" s="29"/>
+      <c r="I202" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="29"/>
+      <c r="K202" s="32">
+        <v>63</v>
+      </c>
+      <c r="L202" s="29"/>
+      <c r="M202" s="33" t="s">
+        <v>339</v>
+      </c>
+      <c r="N202" s="34"/>
+    </row>
+    <row r="203" spans="1:14">
+      <c r="A203" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B203" s="2">
+        <v>44824</v>
+      </c>
+      <c r="C203" s="35">
+        <v>44831</v>
+      </c>
+      <c r="D203" s="29"/>
+      <c r="E203" s="2">
+        <v>44887</v>
+      </c>
+      <c r="F203" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G203" s="31"/>
+      <c r="H203" s="29"/>
+      <c r="I203" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="J203" s="29"/>
+      <c r="K203" s="37">
+        <v>308</v>
+      </c>
+      <c r="L203" s="29"/>
+      <c r="M203" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="N203" s="34"/>
+    </row>
+    <row r="204" spans="1:14">
+      <c r="A204" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B204" s="4">
+        <v>44818</v>
+      </c>
+      <c r="C204" s="28">
+        <v>44832</v>
+      </c>
+      <c r="D204" s="29"/>
+      <c r="E204" s="4">
+        <v>44879</v>
+      </c>
+      <c r="F204" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="G204" s="31"/>
+      <c r="H204" s="29"/>
+      <c r="I204" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="29"/>
+      <c r="K204" s="32">
+        <v>10</v>
+      </c>
+      <c r="L204" s="29"/>
+      <c r="M204" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="N204" s="34"/>
+    </row>
+    <row r="205" spans="1:14">
+      <c r="A205" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B205" s="2">
+        <v>44832</v>
+      </c>
+      <c r="C205" s="35">
+        <v>44832</v>
+      </c>
+      <c r="D205" s="29"/>
+      <c r="E205" s="2">
+        <v>44893</v>
+      </c>
+      <c r="F205" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="G205" s="31"/>
+      <c r="H205" s="29"/>
+      <c r="I205" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J205" s="29"/>
+      <c r="K205" s="37">
+        <v>93</v>
+      </c>
+      <c r="L205" s="29"/>
+      <c r="M205" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="N205" s="34"/>
+    </row>
+    <row r="206" spans="1:14">
+      <c r="A206" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B206" s="4">
+        <v>44820</v>
+      </c>
+      <c r="C206" s="28">
+        <v>44832</v>
+      </c>
+      <c r="D206" s="29"/>
+      <c r="E206" s="4">
+        <v>44849</v>
+      </c>
+      <c r="F206" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="G206" s="31"/>
+      <c r="H206" s="29"/>
+      <c r="I206" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="29"/>
+      <c r="K206" s="32">
+        <v>70</v>
+      </c>
+      <c r="L206" s="29"/>
+      <c r="M206" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="B201" s="48"/>
-      <c r="C201" s="44" t="s">
-        <v>336</v>
-      </c>
-      <c r="D201" s="45"/>
-      <c r="E201" s="46"/>
-      <c r="F201" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="G201" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="H201" s="44" t="s">
-        <v>339</v>
-      </c>
-      <c r="I201" s="46"/>
-      <c r="J201" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="K201" s="46"/>
-      <c r="L201" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="M201" s="46"/>
-      <c r="N201" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" s="8" customFormat="1">
-      <c r="A202" s="42" t="s">
-        <v>343</v>
-      </c>
-      <c r="B202" s="43"/>
-      <c r="C202" s="39">
-        <v>13756</v>
-      </c>
-      <c r="D202" s="40"/>
-      <c r="E202" s="41"/>
-      <c r="F202" s="5">
-        <v>114</v>
-      </c>
-      <c r="G202" s="6">
-        <v>5</v>
-      </c>
-      <c r="H202" s="39">
+      <c r="N206" s="34"/>
+    </row>
+    <row r="207" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A207" s="47" t="s">
+        <v>357</v>
+      </c>
+      <c r="B207" s="48"/>
+      <c r="C207" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="D207" s="45"/>
+      <c r="E207" s="46"/>
+      <c r="F207" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="H207" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="I207" s="46"/>
+      <c r="J207" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="K207" s="46"/>
+      <c r="L207" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="M207" s="46"/>
+      <c r="N207" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" s="9" customFormat="1">
+      <c r="A208" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="B208" s="43"/>
+      <c r="C208" s="39">
+        <v>15205</v>
+      </c>
+      <c r="D208" s="40"/>
+      <c r="E208" s="41"/>
+      <c r="F208" s="7">
+        <v>117</v>
+      </c>
+      <c r="G208" s="7">
+        <v>7</v>
+      </c>
+      <c r="H208" s="39">
         <v>1</v>
       </c>
-      <c r="I202" s="41"/>
-      <c r="J202" s="39">
-        <v>75</v>
-      </c>
-      <c r="K202" s="41"/>
-      <c r="L202" s="39">
+      <c r="I208" s="41"/>
+      <c r="J208" s="39">
+        <v>76</v>
+      </c>
+      <c r="K208" s="41"/>
+      <c r="L208" s="39">
         <v>1</v>
       </c>
-      <c r="M202" s="41"/>
-      <c r="N202" s="7">
+      <c r="M208" s="41"/>
+      <c r="N208" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1002">
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="H202:I202"/>
-    <mergeCell ref="J202:K202"/>
-    <mergeCell ref="L202:M202"/>
-    <mergeCell ref="A202:B202"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="H201:I201"/>
-    <mergeCell ref="J201:K201"/>
-    <mergeCell ref="L201:M201"/>
-    <mergeCell ref="A201:B201"/>
+  <mergeCells count="1032">
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="H208:I208"/>
+    <mergeCell ref="J208:K208"/>
+    <mergeCell ref="L208:M208"/>
+    <mergeCell ref="A208:B208"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="H207:I207"/>
+    <mergeCell ref="J207:K207"/>
+    <mergeCell ref="L207:M207"/>
+    <mergeCell ref="A207:B207"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:H206"/>
+    <mergeCell ref="I206:J206"/>
+    <mergeCell ref="K206:L206"/>
+    <mergeCell ref="M206:N206"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="F205:H205"/>
+    <mergeCell ref="I205:J205"/>
+    <mergeCell ref="K205:L205"/>
+    <mergeCell ref="M205:N205"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="F204:H204"/>
+    <mergeCell ref="I204:J204"/>
+    <mergeCell ref="K204:L204"/>
+    <mergeCell ref="M204:N204"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="F203:H203"/>
+    <mergeCell ref="I203:J203"/>
+    <mergeCell ref="K203:L203"/>
+    <mergeCell ref="M203:N203"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="F202:H202"/>
+    <mergeCell ref="I202:J202"/>
+    <mergeCell ref="K202:L202"/>
+    <mergeCell ref="M202:N202"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="F201:H201"/>
+    <mergeCell ref="I201:J201"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="M201:N201"/>
     <mergeCell ref="C200:D200"/>
     <mergeCell ref="F200:H200"/>
     <mergeCell ref="I200:J200"/>
@@ -9368,6 +9623,18 @@
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="M9:N9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:J8"/>
@@ -9378,8 +9645,6 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="I6:J6"/>
@@ -9390,16 +9655,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12432"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14988" windowHeight="8292"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="369">
   <si>
     <t/>
   </si>
@@ -1103,6 +1103,39 @@
     <t>Bldg. 873 Rogers Rd. NAS North Island  San Diego CA 92135</t>
   </si>
   <si>
+    <t>Albertson's Santa Fe Springs Pharmacy</t>
+  </si>
+  <si>
+    <t>12874 Florence Avenue  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Airgas</t>
+  </si>
+  <si>
+    <t>2355 Workman Mill Road  Whittier CA 90601</t>
+  </si>
+  <si>
+    <t>Oracle America, Inc.</t>
+  </si>
+  <si>
+    <t>500 Oracle Parkway  Redwood City CA 94065</t>
+  </si>
+  <si>
+    <t>Skinny Labs Inc. dba SPIN</t>
+  </si>
+  <si>
+    <t>2 Embarcadero Center 7th Floor, Suite 104  San Francisco CA 94111</t>
+  </si>
+  <si>
+    <t>Yolo County</t>
+  </si>
+  <si>
+    <t>Alforex Seeds, LLC wholly owned subsidiary of Corteva, Inc.</t>
+  </si>
+  <si>
+    <t>18369 Country Road 96  Woodland CA 95695</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1132,11 +1165,11 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 9/28/2022
+ End Date: 10/3/2022
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Report Summary </t>
+    <t>Report Summary</t>
   </si>
 </sst>
 </file>
@@ -1204,12 +1237,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFDCDCDC"/>
       </patternFill>
@@ -1224,6 +1251,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FFDCDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1546,7 +1579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -1567,56 +1600,80 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1628,34 +1685,13 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1673,19 +1709,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1968,130 +2004,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R208"/>
+  <dimension ref="A1:R213"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="3" customWidth="1"/>
-    <col min="4" max="4" width="5.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="11" width="5" customWidth="1"/>
-    <col min="12" max="12" width="5.88671875" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="3" max="3" width="2.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" customWidth="1"/>
     <col min="13" max="13" width="7.109375" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="39.75" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="A1" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="37.5" customHeight="1">
+      <c r="A2" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="21" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="22"/>
-      <c r="K3" s="21" t="s">
+      <c r="J3" s="30"/>
+      <c r="K3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="24" t="s">
+      <c r="L3" s="30"/>
+      <c r="M3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="25"/>
+      <c r="N3" s="33"/>
     </row>
     <row r="4" spans="1:18" ht="24.6">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="25"/>
+      <c r="E4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="16" t="s">
+      <c r="G4" s="26"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="16" t="s">
+      <c r="J4" s="25"/>
+      <c r="K4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="19" t="s">
+      <c r="L4" s="25"/>
+      <c r="M4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="20"/>
+      <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -2100,30 +2136,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="17">
         <v>44750</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="36" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="37">
+      <c r="J5" s="18"/>
+      <c r="K5" s="21">
         <v>2</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="38" t="s">
+      <c r="L5" s="18"/>
+      <c r="M5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="34"/>
+      <c r="N5" s="23"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -2132,30 +2168,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="36">
         <v>44750</v>
       </c>
-      <c r="D6" s="29"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30" t="s">
+      <c r="G6" s="20"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="32">
+      <c r="J6" s="18"/>
+      <c r="K6" s="38">
         <v>13</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="33" t="s">
+      <c r="L6" s="18"/>
+      <c r="M6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="34"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -2164,30 +2200,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="17">
         <v>44750</v>
       </c>
-      <c r="D7" s="29"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="37">
+      <c r="G7" s="20"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="21">
         <v>9</v>
       </c>
-      <c r="L7" s="29"/>
-      <c r="M7" s="38" t="s">
+      <c r="L7" s="18"/>
+      <c r="M7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="34"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -2196,30 +2232,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="36">
         <v>44750</v>
       </c>
-      <c r="D8" s="29"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="32">
+      <c r="G8" s="20"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="38">
         <v>123</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="33" t="s">
+      <c r="L8" s="18"/>
+      <c r="M8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="34"/>
+      <c r="N8" s="23"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -2228,30 +2264,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="17">
         <v>44750</v>
       </c>
-      <c r="D9" s="29"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="37">
+      <c r="G9" s="20"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="21">
         <v>37</v>
       </c>
-      <c r="L9" s="29"/>
-      <c r="M9" s="38" t="s">
+      <c r="L9" s="18"/>
+      <c r="M9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="34"/>
+      <c r="N9" s="23"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -2260,30 +2296,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="36">
         <v>44753</v>
       </c>
-      <c r="D10" s="29"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="32">
+      <c r="G10" s="20"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="18"/>
+      <c r="K10" s="38">
         <v>37</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="33" t="s">
+      <c r="L10" s="18"/>
+      <c r="M10" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="34"/>
+      <c r="N10" s="23"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2292,30 +2328,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="17">
         <v>44753</v>
       </c>
-      <c r="D11" s="29"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="37">
+      <c r="G11" s="20"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="21">
         <v>80</v>
       </c>
-      <c r="L11" s="29"/>
-      <c r="M11" s="38" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="34"/>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2324,30 +2360,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="36">
         <v>44753</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30" t="s">
+      <c r="G12" s="20"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="32">
+      <c r="J12" s="18"/>
+      <c r="K12" s="38">
         <v>229</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="33" t="s">
+      <c r="L12" s="18"/>
+      <c r="M12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="34"/>
+      <c r="N12" s="23"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2356,30 +2392,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="17">
         <v>44753</v>
       </c>
-      <c r="D13" s="29"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="37">
+      <c r="G13" s="20"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="21">
         <v>368</v>
       </c>
-      <c r="L13" s="29"/>
-      <c r="M13" s="38" t="s">
+      <c r="L13" s="18"/>
+      <c r="M13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="34"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2388,30 +2424,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="36">
         <v>44753</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="18"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="32">
+      <c r="G14" s="20"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="38">
         <v>62</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="33" t="s">
+      <c r="L14" s="18"/>
+      <c r="M14" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="34"/>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2420,30 +2456,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="17">
         <v>44753</v>
       </c>
-      <c r="D15" s="29"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="37">
+      <c r="G15" s="20"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="21">
         <v>25</v>
       </c>
-      <c r="L15" s="29"/>
-      <c r="M15" s="38" t="s">
+      <c r="L15" s="18"/>
+      <c r="M15" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="34"/>
+      <c r="N15" s="23"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2452,30 +2488,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="36">
         <v>44753</v>
       </c>
-      <c r="D16" s="29"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="31"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="32">
+      <c r="G16" s="20"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="18"/>
+      <c r="K16" s="38">
         <v>68</v>
       </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="33" t="s">
+      <c r="L16" s="18"/>
+      <c r="M16" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="34"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2484,30 +2520,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="17">
         <v>44753</v>
       </c>
-      <c r="D17" s="29"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="37">
+      <c r="G17" s="20"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="21">
         <v>77</v>
       </c>
-      <c r="L17" s="29"/>
-      <c r="M17" s="38" t="s">
+      <c r="L17" s="18"/>
+      <c r="M17" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="34"/>
+      <c r="N17" s="23"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2516,30 +2552,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="36">
         <v>44754</v>
       </c>
-      <c r="D18" s="29"/>
+      <c r="D18" s="18"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="32">
+      <c r="G18" s="20"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="18"/>
+      <c r="K18" s="38">
         <v>20</v>
       </c>
-      <c r="L18" s="29"/>
-      <c r="M18" s="33" t="s">
+      <c r="L18" s="18"/>
+      <c r="M18" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="34"/>
+      <c r="N18" s="23"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2548,30 +2584,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="17">
         <v>44754</v>
       </c>
-      <c r="D19" s="29"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="29"/>
-      <c r="K19" s="37">
+      <c r="G19" s="20"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="18"/>
+      <c r="K19" s="21">
         <v>5</v>
       </c>
-      <c r="L19" s="29"/>
-      <c r="M19" s="38" t="s">
+      <c r="L19" s="18"/>
+      <c r="M19" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="34"/>
+      <c r="N19" s="23"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2580,30 +2616,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="36">
         <v>44754</v>
       </c>
-      <c r="D20" s="29"/>
+      <c r="D20" s="18"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="31"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="29"/>
-      <c r="K20" s="32">
+      <c r="G20" s="20"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="38">
         <v>2</v>
       </c>
-      <c r="L20" s="29"/>
-      <c r="M20" s="33" t="s">
+      <c r="L20" s="18"/>
+      <c r="M20" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="34"/>
+      <c r="N20" s="23"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2612,30 +2648,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="17">
         <v>44754</v>
       </c>
-      <c r="D21" s="29"/>
+      <c r="D21" s="18"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="29"/>
-      <c r="K21" s="37">
+      <c r="G21" s="20"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="21">
         <v>1</v>
       </c>
-      <c r="L21" s="29"/>
-      <c r="M21" s="38" t="s">
+      <c r="L21" s="18"/>
+      <c r="M21" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="34"/>
+      <c r="N21" s="23"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2644,30 +2680,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="36">
         <v>44754</v>
       </c>
-      <c r="D22" s="29"/>
+      <c r="D22" s="18"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="31"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="29"/>
-      <c r="K22" s="32">
+      <c r="G22" s="20"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="38">
         <v>41</v>
       </c>
-      <c r="L22" s="29"/>
-      <c r="M22" s="33" t="s">
+      <c r="L22" s="18"/>
+      <c r="M22" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="34"/>
+      <c r="N22" s="23"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2676,30 +2712,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="17">
         <v>44754</v>
       </c>
-      <c r="D23" s="29"/>
+      <c r="D23" s="18"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="36" t="s">
+      <c r="G23" s="20"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="29"/>
-      <c r="K23" s="37">
+      <c r="J23" s="18"/>
+      <c r="K23" s="21">
         <v>4</v>
       </c>
-      <c r="L23" s="29"/>
-      <c r="M23" s="38" t="s">
+      <c r="L23" s="18"/>
+      <c r="M23" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="34"/>
+      <c r="N23" s="23"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2708,30 +2744,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="36">
         <v>44754</v>
       </c>
-      <c r="D24" s="29"/>
+      <c r="D24" s="18"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="32">
+      <c r="G24" s="20"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="38">
         <v>211</v>
       </c>
-      <c r="L24" s="29"/>
-      <c r="M24" s="33" t="s">
+      <c r="L24" s="18"/>
+      <c r="M24" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="34"/>
+      <c r="N24" s="23"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2740,30 +2776,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="17">
         <v>44754</v>
       </c>
-      <c r="D25" s="29"/>
+      <c r="D25" s="18"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="36" t="s">
+      <c r="G25" s="20"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="29"/>
-      <c r="K25" s="37">
+      <c r="J25" s="18"/>
+      <c r="K25" s="21">
         <v>10</v>
       </c>
-      <c r="L25" s="29"/>
-      <c r="M25" s="38" t="s">
+      <c r="L25" s="18"/>
+      <c r="M25" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="34"/>
+      <c r="N25" s="23"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2772,30 +2808,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="36">
         <v>44754</v>
       </c>
-      <c r="D26" s="29"/>
+      <c r="D26" s="18"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="30" t="s">
+      <c r="G26" s="20"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="29"/>
-      <c r="K26" s="32">
+      <c r="J26" s="18"/>
+      <c r="K26" s="38">
         <v>1</v>
       </c>
-      <c r="L26" s="29"/>
-      <c r="M26" s="33" t="s">
+      <c r="L26" s="18"/>
+      <c r="M26" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="34"/>
+      <c r="N26" s="23"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2804,30 +2840,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="17">
         <v>44754</v>
       </c>
-      <c r="D27" s="29"/>
+      <c r="D27" s="18"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="29"/>
-      <c r="K27" s="37">
+      <c r="G27" s="20"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="18"/>
+      <c r="K27" s="21">
         <v>94</v>
       </c>
-      <c r="L27" s="29"/>
-      <c r="M27" s="38" t="s">
+      <c r="L27" s="18"/>
+      <c r="M27" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="34"/>
+      <c r="N27" s="23"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2836,30 +2872,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="36">
         <v>44754</v>
       </c>
-      <c r="D28" s="29"/>
+      <c r="D28" s="18"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="30" t="s">
+      <c r="G28" s="20"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="29"/>
-      <c r="K28" s="32">
+      <c r="J28" s="18"/>
+      <c r="K28" s="38">
         <v>9</v>
       </c>
-      <c r="L28" s="29"/>
-      <c r="M28" s="33" t="s">
+      <c r="L28" s="18"/>
+      <c r="M28" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="34"/>
+      <c r="N28" s="23"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2868,30 +2904,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="17">
         <v>44754</v>
       </c>
-      <c r="D29" s="29"/>
+      <c r="D29" s="18"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="36" t="s">
+      <c r="G29" s="20"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="29"/>
-      <c r="K29" s="37">
+      <c r="J29" s="18"/>
+      <c r="K29" s="21">
         <v>6</v>
       </c>
-      <c r="L29" s="29"/>
-      <c r="M29" s="38" t="s">
+      <c r="L29" s="18"/>
+      <c r="M29" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="34"/>
+      <c r="N29" s="23"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2900,30 +2936,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="36">
         <v>44754</v>
       </c>
-      <c r="D30" s="29"/>
+      <c r="D30" s="18"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="31"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="30" t="s">
+      <c r="G30" s="20"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="29"/>
-      <c r="K30" s="32">
-        <v>18</v>
-      </c>
-      <c r="L30" s="29"/>
-      <c r="M30" s="33" t="s">
+      <c r="J30" s="18"/>
+      <c r="K30" s="38">
+        <v>18</v>
+      </c>
+      <c r="L30" s="18"/>
+      <c r="M30" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="34"/>
+      <c r="N30" s="23"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2932,30 +2968,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="17">
         <v>44755</v>
       </c>
-      <c r="D31" s="29"/>
+      <c r="D31" s="18"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="36" t="s">
+      <c r="G31" s="20"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="29"/>
-      <c r="K31" s="37">
+      <c r="J31" s="18"/>
+      <c r="K31" s="21">
         <v>76</v>
       </c>
-      <c r="L31" s="29"/>
-      <c r="M31" s="38" t="s">
+      <c r="L31" s="18"/>
+      <c r="M31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="34"/>
+      <c r="N31" s="23"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -2964,30 +3000,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="36">
         <v>44755</v>
       </c>
-      <c r="D32" s="29"/>
+      <c r="D32" s="18"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="31"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30" t="s">
+      <c r="G32" s="20"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="29"/>
-      <c r="K32" s="32">
+      <c r="J32" s="18"/>
+      <c r="K32" s="38">
         <v>1</v>
       </c>
-      <c r="L32" s="29"/>
-      <c r="M32" s="33" t="s">
+      <c r="L32" s="18"/>
+      <c r="M32" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="34"/>
+      <c r="N32" s="23"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -2996,30 +3032,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="17">
         <v>44755</v>
       </c>
-      <c r="D33" s="29"/>
+      <c r="D33" s="18"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="31"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="36" t="s">
+      <c r="G33" s="20"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="29"/>
-      <c r="K33" s="37">
+      <c r="J33" s="18"/>
+      <c r="K33" s="21">
         <v>27</v>
       </c>
-      <c r="L33" s="29"/>
-      <c r="M33" s="38" t="s">
+      <c r="L33" s="18"/>
+      <c r="M33" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="34"/>
+      <c r="N33" s="23"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -3028,30 +3064,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="36">
         <v>44755</v>
       </c>
-      <c r="D34" s="29"/>
+      <c r="D34" s="18"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="30" t="s">
+      <c r="F34" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="31"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30" t="s">
+      <c r="G34" s="20"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="29"/>
-      <c r="K34" s="32">
+      <c r="J34" s="18"/>
+      <c r="K34" s="38">
         <v>2</v>
       </c>
-      <c r="L34" s="29"/>
-      <c r="M34" s="33" t="s">
+      <c r="L34" s="18"/>
+      <c r="M34" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="34"/>
+      <c r="N34" s="23"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -3060,30 +3096,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="17">
         <v>44756</v>
       </c>
-      <c r="D35" s="29"/>
+      <c r="D35" s="18"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="31"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="29"/>
-      <c r="K35" s="37">
+      <c r="G35" s="20"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="21">
         <v>54</v>
       </c>
-      <c r="L35" s="29"/>
-      <c r="M35" s="38" t="s">
+      <c r="L35" s="18"/>
+      <c r="M35" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="34"/>
+      <c r="N35" s="23"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -3092,30 +3128,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="36">
         <v>44756</v>
       </c>
-      <c r="D36" s="29"/>
+      <c r="D36" s="18"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="30" t="s">
+      <c r="F36" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="31"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="29"/>
-      <c r="K36" s="32">
+      <c r="G36" s="20"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="38">
         <v>105</v>
       </c>
-      <c r="L36" s="29"/>
-      <c r="M36" s="33" t="s">
+      <c r="L36" s="18"/>
+      <c r="M36" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="34"/>
+      <c r="N36" s="23"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -3124,30 +3160,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="17">
         <v>44756</v>
       </c>
-      <c r="D37" s="29"/>
+      <c r="D37" s="18"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="F37" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="31"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="29"/>
-      <c r="K37" s="37">
+      <c r="G37" s="20"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="21">
         <v>71</v>
       </c>
-      <c r="L37" s="29"/>
-      <c r="M37" s="38" t="s">
+      <c r="L37" s="18"/>
+      <c r="M37" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="34"/>
+      <c r="N37" s="23"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -3156,30 +3192,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="36">
         <v>44756</v>
       </c>
-      <c r="D38" s="29"/>
+      <c r="D38" s="18"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="29"/>
-      <c r="K38" s="32">
+      <c r="G38" s="20"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="38">
         <v>125</v>
       </c>
-      <c r="L38" s="29"/>
-      <c r="M38" s="33" t="s">
+      <c r="L38" s="18"/>
+      <c r="M38" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="34"/>
+      <c r="N38" s="23"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -3188,30 +3224,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="17">
         <v>44756</v>
       </c>
-      <c r="D39" s="29"/>
+      <c r="D39" s="18"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="29"/>
-      <c r="K39" s="37">
+      <c r="G39" s="20"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="21">
         <v>55</v>
       </c>
-      <c r="L39" s="29"/>
-      <c r="M39" s="38" t="s">
+      <c r="L39" s="18"/>
+      <c r="M39" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="34"/>
+      <c r="N39" s="23"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -3220,30 +3256,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="36">
         <v>44756</v>
       </c>
-      <c r="D40" s="29"/>
+      <c r="D40" s="18"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="31"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="29"/>
-      <c r="K40" s="32">
+      <c r="G40" s="20"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="38">
         <v>176</v>
       </c>
-      <c r="L40" s="29"/>
-      <c r="M40" s="33" t="s">
+      <c r="L40" s="18"/>
+      <c r="M40" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="34"/>
+      <c r="N40" s="23"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -3252,30 +3288,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="17">
         <v>44757</v>
       </c>
-      <c r="D41" s="29"/>
+      <c r="D41" s="18"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="29"/>
-      <c r="K41" s="37">
+      <c r="G41" s="20"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="18"/>
+      <c r="K41" s="21">
         <v>58</v>
       </c>
-      <c r="L41" s="29"/>
-      <c r="M41" s="38" t="s">
+      <c r="L41" s="18"/>
+      <c r="M41" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="34"/>
+      <c r="N41" s="23"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3284,30 +3320,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="36">
         <v>44757</v>
       </c>
-      <c r="D42" s="29"/>
+      <c r="D42" s="18"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="31"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="29"/>
-      <c r="K42" s="32">
+      <c r="G42" s="20"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="18"/>
+      <c r="K42" s="38">
         <v>180</v>
       </c>
-      <c r="L42" s="29"/>
-      <c r="M42" s="33" t="s">
+      <c r="L42" s="18"/>
+      <c r="M42" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="34"/>
+      <c r="N42" s="23"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3316,30 +3352,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="17">
         <v>44760</v>
       </c>
-      <c r="D43" s="29"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="36" t="s">
+      <c r="G43" s="20"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="29"/>
-      <c r="K43" s="37">
+      <c r="J43" s="18"/>
+      <c r="K43" s="21">
         <v>142</v>
       </c>
-      <c r="L43" s="29"/>
-      <c r="M43" s="38" t="s">
+      <c r="L43" s="18"/>
+      <c r="M43" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="34"/>
+      <c r="N43" s="23"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3348,30 +3384,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="36">
         <v>44760</v>
       </c>
-      <c r="D44" s="29"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="31"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="30" t="s">
+      <c r="G44" s="20"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="29"/>
-      <c r="K44" s="32">
+      <c r="J44" s="18"/>
+      <c r="K44" s="38">
         <v>153</v>
       </c>
-      <c r="L44" s="29"/>
-      <c r="M44" s="33" t="s">
+      <c r="L44" s="18"/>
+      <c r="M44" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="34"/>
+      <c r="N44" s="23"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3380,30 +3416,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="17">
         <v>44761</v>
       </c>
-      <c r="D45" s="29"/>
+      <c r="D45" s="18"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="36" t="s">
+      <c r="F45" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="31"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="29"/>
-      <c r="K45" s="37">
+      <c r="G45" s="20"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="18"/>
+      <c r="K45" s="21">
         <v>12</v>
       </c>
-      <c r="L45" s="29"/>
-      <c r="M45" s="38" t="s">
+      <c r="L45" s="18"/>
+      <c r="M45" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="34"/>
+      <c r="N45" s="23"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3412,30 +3448,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="36">
         <v>44761</v>
       </c>
-      <c r="D46" s="29"/>
+      <c r="D46" s="18"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="30" t="s">
+      <c r="F46" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="31"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="29"/>
-      <c r="K46" s="32">
+      <c r="G46" s="20"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="18"/>
+      <c r="K46" s="38">
         <v>27</v>
       </c>
-      <c r="L46" s="29"/>
-      <c r="M46" s="33" t="s">
+      <c r="L46" s="18"/>
+      <c r="M46" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="34"/>
+      <c r="N46" s="23"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3444,30 +3480,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="17">
         <v>44761</v>
       </c>
-      <c r="D47" s="29"/>
+      <c r="D47" s="18"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="36" t="s">
+      <c r="F47" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="29"/>
-      <c r="K47" s="37">
+      <c r="G47" s="20"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="18"/>
+      <c r="K47" s="21">
         <v>51</v>
       </c>
-      <c r="L47" s="29"/>
-      <c r="M47" s="38" t="s">
+      <c r="L47" s="18"/>
+      <c r="M47" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="34"/>
+      <c r="N47" s="23"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3476,30 +3512,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="36">
         <v>44761</v>
       </c>
-      <c r="D48" s="29"/>
+      <c r="D48" s="18"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="30" t="s">
+      <c r="F48" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="31"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="29"/>
-      <c r="K48" s="32">
+      <c r="G48" s="20"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="18"/>
+      <c r="K48" s="38">
         <v>69</v>
       </c>
-      <c r="L48" s="29"/>
-      <c r="M48" s="33" t="s">
+      <c r="L48" s="18"/>
+      <c r="M48" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="34"/>
+      <c r="N48" s="23"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3508,30 +3544,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="17">
         <v>44762</v>
       </c>
-      <c r="D49" s="29"/>
+      <c r="D49" s="18"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="36" t="s">
+      <c r="F49" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="31"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="36" t="s">
+      <c r="G49" s="20"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="29"/>
-      <c r="K49" s="37">
+      <c r="J49" s="18"/>
+      <c r="K49" s="21">
         <v>104</v>
       </c>
-      <c r="L49" s="29"/>
-      <c r="M49" s="38" t="s">
+      <c r="L49" s="18"/>
+      <c r="M49" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="34"/>
+      <c r="N49" s="23"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3540,30 +3576,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="36">
         <v>44762</v>
       </c>
-      <c r="D50" s="29"/>
+      <c r="D50" s="18"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="30" t="s">
+      <c r="F50" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="31"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="29"/>
-      <c r="K50" s="32">
+      <c r="G50" s="20"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="18"/>
+      <c r="K50" s="38">
         <v>19</v>
       </c>
-      <c r="L50" s="29"/>
-      <c r="M50" s="33" t="s">
+      <c r="L50" s="18"/>
+      <c r="M50" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="34"/>
+      <c r="N50" s="23"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3572,30 +3608,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="17">
         <v>44762</v>
       </c>
-      <c r="D51" s="29"/>
+      <c r="D51" s="18"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="36" t="s">
+      <c r="F51" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="31"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="36" t="s">
+      <c r="G51" s="20"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="29"/>
-      <c r="K51" s="37">
+      <c r="J51" s="18"/>
+      <c r="K51" s="21">
         <v>80</v>
       </c>
-      <c r="L51" s="29"/>
-      <c r="M51" s="38" t="s">
+      <c r="L51" s="18"/>
+      <c r="M51" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="34"/>
+      <c r="N51" s="23"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3604,30 +3640,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="36">
         <v>44763</v>
       </c>
-      <c r="D52" s="29"/>
+      <c r="D52" s="18"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="30" t="s">
+      <c r="F52" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="31"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="29"/>
-      <c r="K52" s="32">
+      <c r="G52" s="20"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="18"/>
+      <c r="K52" s="38">
         <v>99</v>
       </c>
-      <c r="L52" s="29"/>
-      <c r="M52" s="33" t="s">
+      <c r="L52" s="18"/>
+      <c r="M52" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="34"/>
+      <c r="N52" s="23"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3636,30 +3672,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="17">
         <v>44763</v>
       </c>
-      <c r="D53" s="29"/>
+      <c r="D53" s="18"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="36" t="s">
+      <c r="F53" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="29"/>
-      <c r="K53" s="37">
+      <c r="G53" s="20"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="18"/>
+      <c r="K53" s="21">
         <v>60</v>
       </c>
-      <c r="L53" s="29"/>
-      <c r="M53" s="38" t="s">
+      <c r="L53" s="18"/>
+      <c r="M53" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="34"/>
+      <c r="N53" s="23"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3668,30 +3704,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="36">
         <v>44763</v>
       </c>
-      <c r="D54" s="29"/>
+      <c r="D54" s="18"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="29"/>
-      <c r="K54" s="32">
+      <c r="G54" s="20"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="18"/>
+      <c r="K54" s="38">
         <v>4</v>
       </c>
-      <c r="L54" s="29"/>
-      <c r="M54" s="33" t="s">
+      <c r="L54" s="18"/>
+      <c r="M54" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="34"/>
+      <c r="N54" s="23"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3700,30 +3736,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="17">
         <v>44763</v>
       </c>
-      <c r="D55" s="29"/>
+      <c r="D55" s="18"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="36" t="s">
+      <c r="F55" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="31"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="29"/>
-      <c r="K55" s="37">
+      <c r="G55" s="20"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="18"/>
+      <c r="K55" s="21">
         <v>26</v>
       </c>
-      <c r="L55" s="29"/>
-      <c r="M55" s="38" t="s">
+      <c r="L55" s="18"/>
+      <c r="M55" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="34"/>
+      <c r="N55" s="23"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3732,30 +3768,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="36">
         <v>44763</v>
       </c>
-      <c r="D56" s="29"/>
+      <c r="D56" s="18"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="30" t="s">
+      <c r="F56" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="31"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="29"/>
-      <c r="K56" s="32">
+      <c r="G56" s="20"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="18"/>
+      <c r="K56" s="38">
         <v>30</v>
       </c>
-      <c r="L56" s="29"/>
-      <c r="M56" s="33" t="s">
+      <c r="L56" s="18"/>
+      <c r="M56" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="34"/>
+      <c r="N56" s="23"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3764,30 +3800,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="17">
         <v>44763</v>
       </c>
-      <c r="D57" s="29"/>
+      <c r="D57" s="18"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="36" t="s">
+      <c r="F57" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="31"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="29"/>
-      <c r="K57" s="37">
+      <c r="G57" s="20"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="18"/>
+      <c r="K57" s="21">
         <v>2</v>
       </c>
-      <c r="L57" s="29"/>
-      <c r="M57" s="38" t="s">
+      <c r="L57" s="18"/>
+      <c r="M57" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="34"/>
+      <c r="N57" s="23"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3796,30 +3832,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="36">
         <v>44764</v>
       </c>
-      <c r="D58" s="29"/>
+      <c r="D58" s="18"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="30" t="s">
+      <c r="F58" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="31"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="30" t="s">
+      <c r="G58" s="20"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="29"/>
-      <c r="K58" s="32">
+      <c r="J58" s="18"/>
+      <c r="K58" s="38">
         <v>66</v>
       </c>
-      <c r="L58" s="29"/>
-      <c r="M58" s="33" t="s">
+      <c r="L58" s="18"/>
+      <c r="M58" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="34"/>
+      <c r="N58" s="23"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3828,30 +3864,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="17">
         <v>44764</v>
       </c>
-      <c r="D59" s="29"/>
+      <c r="D59" s="18"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F59" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="31"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="36" t="s">
+      <c r="G59" s="20"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="29"/>
-      <c r="K59" s="37">
+      <c r="J59" s="18"/>
+      <c r="K59" s="21">
         <v>85</v>
       </c>
-      <c r="L59" s="29"/>
-      <c r="M59" s="38" t="s">
+      <c r="L59" s="18"/>
+      <c r="M59" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="34"/>
+      <c r="N59" s="23"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3860,30 +3896,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="36">
         <v>44764</v>
       </c>
-      <c r="D60" s="29"/>
+      <c r="D60" s="18"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="30" t="s">
+      <c r="F60" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="31"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="29"/>
-      <c r="K60" s="32">
+      <c r="G60" s="20"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="18"/>
+      <c r="K60" s="38">
         <v>58</v>
       </c>
-      <c r="L60" s="29"/>
-      <c r="M60" s="33" t="s">
+      <c r="L60" s="18"/>
+      <c r="M60" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="34"/>
+      <c r="N60" s="23"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3892,30 +3928,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="35">
+      <c r="C61" s="17">
         <v>44764</v>
       </c>
-      <c r="D61" s="29"/>
+      <c r="D61" s="18"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="36" t="s">
+      <c r="F61" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="29"/>
-      <c r="K61" s="37">
+      <c r="G61" s="20"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="18"/>
+      <c r="K61" s="21">
         <v>80</v>
       </c>
-      <c r="L61" s="29"/>
-      <c r="M61" s="38" t="s">
+      <c r="L61" s="18"/>
+      <c r="M61" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="34"/>
+      <c r="N61" s="23"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3924,30 +3960,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="36">
         <v>44764</v>
       </c>
-      <c r="D62" s="29"/>
+      <c r="D62" s="18"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="30" t="s">
+      <c r="F62" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="29"/>
-      <c r="K62" s="32">
+      <c r="G62" s="20"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="18"/>
+      <c r="K62" s="38">
         <v>55</v>
       </c>
-      <c r="L62" s="29"/>
-      <c r="M62" s="33" t="s">
+      <c r="L62" s="18"/>
+      <c r="M62" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="34"/>
+      <c r="N62" s="23"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -3956,30 +3992,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="35">
+      <c r="C63" s="17">
         <v>44764</v>
       </c>
-      <c r="D63" s="29"/>
+      <c r="D63" s="18"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="36" t="s">
+      <c r="F63" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="31"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="36" t="s">
+      <c r="G63" s="20"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="29"/>
-      <c r="K63" s="37">
+      <c r="J63" s="18"/>
+      <c r="K63" s="21">
         <v>14</v>
       </c>
-      <c r="L63" s="29"/>
-      <c r="M63" s="38" t="s">
+      <c r="L63" s="18"/>
+      <c r="M63" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="34"/>
+      <c r="N63" s="23"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -3988,30 +4024,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="36">
         <v>44764</v>
       </c>
-      <c r="D64" s="29"/>
+      <c r="D64" s="18"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="31"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="30" t="s">
+      <c r="G64" s="20"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="29"/>
-      <c r="K64" s="32">
+      <c r="J64" s="18"/>
+      <c r="K64" s="38">
         <v>90</v>
       </c>
-      <c r="L64" s="29"/>
-      <c r="M64" s="33" t="s">
+      <c r="L64" s="18"/>
+      <c r="M64" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="34"/>
+      <c r="N64" s="23"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -4020,30 +4056,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="17">
         <v>44767</v>
       </c>
-      <c r="D65" s="29"/>
+      <c r="D65" s="18"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="36" t="s">
+      <c r="F65" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="31"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="36" t="s">
+      <c r="G65" s="20"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="29"/>
-      <c r="K65" s="37">
+      <c r="J65" s="18"/>
+      <c r="K65" s="21">
         <v>331</v>
       </c>
-      <c r="L65" s="29"/>
-      <c r="M65" s="38" t="s">
+      <c r="L65" s="18"/>
+      <c r="M65" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="34"/>
+      <c r="N65" s="23"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -4052,30 +4088,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="36">
         <v>44768</v>
       </c>
-      <c r="D66" s="29"/>
+      <c r="D66" s="18"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="30" t="s">
+      <c r="F66" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="31"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="29"/>
-      <c r="K66" s="32">
+      <c r="G66" s="20"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="18"/>
+      <c r="K66" s="38">
         <v>52</v>
       </c>
-      <c r="L66" s="29"/>
-      <c r="M66" s="33" t="s">
+      <c r="L66" s="18"/>
+      <c r="M66" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="34"/>
+      <c r="N66" s="23"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -4084,30 +4120,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="35">
+      <c r="C67" s="17">
         <v>44768</v>
       </c>
-      <c r="D67" s="29"/>
+      <c r="D67" s="18"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="36" t="s">
+      <c r="F67" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="31"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="29"/>
-      <c r="K67" s="37">
+      <c r="G67" s="20"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="18"/>
+      <c r="K67" s="21">
         <v>9</v>
       </c>
-      <c r="L67" s="29"/>
-      <c r="M67" s="38" t="s">
+      <c r="L67" s="18"/>
+      <c r="M67" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="34"/>
+      <c r="N67" s="23"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -4116,30 +4152,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="36">
         <v>44768</v>
       </c>
-      <c r="D68" s="29"/>
+      <c r="D68" s="18"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="30" t="s">
+      <c r="F68" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="31"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="29"/>
-      <c r="K68" s="32">
+      <c r="G68" s="20"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="18"/>
+      <c r="K68" s="38">
         <v>78</v>
       </c>
-      <c r="L68" s="29"/>
-      <c r="M68" s="33" t="s">
+      <c r="L68" s="18"/>
+      <c r="M68" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="34"/>
+      <c r="N68" s="23"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -4148,30 +4184,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="35">
+      <c r="C69" s="17">
         <v>44769</v>
       </c>
-      <c r="D69" s="29"/>
+      <c r="D69" s="18"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="36" t="s">
+      <c r="F69" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="31"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="29"/>
-      <c r="K69" s="37">
+      <c r="G69" s="20"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="18"/>
+      <c r="K69" s="21">
         <v>48</v>
       </c>
-      <c r="L69" s="29"/>
-      <c r="M69" s="38" t="s">
+      <c r="L69" s="18"/>
+      <c r="M69" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="34"/>
+      <c r="N69" s="23"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -4180,30 +4216,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="36">
         <v>44769</v>
       </c>
-      <c r="D70" s="29"/>
+      <c r="D70" s="18"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="30" t="s">
+      <c r="F70" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="31"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="29"/>
-      <c r="K70" s="32">
+      <c r="G70" s="20"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="18"/>
+      <c r="K70" s="38">
         <v>50</v>
       </c>
-      <c r="L70" s="29"/>
-      <c r="M70" s="33" t="s">
+      <c r="L70" s="18"/>
+      <c r="M70" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="34"/>
+      <c r="N70" s="23"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -4212,30 +4248,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="17">
         <v>44769</v>
       </c>
-      <c r="D71" s="29"/>
+      <c r="D71" s="18"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="36" t="s">
+      <c r="F71" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="31"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="29"/>
-      <c r="K71" s="37">
+      <c r="G71" s="20"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="18"/>
+      <c r="K71" s="21">
         <v>736</v>
       </c>
-      <c r="L71" s="29"/>
-      <c r="M71" s="38" t="s">
+      <c r="L71" s="18"/>
+      <c r="M71" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="34"/>
+      <c r="N71" s="23"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -4244,30 +4280,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="36">
         <v>44770</v>
       </c>
-      <c r="D72" s="29"/>
+      <c r="D72" s="18"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="30" t="s">
+      <c r="F72" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="31"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="29"/>
-      <c r="K72" s="32">
+      <c r="G72" s="20"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="18"/>
+      <c r="K72" s="38">
         <v>74</v>
       </c>
-      <c r="L72" s="29"/>
-      <c r="M72" s="33" t="s">
+      <c r="L72" s="18"/>
+      <c r="M72" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="34"/>
+      <c r="N72" s="23"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4276,30 +4312,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="35">
+      <c r="C73" s="17">
         <v>44770</v>
       </c>
-      <c r="D73" s="29"/>
+      <c r="D73" s="18"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="36" t="s">
+      <c r="F73" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="31"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="29"/>
-      <c r="K73" s="37">
+      <c r="G73" s="20"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="18"/>
+      <c r="K73" s="21">
         <v>25</v>
       </c>
-      <c r="L73" s="29"/>
-      <c r="M73" s="38" t="s">
+      <c r="L73" s="18"/>
+      <c r="M73" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="34"/>
+      <c r="N73" s="23"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4308,30 +4344,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="36">
         <v>44770</v>
       </c>
-      <c r="D74" s="29"/>
+      <c r="D74" s="18"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="30" t="s">
+      <c r="F74" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="31"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="29"/>
-      <c r="K74" s="32">
+      <c r="G74" s="20"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="18"/>
+      <c r="K74" s="38">
         <v>25</v>
       </c>
-      <c r="L74" s="29"/>
-      <c r="M74" s="33" t="s">
+      <c r="L74" s="18"/>
+      <c r="M74" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="34"/>
+      <c r="N74" s="23"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4340,30 +4376,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="35">
+      <c r="C75" s="17">
         <v>44770</v>
       </c>
-      <c r="D75" s="29"/>
+      <c r="D75" s="18"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="36" t="s">
+      <c r="F75" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="31"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="36" t="s">
+      <c r="G75" s="20"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="29"/>
-      <c r="K75" s="37">
+      <c r="J75" s="18"/>
+      <c r="K75" s="21">
         <v>225</v>
       </c>
-      <c r="L75" s="29"/>
-      <c r="M75" s="38" t="s">
+      <c r="L75" s="18"/>
+      <c r="M75" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="34"/>
+      <c r="N75" s="23"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4372,30 +4408,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="36">
         <v>44770</v>
       </c>
-      <c r="D76" s="29"/>
+      <c r="D76" s="18"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="30" t="s">
+      <c r="F76" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="31"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="29"/>
-      <c r="K76" s="32">
+      <c r="G76" s="20"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="18"/>
+      <c r="K76" s="38">
         <v>136</v>
       </c>
-      <c r="L76" s="29"/>
-      <c r="M76" s="33" t="s">
+      <c r="L76" s="18"/>
+      <c r="M76" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="34"/>
+      <c r="N76" s="23"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4404,30 +4440,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="35">
+      <c r="C77" s="17">
         <v>44774</v>
       </c>
-      <c r="D77" s="29"/>
+      <c r="D77" s="18"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="36" t="s">
+      <c r="F77" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="31"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="36" t="s">
+      <c r="G77" s="20"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="29"/>
-      <c r="K77" s="37">
+      <c r="J77" s="18"/>
+      <c r="K77" s="21">
         <v>82</v>
       </c>
-      <c r="L77" s="29"/>
-      <c r="M77" s="38" t="s">
+      <c r="L77" s="18"/>
+      <c r="M77" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="34"/>
+      <c r="N77" s="23"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4436,30 +4472,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="36">
         <v>44774</v>
       </c>
-      <c r="D78" s="29"/>
+      <c r="D78" s="18"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="30" t="s">
+      <c r="F78" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="31"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="29"/>
-      <c r="K78" s="32">
+      <c r="G78" s="20"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="18"/>
+      <c r="K78" s="38">
         <v>28</v>
       </c>
-      <c r="L78" s="29"/>
-      <c r="M78" s="33" t="s">
+      <c r="L78" s="18"/>
+      <c r="M78" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="34"/>
+      <c r="N78" s="23"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4468,30 +4504,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="35">
+      <c r="C79" s="17">
         <v>44776</v>
       </c>
-      <c r="D79" s="29"/>
+      <c r="D79" s="18"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="36" t="s">
+      <c r="F79" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="31"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="29"/>
-      <c r="K79" s="37">
+      <c r="G79" s="20"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="18"/>
+      <c r="K79" s="21">
         <v>57</v>
       </c>
-      <c r="L79" s="29"/>
-      <c r="M79" s="38" t="s">
+      <c r="L79" s="18"/>
+      <c r="M79" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="34"/>
+      <c r="N79" s="23"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4500,30 +4536,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="36">
         <v>44778</v>
       </c>
-      <c r="D80" s="29"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="30" t="s">
+      <c r="F80" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="31"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="30" t="s">
+      <c r="G80" s="20"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="29"/>
-      <c r="K80" s="32">
+      <c r="J80" s="18"/>
+      <c r="K80" s="38">
         <v>133</v>
       </c>
-      <c r="L80" s="29"/>
-      <c r="M80" s="33" t="s">
+      <c r="L80" s="18"/>
+      <c r="M80" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="34"/>
+      <c r="N80" s="23"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4532,30 +4568,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="35">
+      <c r="C81" s="17">
         <v>44778</v>
       </c>
-      <c r="D81" s="29"/>
+      <c r="D81" s="18"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="36" t="s">
+      <c r="F81" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="31"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="29"/>
-      <c r="K81" s="37">
+      <c r="G81" s="20"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="18"/>
+      <c r="K81" s="21">
         <v>146</v>
       </c>
-      <c r="L81" s="29"/>
-      <c r="M81" s="38" t="s">
+      <c r="L81" s="18"/>
+      <c r="M81" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="34"/>
+      <c r="N81" s="23"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4564,30 +4600,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="36">
         <v>44778</v>
       </c>
-      <c r="D82" s="29"/>
+      <c r="D82" s="18"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="30" t="s">
+      <c r="F82" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="31"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="30" t="s">
+      <c r="G82" s="20"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="29"/>
-      <c r="K82" s="32">
+      <c r="J82" s="18"/>
+      <c r="K82" s="38">
         <v>68</v>
       </c>
-      <c r="L82" s="29"/>
-      <c r="M82" s="33" t="s">
+      <c r="L82" s="18"/>
+      <c r="M82" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="34"/>
+      <c r="N82" s="23"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4596,30 +4632,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="35">
+      <c r="C83" s="17">
         <v>44781</v>
       </c>
-      <c r="D83" s="29"/>
+      <c r="D83" s="18"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="36" t="s">
+      <c r="F83" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="31"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="29"/>
-      <c r="K83" s="37">
+      <c r="G83" s="20"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="18"/>
+      <c r="K83" s="21">
         <v>111</v>
       </c>
-      <c r="L83" s="29"/>
-      <c r="M83" s="38" t="s">
+      <c r="L83" s="18"/>
+      <c r="M83" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="34"/>
+      <c r="N83" s="23"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4628,30 +4664,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="36">
         <v>44781</v>
       </c>
-      <c r="D84" s="29"/>
+      <c r="D84" s="18"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="30" t="s">
+      <c r="F84" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="31"/>
-      <c r="H84" s="29"/>
-      <c r="I84" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="29"/>
-      <c r="K84" s="32">
+      <c r="G84" s="20"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="18"/>
+      <c r="K84" s="38">
         <v>77</v>
       </c>
-      <c r="L84" s="29"/>
-      <c r="M84" s="33" t="s">
+      <c r="L84" s="18"/>
+      <c r="M84" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="34"/>
+      <c r="N84" s="23"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4660,30 +4696,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="35">
+      <c r="C85" s="17">
         <v>44781</v>
       </c>
-      <c r="D85" s="29"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="36" t="s">
+      <c r="F85" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="31"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="29"/>
-      <c r="K85" s="37">
+      <c r="G85" s="20"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="18"/>
+      <c r="K85" s="21">
         <v>20</v>
       </c>
-      <c r="L85" s="29"/>
-      <c r="M85" s="38" t="s">
+      <c r="L85" s="18"/>
+      <c r="M85" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="34"/>
+      <c r="N85" s="23"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4692,30 +4728,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="36">
         <v>44781</v>
       </c>
-      <c r="D86" s="29"/>
+      <c r="D86" s="18"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="30" t="s">
+      <c r="F86" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="31"/>
-      <c r="H86" s="29"/>
-      <c r="I86" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="29"/>
-      <c r="K86" s="32">
+      <c r="G86" s="20"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="18"/>
+      <c r="K86" s="38">
         <v>25</v>
       </c>
-      <c r="L86" s="29"/>
-      <c r="M86" s="33" t="s">
+      <c r="L86" s="18"/>
+      <c r="M86" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="34"/>
+      <c r="N86" s="23"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4724,30 +4760,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="35">
+      <c r="C87" s="17">
         <v>44781</v>
       </c>
-      <c r="D87" s="29"/>
+      <c r="D87" s="18"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="36" t="s">
+      <c r="F87" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="31"/>
-      <c r="H87" s="29"/>
-      <c r="I87" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="29"/>
-      <c r="K87" s="37">
+      <c r="G87" s="20"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="18"/>
+      <c r="K87" s="21">
         <v>21</v>
       </c>
-      <c r="L87" s="29"/>
-      <c r="M87" s="38" t="s">
+      <c r="L87" s="18"/>
+      <c r="M87" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="34"/>
+      <c r="N87" s="23"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4756,30 +4792,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="36">
         <v>44781</v>
       </c>
-      <c r="D88" s="29"/>
+      <c r="D88" s="18"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="30" t="s">
+      <c r="F88" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="31"/>
-      <c r="H88" s="29"/>
-      <c r="I88" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="29"/>
-      <c r="K88" s="32">
+      <c r="G88" s="20"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="18"/>
+      <c r="K88" s="38">
         <v>86</v>
       </c>
-      <c r="L88" s="29"/>
-      <c r="M88" s="33" t="s">
+      <c r="L88" s="18"/>
+      <c r="M88" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="34"/>
+      <c r="N88" s="23"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4788,30 +4824,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="35">
+      <c r="C89" s="17">
         <v>44781</v>
       </c>
-      <c r="D89" s="29"/>
+      <c r="D89" s="18"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="36" t="s">
+      <c r="F89" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="31"/>
-      <c r="H89" s="29"/>
-      <c r="I89" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="29"/>
-      <c r="K89" s="37">
+      <c r="G89" s="20"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="18"/>
+      <c r="K89" s="21">
         <v>9</v>
       </c>
-      <c r="L89" s="29"/>
-      <c r="M89" s="38" t="s">
+      <c r="L89" s="18"/>
+      <c r="M89" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="34"/>
+      <c r="N89" s="23"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4820,30 +4856,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="36">
         <v>44781</v>
       </c>
-      <c r="D90" s="29"/>
+      <c r="D90" s="18"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="30" t="s">
+      <c r="F90" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="31"/>
-      <c r="H90" s="29"/>
-      <c r="I90" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="29"/>
-      <c r="K90" s="32">
+      <c r="G90" s="20"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="18"/>
+      <c r="K90" s="38">
         <v>2</v>
       </c>
-      <c r="L90" s="29"/>
-      <c r="M90" s="33" t="s">
+      <c r="L90" s="18"/>
+      <c r="M90" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="34"/>
+      <c r="N90" s="23"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4852,30 +4888,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="35">
+      <c r="C91" s="17">
         <v>44781</v>
       </c>
-      <c r="D91" s="29"/>
+      <c r="D91" s="18"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="36" t="s">
+      <c r="F91" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="31"/>
-      <c r="H91" s="29"/>
-      <c r="I91" s="36" t="s">
+      <c r="G91" s="20"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="29"/>
-      <c r="K91" s="37">
+      <c r="J91" s="18"/>
+      <c r="K91" s="21">
         <v>73</v>
       </c>
-      <c r="L91" s="29"/>
-      <c r="M91" s="38" t="s">
+      <c r="L91" s="18"/>
+      <c r="M91" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="34"/>
+      <c r="N91" s="23"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4884,30 +4920,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="36">
         <v>44782</v>
       </c>
-      <c r="D92" s="29"/>
+      <c r="D92" s="18"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="30" t="s">
+      <c r="F92" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="31"/>
-      <c r="H92" s="29"/>
-      <c r="I92" s="30" t="s">
+      <c r="G92" s="20"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="29"/>
-      <c r="K92" s="32">
+      <c r="J92" s="18"/>
+      <c r="K92" s="38">
         <v>33</v>
       </c>
-      <c r="L92" s="29"/>
-      <c r="M92" s="33" t="s">
+      <c r="L92" s="18"/>
+      <c r="M92" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="34"/>
+      <c r="N92" s="23"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4916,30 +4952,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="35">
+      <c r="C93" s="17">
         <v>44782</v>
       </c>
-      <c r="D93" s="29"/>
+      <c r="D93" s="18"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="36" t="s">
+      <c r="F93" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="31"/>
-      <c r="H93" s="29"/>
-      <c r="I93" s="36" t="s">
+      <c r="G93" s="20"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="29"/>
-      <c r="K93" s="37">
+      <c r="J93" s="18"/>
+      <c r="K93" s="21">
         <v>57</v>
       </c>
-      <c r="L93" s="29"/>
-      <c r="M93" s="38" t="s">
+      <c r="L93" s="18"/>
+      <c r="M93" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="34"/>
+      <c r="N93" s="23"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -4948,30 +4984,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="36">
         <v>44782</v>
       </c>
-      <c r="D94" s="29"/>
+      <c r="D94" s="18"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="30" t="s">
+      <c r="F94" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="31"/>
-      <c r="H94" s="29"/>
-      <c r="I94" s="30" t="s">
+      <c r="G94" s="20"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="29"/>
-      <c r="K94" s="32">
+      <c r="J94" s="18"/>
+      <c r="K94" s="38">
         <v>16</v>
       </c>
-      <c r="L94" s="29"/>
-      <c r="M94" s="33" t="s">
+      <c r="L94" s="18"/>
+      <c r="M94" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="34"/>
+      <c r="N94" s="23"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -4980,30 +5016,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="35">
+      <c r="C95" s="17">
         <v>44782</v>
       </c>
-      <c r="D95" s="29"/>
+      <c r="D95" s="18"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="36" t="s">
+      <c r="F95" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="31"/>
-      <c r="H95" s="29"/>
-      <c r="I95" s="36" t="s">
+      <c r="G95" s="20"/>
+      <c r="H95" s="18"/>
+      <c r="I95" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="29"/>
-      <c r="K95" s="37">
+      <c r="J95" s="18"/>
+      <c r="K95" s="21">
         <v>3</v>
       </c>
-      <c r="L95" s="29"/>
-      <c r="M95" s="38" t="s">
+      <c r="L95" s="18"/>
+      <c r="M95" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="34"/>
+      <c r="N95" s="23"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -5012,30 +5048,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="36">
         <v>44782</v>
       </c>
-      <c r="D96" s="29"/>
+      <c r="D96" s="18"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="30" t="s">
+      <c r="F96" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="31"/>
-      <c r="H96" s="29"/>
-      <c r="I96" s="30" t="s">
+      <c r="G96" s="20"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="29"/>
-      <c r="K96" s="32">
+      <c r="J96" s="18"/>
+      <c r="K96" s="38">
         <v>15</v>
       </c>
-      <c r="L96" s="29"/>
-      <c r="M96" s="33" t="s">
+      <c r="L96" s="18"/>
+      <c r="M96" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="34"/>
+      <c r="N96" s="23"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -5044,30 +5080,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="35">
+      <c r="C97" s="17">
         <v>44783</v>
       </c>
-      <c r="D97" s="29"/>
+      <c r="D97" s="18"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="36" t="s">
+      <c r="F97" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="31"/>
-      <c r="H97" s="29"/>
-      <c r="I97" s="36" t="s">
+      <c r="G97" s="20"/>
+      <c r="H97" s="18"/>
+      <c r="I97" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="29"/>
-      <c r="K97" s="37">
+      <c r="J97" s="18"/>
+      <c r="K97" s="21">
         <v>64</v>
       </c>
-      <c r="L97" s="29"/>
-      <c r="M97" s="38" t="s">
+      <c r="L97" s="18"/>
+      <c r="M97" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="34"/>
+      <c r="N97" s="23"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -5076,30 +5112,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="36">
         <v>44783</v>
       </c>
-      <c r="D98" s="29"/>
+      <c r="D98" s="18"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="30" t="s">
+      <c r="F98" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="31"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="30" t="s">
+      <c r="G98" s="20"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="29"/>
-      <c r="K98" s="32">
+      <c r="J98" s="18"/>
+      <c r="K98" s="38">
         <v>100</v>
       </c>
-      <c r="L98" s="29"/>
-      <c r="M98" s="33" t="s">
+      <c r="L98" s="18"/>
+      <c r="M98" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="34"/>
+      <c r="N98" s="23"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -5108,30 +5144,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="35">
+      <c r="C99" s="17">
         <v>44783</v>
       </c>
-      <c r="D99" s="29"/>
+      <c r="D99" s="18"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="36" t="s">
+      <c r="F99" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="31"/>
-      <c r="H99" s="29"/>
-      <c r="I99" s="36" t="s">
+      <c r="G99" s="20"/>
+      <c r="H99" s="18"/>
+      <c r="I99" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="29"/>
-      <c r="K99" s="37">
+      <c r="J99" s="18"/>
+      <c r="K99" s="21">
         <v>193</v>
       </c>
-      <c r="L99" s="29"/>
-      <c r="M99" s="38" t="s">
+      <c r="L99" s="18"/>
+      <c r="M99" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="34"/>
+      <c r="N99" s="23"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -5140,30 +5176,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="36">
         <v>44783</v>
       </c>
-      <c r="D100" s="29"/>
+      <c r="D100" s="18"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="30" t="s">
+      <c r="F100" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="31"/>
-      <c r="H100" s="29"/>
-      <c r="I100" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="29"/>
-      <c r="K100" s="32">
+      <c r="G100" s="20"/>
+      <c r="H100" s="18"/>
+      <c r="I100" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="18"/>
+      <c r="K100" s="38">
         <v>15</v>
       </c>
-      <c r="L100" s="29"/>
-      <c r="M100" s="33" t="s">
+      <c r="L100" s="18"/>
+      <c r="M100" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="34"/>
+      <c r="N100" s="23"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -5172,30 +5208,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="35">
+      <c r="C101" s="17">
         <v>44783</v>
       </c>
-      <c r="D101" s="29"/>
+      <c r="D101" s="18"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="36" t="s">
+      <c r="F101" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="31"/>
-      <c r="H101" s="29"/>
-      <c r="I101" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="29"/>
-      <c r="K101" s="37">
+      <c r="G101" s="20"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="18"/>
+      <c r="K101" s="21">
         <v>65</v>
       </c>
-      <c r="L101" s="29"/>
-      <c r="M101" s="38" t="s">
+      <c r="L101" s="18"/>
+      <c r="M101" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="34"/>
+      <c r="N101" s="23"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -5204,30 +5240,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="36">
         <v>44783</v>
       </c>
-      <c r="D102" s="29"/>
+      <c r="D102" s="18"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="30" t="s">
+      <c r="F102" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="31"/>
-      <c r="H102" s="29"/>
-      <c r="I102" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="29"/>
-      <c r="K102" s="32">
+      <c r="G102" s="20"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="18"/>
+      <c r="K102" s="38">
         <v>66</v>
       </c>
-      <c r="L102" s="29"/>
-      <c r="M102" s="33" t="s">
+      <c r="L102" s="18"/>
+      <c r="M102" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="34"/>
+      <c r="N102" s="23"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -5236,30 +5272,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="35">
+      <c r="C103" s="17">
         <v>44784</v>
       </c>
-      <c r="D103" s="29"/>
+      <c r="D103" s="18"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="36" t="s">
+      <c r="F103" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="31"/>
-      <c r="H103" s="29"/>
-      <c r="I103" s="36" t="s">
+      <c r="G103" s="20"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="29"/>
-      <c r="K103" s="37">
+      <c r="J103" s="18"/>
+      <c r="K103" s="21">
         <v>111</v>
       </c>
-      <c r="L103" s="29"/>
-      <c r="M103" s="38" t="s">
+      <c r="L103" s="18"/>
+      <c r="M103" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="34"/>
+      <c r="N103" s="23"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5268,30 +5304,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="36">
         <v>44784</v>
       </c>
-      <c r="D104" s="29"/>
+      <c r="D104" s="18"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="30" t="s">
+      <c r="F104" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="31"/>
-      <c r="H104" s="29"/>
-      <c r="I104" s="30" t="s">
+      <c r="G104" s="20"/>
+      <c r="H104" s="18"/>
+      <c r="I104" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="29"/>
-      <c r="K104" s="32">
+      <c r="J104" s="18"/>
+      <c r="K104" s="38">
         <v>30</v>
       </c>
-      <c r="L104" s="29"/>
-      <c r="M104" s="33" t="s">
+      <c r="L104" s="18"/>
+      <c r="M104" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="34"/>
+      <c r="N104" s="23"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5300,30 +5336,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="35">
+      <c r="C105" s="17">
         <v>44784</v>
       </c>
-      <c r="D105" s="29"/>
+      <c r="D105" s="18"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="36" t="s">
+      <c r="F105" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="31"/>
-      <c r="H105" s="29"/>
-      <c r="I105" s="36" t="s">
+      <c r="G105" s="20"/>
+      <c r="H105" s="18"/>
+      <c r="I105" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="29"/>
-      <c r="K105" s="37">
+      <c r="J105" s="18"/>
+      <c r="K105" s="21">
         <v>31</v>
       </c>
-      <c r="L105" s="29"/>
-      <c r="M105" s="38" t="s">
+      <c r="L105" s="18"/>
+      <c r="M105" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="34"/>
+      <c r="N105" s="23"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5332,30 +5368,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="36">
         <v>44784</v>
       </c>
-      <c r="D106" s="29"/>
+      <c r="D106" s="18"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="30" t="s">
+      <c r="F106" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="31"/>
-      <c r="H106" s="29"/>
-      <c r="I106" s="30" t="s">
+      <c r="G106" s="20"/>
+      <c r="H106" s="18"/>
+      <c r="I106" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="29"/>
-      <c r="K106" s="32">
+      <c r="J106" s="18"/>
+      <c r="K106" s="38">
         <v>109</v>
       </c>
-      <c r="L106" s="29"/>
-      <c r="M106" s="33" t="s">
+      <c r="L106" s="18"/>
+      <c r="M106" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="34"/>
+      <c r="N106" s="23"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5364,30 +5400,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="35">
+      <c r="C107" s="17">
         <v>44788</v>
       </c>
-      <c r="D107" s="29"/>
+      <c r="D107" s="18"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="36" t="s">
+      <c r="F107" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="31"/>
-      <c r="H107" s="29"/>
-      <c r="I107" s="36" t="s">
+      <c r="G107" s="20"/>
+      <c r="H107" s="18"/>
+      <c r="I107" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="29"/>
-      <c r="K107" s="37">
+      <c r="J107" s="18"/>
+      <c r="K107" s="21">
         <v>5</v>
       </c>
-      <c r="L107" s="29"/>
-      <c r="M107" s="38" t="s">
+      <c r="L107" s="18"/>
+      <c r="M107" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="34"/>
+      <c r="N107" s="23"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5396,30 +5432,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="36">
         <v>44788</v>
       </c>
-      <c r="D108" s="29"/>
+      <c r="D108" s="18"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="30" t="s">
+      <c r="F108" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="31"/>
-      <c r="H108" s="29"/>
-      <c r="I108" s="30" t="s">
+      <c r="G108" s="20"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="29"/>
-      <c r="K108" s="32">
+      <c r="J108" s="18"/>
+      <c r="K108" s="38">
         <v>100</v>
       </c>
-      <c r="L108" s="29"/>
-      <c r="M108" s="33" t="s">
+      <c r="L108" s="18"/>
+      <c r="M108" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="34"/>
+      <c r="N108" s="23"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5428,30 +5464,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="35">
+      <c r="C109" s="17">
         <v>44788</v>
       </c>
-      <c r="D109" s="29"/>
+      <c r="D109" s="18"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="36" t="s">
+      <c r="F109" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="31"/>
-      <c r="H109" s="29"/>
-      <c r="I109" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="29"/>
-      <c r="K109" s="37">
+      <c r="G109" s="20"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="18"/>
+      <c r="K109" s="21">
         <v>54</v>
       </c>
-      <c r="L109" s="29"/>
-      <c r="M109" s="38" t="s">
+      <c r="L109" s="18"/>
+      <c r="M109" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="34"/>
+      <c r="N109" s="23"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5460,30 +5496,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="36">
         <v>44789</v>
       </c>
-      <c r="D110" s="29"/>
+      <c r="D110" s="18"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="30" t="s">
+      <c r="F110" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="31"/>
-      <c r="H110" s="29"/>
-      <c r="I110" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="29"/>
-      <c r="K110" s="32">
+      <c r="G110" s="20"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="18"/>
+      <c r="K110" s="38">
         <v>77</v>
       </c>
-      <c r="L110" s="29"/>
-      <c r="M110" s="33" t="s">
+      <c r="L110" s="18"/>
+      <c r="M110" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="34"/>
+      <c r="N110" s="23"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5492,30 +5528,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="35">
+      <c r="C111" s="17">
         <v>44789</v>
       </c>
-      <c r="D111" s="29"/>
+      <c r="D111" s="18"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="36" t="s">
+      <c r="F111" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="31"/>
-      <c r="H111" s="29"/>
-      <c r="I111" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="29"/>
-      <c r="K111" s="37">
+      <c r="G111" s="20"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="18"/>
+      <c r="K111" s="21">
         <v>52</v>
       </c>
-      <c r="L111" s="29"/>
-      <c r="M111" s="38" t="s">
+      <c r="L111" s="18"/>
+      <c r="M111" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="34"/>
+      <c r="N111" s="23"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5524,30 +5560,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="36">
         <v>44789</v>
       </c>
-      <c r="D112" s="29"/>
+      <c r="D112" s="18"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="30" t="s">
+      <c r="F112" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="31"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="30" t="s">
+      <c r="G112" s="20"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="29"/>
-      <c r="K112" s="32">
+      <c r="J112" s="18"/>
+      <c r="K112" s="38">
         <v>305</v>
       </c>
-      <c r="L112" s="29"/>
-      <c r="M112" s="33" t="s">
+      <c r="L112" s="18"/>
+      <c r="M112" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="34"/>
+      <c r="N112" s="23"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5556,30 +5592,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="35">
+      <c r="C113" s="17">
         <v>44789</v>
       </c>
-      <c r="D113" s="29"/>
+      <c r="D113" s="18"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="36" t="s">
+      <c r="F113" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="31"/>
-      <c r="H113" s="29"/>
-      <c r="I113" s="36" t="s">
+      <c r="G113" s="20"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="29"/>
-      <c r="K113" s="37">
+      <c r="J113" s="18"/>
+      <c r="K113" s="21">
         <v>81</v>
       </c>
-      <c r="L113" s="29"/>
-      <c r="M113" s="38" t="s">
+      <c r="L113" s="18"/>
+      <c r="M113" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="34"/>
+      <c r="N113" s="23"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5588,30 +5624,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="36">
         <v>44789</v>
       </c>
-      <c r="D114" s="29"/>
+      <c r="D114" s="18"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="30" t="s">
+      <c r="F114" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="31"/>
-      <c r="H114" s="29"/>
-      <c r="I114" s="30" t="s">
+      <c r="G114" s="20"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="29"/>
-      <c r="K114" s="32">
+      <c r="J114" s="18"/>
+      <c r="K114" s="38">
         <v>53</v>
       </c>
-      <c r="L114" s="29"/>
-      <c r="M114" s="33" t="s">
+      <c r="L114" s="18"/>
+      <c r="M114" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="34"/>
+      <c r="N114" s="23"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5620,30 +5656,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="35">
+      <c r="C115" s="17">
         <v>44789</v>
       </c>
-      <c r="D115" s="29"/>
+      <c r="D115" s="18"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="36" t="s">
+      <c r="F115" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="31"/>
-      <c r="H115" s="29"/>
-      <c r="I115" s="36" t="s">
+      <c r="G115" s="20"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="29"/>
-      <c r="K115" s="37">
+      <c r="J115" s="18"/>
+      <c r="K115" s="21">
         <v>33</v>
       </c>
-      <c r="L115" s="29"/>
-      <c r="M115" s="38" t="s">
+      <c r="L115" s="18"/>
+      <c r="M115" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="34"/>
+      <c r="N115" s="23"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5652,30 +5688,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="28">
+      <c r="C116" s="36">
         <v>44790</v>
       </c>
-      <c r="D116" s="29"/>
+      <c r="D116" s="18"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="30" t="s">
+      <c r="F116" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="31"/>
-      <c r="H116" s="29"/>
-      <c r="I116" s="30" t="s">
+      <c r="G116" s="20"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="29"/>
-      <c r="K116" s="32">
+      <c r="J116" s="18"/>
+      <c r="K116" s="38">
         <v>145</v>
       </c>
-      <c r="L116" s="29"/>
-      <c r="M116" s="33" t="s">
+      <c r="L116" s="18"/>
+      <c r="M116" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="34"/>
+      <c r="N116" s="23"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5684,30 +5720,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="35">
+      <c r="C117" s="17">
         <v>44790</v>
       </c>
-      <c r="D117" s="29"/>
+      <c r="D117" s="18"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="36" t="s">
+      <c r="F117" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="31"/>
-      <c r="H117" s="29"/>
-      <c r="I117" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="29"/>
-      <c r="K117" s="37">
+      <c r="G117" s="20"/>
+      <c r="H117" s="18"/>
+      <c r="I117" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="18"/>
+      <c r="K117" s="21">
         <v>14</v>
       </c>
-      <c r="L117" s="29"/>
-      <c r="M117" s="38" t="s">
+      <c r="L117" s="18"/>
+      <c r="M117" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="34"/>
+      <c r="N117" s="23"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5716,30 +5752,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="28">
+      <c r="C118" s="36">
         <v>44790</v>
       </c>
-      <c r="D118" s="29"/>
+      <c r="D118" s="18"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="30" t="s">
+      <c r="F118" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="31"/>
-      <c r="H118" s="29"/>
-      <c r="I118" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="29"/>
-      <c r="K118" s="32">
+      <c r="G118" s="20"/>
+      <c r="H118" s="18"/>
+      <c r="I118" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="18"/>
+      <c r="K118" s="38">
         <v>47</v>
       </c>
-      <c r="L118" s="29"/>
-      <c r="M118" s="33" t="s">
+      <c r="L118" s="18"/>
+      <c r="M118" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="34"/>
+      <c r="N118" s="23"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5748,30 +5784,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="35">
+      <c r="C119" s="17">
         <v>44790</v>
       </c>
-      <c r="D119" s="29"/>
+      <c r="D119" s="18"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="36" t="s">
+      <c r="F119" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="31"/>
-      <c r="H119" s="29"/>
-      <c r="I119" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="29"/>
-      <c r="K119" s="37">
+      <c r="G119" s="20"/>
+      <c r="H119" s="18"/>
+      <c r="I119" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="18"/>
+      <c r="K119" s="21">
         <v>16</v>
       </c>
-      <c r="L119" s="29"/>
-      <c r="M119" s="38" t="s">
+      <c r="L119" s="18"/>
+      <c r="M119" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="34"/>
+      <c r="N119" s="23"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5780,30 +5816,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="28">
+      <c r="C120" s="36">
         <v>44790</v>
       </c>
-      <c r="D120" s="29"/>
+      <c r="D120" s="18"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="30" t="s">
+      <c r="F120" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="31"/>
-      <c r="H120" s="29"/>
-      <c r="I120" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="29"/>
-      <c r="K120" s="32">
+      <c r="G120" s="20"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="18"/>
+      <c r="K120" s="38">
         <v>55</v>
       </c>
-      <c r="L120" s="29"/>
-      <c r="M120" s="33" t="s">
+      <c r="L120" s="18"/>
+      <c r="M120" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="34"/>
+      <c r="N120" s="23"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5812,30 +5848,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="35">
+      <c r="C121" s="17">
         <v>44790</v>
       </c>
-      <c r="D121" s="29"/>
+      <c r="D121" s="18"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="36" t="s">
+      <c r="F121" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="31"/>
-      <c r="H121" s="29"/>
-      <c r="I121" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="29"/>
-      <c r="K121" s="37">
+      <c r="G121" s="20"/>
+      <c r="H121" s="18"/>
+      <c r="I121" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="18"/>
+      <c r="K121" s="21">
         <v>8</v>
       </c>
-      <c r="L121" s="29"/>
-      <c r="M121" s="38" t="s">
+      <c r="L121" s="18"/>
+      <c r="M121" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="34"/>
+      <c r="N121" s="23"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5844,30 +5880,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="28">
+      <c r="C122" s="36">
         <v>44790</v>
       </c>
-      <c r="D122" s="29"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="30" t="s">
+      <c r="F122" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="31"/>
-      <c r="H122" s="29"/>
-      <c r="I122" s="30" t="s">
+      <c r="G122" s="20"/>
+      <c r="H122" s="18"/>
+      <c r="I122" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="29"/>
-      <c r="K122" s="32">
+      <c r="J122" s="18"/>
+      <c r="K122" s="38">
         <v>578</v>
       </c>
-      <c r="L122" s="29"/>
-      <c r="M122" s="33" t="s">
+      <c r="L122" s="18"/>
+      <c r="M122" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="34"/>
+      <c r="N122" s="23"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5876,30 +5912,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="35">
+      <c r="C123" s="17">
         <v>44791</v>
       </c>
-      <c r="D123" s="29"/>
+      <c r="D123" s="18"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="36" t="s">
+      <c r="F123" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="31"/>
-      <c r="H123" s="29"/>
-      <c r="I123" s="36" t="s">
+      <c r="G123" s="20"/>
+      <c r="H123" s="18"/>
+      <c r="I123" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="29"/>
-      <c r="K123" s="37">
+      <c r="J123" s="18"/>
+      <c r="K123" s="21">
         <v>111</v>
       </c>
-      <c r="L123" s="29"/>
-      <c r="M123" s="38" t="s">
+      <c r="L123" s="18"/>
+      <c r="M123" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="34"/>
+      <c r="N123" s="23"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5908,30 +5944,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="28">
+      <c r="C124" s="36">
         <v>44791</v>
       </c>
-      <c r="D124" s="29"/>
+      <c r="D124" s="18"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="30" t="s">
+      <c r="F124" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="31"/>
-      <c r="H124" s="29"/>
-      <c r="I124" s="30" t="s">
+      <c r="G124" s="20"/>
+      <c r="H124" s="18"/>
+      <c r="I124" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="29"/>
-      <c r="K124" s="32">
+      <c r="J124" s="18"/>
+      <c r="K124" s="38">
         <v>51</v>
       </c>
-      <c r="L124" s="29"/>
-      <c r="M124" s="33" t="s">
+      <c r="L124" s="18"/>
+      <c r="M124" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="34"/>
+      <c r="N124" s="23"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5940,30 +5976,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="35">
+      <c r="C125" s="17">
         <v>44791</v>
       </c>
-      <c r="D125" s="29"/>
+      <c r="D125" s="18"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="36" t="s">
+      <c r="F125" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="31"/>
-      <c r="H125" s="29"/>
-      <c r="I125" s="36" t="s">
+      <c r="G125" s="20"/>
+      <c r="H125" s="18"/>
+      <c r="I125" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="29"/>
-      <c r="K125" s="37">
+      <c r="J125" s="18"/>
+      <c r="K125" s="21">
         <v>35</v>
       </c>
-      <c r="L125" s="29"/>
-      <c r="M125" s="38" t="s">
+      <c r="L125" s="18"/>
+      <c r="M125" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="34"/>
+      <c r="N125" s="23"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -5972,30 +6008,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="28">
+      <c r="C126" s="36">
         <v>44792</v>
       </c>
-      <c r="D126" s="29"/>
+      <c r="D126" s="18"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="30" t="s">
+      <c r="F126" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="31"/>
-      <c r="H126" s="29"/>
-      <c r="I126" s="30" t="s">
+      <c r="G126" s="20"/>
+      <c r="H126" s="18"/>
+      <c r="I126" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="29"/>
-      <c r="K126" s="32">
+      <c r="J126" s="18"/>
+      <c r="K126" s="38">
         <v>74</v>
       </c>
-      <c r="L126" s="29"/>
-      <c r="M126" s="33" t="s">
+      <c r="L126" s="18"/>
+      <c r="M126" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="34"/>
+      <c r="N126" s="23"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -6004,30 +6040,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="35">
+      <c r="C127" s="17">
         <v>44795</v>
       </c>
-      <c r="D127" s="29"/>
+      <c r="D127" s="18"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="36" t="s">
+      <c r="F127" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="31"/>
-      <c r="H127" s="29"/>
-      <c r="I127" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="29"/>
-      <c r="K127" s="37">
+      <c r="G127" s="20"/>
+      <c r="H127" s="18"/>
+      <c r="I127" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="18"/>
+      <c r="K127" s="21">
         <v>51</v>
       </c>
-      <c r="L127" s="29"/>
-      <c r="M127" s="38" t="s">
+      <c r="L127" s="18"/>
+      <c r="M127" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="34"/>
+      <c r="N127" s="23"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -6036,30 +6072,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="28">
+      <c r="C128" s="36">
         <v>44799</v>
       </c>
-      <c r="D128" s="29"/>
+      <c r="D128" s="18"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="30" t="s">
+      <c r="F128" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="31"/>
-      <c r="H128" s="29"/>
-      <c r="I128" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="29"/>
-      <c r="K128" s="32">
+      <c r="G128" s="20"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="18"/>
+      <c r="K128" s="38">
         <v>80</v>
       </c>
-      <c r="L128" s="29"/>
-      <c r="M128" s="33" t="s">
+      <c r="L128" s="18"/>
+      <c r="M128" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="34"/>
+      <c r="N128" s="23"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -6068,30 +6104,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="35">
+      <c r="C129" s="17">
         <v>44799</v>
       </c>
-      <c r="D129" s="29"/>
+      <c r="D129" s="18"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="36" t="s">
+      <c r="F129" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="31"/>
-      <c r="H129" s="29"/>
-      <c r="I129" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="29"/>
-      <c r="K129" s="37">
+      <c r="G129" s="20"/>
+      <c r="H129" s="18"/>
+      <c r="I129" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="18"/>
+      <c r="K129" s="21">
         <v>100</v>
       </c>
-      <c r="L129" s="29"/>
-      <c r="M129" s="38" t="s">
+      <c r="L129" s="18"/>
+      <c r="M129" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="34"/>
+      <c r="N129" s="23"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -6100,30 +6136,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="28">
+      <c r="C130" s="36">
         <v>44802</v>
       </c>
-      <c r="D130" s="29"/>
+      <c r="D130" s="18"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="30" t="s">
+      <c r="F130" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="31"/>
-      <c r="H130" s="29"/>
-      <c r="I130" s="30" t="s">
+      <c r="G130" s="20"/>
+      <c r="H130" s="18"/>
+      <c r="I130" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="29"/>
-      <c r="K130" s="32">
+      <c r="J130" s="18"/>
+      <c r="K130" s="38">
         <v>96</v>
       </c>
-      <c r="L130" s="29"/>
-      <c r="M130" s="33" t="s">
+      <c r="L130" s="18"/>
+      <c r="M130" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="34"/>
+      <c r="N130" s="23"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -6132,30 +6168,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="35">
+      <c r="C131" s="17">
         <v>44802</v>
       </c>
-      <c r="D131" s="29"/>
+      <c r="D131" s="18"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="36" t="s">
+      <c r="F131" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="31"/>
-      <c r="H131" s="29"/>
-      <c r="I131" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="29"/>
-      <c r="K131" s="37">
+      <c r="G131" s="20"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="18"/>
+      <c r="K131" s="21">
         <v>37</v>
       </c>
-      <c r="L131" s="29"/>
-      <c r="M131" s="38" t="s">
+      <c r="L131" s="18"/>
+      <c r="M131" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="34"/>
+      <c r="N131" s="23"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -6164,30 +6200,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="28">
+      <c r="C132" s="36">
         <v>44804</v>
       </c>
-      <c r="D132" s="29"/>
+      <c r="D132" s="18"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="30" t="s">
+      <c r="F132" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="31"/>
-      <c r="H132" s="29"/>
-      <c r="I132" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="29"/>
-      <c r="K132" s="32">
+      <c r="G132" s="20"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="18"/>
+      <c r="K132" s="38">
         <v>91</v>
       </c>
-      <c r="L132" s="29"/>
-      <c r="M132" s="33" t="s">
+      <c r="L132" s="18"/>
+      <c r="M132" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="34"/>
+      <c r="N132" s="23"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -6196,30 +6232,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="35">
+      <c r="C133" s="17">
         <v>44804</v>
       </c>
-      <c r="D133" s="29"/>
+      <c r="D133" s="18"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="36" t="s">
+      <c r="F133" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="31"/>
-      <c r="H133" s="29"/>
-      <c r="I133" s="36" t="s">
+      <c r="G133" s="20"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="29"/>
-      <c r="K133" s="37">
+      <c r="J133" s="18"/>
+      <c r="K133" s="21">
         <v>56</v>
       </c>
-      <c r="L133" s="29"/>
-      <c r="M133" s="38" t="s">
+      <c r="L133" s="18"/>
+      <c r="M133" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="34"/>
+      <c r="N133" s="23"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -6228,30 +6264,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="28">
+      <c r="C134" s="36">
         <v>44805</v>
       </c>
-      <c r="D134" s="29"/>
+      <c r="D134" s="18"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="30" t="s">
+      <c r="F134" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="31"/>
-      <c r="H134" s="29"/>
-      <c r="I134" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="29"/>
-      <c r="K134" s="32">
+      <c r="G134" s="20"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="18"/>
+      <c r="K134" s="38">
         <v>401</v>
       </c>
-      <c r="L134" s="29"/>
-      <c r="M134" s="33" t="s">
+      <c r="L134" s="18"/>
+      <c r="M134" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="34"/>
+      <c r="N134" s="23"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -6260,30 +6296,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="35">
+      <c r="C135" s="17">
         <v>44805</v>
       </c>
-      <c r="D135" s="29"/>
+      <c r="D135" s="18"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="36" t="s">
+      <c r="F135" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="31"/>
-      <c r="H135" s="29"/>
-      <c r="I135" s="36" t="s">
+      <c r="G135" s="20"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="29"/>
-      <c r="K135" s="37">
+      <c r="J135" s="18"/>
+      <c r="K135" s="21">
         <v>375</v>
       </c>
-      <c r="L135" s="29"/>
-      <c r="M135" s="38" t="s">
+      <c r="L135" s="18"/>
+      <c r="M135" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="34"/>
+      <c r="N135" s="23"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6292,30 +6328,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="28">
+      <c r="C136" s="36">
         <v>44806</v>
       </c>
-      <c r="D136" s="29"/>
+      <c r="D136" s="18"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="30" t="s">
+      <c r="F136" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="31"/>
-      <c r="H136" s="29"/>
-      <c r="I136" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="29"/>
-      <c r="K136" s="32">
+      <c r="G136" s="20"/>
+      <c r="H136" s="18"/>
+      <c r="I136" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="18"/>
+      <c r="K136" s="38">
         <v>44</v>
       </c>
-      <c r="L136" s="29"/>
-      <c r="M136" s="33" t="s">
+      <c r="L136" s="18"/>
+      <c r="M136" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="34"/>
+      <c r="N136" s="23"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6324,30 +6360,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="35">
+      <c r="C137" s="17">
         <v>44806</v>
       </c>
-      <c r="D137" s="29"/>
+      <c r="D137" s="18"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="36" t="s">
+      <c r="F137" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="31"/>
-      <c r="H137" s="29"/>
-      <c r="I137" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="29"/>
-      <c r="K137" s="37">
+      <c r="G137" s="20"/>
+      <c r="H137" s="18"/>
+      <c r="I137" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="18"/>
+      <c r="K137" s="21">
         <v>51</v>
       </c>
-      <c r="L137" s="29"/>
-      <c r="M137" s="38" t="s">
+      <c r="L137" s="18"/>
+      <c r="M137" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="34"/>
+      <c r="N137" s="23"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6356,30 +6392,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="28">
+      <c r="C138" s="36">
         <v>44806</v>
       </c>
-      <c r="D138" s="29"/>
+      <c r="D138" s="18"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="30" t="s">
+      <c r="F138" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="31"/>
-      <c r="H138" s="29"/>
-      <c r="I138" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="29"/>
-      <c r="K138" s="32">
+      <c r="G138" s="20"/>
+      <c r="H138" s="18"/>
+      <c r="I138" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="18"/>
+      <c r="K138" s="38">
         <v>40</v>
       </c>
-      <c r="L138" s="29"/>
-      <c r="M138" s="33" t="s">
+      <c r="L138" s="18"/>
+      <c r="M138" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="34"/>
+      <c r="N138" s="23"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6388,30 +6424,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="35">
+      <c r="C139" s="17">
         <v>44810</v>
       </c>
-      <c r="D139" s="29"/>
+      <c r="D139" s="18"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="36" t="s">
+      <c r="F139" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="31"/>
-      <c r="H139" s="29"/>
-      <c r="I139" s="36" t="s">
+      <c r="G139" s="20"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="29"/>
-      <c r="K139" s="37">
+      <c r="J139" s="18"/>
+      <c r="K139" s="21">
         <v>9</v>
       </c>
-      <c r="L139" s="29"/>
-      <c r="M139" s="38" t="s">
+      <c r="L139" s="18"/>
+      <c r="M139" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="34"/>
+      <c r="N139" s="23"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6420,30 +6456,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="28">
+      <c r="C140" s="36">
         <v>44810</v>
       </c>
-      <c r="D140" s="29"/>
+      <c r="D140" s="18"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="30" t="s">
+      <c r="F140" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="31"/>
-      <c r="H140" s="29"/>
-      <c r="I140" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="29"/>
-      <c r="K140" s="32">
+      <c r="G140" s="20"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="18"/>
+      <c r="K140" s="38">
         <v>17</v>
       </c>
-      <c r="L140" s="29"/>
-      <c r="M140" s="33" t="s">
+      <c r="L140" s="18"/>
+      <c r="M140" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="34"/>
+      <c r="N140" s="23"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6452,30 +6488,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="35">
+      <c r="C141" s="17">
         <v>44810</v>
       </c>
-      <c r="D141" s="29"/>
+      <c r="D141" s="18"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="36" t="s">
+      <c r="F141" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="31"/>
-      <c r="H141" s="29"/>
-      <c r="I141" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="29"/>
-      <c r="K141" s="37">
+      <c r="G141" s="20"/>
+      <c r="H141" s="18"/>
+      <c r="I141" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="18"/>
+      <c r="K141" s="21">
         <v>5</v>
       </c>
-      <c r="L141" s="29"/>
-      <c r="M141" s="38" t="s">
+      <c r="L141" s="18"/>
+      <c r="M141" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="34"/>
+      <c r="N141" s="23"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6484,30 +6520,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="28">
+      <c r="C142" s="36">
         <v>44810</v>
       </c>
-      <c r="D142" s="29"/>
+      <c r="D142" s="18"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="30" t="s">
+      <c r="F142" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="31"/>
-      <c r="H142" s="29"/>
-      <c r="I142" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="29"/>
-      <c r="K142" s="32">
+      <c r="G142" s="20"/>
+      <c r="H142" s="18"/>
+      <c r="I142" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="18"/>
+      <c r="K142" s="38">
         <v>45</v>
       </c>
-      <c r="L142" s="29"/>
-      <c r="M142" s="33" t="s">
+      <c r="L142" s="18"/>
+      <c r="M142" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="34"/>
+      <c r="N142" s="23"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6516,30 +6552,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="35">
+      <c r="C143" s="17">
         <v>44811</v>
       </c>
-      <c r="D143" s="29"/>
+      <c r="D143" s="18"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="36" t="s">
+      <c r="F143" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="31"/>
-      <c r="H143" s="29"/>
-      <c r="I143" s="36" t="s">
+      <c r="G143" s="20"/>
+      <c r="H143" s="18"/>
+      <c r="I143" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="29"/>
-      <c r="K143" s="37">
+      <c r="J143" s="18"/>
+      <c r="K143" s="21">
         <v>132</v>
       </c>
-      <c r="L143" s="29"/>
-      <c r="M143" s="38" t="s">
+      <c r="L143" s="18"/>
+      <c r="M143" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="34"/>
+      <c r="N143" s="23"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6548,30 +6584,30 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="28">
+      <c r="C144" s="36">
         <v>44811</v>
       </c>
-      <c r="D144" s="29"/>
+      <c r="D144" s="18"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="30" t="s">
+      <c r="F144" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="31"/>
-      <c r="H144" s="29"/>
-      <c r="I144" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="29"/>
-      <c r="K144" s="32">
+      <c r="G144" s="20"/>
+      <c r="H144" s="18"/>
+      <c r="I144" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="18"/>
+      <c r="K144" s="38">
         <v>66</v>
       </c>
-      <c r="L144" s="29"/>
-      <c r="M144" s="33" t="s">
+      <c r="L144" s="18"/>
+      <c r="M144" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="34"/>
+      <c r="N144" s="23"/>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
@@ -6580,30 +6616,30 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="35">
+      <c r="C145" s="17">
         <v>44812</v>
       </c>
-      <c r="D145" s="29"/>
+      <c r="D145" s="18"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="36" t="s">
+      <c r="F145" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="31"/>
-      <c r="H145" s="29"/>
-      <c r="I145" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J145" s="29"/>
-      <c r="K145" s="37">
+      <c r="G145" s="20"/>
+      <c r="H145" s="18"/>
+      <c r="I145" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="18"/>
+      <c r="K145" s="21">
         <v>69</v>
       </c>
-      <c r="L145" s="29"/>
-      <c r="M145" s="38" t="s">
+      <c r="L145" s="18"/>
+      <c r="M145" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="N145" s="34"/>
+      <c r="N145" s="23"/>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="3" t="s">
@@ -6612,30 +6648,30 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="28">
+      <c r="C146" s="36">
         <v>44812</v>
       </c>
-      <c r="D146" s="29"/>
+      <c r="D146" s="18"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="30" t="s">
+      <c r="F146" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="G146" s="31"/>
-      <c r="H146" s="29"/>
-      <c r="I146" s="30" t="s">
+      <c r="G146" s="20"/>
+      <c r="H146" s="18"/>
+      <c r="I146" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J146" s="29"/>
-      <c r="K146" s="32">
+      <c r="J146" s="18"/>
+      <c r="K146" s="38">
         <v>48</v>
       </c>
-      <c r="L146" s="29"/>
-      <c r="M146" s="33" t="s">
+      <c r="L146" s="18"/>
+      <c r="M146" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="N146" s="34"/>
+      <c r="N146" s="23"/>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
@@ -6644,30 +6680,30 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="35">
+      <c r="C147" s="17">
         <v>44812</v>
       </c>
-      <c r="D147" s="29"/>
+      <c r="D147" s="18"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="36" t="s">
+      <c r="F147" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="G147" s="31"/>
-      <c r="H147" s="29"/>
-      <c r="I147" s="36" t="s">
+      <c r="G147" s="20"/>
+      <c r="H147" s="18"/>
+      <c r="I147" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J147" s="29"/>
-      <c r="K147" s="37">
+      <c r="J147" s="18"/>
+      <c r="K147" s="21">
         <v>33</v>
       </c>
-      <c r="L147" s="29"/>
-      <c r="M147" s="38" t="s">
+      <c r="L147" s="18"/>
+      <c r="M147" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="N147" s="34"/>
+      <c r="N147" s="23"/>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="3" t="s">
@@ -6676,30 +6712,30 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="28">
+      <c r="C148" s="36">
         <v>44813</v>
       </c>
-      <c r="D148" s="29"/>
+      <c r="D148" s="18"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="30" t="s">
+      <c r="F148" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="G148" s="31"/>
-      <c r="H148" s="29"/>
-      <c r="I148" s="30" t="s">
+      <c r="G148" s="20"/>
+      <c r="H148" s="18"/>
+      <c r="I148" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J148" s="29"/>
-      <c r="K148" s="32">
+      <c r="J148" s="18"/>
+      <c r="K148" s="38">
         <v>5</v>
       </c>
-      <c r="L148" s="29"/>
-      <c r="M148" s="33" t="s">
+      <c r="L148" s="18"/>
+      <c r="M148" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="N148" s="34"/>
+      <c r="N148" s="23"/>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
@@ -6708,30 +6744,30 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="35">
+      <c r="C149" s="17">
         <v>44813</v>
       </c>
-      <c r="D149" s="29"/>
+      <c r="D149" s="18"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="36" t="s">
+      <c r="F149" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="G149" s="31"/>
-      <c r="H149" s="29"/>
-      <c r="I149" s="36" t="s">
+      <c r="G149" s="20"/>
+      <c r="H149" s="18"/>
+      <c r="I149" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J149" s="29"/>
-      <c r="K149" s="37">
+      <c r="J149" s="18"/>
+      <c r="K149" s="21">
         <v>26</v>
       </c>
-      <c r="L149" s="29"/>
-      <c r="M149" s="38" t="s">
+      <c r="L149" s="18"/>
+      <c r="M149" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="N149" s="34"/>
+      <c r="N149" s="23"/>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="3" t="s">
@@ -6740,30 +6776,30 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="28">
+      <c r="C150" s="36">
         <v>44813</v>
       </c>
-      <c r="D150" s="29"/>
+      <c r="D150" s="18"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="30" t="s">
+      <c r="F150" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="G150" s="31"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J150" s="29"/>
-      <c r="K150" s="32">
+      <c r="G150" s="20"/>
+      <c r="H150" s="18"/>
+      <c r="I150" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="18"/>
+      <c r="K150" s="38">
         <v>13</v>
       </c>
-      <c r="L150" s="29"/>
-      <c r="M150" s="33" t="s">
+      <c r="L150" s="18"/>
+      <c r="M150" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="N150" s="34"/>
+      <c r="N150" s="23"/>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
@@ -6772,30 +6808,30 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="35">
+      <c r="C151" s="17">
         <v>44816</v>
       </c>
-      <c r="D151" s="29"/>
+      <c r="D151" s="18"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="36" t="s">
+      <c r="F151" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="G151" s="31"/>
-      <c r="H151" s="29"/>
-      <c r="I151" s="36" t="s">
+      <c r="G151" s="20"/>
+      <c r="H151" s="18"/>
+      <c r="I151" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J151" s="29"/>
-      <c r="K151" s="37">
+      <c r="J151" s="18"/>
+      <c r="K151" s="21">
         <v>50</v>
       </c>
-      <c r="L151" s="29"/>
-      <c r="M151" s="38" t="s">
+      <c r="L151" s="18"/>
+      <c r="M151" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="N151" s="34"/>
+      <c r="N151" s="23"/>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="3" t="s">
@@ -6804,30 +6840,30 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="28">
+      <c r="C152" s="36">
         <v>44816</v>
       </c>
-      <c r="D152" s="29"/>
+      <c r="D152" s="18"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="30" t="s">
+      <c r="F152" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="31"/>
-      <c r="H152" s="29"/>
-      <c r="I152" s="30" t="s">
+      <c r="G152" s="20"/>
+      <c r="H152" s="18"/>
+      <c r="I152" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J152" s="29"/>
-      <c r="K152" s="32">
+      <c r="J152" s="18"/>
+      <c r="K152" s="38">
         <v>104</v>
       </c>
-      <c r="L152" s="29"/>
-      <c r="M152" s="33" t="s">
+      <c r="L152" s="18"/>
+      <c r="M152" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="N152" s="34"/>
+      <c r="N152" s="23"/>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="1" t="s">
@@ -6836,30 +6872,30 @@
       <c r="B153" s="2">
         <v>44813</v>
       </c>
-      <c r="C153" s="35">
+      <c r="C153" s="17">
         <v>44817</v>
       </c>
-      <c r="D153" s="29"/>
+      <c r="D153" s="18"/>
       <c r="E153" s="2">
         <v>45199</v>
       </c>
-      <c r="F153" s="36" t="s">
+      <c r="F153" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G153" s="31"/>
-      <c r="H153" s="29"/>
-      <c r="I153" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J153" s="29"/>
-      <c r="K153" s="37">
+      <c r="G153" s="20"/>
+      <c r="H153" s="18"/>
+      <c r="I153" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="18"/>
+      <c r="K153" s="21">
         <v>1</v>
       </c>
-      <c r="L153" s="29"/>
-      <c r="M153" s="38" t="s">
+      <c r="L153" s="18"/>
+      <c r="M153" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N153" s="34"/>
+      <c r="N153" s="23"/>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="3" t="s">
@@ -6868,30 +6904,30 @@
       <c r="B154" s="4">
         <v>44813</v>
       </c>
-      <c r="C154" s="28">
+      <c r="C154" s="36">
         <v>44817</v>
       </c>
-      <c r="D154" s="29"/>
+      <c r="D154" s="18"/>
       <c r="E154" s="4">
         <v>44848</v>
       </c>
-      <c r="F154" s="30" t="s">
+      <c r="F154" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G154" s="31"/>
-      <c r="H154" s="29"/>
-      <c r="I154" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J154" s="29"/>
-      <c r="K154" s="32">
+      <c r="G154" s="20"/>
+      <c r="H154" s="18"/>
+      <c r="I154" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="18"/>
+      <c r="K154" s="38">
         <v>2</v>
       </c>
-      <c r="L154" s="29"/>
-      <c r="M154" s="33" t="s">
+      <c r="L154" s="18"/>
+      <c r="M154" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N154" s="34"/>
+      <c r="N154" s="23"/>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="1" t="s">
@@ -6900,30 +6936,30 @@
       <c r="B155" s="2">
         <v>44813</v>
       </c>
-      <c r="C155" s="35">
+      <c r="C155" s="17">
         <v>44817</v>
       </c>
-      <c r="D155" s="29"/>
+      <c r="D155" s="18"/>
       <c r="E155" s="2">
         <v>45198</v>
       </c>
-      <c r="F155" s="36" t="s">
+      <c r="F155" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G155" s="31"/>
-      <c r="H155" s="29"/>
-      <c r="I155" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J155" s="29"/>
-      <c r="K155" s="37">
+      <c r="G155" s="20"/>
+      <c r="H155" s="18"/>
+      <c r="I155" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="18"/>
+      <c r="K155" s="21">
         <v>2</v>
       </c>
-      <c r="L155" s="29"/>
-      <c r="M155" s="38" t="s">
+      <c r="L155" s="18"/>
+      <c r="M155" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N155" s="34"/>
+      <c r="N155" s="23"/>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="3" t="s">
@@ -6932,30 +6968,30 @@
       <c r="B156" s="4">
         <v>44813</v>
       </c>
-      <c r="C156" s="28">
+      <c r="C156" s="36">
         <v>44817</v>
       </c>
-      <c r="D156" s="29"/>
+      <c r="D156" s="18"/>
       <c r="E156" s="4">
         <v>45044</v>
       </c>
-      <c r="F156" s="30" t="s">
+      <c r="F156" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G156" s="31"/>
-      <c r="H156" s="29"/>
-      <c r="I156" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J156" s="29"/>
-      <c r="K156" s="32">
+      <c r="G156" s="20"/>
+      <c r="H156" s="18"/>
+      <c r="I156" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="18"/>
+      <c r="K156" s="38">
         <v>5</v>
       </c>
-      <c r="L156" s="29"/>
-      <c r="M156" s="33" t="s">
+      <c r="L156" s="18"/>
+      <c r="M156" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N156" s="34"/>
+      <c r="N156" s="23"/>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="1" t="s">
@@ -6964,30 +7000,30 @@
       <c r="B157" s="2">
         <v>44813</v>
       </c>
-      <c r="C157" s="35">
+      <c r="C157" s="17">
         <v>44817</v>
       </c>
-      <c r="D157" s="29"/>
+      <c r="D157" s="18"/>
       <c r="E157" s="2">
         <v>45107</v>
       </c>
-      <c r="F157" s="36" t="s">
+      <c r="F157" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G157" s="31"/>
-      <c r="H157" s="29"/>
-      <c r="I157" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J157" s="29"/>
-      <c r="K157" s="37">
+      <c r="G157" s="20"/>
+      <c r="H157" s="18"/>
+      <c r="I157" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="18"/>
+      <c r="K157" s="21">
         <v>2</v>
       </c>
-      <c r="L157" s="29"/>
-      <c r="M157" s="38" t="s">
+      <c r="L157" s="18"/>
+      <c r="M157" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N157" s="34"/>
+      <c r="N157" s="23"/>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="3" t="s">
@@ -6996,30 +7032,30 @@
       <c r="B158" s="4">
         <v>44813</v>
       </c>
-      <c r="C158" s="28">
+      <c r="C158" s="36">
         <v>44817</v>
       </c>
-      <c r="D158" s="29"/>
+      <c r="D158" s="18"/>
       <c r="E158" s="4">
         <v>45192</v>
       </c>
-      <c r="F158" s="30" t="s">
+      <c r="F158" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G158" s="31"/>
-      <c r="H158" s="29"/>
-      <c r="I158" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" s="29"/>
-      <c r="K158" s="32">
+      <c r="G158" s="20"/>
+      <c r="H158" s="18"/>
+      <c r="I158" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="18"/>
+      <c r="K158" s="38">
         <v>1</v>
       </c>
-      <c r="L158" s="29"/>
-      <c r="M158" s="33" t="s">
+      <c r="L158" s="18"/>
+      <c r="M158" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N158" s="34"/>
+      <c r="N158" s="23"/>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="1" t="s">
@@ -7028,30 +7064,30 @@
       <c r="B159" s="2">
         <v>44813</v>
       </c>
-      <c r="C159" s="35">
+      <c r="C159" s="17">
         <v>44817</v>
       </c>
-      <c r="D159" s="29"/>
+      <c r="D159" s="18"/>
       <c r="E159" s="2">
         <v>44957</v>
       </c>
-      <c r="F159" s="36" t="s">
+      <c r="F159" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G159" s="31"/>
-      <c r="H159" s="29"/>
-      <c r="I159" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J159" s="29"/>
-      <c r="K159" s="37">
+      <c r="G159" s="20"/>
+      <c r="H159" s="18"/>
+      <c r="I159" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="18"/>
+      <c r="K159" s="21">
         <v>4</v>
       </c>
-      <c r="L159" s="29"/>
-      <c r="M159" s="38" t="s">
+      <c r="L159" s="18"/>
+      <c r="M159" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N159" s="34"/>
+      <c r="N159" s="23"/>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="3" t="s">
@@ -7060,30 +7096,30 @@
       <c r="B160" s="4">
         <v>44813</v>
       </c>
-      <c r="C160" s="28">
+      <c r="C160" s="36">
         <v>44817</v>
       </c>
-      <c r="D160" s="29"/>
+      <c r="D160" s="18"/>
       <c r="E160" s="4">
         <v>44834</v>
       </c>
-      <c r="F160" s="30" t="s">
+      <c r="F160" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G160" s="31"/>
-      <c r="H160" s="29"/>
-      <c r="I160" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J160" s="29"/>
-      <c r="K160" s="32">
+      <c r="G160" s="20"/>
+      <c r="H160" s="18"/>
+      <c r="I160" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="18"/>
+      <c r="K160" s="38">
         <v>4</v>
       </c>
-      <c r="L160" s="29"/>
-      <c r="M160" s="33" t="s">
+      <c r="L160" s="18"/>
+      <c r="M160" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N160" s="34"/>
+      <c r="N160" s="23"/>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="1" t="s">
@@ -7092,30 +7128,30 @@
       <c r="B161" s="2">
         <v>44813</v>
       </c>
-      <c r="C161" s="35">
+      <c r="C161" s="17">
         <v>44817</v>
       </c>
-      <c r="D161" s="29"/>
+      <c r="D161" s="18"/>
       <c r="E161" s="2">
         <v>45077</v>
       </c>
-      <c r="F161" s="36" t="s">
+      <c r="F161" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G161" s="31"/>
-      <c r="H161" s="29"/>
-      <c r="I161" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J161" s="29"/>
-      <c r="K161" s="37">
+      <c r="G161" s="20"/>
+      <c r="H161" s="18"/>
+      <c r="I161" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="18"/>
+      <c r="K161" s="21">
         <v>3</v>
       </c>
-      <c r="L161" s="29"/>
-      <c r="M161" s="38" t="s">
+      <c r="L161" s="18"/>
+      <c r="M161" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N161" s="34"/>
+      <c r="N161" s="23"/>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="3" t="s">
@@ -7124,30 +7160,30 @@
       <c r="B162" s="4">
         <v>44813</v>
       </c>
-      <c r="C162" s="28">
+      <c r="C162" s="36">
         <v>44817</v>
       </c>
-      <c r="D162" s="29"/>
+      <c r="D162" s="18"/>
       <c r="E162" s="4">
         <v>45093</v>
       </c>
-      <c r="F162" s="30" t="s">
+      <c r="F162" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G162" s="31"/>
-      <c r="H162" s="29"/>
-      <c r="I162" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J162" s="29"/>
-      <c r="K162" s="32">
+      <c r="G162" s="20"/>
+      <c r="H162" s="18"/>
+      <c r="I162" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="18"/>
+      <c r="K162" s="38">
         <v>8</v>
       </c>
-      <c r="L162" s="29"/>
-      <c r="M162" s="33" t="s">
+      <c r="L162" s="18"/>
+      <c r="M162" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N162" s="34"/>
+      <c r="N162" s="23"/>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="1" t="s">
@@ -7156,30 +7192,30 @@
       <c r="B163" s="2">
         <v>44813</v>
       </c>
-      <c r="C163" s="35">
+      <c r="C163" s="17">
         <v>44817</v>
       </c>
-      <c r="D163" s="29"/>
+      <c r="D163" s="18"/>
       <c r="E163" s="2">
         <v>45565</v>
       </c>
-      <c r="F163" s="36" t="s">
+      <c r="F163" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G163" s="31"/>
-      <c r="H163" s="29"/>
-      <c r="I163" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J163" s="29"/>
-      <c r="K163" s="37">
+      <c r="G163" s="20"/>
+      <c r="H163" s="18"/>
+      <c r="I163" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="18"/>
+      <c r="K163" s="21">
         <v>1</v>
       </c>
-      <c r="L163" s="29"/>
-      <c r="M163" s="38" t="s">
+      <c r="L163" s="18"/>
+      <c r="M163" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N163" s="34"/>
+      <c r="N163" s="23"/>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="3" t="s">
@@ -7188,30 +7224,30 @@
       <c r="B164" s="4">
         <v>44813</v>
       </c>
-      <c r="C164" s="28">
+      <c r="C164" s="36">
         <v>44817</v>
       </c>
-      <c r="D164" s="29"/>
+      <c r="D164" s="18"/>
       <c r="E164" s="4">
         <v>45227</v>
       </c>
-      <c r="F164" s="30" t="s">
+      <c r="F164" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G164" s="31"/>
-      <c r="H164" s="29"/>
-      <c r="I164" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J164" s="29"/>
-      <c r="K164" s="32">
+      <c r="G164" s="20"/>
+      <c r="H164" s="18"/>
+      <c r="I164" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="18"/>
+      <c r="K164" s="38">
         <v>2</v>
       </c>
-      <c r="L164" s="29"/>
-      <c r="M164" s="33" t="s">
+      <c r="L164" s="18"/>
+      <c r="M164" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N164" s="34"/>
+      <c r="N164" s="23"/>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="1" t="s">
@@ -7220,30 +7256,30 @@
       <c r="B165" s="2">
         <v>44813</v>
       </c>
-      <c r="C165" s="35">
+      <c r="C165" s="17">
         <v>44817</v>
       </c>
-      <c r="D165" s="29"/>
+      <c r="D165" s="18"/>
       <c r="E165" s="2">
         <v>45046</v>
       </c>
-      <c r="F165" s="36" t="s">
+      <c r="F165" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G165" s="31"/>
-      <c r="H165" s="29"/>
-      <c r="I165" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J165" s="29"/>
-      <c r="K165" s="37">
+      <c r="G165" s="20"/>
+      <c r="H165" s="18"/>
+      <c r="I165" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="18"/>
+      <c r="K165" s="21">
         <v>1</v>
       </c>
-      <c r="L165" s="29"/>
-      <c r="M165" s="38" t="s">
+      <c r="L165" s="18"/>
+      <c r="M165" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N165" s="34"/>
+      <c r="N165" s="23"/>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="3" t="s">
@@ -7252,30 +7288,30 @@
       <c r="B166" s="4">
         <v>44813</v>
       </c>
-      <c r="C166" s="28">
+      <c r="C166" s="36">
         <v>44817</v>
       </c>
-      <c r="D166" s="29"/>
+      <c r="D166" s="18"/>
       <c r="E166" s="4">
         <v>45092</v>
       </c>
-      <c r="F166" s="30" t="s">
+      <c r="F166" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G166" s="31"/>
-      <c r="H166" s="29"/>
-      <c r="I166" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J166" s="29"/>
-      <c r="K166" s="32">
+      <c r="G166" s="20"/>
+      <c r="H166" s="18"/>
+      <c r="I166" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="18"/>
+      <c r="K166" s="38">
         <v>3</v>
       </c>
-      <c r="L166" s="29"/>
-      <c r="M166" s="33" t="s">
+      <c r="L166" s="18"/>
+      <c r="M166" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N166" s="34"/>
+      <c r="N166" s="23"/>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="1" t="s">
@@ -7284,30 +7320,30 @@
       <c r="B167" s="2">
         <v>44813</v>
       </c>
-      <c r="C167" s="35">
+      <c r="C167" s="17">
         <v>44817</v>
       </c>
-      <c r="D167" s="29"/>
+      <c r="D167" s="18"/>
       <c r="E167" s="2">
         <v>44985</v>
       </c>
-      <c r="F167" s="36" t="s">
+      <c r="F167" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G167" s="31"/>
-      <c r="H167" s="29"/>
-      <c r="I167" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J167" s="29"/>
-      <c r="K167" s="37">
+      <c r="G167" s="20"/>
+      <c r="H167" s="18"/>
+      <c r="I167" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="18"/>
+      <c r="K167" s="21">
         <v>1</v>
       </c>
-      <c r="L167" s="29"/>
-      <c r="M167" s="38" t="s">
+      <c r="L167" s="18"/>
+      <c r="M167" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="N167" s="34"/>
+      <c r="N167" s="23"/>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="3" t="s">
@@ -7316,30 +7352,30 @@
       <c r="B168" s="4">
         <v>44813</v>
       </c>
-      <c r="C168" s="28">
+      <c r="C168" s="36">
         <v>44817</v>
       </c>
-      <c r="D168" s="29"/>
+      <c r="D168" s="18"/>
       <c r="E168" s="4">
         <v>45555</v>
       </c>
-      <c r="F168" s="30" t="s">
+      <c r="F168" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G168" s="31"/>
-      <c r="H168" s="29"/>
-      <c r="I168" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J168" s="29"/>
-      <c r="K168" s="32">
+      <c r="G168" s="20"/>
+      <c r="H168" s="18"/>
+      <c r="I168" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="18"/>
+      <c r="K168" s="38">
         <v>1</v>
       </c>
-      <c r="L168" s="29"/>
-      <c r="M168" s="33" t="s">
+      <c r="L168" s="18"/>
+      <c r="M168" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="N168" s="34"/>
+      <c r="N168" s="23"/>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="1" t="s">
@@ -7348,30 +7384,30 @@
       <c r="B169" s="2">
         <v>44811</v>
       </c>
-      <c r="C169" s="35">
+      <c r="C169" s="17">
         <v>44817</v>
       </c>
-      <c r="D169" s="29"/>
+      <c r="D169" s="18"/>
       <c r="E169" s="2">
         <v>44882</v>
       </c>
-      <c r="F169" s="36" t="s">
+      <c r="F169" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="G169" s="31"/>
-      <c r="H169" s="29"/>
-      <c r="I169" s="36" t="s">
+      <c r="G169" s="20"/>
+      <c r="H169" s="18"/>
+      <c r="I169" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J169" s="29"/>
-      <c r="K169" s="37">
+      <c r="J169" s="18"/>
+      <c r="K169" s="21">
         <v>92</v>
       </c>
-      <c r="L169" s="29"/>
-      <c r="M169" s="38" t="s">
+      <c r="L169" s="18"/>
+      <c r="M169" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="N169" s="34"/>
+      <c r="N169" s="23"/>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="3" t="s">
@@ -7380,30 +7416,30 @@
       <c r="B170" s="4">
         <v>44811</v>
       </c>
-      <c r="C170" s="28">
+      <c r="C170" s="36">
         <v>44817</v>
       </c>
-      <c r="D170" s="29"/>
+      <c r="D170" s="18"/>
       <c r="E170" s="4">
         <v>44882</v>
       </c>
-      <c r="F170" s="30" t="s">
+      <c r="F170" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="G170" s="31"/>
-      <c r="H170" s="29"/>
-      <c r="I170" s="30" t="s">
+      <c r="G170" s="20"/>
+      <c r="H170" s="18"/>
+      <c r="I170" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J170" s="29"/>
-      <c r="K170" s="32">
+      <c r="J170" s="18"/>
+      <c r="K170" s="38">
         <v>169</v>
       </c>
-      <c r="L170" s="29"/>
-      <c r="M170" s="33" t="s">
+      <c r="L170" s="18"/>
+      <c r="M170" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="N170" s="34"/>
+      <c r="N170" s="23"/>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="1" t="s">
@@ -7412,30 +7448,30 @@
       <c r="B171" s="2">
         <v>44817</v>
       </c>
-      <c r="C171" s="35">
+      <c r="C171" s="17">
         <v>44818</v>
       </c>
-      <c r="D171" s="29"/>
+      <c r="D171" s="18"/>
       <c r="E171" s="2">
         <v>44888</v>
       </c>
-      <c r="F171" s="36" t="s">
+      <c r="F171" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="G171" s="31"/>
-      <c r="H171" s="29"/>
-      <c r="I171" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J171" s="29"/>
-      <c r="K171" s="37">
+      <c r="G171" s="20"/>
+      <c r="H171" s="18"/>
+      <c r="I171" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="18"/>
+      <c r="K171" s="21">
         <v>99</v>
       </c>
-      <c r="L171" s="29"/>
-      <c r="M171" s="38" t="s">
+      <c r="L171" s="18"/>
+      <c r="M171" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="N171" s="34"/>
+      <c r="N171" s="23"/>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="3" t="s">
@@ -7444,30 +7480,30 @@
       <c r="B172" s="4">
         <v>44817</v>
       </c>
-      <c r="C172" s="28">
+      <c r="C172" s="36">
         <v>44818</v>
       </c>
-      <c r="D172" s="29"/>
+      <c r="D172" s="18"/>
       <c r="E172" s="4">
         <v>44911</v>
       </c>
-      <c r="F172" s="30" t="s">
+      <c r="F172" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="G172" s="31"/>
-      <c r="H172" s="29"/>
-      <c r="I172" s="30" t="s">
+      <c r="G172" s="20"/>
+      <c r="H172" s="18"/>
+      <c r="I172" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J172" s="29"/>
-      <c r="K172" s="32">
+      <c r="J172" s="18"/>
+      <c r="K172" s="38">
         <v>10</v>
       </c>
-      <c r="L172" s="29"/>
-      <c r="M172" s="33" t="s">
+      <c r="L172" s="18"/>
+      <c r="M172" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="N172" s="34"/>
+      <c r="N172" s="23"/>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="1" t="s">
@@ -7476,30 +7512,30 @@
       <c r="B173" s="2">
         <v>44817</v>
       </c>
-      <c r="C173" s="35">
+      <c r="C173" s="17">
         <v>44818</v>
       </c>
-      <c r="D173" s="29"/>
+      <c r="D173" s="18"/>
       <c r="E173" s="2">
         <v>44876</v>
       </c>
-      <c r="F173" s="36" t="s">
+      <c r="F173" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="G173" s="31"/>
-      <c r="H173" s="29"/>
-      <c r="I173" s="36" t="s">
+      <c r="G173" s="20"/>
+      <c r="H173" s="18"/>
+      <c r="I173" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J173" s="29"/>
-      <c r="K173" s="37">
+      <c r="J173" s="18"/>
+      <c r="K173" s="21">
         <v>69</v>
       </c>
-      <c r="L173" s="29"/>
-      <c r="M173" s="38" t="s">
+      <c r="L173" s="18"/>
+      <c r="M173" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="N173" s="34"/>
+      <c r="N173" s="23"/>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="3" t="s">
@@ -7508,30 +7544,30 @@
       <c r="B174" s="4">
         <v>44810</v>
       </c>
-      <c r="C174" s="28">
+      <c r="C174" s="36">
         <v>44819</v>
       </c>
-      <c r="D174" s="29"/>
+      <c r="D174" s="18"/>
       <c r="E174" s="4">
         <v>44870</v>
       </c>
-      <c r="F174" s="30" t="s">
+      <c r="F174" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="G174" s="31"/>
-      <c r="H174" s="29"/>
-      <c r="I174" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J174" s="29"/>
-      <c r="K174" s="32">
+      <c r="G174" s="20"/>
+      <c r="H174" s="18"/>
+      <c r="I174" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="18"/>
+      <c r="K174" s="38">
         <v>115</v>
       </c>
-      <c r="L174" s="29"/>
-      <c r="M174" s="33" t="s">
+      <c r="L174" s="18"/>
+      <c r="M174" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="N174" s="34"/>
+      <c r="N174" s="23"/>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="1" t="s">
@@ -7540,30 +7576,30 @@
       <c r="B175" s="2">
         <v>44806</v>
       </c>
-      <c r="C175" s="35">
+      <c r="C175" s="17">
         <v>44819</v>
       </c>
-      <c r="D175" s="29"/>
+      <c r="D175" s="18"/>
       <c r="E175" s="2">
         <v>44867</v>
       </c>
-      <c r="F175" s="36" t="s">
+      <c r="F175" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="G175" s="31"/>
-      <c r="H175" s="29"/>
-      <c r="I175" s="36" t="s">
+      <c r="G175" s="20"/>
+      <c r="H175" s="18"/>
+      <c r="I175" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J175" s="29"/>
-      <c r="K175" s="37">
+      <c r="J175" s="18"/>
+      <c r="K175" s="21">
         <v>109</v>
       </c>
-      <c r="L175" s="29"/>
-      <c r="M175" s="38" t="s">
+      <c r="L175" s="18"/>
+      <c r="M175" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N175" s="34"/>
+      <c r="N175" s="23"/>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="3" t="s">
@@ -7572,30 +7608,30 @@
       <c r="B176" s="4">
         <v>44818</v>
       </c>
-      <c r="C176" s="28">
+      <c r="C176" s="36">
         <v>44819</v>
       </c>
-      <c r="D176" s="29"/>
+      <c r="D176" s="18"/>
       <c r="E176" s="4">
         <v>44883</v>
       </c>
-      <c r="F176" s="30" t="s">
+      <c r="F176" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="G176" s="31"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="30" t="s">
+      <c r="G176" s="20"/>
+      <c r="H176" s="18"/>
+      <c r="I176" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J176" s="29"/>
-      <c r="K176" s="32">
+      <c r="J176" s="18"/>
+      <c r="K176" s="38">
         <v>113</v>
       </c>
-      <c r="L176" s="29"/>
-      <c r="M176" s="33" t="s">
+      <c r="L176" s="18"/>
+      <c r="M176" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="N176" s="34"/>
+      <c r="N176" s="23"/>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="1" t="s">
@@ -7604,30 +7640,30 @@
       <c r="B177" s="2">
         <v>44818</v>
       </c>
-      <c r="C177" s="35">
+      <c r="C177" s="17">
         <v>44819</v>
       </c>
-      <c r="D177" s="29"/>
+      <c r="D177" s="18"/>
       <c r="E177" s="2">
         <v>44872</v>
       </c>
-      <c r="F177" s="36" t="s">
+      <c r="F177" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="G177" s="31"/>
-      <c r="H177" s="29"/>
-      <c r="I177" s="36" t="s">
+      <c r="G177" s="20"/>
+      <c r="H177" s="18"/>
+      <c r="I177" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J177" s="29"/>
-      <c r="K177" s="37">
+      <c r="J177" s="18"/>
+      <c r="K177" s="21">
         <v>13</v>
       </c>
-      <c r="L177" s="29"/>
-      <c r="M177" s="38" t="s">
+      <c r="L177" s="18"/>
+      <c r="M177" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="N177" s="34"/>
+      <c r="N177" s="23"/>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="3" t="s">
@@ -7636,30 +7672,30 @@
       <c r="B178" s="4">
         <v>44818</v>
       </c>
-      <c r="C178" s="28">
+      <c r="C178" s="36">
         <v>44819</v>
       </c>
-      <c r="D178" s="29"/>
+      <c r="D178" s="18"/>
       <c r="E178" s="4">
         <v>44818</v>
       </c>
-      <c r="F178" s="30" t="s">
+      <c r="F178" s="37" t="s">
         <v>294</v>
       </c>
-      <c r="G178" s="31"/>
-      <c r="H178" s="29"/>
-      <c r="I178" s="30" t="s">
+      <c r="G178" s="20"/>
+      <c r="H178" s="18"/>
+      <c r="I178" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J178" s="29"/>
-      <c r="K178" s="32">
+      <c r="J178" s="18"/>
+      <c r="K178" s="38">
         <v>1</v>
       </c>
-      <c r="L178" s="29"/>
-      <c r="M178" s="33" t="s">
+      <c r="L178" s="18"/>
+      <c r="M178" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="N178" s="34"/>
+      <c r="N178" s="23"/>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="1" t="s">
@@ -7668,30 +7704,30 @@
       <c r="B179" s="2">
         <v>44811</v>
       </c>
-      <c r="C179" s="35">
+      <c r="C179" s="17">
         <v>44819</v>
       </c>
-      <c r="D179" s="29"/>
+      <c r="D179" s="18"/>
       <c r="E179" s="2">
         <v>44895</v>
       </c>
-      <c r="F179" s="36" t="s">
+      <c r="F179" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="G179" s="31"/>
-      <c r="H179" s="29"/>
-      <c r="I179" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J179" s="29"/>
-      <c r="K179" s="37">
+      <c r="G179" s="20"/>
+      <c r="H179" s="18"/>
+      <c r="I179" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="18"/>
+      <c r="K179" s="21">
         <v>137</v>
       </c>
-      <c r="L179" s="29"/>
-      <c r="M179" s="38" t="s">
+      <c r="L179" s="18"/>
+      <c r="M179" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="N179" s="34"/>
+      <c r="N179" s="23"/>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="3" t="s">
@@ -7700,30 +7736,30 @@
       <c r="B180" s="4">
         <v>44812</v>
       </c>
-      <c r="C180" s="28">
+      <c r="C180" s="36">
         <v>44819</v>
       </c>
-      <c r="D180" s="29"/>
+      <c r="D180" s="18"/>
       <c r="E180" s="4">
         <v>44873</v>
       </c>
-      <c r="F180" s="30" t="s">
+      <c r="F180" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="G180" s="31"/>
-      <c r="H180" s="29"/>
-      <c r="I180" s="30" t="s">
+      <c r="G180" s="20"/>
+      <c r="H180" s="18"/>
+      <c r="I180" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J180" s="29"/>
-      <c r="K180" s="32">
+      <c r="J180" s="18"/>
+      <c r="K180" s="38">
         <v>73</v>
       </c>
-      <c r="L180" s="29"/>
-      <c r="M180" s="33" t="s">
+      <c r="L180" s="18"/>
+      <c r="M180" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="N180" s="34"/>
+      <c r="N180" s="23"/>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="1" t="s">
@@ -7732,30 +7768,30 @@
       <c r="B181" s="2">
         <v>44818</v>
       </c>
-      <c r="C181" s="35">
+      <c r="C181" s="17">
         <v>44819</v>
       </c>
-      <c r="D181" s="29"/>
+      <c r="D181" s="18"/>
       <c r="E181" s="2">
         <v>44880</v>
       </c>
-      <c r="F181" s="36" t="s">
+      <c r="F181" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="G181" s="31"/>
-      <c r="H181" s="29"/>
-      <c r="I181" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J181" s="29"/>
-      <c r="K181" s="37">
+      <c r="G181" s="20"/>
+      <c r="H181" s="18"/>
+      <c r="I181" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="18"/>
+      <c r="K181" s="21">
         <v>108</v>
       </c>
-      <c r="L181" s="29"/>
-      <c r="M181" s="38" t="s">
+      <c r="L181" s="18"/>
+      <c r="M181" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="N181" s="34"/>
+      <c r="N181" s="23"/>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="3" t="s">
@@ -7764,30 +7800,30 @@
       <c r="B182" s="4">
         <v>44812</v>
       </c>
-      <c r="C182" s="28">
+      <c r="C182" s="36">
         <v>44820</v>
       </c>
-      <c r="D182" s="29"/>
+      <c r="D182" s="18"/>
       <c r="E182" s="4">
         <v>44873</v>
       </c>
-      <c r="F182" s="30" t="s">
+      <c r="F182" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="G182" s="31"/>
-      <c r="H182" s="29"/>
-      <c r="I182" s="30" t="s">
+      <c r="G182" s="20"/>
+      <c r="H182" s="18"/>
+      <c r="I182" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J182" s="29"/>
-      <c r="K182" s="32">
+      <c r="J182" s="18"/>
+      <c r="K182" s="38">
         <v>49</v>
       </c>
-      <c r="L182" s="29"/>
-      <c r="M182" s="33" t="s">
+      <c r="L182" s="18"/>
+      <c r="M182" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="N182" s="34"/>
+      <c r="N182" s="23"/>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="1" t="s">
@@ -7796,30 +7832,30 @@
       <c r="B183" s="2">
         <v>44812</v>
       </c>
-      <c r="C183" s="35">
+      <c r="C183" s="17">
         <v>44820</v>
       </c>
-      <c r="D183" s="29"/>
+      <c r="D183" s="18"/>
       <c r="E183" s="2">
         <v>44873</v>
       </c>
-      <c r="F183" s="36" t="s">
+      <c r="F183" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="G183" s="31"/>
-      <c r="H183" s="29"/>
-      <c r="I183" s="36" t="s">
+      <c r="G183" s="20"/>
+      <c r="H183" s="18"/>
+      <c r="I183" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J183" s="29"/>
-      <c r="K183" s="37">
+      <c r="J183" s="18"/>
+      <c r="K183" s="21">
         <v>49</v>
       </c>
-      <c r="L183" s="29"/>
-      <c r="M183" s="38" t="s">
+      <c r="L183" s="18"/>
+      <c r="M183" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="N183" s="34"/>
+      <c r="N183" s="23"/>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="3" t="s">
@@ -7828,30 +7864,30 @@
       <c r="B184" s="4">
         <v>44812</v>
       </c>
-      <c r="C184" s="28">
+      <c r="C184" s="36">
         <v>44820</v>
       </c>
-      <c r="D184" s="29"/>
+      <c r="D184" s="18"/>
       <c r="E184" s="4">
         <v>44873</v>
       </c>
-      <c r="F184" s="30" t="s">
+      <c r="F184" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="G184" s="31"/>
-      <c r="H184" s="29"/>
-      <c r="I184" s="30" t="s">
+      <c r="G184" s="20"/>
+      <c r="H184" s="18"/>
+      <c r="I184" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J184" s="29"/>
-      <c r="K184" s="32">
+      <c r="J184" s="18"/>
+      <c r="K184" s="38">
         <v>41</v>
       </c>
-      <c r="L184" s="29"/>
-      <c r="M184" s="33" t="s">
+      <c r="L184" s="18"/>
+      <c r="M184" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="N184" s="34"/>
+      <c r="N184" s="23"/>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="1" t="s">
@@ -7860,30 +7896,30 @@
       <c r="B185" s="2">
         <v>44820</v>
       </c>
-      <c r="C185" s="35">
+      <c r="C185" s="17">
         <v>44820</v>
       </c>
-      <c r="D185" s="29"/>
+      <c r="D185" s="18"/>
       <c r="E185" s="2">
         <v>44880</v>
       </c>
-      <c r="F185" s="36" t="s">
+      <c r="F185" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="G185" s="31"/>
-      <c r="H185" s="29"/>
-      <c r="I185" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J185" s="29"/>
-      <c r="K185" s="37">
+      <c r="G185" s="20"/>
+      <c r="H185" s="18"/>
+      <c r="I185" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="18"/>
+      <c r="K185" s="21">
         <v>66</v>
       </c>
-      <c r="L185" s="29"/>
-      <c r="M185" s="38" t="s">
+      <c r="L185" s="18"/>
+      <c r="M185" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="N185" s="34"/>
+      <c r="N185" s="23"/>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="3" t="s">
@@ -7892,30 +7928,30 @@
       <c r="B186" s="4">
         <v>44823</v>
       </c>
-      <c r="C186" s="28">
+      <c r="C186" s="36">
         <v>44823</v>
       </c>
-      <c r="D186" s="29"/>
+      <c r="D186" s="18"/>
       <c r="E186" s="4">
         <v>44883</v>
       </c>
-      <c r="F186" s="30" t="s">
+      <c r="F186" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="G186" s="31"/>
-      <c r="H186" s="29"/>
-      <c r="I186" s="30" t="s">
+      <c r="G186" s="20"/>
+      <c r="H186" s="18"/>
+      <c r="I186" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J186" s="29"/>
-      <c r="K186" s="32">
+      <c r="J186" s="18"/>
+      <c r="K186" s="38">
         <v>57</v>
       </c>
-      <c r="L186" s="29"/>
-      <c r="M186" s="33" t="s">
+      <c r="L186" s="18"/>
+      <c r="M186" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="N186" s="34"/>
+      <c r="N186" s="23"/>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="1" t="s">
@@ -7924,30 +7960,30 @@
       <c r="B187" s="2">
         <v>44823</v>
       </c>
-      <c r="C187" s="35">
+      <c r="C187" s="17">
         <v>44824</v>
       </c>
-      <c r="D187" s="29"/>
+      <c r="D187" s="18"/>
       <c r="E187" s="2">
         <v>44882</v>
       </c>
-      <c r="F187" s="36" t="s">
+      <c r="F187" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="G187" s="31"/>
-      <c r="H187" s="29"/>
-      <c r="I187" s="36" t="s">
+      <c r="G187" s="20"/>
+      <c r="H187" s="18"/>
+      <c r="I187" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J187" s="29"/>
-      <c r="K187" s="37">
+      <c r="J187" s="18"/>
+      <c r="K187" s="21">
         <v>88</v>
       </c>
-      <c r="L187" s="29"/>
-      <c r="M187" s="38" t="s">
+      <c r="L187" s="18"/>
+      <c r="M187" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="N187" s="34"/>
+      <c r="N187" s="23"/>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="3" t="s">
@@ -7956,30 +7992,30 @@
       <c r="B188" s="4">
         <v>44824</v>
       </c>
-      <c r="C188" s="28">
+      <c r="C188" s="36">
         <v>44824</v>
       </c>
-      <c r="D188" s="29"/>
+      <c r="D188" s="18"/>
       <c r="E188" s="4">
         <v>44886</v>
       </c>
-      <c r="F188" s="30" t="s">
+      <c r="F188" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="G188" s="31"/>
-      <c r="H188" s="29"/>
-      <c r="I188" s="30" t="s">
+      <c r="G188" s="20"/>
+      <c r="H188" s="18"/>
+      <c r="I188" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J188" s="29"/>
-      <c r="K188" s="32">
+      <c r="J188" s="18"/>
+      <c r="K188" s="38">
         <v>79</v>
       </c>
-      <c r="L188" s="29"/>
-      <c r="M188" s="33" t="s">
+      <c r="L188" s="18"/>
+      <c r="M188" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="N188" s="34"/>
+      <c r="N188" s="23"/>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="1" t="s">
@@ -7988,30 +8024,30 @@
       <c r="B189" s="2">
         <v>44823</v>
       </c>
-      <c r="C189" s="35">
+      <c r="C189" s="17">
         <v>44825</v>
       </c>
-      <c r="D189" s="29"/>
+      <c r="D189" s="18"/>
       <c r="E189" s="2">
         <v>44883</v>
       </c>
-      <c r="F189" s="36" t="s">
+      <c r="F189" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="G189" s="31"/>
-      <c r="H189" s="29"/>
-      <c r="I189" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J189" s="29"/>
-      <c r="K189" s="37">
+      <c r="G189" s="20"/>
+      <c r="H189" s="18"/>
+      <c r="I189" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="18"/>
+      <c r="K189" s="21">
         <v>49</v>
       </c>
-      <c r="L189" s="29"/>
-      <c r="M189" s="38" t="s">
+      <c r="L189" s="18"/>
+      <c r="M189" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="N189" s="34"/>
+      <c r="N189" s="23"/>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="3" t="s">
@@ -8020,30 +8056,30 @@
       <c r="B190" s="4">
         <v>44824</v>
       </c>
-      <c r="C190" s="28">
+      <c r="C190" s="36">
         <v>44825</v>
       </c>
-      <c r="D190" s="29"/>
+      <c r="D190" s="18"/>
       <c r="E190" s="4">
         <v>44872</v>
       </c>
-      <c r="F190" s="30" t="s">
+      <c r="F190" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="G190" s="31"/>
-      <c r="H190" s="29"/>
-      <c r="I190" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J190" s="29"/>
-      <c r="K190" s="32">
+      <c r="G190" s="20"/>
+      <c r="H190" s="18"/>
+      <c r="I190" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="18"/>
+      <c r="K190" s="38">
         <v>104</v>
       </c>
-      <c r="L190" s="29"/>
-      <c r="M190" s="33" t="s">
+      <c r="L190" s="18"/>
+      <c r="M190" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="N190" s="34"/>
+      <c r="N190" s="23"/>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="1" t="s">
@@ -8052,30 +8088,30 @@
       <c r="B191" s="2">
         <v>44824</v>
       </c>
-      <c r="C191" s="35">
+      <c r="C191" s="17">
         <v>44825</v>
       </c>
-      <c r="D191" s="29"/>
+      <c r="D191" s="18"/>
       <c r="E191" s="2">
         <v>44872</v>
       </c>
-      <c r="F191" s="36" t="s">
+      <c r="F191" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="G191" s="31"/>
-      <c r="H191" s="29"/>
-      <c r="I191" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J191" s="29"/>
-      <c r="K191" s="37">
+      <c r="G191" s="20"/>
+      <c r="H191" s="18"/>
+      <c r="I191" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="18"/>
+      <c r="K191" s="21">
         <v>7</v>
       </c>
-      <c r="L191" s="29"/>
-      <c r="M191" s="38" t="s">
+      <c r="L191" s="18"/>
+      <c r="M191" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="N191" s="34"/>
+      <c r="N191" s="23"/>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="3" t="s">
@@ -8084,30 +8120,30 @@
       <c r="B192" s="4">
         <v>44826</v>
       </c>
-      <c r="C192" s="28">
+      <c r="C192" s="36">
         <v>44826</v>
       </c>
-      <c r="D192" s="29"/>
+      <c r="D192" s="18"/>
       <c r="E192" s="4">
         <v>44888</v>
       </c>
-      <c r="F192" s="30" t="s">
+      <c r="F192" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="G192" s="31"/>
-      <c r="H192" s="29"/>
-      <c r="I192" s="30" t="s">
+      <c r="G192" s="20"/>
+      <c r="H192" s="18"/>
+      <c r="I192" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J192" s="29"/>
-      <c r="K192" s="32">
+      <c r="J192" s="18"/>
+      <c r="K192" s="38">
         <v>15</v>
       </c>
-      <c r="L192" s="29"/>
-      <c r="M192" s="33" t="s">
+      <c r="L192" s="18"/>
+      <c r="M192" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="N192" s="34"/>
+      <c r="N192" s="23"/>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="1" t="s">
@@ -8116,30 +8152,30 @@
       <c r="B193" s="2">
         <v>44825</v>
       </c>
-      <c r="C193" s="35">
+      <c r="C193" s="17">
         <v>44826</v>
       </c>
-      <c r="D193" s="29"/>
+      <c r="D193" s="18"/>
       <c r="E193" s="2">
         <v>44867</v>
       </c>
-      <c r="F193" s="36" t="s">
+      <c r="F193" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="G193" s="31"/>
-      <c r="H193" s="29"/>
-      <c r="I193" s="36" t="s">
+      <c r="G193" s="20"/>
+      <c r="H193" s="18"/>
+      <c r="I193" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J193" s="29"/>
-      <c r="K193" s="37">
-        <v>18</v>
-      </c>
-      <c r="L193" s="29"/>
-      <c r="M193" s="38" t="s">
+      <c r="J193" s="18"/>
+      <c r="K193" s="21">
+        <v>18</v>
+      </c>
+      <c r="L193" s="18"/>
+      <c r="M193" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="N193" s="34"/>
+      <c r="N193" s="23"/>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="3" t="s">
@@ -8148,30 +8184,30 @@
       <c r="B194" s="4">
         <v>44825</v>
       </c>
-      <c r="C194" s="28">
+      <c r="C194" s="36">
         <v>44826</v>
       </c>
-      <c r="D194" s="29"/>
+      <c r="D194" s="18"/>
       <c r="E194" s="4">
         <v>44867</v>
       </c>
-      <c r="F194" s="30" t="s">
+      <c r="F194" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="G194" s="31"/>
-      <c r="H194" s="29"/>
-      <c r="I194" s="30" t="s">
+      <c r="G194" s="20"/>
+      <c r="H194" s="18"/>
+      <c r="I194" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J194" s="29"/>
-      <c r="K194" s="32">
+      <c r="J194" s="18"/>
+      <c r="K194" s="38">
         <v>69</v>
       </c>
-      <c r="L194" s="29"/>
-      <c r="M194" s="33" t="s">
+      <c r="L194" s="18"/>
+      <c r="M194" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="N194" s="34"/>
+      <c r="N194" s="23"/>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="1" t="s">
@@ -8180,30 +8216,30 @@
       <c r="B195" s="2">
         <v>44825</v>
       </c>
-      <c r="C195" s="35">
+      <c r="C195" s="17">
         <v>44826</v>
       </c>
-      <c r="D195" s="29"/>
+      <c r="D195" s="18"/>
       <c r="E195" s="2">
         <v>44867</v>
       </c>
-      <c r="F195" s="36" t="s">
+      <c r="F195" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="G195" s="31"/>
-      <c r="H195" s="29"/>
-      <c r="I195" s="36" t="s">
+      <c r="G195" s="20"/>
+      <c r="H195" s="18"/>
+      <c r="I195" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J195" s="29"/>
-      <c r="K195" s="37">
+      <c r="J195" s="18"/>
+      <c r="K195" s="21">
         <v>11</v>
       </c>
-      <c r="L195" s="29"/>
-      <c r="M195" s="38" t="s">
+      <c r="L195" s="18"/>
+      <c r="M195" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="N195" s="34"/>
+      <c r="N195" s="23"/>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="3" t="s">
@@ -8212,30 +8248,30 @@
       <c r="B196" s="4">
         <v>44825</v>
       </c>
-      <c r="C196" s="28">
+      <c r="C196" s="36">
         <v>44826</v>
       </c>
-      <c r="D196" s="29"/>
+      <c r="D196" s="18"/>
       <c r="E196" s="4">
         <v>44867</v>
       </c>
-      <c r="F196" s="30" t="s">
+      <c r="F196" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="G196" s="31"/>
-      <c r="H196" s="29"/>
-      <c r="I196" s="30" t="s">
+      <c r="G196" s="20"/>
+      <c r="H196" s="18"/>
+      <c r="I196" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J196" s="29"/>
-      <c r="K196" s="32">
+      <c r="J196" s="18"/>
+      <c r="K196" s="38">
         <v>2</v>
       </c>
-      <c r="L196" s="29"/>
-      <c r="M196" s="33" t="s">
+      <c r="L196" s="18"/>
+      <c r="M196" s="39" t="s">
         <v>328</v>
       </c>
-      <c r="N196" s="34"/>
+      <c r="N196" s="23"/>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="1" t="s">
@@ -8244,30 +8280,30 @@
       <c r="B197" s="2">
         <v>44827</v>
       </c>
-      <c r="C197" s="35">
+      <c r="C197" s="17">
         <v>44827</v>
       </c>
-      <c r="D197" s="29"/>
+      <c r="D197" s="18"/>
       <c r="E197" s="2">
         <v>44888</v>
       </c>
-      <c r="F197" s="36" t="s">
+      <c r="F197" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G197" s="31"/>
-      <c r="H197" s="29"/>
-      <c r="I197" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J197" s="29"/>
-      <c r="K197" s="37">
+      <c r="G197" s="20"/>
+      <c r="H197" s="18"/>
+      <c r="I197" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="18"/>
+      <c r="K197" s="21">
         <v>72</v>
       </c>
-      <c r="L197" s="29"/>
-      <c r="M197" s="38" t="s">
+      <c r="L197" s="18"/>
+      <c r="M197" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="N197" s="34"/>
+      <c r="N197" s="23"/>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="3" t="s">
@@ -8276,30 +8312,30 @@
       <c r="B198" s="4">
         <v>44830</v>
       </c>
-      <c r="C198" s="28">
+      <c r="C198" s="36">
         <v>44830</v>
       </c>
-      <c r="D198" s="29"/>
+      <c r="D198" s="18"/>
       <c r="E198" s="4">
         <v>44891</v>
       </c>
-      <c r="F198" s="30" t="s">
+      <c r="F198" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="G198" s="31"/>
-      <c r="H198" s="29"/>
-      <c r="I198" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J198" s="29"/>
-      <c r="K198" s="32">
+      <c r="G198" s="20"/>
+      <c r="H198" s="18"/>
+      <c r="I198" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="18"/>
+      <c r="K198" s="38">
         <v>51</v>
       </c>
-      <c r="L198" s="29"/>
-      <c r="M198" s="33" t="s">
+      <c r="L198" s="18"/>
+      <c r="M198" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="N198" s="34"/>
+      <c r="N198" s="23"/>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="1" t="s">
@@ -8308,30 +8344,30 @@
       <c r="B199" s="2">
         <v>44830</v>
       </c>
-      <c r="C199" s="35">
+      <c r="C199" s="17">
         <v>44830</v>
       </c>
-      <c r="D199" s="29"/>
+      <c r="D199" s="18"/>
       <c r="E199" s="2">
         <v>44892</v>
       </c>
-      <c r="F199" s="36" t="s">
+      <c r="F199" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="G199" s="31"/>
-      <c r="H199" s="29"/>
-      <c r="I199" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="J199" s="29"/>
-      <c r="K199" s="37">
+      <c r="G199" s="20"/>
+      <c r="H199" s="18"/>
+      <c r="I199" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="18"/>
+      <c r="K199" s="21">
         <v>353</v>
       </c>
-      <c r="L199" s="29"/>
-      <c r="M199" s="38" t="s">
+      <c r="L199" s="18"/>
+      <c r="M199" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="N199" s="34"/>
+      <c r="N199" s="23"/>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="3" t="s">
@@ -8340,30 +8376,30 @@
       <c r="B200" s="4">
         <v>44830</v>
       </c>
-      <c r="C200" s="28">
+      <c r="C200" s="36">
         <v>44830</v>
       </c>
-      <c r="D200" s="29"/>
+      <c r="D200" s="18"/>
       <c r="E200" s="4">
         <v>44891</v>
       </c>
-      <c r="F200" s="30" t="s">
+      <c r="F200" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="G200" s="31"/>
-      <c r="H200" s="29"/>
-      <c r="I200" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J200" s="29"/>
-      <c r="K200" s="32">
+      <c r="G200" s="20"/>
+      <c r="H200" s="18"/>
+      <c r="I200" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="18"/>
+      <c r="K200" s="38">
         <v>46</v>
       </c>
-      <c r="L200" s="29"/>
-      <c r="M200" s="33" t="s">
+      <c r="L200" s="18"/>
+      <c r="M200" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="N200" s="34"/>
+      <c r="N200" s="23"/>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="1" t="s">
@@ -8372,30 +8408,30 @@
       <c r="B201" s="2">
         <v>44825</v>
       </c>
-      <c r="C201" s="35">
+      <c r="C201" s="17">
         <v>44831</v>
       </c>
-      <c r="D201" s="29"/>
+      <c r="D201" s="18"/>
       <c r="E201" s="2">
         <v>44888</v>
       </c>
-      <c r="F201" s="36" t="s">
+      <c r="F201" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="G201" s="31"/>
-      <c r="H201" s="29"/>
-      <c r="I201" s="36" t="s">
+      <c r="G201" s="20"/>
+      <c r="H201" s="18"/>
+      <c r="I201" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J201" s="29"/>
-      <c r="K201" s="37">
+      <c r="J201" s="18"/>
+      <c r="K201" s="21">
         <v>905</v>
       </c>
-      <c r="L201" s="29"/>
-      <c r="M201" s="38" t="s">
+      <c r="L201" s="18"/>
+      <c r="M201" s="22" t="s">
         <v>337</v>
       </c>
-      <c r="N201" s="34"/>
+      <c r="N201" s="23"/>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="3" t="s">
@@ -8404,30 +8440,30 @@
       <c r="B202" s="4">
         <v>44830</v>
       </c>
-      <c r="C202" s="28">
+      <c r="C202" s="36">
         <v>44831</v>
       </c>
-      <c r="D202" s="29"/>
+      <c r="D202" s="18"/>
       <c r="E202" s="4">
         <v>44890</v>
       </c>
-      <c r="F202" s="30" t="s">
+      <c r="F202" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="G202" s="31"/>
-      <c r="H202" s="29"/>
-      <c r="I202" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J202" s="29"/>
-      <c r="K202" s="32">
+      <c r="G202" s="20"/>
+      <c r="H202" s="18"/>
+      <c r="I202" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="18"/>
+      <c r="K202" s="38">
         <v>63</v>
       </c>
-      <c r="L202" s="29"/>
-      <c r="M202" s="33" t="s">
+      <c r="L202" s="18"/>
+      <c r="M202" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="N202" s="34"/>
+      <c r="N202" s="23"/>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="1" t="s">
@@ -8436,30 +8472,30 @@
       <c r="B203" s="2">
         <v>44824</v>
       </c>
-      <c r="C203" s="35">
+      <c r="C203" s="17">
         <v>44831</v>
       </c>
-      <c r="D203" s="29"/>
+      <c r="D203" s="18"/>
       <c r="E203" s="2">
         <v>44887</v>
       </c>
-      <c r="F203" s="36" t="s">
+      <c r="F203" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="G203" s="31"/>
-      <c r="H203" s="29"/>
-      <c r="I203" s="36" t="s">
+      <c r="G203" s="20"/>
+      <c r="H203" s="18"/>
+      <c r="I203" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J203" s="29"/>
-      <c r="K203" s="37">
+      <c r="J203" s="18"/>
+      <c r="K203" s="21">
         <v>308</v>
       </c>
-      <c r="L203" s="29"/>
-      <c r="M203" s="38" t="s">
+      <c r="L203" s="18"/>
+      <c r="M203" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="N203" s="34"/>
+      <c r="N203" s="23"/>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="3" t="s">
@@ -8468,30 +8504,30 @@
       <c r="B204" s="4">
         <v>44818</v>
       </c>
-      <c r="C204" s="28">
+      <c r="C204" s="36">
         <v>44832</v>
       </c>
-      <c r="D204" s="29"/>
+      <c r="D204" s="18"/>
       <c r="E204" s="4">
         <v>44879</v>
       </c>
-      <c r="F204" s="30" t="s">
+      <c r="F204" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="G204" s="31"/>
-      <c r="H204" s="29"/>
-      <c r="I204" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J204" s="29"/>
-      <c r="K204" s="32">
+      <c r="G204" s="20"/>
+      <c r="H204" s="18"/>
+      <c r="I204" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="18"/>
+      <c r="K204" s="38">
         <v>10</v>
       </c>
-      <c r="L204" s="29"/>
-      <c r="M204" s="33" t="s">
+      <c r="L204" s="18"/>
+      <c r="M204" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="N204" s="34"/>
+      <c r="N204" s="23"/>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="1" t="s">
@@ -8500,30 +8536,30 @@
       <c r="B205" s="2">
         <v>44832</v>
       </c>
-      <c r="C205" s="35">
+      <c r="C205" s="17">
         <v>44832</v>
       </c>
-      <c r="D205" s="29"/>
+      <c r="D205" s="18"/>
       <c r="E205" s="2">
         <v>44893</v>
       </c>
-      <c r="F205" s="36" t="s">
+      <c r="F205" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="G205" s="31"/>
-      <c r="H205" s="29"/>
-      <c r="I205" s="36" t="s">
+      <c r="G205" s="20"/>
+      <c r="H205" s="18"/>
+      <c r="I205" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J205" s="29"/>
-      <c r="K205" s="37">
+      <c r="J205" s="18"/>
+      <c r="K205" s="21">
         <v>93</v>
       </c>
-      <c r="L205" s="29"/>
-      <c r="M205" s="38" t="s">
+      <c r="L205" s="18"/>
+      <c r="M205" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="N205" s="34"/>
+      <c r="N205" s="23"/>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="3" t="s">
@@ -8532,107 +8568,292 @@
       <c r="B206" s="4">
         <v>44820</v>
       </c>
-      <c r="C206" s="28">
+      <c r="C206" s="36">
         <v>44832</v>
       </c>
-      <c r="D206" s="29"/>
+      <c r="D206" s="18"/>
       <c r="E206" s="4">
         <v>44849</v>
       </c>
-      <c r="F206" s="30" t="s">
+      <c r="F206" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="G206" s="31"/>
-      <c r="H206" s="29"/>
-      <c r="I206" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J206" s="29"/>
-      <c r="K206" s="32">
+      <c r="G206" s="20"/>
+      <c r="H206" s="18"/>
+      <c r="I206" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="18"/>
+      <c r="K206" s="38">
         <v>70</v>
       </c>
-      <c r="L206" s="29"/>
-      <c r="M206" s="33" t="s">
+      <c r="L206" s="18"/>
+      <c r="M206" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="N206" s="34"/>
-    </row>
-    <row r="207" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A207" s="47" t="s">
+      <c r="N206" s="23"/>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B207" s="2">
+        <v>44833</v>
+      </c>
+      <c r="C207" s="17">
+        <v>44833</v>
+      </c>
+      <c r="D207" s="18"/>
+      <c r="E207" s="2">
+        <v>44897</v>
+      </c>
+      <c r="F207" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="G207" s="20"/>
+      <c r="H207" s="18"/>
+      <c r="I207" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J207" s="18"/>
+      <c r="K207" s="21">
+        <v>21</v>
+      </c>
+      <c r="L207" s="18"/>
+      <c r="M207" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="N207" s="23"/>
+    </row>
+    <row r="208" spans="1:14">
+      <c r="A208" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B208" s="4">
+        <v>44834</v>
+      </c>
+      <c r="C208" s="36">
+        <v>44834</v>
+      </c>
+      <c r="D208" s="18"/>
+      <c r="E208" s="4">
+        <v>44896</v>
+      </c>
+      <c r="F208" s="37" t="s">
+        <v>349</v>
+      </c>
+      <c r="G208" s="20"/>
+      <c r="H208" s="18"/>
+      <c r="I208" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="J208" s="18"/>
+      <c r="K208" s="38">
+        <v>28</v>
+      </c>
+      <c r="L208" s="18"/>
+      <c r="M208" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="N208" s="23"/>
+    </row>
+    <row r="209" spans="1:14">
+      <c r="A209" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B209" s="2">
+        <v>44777</v>
+      </c>
+      <c r="C209" s="17">
+        <v>44834</v>
+      </c>
+      <c r="D209" s="18"/>
+      <c r="E209" s="2">
+        <v>44837</v>
+      </c>
+      <c r="F209" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="G209" s="20"/>
+      <c r="H209" s="18"/>
+      <c r="I209" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J209" s="18"/>
+      <c r="K209" s="21">
+        <v>201</v>
+      </c>
+      <c r="L209" s="18"/>
+      <c r="M209" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="N209" s="23"/>
+    </row>
+    <row r="210" spans="1:14">
+      <c r="A210" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B210" s="4">
+        <v>44833</v>
+      </c>
+      <c r="C210" s="36">
+        <v>44837</v>
+      </c>
+      <c r="D210" s="18"/>
+      <c r="E210" s="4">
+        <v>44894</v>
+      </c>
+      <c r="F210" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="G210" s="20"/>
+      <c r="H210" s="18"/>
+      <c r="I210" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J210" s="18"/>
+      <c r="K210" s="38">
+        <v>49</v>
+      </c>
+      <c r="L210" s="18"/>
+      <c r="M210" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="N210" s="23"/>
+    </row>
+    <row r="211" spans="1:14">
+      <c r="A211" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B211" s="2">
+        <v>44834</v>
+      </c>
+      <c r="C211" s="17">
+        <v>44837</v>
+      </c>
+      <c r="D211" s="18"/>
+      <c r="E211" s="2">
+        <v>44906</v>
+      </c>
+      <c r="F211" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="G211" s="20"/>
+      <c r="H211" s="18"/>
+      <c r="I211" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J211" s="18"/>
+      <c r="K211" s="21">
+        <v>7</v>
+      </c>
+      <c r="L211" s="18"/>
+      <c r="M211" s="22" t="s">
         <v>357</v>
       </c>
-      <c r="B207" s="48"/>
-      <c r="C207" s="44" t="s">
-        <v>347</v>
-      </c>
-      <c r="D207" s="45"/>
-      <c r="E207" s="46"/>
-      <c r="F207" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="G207" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="H207" s="44" t="s">
-        <v>350</v>
-      </c>
-      <c r="I207" s="46"/>
-      <c r="J207" s="44" t="s">
-        <v>351</v>
-      </c>
-      <c r="K207" s="46"/>
-      <c r="L207" s="44" t="s">
-        <v>352</v>
-      </c>
-      <c r="M207" s="46"/>
-      <c r="N207" s="11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14" s="9" customFormat="1">
-      <c r="A208" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="B208" s="43"/>
-      <c r="C208" s="39">
-        <v>15205</v>
-      </c>
-      <c r="D208" s="40"/>
-      <c r="E208" s="41"/>
-      <c r="F208" s="7">
-        <v>117</v>
-      </c>
-      <c r="G208" s="7">
+      <c r="N211" s="23"/>
+    </row>
+    <row r="212" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A212" s="48" t="s">
+        <v>368</v>
+      </c>
+      <c r="B212" s="49"/>
+      <c r="C212" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="D212" s="46"/>
+      <c r="E212" s="47"/>
+      <c r="F212" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="G212" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="H212" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="I212" s="47"/>
+      <c r="J212" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="K212" s="47"/>
+      <c r="L212" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="M212" s="47"/>
+      <c r="N212" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" s="10" customFormat="1">
+      <c r="A213" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="B213" s="44"/>
+      <c r="C213" s="40">
+        <v>15511</v>
+      </c>
+      <c r="D213" s="41"/>
+      <c r="E213" s="42"/>
+      <c r="F213" s="7">
+        <v>120</v>
+      </c>
+      <c r="G213" s="8">
         <v>7</v>
       </c>
-      <c r="H208" s="39">
+      <c r="H213" s="40">
         <v>1</v>
       </c>
-      <c r="I208" s="41"/>
-      <c r="J208" s="39">
-        <v>76</v>
-      </c>
-      <c r="K208" s="41"/>
-      <c r="L208" s="39">
+      <c r="I213" s="42"/>
+      <c r="J213" s="40">
+        <v>78</v>
+      </c>
+      <c r="K213" s="42"/>
+      <c r="L213" s="40">
         <v>1</v>
       </c>
-      <c r="M208" s="41"/>
-      <c r="N208" s="8">
+      <c r="M213" s="42"/>
+      <c r="N213" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1032">
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="H208:I208"/>
-    <mergeCell ref="J208:K208"/>
-    <mergeCell ref="L208:M208"/>
-    <mergeCell ref="A208:B208"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="H207:I207"/>
-    <mergeCell ref="J207:K207"/>
-    <mergeCell ref="L207:M207"/>
-    <mergeCell ref="A207:B207"/>
+  <mergeCells count="1057">
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="H213:I213"/>
+    <mergeCell ref="J213:K213"/>
+    <mergeCell ref="L213:M213"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="H212:I212"/>
+    <mergeCell ref="J212:K212"/>
+    <mergeCell ref="L212:M212"/>
+    <mergeCell ref="A212:B212"/>
+    <mergeCell ref="C211:D211"/>
+    <mergeCell ref="F211:H211"/>
+    <mergeCell ref="I211:J211"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="M211:N211"/>
+    <mergeCell ref="C210:D210"/>
+    <mergeCell ref="F210:H210"/>
+    <mergeCell ref="I210:J210"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="C209:D209"/>
+    <mergeCell ref="F209:H209"/>
+    <mergeCell ref="I209:J209"/>
+    <mergeCell ref="K209:L209"/>
+    <mergeCell ref="M209:N209"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="F208:H208"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="M208:N208"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:H207"/>
+    <mergeCell ref="I207:J207"/>
+    <mergeCell ref="K207:L207"/>
+    <mergeCell ref="M207:N207"/>
     <mergeCell ref="C206:D206"/>
     <mergeCell ref="F206:H206"/>
     <mergeCell ref="I206:J206"/>
@@ -9623,18 +9844,6 @@
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="M9:N9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:J8"/>
@@ -9655,6 +9864,18 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18510" windowHeight="8295"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14160" windowHeight="8295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="376">
   <si>
     <t/>
   </si>
@@ -1142,6 +1142,21 @@
     <t>705 Sixth Avenue  San Diego CA 92101</t>
   </si>
   <si>
+    <t>The Honest Kitchen</t>
+  </si>
+  <si>
+    <t>2501 W Rosecrans Ave  Los Angeles CA 90059</t>
+  </si>
+  <si>
+    <t>BioMarin Pharmaceutical Inc.</t>
+  </si>
+  <si>
+    <t>770 Lindaro St  San Rafael CA 94901</t>
+  </si>
+  <si>
+    <t>105 Digital Dr  Novato CA 94949</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1168,7 +1183,7 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 10/5/2022
+ End Date: 10/10/2022
 </t>
   </si>
   <si>
@@ -1661,37 +1676,37 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1724,10 +1739,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2010,62 +2025,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R214"/>
+  <dimension ref="A1:R217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="2.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.5703125" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="2.140625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="6.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" customWidth="1"/>
+    <col min="13" max="13" width="5.140625" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="48" t="s">
-        <v>369</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
+      <c r="A1" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="38.25" customHeight="1">
-      <c r="A2" s="49" t="s">
-        <v>368</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
+      <c r="A2" s="48" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -2142,27 +2157,27 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="27">
         <v>44750</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="28"/>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="28"/>
-      <c r="K5" s="36">
+      <c r="K5" s="31">
         <v>2</v>
       </c>
       <c r="L5" s="28"/>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="32" t="s">
         <v>12</v>
       </c>
       <c r="N5" s="33"/>
@@ -2174,27 +2189,27 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="34">
         <v>44750</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="35" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="28"/>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="28"/>
-      <c r="K6" s="31">
+      <c r="K6" s="36">
         <v>13</v>
       </c>
       <c r="L6" s="28"/>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="37" t="s">
         <v>15</v>
       </c>
       <c r="N6" s="33"/>
@@ -2206,27 +2221,27 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="27">
         <v>44750</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="29" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="28"/>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="28"/>
-      <c r="K7" s="36">
+      <c r="K7" s="31">
         <v>9</v>
       </c>
       <c r="L7" s="28"/>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="32" t="s">
         <v>19</v>
       </c>
       <c r="N7" s="33"/>
@@ -2238,27 +2253,27 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="34">
         <v>44750</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="35" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="28"/>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J8" s="28"/>
-      <c r="K8" s="31">
+      <c r="K8" s="36">
         <v>123</v>
       </c>
       <c r="L8" s="28"/>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="37" t="s">
         <v>20</v>
       </c>
       <c r="N8" s="33"/>
@@ -2270,27 +2285,27 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="27">
         <v>44750</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="29" t="s">
         <v>21</v>
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="28"/>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="28"/>
-      <c r="K9" s="36">
+      <c r="K9" s="31">
         <v>37</v>
       </c>
       <c r="L9" s="28"/>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="32" t="s">
         <v>22</v>
       </c>
       <c r="N9" s="33"/>
@@ -2302,27 +2317,27 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="34">
         <v>44753</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="35" t="s">
         <v>23</v>
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="28"/>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="28"/>
-      <c r="K10" s="31">
+      <c r="K10" s="36">
         <v>37</v>
       </c>
       <c r="L10" s="28"/>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="37" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="33"/>
@@ -2334,27 +2349,27 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="27">
         <v>44753</v>
       </c>
       <c r="D11" s="28"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="28"/>
-      <c r="K11" s="36">
+      <c r="K11" s="31">
         <v>80</v>
       </c>
       <c r="L11" s="28"/>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="32" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="33"/>
@@ -2366,27 +2381,27 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="34">
         <v>44753</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="35" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="28"/>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="28"/>
-      <c r="K12" s="31">
+      <c r="K12" s="36">
         <v>229</v>
       </c>
       <c r="L12" s="28"/>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="37" t="s">
         <v>29</v>
       </c>
       <c r="N12" s="33"/>
@@ -2398,27 +2413,27 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="27">
         <v>44753</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="29" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="28"/>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="28"/>
-      <c r="K13" s="36">
+      <c r="K13" s="31">
         <v>368</v>
       </c>
       <c r="L13" s="28"/>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="32" t="s">
         <v>31</v>
       </c>
       <c r="N13" s="33"/>
@@ -2430,27 +2445,27 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="34">
         <v>44753</v>
       </c>
       <c r="D14" s="28"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="35" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="28"/>
-      <c r="I14" s="29" t="s">
+      <c r="I14" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="28"/>
-      <c r="K14" s="31">
+      <c r="K14" s="36">
         <v>62</v>
       </c>
       <c r="L14" s="28"/>
-      <c r="M14" s="32" t="s">
+      <c r="M14" s="37" t="s">
         <v>34</v>
       </c>
       <c r="N14" s="33"/>
@@ -2462,27 +2477,27 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="27">
         <v>44753</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="28"/>
-      <c r="K15" s="36">
+      <c r="K15" s="31">
         <v>25</v>
       </c>
       <c r="L15" s="28"/>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="32" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="33"/>
@@ -2494,27 +2509,27 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="34">
         <v>44753</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="35" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="30"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="28"/>
-      <c r="K16" s="31">
+      <c r="K16" s="36">
         <v>68</v>
       </c>
       <c r="L16" s="28"/>
-      <c r="M16" s="32" t="s">
+      <c r="M16" s="37" t="s">
         <v>36</v>
       </c>
       <c r="N16" s="33"/>
@@ -2526,27 +2541,27 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="27">
         <v>44753</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="28"/>
-      <c r="I17" s="35" t="s">
+      <c r="I17" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="28"/>
-      <c r="K17" s="36">
+      <c r="K17" s="31">
         <v>77</v>
       </c>
       <c r="L17" s="28"/>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="32" t="s">
         <v>38</v>
       </c>
       <c r="N17" s="33"/>
@@ -2558,27 +2573,27 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="34">
         <v>44754</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="35" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J18" s="28"/>
-      <c r="K18" s="31">
+      <c r="K18" s="36">
         <v>20</v>
       </c>
       <c r="L18" s="28"/>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="37" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="33"/>
@@ -2590,27 +2605,27 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="27">
         <v>44754</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="29" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="30"/>
       <c r="H19" s="28"/>
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J19" s="28"/>
-      <c r="K19" s="36">
+      <c r="K19" s="31">
         <v>5</v>
       </c>
       <c r="L19" s="28"/>
-      <c r="M19" s="37" t="s">
+      <c r="M19" s="32" t="s">
         <v>40</v>
       </c>
       <c r="N19" s="33"/>
@@ -2622,27 +2637,27 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="34">
         <v>44754</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="35" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="28"/>
-      <c r="K20" s="31">
+      <c r="K20" s="36">
         <v>2</v>
       </c>
       <c r="L20" s="28"/>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="37" t="s">
         <v>41</v>
       </c>
       <c r="N20" s="33"/>
@@ -2654,27 +2669,27 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="27">
         <v>44754</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="29" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="30"/>
       <c r="H21" s="28"/>
-      <c r="I21" s="35" t="s">
+      <c r="I21" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J21" s="28"/>
-      <c r="K21" s="36">
+      <c r="K21" s="31">
         <v>1</v>
       </c>
       <c r="L21" s="28"/>
-      <c r="M21" s="37" t="s">
+      <c r="M21" s="32" t="s">
         <v>42</v>
       </c>
       <c r="N21" s="33"/>
@@ -2686,27 +2701,27 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="34">
         <v>44754</v>
       </c>
       <c r="D22" s="28"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="35" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="28"/>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J22" s="28"/>
-      <c r="K22" s="31">
+      <c r="K22" s="36">
         <v>41</v>
       </c>
       <c r="L22" s="28"/>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="33"/>
@@ -2718,27 +2733,27 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="27">
         <v>44754</v>
       </c>
       <c r="D23" s="28"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="29" t="s">
         <v>45</v>
       </c>
       <c r="G23" s="30"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J23" s="28"/>
-      <c r="K23" s="36">
+      <c r="K23" s="31">
         <v>4</v>
       </c>
       <c r="L23" s="28"/>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="32" t="s">
         <v>46</v>
       </c>
       <c r="N23" s="33"/>
@@ -2750,27 +2765,27 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="34">
         <v>44754</v>
       </c>
       <c r="D24" s="28"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="30"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="28"/>
-      <c r="K24" s="31">
+      <c r="K24" s="36">
         <v>211</v>
       </c>
       <c r="L24" s="28"/>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="37" t="s">
         <v>48</v>
       </c>
       <c r="N24" s="33"/>
@@ -2782,27 +2797,27 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="27">
         <v>44754</v>
       </c>
       <c r="D25" s="28"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="29" t="s">
         <v>45</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="35" t="s">
+      <c r="I25" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J25" s="28"/>
-      <c r="K25" s="36">
+      <c r="K25" s="31">
         <v>10</v>
       </c>
       <c r="L25" s="28"/>
-      <c r="M25" s="37" t="s">
+      <c r="M25" s="32" t="s">
         <v>49</v>
       </c>
       <c r="N25" s="33"/>
@@ -2814,27 +2829,27 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="34">
         <v>44754</v>
       </c>
       <c r="D26" s="28"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="35" t="s">
         <v>45</v>
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J26" s="28"/>
-      <c r="K26" s="31">
+      <c r="K26" s="36">
         <v>1</v>
       </c>
       <c r="L26" s="28"/>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="37" t="s">
         <v>50</v>
       </c>
       <c r="N26" s="33"/>
@@ -2846,27 +2861,27 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="27">
         <v>44754</v>
       </c>
       <c r="D27" s="28"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="29" t="s">
         <v>51</v>
       </c>
       <c r="G27" s="30"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="35" t="s">
+      <c r="I27" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="28"/>
-      <c r="K27" s="36">
+      <c r="K27" s="31">
         <v>94</v>
       </c>
       <c r="L27" s="28"/>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="32" t="s">
         <v>52</v>
       </c>
       <c r="N27" s="33"/>
@@ -2878,27 +2893,27 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="34">
         <v>44754</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="35" t="s">
         <v>45</v>
       </c>
       <c r="G28" s="30"/>
       <c r="H28" s="28"/>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J28" s="28"/>
-      <c r="K28" s="31">
+      <c r="K28" s="36">
         <v>9</v>
       </c>
       <c r="L28" s="28"/>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="37" t="s">
         <v>54</v>
       </c>
       <c r="N28" s="33"/>
@@ -2910,27 +2925,27 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="27">
         <v>44754</v>
       </c>
       <c r="D29" s="28"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="29" t="s">
         <v>45</v>
       </c>
       <c r="G29" s="30"/>
       <c r="H29" s="28"/>
-      <c r="I29" s="35" t="s">
+      <c r="I29" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J29" s="28"/>
-      <c r="K29" s="36">
+      <c r="K29" s="31">
         <v>6</v>
       </c>
       <c r="L29" s="28"/>
-      <c r="M29" s="37" t="s">
+      <c r="M29" s="32" t="s">
         <v>55</v>
       </c>
       <c r="N29" s="33"/>
@@ -2942,27 +2957,27 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="34">
         <v>44754</v>
       </c>
       <c r="D30" s="28"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="35" t="s">
         <v>45</v>
       </c>
       <c r="G30" s="30"/>
       <c r="H30" s="28"/>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J30" s="28"/>
-      <c r="K30" s="31">
+      <c r="K30" s="36">
         <v>18</v>
       </c>
       <c r="L30" s="28"/>
-      <c r="M30" s="32" t="s">
+      <c r="M30" s="37" t="s">
         <v>57</v>
       </c>
       <c r="N30" s="33"/>
@@ -2974,27 +2989,27 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="27">
         <v>44755</v>
       </c>
       <c r="D31" s="28"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="29" t="s">
         <v>45</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="28"/>
-      <c r="I31" s="35" t="s">
+      <c r="I31" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J31" s="28"/>
-      <c r="K31" s="36">
+      <c r="K31" s="31">
         <v>76</v>
       </c>
       <c r="L31" s="28"/>
-      <c r="M31" s="37" t="s">
+      <c r="M31" s="32" t="s">
         <v>58</v>
       </c>
       <c r="N31" s="33"/>
@@ -3006,27 +3021,27 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="34">
         <v>44755</v>
       </c>
       <c r="D32" s="28"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="35" t="s">
         <v>45</v>
       </c>
       <c r="G32" s="30"/>
       <c r="H32" s="28"/>
-      <c r="I32" s="29" t="s">
+      <c r="I32" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J32" s="28"/>
-      <c r="K32" s="31">
+      <c r="K32" s="36">
         <v>1</v>
       </c>
       <c r="L32" s="28"/>
-      <c r="M32" s="32" t="s">
+      <c r="M32" s="37" t="s">
         <v>59</v>
       </c>
       <c r="N32" s="33"/>
@@ -3038,27 +3053,27 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="27">
         <v>44755</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="29" t="s">
         <v>45</v>
       </c>
       <c r="G33" s="30"/>
       <c r="H33" s="28"/>
-      <c r="I33" s="35" t="s">
+      <c r="I33" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J33" s="28"/>
-      <c r="K33" s="36">
+      <c r="K33" s="31">
         <v>27</v>
       </c>
       <c r="L33" s="28"/>
-      <c r="M33" s="37" t="s">
+      <c r="M33" s="32" t="s">
         <v>61</v>
       </c>
       <c r="N33" s="33"/>
@@ -3070,27 +3085,27 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="34">
         <v>44755</v>
       </c>
       <c r="D34" s="28"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="35" t="s">
         <v>45</v>
       </c>
       <c r="G34" s="30"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J34" s="28"/>
-      <c r="K34" s="31">
+      <c r="K34" s="36">
         <v>2</v>
       </c>
       <c r="L34" s="28"/>
-      <c r="M34" s="32" t="s">
+      <c r="M34" s="37" t="s">
         <v>62</v>
       </c>
       <c r="N34" s="33"/>
@@ -3102,27 +3117,27 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="27">
         <v>44756</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G35" s="30"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="35" t="s">
+      <c r="I35" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J35" s="28"/>
-      <c r="K35" s="36">
+      <c r="K35" s="31">
         <v>54</v>
       </c>
       <c r="L35" s="28"/>
-      <c r="M35" s="37" t="s">
+      <c r="M35" s="32" t="s">
         <v>64</v>
       </c>
       <c r="N35" s="33"/>
@@ -3134,27 +3149,27 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="34">
         <v>44756</v>
       </c>
       <c r="D36" s="28"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="35" t="s">
         <v>63</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="28"/>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="28"/>
-      <c r="K36" s="31">
+      <c r="K36" s="36">
         <v>105</v>
       </c>
       <c r="L36" s="28"/>
-      <c r="M36" s="32" t="s">
+      <c r="M36" s="37" t="s">
         <v>65</v>
       </c>
       <c r="N36" s="33"/>
@@ -3166,27 +3181,27 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="27">
         <v>44756</v>
       </c>
       <c r="D37" s="28"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="F37" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G37" s="30"/>
       <c r="H37" s="28"/>
-      <c r="I37" s="35" t="s">
+      <c r="I37" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="28"/>
-      <c r="K37" s="36">
+      <c r="K37" s="31">
         <v>71</v>
       </c>
       <c r="L37" s="28"/>
-      <c r="M37" s="37" t="s">
+      <c r="M37" s="32" t="s">
         <v>66</v>
       </c>
       <c r="N37" s="33"/>
@@ -3198,27 +3213,27 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="34">
         <v>44756</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="35" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="30"/>
       <c r="H38" s="28"/>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="28"/>
-      <c r="K38" s="31">
+      <c r="K38" s="36">
         <v>125</v>
       </c>
       <c r="L38" s="28"/>
-      <c r="M38" s="32" t="s">
+      <c r="M38" s="37" t="s">
         <v>68</v>
       </c>
       <c r="N38" s="33"/>
@@ -3230,27 +3245,27 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="27">
         <v>44756</v>
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="F39" s="29" t="s">
         <v>70</v>
       </c>
       <c r="G39" s="30"/>
       <c r="H39" s="28"/>
-      <c r="I39" s="35" t="s">
+      <c r="I39" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="28"/>
-      <c r="K39" s="36">
+      <c r="K39" s="31">
         <v>55</v>
       </c>
       <c r="L39" s="28"/>
-      <c r="M39" s="37" t="s">
+      <c r="M39" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N39" s="33"/>
@@ -3262,27 +3277,27 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="34">
         <v>44756</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="35" t="s">
         <v>63</v>
       </c>
       <c r="G40" s="30"/>
       <c r="H40" s="28"/>
-      <c r="I40" s="29" t="s">
+      <c r="I40" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="28"/>
-      <c r="K40" s="31">
+      <c r="K40" s="36">
         <v>176</v>
       </c>
       <c r="L40" s="28"/>
-      <c r="M40" s="32" t="s">
+      <c r="M40" s="37" t="s">
         <v>72</v>
       </c>
       <c r="N40" s="33"/>
@@ -3294,27 +3309,27 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="27">
         <v>44757</v>
       </c>
       <c r="D41" s="28"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="35" t="s">
+      <c r="F41" s="29" t="s">
         <v>73</v>
       </c>
       <c r="G41" s="30"/>
       <c r="H41" s="28"/>
-      <c r="I41" s="35" t="s">
+      <c r="I41" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="28"/>
-      <c r="K41" s="36">
+      <c r="K41" s="31">
         <v>58</v>
       </c>
       <c r="L41" s="28"/>
-      <c r="M41" s="37" t="s">
+      <c r="M41" s="32" t="s">
         <v>74</v>
       </c>
       <c r="N41" s="33"/>
@@ -3326,27 +3341,27 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="34">
         <v>44757</v>
       </c>
       <c r="D42" s="28"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="35" t="s">
         <v>75</v>
       </c>
       <c r="G42" s="30"/>
       <c r="H42" s="28"/>
-      <c r="I42" s="29" t="s">
+      <c r="I42" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="28"/>
-      <c r="K42" s="31">
+      <c r="K42" s="36">
         <v>180</v>
       </c>
       <c r="L42" s="28"/>
-      <c r="M42" s="32" t="s">
+      <c r="M42" s="37" t="s">
         <v>76</v>
       </c>
       <c r="N42" s="33"/>
@@ -3358,27 +3373,27 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="27">
         <v>44760</v>
       </c>
       <c r="D43" s="28"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="35" t="s">
+      <c r="F43" s="29" t="s">
         <v>77</v>
       </c>
       <c r="G43" s="30"/>
       <c r="H43" s="28"/>
-      <c r="I43" s="35" t="s">
+      <c r="I43" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J43" s="28"/>
-      <c r="K43" s="36">
+      <c r="K43" s="31">
         <v>142</v>
       </c>
       <c r="L43" s="28"/>
-      <c r="M43" s="37" t="s">
+      <c r="M43" s="32" t="s">
         <v>78</v>
       </c>
       <c r="N43" s="33"/>
@@ -3390,27 +3405,27 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="34">
         <v>44760</v>
       </c>
       <c r="D44" s="28"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="29" t="s">
+      <c r="F44" s="35" t="s">
         <v>80</v>
       </c>
       <c r="G44" s="30"/>
       <c r="H44" s="28"/>
-      <c r="I44" s="29" t="s">
+      <c r="I44" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J44" s="28"/>
-      <c r="K44" s="31">
+      <c r="K44" s="36">
         <v>153</v>
       </c>
       <c r="L44" s="28"/>
-      <c r="M44" s="32" t="s">
+      <c r="M44" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N44" s="33"/>
@@ -3422,27 +3437,27 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="27">
         <v>44761</v>
       </c>
       <c r="D45" s="28"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="29" t="s">
         <v>82</v>
       </c>
       <c r="G45" s="30"/>
       <c r="H45" s="28"/>
-      <c r="I45" s="35" t="s">
+      <c r="I45" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="28"/>
-      <c r="K45" s="36">
+      <c r="K45" s="31">
         <v>12</v>
       </c>
       <c r="L45" s="28"/>
-      <c r="M45" s="37" t="s">
+      <c r="M45" s="32" t="s">
         <v>83</v>
       </c>
       <c r="N45" s="33"/>
@@ -3454,27 +3469,27 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="34">
         <v>44761</v>
       </c>
       <c r="D46" s="28"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="35" t="s">
         <v>84</v>
       </c>
       <c r="G46" s="30"/>
       <c r="H46" s="28"/>
-      <c r="I46" s="29" t="s">
+      <c r="I46" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="28"/>
-      <c r="K46" s="31">
+      <c r="K46" s="36">
         <v>27</v>
       </c>
       <c r="L46" s="28"/>
-      <c r="M46" s="32" t="s">
+      <c r="M46" s="37" t="s">
         <v>85</v>
       </c>
       <c r="N46" s="33"/>
@@ -3486,27 +3501,27 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="27">
         <v>44761</v>
       </c>
       <c r="D47" s="28"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="29" t="s">
         <v>84</v>
       </c>
       <c r="G47" s="30"/>
       <c r="H47" s="28"/>
-      <c r="I47" s="35" t="s">
+      <c r="I47" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J47" s="28"/>
-      <c r="K47" s="36">
+      <c r="K47" s="31">
         <v>51</v>
       </c>
       <c r="L47" s="28"/>
-      <c r="M47" s="37" t="s">
+      <c r="M47" s="32" t="s">
         <v>86</v>
       </c>
       <c r="N47" s="33"/>
@@ -3518,27 +3533,27 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="34">
         <v>44761</v>
       </c>
       <c r="D48" s="28"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="35" t="s">
         <v>87</v>
       </c>
       <c r="G48" s="30"/>
       <c r="H48" s="28"/>
-      <c r="I48" s="29" t="s">
+      <c r="I48" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J48" s="28"/>
-      <c r="K48" s="31">
+      <c r="K48" s="36">
         <v>69</v>
       </c>
       <c r="L48" s="28"/>
-      <c r="M48" s="32" t="s">
+      <c r="M48" s="37" t="s">
         <v>88</v>
       </c>
       <c r="N48" s="33"/>
@@ -3550,27 +3565,27 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="27">
         <v>44762</v>
       </c>
       <c r="D49" s="28"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="29" t="s">
         <v>89</v>
       </c>
       <c r="G49" s="30"/>
       <c r="H49" s="28"/>
-      <c r="I49" s="35" t="s">
+      <c r="I49" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J49" s="28"/>
-      <c r="K49" s="36">
+      <c r="K49" s="31">
         <v>104</v>
       </c>
       <c r="L49" s="28"/>
-      <c r="M49" s="37" t="s">
+      <c r="M49" s="32" t="s">
         <v>90</v>
       </c>
       <c r="N49" s="33"/>
@@ -3582,27 +3597,27 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="34">
         <v>44762</v>
       </c>
       <c r="D50" s="28"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="35" t="s">
         <v>91</v>
       </c>
       <c r="G50" s="30"/>
       <c r="H50" s="28"/>
-      <c r="I50" s="29" t="s">
+      <c r="I50" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="28"/>
-      <c r="K50" s="31">
+      <c r="K50" s="36">
         <v>19</v>
       </c>
       <c r="L50" s="28"/>
-      <c r="M50" s="32" t="s">
+      <c r="M50" s="37" t="s">
         <v>92</v>
       </c>
       <c r="N50" s="33"/>
@@ -3614,27 +3629,27 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="27">
         <v>44762</v>
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="35" t="s">
+      <c r="F51" s="29" t="s">
         <v>94</v>
       </c>
       <c r="G51" s="30"/>
       <c r="H51" s="28"/>
-      <c r="I51" s="35" t="s">
+      <c r="I51" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J51" s="28"/>
-      <c r="K51" s="36">
+      <c r="K51" s="31">
         <v>80</v>
       </c>
       <c r="L51" s="28"/>
-      <c r="M51" s="37" t="s">
+      <c r="M51" s="32" t="s">
         <v>95</v>
       </c>
       <c r="N51" s="33"/>
@@ -3646,27 +3661,27 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="34">
         <v>44763</v>
       </c>
       <c r="D52" s="28"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="35" t="s">
         <v>97</v>
       </c>
       <c r="G52" s="30"/>
       <c r="H52" s="28"/>
-      <c r="I52" s="29" t="s">
+      <c r="I52" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="28"/>
-      <c r="K52" s="31">
+      <c r="K52" s="36">
         <v>99</v>
       </c>
       <c r="L52" s="28"/>
-      <c r="M52" s="32" t="s">
+      <c r="M52" s="37" t="s">
         <v>98</v>
       </c>
       <c r="N52" s="33"/>
@@ -3678,27 +3693,27 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="27">
         <v>44763</v>
       </c>
       <c r="D53" s="28"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="29" t="s">
         <v>97</v>
       </c>
       <c r="G53" s="30"/>
       <c r="H53" s="28"/>
-      <c r="I53" s="35" t="s">
+      <c r="I53" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="28"/>
-      <c r="K53" s="36">
+      <c r="K53" s="31">
         <v>60</v>
       </c>
       <c r="L53" s="28"/>
-      <c r="M53" s="37" t="s">
+      <c r="M53" s="32" t="s">
         <v>99</v>
       </c>
       <c r="N53" s="33"/>
@@ -3710,27 +3725,27 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="34">
         <v>44763</v>
       </c>
       <c r="D54" s="28"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="35" t="s">
         <v>97</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="28"/>
-      <c r="I54" s="29" t="s">
+      <c r="I54" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="28"/>
-      <c r="K54" s="31">
+      <c r="K54" s="36">
         <v>4</v>
       </c>
       <c r="L54" s="28"/>
-      <c r="M54" s="32" t="s">
+      <c r="M54" s="37" t="s">
         <v>100</v>
       </c>
       <c r="N54" s="33"/>
@@ -3742,27 +3757,27 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="27">
         <v>44763</v>
       </c>
       <c r="D55" s="28"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="29" t="s">
         <v>97</v>
       </c>
       <c r="G55" s="30"/>
       <c r="H55" s="28"/>
-      <c r="I55" s="35" t="s">
+      <c r="I55" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="28"/>
-      <c r="K55" s="36">
+      <c r="K55" s="31">
         <v>26</v>
       </c>
       <c r="L55" s="28"/>
-      <c r="M55" s="37" t="s">
+      <c r="M55" s="32" t="s">
         <v>101</v>
       </c>
       <c r="N55" s="33"/>
@@ -3774,27 +3789,27 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="34">
         <v>44763</v>
       </c>
       <c r="D56" s="28"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="35" t="s">
         <v>103</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="28"/>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="28"/>
-      <c r="K56" s="31">
+      <c r="K56" s="36">
         <v>30</v>
       </c>
       <c r="L56" s="28"/>
-      <c r="M56" s="32" t="s">
+      <c r="M56" s="37" t="s">
         <v>104</v>
       </c>
       <c r="N56" s="33"/>
@@ -3806,27 +3821,27 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="27">
         <v>44763</v>
       </c>
       <c r="D57" s="28"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="29" t="s">
         <v>103</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="28"/>
-      <c r="I57" s="35" t="s">
+      <c r="I57" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="28"/>
-      <c r="K57" s="36">
+      <c r="K57" s="31">
         <v>2</v>
       </c>
       <c r="L57" s="28"/>
-      <c r="M57" s="37" t="s">
+      <c r="M57" s="32" t="s">
         <v>105</v>
       </c>
       <c r="N57" s="33"/>
@@ -3838,27 +3853,27 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="34">
         <v>44764</v>
       </c>
       <c r="D58" s="28"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="F58" s="35" t="s">
         <v>106</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="28"/>
-      <c r="I58" s="29" t="s">
+      <c r="I58" s="35" t="s">
         <v>107</v>
       </c>
       <c r="J58" s="28"/>
-      <c r="K58" s="31">
+      <c r="K58" s="36">
         <v>66</v>
       </c>
       <c r="L58" s="28"/>
-      <c r="M58" s="32" t="s">
+      <c r="M58" s="37" t="s">
         <v>108</v>
       </c>
       <c r="N58" s="33"/>
@@ -3870,27 +3885,27 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="27">
         <v>44764</v>
       </c>
       <c r="D59" s="28"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="29" t="s">
         <v>109</v>
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="28"/>
-      <c r="I59" s="35" t="s">
+      <c r="I59" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J59" s="28"/>
-      <c r="K59" s="36">
+      <c r="K59" s="31">
         <v>85</v>
       </c>
       <c r="L59" s="28"/>
-      <c r="M59" s="37" t="s">
+      <c r="M59" s="32" t="s">
         <v>110</v>
       </c>
       <c r="N59" s="33"/>
@@ -3902,27 +3917,27 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="34">
         <v>44764</v>
       </c>
       <c r="D60" s="28"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="35" t="s">
         <v>111</v>
       </c>
       <c r="G60" s="30"/>
       <c r="H60" s="28"/>
-      <c r="I60" s="29" t="s">
+      <c r="I60" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J60" s="28"/>
-      <c r="K60" s="31">
+      <c r="K60" s="36">
         <v>58</v>
       </c>
       <c r="L60" s="28"/>
-      <c r="M60" s="32" t="s">
+      <c r="M60" s="37" t="s">
         <v>112</v>
       </c>
       <c r="N60" s="33"/>
@@ -3934,27 +3949,27 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="27">
         <v>44764</v>
       </c>
       <c r="D61" s="28"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="35" t="s">
+      <c r="F61" s="29" t="s">
         <v>114</v>
       </c>
       <c r="G61" s="30"/>
       <c r="H61" s="28"/>
-      <c r="I61" s="35" t="s">
+      <c r="I61" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="28"/>
-      <c r="K61" s="36">
+      <c r="K61" s="31">
         <v>80</v>
       </c>
       <c r="L61" s="28"/>
-      <c r="M61" s="37" t="s">
+      <c r="M61" s="32" t="s">
         <v>115</v>
       </c>
       <c r="N61" s="33"/>
@@ -3966,27 +3981,27 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="34">
         <v>44764</v>
       </c>
       <c r="D62" s="28"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="35" t="s">
         <v>117</v>
       </c>
       <c r="G62" s="30"/>
       <c r="H62" s="28"/>
-      <c r="I62" s="29" t="s">
+      <c r="I62" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="28"/>
-      <c r="K62" s="31">
+      <c r="K62" s="36">
         <v>55</v>
       </c>
       <c r="L62" s="28"/>
-      <c r="M62" s="32" t="s">
+      <c r="M62" s="37" t="s">
         <v>118</v>
       </c>
       <c r="N62" s="33"/>
@@ -3998,27 +4013,27 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="27">
         <v>44764</v>
       </c>
       <c r="D63" s="28"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="35" t="s">
+      <c r="F63" s="29" t="s">
         <v>119</v>
       </c>
       <c r="G63" s="30"/>
       <c r="H63" s="28"/>
-      <c r="I63" s="35" t="s">
+      <c r="I63" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J63" s="28"/>
-      <c r="K63" s="36">
+      <c r="K63" s="31">
         <v>14</v>
       </c>
       <c r="L63" s="28"/>
-      <c r="M63" s="37" t="s">
+      <c r="M63" s="32" t="s">
         <v>120</v>
       </c>
       <c r="N63" s="33"/>
@@ -4030,27 +4045,27 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="34">
         <v>44764</v>
       </c>
       <c r="D64" s="28"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="29" t="s">
+      <c r="F64" s="35" t="s">
         <v>121</v>
       </c>
       <c r="G64" s="30"/>
       <c r="H64" s="28"/>
-      <c r="I64" s="29" t="s">
+      <c r="I64" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J64" s="28"/>
-      <c r="K64" s="31">
+      <c r="K64" s="36">
         <v>90</v>
       </c>
       <c r="L64" s="28"/>
-      <c r="M64" s="32" t="s">
+      <c r="M64" s="37" t="s">
         <v>122</v>
       </c>
       <c r="N64" s="33"/>
@@ -4062,27 +4077,27 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="27">
         <v>44767</v>
       </c>
       <c r="D65" s="28"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="35" t="s">
+      <c r="F65" s="29" t="s">
         <v>123</v>
       </c>
       <c r="G65" s="30"/>
       <c r="H65" s="28"/>
-      <c r="I65" s="35" t="s">
+      <c r="I65" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J65" s="28"/>
-      <c r="K65" s="36">
+      <c r="K65" s="31">
         <v>331</v>
       </c>
       <c r="L65" s="28"/>
-      <c r="M65" s="37" t="s">
+      <c r="M65" s="32" t="s">
         <v>124</v>
       </c>
       <c r="N65" s="33"/>
@@ -4094,27 +4109,27 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="34">
         <v>44768</v>
       </c>
       <c r="D66" s="28"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="29" t="s">
+      <c r="F66" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G66" s="30"/>
       <c r="H66" s="28"/>
-      <c r="I66" s="29" t="s">
+      <c r="I66" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="28"/>
-      <c r="K66" s="31">
+      <c r="K66" s="36">
         <v>52</v>
       </c>
       <c r="L66" s="28"/>
-      <c r="M66" s="32" t="s">
+      <c r="M66" s="37" t="s">
         <v>127</v>
       </c>
       <c r="N66" s="33"/>
@@ -4126,27 +4141,27 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="27">
         <v>44768</v>
       </c>
       <c r="D67" s="28"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="29" t="s">
         <v>128</v>
       </c>
       <c r="G67" s="30"/>
       <c r="H67" s="28"/>
-      <c r="I67" s="35" t="s">
+      <c r="I67" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J67" s="28"/>
-      <c r="K67" s="36">
+      <c r="K67" s="31">
         <v>9</v>
       </c>
       <c r="L67" s="28"/>
-      <c r="M67" s="37" t="s">
+      <c r="M67" s="32" t="s">
         <v>129</v>
       </c>
       <c r="N67" s="33"/>
@@ -4158,27 +4173,27 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="34">
         <v>44768</v>
       </c>
       <c r="D68" s="28"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="35" t="s">
         <v>130</v>
       </c>
       <c r="G68" s="30"/>
       <c r="H68" s="28"/>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="28"/>
-      <c r="K68" s="31">
+      <c r="K68" s="36">
         <v>78</v>
       </c>
       <c r="L68" s="28"/>
-      <c r="M68" s="32" t="s">
+      <c r="M68" s="37" t="s">
         <v>131</v>
       </c>
       <c r="N68" s="33"/>
@@ -4190,27 +4205,27 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="27">
         <v>44769</v>
       </c>
       <c r="D69" s="28"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="35" t="s">
+      <c r="F69" s="29" t="s">
         <v>132</v>
       </c>
       <c r="G69" s="30"/>
       <c r="H69" s="28"/>
-      <c r="I69" s="35" t="s">
+      <c r="I69" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="28"/>
-      <c r="K69" s="36">
+      <c r="K69" s="31">
         <v>48</v>
       </c>
       <c r="L69" s="28"/>
-      <c r="M69" s="37" t="s">
+      <c r="M69" s="32" t="s">
         <v>133</v>
       </c>
       <c r="N69" s="33"/>
@@ -4222,27 +4237,27 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="34">
         <v>44769</v>
       </c>
       <c r="D70" s="28"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="35" t="s">
         <v>134</v>
       </c>
       <c r="G70" s="30"/>
       <c r="H70" s="28"/>
-      <c r="I70" s="29" t="s">
+      <c r="I70" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J70" s="28"/>
-      <c r="K70" s="31">
+      <c r="K70" s="36">
         <v>50</v>
       </c>
       <c r="L70" s="28"/>
-      <c r="M70" s="32" t="s">
+      <c r="M70" s="37" t="s">
         <v>135</v>
       </c>
       <c r="N70" s="33"/>
@@ -4254,27 +4269,27 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="27">
         <v>44769</v>
       </c>
       <c r="D71" s="28"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="35" t="s">
+      <c r="F71" s="29" t="s">
         <v>132</v>
       </c>
       <c r="G71" s="30"/>
       <c r="H71" s="28"/>
-      <c r="I71" s="35" t="s">
+      <c r="I71" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J71" s="28"/>
-      <c r="K71" s="36">
+      <c r="K71" s="31">
         <v>736</v>
       </c>
       <c r="L71" s="28"/>
-      <c r="M71" s="37" t="s">
+      <c r="M71" s="32" t="s">
         <v>136</v>
       </c>
       <c r="N71" s="33"/>
@@ -4286,27 +4301,27 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="34">
         <v>44770</v>
       </c>
       <c r="D72" s="28"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="35" t="s">
         <v>137</v>
       </c>
       <c r="G72" s="30"/>
       <c r="H72" s="28"/>
-      <c r="I72" s="29" t="s">
+      <c r="I72" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="28"/>
-      <c r="K72" s="31">
+      <c r="K72" s="36">
         <v>74</v>
       </c>
       <c r="L72" s="28"/>
-      <c r="M72" s="32" t="s">
+      <c r="M72" s="37" t="s">
         <v>138</v>
       </c>
       <c r="N72" s="33"/>
@@ -4318,27 +4333,27 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C73" s="27">
         <v>44770</v>
       </c>
       <c r="D73" s="28"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="35" t="s">
+      <c r="F73" s="29" t="s">
         <v>139</v>
       </c>
       <c r="G73" s="30"/>
       <c r="H73" s="28"/>
-      <c r="I73" s="35" t="s">
+      <c r="I73" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J73" s="28"/>
-      <c r="K73" s="36">
+      <c r="K73" s="31">
         <v>25</v>
       </c>
       <c r="L73" s="28"/>
-      <c r="M73" s="37" t="s">
+      <c r="M73" s="32" t="s">
         <v>140</v>
       </c>
       <c r="N73" s="33"/>
@@ -4350,27 +4365,27 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="34">
         <v>44770</v>
       </c>
       <c r="D74" s="28"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="35" t="s">
         <v>139</v>
       </c>
       <c r="G74" s="30"/>
       <c r="H74" s="28"/>
-      <c r="I74" s="29" t="s">
+      <c r="I74" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="28"/>
-      <c r="K74" s="31">
+      <c r="K74" s="36">
         <v>25</v>
       </c>
       <c r="L74" s="28"/>
-      <c r="M74" s="32" t="s">
+      <c r="M74" s="37" t="s">
         <v>140</v>
       </c>
       <c r="N74" s="33"/>
@@ -4382,27 +4397,27 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="34">
+      <c r="C75" s="27">
         <v>44770</v>
       </c>
       <c r="D75" s="28"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="29" t="s">
         <v>141</v>
       </c>
       <c r="G75" s="30"/>
       <c r="H75" s="28"/>
-      <c r="I75" s="35" t="s">
+      <c r="I75" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J75" s="28"/>
-      <c r="K75" s="36">
+      <c r="K75" s="31">
         <v>225</v>
       </c>
       <c r="L75" s="28"/>
-      <c r="M75" s="37" t="s">
+      <c r="M75" s="32" t="s">
         <v>142</v>
       </c>
       <c r="N75" s="33"/>
@@ -4414,27 +4429,27 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="34">
         <v>44770</v>
       </c>
       <c r="D76" s="28"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F76" s="35" t="s">
         <v>143</v>
       </c>
       <c r="G76" s="30"/>
       <c r="H76" s="28"/>
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J76" s="28"/>
-      <c r="K76" s="31">
+      <c r="K76" s="36">
         <v>136</v>
       </c>
       <c r="L76" s="28"/>
-      <c r="M76" s="32" t="s">
+      <c r="M76" s="37" t="s">
         <v>144</v>
       </c>
       <c r="N76" s="33"/>
@@ -4446,27 +4461,27 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="34">
+      <c r="C77" s="27">
         <v>44774</v>
       </c>
       <c r="D77" s="28"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="35" t="s">
+      <c r="F77" s="29" t="s">
         <v>145</v>
       </c>
       <c r="G77" s="30"/>
       <c r="H77" s="28"/>
-      <c r="I77" s="35" t="s">
+      <c r="I77" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J77" s="28"/>
-      <c r="K77" s="36">
+      <c r="K77" s="31">
         <v>82</v>
       </c>
       <c r="L77" s="28"/>
-      <c r="M77" s="37" t="s">
+      <c r="M77" s="32" t="s">
         <v>146</v>
       </c>
       <c r="N77" s="33"/>
@@ -4478,27 +4493,27 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="34">
         <v>44774</v>
       </c>
       <c r="D78" s="28"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="35" t="s">
         <v>147</v>
       </c>
       <c r="G78" s="30"/>
       <c r="H78" s="28"/>
-      <c r="I78" s="29" t="s">
+      <c r="I78" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="28"/>
-      <c r="K78" s="31">
+      <c r="K78" s="36">
         <v>28</v>
       </c>
       <c r="L78" s="28"/>
-      <c r="M78" s="32" t="s">
+      <c r="M78" s="37" t="s">
         <v>148</v>
       </c>
       <c r="N78" s="33"/>
@@ -4510,27 +4525,27 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="34">
+      <c r="C79" s="27">
         <v>44776</v>
       </c>
       <c r="D79" s="28"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="35" t="s">
+      <c r="F79" s="29" t="s">
         <v>149</v>
       </c>
       <c r="G79" s="30"/>
       <c r="H79" s="28"/>
-      <c r="I79" s="35" t="s">
+      <c r="I79" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="28"/>
-      <c r="K79" s="36">
+      <c r="K79" s="31">
         <v>57</v>
       </c>
       <c r="L79" s="28"/>
-      <c r="M79" s="37" t="s">
+      <c r="M79" s="32" t="s">
         <v>150</v>
       </c>
       <c r="N79" s="33"/>
@@ -4542,27 +4557,27 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="34">
         <v>44778</v>
       </c>
       <c r="D80" s="28"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="29" t="s">
+      <c r="F80" s="35" t="s">
         <v>151</v>
       </c>
       <c r="G80" s="30"/>
       <c r="H80" s="28"/>
-      <c r="I80" s="29" t="s">
+      <c r="I80" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J80" s="28"/>
-      <c r="K80" s="31">
+      <c r="K80" s="36">
         <v>133</v>
       </c>
       <c r="L80" s="28"/>
-      <c r="M80" s="32" t="s">
+      <c r="M80" s="37" t="s">
         <v>152</v>
       </c>
       <c r="N80" s="33"/>
@@ -4574,27 +4589,27 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="34">
+      <c r="C81" s="27">
         <v>44778</v>
       </c>
       <c r="D81" s="28"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="29" t="s">
         <v>153</v>
       </c>
       <c r="G81" s="30"/>
       <c r="H81" s="28"/>
-      <c r="I81" s="35" t="s">
+      <c r="I81" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="28"/>
-      <c r="K81" s="36">
+      <c r="K81" s="31">
         <v>146</v>
       </c>
       <c r="L81" s="28"/>
-      <c r="M81" s="37" t="s">
+      <c r="M81" s="32" t="s">
         <v>154</v>
       </c>
       <c r="N81" s="33"/>
@@ -4606,27 +4621,27 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="34">
         <v>44778</v>
       </c>
       <c r="D82" s="28"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="35" t="s">
         <v>156</v>
       </c>
       <c r="G82" s="30"/>
       <c r="H82" s="28"/>
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J82" s="28"/>
-      <c r="K82" s="31">
+      <c r="K82" s="36">
         <v>68</v>
       </c>
       <c r="L82" s="28"/>
-      <c r="M82" s="32" t="s">
+      <c r="M82" s="37" t="s">
         <v>157</v>
       </c>
       <c r="N82" s="33"/>
@@ -4638,27 +4653,27 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="34">
+      <c r="C83" s="27">
         <v>44781</v>
       </c>
       <c r="D83" s="28"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="29" t="s">
         <v>158</v>
       </c>
       <c r="G83" s="30"/>
       <c r="H83" s="28"/>
-      <c r="I83" s="35" t="s">
+      <c r="I83" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="28"/>
-      <c r="K83" s="36">
+      <c r="K83" s="31">
         <v>111</v>
       </c>
       <c r="L83" s="28"/>
-      <c r="M83" s="37" t="s">
+      <c r="M83" s="32" t="s">
         <v>159</v>
       </c>
       <c r="N83" s="33"/>
@@ -4670,27 +4685,27 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="34">
         <v>44781</v>
       </c>
       <c r="D84" s="28"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="29" t="s">
+      <c r="F84" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G84" s="30"/>
       <c r="H84" s="28"/>
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J84" s="28"/>
-      <c r="K84" s="31">
+      <c r="K84" s="36">
         <v>77</v>
       </c>
       <c r="L84" s="28"/>
-      <c r="M84" s="32" t="s">
+      <c r="M84" s="37" t="s">
         <v>160</v>
       </c>
       <c r="N84" s="33"/>
@@ -4702,27 +4717,27 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="27">
         <v>44781</v>
       </c>
       <c r="D85" s="28"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="35" t="s">
+      <c r="F85" s="29" t="s">
         <v>158</v>
       </c>
       <c r="G85" s="30"/>
       <c r="H85" s="28"/>
-      <c r="I85" s="35" t="s">
+      <c r="I85" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J85" s="28"/>
-      <c r="K85" s="36">
+      <c r="K85" s="31">
         <v>20</v>
       </c>
       <c r="L85" s="28"/>
-      <c r="M85" s="37" t="s">
+      <c r="M85" s="32" t="s">
         <v>161</v>
       </c>
       <c r="N85" s="33"/>
@@ -4734,27 +4749,27 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="34">
         <v>44781</v>
       </c>
       <c r="D86" s="28"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="29" t="s">
+      <c r="F86" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G86" s="30"/>
       <c r="H86" s="28"/>
-      <c r="I86" s="29" t="s">
+      <c r="I86" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J86" s="28"/>
-      <c r="K86" s="31">
+      <c r="K86" s="36">
         <v>25</v>
       </c>
       <c r="L86" s="28"/>
-      <c r="M86" s="32" t="s">
+      <c r="M86" s="37" t="s">
         <v>162</v>
       </c>
       <c r="N86" s="33"/>
@@ -4766,27 +4781,27 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C87" s="27">
         <v>44781</v>
       </c>
       <c r="D87" s="28"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="35" t="s">
+      <c r="F87" s="29" t="s">
         <v>158</v>
       </c>
       <c r="G87" s="30"/>
       <c r="H87" s="28"/>
-      <c r="I87" s="35" t="s">
+      <c r="I87" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="28"/>
-      <c r="K87" s="36">
+      <c r="K87" s="31">
         <v>21</v>
       </c>
       <c r="L87" s="28"/>
-      <c r="M87" s="37" t="s">
+      <c r="M87" s="32" t="s">
         <v>163</v>
       </c>
       <c r="N87" s="33"/>
@@ -4798,27 +4813,27 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="34">
         <v>44781</v>
       </c>
       <c r="D88" s="28"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="29" t="s">
+      <c r="F88" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G88" s="30"/>
       <c r="H88" s="28"/>
-      <c r="I88" s="29" t="s">
+      <c r="I88" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J88" s="28"/>
-      <c r="K88" s="31">
+      <c r="K88" s="36">
         <v>86</v>
       </c>
       <c r="L88" s="28"/>
-      <c r="M88" s="32" t="s">
+      <c r="M88" s="37" t="s">
         <v>164</v>
       </c>
       <c r="N88" s="33"/>
@@ -4830,27 +4845,27 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="27">
         <v>44781</v>
       </c>
       <c r="D89" s="28"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="35" t="s">
+      <c r="F89" s="29" t="s">
         <v>158</v>
       </c>
       <c r="G89" s="30"/>
       <c r="H89" s="28"/>
-      <c r="I89" s="35" t="s">
+      <c r="I89" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J89" s="28"/>
-      <c r="K89" s="36">
+      <c r="K89" s="31">
         <v>9</v>
       </c>
       <c r="L89" s="28"/>
-      <c r="M89" s="37" t="s">
+      <c r="M89" s="32" t="s">
         <v>165</v>
       </c>
       <c r="N89" s="33"/>
@@ -4862,27 +4877,27 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="34">
         <v>44781</v>
       </c>
       <c r="D90" s="28"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="29" t="s">
+      <c r="F90" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G90" s="30"/>
       <c r="H90" s="28"/>
-      <c r="I90" s="29" t="s">
+      <c r="I90" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J90" s="28"/>
-      <c r="K90" s="31">
+      <c r="K90" s="36">
         <v>2</v>
       </c>
       <c r="L90" s="28"/>
-      <c r="M90" s="32" t="s">
+      <c r="M90" s="37" t="s">
         <v>166</v>
       </c>
       <c r="N90" s="33"/>
@@ -4894,27 +4909,27 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="27">
         <v>44781</v>
       </c>
       <c r="D91" s="28"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="35" t="s">
+      <c r="F91" s="29" t="s">
         <v>167</v>
       </c>
       <c r="G91" s="30"/>
       <c r="H91" s="28"/>
-      <c r="I91" s="35" t="s">
+      <c r="I91" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J91" s="28"/>
-      <c r="K91" s="36">
+      <c r="K91" s="31">
         <v>73</v>
       </c>
       <c r="L91" s="28"/>
-      <c r="M91" s="37" t="s">
+      <c r="M91" s="32" t="s">
         <v>169</v>
       </c>
       <c r="N91" s="33"/>
@@ -4926,27 +4941,27 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="34">
         <v>44782</v>
       </c>
       <c r="D92" s="28"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="35" t="s">
         <v>170</v>
       </c>
       <c r="G92" s="30"/>
       <c r="H92" s="28"/>
-      <c r="I92" s="29" t="s">
+      <c r="I92" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J92" s="28"/>
-      <c r="K92" s="31">
+      <c r="K92" s="36">
         <v>33</v>
       </c>
       <c r="L92" s="28"/>
-      <c r="M92" s="32" t="s">
+      <c r="M92" s="37" t="s">
         <v>171</v>
       </c>
       <c r="N92" s="33"/>
@@ -4958,27 +4973,27 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="34">
+      <c r="C93" s="27">
         <v>44782</v>
       </c>
       <c r="D93" s="28"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="35" t="s">
+      <c r="F93" s="29" t="s">
         <v>170</v>
       </c>
       <c r="G93" s="30"/>
       <c r="H93" s="28"/>
-      <c r="I93" s="35" t="s">
+      <c r="I93" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J93" s="28"/>
-      <c r="K93" s="36">
+      <c r="K93" s="31">
         <v>57</v>
       </c>
       <c r="L93" s="28"/>
-      <c r="M93" s="37" t="s">
+      <c r="M93" s="32" t="s">
         <v>172</v>
       </c>
       <c r="N93" s="33"/>
@@ -4990,27 +5005,27 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="34">
         <v>44782</v>
       </c>
       <c r="D94" s="28"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="29" t="s">
+      <c r="F94" s="35" t="s">
         <v>170</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="28"/>
-      <c r="I94" s="29" t="s">
+      <c r="I94" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J94" s="28"/>
-      <c r="K94" s="31">
+      <c r="K94" s="36">
         <v>16</v>
       </c>
       <c r="L94" s="28"/>
-      <c r="M94" s="32" t="s">
+      <c r="M94" s="37" t="s">
         <v>173</v>
       </c>
       <c r="N94" s="33"/>
@@ -5022,27 +5037,27 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="34">
+      <c r="C95" s="27">
         <v>44782</v>
       </c>
       <c r="D95" s="28"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="35" t="s">
+      <c r="F95" s="29" t="s">
         <v>170</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="28"/>
-      <c r="I95" s="35" t="s">
+      <c r="I95" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J95" s="28"/>
-      <c r="K95" s="36">
+      <c r="K95" s="31">
         <v>3</v>
       </c>
       <c r="L95" s="28"/>
-      <c r="M95" s="37" t="s">
+      <c r="M95" s="32" t="s">
         <v>174</v>
       </c>
       <c r="N95" s="33"/>
@@ -5054,27 +5069,27 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="34">
         <v>44782</v>
       </c>
       <c r="D96" s="28"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="29" t="s">
+      <c r="F96" s="35" t="s">
         <v>170</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="28"/>
-      <c r="I96" s="29" t="s">
+      <c r="I96" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J96" s="28"/>
-      <c r="K96" s="31">
+      <c r="K96" s="36">
         <v>15</v>
       </c>
       <c r="L96" s="28"/>
-      <c r="M96" s="32" t="s">
+      <c r="M96" s="37" t="s">
         <v>175</v>
       </c>
       <c r="N96" s="33"/>
@@ -5086,27 +5101,27 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="34">
+      <c r="C97" s="27">
         <v>44783</v>
       </c>
       <c r="D97" s="28"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="35" t="s">
+      <c r="F97" s="29" t="s">
         <v>176</v>
       </c>
       <c r="G97" s="30"/>
       <c r="H97" s="28"/>
-      <c r="I97" s="35" t="s">
+      <c r="I97" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J97" s="28"/>
-      <c r="K97" s="36">
+      <c r="K97" s="31">
         <v>64</v>
       </c>
       <c r="L97" s="28"/>
-      <c r="M97" s="37" t="s">
+      <c r="M97" s="32" t="s">
         <v>177</v>
       </c>
       <c r="N97" s="33"/>
@@ -5118,27 +5133,27 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="34">
         <v>44783</v>
       </c>
       <c r="D98" s="28"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="29" t="s">
+      <c r="F98" s="35" t="s">
         <v>178</v>
       </c>
       <c r="G98" s="30"/>
       <c r="H98" s="28"/>
-      <c r="I98" s="29" t="s">
+      <c r="I98" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J98" s="28"/>
-      <c r="K98" s="31">
+      <c r="K98" s="36">
         <v>100</v>
       </c>
       <c r="L98" s="28"/>
-      <c r="M98" s="32" t="s">
+      <c r="M98" s="37" t="s">
         <v>179</v>
       </c>
       <c r="N98" s="33"/>
@@ -5150,27 +5165,27 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="34">
+      <c r="C99" s="27">
         <v>44783</v>
       </c>
       <c r="D99" s="28"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="35" t="s">
+      <c r="F99" s="29" t="s">
         <v>180</v>
       </c>
       <c r="G99" s="30"/>
       <c r="H99" s="28"/>
-      <c r="I99" s="35" t="s">
+      <c r="I99" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J99" s="28"/>
-      <c r="K99" s="36">
+      <c r="K99" s="31">
         <v>193</v>
       </c>
       <c r="L99" s="28"/>
-      <c r="M99" s="37" t="s">
+      <c r="M99" s="32" t="s">
         <v>181</v>
       </c>
       <c r="N99" s="33"/>
@@ -5182,27 +5197,27 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="34">
         <v>44783</v>
       </c>
       <c r="D100" s="28"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="29" t="s">
+      <c r="F100" s="35" t="s">
         <v>182</v>
       </c>
       <c r="G100" s="30"/>
       <c r="H100" s="28"/>
-      <c r="I100" s="29" t="s">
+      <c r="I100" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="28"/>
-      <c r="K100" s="31">
+      <c r="K100" s="36">
         <v>15</v>
       </c>
       <c r="L100" s="28"/>
-      <c r="M100" s="32" t="s">
+      <c r="M100" s="37" t="s">
         <v>183</v>
       </c>
       <c r="N100" s="33"/>
@@ -5214,27 +5229,27 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="34">
+      <c r="C101" s="27">
         <v>44783</v>
       </c>
       <c r="D101" s="28"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="35" t="s">
+      <c r="F101" s="29" t="s">
         <v>182</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="28"/>
-      <c r="I101" s="35" t="s">
+      <c r="I101" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="28"/>
-      <c r="K101" s="36">
+      <c r="K101" s="31">
         <v>65</v>
       </c>
       <c r="L101" s="28"/>
-      <c r="M101" s="37" t="s">
+      <c r="M101" s="32" t="s">
         <v>184</v>
       </c>
       <c r="N101" s="33"/>
@@ -5246,27 +5261,27 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="34">
         <v>44783</v>
       </c>
       <c r="D102" s="28"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="29" t="s">
+      <c r="F102" s="35" t="s">
         <v>182</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="28"/>
-      <c r="I102" s="29" t="s">
+      <c r="I102" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="28"/>
-      <c r="K102" s="31">
+      <c r="K102" s="36">
         <v>66</v>
       </c>
       <c r="L102" s="28"/>
-      <c r="M102" s="32" t="s">
+      <c r="M102" s="37" t="s">
         <v>185</v>
       </c>
       <c r="N102" s="33"/>
@@ -5278,27 +5293,27 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="34">
+      <c r="C103" s="27">
         <v>44784</v>
       </c>
       <c r="D103" s="28"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="35" t="s">
+      <c r="F103" s="29" t="s">
         <v>186</v>
       </c>
       <c r="G103" s="30"/>
       <c r="H103" s="28"/>
-      <c r="I103" s="35" t="s">
+      <c r="I103" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J103" s="28"/>
-      <c r="K103" s="36">
+      <c r="K103" s="31">
         <v>111</v>
       </c>
       <c r="L103" s="28"/>
-      <c r="M103" s="37" t="s">
+      <c r="M103" s="32" t="s">
         <v>187</v>
       </c>
       <c r="N103" s="33"/>
@@ -5310,27 +5325,27 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="34">
         <v>44784</v>
       </c>
       <c r="D104" s="28"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="29" t="s">
+      <c r="F104" s="35" t="s">
         <v>186</v>
       </c>
       <c r="G104" s="30"/>
       <c r="H104" s="28"/>
-      <c r="I104" s="29" t="s">
+      <c r="I104" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J104" s="28"/>
-      <c r="K104" s="31">
+      <c r="K104" s="36">
         <v>30</v>
       </c>
       <c r="L104" s="28"/>
-      <c r="M104" s="32" t="s">
+      <c r="M104" s="37" t="s">
         <v>188</v>
       </c>
       <c r="N104" s="33"/>
@@ -5342,27 +5357,27 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="34">
+      <c r="C105" s="27">
         <v>44784</v>
       </c>
       <c r="D105" s="28"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="35" t="s">
+      <c r="F105" s="29" t="s">
         <v>186</v>
       </c>
       <c r="G105" s="30"/>
       <c r="H105" s="28"/>
-      <c r="I105" s="35" t="s">
+      <c r="I105" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J105" s="28"/>
-      <c r="K105" s="36">
+      <c r="K105" s="31">
         <v>31</v>
       </c>
       <c r="L105" s="28"/>
-      <c r="M105" s="37" t="s">
+      <c r="M105" s="32" t="s">
         <v>189</v>
       </c>
       <c r="N105" s="33"/>
@@ -5374,27 +5389,27 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="34">
         <v>44784</v>
       </c>
       <c r="D106" s="28"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="29" t="s">
+      <c r="F106" s="35" t="s">
         <v>186</v>
       </c>
       <c r="G106" s="30"/>
       <c r="H106" s="28"/>
-      <c r="I106" s="29" t="s">
+      <c r="I106" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J106" s="28"/>
-      <c r="K106" s="31">
+      <c r="K106" s="36">
         <v>109</v>
       </c>
       <c r="L106" s="28"/>
-      <c r="M106" s="32" t="s">
+      <c r="M106" s="37" t="s">
         <v>190</v>
       </c>
       <c r="N106" s="33"/>
@@ -5406,27 +5421,27 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="34">
+      <c r="C107" s="27">
         <v>44788</v>
       </c>
       <c r="D107" s="28"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="35" t="s">
+      <c r="F107" s="29" t="s">
         <v>191</v>
       </c>
       <c r="G107" s="30"/>
       <c r="H107" s="28"/>
-      <c r="I107" s="35" t="s">
+      <c r="I107" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J107" s="28"/>
-      <c r="K107" s="36">
+      <c r="K107" s="31">
         <v>5</v>
       </c>
       <c r="L107" s="28"/>
-      <c r="M107" s="37" t="s">
+      <c r="M107" s="32" t="s">
         <v>192</v>
       </c>
       <c r="N107" s="33"/>
@@ -5438,27 +5453,27 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="34">
         <v>44788</v>
       </c>
       <c r="D108" s="28"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="29" t="s">
+      <c r="F108" s="35" t="s">
         <v>193</v>
       </c>
       <c r="G108" s="30"/>
       <c r="H108" s="28"/>
-      <c r="I108" s="29" t="s">
+      <c r="I108" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J108" s="28"/>
-      <c r="K108" s="31">
+      <c r="K108" s="36">
         <v>100</v>
       </c>
       <c r="L108" s="28"/>
-      <c r="M108" s="32" t="s">
+      <c r="M108" s="37" t="s">
         <v>194</v>
       </c>
       <c r="N108" s="33"/>
@@ -5470,27 +5485,27 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="34">
+      <c r="C109" s="27">
         <v>44788</v>
       </c>
       <c r="D109" s="28"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="35" t="s">
+      <c r="F109" s="29" t="s">
         <v>195</v>
       </c>
       <c r="G109" s="30"/>
       <c r="H109" s="28"/>
-      <c r="I109" s="35" t="s">
+      <c r="I109" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="28"/>
-      <c r="K109" s="36">
+      <c r="K109" s="31">
         <v>54</v>
       </c>
       <c r="L109" s="28"/>
-      <c r="M109" s="37" t="s">
+      <c r="M109" s="32" t="s">
         <v>196</v>
       </c>
       <c r="N109" s="33"/>
@@ -5502,27 +5517,27 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="34">
         <v>44789</v>
       </c>
       <c r="D110" s="28"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="29" t="s">
+      <c r="F110" s="35" t="s">
         <v>197</v>
       </c>
       <c r="G110" s="30"/>
       <c r="H110" s="28"/>
-      <c r="I110" s="29" t="s">
+      <c r="I110" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="28"/>
-      <c r="K110" s="31">
+      <c r="K110" s="36">
         <v>77</v>
       </c>
       <c r="L110" s="28"/>
-      <c r="M110" s="32" t="s">
+      <c r="M110" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N110" s="33"/>
@@ -5534,27 +5549,27 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="34">
+      <c r="C111" s="27">
         <v>44789</v>
       </c>
       <c r="D111" s="28"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="35" t="s">
+      <c r="F111" s="29" t="s">
         <v>197</v>
       </c>
       <c r="G111" s="30"/>
       <c r="H111" s="28"/>
-      <c r="I111" s="35" t="s">
+      <c r="I111" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="28"/>
-      <c r="K111" s="36">
+      <c r="K111" s="31">
         <v>52</v>
       </c>
       <c r="L111" s="28"/>
-      <c r="M111" s="37" t="s">
+      <c r="M111" s="32" t="s">
         <v>199</v>
       </c>
       <c r="N111" s="33"/>
@@ -5566,27 +5581,27 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="34">
         <v>44789</v>
       </c>
       <c r="D112" s="28"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="29" t="s">
+      <c r="F112" s="35" t="s">
         <v>200</v>
       </c>
       <c r="G112" s="30"/>
       <c r="H112" s="28"/>
-      <c r="I112" s="29" t="s">
+      <c r="I112" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J112" s="28"/>
-      <c r="K112" s="31">
+      <c r="K112" s="36">
         <v>305</v>
       </c>
       <c r="L112" s="28"/>
-      <c r="M112" s="32" t="s">
+      <c r="M112" s="37" t="s">
         <v>201</v>
       </c>
       <c r="N112" s="33"/>
@@ -5598,27 +5613,27 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="34">
+      <c r="C113" s="27">
         <v>44789</v>
       </c>
       <c r="D113" s="28"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="35" t="s">
+      <c r="F113" s="29" t="s">
         <v>197</v>
       </c>
       <c r="G113" s="30"/>
       <c r="H113" s="28"/>
-      <c r="I113" s="35" t="s">
+      <c r="I113" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J113" s="28"/>
-      <c r="K113" s="36">
+      <c r="K113" s="31">
         <v>81</v>
       </c>
       <c r="L113" s="28"/>
-      <c r="M113" s="37" t="s">
+      <c r="M113" s="32" t="s">
         <v>202</v>
       </c>
       <c r="N113" s="33"/>
@@ -5630,27 +5645,27 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="34">
         <v>44789</v>
       </c>
       <c r="D114" s="28"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="29" t="s">
+      <c r="F114" s="35" t="s">
         <v>197</v>
       </c>
       <c r="G114" s="30"/>
       <c r="H114" s="28"/>
-      <c r="I114" s="29" t="s">
+      <c r="I114" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J114" s="28"/>
-      <c r="K114" s="31">
+      <c r="K114" s="36">
         <v>53</v>
       </c>
       <c r="L114" s="28"/>
-      <c r="M114" s="32" t="s">
+      <c r="M114" s="37" t="s">
         <v>203</v>
       </c>
       <c r="N114" s="33"/>
@@ -5662,27 +5677,27 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="34">
+      <c r="C115" s="27">
         <v>44789</v>
       </c>
       <c r="D115" s="28"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="35" t="s">
+      <c r="F115" s="29" t="s">
         <v>197</v>
       </c>
       <c r="G115" s="30"/>
       <c r="H115" s="28"/>
-      <c r="I115" s="35" t="s">
+      <c r="I115" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J115" s="28"/>
-      <c r="K115" s="36">
+      <c r="K115" s="31">
         <v>33</v>
       </c>
       <c r="L115" s="28"/>
-      <c r="M115" s="37" t="s">
+      <c r="M115" s="32" t="s">
         <v>204</v>
       </c>
       <c r="N115" s="33"/>
@@ -5694,27 +5709,27 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="34">
         <v>44790</v>
       </c>
       <c r="D116" s="28"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="29" t="s">
+      <c r="F116" s="35" t="s">
         <v>206</v>
       </c>
       <c r="G116" s="30"/>
       <c r="H116" s="28"/>
-      <c r="I116" s="29" t="s">
+      <c r="I116" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J116" s="28"/>
-      <c r="K116" s="31">
+      <c r="K116" s="36">
         <v>145</v>
       </c>
       <c r="L116" s="28"/>
-      <c r="M116" s="32" t="s">
+      <c r="M116" s="37" t="s">
         <v>207</v>
       </c>
       <c r="N116" s="33"/>
@@ -5726,27 +5741,27 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="34">
+      <c r="C117" s="27">
         <v>44790</v>
       </c>
       <c r="D117" s="28"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="35" t="s">
+      <c r="F117" s="29" t="s">
         <v>208</v>
       </c>
       <c r="G117" s="30"/>
       <c r="H117" s="28"/>
-      <c r="I117" s="35" t="s">
+      <c r="I117" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J117" s="28"/>
-      <c r="K117" s="36">
+      <c r="K117" s="31">
         <v>14</v>
       </c>
       <c r="L117" s="28"/>
-      <c r="M117" s="37" t="s">
+      <c r="M117" s="32" t="s">
         <v>209</v>
       </c>
       <c r="N117" s="33"/>
@@ -5758,27 +5773,27 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="34">
         <v>44790</v>
       </c>
       <c r="D118" s="28"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="29" t="s">
+      <c r="F118" s="35" t="s">
         <v>210</v>
       </c>
       <c r="G118" s="30"/>
       <c r="H118" s="28"/>
-      <c r="I118" s="29" t="s">
+      <c r="I118" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="28"/>
-      <c r="K118" s="31">
+      <c r="K118" s="36">
         <v>47</v>
       </c>
       <c r="L118" s="28"/>
-      <c r="M118" s="32" t="s">
+      <c r="M118" s="37" t="s">
         <v>211</v>
       </c>
       <c r="N118" s="33"/>
@@ -5790,27 +5805,27 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="34">
+      <c r="C119" s="27">
         <v>44790</v>
       </c>
       <c r="D119" s="28"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="35" t="s">
+      <c r="F119" s="29" t="s">
         <v>212</v>
       </c>
       <c r="G119" s="30"/>
       <c r="H119" s="28"/>
-      <c r="I119" s="35" t="s">
+      <c r="I119" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J119" s="28"/>
-      <c r="K119" s="36">
+      <c r="K119" s="31">
         <v>16</v>
       </c>
       <c r="L119" s="28"/>
-      <c r="M119" s="37" t="s">
+      <c r="M119" s="32" t="s">
         <v>213</v>
       </c>
       <c r="N119" s="33"/>
@@ -5822,27 +5837,27 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="34">
         <v>44790</v>
       </c>
       <c r="D120" s="28"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="29" t="s">
+      <c r="F120" s="35" t="s">
         <v>208</v>
       </c>
       <c r="G120" s="30"/>
       <c r="H120" s="28"/>
-      <c r="I120" s="29" t="s">
+      <c r="I120" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J120" s="28"/>
-      <c r="K120" s="31">
+      <c r="K120" s="36">
         <v>55</v>
       </c>
       <c r="L120" s="28"/>
-      <c r="M120" s="32" t="s">
+      <c r="M120" s="37" t="s">
         <v>214</v>
       </c>
       <c r="N120" s="33"/>
@@ -5854,27 +5869,27 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="34">
+      <c r="C121" s="27">
         <v>44790</v>
       </c>
       <c r="D121" s="28"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="35" t="s">
+      <c r="F121" s="29" t="s">
         <v>208</v>
       </c>
       <c r="G121" s="30"/>
       <c r="H121" s="28"/>
-      <c r="I121" s="35" t="s">
+      <c r="I121" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J121" s="28"/>
-      <c r="K121" s="36">
+      <c r="K121" s="31">
         <v>8</v>
       </c>
       <c r="L121" s="28"/>
-      <c r="M121" s="37" t="s">
+      <c r="M121" s="32" t="s">
         <v>215</v>
       </c>
       <c r="N121" s="33"/>
@@ -5886,27 +5901,27 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="34">
         <v>44790</v>
       </c>
       <c r="D122" s="28"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="29" t="s">
+      <c r="F122" s="35" t="s">
         <v>217</v>
       </c>
       <c r="G122" s="30"/>
       <c r="H122" s="28"/>
-      <c r="I122" s="29" t="s">
+      <c r="I122" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J122" s="28"/>
-      <c r="K122" s="31">
+      <c r="K122" s="36">
         <v>578</v>
       </c>
       <c r="L122" s="28"/>
-      <c r="M122" s="32" t="s">
+      <c r="M122" s="37" t="s">
         <v>218</v>
       </c>
       <c r="N122" s="33"/>
@@ -5918,27 +5933,27 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="34">
+      <c r="C123" s="27">
         <v>44791</v>
       </c>
       <c r="D123" s="28"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="35" t="s">
+      <c r="F123" s="29" t="s">
         <v>220</v>
       </c>
       <c r="G123" s="30"/>
       <c r="H123" s="28"/>
-      <c r="I123" s="35" t="s">
+      <c r="I123" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J123" s="28"/>
-      <c r="K123" s="36">
+      <c r="K123" s="31">
         <v>111</v>
       </c>
       <c r="L123" s="28"/>
-      <c r="M123" s="37" t="s">
+      <c r="M123" s="32" t="s">
         <v>221</v>
       </c>
       <c r="N123" s="33"/>
@@ -5950,27 +5965,27 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="34">
         <v>44791</v>
       </c>
       <c r="D124" s="28"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="29" t="s">
+      <c r="F124" s="35" t="s">
         <v>222</v>
       </c>
       <c r="G124" s="30"/>
       <c r="H124" s="28"/>
-      <c r="I124" s="29" t="s">
+      <c r="I124" s="35" t="s">
         <v>168</v>
       </c>
       <c r="J124" s="28"/>
-      <c r="K124" s="31">
+      <c r="K124" s="36">
         <v>51</v>
       </c>
       <c r="L124" s="28"/>
-      <c r="M124" s="32" t="s">
+      <c r="M124" s="37" t="s">
         <v>223</v>
       </c>
       <c r="N124" s="33"/>
@@ -5982,27 +5997,27 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="34">
+      <c r="C125" s="27">
         <v>44791</v>
       </c>
       <c r="D125" s="28"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="35" t="s">
+      <c r="F125" s="29" t="s">
         <v>222</v>
       </c>
       <c r="G125" s="30"/>
       <c r="H125" s="28"/>
-      <c r="I125" s="35" t="s">
+      <c r="I125" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J125" s="28"/>
-      <c r="K125" s="36">
+      <c r="K125" s="31">
         <v>35</v>
       </c>
       <c r="L125" s="28"/>
-      <c r="M125" s="37" t="s">
+      <c r="M125" s="32" t="s">
         <v>224</v>
       </c>
       <c r="N125" s="33"/>
@@ -6014,27 +6029,27 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="34">
         <v>44792</v>
       </c>
       <c r="D126" s="28"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="29" t="s">
+      <c r="F126" s="35" t="s">
         <v>225</v>
       </c>
       <c r="G126" s="30"/>
       <c r="H126" s="28"/>
-      <c r="I126" s="29" t="s">
+      <c r="I126" s="35" t="s">
         <v>226</v>
       </c>
       <c r="J126" s="28"/>
-      <c r="K126" s="31">
+      <c r="K126" s="36">
         <v>74</v>
       </c>
       <c r="L126" s="28"/>
-      <c r="M126" s="32" t="s">
+      <c r="M126" s="37" t="s">
         <v>227</v>
       </c>
       <c r="N126" s="33"/>
@@ -6046,27 +6061,27 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="34">
+      <c r="C127" s="27">
         <v>44795</v>
       </c>
       <c r="D127" s="28"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="35" t="s">
+      <c r="F127" s="29" t="s">
         <v>228</v>
       </c>
       <c r="G127" s="30"/>
       <c r="H127" s="28"/>
-      <c r="I127" s="35" t="s">
+      <c r="I127" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J127" s="28"/>
-      <c r="K127" s="36">
+      <c r="K127" s="31">
         <v>51</v>
       </c>
       <c r="L127" s="28"/>
-      <c r="M127" s="37" t="s">
+      <c r="M127" s="32" t="s">
         <v>229</v>
       </c>
       <c r="N127" s="33"/>
@@ -6078,27 +6093,27 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="34">
         <v>44799</v>
       </c>
       <c r="D128" s="28"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="29" t="s">
+      <c r="F128" s="35" t="s">
         <v>137</v>
       </c>
       <c r="G128" s="30"/>
       <c r="H128" s="28"/>
-      <c r="I128" s="29" t="s">
+      <c r="I128" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J128" s="28"/>
-      <c r="K128" s="31">
+      <c r="K128" s="36">
         <v>80</v>
       </c>
       <c r="L128" s="28"/>
-      <c r="M128" s="32" t="s">
+      <c r="M128" s="37" t="s">
         <v>138</v>
       </c>
       <c r="N128" s="33"/>
@@ -6110,27 +6125,27 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="34">
+      <c r="C129" s="27">
         <v>44799</v>
       </c>
       <c r="D129" s="28"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="35" t="s">
+      <c r="F129" s="29" t="s">
         <v>230</v>
       </c>
       <c r="G129" s="30"/>
       <c r="H129" s="28"/>
-      <c r="I129" s="35" t="s">
+      <c r="I129" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J129" s="28"/>
-      <c r="K129" s="36">
+      <c r="K129" s="31">
         <v>100</v>
       </c>
       <c r="L129" s="28"/>
-      <c r="M129" s="37" t="s">
+      <c r="M129" s="32" t="s">
         <v>231</v>
       </c>
       <c r="N129" s="33"/>
@@ -6142,27 +6157,27 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="34">
         <v>44802</v>
       </c>
       <c r="D130" s="28"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="29" t="s">
+      <c r="F130" s="35" t="s">
         <v>232</v>
       </c>
       <c r="G130" s="30"/>
       <c r="H130" s="28"/>
-      <c r="I130" s="29" t="s">
+      <c r="I130" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J130" s="28"/>
-      <c r="K130" s="31">
+      <c r="K130" s="36">
         <v>96</v>
       </c>
       <c r="L130" s="28"/>
-      <c r="M130" s="32" t="s">
+      <c r="M130" s="37" t="s">
         <v>233</v>
       </c>
       <c r="N130" s="33"/>
@@ -6174,27 +6189,27 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="34">
+      <c r="C131" s="27">
         <v>44802</v>
       </c>
       <c r="D131" s="28"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="35" t="s">
+      <c r="F131" s="29" t="s">
         <v>234</v>
       </c>
       <c r="G131" s="30"/>
       <c r="H131" s="28"/>
-      <c r="I131" s="35" t="s">
+      <c r="I131" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J131" s="28"/>
-      <c r="K131" s="36">
+      <c r="K131" s="31">
         <v>37</v>
       </c>
       <c r="L131" s="28"/>
-      <c r="M131" s="37" t="s">
+      <c r="M131" s="32" t="s">
         <v>235</v>
       </c>
       <c r="N131" s="33"/>
@@ -6206,27 +6221,27 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="34">
         <v>44804</v>
       </c>
       <c r="D132" s="28"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="29" t="s">
+      <c r="F132" s="35" t="s">
         <v>236</v>
       </c>
       <c r="G132" s="30"/>
       <c r="H132" s="28"/>
-      <c r="I132" s="29" t="s">
+      <c r="I132" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J132" s="28"/>
-      <c r="K132" s="31">
+      <c r="K132" s="36">
         <v>91</v>
       </c>
       <c r="L132" s="28"/>
-      <c r="M132" s="32" t="s">
+      <c r="M132" s="37" t="s">
         <v>237</v>
       </c>
       <c r="N132" s="33"/>
@@ -6238,27 +6253,27 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="34">
+      <c r="C133" s="27">
         <v>44804</v>
       </c>
       <c r="D133" s="28"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="35" t="s">
+      <c r="F133" s="29" t="s">
         <v>238</v>
       </c>
       <c r="G133" s="30"/>
       <c r="H133" s="28"/>
-      <c r="I133" s="35" t="s">
+      <c r="I133" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J133" s="28"/>
-      <c r="K133" s="36">
+      <c r="K133" s="31">
         <v>56</v>
       </c>
       <c r="L133" s="28"/>
-      <c r="M133" s="37" t="s">
+      <c r="M133" s="32" t="s">
         <v>239</v>
       </c>
       <c r="N133" s="33"/>
@@ -6270,27 +6285,27 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="34">
         <v>44805</v>
       </c>
       <c r="D134" s="28"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="29" t="s">
+      <c r="F134" s="35" t="s">
         <v>240</v>
       </c>
       <c r="G134" s="30"/>
       <c r="H134" s="28"/>
-      <c r="I134" s="29" t="s">
+      <c r="I134" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J134" s="28"/>
-      <c r="K134" s="31">
+      <c r="K134" s="36">
         <v>401</v>
       </c>
       <c r="L134" s="28"/>
-      <c r="M134" s="32" t="s">
+      <c r="M134" s="37" t="s">
         <v>241</v>
       </c>
       <c r="N134" s="33"/>
@@ -6302,27 +6317,27 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="34">
+      <c r="C135" s="27">
         <v>44805</v>
       </c>
       <c r="D135" s="28"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="35" t="s">
+      <c r="F135" s="29" t="s">
         <v>242</v>
       </c>
       <c r="G135" s="30"/>
       <c r="H135" s="28"/>
-      <c r="I135" s="35" t="s">
+      <c r="I135" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J135" s="28"/>
-      <c r="K135" s="36">
+      <c r="K135" s="31">
         <v>375</v>
       </c>
       <c r="L135" s="28"/>
-      <c r="M135" s="37" t="s">
+      <c r="M135" s="32" t="s">
         <v>243</v>
       </c>
       <c r="N135" s="33"/>
@@ -6334,27 +6349,27 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="27">
+      <c r="C136" s="34">
         <v>44806</v>
       </c>
       <c r="D136" s="28"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="29" t="s">
+      <c r="F136" s="35" t="s">
         <v>244</v>
       </c>
       <c r="G136" s="30"/>
       <c r="H136" s="28"/>
-      <c r="I136" s="29" t="s">
+      <c r="I136" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J136" s="28"/>
-      <c r="K136" s="31">
+      <c r="K136" s="36">
         <v>44</v>
       </c>
       <c r="L136" s="28"/>
-      <c r="M136" s="32" t="s">
+      <c r="M136" s="37" t="s">
         <v>245</v>
       </c>
       <c r="N136" s="33"/>
@@ -6366,27 +6381,27 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="34">
+      <c r="C137" s="27">
         <v>44806</v>
       </c>
       <c r="D137" s="28"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="35" t="s">
+      <c r="F137" s="29" t="s">
         <v>246</v>
       </c>
       <c r="G137" s="30"/>
       <c r="H137" s="28"/>
-      <c r="I137" s="35" t="s">
+      <c r="I137" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J137" s="28"/>
-      <c r="K137" s="36">
+      <c r="K137" s="31">
         <v>51</v>
       </c>
       <c r="L137" s="28"/>
-      <c r="M137" s="37" t="s">
+      <c r="M137" s="32" t="s">
         <v>247</v>
       </c>
       <c r="N137" s="33"/>
@@ -6398,27 +6413,27 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="27">
+      <c r="C138" s="34">
         <v>44806</v>
       </c>
       <c r="D138" s="28"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="29" t="s">
+      <c r="F138" s="35" t="s">
         <v>240</v>
       </c>
       <c r="G138" s="30"/>
       <c r="H138" s="28"/>
-      <c r="I138" s="29" t="s">
+      <c r="I138" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J138" s="28"/>
-      <c r="K138" s="31">
+      <c r="K138" s="36">
         <v>40</v>
       </c>
       <c r="L138" s="28"/>
-      <c r="M138" s="32" t="s">
+      <c r="M138" s="37" t="s">
         <v>248</v>
       </c>
       <c r="N138" s="33"/>
@@ -6430,27 +6445,27 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="34">
+      <c r="C139" s="27">
         <v>44810</v>
       </c>
       <c r="D139" s="28"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="35" t="s">
+      <c r="F139" s="29" t="s">
         <v>249</v>
       </c>
       <c r="G139" s="30"/>
       <c r="H139" s="28"/>
-      <c r="I139" s="35" t="s">
+      <c r="I139" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J139" s="28"/>
-      <c r="K139" s="36">
+      <c r="K139" s="31">
         <v>9</v>
       </c>
       <c r="L139" s="28"/>
-      <c r="M139" s="37" t="s">
+      <c r="M139" s="32" t="s">
         <v>250</v>
       </c>
       <c r="N139" s="33"/>
@@ -6462,27 +6477,27 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="27">
+      <c r="C140" s="34">
         <v>44810</v>
       </c>
       <c r="D140" s="28"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="29" t="s">
+      <c r="F140" s="35" t="s">
         <v>251</v>
       </c>
       <c r="G140" s="30"/>
       <c r="H140" s="28"/>
-      <c r="I140" s="29" t="s">
+      <c r="I140" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J140" s="28"/>
-      <c r="K140" s="31">
+      <c r="K140" s="36">
         <v>17</v>
       </c>
       <c r="L140" s="28"/>
-      <c r="M140" s="32" t="s">
+      <c r="M140" s="37" t="s">
         <v>252</v>
       </c>
       <c r="N140" s="33"/>
@@ -6494,27 +6509,27 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="34">
+      <c r="C141" s="27">
         <v>44810</v>
       </c>
       <c r="D141" s="28"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="35" t="s">
+      <c r="F141" s="29" t="s">
         <v>251</v>
       </c>
       <c r="G141" s="30"/>
       <c r="H141" s="28"/>
-      <c r="I141" s="35" t="s">
+      <c r="I141" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J141" s="28"/>
-      <c r="K141" s="36">
+      <c r="K141" s="31">
         <v>5</v>
       </c>
       <c r="L141" s="28"/>
-      <c r="M141" s="37" t="s">
+      <c r="M141" s="32" t="s">
         <v>252</v>
       </c>
       <c r="N141" s="33"/>
@@ -6526,27 +6541,27 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="27">
+      <c r="C142" s="34">
         <v>44810</v>
       </c>
       <c r="D142" s="28"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="29" t="s">
+      <c r="F142" s="35" t="s">
         <v>253</v>
       </c>
       <c r="G142" s="30"/>
       <c r="H142" s="28"/>
-      <c r="I142" s="29" t="s">
+      <c r="I142" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J142" s="28"/>
-      <c r="K142" s="31">
+      <c r="K142" s="36">
         <v>45</v>
       </c>
       <c r="L142" s="28"/>
-      <c r="M142" s="32" t="s">
+      <c r="M142" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N142" s="33"/>
@@ -6558,27 +6573,27 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="34">
+      <c r="C143" s="27">
         <v>44811</v>
       </c>
       <c r="D143" s="28"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="35" t="s">
+      <c r="F143" s="29" t="s">
         <v>255</v>
       </c>
       <c r="G143" s="30"/>
       <c r="H143" s="28"/>
-      <c r="I143" s="35" t="s">
+      <c r="I143" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J143" s="28"/>
-      <c r="K143" s="36">
+      <c r="K143" s="31">
         <v>132</v>
       </c>
       <c r="L143" s="28"/>
-      <c r="M143" s="37" t="s">
+      <c r="M143" s="32" t="s">
         <v>256</v>
       </c>
       <c r="N143" s="33"/>
@@ -6590,27 +6605,27 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="27">
+      <c r="C144" s="34">
         <v>44811</v>
       </c>
       <c r="D144" s="28"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="29" t="s">
+      <c r="F144" s="35" t="s">
         <v>257</v>
       </c>
       <c r="G144" s="30"/>
       <c r="H144" s="28"/>
-      <c r="I144" s="29" t="s">
+      <c r="I144" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J144" s="28"/>
-      <c r="K144" s="31">
+      <c r="K144" s="36">
         <v>66</v>
       </c>
       <c r="L144" s="28"/>
-      <c r="M144" s="32" t="s">
+      <c r="M144" s="37" t="s">
         <v>258</v>
       </c>
       <c r="N144" s="33"/>
@@ -6622,27 +6637,27 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="34">
+      <c r="C145" s="27">
         <v>44812</v>
       </c>
       <c r="D145" s="28"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="35" t="s">
+      <c r="F145" s="29" t="s">
         <v>259</v>
       </c>
       <c r="G145" s="30"/>
       <c r="H145" s="28"/>
-      <c r="I145" s="35" t="s">
+      <c r="I145" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J145" s="28"/>
-      <c r="K145" s="36">
+      <c r="K145" s="31">
         <v>69</v>
       </c>
       <c r="L145" s="28"/>
-      <c r="M145" s="37" t="s">
+      <c r="M145" s="32" t="s">
         <v>260</v>
       </c>
       <c r="N145" s="33"/>
@@ -6654,27 +6669,27 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="27">
+      <c r="C146" s="34">
         <v>44812</v>
       </c>
       <c r="D146" s="28"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="29" t="s">
+      <c r="F146" s="35" t="s">
         <v>262</v>
       </c>
       <c r="G146" s="30"/>
       <c r="H146" s="28"/>
-      <c r="I146" s="29" t="s">
+      <c r="I146" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J146" s="28"/>
-      <c r="K146" s="31">
+      <c r="K146" s="36">
         <v>48</v>
       </c>
       <c r="L146" s="28"/>
-      <c r="M146" s="32" t="s">
+      <c r="M146" s="37" t="s">
         <v>263</v>
       </c>
       <c r="N146" s="33"/>
@@ -6686,27 +6701,27 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="34">
+      <c r="C147" s="27">
         <v>44812</v>
       </c>
       <c r="D147" s="28"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="35" t="s">
+      <c r="F147" s="29" t="s">
         <v>264</v>
       </c>
       <c r="G147" s="30"/>
       <c r="H147" s="28"/>
-      <c r="I147" s="35" t="s">
+      <c r="I147" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J147" s="28"/>
-      <c r="K147" s="36">
+      <c r="K147" s="31">
         <v>33</v>
       </c>
       <c r="L147" s="28"/>
-      <c r="M147" s="37" t="s">
+      <c r="M147" s="32" t="s">
         <v>265</v>
       </c>
       <c r="N147" s="33"/>
@@ -6718,27 +6733,27 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="27">
+      <c r="C148" s="34">
         <v>44813</v>
       </c>
       <c r="D148" s="28"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="29" t="s">
+      <c r="F148" s="35" t="s">
         <v>266</v>
       </c>
       <c r="G148" s="30"/>
       <c r="H148" s="28"/>
-      <c r="I148" s="29" t="s">
+      <c r="I148" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J148" s="28"/>
-      <c r="K148" s="31">
+      <c r="K148" s="36">
         <v>5</v>
       </c>
       <c r="L148" s="28"/>
-      <c r="M148" s="32" t="s">
+      <c r="M148" s="37" t="s">
         <v>267</v>
       </c>
       <c r="N148" s="33"/>
@@ -6750,27 +6765,27 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="34">
+      <c r="C149" s="27">
         <v>44813</v>
       </c>
       <c r="D149" s="28"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="35" t="s">
+      <c r="F149" s="29" t="s">
         <v>268</v>
       </c>
       <c r="G149" s="30"/>
       <c r="H149" s="28"/>
-      <c r="I149" s="35" t="s">
+      <c r="I149" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J149" s="28"/>
-      <c r="K149" s="36">
+      <c r="K149" s="31">
         <v>26</v>
       </c>
       <c r="L149" s="28"/>
-      <c r="M149" s="37" t="s">
+      <c r="M149" s="32" t="s">
         <v>269</v>
       </c>
       <c r="N149" s="33"/>
@@ -6782,27 +6797,27 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="27">
+      <c r="C150" s="34">
         <v>44813</v>
       </c>
       <c r="D150" s="28"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="29" t="s">
+      <c r="F150" s="35" t="s">
         <v>270</v>
       </c>
       <c r="G150" s="30"/>
       <c r="H150" s="28"/>
-      <c r="I150" s="29" t="s">
+      <c r="I150" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J150" s="28"/>
-      <c r="K150" s="31">
+      <c r="K150" s="36">
         <v>13</v>
       </c>
       <c r="L150" s="28"/>
-      <c r="M150" s="32" t="s">
+      <c r="M150" s="37" t="s">
         <v>271</v>
       </c>
       <c r="N150" s="33"/>
@@ -6814,27 +6829,27 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="34">
+      <c r="C151" s="27">
         <v>44816</v>
       </c>
       <c r="D151" s="28"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="35" t="s">
+      <c r="F151" s="29" t="s">
         <v>272</v>
       </c>
       <c r="G151" s="30"/>
       <c r="H151" s="28"/>
-      <c r="I151" s="35" t="s">
+      <c r="I151" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J151" s="28"/>
-      <c r="K151" s="36">
+      <c r="K151" s="31">
         <v>50</v>
       </c>
       <c r="L151" s="28"/>
-      <c r="M151" s="37" t="s">
+      <c r="M151" s="32" t="s">
         <v>273</v>
       </c>
       <c r="N151" s="33"/>
@@ -6846,27 +6861,27 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="27">
+      <c r="C152" s="34">
         <v>44816</v>
       </c>
       <c r="D152" s="28"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="29" t="s">
+      <c r="F152" s="35" t="s">
         <v>274</v>
       </c>
       <c r="G152" s="30"/>
       <c r="H152" s="28"/>
-      <c r="I152" s="29" t="s">
+      <c r="I152" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J152" s="28"/>
-      <c r="K152" s="31">
+      <c r="K152" s="36">
         <v>104</v>
       </c>
       <c r="L152" s="28"/>
-      <c r="M152" s="32" t="s">
+      <c r="M152" s="37" t="s">
         <v>275</v>
       </c>
       <c r="N152" s="33"/>
@@ -6878,27 +6893,27 @@
       <c r="B153" s="2">
         <v>44813</v>
       </c>
-      <c r="C153" s="34">
+      <c r="C153" s="27">
         <v>44817</v>
       </c>
       <c r="D153" s="28"/>
       <c r="E153" s="2">
         <v>45199</v>
       </c>
-      <c r="F153" s="35" t="s">
+      <c r="F153" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G153" s="30"/>
       <c r="H153" s="28"/>
-      <c r="I153" s="35" t="s">
+      <c r="I153" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J153" s="28"/>
-      <c r="K153" s="36">
+      <c r="K153" s="31">
         <v>1</v>
       </c>
       <c r="L153" s="28"/>
-      <c r="M153" s="37" t="s">
+      <c r="M153" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N153" s="33"/>
@@ -6910,27 +6925,27 @@
       <c r="B154" s="4">
         <v>44813</v>
       </c>
-      <c r="C154" s="27">
+      <c r="C154" s="34">
         <v>44817</v>
       </c>
       <c r="D154" s="28"/>
       <c r="E154" s="4">
         <v>44848</v>
       </c>
-      <c r="F154" s="29" t="s">
+      <c r="F154" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G154" s="30"/>
       <c r="H154" s="28"/>
-      <c r="I154" s="29" t="s">
+      <c r="I154" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J154" s="28"/>
-      <c r="K154" s="31">
+      <c r="K154" s="36">
         <v>2</v>
       </c>
       <c r="L154" s="28"/>
-      <c r="M154" s="32" t="s">
+      <c r="M154" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N154" s="33"/>
@@ -6942,27 +6957,27 @@
       <c r="B155" s="2">
         <v>44813</v>
       </c>
-      <c r="C155" s="34">
+      <c r="C155" s="27">
         <v>44817</v>
       </c>
       <c r="D155" s="28"/>
       <c r="E155" s="2">
         <v>45198</v>
       </c>
-      <c r="F155" s="35" t="s">
+      <c r="F155" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G155" s="30"/>
       <c r="H155" s="28"/>
-      <c r="I155" s="35" t="s">
+      <c r="I155" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J155" s="28"/>
-      <c r="K155" s="36">
+      <c r="K155" s="31">
         <v>2</v>
       </c>
       <c r="L155" s="28"/>
-      <c r="M155" s="37" t="s">
+      <c r="M155" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N155" s="33"/>
@@ -6974,27 +6989,27 @@
       <c r="B156" s="4">
         <v>44813</v>
       </c>
-      <c r="C156" s="27">
+      <c r="C156" s="34">
         <v>44817</v>
       </c>
       <c r="D156" s="28"/>
       <c r="E156" s="4">
         <v>45044</v>
       </c>
-      <c r="F156" s="29" t="s">
+      <c r="F156" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G156" s="30"/>
       <c r="H156" s="28"/>
-      <c r="I156" s="29" t="s">
+      <c r="I156" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J156" s="28"/>
-      <c r="K156" s="31">
+      <c r="K156" s="36">
         <v>5</v>
       </c>
       <c r="L156" s="28"/>
-      <c r="M156" s="32" t="s">
+      <c r="M156" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N156" s="33"/>
@@ -7006,27 +7021,27 @@
       <c r="B157" s="2">
         <v>44813</v>
       </c>
-      <c r="C157" s="34">
+      <c r="C157" s="27">
         <v>44817</v>
       </c>
       <c r="D157" s="28"/>
       <c r="E157" s="2">
         <v>45107</v>
       </c>
-      <c r="F157" s="35" t="s">
+      <c r="F157" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G157" s="30"/>
       <c r="H157" s="28"/>
-      <c r="I157" s="35" t="s">
+      <c r="I157" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J157" s="28"/>
-      <c r="K157" s="36">
+      <c r="K157" s="31">
         <v>2</v>
       </c>
       <c r="L157" s="28"/>
-      <c r="M157" s="37" t="s">
+      <c r="M157" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N157" s="33"/>
@@ -7038,27 +7053,27 @@
       <c r="B158" s="4">
         <v>44813</v>
       </c>
-      <c r="C158" s="27">
+      <c r="C158" s="34">
         <v>44817</v>
       </c>
       <c r="D158" s="28"/>
       <c r="E158" s="4">
         <v>45192</v>
       </c>
-      <c r="F158" s="29" t="s">
+      <c r="F158" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G158" s="30"/>
       <c r="H158" s="28"/>
-      <c r="I158" s="29" t="s">
+      <c r="I158" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J158" s="28"/>
-      <c r="K158" s="31">
+      <c r="K158" s="36">
         <v>1</v>
       </c>
       <c r="L158" s="28"/>
-      <c r="M158" s="32" t="s">
+      <c r="M158" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N158" s="33"/>
@@ -7070,27 +7085,27 @@
       <c r="B159" s="2">
         <v>44813</v>
       </c>
-      <c r="C159" s="34">
+      <c r="C159" s="27">
         <v>44817</v>
       </c>
       <c r="D159" s="28"/>
       <c r="E159" s="2">
         <v>44957</v>
       </c>
-      <c r="F159" s="35" t="s">
+      <c r="F159" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G159" s="30"/>
       <c r="H159" s="28"/>
-      <c r="I159" s="35" t="s">
+      <c r="I159" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J159" s="28"/>
-      <c r="K159" s="36">
+      <c r="K159" s="31">
         <v>4</v>
       </c>
       <c r="L159" s="28"/>
-      <c r="M159" s="37" t="s">
+      <c r="M159" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N159" s="33"/>
@@ -7102,27 +7117,27 @@
       <c r="B160" s="4">
         <v>44813</v>
       </c>
-      <c r="C160" s="27">
+      <c r="C160" s="34">
         <v>44817</v>
       </c>
       <c r="D160" s="28"/>
       <c r="E160" s="4">
         <v>44834</v>
       </c>
-      <c r="F160" s="29" t="s">
+      <c r="F160" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G160" s="30"/>
       <c r="H160" s="28"/>
-      <c r="I160" s="29" t="s">
+      <c r="I160" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J160" s="28"/>
-      <c r="K160" s="31">
+      <c r="K160" s="36">
         <v>4</v>
       </c>
       <c r="L160" s="28"/>
-      <c r="M160" s="32" t="s">
+      <c r="M160" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N160" s="33"/>
@@ -7134,27 +7149,27 @@
       <c r="B161" s="2">
         <v>44813</v>
       </c>
-      <c r="C161" s="34">
+      <c r="C161" s="27">
         <v>44817</v>
       </c>
       <c r="D161" s="28"/>
       <c r="E161" s="2">
         <v>45077</v>
       </c>
-      <c r="F161" s="35" t="s">
+      <c r="F161" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G161" s="30"/>
       <c r="H161" s="28"/>
-      <c r="I161" s="35" t="s">
+      <c r="I161" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J161" s="28"/>
-      <c r="K161" s="36">
+      <c r="K161" s="31">
         <v>3</v>
       </c>
       <c r="L161" s="28"/>
-      <c r="M161" s="37" t="s">
+      <c r="M161" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N161" s="33"/>
@@ -7166,27 +7181,27 @@
       <c r="B162" s="4">
         <v>44813</v>
       </c>
-      <c r="C162" s="27">
+      <c r="C162" s="34">
         <v>44817</v>
       </c>
       <c r="D162" s="28"/>
       <c r="E162" s="4">
         <v>45093</v>
       </c>
-      <c r="F162" s="29" t="s">
+      <c r="F162" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G162" s="30"/>
       <c r="H162" s="28"/>
-      <c r="I162" s="29" t="s">
+      <c r="I162" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J162" s="28"/>
-      <c r="K162" s="31">
+      <c r="K162" s="36">
         <v>8</v>
       </c>
       <c r="L162" s="28"/>
-      <c r="M162" s="32" t="s">
+      <c r="M162" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N162" s="33"/>
@@ -7198,27 +7213,27 @@
       <c r="B163" s="2">
         <v>44813</v>
       </c>
-      <c r="C163" s="34">
+      <c r="C163" s="27">
         <v>44817</v>
       </c>
       <c r="D163" s="28"/>
       <c r="E163" s="2">
         <v>45565</v>
       </c>
-      <c r="F163" s="35" t="s">
+      <c r="F163" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G163" s="30"/>
       <c r="H163" s="28"/>
-      <c r="I163" s="35" t="s">
+      <c r="I163" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J163" s="28"/>
-      <c r="K163" s="36">
+      <c r="K163" s="31">
         <v>1</v>
       </c>
       <c r="L163" s="28"/>
-      <c r="M163" s="37" t="s">
+      <c r="M163" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N163" s="33"/>
@@ -7230,27 +7245,27 @@
       <c r="B164" s="4">
         <v>44813</v>
       </c>
-      <c r="C164" s="27">
+      <c r="C164" s="34">
         <v>44817</v>
       </c>
       <c r="D164" s="28"/>
       <c r="E164" s="4">
         <v>45227</v>
       </c>
-      <c r="F164" s="29" t="s">
+      <c r="F164" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G164" s="30"/>
       <c r="H164" s="28"/>
-      <c r="I164" s="29" t="s">
+      <c r="I164" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J164" s="28"/>
-      <c r="K164" s="31">
+      <c r="K164" s="36">
         <v>2</v>
       </c>
       <c r="L164" s="28"/>
-      <c r="M164" s="32" t="s">
+      <c r="M164" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N164" s="33"/>
@@ -7262,27 +7277,27 @@
       <c r="B165" s="2">
         <v>44813</v>
       </c>
-      <c r="C165" s="34">
+      <c r="C165" s="27">
         <v>44817</v>
       </c>
       <c r="D165" s="28"/>
       <c r="E165" s="2">
         <v>45046</v>
       </c>
-      <c r="F165" s="35" t="s">
+      <c r="F165" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G165" s="30"/>
       <c r="H165" s="28"/>
-      <c r="I165" s="35" t="s">
+      <c r="I165" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J165" s="28"/>
-      <c r="K165" s="36">
+      <c r="K165" s="31">
         <v>1</v>
       </c>
       <c r="L165" s="28"/>
-      <c r="M165" s="37" t="s">
+      <c r="M165" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N165" s="33"/>
@@ -7294,27 +7309,27 @@
       <c r="B166" s="4">
         <v>44813</v>
       </c>
-      <c r="C166" s="27">
+      <c r="C166" s="34">
         <v>44817</v>
       </c>
       <c r="D166" s="28"/>
       <c r="E166" s="4">
         <v>45092</v>
       </c>
-      <c r="F166" s="29" t="s">
+      <c r="F166" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G166" s="30"/>
       <c r="H166" s="28"/>
-      <c r="I166" s="29" t="s">
+      <c r="I166" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J166" s="28"/>
-      <c r="K166" s="31">
+      <c r="K166" s="36">
         <v>3</v>
       </c>
       <c r="L166" s="28"/>
-      <c r="M166" s="32" t="s">
+      <c r="M166" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N166" s="33"/>
@@ -7326,27 +7341,27 @@
       <c r="B167" s="2">
         <v>44813</v>
       </c>
-      <c r="C167" s="34">
+      <c r="C167" s="27">
         <v>44817</v>
       </c>
       <c r="D167" s="28"/>
       <c r="E167" s="2">
         <v>44985</v>
       </c>
-      <c r="F167" s="35" t="s">
+      <c r="F167" s="29" t="s">
         <v>276</v>
       </c>
       <c r="G167" s="30"/>
       <c r="H167" s="28"/>
-      <c r="I167" s="35" t="s">
+      <c r="I167" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J167" s="28"/>
-      <c r="K167" s="36">
+      <c r="K167" s="31">
         <v>1</v>
       </c>
       <c r="L167" s="28"/>
-      <c r="M167" s="37" t="s">
+      <c r="M167" s="32" t="s">
         <v>254</v>
       </c>
       <c r="N167" s="33"/>
@@ -7358,27 +7373,27 @@
       <c r="B168" s="4">
         <v>44813</v>
       </c>
-      <c r="C168" s="27">
+      <c r="C168" s="34">
         <v>44817</v>
       </c>
       <c r="D168" s="28"/>
       <c r="E168" s="4">
         <v>45555</v>
       </c>
-      <c r="F168" s="29" t="s">
+      <c r="F168" s="35" t="s">
         <v>276</v>
       </c>
       <c r="G168" s="30"/>
       <c r="H168" s="28"/>
-      <c r="I168" s="29" t="s">
+      <c r="I168" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J168" s="28"/>
-      <c r="K168" s="31">
+      <c r="K168" s="36">
         <v>1</v>
       </c>
       <c r="L168" s="28"/>
-      <c r="M168" s="32" t="s">
+      <c r="M168" s="37" t="s">
         <v>254</v>
       </c>
       <c r="N168" s="33"/>
@@ -7390,27 +7405,27 @@
       <c r="B169" s="2">
         <v>44811</v>
       </c>
-      <c r="C169" s="34">
+      <c r="C169" s="27">
         <v>44817</v>
       </c>
       <c r="D169" s="28"/>
       <c r="E169" s="2">
         <v>44882</v>
       </c>
-      <c r="F169" s="35" t="s">
+      <c r="F169" s="29" t="s">
         <v>277</v>
       </c>
       <c r="G169" s="30"/>
       <c r="H169" s="28"/>
-      <c r="I169" s="35" t="s">
+      <c r="I169" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J169" s="28"/>
-      <c r="K169" s="36">
+      <c r="K169" s="31">
         <v>92</v>
       </c>
       <c r="L169" s="28"/>
-      <c r="M169" s="37" t="s">
+      <c r="M169" s="32" t="s">
         <v>278</v>
       </c>
       <c r="N169" s="33"/>
@@ -7422,27 +7437,27 @@
       <c r="B170" s="4">
         <v>44811</v>
       </c>
-      <c r="C170" s="27">
+      <c r="C170" s="34">
         <v>44817</v>
       </c>
       <c r="D170" s="28"/>
       <c r="E170" s="4">
         <v>44882</v>
       </c>
-      <c r="F170" s="29" t="s">
+      <c r="F170" s="35" t="s">
         <v>277</v>
       </c>
       <c r="G170" s="30"/>
       <c r="H170" s="28"/>
-      <c r="I170" s="29" t="s">
+      <c r="I170" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J170" s="28"/>
-      <c r="K170" s="31">
+      <c r="K170" s="36">
         <v>169</v>
       </c>
       <c r="L170" s="28"/>
-      <c r="M170" s="32" t="s">
+      <c r="M170" s="37" t="s">
         <v>279</v>
       </c>
       <c r="N170" s="33"/>
@@ -7454,27 +7469,27 @@
       <c r="B171" s="2">
         <v>44817</v>
       </c>
-      <c r="C171" s="34">
+      <c r="C171" s="27">
         <v>44818</v>
       </c>
       <c r="D171" s="28"/>
       <c r="E171" s="2">
         <v>44888</v>
       </c>
-      <c r="F171" s="35" t="s">
+      <c r="F171" s="29" t="s">
         <v>280</v>
       </c>
       <c r="G171" s="30"/>
       <c r="H171" s="28"/>
-      <c r="I171" s="35" t="s">
+      <c r="I171" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J171" s="28"/>
-      <c r="K171" s="36">
+      <c r="K171" s="31">
         <v>99</v>
       </c>
       <c r="L171" s="28"/>
-      <c r="M171" s="37" t="s">
+      <c r="M171" s="32" t="s">
         <v>281</v>
       </c>
       <c r="N171" s="33"/>
@@ -7486,27 +7501,27 @@
       <c r="B172" s="4">
         <v>44817</v>
       </c>
-      <c r="C172" s="27">
+      <c r="C172" s="34">
         <v>44818</v>
       </c>
       <c r="D172" s="28"/>
       <c r="E172" s="4">
         <v>44911</v>
       </c>
-      <c r="F172" s="29" t="s">
+      <c r="F172" s="35" t="s">
         <v>282</v>
       </c>
       <c r="G172" s="30"/>
       <c r="H172" s="28"/>
-      <c r="I172" s="29" t="s">
+      <c r="I172" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J172" s="28"/>
-      <c r="K172" s="31">
+      <c r="K172" s="36">
         <v>10</v>
       </c>
       <c r="L172" s="28"/>
-      <c r="M172" s="32" t="s">
+      <c r="M172" s="37" t="s">
         <v>283</v>
       </c>
       <c r="N172" s="33"/>
@@ -7518,27 +7533,27 @@
       <c r="B173" s="2">
         <v>44817</v>
       </c>
-      <c r="C173" s="34">
+      <c r="C173" s="27">
         <v>44818</v>
       </c>
       <c r="D173" s="28"/>
       <c r="E173" s="2">
         <v>44876</v>
       </c>
-      <c r="F173" s="35" t="s">
+      <c r="F173" s="29" t="s">
         <v>284</v>
       </c>
       <c r="G173" s="30"/>
       <c r="H173" s="28"/>
-      <c r="I173" s="35" t="s">
+      <c r="I173" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J173" s="28"/>
-      <c r="K173" s="36">
+      <c r="K173" s="31">
         <v>69</v>
       </c>
       <c r="L173" s="28"/>
-      <c r="M173" s="37" t="s">
+      <c r="M173" s="32" t="s">
         <v>285</v>
       </c>
       <c r="N173" s="33"/>
@@ -7550,27 +7565,27 @@
       <c r="B174" s="4">
         <v>44810</v>
       </c>
-      <c r="C174" s="27">
+      <c r="C174" s="34">
         <v>44819</v>
       </c>
       <c r="D174" s="28"/>
       <c r="E174" s="4">
         <v>44870</v>
       </c>
-      <c r="F174" s="29" t="s">
+      <c r="F174" s="35" t="s">
         <v>286</v>
       </c>
       <c r="G174" s="30"/>
       <c r="H174" s="28"/>
-      <c r="I174" s="29" t="s">
+      <c r="I174" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J174" s="28"/>
-      <c r="K174" s="31">
+      <c r="K174" s="36">
         <v>115</v>
       </c>
       <c r="L174" s="28"/>
-      <c r="M174" s="32" t="s">
+      <c r="M174" s="37" t="s">
         <v>287</v>
       </c>
       <c r="N174" s="33"/>
@@ -7582,27 +7597,27 @@
       <c r="B175" s="2">
         <v>44806</v>
       </c>
-      <c r="C175" s="34">
+      <c r="C175" s="27">
         <v>44819</v>
       </c>
       <c r="D175" s="28"/>
       <c r="E175" s="2">
         <v>44867</v>
       </c>
-      <c r="F175" s="35" t="s">
+      <c r="F175" s="29" t="s">
         <v>288</v>
       </c>
       <c r="G175" s="30"/>
       <c r="H175" s="28"/>
-      <c r="I175" s="35" t="s">
+      <c r="I175" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J175" s="28"/>
-      <c r="K175" s="36">
+      <c r="K175" s="31">
         <v>109</v>
       </c>
       <c r="L175" s="28"/>
-      <c r="M175" s="37" t="s">
+      <c r="M175" s="32" t="s">
         <v>50</v>
       </c>
       <c r="N175" s="33"/>
@@ -7614,27 +7629,27 @@
       <c r="B176" s="4">
         <v>44818</v>
       </c>
-      <c r="C176" s="27">
+      <c r="C176" s="34">
         <v>44819</v>
       </c>
       <c r="D176" s="28"/>
       <c r="E176" s="4">
         <v>44883</v>
       </c>
-      <c r="F176" s="29" t="s">
+      <c r="F176" s="35" t="s">
         <v>289</v>
       </c>
       <c r="G176" s="30"/>
       <c r="H176" s="28"/>
-      <c r="I176" s="29" t="s">
+      <c r="I176" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J176" s="28"/>
-      <c r="K176" s="31">
+      <c r="K176" s="36">
         <v>113</v>
       </c>
       <c r="L176" s="28"/>
-      <c r="M176" s="32" t="s">
+      <c r="M176" s="37" t="s">
         <v>290</v>
       </c>
       <c r="N176" s="33"/>
@@ -7646,27 +7661,27 @@
       <c r="B177" s="2">
         <v>44818</v>
       </c>
-      <c r="C177" s="34">
+      <c r="C177" s="27">
         <v>44819</v>
       </c>
       <c r="D177" s="28"/>
       <c r="E177" s="2">
         <v>44872</v>
       </c>
-      <c r="F177" s="35" t="s">
+      <c r="F177" s="29" t="s">
         <v>292</v>
       </c>
       <c r="G177" s="30"/>
       <c r="H177" s="28"/>
-      <c r="I177" s="35" t="s">
+      <c r="I177" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J177" s="28"/>
-      <c r="K177" s="36">
+      <c r="K177" s="31">
         <v>13</v>
       </c>
       <c r="L177" s="28"/>
-      <c r="M177" s="37" t="s">
+      <c r="M177" s="32" t="s">
         <v>293</v>
       </c>
       <c r="N177" s="33"/>
@@ -7678,27 +7693,27 @@
       <c r="B178" s="4">
         <v>44818</v>
       </c>
-      <c r="C178" s="27">
+      <c r="C178" s="34">
         <v>44819</v>
       </c>
       <c r="D178" s="28"/>
       <c r="E178" s="4">
         <v>44818</v>
       </c>
-      <c r="F178" s="29" t="s">
+      <c r="F178" s="35" t="s">
         <v>294</v>
       </c>
       <c r="G178" s="30"/>
       <c r="H178" s="28"/>
-      <c r="I178" s="29" t="s">
+      <c r="I178" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J178" s="28"/>
-      <c r="K178" s="31">
+      <c r="K178" s="36">
         <v>1</v>
       </c>
       <c r="L178" s="28"/>
-      <c r="M178" s="32" t="s">
+      <c r="M178" s="37" t="s">
         <v>295</v>
       </c>
       <c r="N178" s="33"/>
@@ -7710,27 +7725,27 @@
       <c r="B179" s="2">
         <v>44811</v>
       </c>
-      <c r="C179" s="34">
+      <c r="C179" s="27">
         <v>44819</v>
       </c>
       <c r="D179" s="28"/>
       <c r="E179" s="2">
         <v>44895</v>
       </c>
-      <c r="F179" s="35" t="s">
+      <c r="F179" s="29" t="s">
         <v>296</v>
       </c>
       <c r="G179" s="30"/>
       <c r="H179" s="28"/>
-      <c r="I179" s="35" t="s">
+      <c r="I179" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J179" s="28"/>
-      <c r="K179" s="36">
+      <c r="K179" s="31">
         <v>137</v>
       </c>
       <c r="L179" s="28"/>
-      <c r="M179" s="37" t="s">
+      <c r="M179" s="32" t="s">
         <v>297</v>
       </c>
       <c r="N179" s="33"/>
@@ -7742,27 +7757,27 @@
       <c r="B180" s="4">
         <v>44812</v>
       </c>
-      <c r="C180" s="27">
+      <c r="C180" s="34">
         <v>44819</v>
       </c>
       <c r="D180" s="28"/>
       <c r="E180" s="4">
         <v>44873</v>
       </c>
-      <c r="F180" s="29" t="s">
+      <c r="F180" s="35" t="s">
         <v>298</v>
       </c>
       <c r="G180" s="30"/>
       <c r="H180" s="28"/>
-      <c r="I180" s="29" t="s">
+      <c r="I180" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J180" s="28"/>
-      <c r="K180" s="31">
+      <c r="K180" s="36">
         <v>73</v>
       </c>
       <c r="L180" s="28"/>
-      <c r="M180" s="32" t="s">
+      <c r="M180" s="37" t="s">
         <v>299</v>
       </c>
       <c r="N180" s="33"/>
@@ -7774,27 +7789,27 @@
       <c r="B181" s="2">
         <v>44818</v>
       </c>
-      <c r="C181" s="34">
+      <c r="C181" s="27">
         <v>44819</v>
       </c>
       <c r="D181" s="28"/>
       <c r="E181" s="2">
         <v>44880</v>
       </c>
-      <c r="F181" s="35" t="s">
+      <c r="F181" s="29" t="s">
         <v>300</v>
       </c>
       <c r="G181" s="30"/>
       <c r="H181" s="28"/>
-      <c r="I181" s="35" t="s">
+      <c r="I181" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J181" s="28"/>
-      <c r="K181" s="36">
+      <c r="K181" s="31">
         <v>108</v>
       </c>
       <c r="L181" s="28"/>
-      <c r="M181" s="37" t="s">
+      <c r="M181" s="32" t="s">
         <v>301</v>
       </c>
       <c r="N181" s="33"/>
@@ -7806,27 +7821,27 @@
       <c r="B182" s="4">
         <v>44812</v>
       </c>
-      <c r="C182" s="27">
+      <c r="C182" s="34">
         <v>44820</v>
       </c>
       <c r="D182" s="28"/>
       <c r="E182" s="4">
         <v>44873</v>
       </c>
-      <c r="F182" s="29" t="s">
+      <c r="F182" s="35" t="s">
         <v>303</v>
       </c>
       <c r="G182" s="30"/>
       <c r="H182" s="28"/>
-      <c r="I182" s="29" t="s">
+      <c r="I182" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J182" s="28"/>
-      <c r="K182" s="31">
+      <c r="K182" s="36">
         <v>49</v>
       </c>
       <c r="L182" s="28"/>
-      <c r="M182" s="32" t="s">
+      <c r="M182" s="37" t="s">
         <v>304</v>
       </c>
       <c r="N182" s="33"/>
@@ -7838,27 +7853,27 @@
       <c r="B183" s="2">
         <v>44812</v>
       </c>
-      <c r="C183" s="34">
+      <c r="C183" s="27">
         <v>44820</v>
       </c>
       <c r="D183" s="28"/>
       <c r="E183" s="2">
         <v>44873</v>
       </c>
-      <c r="F183" s="35" t="s">
+      <c r="F183" s="29" t="s">
         <v>303</v>
       </c>
       <c r="G183" s="30"/>
       <c r="H183" s="28"/>
-      <c r="I183" s="35" t="s">
+      <c r="I183" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J183" s="28"/>
-      <c r="K183" s="36">
+      <c r="K183" s="31">
         <v>49</v>
       </c>
       <c r="L183" s="28"/>
-      <c r="M183" s="37" t="s">
+      <c r="M183" s="32" t="s">
         <v>305</v>
       </c>
       <c r="N183" s="33"/>
@@ -7870,27 +7885,27 @@
       <c r="B184" s="4">
         <v>44812</v>
       </c>
-      <c r="C184" s="27">
+      <c r="C184" s="34">
         <v>44820</v>
       </c>
       <c r="D184" s="28"/>
       <c r="E184" s="4">
         <v>44873</v>
       </c>
-      <c r="F184" s="29" t="s">
+      <c r="F184" s="35" t="s">
         <v>303</v>
       </c>
       <c r="G184" s="30"/>
       <c r="H184" s="28"/>
-      <c r="I184" s="29" t="s">
+      <c r="I184" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J184" s="28"/>
-      <c r="K184" s="31">
+      <c r="K184" s="36">
         <v>41</v>
       </c>
       <c r="L184" s="28"/>
-      <c r="M184" s="32" t="s">
+      <c r="M184" s="37" t="s">
         <v>306</v>
       </c>
       <c r="N184" s="33"/>
@@ -7902,27 +7917,27 @@
       <c r="B185" s="2">
         <v>44820</v>
       </c>
-      <c r="C185" s="34">
+      <c r="C185" s="27">
         <v>44820</v>
       </c>
       <c r="D185" s="28"/>
       <c r="E185" s="2">
         <v>44880</v>
       </c>
-      <c r="F185" s="35" t="s">
+      <c r="F185" s="29" t="s">
         <v>307</v>
       </c>
       <c r="G185" s="30"/>
       <c r="H185" s="28"/>
-      <c r="I185" s="35" t="s">
+      <c r="I185" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J185" s="28"/>
-      <c r="K185" s="36">
+      <c r="K185" s="31">
         <v>66</v>
       </c>
       <c r="L185" s="28"/>
-      <c r="M185" s="37" t="s">
+      <c r="M185" s="32" t="s">
         <v>308</v>
       </c>
       <c r="N185" s="33"/>
@@ -7934,27 +7949,27 @@
       <c r="B186" s="4">
         <v>44823</v>
       </c>
-      <c r="C186" s="27">
+      <c r="C186" s="34">
         <v>44823</v>
       </c>
       <c r="D186" s="28"/>
       <c r="E186" s="4">
         <v>44883</v>
       </c>
-      <c r="F186" s="29" t="s">
+      <c r="F186" s="35" t="s">
         <v>309</v>
       </c>
       <c r="G186" s="30"/>
       <c r="H186" s="28"/>
-      <c r="I186" s="29" t="s">
+      <c r="I186" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J186" s="28"/>
-      <c r="K186" s="31">
+      <c r="K186" s="36">
         <v>57</v>
       </c>
       <c r="L186" s="28"/>
-      <c r="M186" s="32" t="s">
+      <c r="M186" s="37" t="s">
         <v>310</v>
       </c>
       <c r="N186" s="33"/>
@@ -7966,27 +7981,27 @@
       <c r="B187" s="2">
         <v>44823</v>
       </c>
-      <c r="C187" s="34">
+      <c r="C187" s="27">
         <v>44824</v>
       </c>
       <c r="D187" s="28"/>
       <c r="E187" s="2">
         <v>44882</v>
       </c>
-      <c r="F187" s="35" t="s">
+      <c r="F187" s="29" t="s">
         <v>311</v>
       </c>
       <c r="G187" s="30"/>
       <c r="H187" s="28"/>
-      <c r="I187" s="35" t="s">
+      <c r="I187" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J187" s="28"/>
-      <c r="K187" s="36">
+      <c r="K187" s="31">
         <v>88</v>
       </c>
       <c r="L187" s="28"/>
-      <c r="M187" s="37" t="s">
+      <c r="M187" s="32" t="s">
         <v>312</v>
       </c>
       <c r="N187" s="33"/>
@@ -7998,27 +8013,27 @@
       <c r="B188" s="4">
         <v>44824</v>
       </c>
-      <c r="C188" s="27">
+      <c r="C188" s="34">
         <v>44824</v>
       </c>
       <c r="D188" s="28"/>
       <c r="E188" s="4">
         <v>44886</v>
       </c>
-      <c r="F188" s="29" t="s">
+      <c r="F188" s="35" t="s">
         <v>313</v>
       </c>
       <c r="G188" s="30"/>
       <c r="H188" s="28"/>
-      <c r="I188" s="29" t="s">
+      <c r="I188" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J188" s="28"/>
-      <c r="K188" s="31">
+      <c r="K188" s="36">
         <v>79</v>
       </c>
       <c r="L188" s="28"/>
-      <c r="M188" s="32" t="s">
+      <c r="M188" s="37" t="s">
         <v>314</v>
       </c>
       <c r="N188" s="33"/>
@@ -8030,27 +8045,27 @@
       <c r="B189" s="2">
         <v>44823</v>
       </c>
-      <c r="C189" s="34">
+      <c r="C189" s="27">
         <v>44825</v>
       </c>
       <c r="D189" s="28"/>
       <c r="E189" s="2">
         <v>44883</v>
       </c>
-      <c r="F189" s="35" t="s">
+      <c r="F189" s="29" t="s">
         <v>315</v>
       </c>
       <c r="G189" s="30"/>
       <c r="H189" s="28"/>
-      <c r="I189" s="35" t="s">
+      <c r="I189" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J189" s="28"/>
-      <c r="K189" s="36">
+      <c r="K189" s="31">
         <v>49</v>
       </c>
       <c r="L189" s="28"/>
-      <c r="M189" s="37" t="s">
+      <c r="M189" s="32" t="s">
         <v>316</v>
       </c>
       <c r="N189" s="33"/>
@@ -8062,27 +8077,27 @@
       <c r="B190" s="4">
         <v>44824</v>
       </c>
-      <c r="C190" s="27">
+      <c r="C190" s="34">
         <v>44825</v>
       </c>
       <c r="D190" s="28"/>
       <c r="E190" s="4">
         <v>44872</v>
       </c>
-      <c r="F190" s="29" t="s">
+      <c r="F190" s="35" t="s">
         <v>317</v>
       </c>
       <c r="G190" s="30"/>
       <c r="H190" s="28"/>
-      <c r="I190" s="29" t="s">
+      <c r="I190" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J190" s="28"/>
-      <c r="K190" s="31">
+      <c r="K190" s="36">
         <v>104</v>
       </c>
       <c r="L190" s="28"/>
-      <c r="M190" s="32" t="s">
+      <c r="M190" s="37" t="s">
         <v>318</v>
       </c>
       <c r="N190" s="33"/>
@@ -8094,27 +8109,27 @@
       <c r="B191" s="2">
         <v>44824</v>
       </c>
-      <c r="C191" s="34">
+      <c r="C191" s="27">
         <v>44825</v>
       </c>
       <c r="D191" s="28"/>
       <c r="E191" s="2">
         <v>44872</v>
       </c>
-      <c r="F191" s="35" t="s">
+      <c r="F191" s="29" t="s">
         <v>317</v>
       </c>
       <c r="G191" s="30"/>
       <c r="H191" s="28"/>
-      <c r="I191" s="35" t="s">
+      <c r="I191" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J191" s="28"/>
-      <c r="K191" s="36">
+      <c r="K191" s="31">
         <v>7</v>
       </c>
       <c r="L191" s="28"/>
-      <c r="M191" s="37" t="s">
+      <c r="M191" s="32" t="s">
         <v>319</v>
       </c>
       <c r="N191" s="33"/>
@@ -8126,27 +8141,27 @@
       <c r="B192" s="4">
         <v>44826</v>
       </c>
-      <c r="C192" s="27">
+      <c r="C192" s="34">
         <v>44826</v>
       </c>
       <c r="D192" s="28"/>
       <c r="E192" s="4">
         <v>44888</v>
       </c>
-      <c r="F192" s="29" t="s">
+      <c r="F192" s="35" t="s">
         <v>128</v>
       </c>
       <c r="G192" s="30"/>
       <c r="H192" s="28"/>
-      <c r="I192" s="29" t="s">
+      <c r="I192" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J192" s="28"/>
-      <c r="K192" s="31">
+      <c r="K192" s="36">
         <v>15</v>
       </c>
       <c r="L192" s="28"/>
-      <c r="M192" s="32" t="s">
+      <c r="M192" s="37" t="s">
         <v>320</v>
       </c>
       <c r="N192" s="33"/>
@@ -8158,27 +8173,27 @@
       <c r="B193" s="2">
         <v>44825</v>
       </c>
-      <c r="C193" s="34">
+      <c r="C193" s="27">
         <v>44826</v>
       </c>
       <c r="D193" s="28"/>
       <c r="E193" s="2">
         <v>44867</v>
       </c>
-      <c r="F193" s="35" t="s">
+      <c r="F193" s="29" t="s">
         <v>321</v>
       </c>
       <c r="G193" s="30"/>
       <c r="H193" s="28"/>
-      <c r="I193" s="35" t="s">
+      <c r="I193" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J193" s="28"/>
-      <c r="K193" s="36">
+      <c r="K193" s="31">
         <v>18</v>
       </c>
       <c r="L193" s="28"/>
-      <c r="M193" s="37" t="s">
+      <c r="M193" s="32" t="s">
         <v>322</v>
       </c>
       <c r="N193" s="33"/>
@@ -8190,27 +8205,27 @@
       <c r="B194" s="4">
         <v>44825</v>
       </c>
-      <c r="C194" s="27">
+      <c r="C194" s="34">
         <v>44826</v>
       </c>
       <c r="D194" s="28"/>
       <c r="E194" s="4">
         <v>44867</v>
       </c>
-      <c r="F194" s="29" t="s">
+      <c r="F194" s="35" t="s">
         <v>323</v>
       </c>
       <c r="G194" s="30"/>
       <c r="H194" s="28"/>
-      <c r="I194" s="29" t="s">
+      <c r="I194" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J194" s="28"/>
-      <c r="K194" s="31">
+      <c r="K194" s="36">
         <v>69</v>
       </c>
       <c r="L194" s="28"/>
-      <c r="M194" s="32" t="s">
+      <c r="M194" s="37" t="s">
         <v>324</v>
       </c>
       <c r="N194" s="33"/>
@@ -8222,27 +8237,27 @@
       <c r="B195" s="2">
         <v>44825</v>
       </c>
-      <c r="C195" s="34">
+      <c r="C195" s="27">
         <v>44826</v>
       </c>
       <c r="D195" s="28"/>
       <c r="E195" s="2">
         <v>44867</v>
       </c>
-      <c r="F195" s="35" t="s">
+      <c r="F195" s="29" t="s">
         <v>325</v>
       </c>
       <c r="G195" s="30"/>
       <c r="H195" s="28"/>
-      <c r="I195" s="35" t="s">
+      <c r="I195" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J195" s="28"/>
-      <c r="K195" s="36">
+      <c r="K195" s="31">
         <v>11</v>
       </c>
       <c r="L195" s="28"/>
-      <c r="M195" s="37" t="s">
+      <c r="M195" s="32" t="s">
         <v>326</v>
       </c>
       <c r="N195" s="33"/>
@@ -8254,27 +8269,27 @@
       <c r="B196" s="4">
         <v>44825</v>
       </c>
-      <c r="C196" s="27">
+      <c r="C196" s="34">
         <v>44826</v>
       </c>
       <c r="D196" s="28"/>
       <c r="E196" s="4">
         <v>44867</v>
       </c>
-      <c r="F196" s="29" t="s">
+      <c r="F196" s="35" t="s">
         <v>327</v>
       </c>
       <c r="G196" s="30"/>
       <c r="H196" s="28"/>
-      <c r="I196" s="29" t="s">
+      <c r="I196" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J196" s="28"/>
-      <c r="K196" s="31">
+      <c r="K196" s="36">
         <v>2</v>
       </c>
       <c r="L196" s="28"/>
-      <c r="M196" s="32" t="s">
+      <c r="M196" s="37" t="s">
         <v>328</v>
       </c>
       <c r="N196" s="33"/>
@@ -8286,27 +8301,27 @@
       <c r="B197" s="2">
         <v>44827</v>
       </c>
-      <c r="C197" s="34">
+      <c r="C197" s="27">
         <v>44827</v>
       </c>
       <c r="D197" s="28"/>
       <c r="E197" s="2">
         <v>44888</v>
       </c>
-      <c r="F197" s="35" t="s">
+      <c r="F197" s="29" t="s">
         <v>329</v>
       </c>
       <c r="G197" s="30"/>
       <c r="H197" s="28"/>
-      <c r="I197" s="35" t="s">
+      <c r="I197" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J197" s="28"/>
-      <c r="K197" s="36">
+      <c r="K197" s="31">
         <v>72</v>
       </c>
       <c r="L197" s="28"/>
-      <c r="M197" s="37" t="s">
+      <c r="M197" s="32" t="s">
         <v>330</v>
       </c>
       <c r="N197" s="33"/>
@@ -8318,27 +8333,27 @@
       <c r="B198" s="4">
         <v>44830</v>
       </c>
-      <c r="C198" s="27">
+      <c r="C198" s="34">
         <v>44830</v>
       </c>
       <c r="D198" s="28"/>
       <c r="E198" s="4">
         <v>44891</v>
       </c>
-      <c r="F198" s="29" t="s">
+      <c r="F198" s="35" t="s">
         <v>331</v>
       </c>
       <c r="G198" s="30"/>
       <c r="H198" s="28"/>
-      <c r="I198" s="29" t="s">
+      <c r="I198" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J198" s="28"/>
-      <c r="K198" s="31">
+      <c r="K198" s="36">
         <v>51</v>
       </c>
       <c r="L198" s="28"/>
-      <c r="M198" s="32" t="s">
+      <c r="M198" s="37" t="s">
         <v>332</v>
       </c>
       <c r="N198" s="33"/>
@@ -8350,27 +8365,27 @@
       <c r="B199" s="2">
         <v>44830</v>
       </c>
-      <c r="C199" s="34">
+      <c r="C199" s="27">
         <v>44830</v>
       </c>
       <c r="D199" s="28"/>
       <c r="E199" s="2">
         <v>44892</v>
       </c>
-      <c r="F199" s="35" t="s">
+      <c r="F199" s="29" t="s">
         <v>333</v>
       </c>
       <c r="G199" s="30"/>
       <c r="H199" s="28"/>
-      <c r="I199" s="35" t="s">
+      <c r="I199" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J199" s="28"/>
-      <c r="K199" s="36">
+      <c r="K199" s="31">
         <v>353</v>
       </c>
       <c r="L199" s="28"/>
-      <c r="M199" s="37" t="s">
+      <c r="M199" s="32" t="s">
         <v>334</v>
       </c>
       <c r="N199" s="33"/>
@@ -8382,27 +8397,27 @@
       <c r="B200" s="4">
         <v>44830</v>
       </c>
-      <c r="C200" s="27">
+      <c r="C200" s="34">
         <v>44830</v>
       </c>
       <c r="D200" s="28"/>
       <c r="E200" s="4">
         <v>44891</v>
       </c>
-      <c r="F200" s="29" t="s">
+      <c r="F200" s="35" t="s">
         <v>331</v>
       </c>
       <c r="G200" s="30"/>
       <c r="H200" s="28"/>
-      <c r="I200" s="29" t="s">
+      <c r="I200" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J200" s="28"/>
-      <c r="K200" s="31">
+      <c r="K200" s="36">
         <v>46</v>
       </c>
       <c r="L200" s="28"/>
-      <c r="M200" s="32" t="s">
+      <c r="M200" s="37" t="s">
         <v>335</v>
       </c>
       <c r="N200" s="33"/>
@@ -8414,27 +8429,27 @@
       <c r="B201" s="2">
         <v>44825</v>
       </c>
-      <c r="C201" s="34">
+      <c r="C201" s="27">
         <v>44831</v>
       </c>
       <c r="D201" s="28"/>
       <c r="E201" s="2">
         <v>44888</v>
       </c>
-      <c r="F201" s="35" t="s">
+      <c r="F201" s="29" t="s">
         <v>336</v>
       </c>
       <c r="G201" s="30"/>
       <c r="H201" s="28"/>
-      <c r="I201" s="35" t="s">
+      <c r="I201" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J201" s="28"/>
-      <c r="K201" s="36">
+      <c r="K201" s="31">
         <v>905</v>
       </c>
       <c r="L201" s="28"/>
-      <c r="M201" s="37" t="s">
+      <c r="M201" s="32" t="s">
         <v>337</v>
       </c>
       <c r="N201" s="33"/>
@@ -8446,27 +8461,27 @@
       <c r="B202" s="4">
         <v>44830</v>
       </c>
-      <c r="C202" s="27">
+      <c r="C202" s="34">
         <v>44831</v>
       </c>
       <c r="D202" s="28"/>
       <c r="E202" s="4">
         <v>44890</v>
       </c>
-      <c r="F202" s="29" t="s">
+      <c r="F202" s="35" t="s">
         <v>338</v>
       </c>
       <c r="G202" s="30"/>
       <c r="H202" s="28"/>
-      <c r="I202" s="29" t="s">
+      <c r="I202" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J202" s="28"/>
-      <c r="K202" s="31">
+      <c r="K202" s="36">
         <v>63</v>
       </c>
       <c r="L202" s="28"/>
-      <c r="M202" s="32" t="s">
+      <c r="M202" s="37" t="s">
         <v>339</v>
       </c>
       <c r="N202" s="33"/>
@@ -8478,27 +8493,27 @@
       <c r="B203" s="2">
         <v>44824</v>
       </c>
-      <c r="C203" s="34">
+      <c r="C203" s="27">
         <v>44831</v>
       </c>
       <c r="D203" s="28"/>
       <c r="E203" s="2">
         <v>44887</v>
       </c>
-      <c r="F203" s="35" t="s">
+      <c r="F203" s="29" t="s">
         <v>336</v>
       </c>
       <c r="G203" s="30"/>
       <c r="H203" s="28"/>
-      <c r="I203" s="35" t="s">
+      <c r="I203" s="29" t="s">
         <v>168</v>
       </c>
       <c r="J203" s="28"/>
-      <c r="K203" s="36">
+      <c r="K203" s="31">
         <v>308</v>
       </c>
       <c r="L203" s="28"/>
-      <c r="M203" s="37" t="s">
+      <c r="M203" s="32" t="s">
         <v>340</v>
       </c>
       <c r="N203" s="33"/>
@@ -8510,27 +8525,27 @@
       <c r="B204" s="4">
         <v>44818</v>
       </c>
-      <c r="C204" s="27">
+      <c r="C204" s="34">
         <v>44832</v>
       </c>
       <c r="D204" s="28"/>
       <c r="E204" s="4">
         <v>44879</v>
       </c>
-      <c r="F204" s="29" t="s">
+      <c r="F204" s="35" t="s">
         <v>341</v>
       </c>
       <c r="G204" s="30"/>
       <c r="H204" s="28"/>
-      <c r="I204" s="29" t="s">
+      <c r="I204" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J204" s="28"/>
-      <c r="K204" s="31">
+      <c r="K204" s="36">
         <v>10</v>
       </c>
       <c r="L204" s="28"/>
-      <c r="M204" s="32" t="s">
+      <c r="M204" s="37" t="s">
         <v>342</v>
       </c>
       <c r="N204" s="33"/>
@@ -8542,27 +8557,27 @@
       <c r="B205" s="2">
         <v>44832</v>
       </c>
-      <c r="C205" s="34">
+      <c r="C205" s="27">
         <v>44832</v>
       </c>
       <c r="D205" s="28"/>
       <c r="E205" s="2">
         <v>44893</v>
       </c>
-      <c r="F205" s="35" t="s">
+      <c r="F205" s="29" t="s">
         <v>343</v>
       </c>
       <c r="G205" s="30"/>
       <c r="H205" s="28"/>
-      <c r="I205" s="35" t="s">
+      <c r="I205" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J205" s="28"/>
-      <c r="K205" s="36">
+      <c r="K205" s="31">
         <v>93</v>
       </c>
       <c r="L205" s="28"/>
-      <c r="M205" s="37" t="s">
+      <c r="M205" s="32" t="s">
         <v>344</v>
       </c>
       <c r="N205" s="33"/>
@@ -8574,27 +8589,27 @@
       <c r="B206" s="4">
         <v>44820</v>
       </c>
-      <c r="C206" s="27">
+      <c r="C206" s="34">
         <v>44832</v>
       </c>
       <c r="D206" s="28"/>
       <c r="E206" s="4">
         <v>44849</v>
       </c>
-      <c r="F206" s="29" t="s">
+      <c r="F206" s="35" t="s">
         <v>345</v>
       </c>
       <c r="G206" s="30"/>
       <c r="H206" s="28"/>
-      <c r="I206" s="29" t="s">
+      <c r="I206" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J206" s="28"/>
-      <c r="K206" s="31">
+      <c r="K206" s="36">
         <v>70</v>
       </c>
       <c r="L206" s="28"/>
-      <c r="M206" s="32" t="s">
+      <c r="M206" s="37" t="s">
         <v>346</v>
       </c>
       <c r="N206" s="33"/>
@@ -8606,27 +8621,27 @@
       <c r="B207" s="2">
         <v>44833</v>
       </c>
-      <c r="C207" s="34">
+      <c r="C207" s="27">
         <v>44833</v>
       </c>
       <c r="D207" s="28"/>
       <c r="E207" s="2">
         <v>44897</v>
       </c>
-      <c r="F207" s="35" t="s">
+      <c r="F207" s="29" t="s">
         <v>347</v>
       </c>
       <c r="G207" s="30"/>
       <c r="H207" s="28"/>
-      <c r="I207" s="35" t="s">
+      <c r="I207" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J207" s="28"/>
-      <c r="K207" s="36">
+      <c r="K207" s="31">
         <v>21</v>
       </c>
       <c r="L207" s="28"/>
-      <c r="M207" s="37" t="s">
+      <c r="M207" s="32" t="s">
         <v>348</v>
       </c>
       <c r="N207" s="33"/>
@@ -8638,27 +8653,27 @@
       <c r="B208" s="4">
         <v>44834</v>
       </c>
-      <c r="C208" s="27">
+      <c r="C208" s="34">
         <v>44834</v>
       </c>
       <c r="D208" s="28"/>
       <c r="E208" s="4">
         <v>44896</v>
       </c>
-      <c r="F208" s="29" t="s">
+      <c r="F208" s="35" t="s">
         <v>349</v>
       </c>
       <c r="G208" s="30"/>
       <c r="H208" s="28"/>
-      <c r="I208" s="29" t="s">
+      <c r="I208" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J208" s="28"/>
-      <c r="K208" s="31">
+      <c r="K208" s="36">
         <v>28</v>
       </c>
       <c r="L208" s="28"/>
-      <c r="M208" s="32" t="s">
+      <c r="M208" s="37" t="s">
         <v>350</v>
       </c>
       <c r="N208" s="33"/>
@@ -8670,27 +8685,27 @@
       <c r="B209" s="2">
         <v>44777</v>
       </c>
-      <c r="C209" s="34">
+      <c r="C209" s="27">
         <v>44834</v>
       </c>
       <c r="D209" s="28"/>
       <c r="E209" s="2">
         <v>44837</v>
       </c>
-      <c r="F209" s="35" t="s">
+      <c r="F209" s="29" t="s">
         <v>351</v>
       </c>
       <c r="G209" s="30"/>
       <c r="H209" s="28"/>
-      <c r="I209" s="35" t="s">
+      <c r="I209" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J209" s="28"/>
-      <c r="K209" s="36">
+      <c r="K209" s="31">
         <v>201</v>
       </c>
       <c r="L209" s="28"/>
-      <c r="M209" s="37" t="s">
+      <c r="M209" s="32" t="s">
         <v>352</v>
       </c>
       <c r="N209" s="33"/>
@@ -8702,27 +8717,27 @@
       <c r="B210" s="4">
         <v>44833</v>
       </c>
-      <c r="C210" s="27">
+      <c r="C210" s="34">
         <v>44837</v>
       </c>
       <c r="D210" s="28"/>
       <c r="E210" s="4">
         <v>44894</v>
       </c>
-      <c r="F210" s="29" t="s">
+      <c r="F210" s="35" t="s">
         <v>353</v>
       </c>
       <c r="G210" s="30"/>
       <c r="H210" s="28"/>
-      <c r="I210" s="29" t="s">
+      <c r="I210" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J210" s="28"/>
-      <c r="K210" s="31">
+      <c r="K210" s="36">
         <v>49</v>
       </c>
       <c r="L210" s="28"/>
-      <c r="M210" s="32" t="s">
+      <c r="M210" s="37" t="s">
         <v>354</v>
       </c>
       <c r="N210" s="33"/>
@@ -8734,27 +8749,27 @@
       <c r="B211" s="2">
         <v>44834</v>
       </c>
-      <c r="C211" s="34">
+      <c r="C211" s="27">
         <v>44837</v>
       </c>
       <c r="D211" s="28"/>
       <c r="E211" s="2">
         <v>44906</v>
       </c>
-      <c r="F211" s="35" t="s">
+      <c r="F211" s="29" t="s">
         <v>356</v>
       </c>
       <c r="G211" s="30"/>
       <c r="H211" s="28"/>
-      <c r="I211" s="35" t="s">
+      <c r="I211" s="29" t="s">
         <v>18</v>
       </c>
       <c r="J211" s="28"/>
-      <c r="K211" s="36">
+      <c r="K211" s="31">
         <v>7</v>
       </c>
       <c r="L211" s="28"/>
-      <c r="M211" s="37" t="s">
+      <c r="M211" s="32" t="s">
         <v>357</v>
       </c>
       <c r="N211" s="33"/>
@@ -8766,104 +8781,193 @@
       <c r="B212" s="4">
         <v>44837</v>
       </c>
-      <c r="C212" s="27">
+      <c r="C212" s="34">
         <v>44838</v>
       </c>
       <c r="D212" s="28"/>
       <c r="E212" s="4">
         <v>44897</v>
       </c>
-      <c r="F212" s="29" t="s">
+      <c r="F212" s="35" t="s">
         <v>358</v>
       </c>
       <c r="G212" s="30"/>
       <c r="H212" s="28"/>
-      <c r="I212" s="29" t="s">
+      <c r="I212" s="35" t="s">
         <v>11</v>
       </c>
       <c r="J212" s="28"/>
-      <c r="K212" s="31">
+      <c r="K212" s="36">
         <v>44</v>
       </c>
       <c r="L212" s="28"/>
-      <c r="M212" s="32" t="s">
+      <c r="M212" s="37" t="s">
         <v>359</v>
       </c>
       <c r="N212" s="33"/>
     </row>
-    <row r="213" spans="1:14" ht="31.5" customHeight="1">
-      <c r="A213" s="25" t="s">
+    <row r="213" spans="1:14">
+      <c r="A213" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B213" s="2">
+        <v>44841</v>
+      </c>
+      <c r="C213" s="27">
+        <v>44844</v>
+      </c>
+      <c r="D213" s="28"/>
+      <c r="E213" s="2">
+        <v>44901</v>
+      </c>
+      <c r="F213" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="G213" s="30"/>
+      <c r="H213" s="28"/>
+      <c r="I213" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J213" s="28"/>
+      <c r="K213" s="31">
+        <v>6</v>
+      </c>
+      <c r="L213" s="28"/>
+      <c r="M213" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="N213" s="33"/>
+    </row>
+    <row r="214" spans="1:14">
+      <c r="A214" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B214" s="4">
+        <v>44840</v>
+      </c>
+      <c r="C214" s="34">
+        <v>44844</v>
+      </c>
+      <c r="D214" s="28"/>
+      <c r="E214" s="4">
+        <v>44901</v>
+      </c>
+      <c r="F214" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="G214" s="30"/>
+      <c r="H214" s="28"/>
+      <c r="I214" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="28"/>
+      <c r="K214" s="36">
+        <v>62</v>
+      </c>
+      <c r="L214" s="28"/>
+      <c r="M214" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="N214" s="33"/>
+    </row>
+    <row r="215" spans="1:14">
+      <c r="A215" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215" s="2">
+        <v>44840</v>
+      </c>
+      <c r="C215" s="27">
+        <v>44844</v>
+      </c>
+      <c r="D215" s="28"/>
+      <c r="E215" s="2">
+        <v>44901</v>
+      </c>
+      <c r="F215" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="G215" s="30"/>
+      <c r="H215" s="28"/>
+      <c r="I215" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J215" s="28"/>
+      <c r="K215" s="31">
+        <v>32</v>
+      </c>
+      <c r="L215" s="28"/>
+      <c r="M215" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="N215" s="33"/>
+    </row>
+    <row r="216" spans="1:14" ht="30" customHeight="1">
+      <c r="A216" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B216" s="26"/>
+      <c r="C216" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="D216" s="23"/>
+      <c r="E216" s="24"/>
+      <c r="F216" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="G216" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="H216" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="I216" s="24"/>
+      <c r="J216" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="K216" s="24"/>
+      <c r="L216" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="B213" s="26"/>
-      <c r="C213" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="D213" s="23"/>
-      <c r="E213" s="24"/>
-      <c r="F213" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="G213" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="H213" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="I213" s="24"/>
-      <c r="J213" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="K213" s="24"/>
-      <c r="L213" s="22" t="s">
-        <v>365</v>
-      </c>
-      <c r="M213" s="24"/>
-      <c r="N213" s="12" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14" s="10" customFormat="1">
-      <c r="A214" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B214" s="21"/>
-      <c r="C214" s="17">
-        <v>15555</v>
-      </c>
-      <c r="D214" s="18"/>
-      <c r="E214" s="19"/>
-      <c r="F214" s="7">
-        <v>120</v>
-      </c>
-      <c r="G214" s="8">
+      <c r="M216" s="24"/>
+      <c r="N216" s="12" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" s="10" customFormat="1">
+      <c r="A217" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B217" s="21"/>
+      <c r="C217" s="17">
+        <v>15655</v>
+      </c>
+      <c r="D217" s="18"/>
+      <c r="E217" s="19"/>
+      <c r="F217" s="7">
+        <v>122</v>
+      </c>
+      <c r="G217" s="8">
         <v>7</v>
       </c>
-      <c r="H214" s="17">
+      <c r="H217" s="17">
         <v>1</v>
       </c>
-      <c r="I214" s="19"/>
-      <c r="J214" s="17">
-        <v>79</v>
-      </c>
-      <c r="K214" s="19"/>
-      <c r="L214" s="17">
+      <c r="I217" s="19"/>
+      <c r="J217" s="17">
+        <v>80</v>
+      </c>
+      <c r="K217" s="19"/>
+      <c r="L217" s="17">
         <v>1</v>
       </c>
-      <c r="M214" s="19"/>
-      <c r="N214" s="9">
+      <c r="M217" s="19"/>
+      <c r="N217" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1062">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
+  <mergeCells count="1077">
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I5:J5"/>
@@ -8879,11 +8983,8 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:J9"/>
@@ -8899,11 +9000,11 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:J13"/>
@@ -8919,11 +9020,11 @@
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -8939,11 +9040,11 @@
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="M15:N15"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="I21:J21"/>
@@ -8959,11 +9060,11 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="M19:N19"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="I25:J25"/>
@@ -8979,11 +9080,11 @@
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I29:J29"/>
@@ -8999,11 +9100,11 @@
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="M27:N27"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="I33:J33"/>
@@ -9019,11 +9120,11 @@
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="M31:N31"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:N30"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="I37:J37"/>
@@ -9039,11 +9140,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="M35:N35"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="I41:J41"/>
@@ -9059,11 +9160,11 @@
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="F45:H45"/>
     <mergeCell ref="I45:J45"/>
@@ -9079,11 +9180,11 @@
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="M43:N43"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="M42:N42"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="I49:J49"/>
@@ -9099,11 +9200,11 @@
     <mergeCell ref="I47:J47"/>
     <mergeCell ref="K47:L47"/>
     <mergeCell ref="M47:N47"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="M46:N46"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="I53:J53"/>
@@ -9119,11 +9220,11 @@
     <mergeCell ref="I51:J51"/>
     <mergeCell ref="K51:L51"/>
     <mergeCell ref="M51:N51"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="F57:H57"/>
     <mergeCell ref="I57:J57"/>
@@ -9139,11 +9240,11 @@
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="K55:L55"/>
     <mergeCell ref="M55:N55"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="M54:N54"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="F61:H61"/>
     <mergeCell ref="I61:J61"/>
@@ -9159,11 +9260,11 @@
     <mergeCell ref="I59:J59"/>
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="M59:N59"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="F65:H65"/>
     <mergeCell ref="I65:J65"/>
@@ -9179,11 +9280,11 @@
     <mergeCell ref="I63:J63"/>
     <mergeCell ref="K63:L63"/>
     <mergeCell ref="M63:N63"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
     <mergeCell ref="C69:D69"/>
     <mergeCell ref="F69:H69"/>
     <mergeCell ref="I69:J69"/>
@@ -9199,11 +9300,11 @@
     <mergeCell ref="I67:J67"/>
     <mergeCell ref="K67:L67"/>
     <mergeCell ref="M67:N67"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="F74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="F73:H73"/>
     <mergeCell ref="I73:J73"/>
@@ -9219,11 +9320,11 @@
     <mergeCell ref="I71:J71"/>
     <mergeCell ref="K71:L71"/>
     <mergeCell ref="M71:N71"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
     <mergeCell ref="C77:D77"/>
     <mergeCell ref="F77:H77"/>
     <mergeCell ref="I77:J77"/>
@@ -9239,11 +9340,11 @@
     <mergeCell ref="I75:J75"/>
     <mergeCell ref="K75:L75"/>
     <mergeCell ref="M75:N75"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="F74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="M74:N74"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="F81:H81"/>
     <mergeCell ref="I81:J81"/>
@@ -9259,11 +9360,11 @@
     <mergeCell ref="I79:J79"/>
     <mergeCell ref="K79:L79"/>
     <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="M78:N78"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="I85:J85"/>
@@ -9279,11 +9380,11 @@
     <mergeCell ref="I83:J83"/>
     <mergeCell ref="K83:L83"/>
     <mergeCell ref="M83:N83"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="M82:N82"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="I89:J89"/>
@@ -9299,11 +9400,11 @@
     <mergeCell ref="I87:J87"/>
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="M87:N87"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
     <mergeCell ref="C93:D93"/>
     <mergeCell ref="F93:H93"/>
     <mergeCell ref="I93:J93"/>
@@ -9319,11 +9420,11 @@
     <mergeCell ref="I91:J91"/>
     <mergeCell ref="K91:L91"/>
     <mergeCell ref="M91:N91"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
     <mergeCell ref="C97:D97"/>
     <mergeCell ref="F97:H97"/>
     <mergeCell ref="I97:J97"/>
@@ -9339,11 +9440,11 @@
     <mergeCell ref="I95:J95"/>
     <mergeCell ref="K95:L95"/>
     <mergeCell ref="M95:N95"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="M94:N94"/>
     <mergeCell ref="C101:D101"/>
     <mergeCell ref="F101:H101"/>
     <mergeCell ref="I101:J101"/>
@@ -9359,11 +9460,11 @@
     <mergeCell ref="I99:J99"/>
     <mergeCell ref="K99:L99"/>
     <mergeCell ref="M99:N99"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="I106:J106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="M98:N98"/>
     <mergeCell ref="C105:D105"/>
     <mergeCell ref="F105:H105"/>
     <mergeCell ref="I105:J105"/>
@@ -9379,11 +9480,11 @@
     <mergeCell ref="I103:J103"/>
     <mergeCell ref="K103:L103"/>
     <mergeCell ref="M103:N103"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="I110:J110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
     <mergeCell ref="C109:D109"/>
     <mergeCell ref="F109:H109"/>
     <mergeCell ref="I109:J109"/>
@@ -9399,11 +9500,11 @@
     <mergeCell ref="I107:J107"/>
     <mergeCell ref="K107:L107"/>
     <mergeCell ref="M107:N107"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="I106:J106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="M106:N106"/>
     <mergeCell ref="C113:D113"/>
     <mergeCell ref="F113:H113"/>
     <mergeCell ref="I113:J113"/>
@@ -9419,11 +9520,11 @@
     <mergeCell ref="I111:J111"/>
     <mergeCell ref="K111:L111"/>
     <mergeCell ref="M111:N111"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="I118:J118"/>
-    <mergeCell ref="K118:L118"/>
-    <mergeCell ref="M118:N118"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="I110:J110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="M110:N110"/>
     <mergeCell ref="C117:D117"/>
     <mergeCell ref="F117:H117"/>
     <mergeCell ref="I117:J117"/>
@@ -9439,11 +9540,11 @@
     <mergeCell ref="I115:J115"/>
     <mergeCell ref="K115:L115"/>
     <mergeCell ref="M115:N115"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="M122:N122"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
     <mergeCell ref="C121:D121"/>
     <mergeCell ref="F121:H121"/>
     <mergeCell ref="I121:J121"/>
@@ -9459,11 +9560,11 @@
     <mergeCell ref="I119:J119"/>
     <mergeCell ref="K119:L119"/>
     <mergeCell ref="M119:N119"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="M126:N126"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="I118:J118"/>
+    <mergeCell ref="K118:L118"/>
+    <mergeCell ref="M118:N118"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="F125:H125"/>
     <mergeCell ref="I125:J125"/>
@@ -9479,11 +9580,11 @@
     <mergeCell ref="I123:J123"/>
     <mergeCell ref="K123:L123"/>
     <mergeCell ref="M123:N123"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="K130:L130"/>
-    <mergeCell ref="M130:N130"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="M122:N122"/>
     <mergeCell ref="C129:D129"/>
     <mergeCell ref="F129:H129"/>
     <mergeCell ref="I129:J129"/>
@@ -9499,11 +9600,11 @@
     <mergeCell ref="I127:J127"/>
     <mergeCell ref="K127:L127"/>
     <mergeCell ref="M127:N127"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="M134:N134"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="M126:N126"/>
     <mergeCell ref="C133:D133"/>
     <mergeCell ref="F133:H133"/>
     <mergeCell ref="I133:J133"/>
@@ -9519,11 +9620,11 @@
     <mergeCell ref="I131:J131"/>
     <mergeCell ref="K131:L131"/>
     <mergeCell ref="M131:N131"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="K130:L130"/>
+    <mergeCell ref="M130:N130"/>
     <mergeCell ref="C137:D137"/>
     <mergeCell ref="F137:H137"/>
     <mergeCell ref="I137:J137"/>
@@ -9539,11 +9640,11 @@
     <mergeCell ref="I135:J135"/>
     <mergeCell ref="K135:L135"/>
     <mergeCell ref="M135:N135"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="I142:J142"/>
-    <mergeCell ref="K142:L142"/>
-    <mergeCell ref="M142:N142"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="M134:N134"/>
     <mergeCell ref="C141:D141"/>
     <mergeCell ref="F141:H141"/>
     <mergeCell ref="I141:J141"/>
@@ -9559,11 +9660,11 @@
     <mergeCell ref="I139:J139"/>
     <mergeCell ref="K139:L139"/>
     <mergeCell ref="M139:N139"/>
-    <mergeCell ref="C146:D146"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="I146:J146"/>
-    <mergeCell ref="K146:L146"/>
-    <mergeCell ref="M146:N146"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="M138:N138"/>
     <mergeCell ref="C145:D145"/>
     <mergeCell ref="F145:H145"/>
     <mergeCell ref="I145:J145"/>
@@ -9579,11 +9680,11 @@
     <mergeCell ref="I143:J143"/>
     <mergeCell ref="K143:L143"/>
     <mergeCell ref="M143:N143"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="I150:J150"/>
-    <mergeCell ref="K150:L150"/>
-    <mergeCell ref="M150:N150"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="I142:J142"/>
+    <mergeCell ref="K142:L142"/>
+    <mergeCell ref="M142:N142"/>
     <mergeCell ref="C149:D149"/>
     <mergeCell ref="F149:H149"/>
     <mergeCell ref="I149:J149"/>
@@ -9599,11 +9700,11 @@
     <mergeCell ref="I147:J147"/>
     <mergeCell ref="K147:L147"/>
     <mergeCell ref="M147:N147"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="M154:N154"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="K146:L146"/>
+    <mergeCell ref="M146:N146"/>
     <mergeCell ref="C153:D153"/>
     <mergeCell ref="F153:H153"/>
     <mergeCell ref="I153:J153"/>
@@ -9619,11 +9720,11 @@
     <mergeCell ref="I151:J151"/>
     <mergeCell ref="K151:L151"/>
     <mergeCell ref="M151:N151"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="I158:J158"/>
-    <mergeCell ref="K158:L158"/>
-    <mergeCell ref="M158:N158"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="K150:L150"/>
+    <mergeCell ref="M150:N150"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="F157:H157"/>
     <mergeCell ref="I157:J157"/>
@@ -9639,11 +9740,11 @@
     <mergeCell ref="I155:J155"/>
     <mergeCell ref="K155:L155"/>
     <mergeCell ref="M155:N155"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="F162:H162"/>
-    <mergeCell ref="I162:J162"/>
-    <mergeCell ref="K162:L162"/>
-    <mergeCell ref="M162:N162"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="M154:N154"/>
     <mergeCell ref="C161:D161"/>
     <mergeCell ref="F161:H161"/>
     <mergeCell ref="I161:J161"/>
@@ -9659,11 +9760,11 @@
     <mergeCell ref="I159:J159"/>
     <mergeCell ref="K159:L159"/>
     <mergeCell ref="M159:N159"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="I166:J166"/>
-    <mergeCell ref="K166:L166"/>
-    <mergeCell ref="M166:N166"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="I158:J158"/>
+    <mergeCell ref="K158:L158"/>
+    <mergeCell ref="M158:N158"/>
     <mergeCell ref="C165:D165"/>
     <mergeCell ref="F165:H165"/>
     <mergeCell ref="I165:J165"/>
@@ -9679,11 +9780,11 @@
     <mergeCell ref="I163:J163"/>
     <mergeCell ref="K163:L163"/>
     <mergeCell ref="M163:N163"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="F170:H170"/>
-    <mergeCell ref="I170:J170"/>
-    <mergeCell ref="K170:L170"/>
-    <mergeCell ref="M170:N170"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="F162:H162"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="K162:L162"/>
+    <mergeCell ref="M162:N162"/>
     <mergeCell ref="C169:D169"/>
     <mergeCell ref="F169:H169"/>
     <mergeCell ref="I169:J169"/>
@@ -9699,11 +9800,11 @@
     <mergeCell ref="I167:J167"/>
     <mergeCell ref="K167:L167"/>
     <mergeCell ref="M167:N167"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="F174:H174"/>
-    <mergeCell ref="I174:J174"/>
-    <mergeCell ref="K174:L174"/>
-    <mergeCell ref="M174:N174"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="I166:J166"/>
+    <mergeCell ref="K166:L166"/>
+    <mergeCell ref="M166:N166"/>
     <mergeCell ref="C173:D173"/>
     <mergeCell ref="F173:H173"/>
     <mergeCell ref="I173:J173"/>
@@ -9719,11 +9820,11 @@
     <mergeCell ref="I171:J171"/>
     <mergeCell ref="K171:L171"/>
     <mergeCell ref="M171:N171"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="I178:J178"/>
-    <mergeCell ref="K178:L178"/>
-    <mergeCell ref="M178:N178"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="F170:H170"/>
+    <mergeCell ref="I170:J170"/>
+    <mergeCell ref="K170:L170"/>
+    <mergeCell ref="M170:N170"/>
     <mergeCell ref="C177:D177"/>
     <mergeCell ref="F177:H177"/>
     <mergeCell ref="I177:J177"/>
@@ -9739,11 +9840,11 @@
     <mergeCell ref="I175:J175"/>
     <mergeCell ref="K175:L175"/>
     <mergeCell ref="M175:N175"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="F182:H182"/>
-    <mergeCell ref="I182:J182"/>
-    <mergeCell ref="K182:L182"/>
-    <mergeCell ref="M182:N182"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="F174:H174"/>
+    <mergeCell ref="I174:J174"/>
+    <mergeCell ref="K174:L174"/>
+    <mergeCell ref="M174:N174"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="F181:H181"/>
     <mergeCell ref="I181:J181"/>
@@ -9759,11 +9860,11 @@
     <mergeCell ref="I179:J179"/>
     <mergeCell ref="K179:L179"/>
     <mergeCell ref="M179:N179"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="I186:J186"/>
-    <mergeCell ref="K186:L186"/>
-    <mergeCell ref="M186:N186"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="I178:J178"/>
+    <mergeCell ref="K178:L178"/>
+    <mergeCell ref="M178:N178"/>
     <mergeCell ref="C185:D185"/>
     <mergeCell ref="F185:H185"/>
     <mergeCell ref="I185:J185"/>
@@ -9779,11 +9880,11 @@
     <mergeCell ref="I183:J183"/>
     <mergeCell ref="K183:L183"/>
     <mergeCell ref="M183:N183"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="I190:J190"/>
-    <mergeCell ref="K190:L190"/>
-    <mergeCell ref="M190:N190"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="F182:H182"/>
+    <mergeCell ref="I182:J182"/>
+    <mergeCell ref="K182:L182"/>
+    <mergeCell ref="M182:N182"/>
     <mergeCell ref="C189:D189"/>
     <mergeCell ref="F189:H189"/>
     <mergeCell ref="I189:J189"/>
@@ -9799,11 +9900,11 @@
     <mergeCell ref="I187:J187"/>
     <mergeCell ref="K187:L187"/>
     <mergeCell ref="M187:N187"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="F194:H194"/>
-    <mergeCell ref="I194:J194"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="M194:N194"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="I186:J186"/>
+    <mergeCell ref="K186:L186"/>
+    <mergeCell ref="M186:N186"/>
     <mergeCell ref="C193:D193"/>
     <mergeCell ref="F193:H193"/>
     <mergeCell ref="I193:J193"/>
@@ -9819,11 +9920,11 @@
     <mergeCell ref="I191:J191"/>
     <mergeCell ref="K191:L191"/>
     <mergeCell ref="M191:N191"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:H198"/>
-    <mergeCell ref="I198:J198"/>
-    <mergeCell ref="K198:L198"/>
-    <mergeCell ref="M198:N198"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="K190:L190"/>
+    <mergeCell ref="M190:N190"/>
     <mergeCell ref="C197:D197"/>
     <mergeCell ref="F197:H197"/>
     <mergeCell ref="I197:J197"/>
@@ -9839,11 +9940,11 @@
     <mergeCell ref="I195:J195"/>
     <mergeCell ref="K195:L195"/>
     <mergeCell ref="M195:N195"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="F202:H202"/>
-    <mergeCell ref="I202:J202"/>
-    <mergeCell ref="K202:L202"/>
-    <mergeCell ref="M202:N202"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="F194:H194"/>
+    <mergeCell ref="I194:J194"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="M194:N194"/>
     <mergeCell ref="C201:D201"/>
     <mergeCell ref="F201:H201"/>
     <mergeCell ref="I201:J201"/>
@@ -9859,11 +9960,11 @@
     <mergeCell ref="I199:J199"/>
     <mergeCell ref="K199:L199"/>
     <mergeCell ref="M199:N199"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:H206"/>
-    <mergeCell ref="I206:J206"/>
-    <mergeCell ref="K206:L206"/>
-    <mergeCell ref="M206:N206"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:H198"/>
+    <mergeCell ref="I198:J198"/>
+    <mergeCell ref="K198:L198"/>
+    <mergeCell ref="M198:N198"/>
     <mergeCell ref="C205:D205"/>
     <mergeCell ref="F205:H205"/>
     <mergeCell ref="I205:J205"/>
@@ -9879,11 +9980,11 @@
     <mergeCell ref="I203:J203"/>
     <mergeCell ref="K203:L203"/>
     <mergeCell ref="M203:N203"/>
-    <mergeCell ref="C210:D210"/>
-    <mergeCell ref="F210:H210"/>
-    <mergeCell ref="I210:J210"/>
-    <mergeCell ref="K210:L210"/>
-    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="F202:H202"/>
+    <mergeCell ref="I202:J202"/>
+    <mergeCell ref="K202:L202"/>
+    <mergeCell ref="M202:N202"/>
     <mergeCell ref="C209:D209"/>
     <mergeCell ref="F209:H209"/>
     <mergeCell ref="I209:J209"/>
@@ -9899,16 +10000,16 @@
     <mergeCell ref="I207:J207"/>
     <mergeCell ref="K207:L207"/>
     <mergeCell ref="M207:N207"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="H214:I214"/>
-    <mergeCell ref="J214:K214"/>
-    <mergeCell ref="L214:M214"/>
-    <mergeCell ref="A214:B214"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="H213:I213"/>
-    <mergeCell ref="J213:K213"/>
-    <mergeCell ref="L213:M213"/>
-    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:H206"/>
+    <mergeCell ref="I206:J206"/>
+    <mergeCell ref="K206:L206"/>
+    <mergeCell ref="M206:N206"/>
+    <mergeCell ref="C213:D213"/>
+    <mergeCell ref="F213:H213"/>
+    <mergeCell ref="I213:J213"/>
+    <mergeCell ref="K213:L213"/>
+    <mergeCell ref="M213:N213"/>
     <mergeCell ref="C212:D212"/>
     <mergeCell ref="F212:H212"/>
     <mergeCell ref="I212:J212"/>
@@ -9919,6 +10020,31 @@
     <mergeCell ref="I211:J211"/>
     <mergeCell ref="K211:L211"/>
     <mergeCell ref="M211:N211"/>
+    <mergeCell ref="C210:D210"/>
+    <mergeCell ref="F210:H210"/>
+    <mergeCell ref="I210:J210"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="H217:I217"/>
+    <mergeCell ref="J217:K217"/>
+    <mergeCell ref="L217:M217"/>
+    <mergeCell ref="A217:B217"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="H216:I216"/>
+    <mergeCell ref="J216:K216"/>
+    <mergeCell ref="L216:M216"/>
+    <mergeCell ref="A216:B216"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:H215"/>
+    <mergeCell ref="I215:J215"/>
+    <mergeCell ref="K215:L215"/>
+    <mergeCell ref="M215:N215"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="F214:H214"/>
+    <mergeCell ref="I214:J214"/>
+    <mergeCell ref="K214:L214"/>
+    <mergeCell ref="M214:N214"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14160" windowHeight="8295"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18915" windowHeight="8295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="384">
   <si>
     <t/>
   </si>
@@ -1157,6 +1157,30 @@
     <t>105 Digital Dr  Novato CA 94949</t>
   </si>
   <si>
+    <t>Grocery Delivery E-Services USA, Inc. dba HelloFresh</t>
+  </si>
+  <si>
+    <t>2041 Factory Street  Richmond CA 94801</t>
+  </si>
+  <si>
+    <t>King's Fish House</t>
+  </si>
+  <si>
+    <t>12427 North Main Street  Rancho Cucamonga CA 91739</t>
+  </si>
+  <si>
+    <t>Clear Capital</t>
+  </si>
+  <si>
+    <t>1410 Rocky Ridge Drive, Suite 250  Roseville CA 95661</t>
+  </si>
+  <si>
+    <t>Keeco, LLC</t>
+  </si>
+  <si>
+    <t>1420 N. Tamarind Avenue  Rialto CA 92376</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1179,15 +1203,15 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>WARN Summary</t>
   </si>
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 10/10/2022
+ End Date: 10/12/2022
 </t>
-  </si>
-  <si>
-    <t>WARN Summary</t>
   </si>
   <si>
     <t>Report Summary</t>
@@ -1259,13 +1283,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFDCDCDC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFDCDCDC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1566,6 +1590,19 @@
         <color rgb="FFA9A9A9"/>
       </top>
       <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -1583,24 +1620,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9A9A9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9A9A9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -1621,17 +1645,14 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1655,25 +1676,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1739,10 +1760,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2025,48 +2046,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R217"/>
+  <dimension ref="A1:R221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="2.140625" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
     <col min="10" max="10" width="7.28515625" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" customWidth="1"/>
-    <col min="13" max="13" width="5.140625" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="11" max="11" width="5.85546875" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="49" t="s">
-        <v>374</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
+      <c r="A1" s="47" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
     </row>
-    <row r="2" spans="1:18" ht="38.25" customHeight="1">
+    <row r="2" spans="1:18" ht="37.5" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -2087,68 +2108,68 @@
       <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="43"/>
+      <c r="E3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43" t="s">
+      <c r="G3" s="44"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="43" t="s">
+      <c r="J3" s="43"/>
+      <c r="K3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="44"/>
-      <c r="M3" s="46" t="s">
+      <c r="L3" s="43"/>
+      <c r="M3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="47"/>
+      <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:18" ht="24.75">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="38"/>
+      <c r="E4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="38" t="s">
+      <c r="G4" s="39"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="38" t="s">
+      <c r="J4" s="38"/>
+      <c r="K4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="41" t="s">
+      <c r="L4" s="38"/>
+      <c r="M4" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="42"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
@@ -2157,30 +2178,30 @@
       <c r="B5" s="2">
         <v>44727</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>44750</v>
       </c>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="2">
         <v>44897</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="29"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="31">
+      <c r="J5" s="27"/>
+      <c r="K5" s="30">
         <v>2</v>
       </c>
-      <c r="L5" s="28"/>
-      <c r="M5" s="32" t="s">
+      <c r="L5" s="27"/>
+      <c r="M5" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="33"/>
+      <c r="N5" s="32"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
@@ -2189,30 +2210,30 @@
       <c r="B6" s="4">
         <v>44736</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>44750</v>
       </c>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="4">
         <v>44794</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="35" t="s">
+      <c r="G6" s="29"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="36">
+      <c r="J6" s="27"/>
+      <c r="K6" s="35">
         <v>13</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="37" t="s">
+      <c r="L6" s="27"/>
+      <c r="M6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="33"/>
+      <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
@@ -2221,30 +2242,30 @@
       <c r="B7" s="2">
         <v>44735</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>44750</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="2">
         <v>44796</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="31">
+      <c r="G7" s="29"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="27"/>
+      <c r="K7" s="30">
         <v>9</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="32" t="s">
+      <c r="L7" s="27"/>
+      <c r="M7" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="33"/>
+      <c r="N7" s="32"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
@@ -2253,30 +2274,30 @@
       <c r="B8" s="4">
         <v>44735</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>44750</v>
       </c>
-      <c r="D8" s="28"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="4">
         <v>44796</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="36">
+      <c r="G8" s="29"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="27"/>
+      <c r="K8" s="35">
         <v>123</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="37" t="s">
+      <c r="L8" s="27"/>
+      <c r="M8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="33"/>
+      <c r="N8" s="32"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
@@ -2285,30 +2306,30 @@
       <c r="B9" s="2">
         <v>44735</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>44750</v>
       </c>
-      <c r="D9" s="28"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="2">
         <v>44796</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="31">
+      <c r="G9" s="29"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="27"/>
+      <c r="K9" s="30">
         <v>37</v>
       </c>
-      <c r="L9" s="28"/>
-      <c r="M9" s="32" t="s">
+      <c r="L9" s="27"/>
+      <c r="M9" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="33"/>
+      <c r="N9" s="32"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -2317,30 +2338,30 @@
       <c r="B10" s="4">
         <v>44727</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <v>44753</v>
       </c>
-      <c r="D10" s="28"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="4">
         <v>44784</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="36">
+      <c r="G10" s="29"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="35">
         <v>37</v>
       </c>
-      <c r="L10" s="28"/>
-      <c r="M10" s="37" t="s">
+      <c r="L10" s="27"/>
+      <c r="M10" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="33"/>
+      <c r="N10" s="32"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
@@ -2349,30 +2370,30 @@
       <c r="B11" s="2">
         <v>44739</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>44753</v>
       </c>
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="2">
         <v>44799</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="31">
+      <c r="G11" s="29"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="30">
         <v>80</v>
       </c>
-      <c r="L11" s="28"/>
-      <c r="M11" s="32" t="s">
+      <c r="L11" s="27"/>
+      <c r="M11" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="33"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
@@ -2381,30 +2402,30 @@
       <c r="B12" s="4">
         <v>44741</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>44753</v>
       </c>
-      <c r="D12" s="28"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="4">
         <v>44800</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="35" t="s">
+      <c r="G12" s="29"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="28"/>
-      <c r="K12" s="36">
+      <c r="J12" s="27"/>
+      <c r="K12" s="35">
         <v>229</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="37" t="s">
+      <c r="L12" s="27"/>
+      <c r="M12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="33"/>
+      <c r="N12" s="32"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
@@ -2413,30 +2434,30 @@
       <c r="B13" s="2">
         <v>44743</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>44753</v>
       </c>
-      <c r="D13" s="28"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="2">
         <v>44766</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="31">
+      <c r="G13" s="29"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="27"/>
+      <c r="K13" s="30">
         <v>368</v>
       </c>
-      <c r="L13" s="28"/>
-      <c r="M13" s="32" t="s">
+      <c r="L13" s="27"/>
+      <c r="M13" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="33"/>
+      <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -2445,30 +2466,30 @@
       <c r="B14" s="4">
         <v>44739</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>44753</v>
       </c>
-      <c r="D14" s="28"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="4">
         <v>44799</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="36">
+      <c r="G14" s="29"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="35">
         <v>62</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="37" t="s">
+      <c r="L14" s="27"/>
+      <c r="M14" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="33"/>
+      <c r="N14" s="32"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
@@ -2477,30 +2498,30 @@
       <c r="B15" s="2">
         <v>44727</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>44753</v>
       </c>
-      <c r="D15" s="28"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="2">
         <v>44784</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="31">
+      <c r="G15" s="29"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="27"/>
+      <c r="K15" s="30">
         <v>25</v>
       </c>
-      <c r="L15" s="28"/>
-      <c r="M15" s="32" t="s">
+      <c r="L15" s="27"/>
+      <c r="M15" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="33"/>
+      <c r="N15" s="32"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
@@ -2509,30 +2530,30 @@
       <c r="B16" s="4">
         <v>44727</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>44753</v>
       </c>
-      <c r="D16" s="28"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="4">
         <v>44784</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="36">
+      <c r="G16" s="29"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="27"/>
+      <c r="K16" s="35">
         <v>68</v>
       </c>
-      <c r="L16" s="28"/>
-      <c r="M16" s="37" t="s">
+      <c r="L16" s="27"/>
+      <c r="M16" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="33"/>
+      <c r="N16" s="32"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2541,30 +2562,30 @@
       <c r="B17" s="2">
         <v>44741</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>44753</v>
       </c>
-      <c r="D17" s="28"/>
+      <c r="D17" s="27"/>
       <c r="E17" s="2">
         <v>44801</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="31">
+      <c r="G17" s="29"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="27"/>
+      <c r="K17" s="30">
         <v>77</v>
       </c>
-      <c r="L17" s="28"/>
-      <c r="M17" s="32" t="s">
+      <c r="L17" s="27"/>
+      <c r="M17" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="33"/>
+      <c r="N17" s="32"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
@@ -2573,30 +2594,30 @@
       <c r="B18" s="4">
         <v>44739</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="33">
         <v>44754</v>
       </c>
-      <c r="D18" s="28"/>
+      <c r="D18" s="27"/>
       <c r="E18" s="4">
         <v>44800</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="36">
+      <c r="G18" s="29"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="27"/>
+      <c r="K18" s="35">
         <v>20</v>
       </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="37" t="s">
+      <c r="L18" s="27"/>
+      <c r="M18" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="33"/>
+      <c r="N18" s="32"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
@@ -2605,30 +2626,30 @@
       <c r="B19" s="2">
         <v>44739</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>44754</v>
       </c>
-      <c r="D19" s="28"/>
+      <c r="D19" s="27"/>
       <c r="E19" s="2">
         <v>44800</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="30"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="31">
+      <c r="G19" s="29"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="27"/>
+      <c r="K19" s="30">
         <v>5</v>
       </c>
-      <c r="L19" s="28"/>
-      <c r="M19" s="32" t="s">
+      <c r="L19" s="27"/>
+      <c r="M19" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="33"/>
+      <c r="N19" s="32"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
@@ -2637,30 +2658,30 @@
       <c r="B20" s="4">
         <v>44739</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>44754</v>
       </c>
-      <c r="D20" s="28"/>
+      <c r="D20" s="27"/>
       <c r="E20" s="4">
         <v>44800</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="36">
+      <c r="G20" s="29"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="27"/>
+      <c r="K20" s="35">
         <v>2</v>
       </c>
-      <c r="L20" s="28"/>
-      <c r="M20" s="37" t="s">
+      <c r="L20" s="27"/>
+      <c r="M20" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="N20" s="33"/>
+      <c r="N20" s="32"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
@@ -2669,30 +2690,30 @@
       <c r="B21" s="2">
         <v>44739</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>44754</v>
       </c>
-      <c r="D21" s="28"/>
+      <c r="D21" s="27"/>
       <c r="E21" s="2">
         <v>44800</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="31">
+      <c r="G21" s="29"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="27"/>
+      <c r="K21" s="30">
         <v>1</v>
       </c>
-      <c r="L21" s="28"/>
-      <c r="M21" s="32" t="s">
+      <c r="L21" s="27"/>
+      <c r="M21" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="33"/>
+      <c r="N21" s="32"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
@@ -2701,30 +2722,30 @@
       <c r="B22" s="4">
         <v>44739</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>44754</v>
       </c>
-      <c r="D22" s="28"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="4">
         <v>44800</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="36">
+      <c r="G22" s="29"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="27"/>
+      <c r="K22" s="35">
         <v>41</v>
       </c>
-      <c r="L22" s="28"/>
-      <c r="M22" s="37" t="s">
+      <c r="L22" s="27"/>
+      <c r="M22" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="33"/>
+      <c r="N22" s="32"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
@@ -2733,30 +2754,30 @@
       <c r="B23" s="2">
         <v>44743</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>44754</v>
       </c>
-      <c r="D23" s="28"/>
+      <c r="D23" s="27"/>
       <c r="E23" s="2">
         <v>44804</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29" t="s">
+      <c r="G23" s="29"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="31">
+      <c r="J23" s="27"/>
+      <c r="K23" s="30">
         <v>4</v>
       </c>
-      <c r="L23" s="28"/>
-      <c r="M23" s="32" t="s">
+      <c r="L23" s="27"/>
+      <c r="M23" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="33"/>
+      <c r="N23" s="32"/>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
@@ -2765,30 +2786,30 @@
       <c r="B24" s="4">
         <v>44732</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>44754</v>
       </c>
-      <c r="D24" s="28"/>
+      <c r="D24" s="27"/>
       <c r="E24" s="4">
         <v>44926</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="36">
+      <c r="G24" s="29"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="27"/>
+      <c r="K24" s="35">
         <v>211</v>
       </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="37" t="s">
+      <c r="L24" s="27"/>
+      <c r="M24" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="33"/>
+      <c r="N24" s="32"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
@@ -2797,30 +2818,30 @@
       <c r="B25" s="2">
         <v>44743</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>44754</v>
       </c>
-      <c r="D25" s="28"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="2">
         <v>44804</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29" t="s">
+      <c r="G25" s="29"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="31">
+      <c r="J25" s="27"/>
+      <c r="K25" s="30">
         <v>10</v>
       </c>
-      <c r="L25" s="28"/>
-      <c r="M25" s="32" t="s">
+      <c r="L25" s="27"/>
+      <c r="M25" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="33"/>
+      <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
@@ -2829,30 +2850,30 @@
       <c r="B26" s="4">
         <v>44743</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <v>44754</v>
       </c>
-      <c r="D26" s="28"/>
+      <c r="D26" s="27"/>
       <c r="E26" s="4">
         <v>44804</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="30"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="35" t="s">
+      <c r="G26" s="29"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="36">
+      <c r="J26" s="27"/>
+      <c r="K26" s="35">
         <v>1</v>
       </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="37" t="s">
+      <c r="L26" s="27"/>
+      <c r="M26" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="33"/>
+      <c r="N26" s="32"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
@@ -2861,30 +2882,30 @@
       <c r="B27" s="2">
         <v>44742</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>44754</v>
       </c>
-      <c r="D27" s="28"/>
+      <c r="D27" s="27"/>
       <c r="E27" s="2">
         <v>44802</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="30"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="31">
+      <c r="G27" s="29"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="27"/>
+      <c r="K27" s="30">
         <v>94</v>
       </c>
-      <c r="L27" s="28"/>
-      <c r="M27" s="32" t="s">
+      <c r="L27" s="27"/>
+      <c r="M27" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="33"/>
+      <c r="N27" s="32"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
@@ -2893,30 +2914,30 @@
       <c r="B28" s="4">
         <v>44743</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <v>44754</v>
       </c>
-      <c r="D28" s="28"/>
+      <c r="D28" s="27"/>
       <c r="E28" s="4">
         <v>44804</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="35" t="s">
+      <c r="G28" s="29"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="36">
+      <c r="J28" s="27"/>
+      <c r="K28" s="35">
         <v>9</v>
       </c>
-      <c r="L28" s="28"/>
-      <c r="M28" s="37" t="s">
+      <c r="L28" s="27"/>
+      <c r="M28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="N28" s="33"/>
+      <c r="N28" s="32"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
@@ -2925,30 +2946,30 @@
       <c r="B29" s="2">
         <v>44743</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>44754</v>
       </c>
-      <c r="D29" s="28"/>
+      <c r="D29" s="27"/>
       <c r="E29" s="2">
         <v>44804</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="30"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29" t="s">
+      <c r="G29" s="29"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="31">
+      <c r="J29" s="27"/>
+      <c r="K29" s="30">
         <v>6</v>
       </c>
-      <c r="L29" s="28"/>
-      <c r="M29" s="32" t="s">
+      <c r="L29" s="27"/>
+      <c r="M29" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="33"/>
+      <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
@@ -2957,30 +2978,30 @@
       <c r="B30" s="4">
         <v>44743</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="33">
         <v>44754</v>
       </c>
-      <c r="D30" s="28"/>
+      <c r="D30" s="27"/>
       <c r="E30" s="4">
         <v>44804</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="35" t="s">
+      <c r="G30" s="29"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="36">
-        <v>18</v>
-      </c>
-      <c r="L30" s="28"/>
-      <c r="M30" s="37" t="s">
+      <c r="J30" s="27"/>
+      <c r="K30" s="35">
+        <v>18</v>
+      </c>
+      <c r="L30" s="27"/>
+      <c r="M30" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="33"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
@@ -2989,30 +3010,30 @@
       <c r="B31" s="2">
         <v>44743</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>44755</v>
       </c>
-      <c r="D31" s="28"/>
+      <c r="D31" s="27"/>
       <c r="E31" s="2">
         <v>44804</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="30"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="29" t="s">
+      <c r="G31" s="29"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="28"/>
-      <c r="K31" s="31">
+      <c r="J31" s="27"/>
+      <c r="K31" s="30">
         <v>76</v>
       </c>
-      <c r="L31" s="28"/>
-      <c r="M31" s="32" t="s">
+      <c r="L31" s="27"/>
+      <c r="M31" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="33"/>
+      <c r="N31" s="32"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
@@ -3021,30 +3042,30 @@
       <c r="B32" s="4">
         <v>44743</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="33">
         <v>44755</v>
       </c>
-      <c r="D32" s="28"/>
+      <c r="D32" s="27"/>
       <c r="E32" s="4">
         <v>44804</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="30"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="35" t="s">
+      <c r="G32" s="29"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="28"/>
-      <c r="K32" s="36">
+      <c r="J32" s="27"/>
+      <c r="K32" s="35">
         <v>1</v>
       </c>
-      <c r="L32" s="28"/>
-      <c r="M32" s="37" t="s">
+      <c r="L32" s="27"/>
+      <c r="M32" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="N32" s="33"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
@@ -3053,30 +3074,30 @@
       <c r="B33" s="2">
         <v>44743</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <v>44755</v>
       </c>
-      <c r="D33" s="28"/>
+      <c r="D33" s="27"/>
       <c r="E33" s="2">
         <v>44804</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="29" t="s">
+      <c r="G33" s="29"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="28"/>
-      <c r="K33" s="31">
+      <c r="J33" s="27"/>
+      <c r="K33" s="30">
         <v>27</v>
       </c>
-      <c r="L33" s="28"/>
-      <c r="M33" s="32" t="s">
+      <c r="L33" s="27"/>
+      <c r="M33" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="N33" s="33"/>
+      <c r="N33" s="32"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -3085,30 +3106,30 @@
       <c r="B34" s="4">
         <v>44743</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="33">
         <v>44755</v>
       </c>
-      <c r="D34" s="28"/>
+      <c r="D34" s="27"/>
       <c r="E34" s="4">
         <v>44804</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="30"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="35" t="s">
+      <c r="G34" s="29"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="36">
+      <c r="J34" s="27"/>
+      <c r="K34" s="35">
         <v>2</v>
       </c>
-      <c r="L34" s="28"/>
-      <c r="M34" s="37" t="s">
+      <c r="L34" s="27"/>
+      <c r="M34" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="N34" s="33"/>
+      <c r="N34" s="32"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
@@ -3117,30 +3138,30 @@
       <c r="B35" s="2">
         <v>44747</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="26">
         <v>44756</v>
       </c>
-      <c r="D35" s="28"/>
+      <c r="D35" s="27"/>
       <c r="E35" s="2">
         <v>44788</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="30"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="28"/>
-      <c r="K35" s="31">
+      <c r="G35" s="29"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="27"/>
+      <c r="K35" s="30">
         <v>54</v>
       </c>
-      <c r="L35" s="28"/>
-      <c r="M35" s="32" t="s">
+      <c r="L35" s="27"/>
+      <c r="M35" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="33"/>
+      <c r="N35" s="32"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -3149,30 +3170,30 @@
       <c r="B36" s="4">
         <v>44743</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <v>44756</v>
       </c>
-      <c r="D36" s="28"/>
+      <c r="D36" s="27"/>
       <c r="E36" s="4">
         <v>44799</v>
       </c>
-      <c r="F36" s="35" t="s">
+      <c r="F36" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="30"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="28"/>
-      <c r="K36" s="36">
+      <c r="G36" s="29"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="27"/>
+      <c r="K36" s="35">
         <v>105</v>
       </c>
-      <c r="L36" s="28"/>
-      <c r="M36" s="37" t="s">
+      <c r="L36" s="27"/>
+      <c r="M36" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
@@ -3181,30 +3202,30 @@
       <c r="B37" s="2">
         <v>44743</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="26">
         <v>44756</v>
       </c>
-      <c r="D37" s="28"/>
+      <c r="D37" s="27"/>
       <c r="E37" s="2">
         <v>44799</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="30"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="28"/>
-      <c r="K37" s="31">
+      <c r="G37" s="29"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="27"/>
+      <c r="K37" s="30">
         <v>71</v>
       </c>
-      <c r="L37" s="28"/>
-      <c r="M37" s="32" t="s">
+      <c r="L37" s="27"/>
+      <c r="M37" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="N37" s="33"/>
+      <c r="N37" s="32"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -3213,30 +3234,30 @@
       <c r="B38" s="4">
         <v>44748</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="33">
         <v>44756</v>
       </c>
-      <c r="D38" s="28"/>
+      <c r="D38" s="27"/>
       <c r="E38" s="4">
         <v>44809</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="30"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="28"/>
-      <c r="K38" s="36">
+      <c r="G38" s="29"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="27"/>
+      <c r="K38" s="35">
         <v>125</v>
       </c>
-      <c r="L38" s="28"/>
-      <c r="M38" s="37" t="s">
+      <c r="L38" s="27"/>
+      <c r="M38" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="N38" s="33"/>
+      <c r="N38" s="32"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
@@ -3245,30 +3266,30 @@
       <c r="B39" s="2">
         <v>44753</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="26">
         <v>44756</v>
       </c>
-      <c r="D39" s="28"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="2">
         <v>44813</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="31">
+      <c r="G39" s="29"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="27"/>
+      <c r="K39" s="30">
         <v>55</v>
       </c>
-      <c r="L39" s="28"/>
-      <c r="M39" s="32" t="s">
+      <c r="L39" s="27"/>
+      <c r="M39" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="N39" s="33"/>
+      <c r="N39" s="32"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
@@ -3277,30 +3298,30 @@
       <c r="B40" s="4">
         <v>44743</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="33">
         <v>44756</v>
       </c>
-      <c r="D40" s="28"/>
+      <c r="D40" s="27"/>
       <c r="E40" s="4">
         <v>44799</v>
       </c>
-      <c r="F40" s="35" t="s">
+      <c r="F40" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="28"/>
-      <c r="K40" s="36">
+      <c r="G40" s="29"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="27"/>
+      <c r="K40" s="35">
         <v>176</v>
       </c>
-      <c r="L40" s="28"/>
-      <c r="M40" s="37" t="s">
+      <c r="L40" s="27"/>
+      <c r="M40" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="N40" s="33"/>
+      <c r="N40" s="32"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
@@ -3309,30 +3330,30 @@
       <c r="B41" s="2">
         <v>44749</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="26">
         <v>44757</v>
       </c>
-      <c r="D41" s="28"/>
+      <c r="D41" s="27"/>
       <c r="E41" s="2">
         <v>44809</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="28"/>
-      <c r="K41" s="31">
+      <c r="G41" s="29"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="27"/>
+      <c r="K41" s="30">
         <v>58</v>
       </c>
-      <c r="L41" s="28"/>
-      <c r="M41" s="32" t="s">
+      <c r="L41" s="27"/>
+      <c r="M41" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="33"/>
+      <c r="N41" s="32"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3" t="s">
@@ -3341,30 +3362,30 @@
       <c r="B42" s="4">
         <v>44749</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="33">
         <v>44757</v>
       </c>
-      <c r="D42" s="28"/>
+      <c r="D42" s="27"/>
       <c r="E42" s="4">
         <v>44810</v>
       </c>
-      <c r="F42" s="35" t="s">
+      <c r="F42" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="G42" s="30"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="28"/>
-      <c r="K42" s="36">
+      <c r="G42" s="29"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="27"/>
+      <c r="K42" s="35">
         <v>180</v>
       </c>
-      <c r="L42" s="28"/>
-      <c r="M42" s="37" t="s">
+      <c r="L42" s="27"/>
+      <c r="M42" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="N42" s="33"/>
+      <c r="N42" s="32"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
@@ -3373,30 +3394,30 @@
       <c r="B43" s="2">
         <v>44749</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="26">
         <v>44760</v>
       </c>
-      <c r="D43" s="28"/>
+      <c r="D43" s="27"/>
       <c r="E43" s="2">
         <v>44813</v>
       </c>
-      <c r="F43" s="29" t="s">
+      <c r="F43" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="30"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="29" t="s">
+      <c r="G43" s="29"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="28"/>
-      <c r="K43" s="31">
+      <c r="J43" s="27"/>
+      <c r="K43" s="30">
         <v>142</v>
       </c>
-      <c r="L43" s="28"/>
-      <c r="M43" s="32" t="s">
+      <c r="L43" s="27"/>
+      <c r="M43" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="N43" s="33"/>
+      <c r="N43" s="32"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="3" t="s">
@@ -3405,30 +3426,30 @@
       <c r="B44" s="4">
         <v>44753</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="33">
         <v>44760</v>
       </c>
-      <c r="D44" s="28"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="4">
         <v>44804</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F44" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="30"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="35" t="s">
+      <c r="G44" s="29"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="28"/>
-      <c r="K44" s="36">
+      <c r="J44" s="27"/>
+      <c r="K44" s="35">
         <v>153</v>
       </c>
-      <c r="L44" s="28"/>
-      <c r="M44" s="37" t="s">
+      <c r="L44" s="27"/>
+      <c r="M44" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="N44" s="33"/>
+      <c r="N44" s="32"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
@@ -3437,30 +3458,30 @@
       <c r="B45" s="2">
         <v>44754</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="26">
         <v>44761</v>
       </c>
-      <c r="D45" s="28"/>
+      <c r="D45" s="27"/>
       <c r="E45" s="2">
         <v>44820</v>
       </c>
-      <c r="F45" s="29" t="s">
+      <c r="F45" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="30"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="28"/>
-      <c r="K45" s="31">
+      <c r="G45" s="29"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="27"/>
+      <c r="K45" s="30">
         <v>12</v>
       </c>
-      <c r="L45" s="28"/>
-      <c r="M45" s="32" t="s">
+      <c r="L45" s="27"/>
+      <c r="M45" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="N45" s="33"/>
+      <c r="N45" s="32"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="3" t="s">
@@ -3469,30 +3490,30 @@
       <c r="B46" s="4">
         <v>44749</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="33">
         <v>44761</v>
       </c>
-      <c r="D46" s="28"/>
+      <c r="D46" s="27"/>
       <c r="E46" s="4">
         <v>44749</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="30"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="28"/>
-      <c r="K46" s="36">
+      <c r="G46" s="29"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="27"/>
+      <c r="K46" s="35">
         <v>27</v>
       </c>
-      <c r="L46" s="28"/>
-      <c r="M46" s="37" t="s">
+      <c r="L46" s="27"/>
+      <c r="M46" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="N46" s="33"/>
+      <c r="N46" s="32"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
@@ -3501,30 +3522,30 @@
       <c r="B47" s="2">
         <v>44749</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="26">
         <v>44761</v>
       </c>
-      <c r="D47" s="28"/>
+      <c r="D47" s="27"/>
       <c r="E47" s="2">
         <v>44749</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="30"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="28"/>
-      <c r="K47" s="31">
+      <c r="G47" s="29"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="27"/>
+      <c r="K47" s="30">
         <v>51</v>
       </c>
-      <c r="L47" s="28"/>
-      <c r="M47" s="32" t="s">
+      <c r="L47" s="27"/>
+      <c r="M47" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="N47" s="33"/>
+      <c r="N47" s="32"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="3" t="s">
@@ -3533,30 +3554,30 @@
       <c r="B48" s="4">
         <v>44755</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="33">
         <v>44761</v>
       </c>
-      <c r="D48" s="28"/>
+      <c r="D48" s="27"/>
       <c r="E48" s="4">
         <v>44806</v>
       </c>
-      <c r="F48" s="35" t="s">
+      <c r="F48" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="30"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="28"/>
-      <c r="K48" s="36">
+      <c r="G48" s="29"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="27"/>
+      <c r="K48" s="35">
         <v>69</v>
       </c>
-      <c r="L48" s="28"/>
-      <c r="M48" s="37" t="s">
+      <c r="L48" s="27"/>
+      <c r="M48" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="N48" s="33"/>
+      <c r="N48" s="32"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
@@ -3565,30 +3586,30 @@
       <c r="B49" s="2">
         <v>44754</v>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="26">
         <v>44762</v>
       </c>
-      <c r="D49" s="28"/>
+      <c r="D49" s="27"/>
       <c r="E49" s="2">
         <v>44814</v>
       </c>
-      <c r="F49" s="29" t="s">
+      <c r="F49" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="30"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="29" t="s">
+      <c r="G49" s="29"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="28"/>
-      <c r="K49" s="31">
+      <c r="J49" s="27"/>
+      <c r="K49" s="30">
         <v>104</v>
       </c>
-      <c r="L49" s="28"/>
-      <c r="M49" s="32" t="s">
+      <c r="L49" s="27"/>
+      <c r="M49" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="33"/>
+      <c r="N49" s="32"/>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="3" t="s">
@@ -3597,30 +3618,30 @@
       <c r="B50" s="4">
         <v>44692</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="33">
         <v>44762</v>
       </c>
-      <c r="D50" s="28"/>
+      <c r="D50" s="27"/>
       <c r="E50" s="4">
         <v>44753</v>
       </c>
-      <c r="F50" s="35" t="s">
+      <c r="F50" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="30"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="28"/>
-      <c r="K50" s="36">
+      <c r="G50" s="29"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="27"/>
+      <c r="K50" s="35">
         <v>19</v>
       </c>
-      <c r="L50" s="28"/>
-      <c r="M50" s="37" t="s">
+      <c r="L50" s="27"/>
+      <c r="M50" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="N50" s="33"/>
+      <c r="N50" s="32"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
@@ -3629,30 +3650,30 @@
       <c r="B51" s="2">
         <v>44713</v>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="26">
         <v>44762</v>
       </c>
-      <c r="D51" s="28"/>
+      <c r="D51" s="27"/>
       <c r="E51" s="2">
         <v>44713</v>
       </c>
-      <c r="F51" s="29" t="s">
+      <c r="F51" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="30"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="29" t="s">
+      <c r="G51" s="29"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="28"/>
-      <c r="K51" s="31">
+      <c r="J51" s="27"/>
+      <c r="K51" s="30">
         <v>80</v>
       </c>
-      <c r="L51" s="28"/>
-      <c r="M51" s="32" t="s">
+      <c r="L51" s="27"/>
+      <c r="M51" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="N51" s="33"/>
+      <c r="N51" s="32"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="3" t="s">
@@ -3661,30 +3682,30 @@
       <c r="B52" s="4">
         <v>44753</v>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="33">
         <v>44763</v>
       </c>
-      <c r="D52" s="28"/>
+      <c r="D52" s="27"/>
       <c r="E52" s="4">
         <v>44795</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="30"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="28"/>
-      <c r="K52" s="36">
+      <c r="G52" s="29"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="27"/>
+      <c r="K52" s="35">
         <v>99</v>
       </c>
-      <c r="L52" s="28"/>
-      <c r="M52" s="37" t="s">
+      <c r="L52" s="27"/>
+      <c r="M52" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="N52" s="33"/>
+      <c r="N52" s="32"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
@@ -3693,30 +3714,30 @@
       <c r="B53" s="2">
         <v>44753</v>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="26">
         <v>44763</v>
       </c>
-      <c r="D53" s="28"/>
+      <c r="D53" s="27"/>
       <c r="E53" s="2">
         <v>44795</v>
       </c>
-      <c r="F53" s="29" t="s">
+      <c r="F53" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G53" s="30"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="28"/>
-      <c r="K53" s="31">
+      <c r="G53" s="29"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="27"/>
+      <c r="K53" s="30">
         <v>60</v>
       </c>
-      <c r="L53" s="28"/>
-      <c r="M53" s="32" t="s">
+      <c r="L53" s="27"/>
+      <c r="M53" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="33"/>
+      <c r="N53" s="32"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="3" t="s">
@@ -3725,30 +3746,30 @@
       <c r="B54" s="4">
         <v>44753</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="33">
         <v>44763</v>
       </c>
-      <c r="D54" s="28"/>
+      <c r="D54" s="27"/>
       <c r="E54" s="4">
         <v>44795</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="G54" s="30"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="28"/>
-      <c r="K54" s="36">
+      <c r="G54" s="29"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="27"/>
+      <c r="K54" s="35">
         <v>4</v>
       </c>
-      <c r="L54" s="28"/>
-      <c r="M54" s="37" t="s">
+      <c r="L54" s="27"/>
+      <c r="M54" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="N54" s="33"/>
+      <c r="N54" s="32"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
@@ -3757,30 +3778,30 @@
       <c r="B55" s="2">
         <v>44753</v>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="26">
         <v>44763</v>
       </c>
-      <c r="D55" s="28"/>
+      <c r="D55" s="27"/>
       <c r="E55" s="2">
         <v>44795</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="30"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="28"/>
-      <c r="K55" s="31">
+      <c r="G55" s="29"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="27"/>
+      <c r="K55" s="30">
         <v>26</v>
       </c>
-      <c r="L55" s="28"/>
-      <c r="M55" s="32" t="s">
+      <c r="L55" s="27"/>
+      <c r="M55" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="N55" s="33"/>
+      <c r="N55" s="32"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="3" t="s">
@@ -3789,30 +3810,30 @@
       <c r="B56" s="4">
         <v>44700</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="33">
         <v>44763</v>
       </c>
-      <c r="D56" s="28"/>
+      <c r="D56" s="27"/>
       <c r="E56" s="4">
         <v>44760</v>
       </c>
-      <c r="F56" s="35" t="s">
+      <c r="F56" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="30"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="28"/>
-      <c r="K56" s="36">
+      <c r="G56" s="29"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="27"/>
+      <c r="K56" s="35">
         <v>30</v>
       </c>
-      <c r="L56" s="28"/>
-      <c r="M56" s="37" t="s">
+      <c r="L56" s="27"/>
+      <c r="M56" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="33"/>
+      <c r="N56" s="32"/>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
@@ -3821,30 +3842,30 @@
       <c r="B57" s="2">
         <v>44700</v>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="26">
         <v>44763</v>
       </c>
-      <c r="D57" s="28"/>
+      <c r="D57" s="27"/>
       <c r="E57" s="2">
         <v>44760</v>
       </c>
-      <c r="F57" s="29" t="s">
+      <c r="F57" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="30"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="28"/>
-      <c r="K57" s="31">
+      <c r="G57" s="29"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="27"/>
+      <c r="K57" s="30">
         <v>2</v>
       </c>
-      <c r="L57" s="28"/>
-      <c r="M57" s="32" t="s">
+      <c r="L57" s="27"/>
+      <c r="M57" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="N57" s="33"/>
+      <c r="N57" s="32"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="3" t="s">
@@ -3853,30 +3874,30 @@
       <c r="B58" s="4">
         <v>44755</v>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="33">
         <v>44764</v>
       </c>
-      <c r="D58" s="28"/>
+      <c r="D58" s="27"/>
       <c r="E58" s="4">
         <v>44755</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="30"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="35" t="s">
+      <c r="G58" s="29"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="J58" s="28"/>
-      <c r="K58" s="36">
+      <c r="J58" s="27"/>
+      <c r="K58" s="35">
         <v>66</v>
       </c>
-      <c r="L58" s="28"/>
-      <c r="M58" s="37" t="s">
+      <c r="L58" s="27"/>
+      <c r="M58" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="N58" s="33"/>
+      <c r="N58" s="32"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
@@ -3885,30 +3906,30 @@
       <c r="B59" s="2">
         <v>44762</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="26">
         <v>44764</v>
       </c>
-      <c r="D59" s="28"/>
+      <c r="D59" s="27"/>
       <c r="E59" s="2">
         <v>44837</v>
       </c>
-      <c r="F59" s="29" t="s">
+      <c r="F59" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="30"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="29" t="s">
+      <c r="G59" s="29"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="28"/>
-      <c r="K59" s="31">
+      <c r="J59" s="27"/>
+      <c r="K59" s="30">
         <v>85</v>
       </c>
-      <c r="L59" s="28"/>
-      <c r="M59" s="32" t="s">
+      <c r="L59" s="27"/>
+      <c r="M59" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="N59" s="33"/>
+      <c r="N59" s="32"/>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="3" t="s">
@@ -3917,30 +3938,30 @@
       <c r="B60" s="4">
         <v>44756</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="33">
         <v>44764</v>
       </c>
-      <c r="D60" s="28"/>
+      <c r="D60" s="27"/>
       <c r="E60" s="4">
         <v>44816</v>
       </c>
-      <c r="F60" s="35" t="s">
+      <c r="F60" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="30"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="28"/>
-      <c r="K60" s="36">
+      <c r="G60" s="29"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="27"/>
+      <c r="K60" s="35">
         <v>58</v>
       </c>
-      <c r="L60" s="28"/>
-      <c r="M60" s="37" t="s">
+      <c r="L60" s="27"/>
+      <c r="M60" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="N60" s="33"/>
+      <c r="N60" s="32"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
@@ -3949,30 +3970,30 @@
       <c r="B61" s="2">
         <v>44755</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="26">
         <v>44764</v>
       </c>
-      <c r="D61" s="28"/>
+      <c r="D61" s="27"/>
       <c r="E61" s="2">
         <v>44816</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F61" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G61" s="30"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="28"/>
-      <c r="K61" s="31">
+      <c r="G61" s="29"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="27"/>
+      <c r="K61" s="30">
         <v>80</v>
       </c>
-      <c r="L61" s="28"/>
-      <c r="M61" s="32" t="s">
+      <c r="L61" s="27"/>
+      <c r="M61" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="N61" s="33"/>
+      <c r="N61" s="32"/>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="3" t="s">
@@ -3981,30 +4002,30 @@
       <c r="B62" s="4">
         <v>44762</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="33">
         <v>44764</v>
       </c>
-      <c r="D62" s="28"/>
+      <c r="D62" s="27"/>
       <c r="E62" s="4">
         <v>44835</v>
       </c>
-      <c r="F62" s="35" t="s">
+      <c r="F62" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="G62" s="30"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="28"/>
-      <c r="K62" s="36">
+      <c r="G62" s="29"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="27"/>
+      <c r="K62" s="35">
         <v>55</v>
       </c>
-      <c r="L62" s="28"/>
-      <c r="M62" s="37" t="s">
+      <c r="L62" s="27"/>
+      <c r="M62" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="N62" s="33"/>
+      <c r="N62" s="32"/>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
@@ -4013,30 +4034,30 @@
       <c r="B63" s="2">
         <v>44756</v>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="26">
         <v>44764</v>
       </c>
-      <c r="D63" s="28"/>
+      <c r="D63" s="27"/>
       <c r="E63" s="2">
         <v>44818</v>
       </c>
-      <c r="F63" s="29" t="s">
+      <c r="F63" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="30"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="29" t="s">
+      <c r="G63" s="29"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="28"/>
-      <c r="K63" s="31">
+      <c r="J63" s="27"/>
+      <c r="K63" s="30">
         <v>14</v>
       </c>
-      <c r="L63" s="28"/>
-      <c r="M63" s="32" t="s">
+      <c r="L63" s="27"/>
+      <c r="M63" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="N63" s="33"/>
+      <c r="N63" s="32"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="3" t="s">
@@ -4045,30 +4066,30 @@
       <c r="B64" s="4">
         <v>44757</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="33">
         <v>44764</v>
       </c>
-      <c r="D64" s="28"/>
+      <c r="D64" s="27"/>
       <c r="E64" s="4">
         <v>44819</v>
       </c>
-      <c r="F64" s="35" t="s">
+      <c r="F64" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="G64" s="30"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="35" t="s">
+      <c r="G64" s="29"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="28"/>
-      <c r="K64" s="36">
+      <c r="J64" s="27"/>
+      <c r="K64" s="35">
         <v>90</v>
       </c>
-      <c r="L64" s="28"/>
-      <c r="M64" s="37" t="s">
+      <c r="L64" s="27"/>
+      <c r="M64" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="N64" s="33"/>
+      <c r="N64" s="32"/>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
@@ -4077,30 +4098,30 @@
       <c r="B65" s="2">
         <v>44761</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="26">
         <v>44767</v>
       </c>
-      <c r="D65" s="28"/>
+      <c r="D65" s="27"/>
       <c r="E65" s="2">
         <v>44820</v>
       </c>
-      <c r="F65" s="29" t="s">
+      <c r="F65" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="30"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="29" t="s">
+      <c r="G65" s="29"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="28"/>
-      <c r="K65" s="31">
+      <c r="J65" s="27"/>
+      <c r="K65" s="30">
         <v>331</v>
       </c>
-      <c r="L65" s="28"/>
-      <c r="M65" s="32" t="s">
+      <c r="L65" s="27"/>
+      <c r="M65" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="N65" s="33"/>
+      <c r="N65" s="32"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="3" t="s">
@@ -4109,30 +4130,30 @@
       <c r="B66" s="4">
         <v>44764</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="33">
         <v>44768</v>
       </c>
-      <c r="D66" s="28"/>
+      <c r="D66" s="27"/>
       <c r="E66" s="4">
         <v>44761</v>
       </c>
-      <c r="F66" s="35" t="s">
+      <c r="F66" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="G66" s="30"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="28"/>
-      <c r="K66" s="36">
+      <c r="G66" s="29"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="27"/>
+      <c r="K66" s="35">
         <v>52</v>
       </c>
-      <c r="L66" s="28"/>
-      <c r="M66" s="37" t="s">
+      <c r="L66" s="27"/>
+      <c r="M66" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="N66" s="33"/>
+      <c r="N66" s="32"/>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
@@ -4141,30 +4162,30 @@
       <c r="B67" s="2">
         <v>44767</v>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="26">
         <v>44768</v>
       </c>
-      <c r="D67" s="28"/>
+      <c r="D67" s="27"/>
       <c r="E67" s="2">
         <v>44827</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="G67" s="30"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="28"/>
-      <c r="K67" s="31">
+      <c r="G67" s="29"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="27"/>
+      <c r="K67" s="30">
         <v>9</v>
       </c>
-      <c r="L67" s="28"/>
-      <c r="M67" s="32" t="s">
+      <c r="L67" s="27"/>
+      <c r="M67" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="N67" s="33"/>
+      <c r="N67" s="32"/>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="3" t="s">
@@ -4173,30 +4194,30 @@
       <c r="B68" s="4">
         <v>44763</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="33">
         <v>44768</v>
       </c>
-      <c r="D68" s="28"/>
+      <c r="D68" s="27"/>
       <c r="E68" s="4">
         <v>44834</v>
       </c>
-      <c r="F68" s="35" t="s">
+      <c r="F68" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="G68" s="30"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="28"/>
-      <c r="K68" s="36">
+      <c r="G68" s="29"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="27"/>
+      <c r="K68" s="35">
         <v>78</v>
       </c>
-      <c r="L68" s="28"/>
-      <c r="M68" s="37" t="s">
+      <c r="L68" s="27"/>
+      <c r="M68" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="N68" s="33"/>
+      <c r="N68" s="32"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
@@ -4205,30 +4226,30 @@
       <c r="B69" s="2">
         <v>44760</v>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="26">
         <v>44769</v>
       </c>
-      <c r="D69" s="28"/>
+      <c r="D69" s="27"/>
       <c r="E69" s="2">
         <v>44822</v>
       </c>
-      <c r="F69" s="29" t="s">
+      <c r="F69" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="30"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="28"/>
-      <c r="K69" s="31">
+      <c r="G69" s="29"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="27"/>
+      <c r="K69" s="30">
         <v>48</v>
       </c>
-      <c r="L69" s="28"/>
-      <c r="M69" s="32" t="s">
+      <c r="L69" s="27"/>
+      <c r="M69" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="N69" s="33"/>
+      <c r="N69" s="32"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="3" t="s">
@@ -4237,30 +4258,30 @@
       <c r="B70" s="4">
         <v>44760</v>
       </c>
-      <c r="C70" s="34">
+      <c r="C70" s="33">
         <v>44769</v>
       </c>
-      <c r="D70" s="28"/>
+      <c r="D70" s="27"/>
       <c r="E70" s="4">
         <v>44820</v>
       </c>
-      <c r="F70" s="35" t="s">
+      <c r="F70" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="30"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="28"/>
-      <c r="K70" s="36">
+      <c r="G70" s="29"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="27"/>
+      <c r="K70" s="35">
         <v>50</v>
       </c>
-      <c r="L70" s="28"/>
-      <c r="M70" s="37" t="s">
+      <c r="L70" s="27"/>
+      <c r="M70" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="N70" s="33"/>
+      <c r="N70" s="32"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
@@ -4269,30 +4290,30 @@
       <c r="B71" s="2">
         <v>44760</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="26">
         <v>44769</v>
       </c>
-      <c r="D71" s="28"/>
+      <c r="D71" s="27"/>
       <c r="E71" s="2">
         <v>44822</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="G71" s="30"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="28"/>
-      <c r="K71" s="31">
+      <c r="G71" s="29"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="27"/>
+      <c r="K71" s="30">
         <v>736</v>
       </c>
-      <c r="L71" s="28"/>
-      <c r="M71" s="32" t="s">
+      <c r="L71" s="27"/>
+      <c r="M71" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="N71" s="33"/>
+      <c r="N71" s="32"/>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="3" t="s">
@@ -4301,30 +4322,30 @@
       <c r="B72" s="4">
         <v>44768</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="33">
         <v>44770</v>
       </c>
-      <c r="D72" s="28"/>
+      <c r="D72" s="27"/>
       <c r="E72" s="4">
         <v>44830</v>
       </c>
-      <c r="F72" s="35" t="s">
+      <c r="F72" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="30"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="28"/>
-      <c r="K72" s="36">
+      <c r="G72" s="29"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="27"/>
+      <c r="K72" s="35">
         <v>74</v>
       </c>
-      <c r="L72" s="28"/>
-      <c r="M72" s="37" t="s">
+      <c r="L72" s="27"/>
+      <c r="M72" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="N72" s="33"/>
+      <c r="N72" s="32"/>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
@@ -4333,30 +4354,30 @@
       <c r="B73" s="2">
         <v>44762</v>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="26">
         <v>44770</v>
       </c>
-      <c r="D73" s="28"/>
+      <c r="D73" s="27"/>
       <c r="E73" s="2">
         <v>44822</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G73" s="30"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="28"/>
-      <c r="K73" s="31">
+      <c r="G73" s="29"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="27"/>
+      <c r="K73" s="30">
         <v>25</v>
       </c>
-      <c r="L73" s="28"/>
-      <c r="M73" s="32" t="s">
+      <c r="L73" s="27"/>
+      <c r="M73" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="N73" s="33"/>
+      <c r="N73" s="32"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="3" t="s">
@@ -4365,30 +4386,30 @@
       <c r="B74" s="4">
         <v>44762</v>
       </c>
-      <c r="C74" s="34">
+      <c r="C74" s="33">
         <v>44770</v>
       </c>
-      <c r="D74" s="28"/>
+      <c r="D74" s="27"/>
       <c r="E74" s="4">
         <v>44829</v>
       </c>
-      <c r="F74" s="35" t="s">
+      <c r="F74" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="G74" s="30"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="28"/>
-      <c r="K74" s="36">
+      <c r="G74" s="29"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="27"/>
+      <c r="K74" s="35">
         <v>25</v>
       </c>
-      <c r="L74" s="28"/>
-      <c r="M74" s="37" t="s">
+      <c r="L74" s="27"/>
+      <c r="M74" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="N74" s="33"/>
+      <c r="N74" s="32"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
@@ -4397,30 +4418,30 @@
       <c r="B75" s="2">
         <v>44770</v>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="26">
         <v>44770</v>
       </c>
-      <c r="D75" s="28"/>
+      <c r="D75" s="27"/>
       <c r="E75" s="2">
         <v>44865</v>
       </c>
-      <c r="F75" s="29" t="s">
+      <c r="F75" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="G75" s="30"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="29" t="s">
+      <c r="G75" s="29"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="28"/>
-      <c r="K75" s="31">
+      <c r="J75" s="27"/>
+      <c r="K75" s="30">
         <v>225</v>
       </c>
-      <c r="L75" s="28"/>
-      <c r="M75" s="32" t="s">
+      <c r="L75" s="27"/>
+      <c r="M75" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="N75" s="33"/>
+      <c r="N75" s="32"/>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="3" t="s">
@@ -4429,30 +4450,30 @@
       <c r="B76" s="4">
         <v>44769</v>
       </c>
-      <c r="C76" s="34">
+      <c r="C76" s="33">
         <v>44770</v>
       </c>
-      <c r="D76" s="28"/>
+      <c r="D76" s="27"/>
       <c r="E76" s="4">
         <v>44837</v>
       </c>
-      <c r="F76" s="35" t="s">
+      <c r="F76" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="G76" s="30"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="28"/>
-      <c r="K76" s="36">
+      <c r="G76" s="29"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="27"/>
+      <c r="K76" s="35">
         <v>136</v>
       </c>
-      <c r="L76" s="28"/>
-      <c r="M76" s="37" t="s">
+      <c r="L76" s="27"/>
+      <c r="M76" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="N76" s="33"/>
+      <c r="N76" s="32"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
@@ -4461,30 +4482,30 @@
       <c r="B77" s="2">
         <v>44774</v>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="26">
         <v>44774</v>
       </c>
-      <c r="D77" s="28"/>
+      <c r="D77" s="27"/>
       <c r="E77" s="2">
         <v>44834</v>
       </c>
-      <c r="F77" s="29" t="s">
+      <c r="F77" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="G77" s="30"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29" t="s">
+      <c r="G77" s="29"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="28"/>
-      <c r="K77" s="31">
+      <c r="J77" s="27"/>
+      <c r="K77" s="30">
         <v>82</v>
       </c>
-      <c r="L77" s="28"/>
-      <c r="M77" s="32" t="s">
+      <c r="L77" s="27"/>
+      <c r="M77" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="N77" s="33"/>
+      <c r="N77" s="32"/>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="3" t="s">
@@ -4493,30 +4514,30 @@
       <c r="B78" s="4">
         <v>44774</v>
       </c>
-      <c r="C78" s="34">
+      <c r="C78" s="33">
         <v>44774</v>
       </c>
-      <c r="D78" s="28"/>
+      <c r="D78" s="27"/>
       <c r="E78" s="4">
         <v>44841</v>
       </c>
-      <c r="F78" s="35" t="s">
+      <c r="F78" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="30"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="28"/>
-      <c r="K78" s="36">
+      <c r="G78" s="29"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="27"/>
+      <c r="K78" s="35">
         <v>28</v>
       </c>
-      <c r="L78" s="28"/>
-      <c r="M78" s="37" t="s">
+      <c r="L78" s="27"/>
+      <c r="M78" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="N78" s="33"/>
+      <c r="N78" s="32"/>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
@@ -4525,30 +4546,30 @@
       <c r="B79" s="2">
         <v>44774</v>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="26">
         <v>44776</v>
       </c>
-      <c r="D79" s="28"/>
+      <c r="D79" s="27"/>
       <c r="E79" s="2">
         <v>44774</v>
       </c>
-      <c r="F79" s="29" t="s">
+      <c r="F79" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="30"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="28"/>
-      <c r="K79" s="31">
+      <c r="G79" s="29"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="27"/>
+      <c r="K79" s="30">
         <v>57</v>
       </c>
-      <c r="L79" s="28"/>
-      <c r="M79" s="32" t="s">
+      <c r="L79" s="27"/>
+      <c r="M79" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="33"/>
+      <c r="N79" s="32"/>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="3" t="s">
@@ -4557,30 +4578,30 @@
       <c r="B80" s="4">
         <v>44767</v>
       </c>
-      <c r="C80" s="34">
+      <c r="C80" s="33">
         <v>44778</v>
       </c>
-      <c r="D80" s="28"/>
+      <c r="D80" s="27"/>
       <c r="E80" s="4">
         <v>44834</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="30"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="35" t="s">
+      <c r="G80" s="29"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="28"/>
-      <c r="K80" s="36">
+      <c r="J80" s="27"/>
+      <c r="K80" s="35">
         <v>133</v>
       </c>
-      <c r="L80" s="28"/>
-      <c r="M80" s="37" t="s">
+      <c r="L80" s="27"/>
+      <c r="M80" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="33"/>
+      <c r="N80" s="32"/>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
@@ -4589,30 +4610,30 @@
       <c r="B81" s="2">
         <v>44775</v>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="26">
         <v>44778</v>
       </c>
-      <c r="D81" s="28"/>
+      <c r="D81" s="27"/>
       <c r="E81" s="2">
         <v>44835</v>
       </c>
-      <c r="F81" s="29" t="s">
+      <c r="F81" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="G81" s="30"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="28"/>
-      <c r="K81" s="31">
+      <c r="G81" s="29"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="27"/>
+      <c r="K81" s="30">
         <v>146</v>
       </c>
-      <c r="L81" s="28"/>
-      <c r="M81" s="32" t="s">
+      <c r="L81" s="27"/>
+      <c r="M81" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="N81" s="33"/>
+      <c r="N81" s="32"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="3" t="s">
@@ -4621,30 +4642,30 @@
       <c r="B82" s="4">
         <v>44770</v>
       </c>
-      <c r="C82" s="34">
+      <c r="C82" s="33">
         <v>44778</v>
       </c>
-      <c r="D82" s="28"/>
+      <c r="D82" s="27"/>
       <c r="E82" s="4">
         <v>44835</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="G82" s="30"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="35" t="s">
+      <c r="G82" s="29"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="28"/>
-      <c r="K82" s="36">
+      <c r="J82" s="27"/>
+      <c r="K82" s="35">
         <v>68</v>
       </c>
-      <c r="L82" s="28"/>
-      <c r="M82" s="37" t="s">
+      <c r="L82" s="27"/>
+      <c r="M82" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="N82" s="33"/>
+      <c r="N82" s="32"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
@@ -4653,30 +4674,30 @@
       <c r="B83" s="2">
         <v>44769</v>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="26">
         <v>44781</v>
       </c>
-      <c r="D83" s="28"/>
+      <c r="D83" s="27"/>
       <c r="E83" s="2">
         <v>44841</v>
       </c>
-      <c r="F83" s="29" t="s">
+      <c r="F83" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G83" s="30"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="28"/>
-      <c r="K83" s="31">
+      <c r="G83" s="29"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="27"/>
+      <c r="K83" s="30">
         <v>111</v>
       </c>
-      <c r="L83" s="28"/>
-      <c r="M83" s="32" t="s">
+      <c r="L83" s="27"/>
+      <c r="M83" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="N83" s="33"/>
+      <c r="N83" s="32"/>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="3" t="s">
@@ -4685,30 +4706,30 @@
       <c r="B84" s="4">
         <v>44769</v>
       </c>
-      <c r="C84" s="34">
+      <c r="C84" s="33">
         <v>44781</v>
       </c>
-      <c r="D84" s="28"/>
+      <c r="D84" s="27"/>
       <c r="E84" s="4">
         <v>44841</v>
       </c>
-      <c r="F84" s="35" t="s">
+      <c r="F84" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="G84" s="30"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="28"/>
-      <c r="K84" s="36">
+      <c r="G84" s="29"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="27"/>
+      <c r="K84" s="35">
         <v>77</v>
       </c>
-      <c r="L84" s="28"/>
-      <c r="M84" s="37" t="s">
+      <c r="L84" s="27"/>
+      <c r="M84" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="N84" s="33"/>
+      <c r="N84" s="32"/>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
@@ -4717,30 +4738,30 @@
       <c r="B85" s="2">
         <v>44769</v>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="26">
         <v>44781</v>
       </c>
-      <c r="D85" s="28"/>
+      <c r="D85" s="27"/>
       <c r="E85" s="2">
         <v>44841</v>
       </c>
-      <c r="F85" s="29" t="s">
+      <c r="F85" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G85" s="30"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="28"/>
-      <c r="K85" s="31">
+      <c r="G85" s="29"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="27"/>
+      <c r="K85" s="30">
         <v>20</v>
       </c>
-      <c r="L85" s="28"/>
-      <c r="M85" s="32" t="s">
+      <c r="L85" s="27"/>
+      <c r="M85" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="33"/>
+      <c r="N85" s="32"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="3" t="s">
@@ -4749,30 +4770,30 @@
       <c r="B86" s="4">
         <v>44769</v>
       </c>
-      <c r="C86" s="34">
+      <c r="C86" s="33">
         <v>44781</v>
       </c>
-      <c r="D86" s="28"/>
+      <c r="D86" s="27"/>
       <c r="E86" s="4">
         <v>44841</v>
       </c>
-      <c r="F86" s="35" t="s">
+      <c r="F86" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="G86" s="30"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="28"/>
-      <c r="K86" s="36">
+      <c r="G86" s="29"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="27"/>
+      <c r="K86" s="35">
         <v>25</v>
       </c>
-      <c r="L86" s="28"/>
-      <c r="M86" s="37" t="s">
+      <c r="L86" s="27"/>
+      <c r="M86" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="N86" s="33"/>
+      <c r="N86" s="32"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
@@ -4781,30 +4802,30 @@
       <c r="B87" s="2">
         <v>44769</v>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="26">
         <v>44781</v>
       </c>
-      <c r="D87" s="28"/>
+      <c r="D87" s="27"/>
       <c r="E87" s="2">
         <v>44841</v>
       </c>
-      <c r="F87" s="29" t="s">
+      <c r="F87" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G87" s="30"/>
-      <c r="H87" s="28"/>
-      <c r="I87" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="28"/>
-      <c r="K87" s="31">
+      <c r="G87" s="29"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="27"/>
+      <c r="K87" s="30">
         <v>21</v>
       </c>
-      <c r="L87" s="28"/>
-      <c r="M87" s="32" t="s">
+      <c r="L87" s="27"/>
+      <c r="M87" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="N87" s="33"/>
+      <c r="N87" s="32"/>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="3" t="s">
@@ -4813,30 +4834,30 @@
       <c r="B88" s="4">
         <v>44769</v>
       </c>
-      <c r="C88" s="34">
+      <c r="C88" s="33">
         <v>44781</v>
       </c>
-      <c r="D88" s="28"/>
+      <c r="D88" s="27"/>
       <c r="E88" s="4">
         <v>44841</v>
       </c>
-      <c r="F88" s="35" t="s">
+      <c r="F88" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="G88" s="30"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="28"/>
-      <c r="K88" s="36">
+      <c r="G88" s="29"/>
+      <c r="H88" s="27"/>
+      <c r="I88" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="27"/>
+      <c r="K88" s="35">
         <v>86</v>
       </c>
-      <c r="L88" s="28"/>
-      <c r="M88" s="37" t="s">
+      <c r="L88" s="27"/>
+      <c r="M88" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="N88" s="33"/>
+      <c r="N88" s="32"/>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
@@ -4845,30 +4866,30 @@
       <c r="B89" s="2">
         <v>44769</v>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="26">
         <v>44781</v>
       </c>
-      <c r="D89" s="28"/>
+      <c r="D89" s="27"/>
       <c r="E89" s="2">
         <v>44841</v>
       </c>
-      <c r="F89" s="29" t="s">
+      <c r="F89" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G89" s="30"/>
-      <c r="H89" s="28"/>
-      <c r="I89" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="28"/>
-      <c r="K89" s="31">
+      <c r="G89" s="29"/>
+      <c r="H89" s="27"/>
+      <c r="I89" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="27"/>
+      <c r="K89" s="30">
         <v>9</v>
       </c>
-      <c r="L89" s="28"/>
-      <c r="M89" s="32" t="s">
+      <c r="L89" s="27"/>
+      <c r="M89" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="N89" s="33"/>
+      <c r="N89" s="32"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="3" t="s">
@@ -4877,30 +4898,30 @@
       <c r="B90" s="4">
         <v>44769</v>
       </c>
-      <c r="C90" s="34">
+      <c r="C90" s="33">
         <v>44781</v>
       </c>
-      <c r="D90" s="28"/>
+      <c r="D90" s="27"/>
       <c r="E90" s="4">
         <v>44841</v>
       </c>
-      <c r="F90" s="35" t="s">
+      <c r="F90" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="G90" s="30"/>
-      <c r="H90" s="28"/>
-      <c r="I90" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="28"/>
-      <c r="K90" s="36">
+      <c r="G90" s="29"/>
+      <c r="H90" s="27"/>
+      <c r="I90" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="27"/>
+      <c r="K90" s="35">
         <v>2</v>
       </c>
-      <c r="L90" s="28"/>
-      <c r="M90" s="37" t="s">
+      <c r="L90" s="27"/>
+      <c r="M90" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="N90" s="33"/>
+      <c r="N90" s="32"/>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
@@ -4909,30 +4930,30 @@
       <c r="B91" s="2">
         <v>44774</v>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="26">
         <v>44781</v>
       </c>
-      <c r="D91" s="28"/>
+      <c r="D91" s="27"/>
       <c r="E91" s="2">
         <v>44836</v>
       </c>
-      <c r="F91" s="29" t="s">
+      <c r="F91" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="30"/>
-      <c r="H91" s="28"/>
-      <c r="I91" s="29" t="s">
+      <c r="G91" s="29"/>
+      <c r="H91" s="27"/>
+      <c r="I91" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J91" s="28"/>
-      <c r="K91" s="31">
+      <c r="J91" s="27"/>
+      <c r="K91" s="30">
         <v>73</v>
       </c>
-      <c r="L91" s="28"/>
-      <c r="M91" s="32" t="s">
+      <c r="L91" s="27"/>
+      <c r="M91" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="N91" s="33"/>
+      <c r="N91" s="32"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="3" t="s">
@@ -4941,30 +4962,30 @@
       <c r="B92" s="4">
         <v>44782</v>
       </c>
-      <c r="C92" s="34">
+      <c r="C92" s="33">
         <v>44782</v>
       </c>
-      <c r="D92" s="28"/>
+      <c r="D92" s="27"/>
       <c r="E92" s="4">
         <v>44838</v>
       </c>
-      <c r="F92" s="35" t="s">
+      <c r="F92" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="30"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="35" t="s">
+      <c r="G92" s="29"/>
+      <c r="H92" s="27"/>
+      <c r="I92" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J92" s="28"/>
-      <c r="K92" s="36">
+      <c r="J92" s="27"/>
+      <c r="K92" s="35">
         <v>33</v>
       </c>
-      <c r="L92" s="28"/>
-      <c r="M92" s="37" t="s">
+      <c r="L92" s="27"/>
+      <c r="M92" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="N92" s="33"/>
+      <c r="N92" s="32"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4973,30 +4994,30 @@
       <c r="B93" s="2">
         <v>44782</v>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="26">
         <v>44782</v>
       </c>
-      <c r="D93" s="28"/>
+      <c r="D93" s="27"/>
       <c r="E93" s="2">
         <v>44838</v>
       </c>
-      <c r="F93" s="29" t="s">
+      <c r="F93" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="30"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29" t="s">
+      <c r="G93" s="29"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J93" s="28"/>
-      <c r="K93" s="31">
+      <c r="J93" s="27"/>
+      <c r="K93" s="30">
         <v>57</v>
       </c>
-      <c r="L93" s="28"/>
-      <c r="M93" s="32" t="s">
+      <c r="L93" s="27"/>
+      <c r="M93" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="N93" s="33"/>
+      <c r="N93" s="32"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="3" t="s">
@@ -5005,30 +5026,30 @@
       <c r="B94" s="4">
         <v>44782</v>
       </c>
-      <c r="C94" s="34">
+      <c r="C94" s="33">
         <v>44782</v>
       </c>
-      <c r="D94" s="28"/>
+      <c r="D94" s="27"/>
       <c r="E94" s="4">
         <v>44838</v>
       </c>
-      <c r="F94" s="35" t="s">
+      <c r="F94" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="G94" s="30"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="35" t="s">
+      <c r="G94" s="29"/>
+      <c r="H94" s="27"/>
+      <c r="I94" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="28"/>
-      <c r="K94" s="36">
+      <c r="J94" s="27"/>
+      <c r="K94" s="35">
         <v>16</v>
       </c>
-      <c r="L94" s="28"/>
-      <c r="M94" s="37" t="s">
+      <c r="L94" s="27"/>
+      <c r="M94" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="N94" s="33"/>
+      <c r="N94" s="32"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
@@ -5037,30 +5058,30 @@
       <c r="B95" s="2">
         <v>44782</v>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="26">
         <v>44782</v>
       </c>
-      <c r="D95" s="28"/>
+      <c r="D95" s="27"/>
       <c r="E95" s="2">
         <v>44838</v>
       </c>
-      <c r="F95" s="29" t="s">
+      <c r="F95" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="30"/>
-      <c r="H95" s="28"/>
-      <c r="I95" s="29" t="s">
+      <c r="G95" s="29"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J95" s="28"/>
-      <c r="K95" s="31">
+      <c r="J95" s="27"/>
+      <c r="K95" s="30">
         <v>3</v>
       </c>
-      <c r="L95" s="28"/>
-      <c r="M95" s="32" t="s">
+      <c r="L95" s="27"/>
+      <c r="M95" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="N95" s="33"/>
+      <c r="N95" s="32"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="3" t="s">
@@ -5069,30 +5090,30 @@
       <c r="B96" s="4">
         <v>44782</v>
       </c>
-      <c r="C96" s="34">
+      <c r="C96" s="33">
         <v>44782</v>
       </c>
-      <c r="D96" s="28"/>
+      <c r="D96" s="27"/>
       <c r="E96" s="4">
         <v>44838</v>
       </c>
-      <c r="F96" s="35" t="s">
+      <c r="F96" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="G96" s="30"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="35" t="s">
+      <c r="G96" s="29"/>
+      <c r="H96" s="27"/>
+      <c r="I96" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="28"/>
-      <c r="K96" s="36">
+      <c r="J96" s="27"/>
+      <c r="K96" s="35">
         <v>15</v>
       </c>
-      <c r="L96" s="28"/>
-      <c r="M96" s="37" t="s">
+      <c r="L96" s="27"/>
+      <c r="M96" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="N96" s="33"/>
+      <c r="N96" s="32"/>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
@@ -5101,30 +5122,30 @@
       <c r="B97" s="2">
         <v>44776</v>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="26">
         <v>44783</v>
       </c>
-      <c r="D97" s="28"/>
+      <c r="D97" s="27"/>
       <c r="E97" s="2">
         <v>44838</v>
       </c>
-      <c r="F97" s="29" t="s">
+      <c r="F97" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="G97" s="30"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29" t="s">
+      <c r="G97" s="29"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="28"/>
-      <c r="K97" s="31">
+      <c r="J97" s="27"/>
+      <c r="K97" s="30">
         <v>64</v>
       </c>
-      <c r="L97" s="28"/>
-      <c r="M97" s="32" t="s">
+      <c r="L97" s="27"/>
+      <c r="M97" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="N97" s="33"/>
+      <c r="N97" s="32"/>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
@@ -5133,30 +5154,30 @@
       <c r="B98" s="4">
         <v>44777</v>
       </c>
-      <c r="C98" s="34">
+      <c r="C98" s="33">
         <v>44783</v>
       </c>
-      <c r="D98" s="28"/>
+      <c r="D98" s="27"/>
       <c r="E98" s="4">
         <v>44841</v>
       </c>
-      <c r="F98" s="35" t="s">
+      <c r="F98" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="G98" s="30"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="35" t="s">
+      <c r="G98" s="29"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="28"/>
-      <c r="K98" s="36">
+      <c r="J98" s="27"/>
+      <c r="K98" s="35">
         <v>100</v>
       </c>
-      <c r="L98" s="28"/>
-      <c r="M98" s="37" t="s">
+      <c r="L98" s="27"/>
+      <c r="M98" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="N98" s="33"/>
+      <c r="N98" s="32"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
@@ -5165,30 +5186,30 @@
       <c r="B99" s="2">
         <v>44778</v>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="26">
         <v>44783</v>
       </c>
-      <c r="D99" s="28"/>
+      <c r="D99" s="27"/>
       <c r="E99" s="2">
         <v>44839</v>
       </c>
-      <c r="F99" s="29" t="s">
+      <c r="F99" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="30"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="29" t="s">
+      <c r="G99" s="29"/>
+      <c r="H99" s="27"/>
+      <c r="I99" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="28"/>
-      <c r="K99" s="31">
+      <c r="J99" s="27"/>
+      <c r="K99" s="30">
         <v>193</v>
       </c>
-      <c r="L99" s="28"/>
-      <c r="M99" s="32" t="s">
+      <c r="L99" s="27"/>
+      <c r="M99" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="N99" s="33"/>
+      <c r="N99" s="32"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
@@ -5197,30 +5218,30 @@
       <c r="B100" s="4">
         <v>44771</v>
       </c>
-      <c r="C100" s="34">
+      <c r="C100" s="33">
         <v>44783</v>
       </c>
-      <c r="D100" s="28"/>
+      <c r="D100" s="27"/>
       <c r="E100" s="4">
         <v>44834</v>
       </c>
-      <c r="F100" s="35" t="s">
+      <c r="F100" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="G100" s="30"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="28"/>
-      <c r="K100" s="36">
+      <c r="G100" s="29"/>
+      <c r="H100" s="27"/>
+      <c r="I100" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="27"/>
+      <c r="K100" s="35">
         <v>15</v>
       </c>
-      <c r="L100" s="28"/>
-      <c r="M100" s="37" t="s">
+      <c r="L100" s="27"/>
+      <c r="M100" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="N100" s="33"/>
+      <c r="N100" s="32"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
@@ -5229,30 +5250,30 @@
       <c r="B101" s="2">
         <v>44771</v>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="26">
         <v>44783</v>
       </c>
-      <c r="D101" s="28"/>
+      <c r="D101" s="27"/>
       <c r="E101" s="2">
         <v>44834</v>
       </c>
-      <c r="F101" s="29" t="s">
+      <c r="F101" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="G101" s="30"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="28"/>
-      <c r="K101" s="31">
+      <c r="G101" s="29"/>
+      <c r="H101" s="27"/>
+      <c r="I101" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="27"/>
+      <c r="K101" s="30">
         <v>65</v>
       </c>
-      <c r="L101" s="28"/>
-      <c r="M101" s="32" t="s">
+      <c r="L101" s="27"/>
+      <c r="M101" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="N101" s="33"/>
+      <c r="N101" s="32"/>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
@@ -5261,30 +5282,30 @@
       <c r="B102" s="4">
         <v>44771</v>
       </c>
-      <c r="C102" s="34">
+      <c r="C102" s="33">
         <v>44783</v>
       </c>
-      <c r="D102" s="28"/>
+      <c r="D102" s="27"/>
       <c r="E102" s="4">
         <v>44834</v>
       </c>
-      <c r="F102" s="35" t="s">
+      <c r="F102" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="G102" s="30"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="28"/>
-      <c r="K102" s="36">
+      <c r="G102" s="29"/>
+      <c r="H102" s="27"/>
+      <c r="I102" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="27"/>
+      <c r="K102" s="35">
         <v>66</v>
       </c>
-      <c r="L102" s="28"/>
-      <c r="M102" s="37" t="s">
+      <c r="L102" s="27"/>
+      <c r="M102" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="N102" s="33"/>
+      <c r="N102" s="32"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
@@ -5293,30 +5314,30 @@
       <c r="B103" s="2">
         <v>44781</v>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="26">
         <v>44784</v>
       </c>
-      <c r="D103" s="28"/>
+      <c r="D103" s="27"/>
       <c r="E103" s="2">
         <v>44781</v>
       </c>
-      <c r="F103" s="29" t="s">
+      <c r="F103" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="G103" s="30"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="29" t="s">
+      <c r="G103" s="29"/>
+      <c r="H103" s="27"/>
+      <c r="I103" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J103" s="28"/>
-      <c r="K103" s="31">
+      <c r="J103" s="27"/>
+      <c r="K103" s="30">
         <v>111</v>
       </c>
-      <c r="L103" s="28"/>
-      <c r="M103" s="32" t="s">
+      <c r="L103" s="27"/>
+      <c r="M103" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="N103" s="33"/>
+      <c r="N103" s="32"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
@@ -5325,30 +5346,30 @@
       <c r="B104" s="4">
         <v>44781</v>
       </c>
-      <c r="C104" s="34">
+      <c r="C104" s="33">
         <v>44784</v>
       </c>
-      <c r="D104" s="28"/>
+      <c r="D104" s="27"/>
       <c r="E104" s="4">
         <v>44781</v>
       </c>
-      <c r="F104" s="35" t="s">
+      <c r="F104" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="G104" s="30"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="35" t="s">
+      <c r="G104" s="29"/>
+      <c r="H104" s="27"/>
+      <c r="I104" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J104" s="28"/>
-      <c r="K104" s="36">
+      <c r="J104" s="27"/>
+      <c r="K104" s="35">
         <v>30</v>
       </c>
-      <c r="L104" s="28"/>
-      <c r="M104" s="37" t="s">
+      <c r="L104" s="27"/>
+      <c r="M104" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="N104" s="33"/>
+      <c r="N104" s="32"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
@@ -5357,30 +5378,30 @@
       <c r="B105" s="2">
         <v>44781</v>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="26">
         <v>44784</v>
       </c>
-      <c r="D105" s="28"/>
+      <c r="D105" s="27"/>
       <c r="E105" s="2">
         <v>44781</v>
       </c>
-      <c r="F105" s="29" t="s">
+      <c r="F105" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="G105" s="30"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="29" t="s">
+      <c r="G105" s="29"/>
+      <c r="H105" s="27"/>
+      <c r="I105" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J105" s="28"/>
-      <c r="K105" s="31">
+      <c r="J105" s="27"/>
+      <c r="K105" s="30">
         <v>31</v>
       </c>
-      <c r="L105" s="28"/>
-      <c r="M105" s="32" t="s">
+      <c r="L105" s="27"/>
+      <c r="M105" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="N105" s="33"/>
+      <c r="N105" s="32"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
@@ -5389,30 +5410,30 @@
       <c r="B106" s="4">
         <v>44781</v>
       </c>
-      <c r="C106" s="34">
+      <c r="C106" s="33">
         <v>44784</v>
       </c>
-      <c r="D106" s="28"/>
+      <c r="D106" s="27"/>
       <c r="E106" s="4">
         <v>44781</v>
       </c>
-      <c r="F106" s="35" t="s">
+      <c r="F106" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="30"/>
-      <c r="H106" s="28"/>
-      <c r="I106" s="35" t="s">
+      <c r="G106" s="29"/>
+      <c r="H106" s="27"/>
+      <c r="I106" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J106" s="28"/>
-      <c r="K106" s="36">
+      <c r="J106" s="27"/>
+      <c r="K106" s="35">
         <v>109</v>
       </c>
-      <c r="L106" s="28"/>
-      <c r="M106" s="37" t="s">
+      <c r="L106" s="27"/>
+      <c r="M106" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="N106" s="33"/>
+      <c r="N106" s="32"/>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
@@ -5421,30 +5442,30 @@
       <c r="B107" s="2">
         <v>44784</v>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="26">
         <v>44788</v>
       </c>
-      <c r="D107" s="28"/>
+      <c r="D107" s="27"/>
       <c r="E107" s="2">
         <v>44865</v>
       </c>
-      <c r="F107" s="29" t="s">
+      <c r="F107" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="G107" s="30"/>
-      <c r="H107" s="28"/>
-      <c r="I107" s="29" t="s">
+      <c r="G107" s="29"/>
+      <c r="H107" s="27"/>
+      <c r="I107" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J107" s="28"/>
-      <c r="K107" s="31">
+      <c r="J107" s="27"/>
+      <c r="K107" s="30">
         <v>5</v>
       </c>
-      <c r="L107" s="28"/>
-      <c r="M107" s="32" t="s">
+      <c r="L107" s="27"/>
+      <c r="M107" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="N107" s="33"/>
+      <c r="N107" s="32"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
@@ -5453,30 +5474,30 @@
       <c r="B108" s="4">
         <v>44774</v>
       </c>
-      <c r="C108" s="34">
+      <c r="C108" s="33">
         <v>44788</v>
       </c>
-      <c r="D108" s="28"/>
+      <c r="D108" s="27"/>
       <c r="E108" s="4">
         <v>44834</v>
       </c>
-      <c r="F108" s="35" t="s">
+      <c r="F108" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="G108" s="30"/>
-      <c r="H108" s="28"/>
-      <c r="I108" s="35" t="s">
+      <c r="G108" s="29"/>
+      <c r="H108" s="27"/>
+      <c r="I108" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J108" s="28"/>
-      <c r="K108" s="36">
+      <c r="J108" s="27"/>
+      <c r="K108" s="35">
         <v>100</v>
       </c>
-      <c r="L108" s="28"/>
-      <c r="M108" s="37" t="s">
+      <c r="L108" s="27"/>
+      <c r="M108" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="N108" s="33"/>
+      <c r="N108" s="32"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
@@ -5485,30 +5506,30 @@
       <c r="B109" s="2">
         <v>44781</v>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="26">
         <v>44788</v>
       </c>
-      <c r="D109" s="28"/>
+      <c r="D109" s="27"/>
       <c r="E109" s="2">
         <v>44792</v>
       </c>
-      <c r="F109" s="29" t="s">
+      <c r="F109" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="G109" s="30"/>
-      <c r="H109" s="28"/>
-      <c r="I109" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="28"/>
-      <c r="K109" s="31">
+      <c r="G109" s="29"/>
+      <c r="H109" s="27"/>
+      <c r="I109" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="27"/>
+      <c r="K109" s="30">
         <v>54</v>
       </c>
-      <c r="L109" s="28"/>
-      <c r="M109" s="32" t="s">
+      <c r="L109" s="27"/>
+      <c r="M109" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="N109" s="33"/>
+      <c r="N109" s="32"/>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
@@ -5517,30 +5538,30 @@
       <c r="B110" s="4">
         <v>44782</v>
       </c>
-      <c r="C110" s="34">
+      <c r="C110" s="33">
         <v>44789</v>
       </c>
-      <c r="D110" s="28"/>
+      <c r="D110" s="27"/>
       <c r="E110" s="4">
         <v>44842</v>
       </c>
-      <c r="F110" s="35" t="s">
+      <c r="F110" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="G110" s="30"/>
-      <c r="H110" s="28"/>
-      <c r="I110" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="28"/>
-      <c r="K110" s="36">
+      <c r="G110" s="29"/>
+      <c r="H110" s="27"/>
+      <c r="I110" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="27"/>
+      <c r="K110" s="35">
         <v>77</v>
       </c>
-      <c r="L110" s="28"/>
-      <c r="M110" s="37" t="s">
+      <c r="L110" s="27"/>
+      <c r="M110" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="N110" s="33"/>
+      <c r="N110" s="32"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
@@ -5549,30 +5570,30 @@
       <c r="B111" s="2">
         <v>44782</v>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="26">
         <v>44789</v>
       </c>
-      <c r="D111" s="28"/>
+      <c r="D111" s="27"/>
       <c r="E111" s="2">
         <v>44842</v>
       </c>
-      <c r="F111" s="29" t="s">
+      <c r="F111" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="G111" s="30"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="28"/>
-      <c r="K111" s="31">
+      <c r="G111" s="29"/>
+      <c r="H111" s="27"/>
+      <c r="I111" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="27"/>
+      <c r="K111" s="30">
         <v>52</v>
       </c>
-      <c r="L111" s="28"/>
-      <c r="M111" s="32" t="s">
+      <c r="L111" s="27"/>
+      <c r="M111" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="N111" s="33"/>
+      <c r="N111" s="32"/>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
@@ -5581,30 +5602,30 @@
       <c r="B112" s="4">
         <v>44642</v>
       </c>
-      <c r="C112" s="34">
+      <c r="C112" s="33">
         <v>44789</v>
       </c>
-      <c r="D112" s="28"/>
+      <c r="D112" s="27"/>
       <c r="E112" s="4">
         <v>44726</v>
       </c>
-      <c r="F112" s="35" t="s">
+      <c r="F112" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="G112" s="30"/>
-      <c r="H112" s="28"/>
-      <c r="I112" s="35" t="s">
+      <c r="G112" s="29"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J112" s="28"/>
-      <c r="K112" s="36">
+      <c r="J112" s="27"/>
+      <c r="K112" s="35">
         <v>305</v>
       </c>
-      <c r="L112" s="28"/>
-      <c r="M112" s="37" t="s">
+      <c r="L112" s="27"/>
+      <c r="M112" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="N112" s="33"/>
+      <c r="N112" s="32"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
@@ -5613,30 +5634,30 @@
       <c r="B113" s="2">
         <v>44782</v>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="26">
         <v>44789</v>
       </c>
-      <c r="D113" s="28"/>
+      <c r="D113" s="27"/>
       <c r="E113" s="2">
         <v>44842</v>
       </c>
-      <c r="F113" s="29" t="s">
+      <c r="F113" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="G113" s="30"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="29" t="s">
+      <c r="G113" s="29"/>
+      <c r="H113" s="27"/>
+      <c r="I113" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J113" s="28"/>
-      <c r="K113" s="31">
+      <c r="J113" s="27"/>
+      <c r="K113" s="30">
         <v>81</v>
       </c>
-      <c r="L113" s="28"/>
-      <c r="M113" s="32" t="s">
+      <c r="L113" s="27"/>
+      <c r="M113" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="N113" s="33"/>
+      <c r="N113" s="32"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
@@ -5645,30 +5666,30 @@
       <c r="B114" s="4">
         <v>44782</v>
       </c>
-      <c r="C114" s="34">
+      <c r="C114" s="33">
         <v>44789</v>
       </c>
-      <c r="D114" s="28"/>
+      <c r="D114" s="27"/>
       <c r="E114" s="4">
         <v>44842</v>
       </c>
-      <c r="F114" s="35" t="s">
+      <c r="F114" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="G114" s="30"/>
-      <c r="H114" s="28"/>
-      <c r="I114" s="35" t="s">
+      <c r="G114" s="29"/>
+      <c r="H114" s="27"/>
+      <c r="I114" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J114" s="28"/>
-      <c r="K114" s="36">
+      <c r="J114" s="27"/>
+      <c r="K114" s="35">
         <v>53</v>
       </c>
-      <c r="L114" s="28"/>
-      <c r="M114" s="37" t="s">
+      <c r="L114" s="27"/>
+      <c r="M114" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="N114" s="33"/>
+      <c r="N114" s="32"/>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
@@ -5677,30 +5698,30 @@
       <c r="B115" s="2">
         <v>44782</v>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="26">
         <v>44789</v>
       </c>
-      <c r="D115" s="28"/>
+      <c r="D115" s="27"/>
       <c r="E115" s="2">
         <v>44842</v>
       </c>
-      <c r="F115" s="29" t="s">
+      <c r="F115" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="G115" s="30"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="29" t="s">
+      <c r="G115" s="29"/>
+      <c r="H115" s="27"/>
+      <c r="I115" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J115" s="28"/>
-      <c r="K115" s="31">
+      <c r="J115" s="27"/>
+      <c r="K115" s="30">
         <v>33</v>
       </c>
-      <c r="L115" s="28"/>
-      <c r="M115" s="32" t="s">
+      <c r="L115" s="27"/>
+      <c r="M115" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="N115" s="33"/>
+      <c r="N115" s="32"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
@@ -5709,30 +5730,30 @@
       <c r="B116" s="4">
         <v>44788</v>
       </c>
-      <c r="C116" s="34">
+      <c r="C116" s="33">
         <v>44790</v>
       </c>
-      <c r="D116" s="28"/>
+      <c r="D116" s="27"/>
       <c r="E116" s="4">
         <v>44783</v>
       </c>
-      <c r="F116" s="35" t="s">
+      <c r="F116" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="G116" s="30"/>
-      <c r="H116" s="28"/>
-      <c r="I116" s="35" t="s">
+      <c r="G116" s="29"/>
+      <c r="H116" s="27"/>
+      <c r="I116" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J116" s="28"/>
-      <c r="K116" s="36">
+      <c r="J116" s="27"/>
+      <c r="K116" s="35">
         <v>145</v>
       </c>
-      <c r="L116" s="28"/>
-      <c r="M116" s="37" t="s">
+      <c r="L116" s="27"/>
+      <c r="M116" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="N116" s="33"/>
+      <c r="N116" s="32"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
@@ -5741,30 +5762,30 @@
       <c r="B117" s="2">
         <v>44781</v>
       </c>
-      <c r="C117" s="27">
+      <c r="C117" s="26">
         <v>44790</v>
       </c>
-      <c r="D117" s="28"/>
+      <c r="D117" s="27"/>
       <c r="E117" s="2">
         <v>44841</v>
       </c>
-      <c r="F117" s="29" t="s">
+      <c r="F117" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G117" s="30"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="28"/>
-      <c r="K117" s="31">
+      <c r="G117" s="29"/>
+      <c r="H117" s="27"/>
+      <c r="I117" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="27"/>
+      <c r="K117" s="30">
         <v>14</v>
       </c>
-      <c r="L117" s="28"/>
-      <c r="M117" s="32" t="s">
+      <c r="L117" s="27"/>
+      <c r="M117" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="N117" s="33"/>
+      <c r="N117" s="32"/>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
@@ -5773,30 +5794,30 @@
       <c r="B118" s="4">
         <v>44785</v>
       </c>
-      <c r="C118" s="34">
+      <c r="C118" s="33">
         <v>44790</v>
       </c>
-      <c r="D118" s="28"/>
+      <c r="D118" s="27"/>
       <c r="E118" s="4">
         <v>44788</v>
       </c>
-      <c r="F118" s="35" t="s">
+      <c r="F118" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="30"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="28"/>
-      <c r="K118" s="36">
+      <c r="G118" s="29"/>
+      <c r="H118" s="27"/>
+      <c r="I118" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="27"/>
+      <c r="K118" s="35">
         <v>47</v>
       </c>
-      <c r="L118" s="28"/>
-      <c r="M118" s="37" t="s">
+      <c r="L118" s="27"/>
+      <c r="M118" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="N118" s="33"/>
+      <c r="N118" s="32"/>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
@@ -5805,30 +5826,30 @@
       <c r="B119" s="2">
         <v>44788</v>
       </c>
-      <c r="C119" s="27">
+      <c r="C119" s="26">
         <v>44790</v>
       </c>
-      <c r="D119" s="28"/>
+      <c r="D119" s="27"/>
       <c r="E119" s="2">
         <v>44848</v>
       </c>
-      <c r="F119" s="29" t="s">
+      <c r="F119" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="G119" s="30"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="28"/>
-      <c r="K119" s="31">
+      <c r="G119" s="29"/>
+      <c r="H119" s="27"/>
+      <c r="I119" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="27"/>
+      <c r="K119" s="30">
         <v>16</v>
       </c>
-      <c r="L119" s="28"/>
-      <c r="M119" s="32" t="s">
+      <c r="L119" s="27"/>
+      <c r="M119" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="N119" s="33"/>
+      <c r="N119" s="32"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
@@ -5837,30 +5858,30 @@
       <c r="B120" s="4">
         <v>44781</v>
       </c>
-      <c r="C120" s="34">
+      <c r="C120" s="33">
         <v>44790</v>
       </c>
-      <c r="D120" s="28"/>
+      <c r="D120" s="27"/>
       <c r="E120" s="4">
         <v>44841</v>
       </c>
-      <c r="F120" s="35" t="s">
+      <c r="F120" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="G120" s="30"/>
-      <c r="H120" s="28"/>
-      <c r="I120" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="28"/>
-      <c r="K120" s="36">
+      <c r="G120" s="29"/>
+      <c r="H120" s="27"/>
+      <c r="I120" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="27"/>
+      <c r="K120" s="35">
         <v>55</v>
       </c>
-      <c r="L120" s="28"/>
-      <c r="M120" s="37" t="s">
+      <c r="L120" s="27"/>
+      <c r="M120" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="N120" s="33"/>
+      <c r="N120" s="32"/>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
@@ -5869,30 +5890,30 @@
       <c r="B121" s="2">
         <v>44781</v>
       </c>
-      <c r="C121" s="27">
+      <c r="C121" s="26">
         <v>44790</v>
       </c>
-      <c r="D121" s="28"/>
+      <c r="D121" s="27"/>
       <c r="E121" s="2">
         <v>44841</v>
       </c>
-      <c r="F121" s="29" t="s">
+      <c r="F121" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="30"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="28"/>
-      <c r="K121" s="31">
+      <c r="G121" s="29"/>
+      <c r="H121" s="27"/>
+      <c r="I121" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="27"/>
+      <c r="K121" s="30">
         <v>8</v>
       </c>
-      <c r="L121" s="28"/>
-      <c r="M121" s="32" t="s">
+      <c r="L121" s="27"/>
+      <c r="M121" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="N121" s="33"/>
+      <c r="N121" s="32"/>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
@@ -5901,30 +5922,30 @@
       <c r="B122" s="4">
         <v>44788</v>
       </c>
-      <c r="C122" s="34">
+      <c r="C122" s="33">
         <v>44790</v>
       </c>
-      <c r="D122" s="28"/>
+      <c r="D122" s="27"/>
       <c r="E122" s="4">
         <v>44848</v>
       </c>
-      <c r="F122" s="35" t="s">
+      <c r="F122" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="G122" s="30"/>
-      <c r="H122" s="28"/>
-      <c r="I122" s="35" t="s">
+      <c r="G122" s="29"/>
+      <c r="H122" s="27"/>
+      <c r="I122" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J122" s="28"/>
-      <c r="K122" s="36">
+      <c r="J122" s="27"/>
+      <c r="K122" s="35">
         <v>578</v>
       </c>
-      <c r="L122" s="28"/>
-      <c r="M122" s="37" t="s">
+      <c r="L122" s="27"/>
+      <c r="M122" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="N122" s="33"/>
+      <c r="N122" s="32"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
@@ -5933,30 +5954,30 @@
       <c r="B123" s="2">
         <v>44776</v>
       </c>
-      <c r="C123" s="27">
+      <c r="C123" s="26">
         <v>44791</v>
       </c>
-      <c r="D123" s="28"/>
+      <c r="D123" s="27"/>
       <c r="E123" s="2">
         <v>44834</v>
       </c>
-      <c r="F123" s="29" t="s">
+      <c r="F123" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="G123" s="30"/>
-      <c r="H123" s="28"/>
-      <c r="I123" s="29" t="s">
+      <c r="G123" s="29"/>
+      <c r="H123" s="27"/>
+      <c r="I123" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J123" s="28"/>
-      <c r="K123" s="31">
+      <c r="J123" s="27"/>
+      <c r="K123" s="30">
         <v>111</v>
       </c>
-      <c r="L123" s="28"/>
-      <c r="M123" s="32" t="s">
+      <c r="L123" s="27"/>
+      <c r="M123" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="N123" s="33"/>
+      <c r="N123" s="32"/>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
@@ -5965,30 +5986,30 @@
       <c r="B124" s="4">
         <v>44771</v>
       </c>
-      <c r="C124" s="34">
+      <c r="C124" s="33">
         <v>44791</v>
       </c>
-      <c r="D124" s="28"/>
+      <c r="D124" s="27"/>
       <c r="E124" s="4">
         <v>44837</v>
       </c>
-      <c r="F124" s="35" t="s">
+      <c r="F124" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="G124" s="30"/>
-      <c r="H124" s="28"/>
-      <c r="I124" s="35" t="s">
+      <c r="G124" s="29"/>
+      <c r="H124" s="27"/>
+      <c r="I124" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="J124" s="28"/>
-      <c r="K124" s="36">
+      <c r="J124" s="27"/>
+      <c r="K124" s="35">
         <v>51</v>
       </c>
-      <c r="L124" s="28"/>
-      <c r="M124" s="37" t="s">
+      <c r="L124" s="27"/>
+      <c r="M124" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="33"/>
+      <c r="N124" s="32"/>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
@@ -5997,30 +6018,30 @@
       <c r="B125" s="2">
         <v>44784</v>
       </c>
-      <c r="C125" s="27">
+      <c r="C125" s="26">
         <v>44791</v>
       </c>
-      <c r="D125" s="28"/>
+      <c r="D125" s="27"/>
       <c r="E125" s="2">
         <v>44844</v>
       </c>
-      <c r="F125" s="29" t="s">
+      <c r="F125" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="G125" s="30"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="29" t="s">
+      <c r="G125" s="29"/>
+      <c r="H125" s="27"/>
+      <c r="I125" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J125" s="28"/>
-      <c r="K125" s="31">
+      <c r="J125" s="27"/>
+      <c r="K125" s="30">
         <v>35</v>
       </c>
-      <c r="L125" s="28"/>
-      <c r="M125" s="32" t="s">
+      <c r="L125" s="27"/>
+      <c r="M125" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="33"/>
+      <c r="N125" s="32"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
@@ -6029,30 +6050,30 @@
       <c r="B126" s="4">
         <v>44763</v>
       </c>
-      <c r="C126" s="34">
+      <c r="C126" s="33">
         <v>44792</v>
       </c>
-      <c r="D126" s="28"/>
+      <c r="D126" s="27"/>
       <c r="E126" s="4">
         <v>44845</v>
       </c>
-      <c r="F126" s="35" t="s">
+      <c r="F126" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="G126" s="30"/>
-      <c r="H126" s="28"/>
-      <c r="I126" s="35" t="s">
+      <c r="G126" s="29"/>
+      <c r="H126" s="27"/>
+      <c r="I126" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="J126" s="28"/>
-      <c r="K126" s="36">
+      <c r="J126" s="27"/>
+      <c r="K126" s="35">
         <v>74</v>
       </c>
-      <c r="L126" s="28"/>
-      <c r="M126" s="37" t="s">
+      <c r="L126" s="27"/>
+      <c r="M126" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="N126" s="33"/>
+      <c r="N126" s="32"/>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
@@ -6061,30 +6082,30 @@
       <c r="B127" s="2">
         <v>44792</v>
       </c>
-      <c r="C127" s="27">
+      <c r="C127" s="26">
         <v>44795</v>
       </c>
-      <c r="D127" s="28"/>
+      <c r="D127" s="27"/>
       <c r="E127" s="2">
         <v>44834</v>
       </c>
-      <c r="F127" s="29" t="s">
+      <c r="F127" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="G127" s="30"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="28"/>
-      <c r="K127" s="31">
+      <c r="G127" s="29"/>
+      <c r="H127" s="27"/>
+      <c r="I127" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="27"/>
+      <c r="K127" s="30">
         <v>51</v>
       </c>
-      <c r="L127" s="28"/>
-      <c r="M127" s="32" t="s">
+      <c r="L127" s="27"/>
+      <c r="M127" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="N127" s="33"/>
+      <c r="N127" s="32"/>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
@@ -6093,30 +6114,30 @@
       <c r="B128" s="4">
         <v>44798</v>
       </c>
-      <c r="C128" s="34">
+      <c r="C128" s="33">
         <v>44799</v>
       </c>
-      <c r="D128" s="28"/>
+      <c r="D128" s="27"/>
       <c r="E128" s="4">
         <v>44858</v>
       </c>
-      <c r="F128" s="35" t="s">
+      <c r="F128" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="G128" s="30"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="28"/>
-      <c r="K128" s="36">
+      <c r="G128" s="29"/>
+      <c r="H128" s="27"/>
+      <c r="I128" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="27"/>
+      <c r="K128" s="35">
         <v>80</v>
       </c>
-      <c r="L128" s="28"/>
-      <c r="M128" s="37" t="s">
+      <c r="L128" s="27"/>
+      <c r="M128" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="N128" s="33"/>
+      <c r="N128" s="32"/>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
@@ -6125,30 +6146,30 @@
       <c r="B129" s="2">
         <v>44799</v>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="26">
         <v>44799</v>
       </c>
-      <c r="D129" s="28"/>
+      <c r="D129" s="27"/>
       <c r="E129" s="2">
         <v>44865</v>
       </c>
-      <c r="F129" s="29" t="s">
+      <c r="F129" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="G129" s="30"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="28"/>
-      <c r="K129" s="31">
+      <c r="G129" s="29"/>
+      <c r="H129" s="27"/>
+      <c r="I129" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="27"/>
+      <c r="K129" s="30">
         <v>100</v>
       </c>
-      <c r="L129" s="28"/>
-      <c r="M129" s="32" t="s">
+      <c r="L129" s="27"/>
+      <c r="M129" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="N129" s="33"/>
+      <c r="N129" s="32"/>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="3" t="s">
@@ -6157,30 +6178,30 @@
       <c r="B130" s="4">
         <v>44802</v>
       </c>
-      <c r="C130" s="34">
+      <c r="C130" s="33">
         <v>44802</v>
       </c>
-      <c r="D130" s="28"/>
+      <c r="D130" s="27"/>
       <c r="E130" s="4">
         <v>44865</v>
       </c>
-      <c r="F130" s="35" t="s">
+      <c r="F130" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="G130" s="30"/>
-      <c r="H130" s="28"/>
-      <c r="I130" s="35" t="s">
+      <c r="G130" s="29"/>
+      <c r="H130" s="27"/>
+      <c r="I130" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J130" s="28"/>
-      <c r="K130" s="36">
+      <c r="J130" s="27"/>
+      <c r="K130" s="35">
         <v>96</v>
       </c>
-      <c r="L130" s="28"/>
-      <c r="M130" s="37" t="s">
+      <c r="L130" s="27"/>
+      <c r="M130" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="N130" s="33"/>
+      <c r="N130" s="32"/>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
@@ -6189,30 +6210,30 @@
       <c r="B131" s="2">
         <v>44799</v>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="26">
         <v>44802</v>
       </c>
-      <c r="D131" s="28"/>
+      <c r="D131" s="27"/>
       <c r="E131" s="2">
         <v>44859</v>
       </c>
-      <c r="F131" s="29" t="s">
+      <c r="F131" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="G131" s="30"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J131" s="28"/>
-      <c r="K131" s="31">
+      <c r="G131" s="29"/>
+      <c r="H131" s="27"/>
+      <c r="I131" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="27"/>
+      <c r="K131" s="30">
         <v>37</v>
       </c>
-      <c r="L131" s="28"/>
-      <c r="M131" s="32" t="s">
+      <c r="L131" s="27"/>
+      <c r="M131" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="N131" s="33"/>
+      <c r="N131" s="32"/>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="3" t="s">
@@ -6221,30 +6242,30 @@
       <c r="B132" s="4">
         <v>44799</v>
       </c>
-      <c r="C132" s="34">
+      <c r="C132" s="33">
         <v>44804</v>
       </c>
-      <c r="D132" s="28"/>
+      <c r="D132" s="27"/>
       <c r="E132" s="4">
         <v>44862</v>
       </c>
-      <c r="F132" s="35" t="s">
+      <c r="F132" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="G132" s="30"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" s="28"/>
-      <c r="K132" s="36">
+      <c r="G132" s="29"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="27"/>
+      <c r="K132" s="35">
         <v>91</v>
       </c>
-      <c r="L132" s="28"/>
-      <c r="M132" s="37" t="s">
+      <c r="L132" s="27"/>
+      <c r="M132" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="N132" s="33"/>
+      <c r="N132" s="32"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
@@ -6253,30 +6274,30 @@
       <c r="B133" s="2">
         <v>44798</v>
       </c>
-      <c r="C133" s="27">
+      <c r="C133" s="26">
         <v>44804</v>
       </c>
-      <c r="D133" s="28"/>
+      <c r="D133" s="27"/>
       <c r="E133" s="2">
         <v>44837</v>
       </c>
-      <c r="F133" s="29" t="s">
+      <c r="F133" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="G133" s="30"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="29" t="s">
+      <c r="G133" s="29"/>
+      <c r="H133" s="27"/>
+      <c r="I133" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J133" s="28"/>
-      <c r="K133" s="31">
+      <c r="J133" s="27"/>
+      <c r="K133" s="30">
         <v>56</v>
       </c>
-      <c r="L133" s="28"/>
-      <c r="M133" s="32" t="s">
+      <c r="L133" s="27"/>
+      <c r="M133" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="N133" s="33"/>
+      <c r="N133" s="32"/>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="3" t="s">
@@ -6285,30 +6306,30 @@
       <c r="B134" s="4">
         <v>44804</v>
       </c>
-      <c r="C134" s="34">
+      <c r="C134" s="33">
         <v>44805</v>
       </c>
-      <c r="D134" s="28"/>
+      <c r="D134" s="27"/>
       <c r="E134" s="4">
         <v>44805</v>
       </c>
-      <c r="F134" s="35" t="s">
+      <c r="F134" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="G134" s="30"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="28"/>
-      <c r="K134" s="36">
+      <c r="G134" s="29"/>
+      <c r="H134" s="27"/>
+      <c r="I134" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="27"/>
+      <c r="K134" s="35">
         <v>401</v>
       </c>
-      <c r="L134" s="28"/>
-      <c r="M134" s="37" t="s">
+      <c r="L134" s="27"/>
+      <c r="M134" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="N134" s="33"/>
+      <c r="N134" s="32"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
@@ -6317,30 +6338,30 @@
       <c r="B135" s="2">
         <v>44804</v>
       </c>
-      <c r="C135" s="27">
+      <c r="C135" s="26">
         <v>44805</v>
       </c>
-      <c r="D135" s="28"/>
+      <c r="D135" s="27"/>
       <c r="E135" s="2">
         <v>44866</v>
       </c>
-      <c r="F135" s="29" t="s">
+      <c r="F135" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="30"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="29" t="s">
+      <c r="G135" s="29"/>
+      <c r="H135" s="27"/>
+      <c r="I135" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="28"/>
-      <c r="K135" s="31">
+      <c r="J135" s="27"/>
+      <c r="K135" s="30">
         <v>375</v>
       </c>
-      <c r="L135" s="28"/>
-      <c r="M135" s="32" t="s">
+      <c r="L135" s="27"/>
+      <c r="M135" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="N135" s="33"/>
+      <c r="N135" s="32"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="3" t="s">
@@ -6349,30 +6370,30 @@
       <c r="B136" s="4">
         <v>44804</v>
       </c>
-      <c r="C136" s="34">
+      <c r="C136" s="33">
         <v>44806</v>
       </c>
-      <c r="D136" s="28"/>
+      <c r="D136" s="27"/>
       <c r="E136" s="4">
         <v>44805</v>
       </c>
-      <c r="F136" s="35" t="s">
+      <c r="F136" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="G136" s="30"/>
-      <c r="H136" s="28"/>
-      <c r="I136" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="28"/>
-      <c r="K136" s="36">
+      <c r="G136" s="29"/>
+      <c r="H136" s="27"/>
+      <c r="I136" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="27"/>
+      <c r="K136" s="35">
         <v>44</v>
       </c>
-      <c r="L136" s="28"/>
-      <c r="M136" s="37" t="s">
+      <c r="L136" s="27"/>
+      <c r="M136" s="36" t="s">
         <v>245</v>
       </c>
-      <c r="N136" s="33"/>
+      <c r="N136" s="32"/>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
@@ -6381,30 +6402,30 @@
       <c r="B137" s="2">
         <v>44805</v>
       </c>
-      <c r="C137" s="27">
+      <c r="C137" s="26">
         <v>44806</v>
       </c>
-      <c r="D137" s="28"/>
+      <c r="D137" s="27"/>
       <c r="E137" s="2">
         <v>44834</v>
       </c>
-      <c r="F137" s="29" t="s">
+      <c r="F137" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="G137" s="30"/>
-      <c r="H137" s="28"/>
-      <c r="I137" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J137" s="28"/>
-      <c r="K137" s="31">
+      <c r="G137" s="29"/>
+      <c r="H137" s="27"/>
+      <c r="I137" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="27"/>
+      <c r="K137" s="30">
         <v>51</v>
       </c>
-      <c r="L137" s="28"/>
-      <c r="M137" s="32" t="s">
+      <c r="L137" s="27"/>
+      <c r="M137" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="N137" s="33"/>
+      <c r="N137" s="32"/>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="3" t="s">
@@ -6413,30 +6434,30 @@
       <c r="B138" s="4">
         <v>44804</v>
       </c>
-      <c r="C138" s="34">
+      <c r="C138" s="33">
         <v>44806</v>
       </c>
-      <c r="D138" s="28"/>
+      <c r="D138" s="27"/>
       <c r="E138" s="4">
         <v>44805</v>
       </c>
-      <c r="F138" s="35" t="s">
+      <c r="F138" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="G138" s="30"/>
-      <c r="H138" s="28"/>
-      <c r="I138" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="28"/>
-      <c r="K138" s="36">
+      <c r="G138" s="29"/>
+      <c r="H138" s="27"/>
+      <c r="I138" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="27"/>
+      <c r="K138" s="35">
         <v>40</v>
       </c>
-      <c r="L138" s="28"/>
-      <c r="M138" s="37" t="s">
+      <c r="L138" s="27"/>
+      <c r="M138" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="N138" s="33"/>
+      <c r="N138" s="32"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
@@ -6445,30 +6466,30 @@
       <c r="B139" s="2">
         <v>44805</v>
       </c>
-      <c r="C139" s="27">
+      <c r="C139" s="26">
         <v>44810</v>
       </c>
-      <c r="D139" s="28"/>
+      <c r="D139" s="27"/>
       <c r="E139" s="2">
         <v>44865</v>
       </c>
-      <c r="F139" s="29" t="s">
+      <c r="F139" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="G139" s="30"/>
-      <c r="H139" s="28"/>
-      <c r="I139" s="29" t="s">
+      <c r="G139" s="29"/>
+      <c r="H139" s="27"/>
+      <c r="I139" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J139" s="28"/>
-      <c r="K139" s="31">
+      <c r="J139" s="27"/>
+      <c r="K139" s="30">
         <v>9</v>
       </c>
-      <c r="L139" s="28"/>
-      <c r="M139" s="32" t="s">
+      <c r="L139" s="27"/>
+      <c r="M139" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="N139" s="33"/>
+      <c r="N139" s="32"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="3" t="s">
@@ -6477,30 +6498,30 @@
       <c r="B140" s="4">
         <v>44805</v>
       </c>
-      <c r="C140" s="34">
+      <c r="C140" s="33">
         <v>44810</v>
       </c>
-      <c r="D140" s="28"/>
+      <c r="D140" s="27"/>
       <c r="E140" s="4">
         <v>44848</v>
       </c>
-      <c r="F140" s="35" t="s">
+      <c r="F140" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="30"/>
-      <c r="H140" s="28"/>
-      <c r="I140" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J140" s="28"/>
-      <c r="K140" s="36">
+      <c r="G140" s="29"/>
+      <c r="H140" s="27"/>
+      <c r="I140" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="27"/>
+      <c r="K140" s="35">
         <v>17</v>
       </c>
-      <c r="L140" s="28"/>
-      <c r="M140" s="37" t="s">
+      <c r="L140" s="27"/>
+      <c r="M140" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="N140" s="33"/>
+      <c r="N140" s="32"/>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
@@ -6509,30 +6530,30 @@
       <c r="B141" s="2">
         <v>44805</v>
       </c>
-      <c r="C141" s="27">
+      <c r="C141" s="26">
         <v>44810</v>
       </c>
-      <c r="D141" s="28"/>
+      <c r="D141" s="27"/>
       <c r="E141" s="2">
         <v>44957</v>
       </c>
-      <c r="F141" s="29" t="s">
+      <c r="F141" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="G141" s="30"/>
-      <c r="H141" s="28"/>
-      <c r="I141" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J141" s="28"/>
-      <c r="K141" s="31">
+      <c r="G141" s="29"/>
+      <c r="H141" s="27"/>
+      <c r="I141" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="27"/>
+      <c r="K141" s="30">
         <v>5</v>
       </c>
-      <c r="L141" s="28"/>
-      <c r="M141" s="32" t="s">
+      <c r="L141" s="27"/>
+      <c r="M141" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="N141" s="33"/>
+      <c r="N141" s="32"/>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="3" t="s">
@@ -6541,30 +6562,30 @@
       <c r="B142" s="4">
         <v>44805</v>
       </c>
-      <c r="C142" s="34">
+      <c r="C142" s="33">
         <v>44810</v>
       </c>
-      <c r="D142" s="28"/>
+      <c r="D142" s="27"/>
       <c r="E142" s="4">
         <v>44824</v>
       </c>
-      <c r="F142" s="35" t="s">
+      <c r="F142" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="G142" s="30"/>
-      <c r="H142" s="28"/>
-      <c r="I142" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J142" s="28"/>
-      <c r="K142" s="36">
+      <c r="G142" s="29"/>
+      <c r="H142" s="27"/>
+      <c r="I142" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="27"/>
+      <c r="K142" s="35">
         <v>45</v>
       </c>
-      <c r="L142" s="28"/>
-      <c r="M142" s="37" t="s">
+      <c r="L142" s="27"/>
+      <c r="M142" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N142" s="33"/>
+      <c r="N142" s="32"/>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
@@ -6573,30 +6594,30 @@
       <c r="B143" s="2">
         <v>44807</v>
       </c>
-      <c r="C143" s="27">
+      <c r="C143" s="26">
         <v>44811</v>
       </c>
-      <c r="D143" s="28"/>
+      <c r="D143" s="27"/>
       <c r="E143" s="2">
         <v>44813</v>
       </c>
-      <c r="F143" s="29" t="s">
+      <c r="F143" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="G143" s="30"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="29" t="s">
+      <c r="G143" s="29"/>
+      <c r="H143" s="27"/>
+      <c r="I143" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J143" s="28"/>
-      <c r="K143" s="31">
+      <c r="J143" s="27"/>
+      <c r="K143" s="30">
         <v>132</v>
       </c>
-      <c r="L143" s="28"/>
-      <c r="M143" s="32" t="s">
+      <c r="L143" s="27"/>
+      <c r="M143" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="N143" s="33"/>
+      <c r="N143" s="32"/>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="3" t="s">
@@ -6605,30 +6626,30 @@
       <c r="B144" s="4">
         <v>44805</v>
       </c>
-      <c r="C144" s="34">
+      <c r="C144" s="33">
         <v>44811</v>
       </c>
-      <c r="D144" s="28"/>
+      <c r="D144" s="27"/>
       <c r="E144" s="4">
         <v>44865</v>
       </c>
-      <c r="F144" s="35" t="s">
+      <c r="F144" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="G144" s="30"/>
-      <c r="H144" s="28"/>
-      <c r="I144" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J144" s="28"/>
-      <c r="K144" s="36">
+      <c r="G144" s="29"/>
+      <c r="H144" s="27"/>
+      <c r="I144" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="27"/>
+      <c r="K144" s="35">
         <v>66</v>
       </c>
-      <c r="L144" s="28"/>
-      <c r="M144" s="37" t="s">
+      <c r="L144" s="27"/>
+      <c r="M144" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="N144" s="33"/>
+      <c r="N144" s="32"/>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
@@ -6637,30 +6658,30 @@
       <c r="B145" s="2">
         <v>44804</v>
       </c>
-      <c r="C145" s="27">
+      <c r="C145" s="26">
         <v>44812</v>
       </c>
-      <c r="D145" s="28"/>
+      <c r="D145" s="27"/>
       <c r="E145" s="2">
         <v>44864</v>
       </c>
-      <c r="F145" s="29" t="s">
+      <c r="F145" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="30"/>
-      <c r="H145" s="28"/>
-      <c r="I145" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J145" s="28"/>
-      <c r="K145" s="31">
+      <c r="G145" s="29"/>
+      <c r="H145" s="27"/>
+      <c r="I145" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="27"/>
+      <c r="K145" s="30">
         <v>69</v>
       </c>
-      <c r="L145" s="28"/>
-      <c r="M145" s="32" t="s">
+      <c r="L145" s="27"/>
+      <c r="M145" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="N145" s="33"/>
+      <c r="N145" s="32"/>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="3" t="s">
@@ -6669,30 +6690,30 @@
       <c r="B146" s="4">
         <v>44812</v>
       </c>
-      <c r="C146" s="34">
+      <c r="C146" s="33">
         <v>44812</v>
       </c>
-      <c r="D146" s="28"/>
+      <c r="D146" s="27"/>
       <c r="E146" s="4">
         <v>44876</v>
       </c>
-      <c r="F146" s="35" t="s">
+      <c r="F146" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="G146" s="30"/>
-      <c r="H146" s="28"/>
-      <c r="I146" s="35" t="s">
+      <c r="G146" s="29"/>
+      <c r="H146" s="27"/>
+      <c r="I146" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J146" s="28"/>
-      <c r="K146" s="36">
+      <c r="J146" s="27"/>
+      <c r="K146" s="35">
         <v>48</v>
       </c>
-      <c r="L146" s="28"/>
-      <c r="M146" s="37" t="s">
+      <c r="L146" s="27"/>
+      <c r="M146" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="N146" s="33"/>
+      <c r="N146" s="32"/>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
@@ -6701,30 +6722,30 @@
       <c r="B147" s="2">
         <v>44810</v>
       </c>
-      <c r="C147" s="27">
+      <c r="C147" s="26">
         <v>44812</v>
       </c>
-      <c r="D147" s="28"/>
+      <c r="D147" s="27"/>
       <c r="E147" s="2">
         <v>44876</v>
       </c>
-      <c r="F147" s="29" t="s">
+      <c r="F147" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="G147" s="30"/>
-      <c r="H147" s="28"/>
-      <c r="I147" s="29" t="s">
+      <c r="G147" s="29"/>
+      <c r="H147" s="27"/>
+      <c r="I147" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J147" s="28"/>
-      <c r="K147" s="31">
+      <c r="J147" s="27"/>
+      <c r="K147" s="30">
         <v>33</v>
       </c>
-      <c r="L147" s="28"/>
-      <c r="M147" s="32" t="s">
+      <c r="L147" s="27"/>
+      <c r="M147" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="N147" s="33"/>
+      <c r="N147" s="32"/>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="3" t="s">
@@ -6733,30 +6754,30 @@
       <c r="B148" s="4">
         <v>44778</v>
       </c>
-      <c r="C148" s="34">
+      <c r="C148" s="33">
         <v>44813</v>
       </c>
-      <c r="D148" s="28"/>
+      <c r="D148" s="27"/>
       <c r="E148" s="4">
         <v>44926</v>
       </c>
-      <c r="F148" s="35" t="s">
+      <c r="F148" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="G148" s="30"/>
-      <c r="H148" s="28"/>
-      <c r="I148" s="35" t="s">
+      <c r="G148" s="29"/>
+      <c r="H148" s="27"/>
+      <c r="I148" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J148" s="28"/>
-      <c r="K148" s="36">
+      <c r="J148" s="27"/>
+      <c r="K148" s="35">
         <v>5</v>
       </c>
-      <c r="L148" s="28"/>
-      <c r="M148" s="37" t="s">
+      <c r="L148" s="27"/>
+      <c r="M148" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="N148" s="33"/>
+      <c r="N148" s="32"/>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
@@ -6765,30 +6786,30 @@
       <c r="B149" s="2">
         <v>44811</v>
       </c>
-      <c r="C149" s="27">
+      <c r="C149" s="26">
         <v>44813</v>
       </c>
-      <c r="D149" s="28"/>
+      <c r="D149" s="27"/>
       <c r="E149" s="2">
         <v>45046</v>
       </c>
-      <c r="F149" s="29" t="s">
+      <c r="F149" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="G149" s="30"/>
-      <c r="H149" s="28"/>
-      <c r="I149" s="29" t="s">
+      <c r="G149" s="29"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J149" s="28"/>
-      <c r="K149" s="31">
+      <c r="J149" s="27"/>
+      <c r="K149" s="30">
         <v>26</v>
       </c>
-      <c r="L149" s="28"/>
-      <c r="M149" s="32" t="s">
+      <c r="L149" s="27"/>
+      <c r="M149" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="N149" s="33"/>
+      <c r="N149" s="32"/>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="3" t="s">
@@ -6797,30 +6818,30 @@
       <c r="B150" s="4">
         <v>44810</v>
       </c>
-      <c r="C150" s="34">
+      <c r="C150" s="33">
         <v>44813</v>
       </c>
-      <c r="D150" s="28"/>
+      <c r="D150" s="27"/>
       <c r="E150" s="4">
         <v>44870</v>
       </c>
-      <c r="F150" s="35" t="s">
+      <c r="F150" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="G150" s="30"/>
-      <c r="H150" s="28"/>
-      <c r="I150" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J150" s="28"/>
-      <c r="K150" s="36">
+      <c r="G150" s="29"/>
+      <c r="H150" s="27"/>
+      <c r="I150" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="27"/>
+      <c r="K150" s="35">
         <v>13</v>
       </c>
-      <c r="L150" s="28"/>
-      <c r="M150" s="37" t="s">
+      <c r="L150" s="27"/>
+      <c r="M150" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="N150" s="33"/>
+      <c r="N150" s="32"/>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
@@ -6829,30 +6850,30 @@
       <c r="B151" s="2">
         <v>44812</v>
       </c>
-      <c r="C151" s="27">
+      <c r="C151" s="26">
         <v>44816</v>
       </c>
-      <c r="D151" s="28"/>
+      <c r="D151" s="27"/>
       <c r="E151" s="2">
         <v>44873</v>
       </c>
-      <c r="F151" s="29" t="s">
+      <c r="F151" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="G151" s="30"/>
-      <c r="H151" s="28"/>
-      <c r="I151" s="29" t="s">
+      <c r="G151" s="29"/>
+      <c r="H151" s="27"/>
+      <c r="I151" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J151" s="28"/>
-      <c r="K151" s="31">
+      <c r="J151" s="27"/>
+      <c r="K151" s="30">
         <v>50</v>
       </c>
-      <c r="L151" s="28"/>
-      <c r="M151" s="32" t="s">
+      <c r="L151" s="27"/>
+      <c r="M151" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="N151" s="33"/>
+      <c r="N151" s="32"/>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="3" t="s">
@@ -6861,30 +6882,30 @@
       <c r="B152" s="4">
         <v>44791</v>
       </c>
-      <c r="C152" s="34">
+      <c r="C152" s="33">
         <v>44816</v>
       </c>
-      <c r="D152" s="28"/>
+      <c r="D152" s="27"/>
       <c r="E152" s="4">
         <v>44856</v>
       </c>
-      <c r="F152" s="35" t="s">
+      <c r="F152" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="30"/>
-      <c r="H152" s="28"/>
-      <c r="I152" s="35" t="s">
+      <c r="G152" s="29"/>
+      <c r="H152" s="27"/>
+      <c r="I152" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J152" s="28"/>
-      <c r="K152" s="36">
+      <c r="J152" s="27"/>
+      <c r="K152" s="35">
         <v>104</v>
       </c>
-      <c r="L152" s="28"/>
-      <c r="M152" s="37" t="s">
+      <c r="L152" s="27"/>
+      <c r="M152" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="N152" s="33"/>
+      <c r="N152" s="32"/>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="1" t="s">
@@ -6893,30 +6914,30 @@
       <c r="B153" s="2">
         <v>44813</v>
       </c>
-      <c r="C153" s="27">
+      <c r="C153" s="26">
         <v>44817</v>
       </c>
-      <c r="D153" s="28"/>
+      <c r="D153" s="27"/>
       <c r="E153" s="2">
         <v>45199</v>
       </c>
-      <c r="F153" s="29" t="s">
+      <c r="F153" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G153" s="30"/>
-      <c r="H153" s="28"/>
-      <c r="I153" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J153" s="28"/>
-      <c r="K153" s="31">
+      <c r="G153" s="29"/>
+      <c r="H153" s="27"/>
+      <c r="I153" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="27"/>
+      <c r="K153" s="30">
         <v>1</v>
       </c>
-      <c r="L153" s="28"/>
-      <c r="M153" s="32" t="s">
+      <c r="L153" s="27"/>
+      <c r="M153" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N153" s="33"/>
+      <c r="N153" s="32"/>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="3" t="s">
@@ -6925,30 +6946,30 @@
       <c r="B154" s="4">
         <v>44813</v>
       </c>
-      <c r="C154" s="34">
+      <c r="C154" s="33">
         <v>44817</v>
       </c>
-      <c r="D154" s="28"/>
+      <c r="D154" s="27"/>
       <c r="E154" s="4">
         <v>44848</v>
       </c>
-      <c r="F154" s="35" t="s">
+      <c r="F154" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G154" s="30"/>
-      <c r="H154" s="28"/>
-      <c r="I154" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J154" s="28"/>
-      <c r="K154" s="36">
+      <c r="G154" s="29"/>
+      <c r="H154" s="27"/>
+      <c r="I154" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="27"/>
+      <c r="K154" s="35">
         <v>2</v>
       </c>
-      <c r="L154" s="28"/>
-      <c r="M154" s="37" t="s">
+      <c r="L154" s="27"/>
+      <c r="M154" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N154" s="33"/>
+      <c r="N154" s="32"/>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="1" t="s">
@@ -6957,30 +6978,30 @@
       <c r="B155" s="2">
         <v>44813</v>
       </c>
-      <c r="C155" s="27">
+      <c r="C155" s="26">
         <v>44817</v>
       </c>
-      <c r="D155" s="28"/>
+      <c r="D155" s="27"/>
       <c r="E155" s="2">
         <v>45198</v>
       </c>
-      <c r="F155" s="29" t="s">
+      <c r="F155" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G155" s="30"/>
-      <c r="H155" s="28"/>
-      <c r="I155" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J155" s="28"/>
-      <c r="K155" s="31">
+      <c r="G155" s="29"/>
+      <c r="H155" s="27"/>
+      <c r="I155" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="27"/>
+      <c r="K155" s="30">
         <v>2</v>
       </c>
-      <c r="L155" s="28"/>
-      <c r="M155" s="32" t="s">
+      <c r="L155" s="27"/>
+      <c r="M155" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N155" s="33"/>
+      <c r="N155" s="32"/>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="3" t="s">
@@ -6989,30 +7010,30 @@
       <c r="B156" s="4">
         <v>44813</v>
       </c>
-      <c r="C156" s="34">
+      <c r="C156" s="33">
         <v>44817</v>
       </c>
-      <c r="D156" s="28"/>
+      <c r="D156" s="27"/>
       <c r="E156" s="4">
         <v>45044</v>
       </c>
-      <c r="F156" s="35" t="s">
+      <c r="F156" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G156" s="30"/>
-      <c r="H156" s="28"/>
-      <c r="I156" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J156" s="28"/>
-      <c r="K156" s="36">
+      <c r="G156" s="29"/>
+      <c r="H156" s="27"/>
+      <c r="I156" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="27"/>
+      <c r="K156" s="35">
         <v>5</v>
       </c>
-      <c r="L156" s="28"/>
-      <c r="M156" s="37" t="s">
+      <c r="L156" s="27"/>
+      <c r="M156" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N156" s="33"/>
+      <c r="N156" s="32"/>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="1" t="s">
@@ -7021,30 +7042,30 @@
       <c r="B157" s="2">
         <v>44813</v>
       </c>
-      <c r="C157" s="27">
+      <c r="C157" s="26">
         <v>44817</v>
       </c>
-      <c r="D157" s="28"/>
+      <c r="D157" s="27"/>
       <c r="E157" s="2">
         <v>45107</v>
       </c>
-      <c r="F157" s="29" t="s">
+      <c r="F157" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G157" s="30"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J157" s="28"/>
-      <c r="K157" s="31">
+      <c r="G157" s="29"/>
+      <c r="H157" s="27"/>
+      <c r="I157" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="27"/>
+      <c r="K157" s="30">
         <v>2</v>
       </c>
-      <c r="L157" s="28"/>
-      <c r="M157" s="32" t="s">
+      <c r="L157" s="27"/>
+      <c r="M157" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N157" s="33"/>
+      <c r="N157" s="32"/>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="3" t="s">
@@ -7053,30 +7074,30 @@
       <c r="B158" s="4">
         <v>44813</v>
       </c>
-      <c r="C158" s="34">
+      <c r="C158" s="33">
         <v>44817</v>
       </c>
-      <c r="D158" s="28"/>
+      <c r="D158" s="27"/>
       <c r="E158" s="4">
         <v>45192</v>
       </c>
-      <c r="F158" s="35" t="s">
+      <c r="F158" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G158" s="30"/>
-      <c r="H158" s="28"/>
-      <c r="I158" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" s="28"/>
-      <c r="K158" s="36">
+      <c r="G158" s="29"/>
+      <c r="H158" s="27"/>
+      <c r="I158" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="27"/>
+      <c r="K158" s="35">
         <v>1</v>
       </c>
-      <c r="L158" s="28"/>
-      <c r="M158" s="37" t="s">
+      <c r="L158" s="27"/>
+      <c r="M158" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N158" s="33"/>
+      <c r="N158" s="32"/>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="1" t="s">
@@ -7085,30 +7106,30 @@
       <c r="B159" s="2">
         <v>44813</v>
       </c>
-      <c r="C159" s="27">
+      <c r="C159" s="26">
         <v>44817</v>
       </c>
-      <c r="D159" s="28"/>
+      <c r="D159" s="27"/>
       <c r="E159" s="2">
         <v>44957</v>
       </c>
-      <c r="F159" s="29" t="s">
+      <c r="F159" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G159" s="30"/>
-      <c r="H159" s="28"/>
-      <c r="I159" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J159" s="28"/>
-      <c r="K159" s="31">
+      <c r="G159" s="29"/>
+      <c r="H159" s="27"/>
+      <c r="I159" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="27"/>
+      <c r="K159" s="30">
         <v>4</v>
       </c>
-      <c r="L159" s="28"/>
-      <c r="M159" s="32" t="s">
+      <c r="L159" s="27"/>
+      <c r="M159" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N159" s="33"/>
+      <c r="N159" s="32"/>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="3" t="s">
@@ -7117,30 +7138,30 @@
       <c r="B160" s="4">
         <v>44813</v>
       </c>
-      <c r="C160" s="34">
+      <c r="C160" s="33">
         <v>44817</v>
       </c>
-      <c r="D160" s="28"/>
+      <c r="D160" s="27"/>
       <c r="E160" s="4">
         <v>44834</v>
       </c>
-      <c r="F160" s="35" t="s">
+      <c r="F160" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G160" s="30"/>
-      <c r="H160" s="28"/>
-      <c r="I160" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J160" s="28"/>
-      <c r="K160" s="36">
+      <c r="G160" s="29"/>
+      <c r="H160" s="27"/>
+      <c r="I160" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="27"/>
+      <c r="K160" s="35">
         <v>4</v>
       </c>
-      <c r="L160" s="28"/>
-      <c r="M160" s="37" t="s">
+      <c r="L160" s="27"/>
+      <c r="M160" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N160" s="33"/>
+      <c r="N160" s="32"/>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="1" t="s">
@@ -7149,30 +7170,30 @@
       <c r="B161" s="2">
         <v>44813</v>
       </c>
-      <c r="C161" s="27">
+      <c r="C161" s="26">
         <v>44817</v>
       </c>
-      <c r="D161" s="28"/>
+      <c r="D161" s="27"/>
       <c r="E161" s="2">
         <v>45077</v>
       </c>
-      <c r="F161" s="29" t="s">
+      <c r="F161" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G161" s="30"/>
-      <c r="H161" s="28"/>
-      <c r="I161" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J161" s="28"/>
-      <c r="K161" s="31">
+      <c r="G161" s="29"/>
+      <c r="H161" s="27"/>
+      <c r="I161" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="27"/>
+      <c r="K161" s="30">
         <v>3</v>
       </c>
-      <c r="L161" s="28"/>
-      <c r="M161" s="32" t="s">
+      <c r="L161" s="27"/>
+      <c r="M161" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N161" s="33"/>
+      <c r="N161" s="32"/>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="3" t="s">
@@ -7181,30 +7202,30 @@
       <c r="B162" s="4">
         <v>44813</v>
       </c>
-      <c r="C162" s="34">
+      <c r="C162" s="33">
         <v>44817</v>
       </c>
-      <c r="D162" s="28"/>
+      <c r="D162" s="27"/>
       <c r="E162" s="4">
         <v>45093</v>
       </c>
-      <c r="F162" s="35" t="s">
+      <c r="F162" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G162" s="30"/>
-      <c r="H162" s="28"/>
-      <c r="I162" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J162" s="28"/>
-      <c r="K162" s="36">
+      <c r="G162" s="29"/>
+      <c r="H162" s="27"/>
+      <c r="I162" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="27"/>
+      <c r="K162" s="35">
         <v>8</v>
       </c>
-      <c r="L162" s="28"/>
-      <c r="M162" s="37" t="s">
+      <c r="L162" s="27"/>
+      <c r="M162" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N162" s="33"/>
+      <c r="N162" s="32"/>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="1" t="s">
@@ -7213,30 +7234,30 @@
       <c r="B163" s="2">
         <v>44813</v>
       </c>
-      <c r="C163" s="27">
+      <c r="C163" s="26">
         <v>44817</v>
       </c>
-      <c r="D163" s="28"/>
+      <c r="D163" s="27"/>
       <c r="E163" s="2">
         <v>45565</v>
       </c>
-      <c r="F163" s="29" t="s">
+      <c r="F163" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G163" s="30"/>
-      <c r="H163" s="28"/>
-      <c r="I163" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J163" s="28"/>
-      <c r="K163" s="31">
+      <c r="G163" s="29"/>
+      <c r="H163" s="27"/>
+      <c r="I163" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="27"/>
+      <c r="K163" s="30">
         <v>1</v>
       </c>
-      <c r="L163" s="28"/>
-      <c r="M163" s="32" t="s">
+      <c r="L163" s="27"/>
+      <c r="M163" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N163" s="33"/>
+      <c r="N163" s="32"/>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="3" t="s">
@@ -7245,30 +7266,30 @@
       <c r="B164" s="4">
         <v>44813</v>
       </c>
-      <c r="C164" s="34">
+      <c r="C164" s="33">
         <v>44817</v>
       </c>
-      <c r="D164" s="28"/>
+      <c r="D164" s="27"/>
       <c r="E164" s="4">
         <v>45227</v>
       </c>
-      <c r="F164" s="35" t="s">
+      <c r="F164" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G164" s="30"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J164" s="28"/>
-      <c r="K164" s="36">
+      <c r="G164" s="29"/>
+      <c r="H164" s="27"/>
+      <c r="I164" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="27"/>
+      <c r="K164" s="35">
         <v>2</v>
       </c>
-      <c r="L164" s="28"/>
-      <c r="M164" s="37" t="s">
+      <c r="L164" s="27"/>
+      <c r="M164" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N164" s="33"/>
+      <c r="N164" s="32"/>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="1" t="s">
@@ -7277,30 +7298,30 @@
       <c r="B165" s="2">
         <v>44813</v>
       </c>
-      <c r="C165" s="27">
+      <c r="C165" s="26">
         <v>44817</v>
       </c>
-      <c r="D165" s="28"/>
+      <c r="D165" s="27"/>
       <c r="E165" s="2">
         <v>45046</v>
       </c>
-      <c r="F165" s="29" t="s">
+      <c r="F165" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G165" s="30"/>
-      <c r="H165" s="28"/>
-      <c r="I165" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J165" s="28"/>
-      <c r="K165" s="31">
+      <c r="G165" s="29"/>
+      <c r="H165" s="27"/>
+      <c r="I165" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="27"/>
+      <c r="K165" s="30">
         <v>1</v>
       </c>
-      <c r="L165" s="28"/>
-      <c r="M165" s="32" t="s">
+      <c r="L165" s="27"/>
+      <c r="M165" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N165" s="33"/>
+      <c r="N165" s="32"/>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="3" t="s">
@@ -7309,30 +7330,30 @@
       <c r="B166" s="4">
         <v>44813</v>
       </c>
-      <c r="C166" s="34">
+      <c r="C166" s="33">
         <v>44817</v>
       </c>
-      <c r="D166" s="28"/>
+      <c r="D166" s="27"/>
       <c r="E166" s="4">
         <v>45092</v>
       </c>
-      <c r="F166" s="35" t="s">
+      <c r="F166" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G166" s="30"/>
-      <c r="H166" s="28"/>
-      <c r="I166" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J166" s="28"/>
-      <c r="K166" s="36">
+      <c r="G166" s="29"/>
+      <c r="H166" s="27"/>
+      <c r="I166" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="27"/>
+      <c r="K166" s="35">
         <v>3</v>
       </c>
-      <c r="L166" s="28"/>
-      <c r="M166" s="37" t="s">
+      <c r="L166" s="27"/>
+      <c r="M166" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N166" s="33"/>
+      <c r="N166" s="32"/>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="1" t="s">
@@ -7341,30 +7362,30 @@
       <c r="B167" s="2">
         <v>44813</v>
       </c>
-      <c r="C167" s="27">
+      <c r="C167" s="26">
         <v>44817</v>
       </c>
-      <c r="D167" s="28"/>
+      <c r="D167" s="27"/>
       <c r="E167" s="2">
         <v>44985</v>
       </c>
-      <c r="F167" s="29" t="s">
+      <c r="F167" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G167" s="30"/>
-      <c r="H167" s="28"/>
-      <c r="I167" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J167" s="28"/>
-      <c r="K167" s="31">
+      <c r="G167" s="29"/>
+      <c r="H167" s="27"/>
+      <c r="I167" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="27"/>
+      <c r="K167" s="30">
         <v>1</v>
       </c>
-      <c r="L167" s="28"/>
-      <c r="M167" s="32" t="s">
+      <c r="L167" s="27"/>
+      <c r="M167" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="N167" s="33"/>
+      <c r="N167" s="32"/>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="3" t="s">
@@ -7373,30 +7394,30 @@
       <c r="B168" s="4">
         <v>44813</v>
       </c>
-      <c r="C168" s="34">
+      <c r="C168" s="33">
         <v>44817</v>
       </c>
-      <c r="D168" s="28"/>
+      <c r="D168" s="27"/>
       <c r="E168" s="4">
         <v>45555</v>
       </c>
-      <c r="F168" s="35" t="s">
+      <c r="F168" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="G168" s="30"/>
-      <c r="H168" s="28"/>
-      <c r="I168" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J168" s="28"/>
-      <c r="K168" s="36">
+      <c r="G168" s="29"/>
+      <c r="H168" s="27"/>
+      <c r="I168" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="27"/>
+      <c r="K168" s="35">
         <v>1</v>
       </c>
-      <c r="L168" s="28"/>
-      <c r="M168" s="37" t="s">
+      <c r="L168" s="27"/>
+      <c r="M168" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="N168" s="33"/>
+      <c r="N168" s="32"/>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="1" t="s">
@@ -7405,30 +7426,30 @@
       <c r="B169" s="2">
         <v>44811</v>
       </c>
-      <c r="C169" s="27">
+      <c r="C169" s="26">
         <v>44817</v>
       </c>
-      <c r="D169" s="28"/>
+      <c r="D169" s="27"/>
       <c r="E169" s="2">
         <v>44882</v>
       </c>
-      <c r="F169" s="29" t="s">
+      <c r="F169" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="G169" s="30"/>
-      <c r="H169" s="28"/>
-      <c r="I169" s="29" t="s">
+      <c r="G169" s="29"/>
+      <c r="H169" s="27"/>
+      <c r="I169" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J169" s="28"/>
-      <c r="K169" s="31">
+      <c r="J169" s="27"/>
+      <c r="K169" s="30">
         <v>92</v>
       </c>
-      <c r="L169" s="28"/>
-      <c r="M169" s="32" t="s">
+      <c r="L169" s="27"/>
+      <c r="M169" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="N169" s="33"/>
+      <c r="N169" s="32"/>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="3" t="s">
@@ -7437,30 +7458,30 @@
       <c r="B170" s="4">
         <v>44811</v>
       </c>
-      <c r="C170" s="34">
+      <c r="C170" s="33">
         <v>44817</v>
       </c>
-      <c r="D170" s="28"/>
+      <c r="D170" s="27"/>
       <c r="E170" s="4">
         <v>44882</v>
       </c>
-      <c r="F170" s="35" t="s">
+      <c r="F170" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="G170" s="30"/>
-      <c r="H170" s="28"/>
-      <c r="I170" s="35" t="s">
+      <c r="G170" s="29"/>
+      <c r="H170" s="27"/>
+      <c r="I170" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J170" s="28"/>
-      <c r="K170" s="36">
+      <c r="J170" s="27"/>
+      <c r="K170" s="35">
         <v>169</v>
       </c>
-      <c r="L170" s="28"/>
-      <c r="M170" s="37" t="s">
+      <c r="L170" s="27"/>
+      <c r="M170" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="N170" s="33"/>
+      <c r="N170" s="32"/>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="1" t="s">
@@ -7469,30 +7490,30 @@
       <c r="B171" s="2">
         <v>44817</v>
       </c>
-      <c r="C171" s="27">
+      <c r="C171" s="26">
         <v>44818</v>
       </c>
-      <c r="D171" s="28"/>
+      <c r="D171" s="27"/>
       <c r="E171" s="2">
         <v>44888</v>
       </c>
-      <c r="F171" s="29" t="s">
+      <c r="F171" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="G171" s="30"/>
-      <c r="H171" s="28"/>
-      <c r="I171" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J171" s="28"/>
-      <c r="K171" s="31">
+      <c r="G171" s="29"/>
+      <c r="H171" s="27"/>
+      <c r="I171" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="27"/>
+      <c r="K171" s="30">
         <v>99</v>
       </c>
-      <c r="L171" s="28"/>
-      <c r="M171" s="32" t="s">
+      <c r="L171" s="27"/>
+      <c r="M171" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="N171" s="33"/>
+      <c r="N171" s="32"/>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="3" t="s">
@@ -7501,30 +7522,30 @@
       <c r="B172" s="4">
         <v>44817</v>
       </c>
-      <c r="C172" s="34">
+      <c r="C172" s="33">
         <v>44818</v>
       </c>
-      <c r="D172" s="28"/>
+      <c r="D172" s="27"/>
       <c r="E172" s="4">
         <v>44911</v>
       </c>
-      <c r="F172" s="35" t="s">
+      <c r="F172" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="G172" s="30"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="35" t="s">
+      <c r="G172" s="29"/>
+      <c r="H172" s="27"/>
+      <c r="I172" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J172" s="28"/>
-      <c r="K172" s="36">
+      <c r="J172" s="27"/>
+      <c r="K172" s="35">
         <v>10</v>
       </c>
-      <c r="L172" s="28"/>
-      <c r="M172" s="37" t="s">
+      <c r="L172" s="27"/>
+      <c r="M172" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="N172" s="33"/>
+      <c r="N172" s="32"/>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="1" t="s">
@@ -7533,30 +7554,30 @@
       <c r="B173" s="2">
         <v>44817</v>
       </c>
-      <c r="C173" s="27">
+      <c r="C173" s="26">
         <v>44818</v>
       </c>
-      <c r="D173" s="28"/>
+      <c r="D173" s="27"/>
       <c r="E173" s="2">
         <v>44876</v>
       </c>
-      <c r="F173" s="29" t="s">
+      <c r="F173" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="G173" s="30"/>
-      <c r="H173" s="28"/>
-      <c r="I173" s="29" t="s">
+      <c r="G173" s="29"/>
+      <c r="H173" s="27"/>
+      <c r="I173" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J173" s="28"/>
-      <c r="K173" s="31">
+      <c r="J173" s="27"/>
+      <c r="K173" s="30">
         <v>69</v>
       </c>
-      <c r="L173" s="28"/>
-      <c r="M173" s="32" t="s">
+      <c r="L173" s="27"/>
+      <c r="M173" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="N173" s="33"/>
+      <c r="N173" s="32"/>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="3" t="s">
@@ -7565,30 +7586,30 @@
       <c r="B174" s="4">
         <v>44810</v>
       </c>
-      <c r="C174" s="34">
+      <c r="C174" s="33">
         <v>44819</v>
       </c>
-      <c r="D174" s="28"/>
+      <c r="D174" s="27"/>
       <c r="E174" s="4">
         <v>44870</v>
       </c>
-      <c r="F174" s="35" t="s">
+      <c r="F174" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="G174" s="30"/>
-      <c r="H174" s="28"/>
-      <c r="I174" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J174" s="28"/>
-      <c r="K174" s="36">
+      <c r="G174" s="29"/>
+      <c r="H174" s="27"/>
+      <c r="I174" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="27"/>
+      <c r="K174" s="35">
         <v>115</v>
       </c>
-      <c r="L174" s="28"/>
-      <c r="M174" s="37" t="s">
+      <c r="L174" s="27"/>
+      <c r="M174" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="N174" s="33"/>
+      <c r="N174" s="32"/>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="1" t="s">
@@ -7597,30 +7618,30 @@
       <c r="B175" s="2">
         <v>44806</v>
       </c>
-      <c r="C175" s="27">
+      <c r="C175" s="26">
         <v>44819</v>
       </c>
-      <c r="D175" s="28"/>
+      <c r="D175" s="27"/>
       <c r="E175" s="2">
         <v>44867</v>
       </c>
-      <c r="F175" s="29" t="s">
+      <c r="F175" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="G175" s="30"/>
-      <c r="H175" s="28"/>
-      <c r="I175" s="29" t="s">
+      <c r="G175" s="29"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J175" s="28"/>
-      <c r="K175" s="31">
+      <c r="J175" s="27"/>
+      <c r="K175" s="30">
         <v>109</v>
       </c>
-      <c r="L175" s="28"/>
-      <c r="M175" s="32" t="s">
+      <c r="L175" s="27"/>
+      <c r="M175" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="N175" s="33"/>
+      <c r="N175" s="32"/>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="3" t="s">
@@ -7629,30 +7650,30 @@
       <c r="B176" s="4">
         <v>44818</v>
       </c>
-      <c r="C176" s="34">
+      <c r="C176" s="33">
         <v>44819</v>
       </c>
-      <c r="D176" s="28"/>
+      <c r="D176" s="27"/>
       <c r="E176" s="4">
         <v>44883</v>
       </c>
-      <c r="F176" s="35" t="s">
+      <c r="F176" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="G176" s="30"/>
-      <c r="H176" s="28"/>
-      <c r="I176" s="35" t="s">
+      <c r="G176" s="29"/>
+      <c r="H176" s="27"/>
+      <c r="I176" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J176" s="28"/>
-      <c r="K176" s="36">
+      <c r="J176" s="27"/>
+      <c r="K176" s="35">
         <v>113</v>
       </c>
-      <c r="L176" s="28"/>
-      <c r="M176" s="37" t="s">
+      <c r="L176" s="27"/>
+      <c r="M176" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="N176" s="33"/>
+      <c r="N176" s="32"/>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="1" t="s">
@@ -7661,30 +7682,30 @@
       <c r="B177" s="2">
         <v>44818</v>
       </c>
-      <c r="C177" s="27">
+      <c r="C177" s="26">
         <v>44819</v>
       </c>
-      <c r="D177" s="28"/>
+      <c r="D177" s="27"/>
       <c r="E177" s="2">
         <v>44872</v>
       </c>
-      <c r="F177" s="29" t="s">
+      <c r="F177" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="G177" s="30"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="29" t="s">
+      <c r="G177" s="29"/>
+      <c r="H177" s="27"/>
+      <c r="I177" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J177" s="28"/>
-      <c r="K177" s="31">
+      <c r="J177" s="27"/>
+      <c r="K177" s="30">
         <v>13</v>
       </c>
-      <c r="L177" s="28"/>
-      <c r="M177" s="32" t="s">
+      <c r="L177" s="27"/>
+      <c r="M177" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="N177" s="33"/>
+      <c r="N177" s="32"/>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="3" t="s">
@@ -7693,30 +7714,30 @@
       <c r="B178" s="4">
         <v>44818</v>
       </c>
-      <c r="C178" s="34">
+      <c r="C178" s="33">
         <v>44819</v>
       </c>
-      <c r="D178" s="28"/>
+      <c r="D178" s="27"/>
       <c r="E178" s="4">
         <v>44818</v>
       </c>
-      <c r="F178" s="35" t="s">
+      <c r="F178" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="G178" s="30"/>
-      <c r="H178" s="28"/>
-      <c r="I178" s="35" t="s">
+      <c r="G178" s="29"/>
+      <c r="H178" s="27"/>
+      <c r="I178" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J178" s="28"/>
-      <c r="K178" s="36">
+      <c r="J178" s="27"/>
+      <c r="K178" s="35">
         <v>1</v>
       </c>
-      <c r="L178" s="28"/>
-      <c r="M178" s="37" t="s">
+      <c r="L178" s="27"/>
+      <c r="M178" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="N178" s="33"/>
+      <c r="N178" s="32"/>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="1" t="s">
@@ -7725,30 +7746,30 @@
       <c r="B179" s="2">
         <v>44811</v>
       </c>
-      <c r="C179" s="27">
+      <c r="C179" s="26">
         <v>44819</v>
       </c>
-      <c r="D179" s="28"/>
+      <c r="D179" s="27"/>
       <c r="E179" s="2">
         <v>44895</v>
       </c>
-      <c r="F179" s="29" t="s">
+      <c r="F179" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="G179" s="30"/>
-      <c r="H179" s="28"/>
-      <c r="I179" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J179" s="28"/>
-      <c r="K179" s="31">
+      <c r="G179" s="29"/>
+      <c r="H179" s="27"/>
+      <c r="I179" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="27"/>
+      <c r="K179" s="30">
         <v>137</v>
       </c>
-      <c r="L179" s="28"/>
-      <c r="M179" s="32" t="s">
+      <c r="L179" s="27"/>
+      <c r="M179" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="N179" s="33"/>
+      <c r="N179" s="32"/>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="3" t="s">
@@ -7757,30 +7778,30 @@
       <c r="B180" s="4">
         <v>44812</v>
       </c>
-      <c r="C180" s="34">
+      <c r="C180" s="33">
         <v>44819</v>
       </c>
-      <c r="D180" s="28"/>
+      <c r="D180" s="27"/>
       <c r="E180" s="4">
         <v>44873</v>
       </c>
-      <c r="F180" s="35" t="s">
+      <c r="F180" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="G180" s="30"/>
-      <c r="H180" s="28"/>
-      <c r="I180" s="35" t="s">
+      <c r="G180" s="29"/>
+      <c r="H180" s="27"/>
+      <c r="I180" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J180" s="28"/>
-      <c r="K180" s="36">
+      <c r="J180" s="27"/>
+      <c r="K180" s="35">
         <v>73</v>
       </c>
-      <c r="L180" s="28"/>
-      <c r="M180" s="37" t="s">
+      <c r="L180" s="27"/>
+      <c r="M180" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="N180" s="33"/>
+      <c r="N180" s="32"/>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="1" t="s">
@@ -7789,30 +7810,30 @@
       <c r="B181" s="2">
         <v>44818</v>
       </c>
-      <c r="C181" s="27">
+      <c r="C181" s="26">
         <v>44819</v>
       </c>
-      <c r="D181" s="28"/>
+      <c r="D181" s="27"/>
       <c r="E181" s="2">
         <v>44880</v>
       </c>
-      <c r="F181" s="29" t="s">
+      <c r="F181" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="G181" s="30"/>
-      <c r="H181" s="28"/>
-      <c r="I181" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J181" s="28"/>
-      <c r="K181" s="31">
+      <c r="G181" s="29"/>
+      <c r="H181" s="27"/>
+      <c r="I181" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="27"/>
+      <c r="K181" s="30">
         <v>108</v>
       </c>
-      <c r="L181" s="28"/>
-      <c r="M181" s="32" t="s">
+      <c r="L181" s="27"/>
+      <c r="M181" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="N181" s="33"/>
+      <c r="N181" s="32"/>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="3" t="s">
@@ -7821,30 +7842,30 @@
       <c r="B182" s="4">
         <v>44812</v>
       </c>
-      <c r="C182" s="34">
+      <c r="C182" s="33">
         <v>44820</v>
       </c>
-      <c r="D182" s="28"/>
+      <c r="D182" s="27"/>
       <c r="E182" s="4">
         <v>44873</v>
       </c>
-      <c r="F182" s="35" t="s">
+      <c r="F182" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="G182" s="30"/>
-      <c r="H182" s="28"/>
-      <c r="I182" s="35" t="s">
+      <c r="G182" s="29"/>
+      <c r="H182" s="27"/>
+      <c r="I182" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J182" s="28"/>
-      <c r="K182" s="36">
+      <c r="J182" s="27"/>
+      <c r="K182" s="35">
         <v>49</v>
       </c>
-      <c r="L182" s="28"/>
-      <c r="M182" s="37" t="s">
+      <c r="L182" s="27"/>
+      <c r="M182" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="N182" s="33"/>
+      <c r="N182" s="32"/>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="1" t="s">
@@ -7853,30 +7874,30 @@
       <c r="B183" s="2">
         <v>44812</v>
       </c>
-      <c r="C183" s="27">
+      <c r="C183" s="26">
         <v>44820</v>
       </c>
-      <c r="D183" s="28"/>
+      <c r="D183" s="27"/>
       <c r="E183" s="2">
         <v>44873</v>
       </c>
-      <c r="F183" s="29" t="s">
+      <c r="F183" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="G183" s="30"/>
-      <c r="H183" s="28"/>
-      <c r="I183" s="29" t="s">
+      <c r="G183" s="29"/>
+      <c r="H183" s="27"/>
+      <c r="I183" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J183" s="28"/>
-      <c r="K183" s="31">
+      <c r="J183" s="27"/>
+      <c r="K183" s="30">
         <v>49</v>
       </c>
-      <c r="L183" s="28"/>
-      <c r="M183" s="32" t="s">
+      <c r="L183" s="27"/>
+      <c r="M183" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="N183" s="33"/>
+      <c r="N183" s="32"/>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="3" t="s">
@@ -7885,30 +7906,30 @@
       <c r="B184" s="4">
         <v>44812</v>
       </c>
-      <c r="C184" s="34">
+      <c r="C184" s="33">
         <v>44820</v>
       </c>
-      <c r="D184" s="28"/>
+      <c r="D184" s="27"/>
       <c r="E184" s="4">
         <v>44873</v>
       </c>
-      <c r="F184" s="35" t="s">
+      <c r="F184" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="G184" s="30"/>
-      <c r="H184" s="28"/>
-      <c r="I184" s="35" t="s">
+      <c r="G184" s="29"/>
+      <c r="H184" s="27"/>
+      <c r="I184" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J184" s="28"/>
-      <c r="K184" s="36">
+      <c r="J184" s="27"/>
+      <c r="K184" s="35">
         <v>41</v>
       </c>
-      <c r="L184" s="28"/>
-      <c r="M184" s="37" t="s">
+      <c r="L184" s="27"/>
+      <c r="M184" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="N184" s="33"/>
+      <c r="N184" s="32"/>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="1" t="s">
@@ -7917,30 +7938,30 @@
       <c r="B185" s="2">
         <v>44820</v>
       </c>
-      <c r="C185" s="27">
+      <c r="C185" s="26">
         <v>44820</v>
       </c>
-      <c r="D185" s="28"/>
+      <c r="D185" s="27"/>
       <c r="E185" s="2">
         <v>44880</v>
       </c>
-      <c r="F185" s="29" t="s">
+      <c r="F185" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="G185" s="30"/>
-      <c r="H185" s="28"/>
-      <c r="I185" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J185" s="28"/>
-      <c r="K185" s="31">
+      <c r="G185" s="29"/>
+      <c r="H185" s="27"/>
+      <c r="I185" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="27"/>
+      <c r="K185" s="30">
         <v>66</v>
       </c>
-      <c r="L185" s="28"/>
-      <c r="M185" s="32" t="s">
+      <c r="L185" s="27"/>
+      <c r="M185" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="N185" s="33"/>
+      <c r="N185" s="32"/>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="3" t="s">
@@ -7949,30 +7970,30 @@
       <c r="B186" s="4">
         <v>44823</v>
       </c>
-      <c r="C186" s="34">
+      <c r="C186" s="33">
         <v>44823</v>
       </c>
-      <c r="D186" s="28"/>
+      <c r="D186" s="27"/>
       <c r="E186" s="4">
         <v>44883</v>
       </c>
-      <c r="F186" s="35" t="s">
+      <c r="F186" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="G186" s="30"/>
-      <c r="H186" s="28"/>
-      <c r="I186" s="35" t="s">
+      <c r="G186" s="29"/>
+      <c r="H186" s="27"/>
+      <c r="I186" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J186" s="28"/>
-      <c r="K186" s="36">
+      <c r="J186" s="27"/>
+      <c r="K186" s="35">
         <v>57</v>
       </c>
-      <c r="L186" s="28"/>
-      <c r="M186" s="37" t="s">
+      <c r="L186" s="27"/>
+      <c r="M186" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="N186" s="33"/>
+      <c r="N186" s="32"/>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="1" t="s">
@@ -7981,30 +8002,30 @@
       <c r="B187" s="2">
         <v>44823</v>
       </c>
-      <c r="C187" s="27">
+      <c r="C187" s="26">
         <v>44824</v>
       </c>
-      <c r="D187" s="28"/>
+      <c r="D187" s="27"/>
       <c r="E187" s="2">
         <v>44882</v>
       </c>
-      <c r="F187" s="29" t="s">
+      <c r="F187" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="G187" s="30"/>
-      <c r="H187" s="28"/>
-      <c r="I187" s="29" t="s">
+      <c r="G187" s="29"/>
+      <c r="H187" s="27"/>
+      <c r="I187" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J187" s="28"/>
-      <c r="K187" s="31">
+      <c r="J187" s="27"/>
+      <c r="K187" s="30">
         <v>88</v>
       </c>
-      <c r="L187" s="28"/>
-      <c r="M187" s="32" t="s">
+      <c r="L187" s="27"/>
+      <c r="M187" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="N187" s="33"/>
+      <c r="N187" s="32"/>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="3" t="s">
@@ -8013,30 +8034,30 @@
       <c r="B188" s="4">
         <v>44824</v>
       </c>
-      <c r="C188" s="34">
+      <c r="C188" s="33">
         <v>44824</v>
       </c>
-      <c r="D188" s="28"/>
+      <c r="D188" s="27"/>
       <c r="E188" s="4">
         <v>44886</v>
       </c>
-      <c r="F188" s="35" t="s">
+      <c r="F188" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="G188" s="30"/>
-      <c r="H188" s="28"/>
-      <c r="I188" s="35" t="s">
+      <c r="G188" s="29"/>
+      <c r="H188" s="27"/>
+      <c r="I188" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J188" s="28"/>
-      <c r="K188" s="36">
+      <c r="J188" s="27"/>
+      <c r="K188" s="35">
         <v>79</v>
       </c>
-      <c r="L188" s="28"/>
-      <c r="M188" s="37" t="s">
+      <c r="L188" s="27"/>
+      <c r="M188" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="N188" s="33"/>
+      <c r="N188" s="32"/>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="1" t="s">
@@ -8045,30 +8066,30 @@
       <c r="B189" s="2">
         <v>44823</v>
       </c>
-      <c r="C189" s="27">
+      <c r="C189" s="26">
         <v>44825</v>
       </c>
-      <c r="D189" s="28"/>
+      <c r="D189" s="27"/>
       <c r="E189" s="2">
         <v>44883</v>
       </c>
-      <c r="F189" s="29" t="s">
+      <c r="F189" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="G189" s="30"/>
-      <c r="H189" s="28"/>
-      <c r="I189" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J189" s="28"/>
-      <c r="K189" s="31">
+      <c r="G189" s="29"/>
+      <c r="H189" s="27"/>
+      <c r="I189" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="27"/>
+      <c r="K189" s="30">
         <v>49</v>
       </c>
-      <c r="L189" s="28"/>
-      <c r="M189" s="32" t="s">
+      <c r="L189" s="27"/>
+      <c r="M189" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="N189" s="33"/>
+      <c r="N189" s="32"/>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="3" t="s">
@@ -8077,30 +8098,30 @@
       <c r="B190" s="4">
         <v>44824</v>
       </c>
-      <c r="C190" s="34">
+      <c r="C190" s="33">
         <v>44825</v>
       </c>
-      <c r="D190" s="28"/>
+      <c r="D190" s="27"/>
       <c r="E190" s="4">
         <v>44872</v>
       </c>
-      <c r="F190" s="35" t="s">
+      <c r="F190" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="G190" s="30"/>
-      <c r="H190" s="28"/>
-      <c r="I190" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J190" s="28"/>
-      <c r="K190" s="36">
+      <c r="G190" s="29"/>
+      <c r="H190" s="27"/>
+      <c r="I190" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="27"/>
+      <c r="K190" s="35">
         <v>104</v>
       </c>
-      <c r="L190" s="28"/>
-      <c r="M190" s="37" t="s">
+      <c r="L190" s="27"/>
+      <c r="M190" s="36" t="s">
         <v>318</v>
       </c>
-      <c r="N190" s="33"/>
+      <c r="N190" s="32"/>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="1" t="s">
@@ -8109,30 +8130,30 @@
       <c r="B191" s="2">
         <v>44824</v>
       </c>
-      <c r="C191" s="27">
+      <c r="C191" s="26">
         <v>44825</v>
       </c>
-      <c r="D191" s="28"/>
+      <c r="D191" s="27"/>
       <c r="E191" s="2">
         <v>44872</v>
       </c>
-      <c r="F191" s="29" t="s">
+      <c r="F191" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="G191" s="30"/>
-      <c r="H191" s="28"/>
-      <c r="I191" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J191" s="28"/>
-      <c r="K191" s="31">
+      <c r="G191" s="29"/>
+      <c r="H191" s="27"/>
+      <c r="I191" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="27"/>
+      <c r="K191" s="30">
         <v>7</v>
       </c>
-      <c r="L191" s="28"/>
-      <c r="M191" s="32" t="s">
+      <c r="L191" s="27"/>
+      <c r="M191" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="N191" s="33"/>
+      <c r="N191" s="32"/>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="3" t="s">
@@ -8141,30 +8162,30 @@
       <c r="B192" s="4">
         <v>44826</v>
       </c>
-      <c r="C192" s="34">
+      <c r="C192" s="33">
         <v>44826</v>
       </c>
-      <c r="D192" s="28"/>
+      <c r="D192" s="27"/>
       <c r="E192" s="4">
         <v>44888</v>
       </c>
-      <c r="F192" s="35" t="s">
+      <c r="F192" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="G192" s="30"/>
-      <c r="H192" s="28"/>
-      <c r="I192" s="35" t="s">
+      <c r="G192" s="29"/>
+      <c r="H192" s="27"/>
+      <c r="I192" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J192" s="28"/>
-      <c r="K192" s="36">
+      <c r="J192" s="27"/>
+      <c r="K192" s="35">
         <v>15</v>
       </c>
-      <c r="L192" s="28"/>
-      <c r="M192" s="37" t="s">
+      <c r="L192" s="27"/>
+      <c r="M192" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="N192" s="33"/>
+      <c r="N192" s="32"/>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="1" t="s">
@@ -8173,30 +8194,30 @@
       <c r="B193" s="2">
         <v>44825</v>
       </c>
-      <c r="C193" s="27">
+      <c r="C193" s="26">
         <v>44826</v>
       </c>
-      <c r="D193" s="28"/>
+      <c r="D193" s="27"/>
       <c r="E193" s="2">
         <v>44867</v>
       </c>
-      <c r="F193" s="29" t="s">
+      <c r="F193" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="G193" s="30"/>
-      <c r="H193" s="28"/>
-      <c r="I193" s="29" t="s">
+      <c r="G193" s="29"/>
+      <c r="H193" s="27"/>
+      <c r="I193" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J193" s="28"/>
-      <c r="K193" s="31">
-        <v>18</v>
-      </c>
-      <c r="L193" s="28"/>
-      <c r="M193" s="32" t="s">
+      <c r="J193" s="27"/>
+      <c r="K193" s="30">
+        <v>18</v>
+      </c>
+      <c r="L193" s="27"/>
+      <c r="M193" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="N193" s="33"/>
+      <c r="N193" s="32"/>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="3" t="s">
@@ -8205,30 +8226,30 @@
       <c r="B194" s="4">
         <v>44825</v>
       </c>
-      <c r="C194" s="34">
+      <c r="C194" s="33">
         <v>44826</v>
       </c>
-      <c r="D194" s="28"/>
+      <c r="D194" s="27"/>
       <c r="E194" s="4">
         <v>44867</v>
       </c>
-      <c r="F194" s="35" t="s">
+      <c r="F194" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="G194" s="30"/>
-      <c r="H194" s="28"/>
-      <c r="I194" s="35" t="s">
+      <c r="G194" s="29"/>
+      <c r="H194" s="27"/>
+      <c r="I194" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J194" s="28"/>
-      <c r="K194" s="36">
+      <c r="J194" s="27"/>
+      <c r="K194" s="35">
         <v>69</v>
       </c>
-      <c r="L194" s="28"/>
-      <c r="M194" s="37" t="s">
+      <c r="L194" s="27"/>
+      <c r="M194" s="36" t="s">
         <v>324</v>
       </c>
-      <c r="N194" s="33"/>
+      <c r="N194" s="32"/>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="1" t="s">
@@ -8237,30 +8258,30 @@
       <c r="B195" s="2">
         <v>44825</v>
       </c>
-      <c r="C195" s="27">
+      <c r="C195" s="26">
         <v>44826</v>
       </c>
-      <c r="D195" s="28"/>
+      <c r="D195" s="27"/>
       <c r="E195" s="2">
         <v>44867</v>
       </c>
-      <c r="F195" s="29" t="s">
+      <c r="F195" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="G195" s="30"/>
-      <c r="H195" s="28"/>
-      <c r="I195" s="29" t="s">
+      <c r="G195" s="29"/>
+      <c r="H195" s="27"/>
+      <c r="I195" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J195" s="28"/>
-      <c r="K195" s="31">
+      <c r="J195" s="27"/>
+      <c r="K195" s="30">
         <v>11</v>
       </c>
-      <c r="L195" s="28"/>
-      <c r="M195" s="32" t="s">
+      <c r="L195" s="27"/>
+      <c r="M195" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="N195" s="33"/>
+      <c r="N195" s="32"/>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="3" t="s">
@@ -8269,30 +8290,30 @@
       <c r="B196" s="4">
         <v>44825</v>
       </c>
-      <c r="C196" s="34">
+      <c r="C196" s="33">
         <v>44826</v>
       </c>
-      <c r="D196" s="28"/>
+      <c r="D196" s="27"/>
       <c r="E196" s="4">
         <v>44867</v>
       </c>
-      <c r="F196" s="35" t="s">
+      <c r="F196" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="G196" s="30"/>
-      <c r="H196" s="28"/>
-      <c r="I196" s="35" t="s">
+      <c r="G196" s="29"/>
+      <c r="H196" s="27"/>
+      <c r="I196" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J196" s="28"/>
-      <c r="K196" s="36">
+      <c r="J196" s="27"/>
+      <c r="K196" s="35">
         <v>2</v>
       </c>
-      <c r="L196" s="28"/>
-      <c r="M196" s="37" t="s">
+      <c r="L196" s="27"/>
+      <c r="M196" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="N196" s="33"/>
+      <c r="N196" s="32"/>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="1" t="s">
@@ -8301,30 +8322,30 @@
       <c r="B197" s="2">
         <v>44827</v>
       </c>
-      <c r="C197" s="27">
+      <c r="C197" s="26">
         <v>44827</v>
       </c>
-      <c r="D197" s="28"/>
+      <c r="D197" s="27"/>
       <c r="E197" s="2">
         <v>44888</v>
       </c>
-      <c r="F197" s="29" t="s">
+      <c r="F197" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="G197" s="30"/>
-      <c r="H197" s="28"/>
-      <c r="I197" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J197" s="28"/>
-      <c r="K197" s="31">
+      <c r="G197" s="29"/>
+      <c r="H197" s="27"/>
+      <c r="I197" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="27"/>
+      <c r="K197" s="30">
         <v>72</v>
       </c>
-      <c r="L197" s="28"/>
-      <c r="M197" s="32" t="s">
+      <c r="L197" s="27"/>
+      <c r="M197" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="N197" s="33"/>
+      <c r="N197" s="32"/>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="3" t="s">
@@ -8333,30 +8354,30 @@
       <c r="B198" s="4">
         <v>44830</v>
       </c>
-      <c r="C198" s="34">
+      <c r="C198" s="33">
         <v>44830</v>
       </c>
-      <c r="D198" s="28"/>
+      <c r="D198" s="27"/>
       <c r="E198" s="4">
         <v>44891</v>
       </c>
-      <c r="F198" s="35" t="s">
+      <c r="F198" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="G198" s="30"/>
-      <c r="H198" s="28"/>
-      <c r="I198" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J198" s="28"/>
-      <c r="K198" s="36">
+      <c r="G198" s="29"/>
+      <c r="H198" s="27"/>
+      <c r="I198" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="27"/>
+      <c r="K198" s="35">
         <v>51</v>
       </c>
-      <c r="L198" s="28"/>
-      <c r="M198" s="37" t="s">
+      <c r="L198" s="27"/>
+      <c r="M198" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="N198" s="33"/>
+      <c r="N198" s="32"/>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="1" t="s">
@@ -8365,30 +8386,30 @@
       <c r="B199" s="2">
         <v>44830</v>
       </c>
-      <c r="C199" s="27">
+      <c r="C199" s="26">
         <v>44830</v>
       </c>
-      <c r="D199" s="28"/>
+      <c r="D199" s="27"/>
       <c r="E199" s="2">
         <v>44892</v>
       </c>
-      <c r="F199" s="29" t="s">
+      <c r="F199" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="G199" s="30"/>
-      <c r="H199" s="28"/>
-      <c r="I199" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J199" s="28"/>
-      <c r="K199" s="31">
+      <c r="G199" s="29"/>
+      <c r="H199" s="27"/>
+      <c r="I199" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="27"/>
+      <c r="K199" s="30">
         <v>353</v>
       </c>
-      <c r="L199" s="28"/>
-      <c r="M199" s="32" t="s">
+      <c r="L199" s="27"/>
+      <c r="M199" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="N199" s="33"/>
+      <c r="N199" s="32"/>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="3" t="s">
@@ -8397,30 +8418,30 @@
       <c r="B200" s="4">
         <v>44830</v>
       </c>
-      <c r="C200" s="34">
+      <c r="C200" s="33">
         <v>44830</v>
       </c>
-      <c r="D200" s="28"/>
+      <c r="D200" s="27"/>
       <c r="E200" s="4">
         <v>44891</v>
       </c>
-      <c r="F200" s="35" t="s">
+      <c r="F200" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="G200" s="30"/>
-      <c r="H200" s="28"/>
-      <c r="I200" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J200" s="28"/>
-      <c r="K200" s="36">
+      <c r="G200" s="29"/>
+      <c r="H200" s="27"/>
+      <c r="I200" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="27"/>
+      <c r="K200" s="35">
         <v>46</v>
       </c>
-      <c r="L200" s="28"/>
-      <c r="M200" s="37" t="s">
+      <c r="L200" s="27"/>
+      <c r="M200" s="36" t="s">
         <v>335</v>
       </c>
-      <c r="N200" s="33"/>
+      <c r="N200" s="32"/>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="1" t="s">
@@ -8429,30 +8450,30 @@
       <c r="B201" s="2">
         <v>44825</v>
       </c>
-      <c r="C201" s="27">
+      <c r="C201" s="26">
         <v>44831</v>
       </c>
-      <c r="D201" s="28"/>
+      <c r="D201" s="27"/>
       <c r="E201" s="2">
         <v>44888</v>
       </c>
-      <c r="F201" s="29" t="s">
+      <c r="F201" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="G201" s="30"/>
-      <c r="H201" s="28"/>
-      <c r="I201" s="29" t="s">
+      <c r="G201" s="29"/>
+      <c r="H201" s="27"/>
+      <c r="I201" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J201" s="28"/>
-      <c r="K201" s="31">
+      <c r="J201" s="27"/>
+      <c r="K201" s="30">
         <v>905</v>
       </c>
-      <c r="L201" s="28"/>
-      <c r="M201" s="32" t="s">
+      <c r="L201" s="27"/>
+      <c r="M201" s="31" t="s">
         <v>337</v>
       </c>
-      <c r="N201" s="33"/>
+      <c r="N201" s="32"/>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="3" t="s">
@@ -8461,30 +8482,30 @@
       <c r="B202" s="4">
         <v>44830</v>
       </c>
-      <c r="C202" s="34">
+      <c r="C202" s="33">
         <v>44831</v>
       </c>
-      <c r="D202" s="28"/>
+      <c r="D202" s="27"/>
       <c r="E202" s="4">
         <v>44890</v>
       </c>
-      <c r="F202" s="35" t="s">
+      <c r="F202" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="G202" s="30"/>
-      <c r="H202" s="28"/>
-      <c r="I202" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J202" s="28"/>
-      <c r="K202" s="36">
+      <c r="G202" s="29"/>
+      <c r="H202" s="27"/>
+      <c r="I202" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="27"/>
+      <c r="K202" s="35">
         <v>63</v>
       </c>
-      <c r="L202" s="28"/>
-      <c r="M202" s="37" t="s">
+      <c r="L202" s="27"/>
+      <c r="M202" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="N202" s="33"/>
+      <c r="N202" s="32"/>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="1" t="s">
@@ -8493,30 +8514,30 @@
       <c r="B203" s="2">
         <v>44824</v>
       </c>
-      <c r="C203" s="27">
+      <c r="C203" s="26">
         <v>44831</v>
       </c>
-      <c r="D203" s="28"/>
+      <c r="D203" s="27"/>
       <c r="E203" s="2">
         <v>44887</v>
       </c>
-      <c r="F203" s="29" t="s">
+      <c r="F203" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="G203" s="30"/>
-      <c r="H203" s="28"/>
-      <c r="I203" s="29" t="s">
+      <c r="G203" s="29"/>
+      <c r="H203" s="27"/>
+      <c r="I203" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J203" s="28"/>
-      <c r="K203" s="31">
+      <c r="J203" s="27"/>
+      <c r="K203" s="30">
         <v>308</v>
       </c>
-      <c r="L203" s="28"/>
-      <c r="M203" s="32" t="s">
+      <c r="L203" s="27"/>
+      <c r="M203" s="31" t="s">
         <v>340</v>
       </c>
-      <c r="N203" s="33"/>
+      <c r="N203" s="32"/>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="3" t="s">
@@ -8525,30 +8546,30 @@
       <c r="B204" s="4">
         <v>44818</v>
       </c>
-      <c r="C204" s="34">
+      <c r="C204" s="33">
         <v>44832</v>
       </c>
-      <c r="D204" s="28"/>
+      <c r="D204" s="27"/>
       <c r="E204" s="4">
         <v>44879</v>
       </c>
-      <c r="F204" s="35" t="s">
+      <c r="F204" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="G204" s="30"/>
-      <c r="H204" s="28"/>
-      <c r="I204" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J204" s="28"/>
-      <c r="K204" s="36">
+      <c r="G204" s="29"/>
+      <c r="H204" s="27"/>
+      <c r="I204" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="27"/>
+      <c r="K204" s="35">
         <v>10</v>
       </c>
-      <c r="L204" s="28"/>
-      <c r="M204" s="37" t="s">
+      <c r="L204" s="27"/>
+      <c r="M204" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="N204" s="33"/>
+      <c r="N204" s="32"/>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="1" t="s">
@@ -8557,30 +8578,30 @@
       <c r="B205" s="2">
         <v>44832</v>
       </c>
-      <c r="C205" s="27">
+      <c r="C205" s="26">
         <v>44832</v>
       </c>
-      <c r="D205" s="28"/>
+      <c r="D205" s="27"/>
       <c r="E205" s="2">
         <v>44893</v>
       </c>
-      <c r="F205" s="29" t="s">
+      <c r="F205" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G205" s="30"/>
-      <c r="H205" s="28"/>
-      <c r="I205" s="29" t="s">
+      <c r="G205" s="29"/>
+      <c r="H205" s="27"/>
+      <c r="I205" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J205" s="28"/>
-      <c r="K205" s="31">
+      <c r="J205" s="27"/>
+      <c r="K205" s="30">
         <v>93</v>
       </c>
-      <c r="L205" s="28"/>
-      <c r="M205" s="32" t="s">
+      <c r="L205" s="27"/>
+      <c r="M205" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="N205" s="33"/>
+      <c r="N205" s="32"/>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="3" t="s">
@@ -8589,30 +8610,30 @@
       <c r="B206" s="4">
         <v>44820</v>
       </c>
-      <c r="C206" s="34">
+      <c r="C206" s="33">
         <v>44832</v>
       </c>
-      <c r="D206" s="28"/>
+      <c r="D206" s="27"/>
       <c r="E206" s="4">
         <v>44849</v>
       </c>
-      <c r="F206" s="35" t="s">
+      <c r="F206" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="G206" s="30"/>
-      <c r="H206" s="28"/>
-      <c r="I206" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J206" s="28"/>
-      <c r="K206" s="36">
+      <c r="G206" s="29"/>
+      <c r="H206" s="27"/>
+      <c r="I206" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="27"/>
+      <c r="K206" s="35">
         <v>70</v>
       </c>
-      <c r="L206" s="28"/>
-      <c r="M206" s="37" t="s">
+      <c r="L206" s="27"/>
+      <c r="M206" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="N206" s="33"/>
+      <c r="N206" s="32"/>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="1" t="s">
@@ -8621,30 +8642,30 @@
       <c r="B207" s="2">
         <v>44833</v>
       </c>
-      <c r="C207" s="27">
+      <c r="C207" s="26">
         <v>44833</v>
       </c>
-      <c r="D207" s="28"/>
+      <c r="D207" s="27"/>
       <c r="E207" s="2">
         <v>44897</v>
       </c>
-      <c r="F207" s="29" t="s">
+      <c r="F207" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="G207" s="30"/>
-      <c r="H207" s="28"/>
-      <c r="I207" s="29" t="s">
+      <c r="G207" s="29"/>
+      <c r="H207" s="27"/>
+      <c r="I207" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J207" s="28"/>
-      <c r="K207" s="31">
+      <c r="J207" s="27"/>
+      <c r="K207" s="30">
         <v>21</v>
       </c>
-      <c r="L207" s="28"/>
-      <c r="M207" s="32" t="s">
+      <c r="L207" s="27"/>
+      <c r="M207" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="N207" s="33"/>
+      <c r="N207" s="32"/>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="3" t="s">
@@ -8653,30 +8674,30 @@
       <c r="B208" s="4">
         <v>44834</v>
       </c>
-      <c r="C208" s="34">
+      <c r="C208" s="33">
         <v>44834</v>
       </c>
-      <c r="D208" s="28"/>
+      <c r="D208" s="27"/>
       <c r="E208" s="4">
         <v>44896</v>
       </c>
-      <c r="F208" s="35" t="s">
+      <c r="F208" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="G208" s="30"/>
-      <c r="H208" s="28"/>
-      <c r="I208" s="35" t="s">
+      <c r="G208" s="29"/>
+      <c r="H208" s="27"/>
+      <c r="I208" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J208" s="28"/>
-      <c r="K208" s="36">
+      <c r="J208" s="27"/>
+      <c r="K208" s="35">
         <v>28</v>
       </c>
-      <c r="L208" s="28"/>
-      <c r="M208" s="37" t="s">
+      <c r="L208" s="27"/>
+      <c r="M208" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="N208" s="33"/>
+      <c r="N208" s="32"/>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="1" t="s">
@@ -8685,30 +8706,30 @@
       <c r="B209" s="2">
         <v>44777</v>
       </c>
-      <c r="C209" s="27">
+      <c r="C209" s="26">
         <v>44834</v>
       </c>
-      <c r="D209" s="28"/>
+      <c r="D209" s="27"/>
       <c r="E209" s="2">
         <v>44837</v>
       </c>
-      <c r="F209" s="29" t="s">
+      <c r="F209" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="G209" s="30"/>
-      <c r="H209" s="28"/>
-      <c r="I209" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J209" s="28"/>
-      <c r="K209" s="31">
+      <c r="G209" s="29"/>
+      <c r="H209" s="27"/>
+      <c r="I209" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J209" s="27"/>
+      <c r="K209" s="30">
         <v>201</v>
       </c>
-      <c r="L209" s="28"/>
-      <c r="M209" s="32" t="s">
+      <c r="L209" s="27"/>
+      <c r="M209" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="N209" s="33"/>
+      <c r="N209" s="32"/>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="3" t="s">
@@ -8717,30 +8738,30 @@
       <c r="B210" s="4">
         <v>44833</v>
       </c>
-      <c r="C210" s="34">
+      <c r="C210" s="33">
         <v>44837</v>
       </c>
-      <c r="D210" s="28"/>
+      <c r="D210" s="27"/>
       <c r="E210" s="4">
         <v>44894</v>
       </c>
-      <c r="F210" s="35" t="s">
+      <c r="F210" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="G210" s="30"/>
-      <c r="H210" s="28"/>
-      <c r="I210" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J210" s="28"/>
-      <c r="K210" s="36">
+      <c r="G210" s="29"/>
+      <c r="H210" s="27"/>
+      <c r="I210" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J210" s="27"/>
+      <c r="K210" s="35">
         <v>49</v>
       </c>
-      <c r="L210" s="28"/>
-      <c r="M210" s="37" t="s">
+      <c r="L210" s="27"/>
+      <c r="M210" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="N210" s="33"/>
+      <c r="N210" s="32"/>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="1" t="s">
@@ -8749,30 +8770,30 @@
       <c r="B211" s="2">
         <v>44834</v>
       </c>
-      <c r="C211" s="27">
+      <c r="C211" s="26">
         <v>44837</v>
       </c>
-      <c r="D211" s="28"/>
+      <c r="D211" s="27"/>
       <c r="E211" s="2">
         <v>44906</v>
       </c>
-      <c r="F211" s="29" t="s">
+      <c r="F211" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="G211" s="30"/>
-      <c r="H211" s="28"/>
-      <c r="I211" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J211" s="28"/>
-      <c r="K211" s="31">
+      <c r="G211" s="29"/>
+      <c r="H211" s="27"/>
+      <c r="I211" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J211" s="27"/>
+      <c r="K211" s="30">
         <v>7</v>
       </c>
-      <c r="L211" s="28"/>
-      <c r="M211" s="32" t="s">
+      <c r="L211" s="27"/>
+      <c r="M211" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="N211" s="33"/>
+      <c r="N211" s="32"/>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="3" t="s">
@@ -8781,30 +8802,30 @@
       <c r="B212" s="4">
         <v>44837</v>
       </c>
-      <c r="C212" s="34">
+      <c r="C212" s="33">
         <v>44838</v>
       </c>
-      <c r="D212" s="28"/>
+      <c r="D212" s="27"/>
       <c r="E212" s="4">
         <v>44897</v>
       </c>
-      <c r="F212" s="35" t="s">
+      <c r="F212" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="G212" s="30"/>
-      <c r="H212" s="28"/>
-      <c r="I212" s="35" t="s">
+      <c r="G212" s="29"/>
+      <c r="H212" s="27"/>
+      <c r="I212" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J212" s="28"/>
-      <c r="K212" s="36">
+      <c r="J212" s="27"/>
+      <c r="K212" s="35">
         <v>44</v>
       </c>
-      <c r="L212" s="28"/>
-      <c r="M212" s="37" t="s">
+      <c r="L212" s="27"/>
+      <c r="M212" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="N212" s="33"/>
+      <c r="N212" s="32"/>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="1" t="s">
@@ -8813,30 +8834,30 @@
       <c r="B213" s="2">
         <v>44841</v>
       </c>
-      <c r="C213" s="27">
+      <c r="C213" s="26">
         <v>44844</v>
       </c>
-      <c r="D213" s="28"/>
+      <c r="D213" s="27"/>
       <c r="E213" s="2">
         <v>44901</v>
       </c>
-      <c r="F213" s="29" t="s">
+      <c r="F213" s="28" t="s">
         <v>360</v>
       </c>
-      <c r="G213" s="30"/>
-      <c r="H213" s="28"/>
-      <c r="I213" s="29" t="s">
+      <c r="G213" s="29"/>
+      <c r="H213" s="27"/>
+      <c r="I213" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J213" s="28"/>
-      <c r="K213" s="31">
+      <c r="J213" s="27"/>
+      <c r="K213" s="30">
         <v>6</v>
       </c>
-      <c r="L213" s="28"/>
-      <c r="M213" s="32" t="s">
+      <c r="L213" s="27"/>
+      <c r="M213" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="N213" s="33"/>
+      <c r="N213" s="32"/>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="3" t="s">
@@ -8845,30 +8866,30 @@
       <c r="B214" s="4">
         <v>44840</v>
       </c>
-      <c r="C214" s="34">
+      <c r="C214" s="33">
         <v>44844</v>
       </c>
-      <c r="D214" s="28"/>
+      <c r="D214" s="27"/>
       <c r="E214" s="4">
         <v>44901</v>
       </c>
-      <c r="F214" s="35" t="s">
+      <c r="F214" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="G214" s="30"/>
-      <c r="H214" s="28"/>
-      <c r="I214" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J214" s="28"/>
-      <c r="K214" s="36">
+      <c r="G214" s="29"/>
+      <c r="H214" s="27"/>
+      <c r="I214" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="27"/>
+      <c r="K214" s="35">
         <v>62</v>
       </c>
-      <c r="L214" s="28"/>
-      <c r="M214" s="37" t="s">
+      <c r="L214" s="27"/>
+      <c r="M214" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="N214" s="33"/>
+      <c r="N214" s="32"/>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="1" t="s">
@@ -8877,97 +8898,225 @@
       <c r="B215" s="2">
         <v>44840</v>
       </c>
-      <c r="C215" s="27">
+      <c r="C215" s="26">
         <v>44844</v>
       </c>
-      <c r="D215" s="28"/>
+      <c r="D215" s="27"/>
       <c r="E215" s="2">
         <v>44901</v>
       </c>
-      <c r="F215" s="29" t="s">
+      <c r="F215" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="G215" s="30"/>
-      <c r="H215" s="28"/>
-      <c r="I215" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J215" s="28"/>
-      <c r="K215" s="31">
+      <c r="G215" s="29"/>
+      <c r="H215" s="27"/>
+      <c r="I215" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J215" s="27"/>
+      <c r="K215" s="30">
         <v>32</v>
       </c>
-      <c r="L215" s="28"/>
-      <c r="M215" s="32" t="s">
+      <c r="L215" s="27"/>
+      <c r="M215" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="N215" s="33"/>
-    </row>
-    <row r="216" spans="1:14" ht="30" customHeight="1">
-      <c r="A216" s="25" t="s">
+      <c r="N215" s="32"/>
+    </row>
+    <row r="216" spans="1:14">
+      <c r="A216" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B216" s="4">
+        <v>44844</v>
+      </c>
+      <c r="C216" s="33">
+        <v>44845</v>
+      </c>
+      <c r="D216" s="27"/>
+      <c r="E216" s="4">
+        <v>44906</v>
+      </c>
+      <c r="F216" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G216" s="29"/>
+      <c r="H216" s="27"/>
+      <c r="I216" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="J216" s="27"/>
+      <c r="K216" s="35">
+        <v>611</v>
+      </c>
+      <c r="L216" s="27"/>
+      <c r="M216" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="N216" s="32"/>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="A217" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B217" s="2">
+        <v>44840</v>
+      </c>
+      <c r="C217" s="26">
+        <v>44845</v>
+      </c>
+      <c r="D217" s="27"/>
+      <c r="E217" s="2">
+        <v>44934</v>
+      </c>
+      <c r="F217" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="G217" s="29"/>
+      <c r="H217" s="27"/>
+      <c r="I217" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="J217" s="27"/>
+      <c r="K217" s="30">
+        <v>94</v>
+      </c>
+      <c r="L217" s="27"/>
+      <c r="M217" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="N217" s="32"/>
+    </row>
+    <row r="218" spans="1:14">
+      <c r="A218" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B218" s="4">
+        <v>44845</v>
+      </c>
+      <c r="C218" s="33">
+        <v>44846</v>
+      </c>
+      <c r="D218" s="27"/>
+      <c r="E218" s="4">
+        <v>44911</v>
+      </c>
+      <c r="F218" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="G218" s="29"/>
+      <c r="H218" s="27"/>
+      <c r="I218" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J218" s="27"/>
+      <c r="K218" s="35">
+        <v>108</v>
+      </c>
+      <c r="L218" s="27"/>
+      <c r="M218" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="N218" s="32"/>
+    </row>
+    <row r="219" spans="1:14">
+      <c r="A219" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B219" s="2">
+        <v>44845</v>
+      </c>
+      <c r="C219" s="26">
+        <v>44846</v>
+      </c>
+      <c r="D219" s="27"/>
+      <c r="E219" s="2">
+        <v>44907</v>
+      </c>
+      <c r="F219" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="G219" s="29"/>
+      <c r="H219" s="27"/>
+      <c r="I219" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J219" s="27"/>
+      <c r="K219" s="30">
+        <v>168</v>
+      </c>
+      <c r="L219" s="27"/>
+      <c r="M219" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="N219" s="32"/>
+    </row>
+    <row r="220" spans="1:14" ht="30.75" customHeight="1">
+      <c r="A220" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="B220" s="25"/>
+      <c r="C220" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="D220" s="22"/>
+      <c r="E220" s="23"/>
+      <c r="F220" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="G220" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B216" s="26"/>
-      <c r="C216" s="22" t="s">
-        <v>365</v>
-      </c>
-      <c r="D216" s="23"/>
-      <c r="E216" s="24"/>
-      <c r="F216" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="G216" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="H216" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="I216" s="24"/>
-      <c r="J216" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="K216" s="24"/>
-      <c r="L216" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="M216" s="24"/>
-      <c r="N216" s="12" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14" s="10" customFormat="1">
-      <c r="A217" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B217" s="21"/>
-      <c r="C217" s="17">
-        <v>15655</v>
-      </c>
-      <c r="D217" s="18"/>
-      <c r="E217" s="19"/>
-      <c r="F217" s="7">
-        <v>122</v>
-      </c>
-      <c r="G217" s="8">
+      <c r="H220" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="I220" s="23"/>
+      <c r="J220" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="K220" s="23"/>
+      <c r="L220" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="M220" s="23"/>
+      <c r="N220" s="11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" s="9" customFormat="1">
+      <c r="A221" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B221" s="20"/>
+      <c r="C221" s="16">
+        <v>16636</v>
+      </c>
+      <c r="D221" s="17"/>
+      <c r="E221" s="18"/>
+      <c r="F221" s="7">
+        <v>123</v>
+      </c>
+      <c r="G221" s="7">
         <v>7</v>
       </c>
-      <c r="H217" s="17">
+      <c r="H221" s="16">
         <v>1</v>
       </c>
-      <c r="I217" s="19"/>
-      <c r="J217" s="17">
-        <v>80</v>
-      </c>
-      <c r="K217" s="19"/>
-      <c r="L217" s="17">
-        <v>1</v>
-      </c>
-      <c r="M217" s="19"/>
-      <c r="N217" s="9">
+      <c r="I221" s="18"/>
+      <c r="J221" s="16">
+        <v>82</v>
+      </c>
+      <c r="K221" s="18"/>
+      <c r="L221" s="16">
+        <v>2</v>
+      </c>
+      <c r="M221" s="18"/>
+      <c r="N221" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1077">
+  <mergeCells count="1097">
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I5:J5"/>
@@ -8983,8 +9132,8 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:J9"/>
@@ -10025,16 +10174,16 @@
     <mergeCell ref="I210:J210"/>
     <mergeCell ref="K210:L210"/>
     <mergeCell ref="M210:N210"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="H217:I217"/>
-    <mergeCell ref="J217:K217"/>
-    <mergeCell ref="L217:M217"/>
-    <mergeCell ref="A217:B217"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="H216:I216"/>
-    <mergeCell ref="J216:K216"/>
-    <mergeCell ref="L216:M216"/>
-    <mergeCell ref="A216:B216"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="F217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="M217:N217"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="F216:H216"/>
+    <mergeCell ref="I216:J216"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="M216:N216"/>
     <mergeCell ref="C215:D215"/>
     <mergeCell ref="F215:H215"/>
     <mergeCell ref="I215:J215"/>
@@ -10045,6 +10194,26 @@
     <mergeCell ref="I214:J214"/>
     <mergeCell ref="K214:L214"/>
     <mergeCell ref="M214:N214"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="H221:I221"/>
+    <mergeCell ref="J221:K221"/>
+    <mergeCell ref="L221:M221"/>
+    <mergeCell ref="A221:B221"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="H220:I220"/>
+    <mergeCell ref="J220:K220"/>
+    <mergeCell ref="L220:M220"/>
+    <mergeCell ref="A220:B220"/>
+    <mergeCell ref="C219:D219"/>
+    <mergeCell ref="F219:H219"/>
+    <mergeCell ref="I219:J219"/>
+    <mergeCell ref="K219:L219"/>
+    <mergeCell ref="M219:N219"/>
+    <mergeCell ref="C218:D218"/>
+    <mergeCell ref="F218:H218"/>
+    <mergeCell ref="I218:J218"/>
+    <mergeCell ref="K218:L218"/>
+    <mergeCell ref="M218:N218"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13095" windowHeight="8295"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15780" windowHeight="8685"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="450">
   <si>
     <t/>
   </si>
@@ -1286,6 +1286,99 @@
     <t>3750 Torrey View Court  San Diego CA 92130</t>
   </si>
   <si>
+    <t>Roth Staffing Companies, L.P. dba Ultimate Staffing Services at FormFactor, Inc.</t>
+  </si>
+  <si>
+    <t>TAP Manufacturing LLC and TAP Worldwide LLC dba 4 Wheel Parts</t>
+  </si>
+  <si>
+    <t>400 West Artesia Blvd.  Compton CA 90220</t>
+  </si>
+  <si>
+    <t>3143 Townsgate Road  Westlake Village CA 91361</t>
+  </si>
+  <si>
+    <t>6101 Condor Drive  Moorpark CA 93021</t>
+  </si>
+  <si>
+    <t>Napa County</t>
+  </si>
+  <si>
+    <t>Terre du Soleil dba Auberge du Soleil</t>
+  </si>
+  <si>
+    <t>180 Rutherford Hill Road  Rutherford CA 94573</t>
+  </si>
+  <si>
+    <t>Demetrix, Inc.</t>
+  </si>
+  <si>
+    <t>7th 2929 Street  Berkeley CA 94710</t>
+  </si>
+  <si>
+    <t>Selman Breitman LLP</t>
+  </si>
+  <si>
+    <t>11766 Wilshire Boulevard  Los Angeles CA 90025</t>
+  </si>
+  <si>
+    <t>42375 Remington Ave  Temecula CA 92590</t>
+  </si>
+  <si>
+    <t>San Luis Obispo County</t>
+  </si>
+  <si>
+    <t>Mindbody, Inc.</t>
+  </si>
+  <si>
+    <t>651 Tank Farm Road  San Luis Obispo CA 93401</t>
+  </si>
+  <si>
+    <t>Cepheid</t>
+  </si>
+  <si>
+    <t>7000 Gateway Blvd  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>6601 Overlake Place  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>904 Caribbean Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>630-632 Caribbean Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>1339 Moffett Park Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>1325-1327 Chesapeake Terrace  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>1315 Chesapeake Terrace  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>914-918 Caribbean Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>1324 Chesapeake Terrace  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>2550 Great America Way  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>225 North Guild Avenue  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>121 North Guild Avenue  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>850 Thurman Street  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>1330 East Thurman Road  Lodi CA 95240</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1315,7 +1408,7 @@
   <si>
     <t xml:space="preserve"> Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 10/26/2022
+ End Date: 10/31/2022
 </t>
   </si>
   <si>
@@ -1695,19 +1788,6 @@
         <color rgb="FFA9A9A9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFA9A9A9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9A9A9"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -1722,6 +1802,19 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1781,10 +1874,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,7 +1889,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2151,26 +2244,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R244"/>
+  <dimension ref="A1:R268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="2.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" customWidth="1"/>
     <col min="11" max="11" width="5.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" customWidth="1"/>
-    <col min="13" max="13" width="7.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="47" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2185,14 +2278,14 @@
       <c r="L1" s="47"/>
       <c r="M1" s="47"/>
       <c r="N1" s="47"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" ht="37.5" customHeight="1">
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="38.25" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -2207,10 +2300,10 @@
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="7" t="s">
@@ -9892,72 +9985,840 @@
       </c>
       <c r="N242" s="32"/>
     </row>
-    <row r="243" spans="1:14" ht="30" customHeight="1">
-      <c r="A243" s="24" t="s">
+    <row r="243" spans="1:14">
+      <c r="A243" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" s="2">
+        <v>44859</v>
+      </c>
+      <c r="C243" s="33">
+        <v>44861</v>
+      </c>
+      <c r="D243" s="27"/>
+      <c r="E243" s="2">
+        <v>44859</v>
+      </c>
+      <c r="F243" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="G243" s="29"/>
+      <c r="H243" s="27"/>
+      <c r="I243" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J243" s="27"/>
+      <c r="K243" s="35">
+        <v>164</v>
+      </c>
+      <c r="L243" s="27"/>
+      <c r="M243" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="N243" s="32"/>
+    </row>
+    <row r="244" spans="1:14">
+      <c r="A244" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B244" s="4">
+        <v>44839</v>
+      </c>
+      <c r="C244" s="26">
+        <v>44861</v>
+      </c>
+      <c r="D244" s="27"/>
+      <c r="E244" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F244" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="G244" s="29"/>
+      <c r="H244" s="27"/>
+      <c r="I244" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J244" s="27"/>
+      <c r="K244" s="30">
+        <v>293</v>
+      </c>
+      <c r="L244" s="27"/>
+      <c r="M244" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="N244" s="32"/>
+    </row>
+    <row r="245" spans="1:14">
+      <c r="A245" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B245" s="2">
+        <v>44859</v>
+      </c>
+      <c r="C245" s="33">
+        <v>44861</v>
+      </c>
+      <c r="D245" s="27"/>
+      <c r="E245" s="2">
+        <v>44925</v>
+      </c>
+      <c r="F245" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G245" s="29"/>
+      <c r="H245" s="27"/>
+      <c r="I245" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J245" s="27"/>
+      <c r="K245" s="35">
+        <v>12</v>
+      </c>
+      <c r="L245" s="27"/>
+      <c r="M245" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="N245" s="32"/>
+    </row>
+    <row r="246" spans="1:14">
+      <c r="A246" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B246" s="4">
+        <v>44859</v>
+      </c>
+      <c r="C246" s="26">
+        <v>44861</v>
+      </c>
+      <c r="D246" s="27"/>
+      <c r="E246" s="4">
+        <v>44925</v>
+      </c>
+      <c r="F246" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G246" s="29"/>
+      <c r="H246" s="27"/>
+      <c r="I246" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J246" s="27"/>
+      <c r="K246" s="30">
+        <v>27</v>
+      </c>
+      <c r="L246" s="27"/>
+      <c r="M246" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="N246" s="32"/>
+    </row>
+    <row r="247" spans="1:14">
+      <c r="A247" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B247" s="2">
+        <v>44859</v>
+      </c>
+      <c r="C247" s="33">
+        <v>44861</v>
+      </c>
+      <c r="D247" s="27"/>
+      <c r="E247" s="2">
+        <v>44925</v>
+      </c>
+      <c r="F247" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G247" s="29"/>
+      <c r="H247" s="27"/>
+      <c r="I247" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J247" s="27"/>
+      <c r="K247" s="35">
+        <v>10</v>
+      </c>
+      <c r="L247" s="27"/>
+      <c r="M247" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="N247" s="32"/>
+    </row>
+    <row r="248" spans="1:14">
+      <c r="A248" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B248" s="4">
+        <v>44859</v>
+      </c>
+      <c r="C248" s="26">
+        <v>44861</v>
+      </c>
+      <c r="D248" s="27"/>
+      <c r="E248" s="4">
+        <v>44928</v>
+      </c>
+      <c r="F248" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="G248" s="29"/>
+      <c r="H248" s="27"/>
+      <c r="I248" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="J248" s="27"/>
+      <c r="K248" s="30">
+        <v>206</v>
+      </c>
+      <c r="L248" s="27"/>
+      <c r="M248" s="31" t="s">
+        <v>415</v>
+      </c>
+      <c r="N248" s="32"/>
+    </row>
+    <row r="249" spans="1:14">
+      <c r="A249" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B249" s="2">
+        <v>44834</v>
+      </c>
+      <c r="C249" s="33">
+        <v>44862</v>
+      </c>
+      <c r="D249" s="27"/>
+      <c r="E249" s="2">
+        <v>44895</v>
+      </c>
+      <c r="F249" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="G249" s="29"/>
+      <c r="H249" s="27"/>
+      <c r="I249" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J249" s="27"/>
+      <c r="K249" s="35">
+        <v>4</v>
+      </c>
+      <c r="L249" s="27"/>
+      <c r="M249" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="N249" s="32"/>
+    </row>
+    <row r="250" spans="1:14">
+      <c r="A250" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B250" s="4">
+        <v>44862</v>
+      </c>
+      <c r="C250" s="26">
+        <v>44862</v>
+      </c>
+      <c r="D250" s="27"/>
+      <c r="E250" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F250" s="28" t="s">
         <v>418</v>
       </c>
-      <c r="B243" s="25"/>
-      <c r="C243" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="D243" s="22"/>
-      <c r="E243" s="23"/>
-      <c r="F243" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="G243" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="H243" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="I243" s="23"/>
-      <c r="J243" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="K243" s="23"/>
-      <c r="L243" s="21" t="s">
-        <v>413</v>
-      </c>
-      <c r="M243" s="23"/>
-      <c r="N243" s="15" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="244" spans="1:14" s="13" customFormat="1">
-      <c r="A244" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="B244" s="20"/>
-      <c r="C244" s="16">
-        <v>19219</v>
-      </c>
-      <c r="D244" s="17"/>
-      <c r="E244" s="18"/>
-      <c r="F244" s="11">
-        <v>133</v>
-      </c>
-      <c r="G244" s="11">
+      <c r="G250" s="29"/>
+      <c r="H250" s="27"/>
+      <c r="I250" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J250" s="27"/>
+      <c r="K250" s="30">
+        <v>81</v>
+      </c>
+      <c r="L250" s="27"/>
+      <c r="M250" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="N250" s="32"/>
+    </row>
+    <row r="251" spans="1:14">
+      <c r="A251" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B251" s="2">
+        <v>44861</v>
+      </c>
+      <c r="C251" s="33">
+        <v>44862</v>
+      </c>
+      <c r="D251" s="27"/>
+      <c r="E251" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F251" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G251" s="29"/>
+      <c r="H251" s="27"/>
+      <c r="I251" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J251" s="27"/>
+      <c r="K251" s="35">
+        <v>15</v>
+      </c>
+      <c r="L251" s="27"/>
+      <c r="M251" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="N251" s="32"/>
+    </row>
+    <row r="252" spans="1:14">
+      <c r="A252" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B252" s="4">
+        <v>44860</v>
+      </c>
+      <c r="C252" s="26">
+        <v>44862</v>
+      </c>
+      <c r="D252" s="27"/>
+      <c r="E252" s="4">
+        <v>44866</v>
+      </c>
+      <c r="F252" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="G252" s="29"/>
+      <c r="H252" s="27"/>
+      <c r="I252" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J252" s="27"/>
+      <c r="K252" s="30">
+        <v>94</v>
+      </c>
+      <c r="L252" s="27"/>
+      <c r="M252" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="N252" s="32"/>
+    </row>
+    <row r="253" spans="1:14">
+      <c r="A253" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C253" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D253" s="27"/>
+      <c r="E253" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F253" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G253" s="29"/>
+      <c r="H253" s="27"/>
+      <c r="I253" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="J253" s="27"/>
+      <c r="K253" s="35">
+        <v>632</v>
+      </c>
+      <c r="L253" s="27"/>
+      <c r="M253" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="N253" s="32"/>
+    </row>
+    <row r="254" spans="1:14">
+      <c r="A254" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C254" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D254" s="27"/>
+      <c r="E254" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F254" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G254" s="29"/>
+      <c r="H254" s="27"/>
+      <c r="I254" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J254" s="27"/>
+      <c r="K254" s="30">
+        <v>36</v>
+      </c>
+      <c r="L254" s="27"/>
+      <c r="M254" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="N254" s="32"/>
+    </row>
+    <row r="255" spans="1:14">
+      <c r="A255" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B255" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C255" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D255" s="27"/>
+      <c r="E255" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F255" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G255" s="29"/>
+      <c r="H255" s="27"/>
+      <c r="I255" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J255" s="27"/>
+      <c r="K255" s="35">
+        <v>250</v>
+      </c>
+      <c r="L255" s="27"/>
+      <c r="M255" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="N255" s="32"/>
+    </row>
+    <row r="256" spans="1:14">
+      <c r="A256" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B256" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C256" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D256" s="27"/>
+      <c r="E256" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F256" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G256" s="29"/>
+      <c r="H256" s="27"/>
+      <c r="I256" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J256" s="27"/>
+      <c r="K256" s="30">
+        <v>1</v>
+      </c>
+      <c r="L256" s="27"/>
+      <c r="M256" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="N256" s="32"/>
+    </row>
+    <row r="257" spans="1:14">
+      <c r="A257" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B257" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C257" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D257" s="27"/>
+      <c r="E257" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F257" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G257" s="29"/>
+      <c r="H257" s="27"/>
+      <c r="I257" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J257" s="27"/>
+      <c r="K257" s="35">
+        <v>1</v>
+      </c>
+      <c r="L257" s="27"/>
+      <c r="M257" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="N257" s="32"/>
+    </row>
+    <row r="258" spans="1:14">
+      <c r="A258" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B258" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C258" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D258" s="27"/>
+      <c r="E258" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F258" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G258" s="29"/>
+      <c r="H258" s="27"/>
+      <c r="I258" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J258" s="27"/>
+      <c r="K258" s="30">
+        <v>1</v>
+      </c>
+      <c r="L258" s="27"/>
+      <c r="M258" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="N258" s="32"/>
+    </row>
+    <row r="259" spans="1:14">
+      <c r="A259" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B259" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C259" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D259" s="27"/>
+      <c r="E259" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F259" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G259" s="29"/>
+      <c r="H259" s="27"/>
+      <c r="I259" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J259" s="27"/>
+      <c r="K259" s="35">
+        <v>1</v>
+      </c>
+      <c r="L259" s="27"/>
+      <c r="M259" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="N259" s="32"/>
+    </row>
+    <row r="260" spans="1:14">
+      <c r="A260" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B260" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C260" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D260" s="27"/>
+      <c r="E260" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F260" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G260" s="29"/>
+      <c r="H260" s="27"/>
+      <c r="I260" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J260" s="27"/>
+      <c r="K260" s="30">
+        <v>1</v>
+      </c>
+      <c r="L260" s="27"/>
+      <c r="M260" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="N260" s="32"/>
+    </row>
+    <row r="261" spans="1:14">
+      <c r="A261" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B261" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C261" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D261" s="27"/>
+      <c r="E261" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F261" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G261" s="29"/>
+      <c r="H261" s="27"/>
+      <c r="I261" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J261" s="27"/>
+      <c r="K261" s="35">
+        <v>1</v>
+      </c>
+      <c r="L261" s="27"/>
+      <c r="M261" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="N261" s="32"/>
+    </row>
+    <row r="262" spans="1:14">
+      <c r="A262" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B262" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C262" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D262" s="27"/>
+      <c r="E262" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F262" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G262" s="29"/>
+      <c r="H262" s="27"/>
+      <c r="I262" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J262" s="27"/>
+      <c r="K262" s="30">
+        <v>1</v>
+      </c>
+      <c r="L262" s="27"/>
+      <c r="M262" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="N262" s="32"/>
+    </row>
+    <row r="263" spans="1:14">
+      <c r="A263" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B263" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C263" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D263" s="27"/>
+      <c r="E263" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F263" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G263" s="29"/>
+      <c r="H263" s="27"/>
+      <c r="I263" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J263" s="27"/>
+      <c r="K263" s="35">
+        <v>20</v>
+      </c>
+      <c r="L263" s="27"/>
+      <c r="M263" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="N263" s="32"/>
+    </row>
+    <row r="264" spans="1:14">
+      <c r="A264" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B264" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C264" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D264" s="27"/>
+      <c r="E264" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F264" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G264" s="29"/>
+      <c r="H264" s="27"/>
+      <c r="I264" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J264" s="27"/>
+      <c r="K264" s="30">
+        <v>1</v>
+      </c>
+      <c r="L264" s="27"/>
+      <c r="M264" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="N264" s="32"/>
+    </row>
+    <row r="265" spans="1:14">
+      <c r="A265" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B265" s="2">
+        <v>44789</v>
+      </c>
+      <c r="C265" s="33">
+        <v>44865</v>
+      </c>
+      <c r="D265" s="27"/>
+      <c r="E265" s="2">
+        <v>44852</v>
+      </c>
+      <c r="F265" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="G265" s="29"/>
+      <c r="H265" s="27"/>
+      <c r="I265" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J265" s="27"/>
+      <c r="K265" s="35">
+        <v>1</v>
+      </c>
+      <c r="L265" s="27"/>
+      <c r="M265" s="36" t="s">
+        <v>437</v>
+      </c>
+      <c r="N265" s="32"/>
+    </row>
+    <row r="266" spans="1:14">
+      <c r="A266" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B266" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C266" s="26">
+        <v>44865</v>
+      </c>
+      <c r="D266" s="27"/>
+      <c r="E266" s="4">
+        <v>44852</v>
+      </c>
+      <c r="F266" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="G266" s="29"/>
+      <c r="H266" s="27"/>
+      <c r="I266" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J266" s="27"/>
+      <c r="K266" s="30">
+        <v>1</v>
+      </c>
+      <c r="L266" s="27"/>
+      <c r="M266" s="31" t="s">
+        <v>438</v>
+      </c>
+      <c r="N266" s="32"/>
+    </row>
+    <row r="267" spans="1:14" ht="30" customHeight="1">
+      <c r="A267" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="B267" s="25"/>
+      <c r="C267" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="D267" s="22"/>
+      <c r="E267" s="23"/>
+      <c r="F267" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="G267" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="H267" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="I267" s="23"/>
+      <c r="J267" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="K267" s="23"/>
+      <c r="L267" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="M267" s="23"/>
+      <c r="N267" s="15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" s="13" customFormat="1">
+      <c r="A268" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="B268" s="20"/>
+      <c r="C268" s="16">
+        <v>21073</v>
+      </c>
+      <c r="D268" s="17"/>
+      <c r="E268" s="18"/>
+      <c r="F268" s="11">
+        <v>153</v>
+      </c>
+      <c r="G268" s="11">
         <v>8</v>
       </c>
-      <c r="H244" s="16">
+      <c r="H268" s="16">
         <v>1</v>
       </c>
-      <c r="I244" s="18"/>
-      <c r="J244" s="16">
-        <v>88</v>
-      </c>
-      <c r="K244" s="18"/>
-      <c r="L244" s="16">
-        <v>8</v>
-      </c>
-      <c r="M244" s="18"/>
-      <c r="N244" s="12">
+      <c r="I268" s="18"/>
+      <c r="J268" s="16">
+        <v>91</v>
+      </c>
+      <c r="K268" s="18"/>
+      <c r="L268" s="16">
+        <v>9</v>
+      </c>
+      <c r="M268" s="18"/>
+      <c r="N268" s="12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1212">
+  <mergeCells count="1332">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:J4"/>
@@ -11150,16 +12011,16 @@
     <mergeCell ref="I237:J237"/>
     <mergeCell ref="K237:L237"/>
     <mergeCell ref="M237:N237"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="H244:I244"/>
-    <mergeCell ref="J244:K244"/>
-    <mergeCell ref="L244:M244"/>
-    <mergeCell ref="A244:B244"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="H243:I243"/>
-    <mergeCell ref="J243:K243"/>
-    <mergeCell ref="L243:M243"/>
-    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="C244:D244"/>
+    <mergeCell ref="F244:H244"/>
+    <mergeCell ref="I244:J244"/>
+    <mergeCell ref="K244:L244"/>
+    <mergeCell ref="M244:N244"/>
+    <mergeCell ref="C243:D243"/>
+    <mergeCell ref="F243:H243"/>
+    <mergeCell ref="I243:J243"/>
+    <mergeCell ref="K243:L243"/>
+    <mergeCell ref="M243:N243"/>
     <mergeCell ref="C242:D242"/>
     <mergeCell ref="F242:H242"/>
     <mergeCell ref="I242:J242"/>
@@ -11170,6 +12031,126 @@
     <mergeCell ref="I241:J241"/>
     <mergeCell ref="K241:L241"/>
     <mergeCell ref="M241:N241"/>
+    <mergeCell ref="C248:D248"/>
+    <mergeCell ref="F248:H248"/>
+    <mergeCell ref="I248:J248"/>
+    <mergeCell ref="K248:L248"/>
+    <mergeCell ref="M248:N248"/>
+    <mergeCell ref="C247:D247"/>
+    <mergeCell ref="F247:H247"/>
+    <mergeCell ref="I247:J247"/>
+    <mergeCell ref="K247:L247"/>
+    <mergeCell ref="M247:N247"/>
+    <mergeCell ref="C246:D246"/>
+    <mergeCell ref="F246:H246"/>
+    <mergeCell ref="I246:J246"/>
+    <mergeCell ref="K246:L246"/>
+    <mergeCell ref="M246:N246"/>
+    <mergeCell ref="C245:D245"/>
+    <mergeCell ref="F245:H245"/>
+    <mergeCell ref="I245:J245"/>
+    <mergeCell ref="K245:L245"/>
+    <mergeCell ref="M245:N245"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:H252"/>
+    <mergeCell ref="I252:J252"/>
+    <mergeCell ref="K252:L252"/>
+    <mergeCell ref="M252:N252"/>
+    <mergeCell ref="C251:D251"/>
+    <mergeCell ref="F251:H251"/>
+    <mergeCell ref="I251:J251"/>
+    <mergeCell ref="K251:L251"/>
+    <mergeCell ref="M251:N251"/>
+    <mergeCell ref="C250:D250"/>
+    <mergeCell ref="F250:H250"/>
+    <mergeCell ref="I250:J250"/>
+    <mergeCell ref="K250:L250"/>
+    <mergeCell ref="M250:N250"/>
+    <mergeCell ref="C249:D249"/>
+    <mergeCell ref="F249:H249"/>
+    <mergeCell ref="I249:J249"/>
+    <mergeCell ref="K249:L249"/>
+    <mergeCell ref="M249:N249"/>
+    <mergeCell ref="C256:D256"/>
+    <mergeCell ref="F256:H256"/>
+    <mergeCell ref="I256:J256"/>
+    <mergeCell ref="K256:L256"/>
+    <mergeCell ref="M256:N256"/>
+    <mergeCell ref="C255:D255"/>
+    <mergeCell ref="F255:H255"/>
+    <mergeCell ref="I255:J255"/>
+    <mergeCell ref="K255:L255"/>
+    <mergeCell ref="M255:N255"/>
+    <mergeCell ref="C254:D254"/>
+    <mergeCell ref="F254:H254"/>
+    <mergeCell ref="I254:J254"/>
+    <mergeCell ref="K254:L254"/>
+    <mergeCell ref="M254:N254"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:H253"/>
+    <mergeCell ref="I253:J253"/>
+    <mergeCell ref="K253:L253"/>
+    <mergeCell ref="M253:N253"/>
+    <mergeCell ref="C260:D260"/>
+    <mergeCell ref="F260:H260"/>
+    <mergeCell ref="I260:J260"/>
+    <mergeCell ref="K260:L260"/>
+    <mergeCell ref="M260:N260"/>
+    <mergeCell ref="C259:D259"/>
+    <mergeCell ref="F259:H259"/>
+    <mergeCell ref="I259:J259"/>
+    <mergeCell ref="K259:L259"/>
+    <mergeCell ref="M259:N259"/>
+    <mergeCell ref="C258:D258"/>
+    <mergeCell ref="F258:H258"/>
+    <mergeCell ref="I258:J258"/>
+    <mergeCell ref="K258:L258"/>
+    <mergeCell ref="M258:N258"/>
+    <mergeCell ref="C257:D257"/>
+    <mergeCell ref="F257:H257"/>
+    <mergeCell ref="I257:J257"/>
+    <mergeCell ref="K257:L257"/>
+    <mergeCell ref="M257:N257"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:H264"/>
+    <mergeCell ref="I264:J264"/>
+    <mergeCell ref="K264:L264"/>
+    <mergeCell ref="M264:N264"/>
+    <mergeCell ref="C263:D263"/>
+    <mergeCell ref="F263:H263"/>
+    <mergeCell ref="I263:J263"/>
+    <mergeCell ref="K263:L263"/>
+    <mergeCell ref="M263:N263"/>
+    <mergeCell ref="C262:D262"/>
+    <mergeCell ref="F262:H262"/>
+    <mergeCell ref="I262:J262"/>
+    <mergeCell ref="K262:L262"/>
+    <mergeCell ref="M262:N262"/>
+    <mergeCell ref="C261:D261"/>
+    <mergeCell ref="F261:H261"/>
+    <mergeCell ref="I261:J261"/>
+    <mergeCell ref="K261:L261"/>
+    <mergeCell ref="M261:N261"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="H268:I268"/>
+    <mergeCell ref="J268:K268"/>
+    <mergeCell ref="L268:M268"/>
+    <mergeCell ref="A268:B268"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="H267:I267"/>
+    <mergeCell ref="J267:K267"/>
+    <mergeCell ref="L267:M267"/>
+    <mergeCell ref="A267:B267"/>
+    <mergeCell ref="C266:D266"/>
+    <mergeCell ref="F266:H266"/>
+    <mergeCell ref="I266:J266"/>
+    <mergeCell ref="K266:L266"/>
+    <mergeCell ref="M266:N266"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:H265"/>
+    <mergeCell ref="I265:J265"/>
+    <mergeCell ref="K265:L265"/>
+    <mergeCell ref="M265:N265"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="7080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19692" windowHeight="10860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="618">
   <si>
     <t/>
   </si>
@@ -1865,6 +1865,24 @@
     <t>18191 Von Karman Avenue  Irvine CA 92612</t>
   </si>
   <si>
+    <t>Meta Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>12105 E Waterfront Dr.  Los Angeles CA 90094</t>
+  </si>
+  <si>
+    <t>Smithfield Distribution, LLC</t>
+  </si>
+  <si>
+    <t>3163 E. Vernon Avenue  Vernon CA 90058</t>
+  </si>
+  <si>
+    <t>3049 E. Vernon Ave.  Vernon CA 90058</t>
+  </si>
+  <si>
+    <t>250 Howard St.  San Francisco CA 94105</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1892,13 +1910,13 @@
     <t>WARN Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">  Filter By Date: Received Date
+    <t xml:space="preserve">Filter By Date: Received Date
  Start Date: 7/1/2022
- End Date: 11/14/2022
+ End Date: 11/16/2022
 </t>
   </si>
   <si>
-    <t>Report Summary</t>
+    <t xml:space="preserve">Report Summary </t>
   </si>
 </sst>
 </file>
@@ -1967,12 +1985,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFDCDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1986,6 +1998,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFDCDCDC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2326,18 +2344,6 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2345,31 +2351,43 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2405,19 +2423,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2435,19 +2453,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2730,79 +2748,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R363"/>
+  <dimension ref="A1:R367"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="2.88671875" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" customWidth="1"/>
-    <col min="10" max="10" width="7.44140625" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" customWidth="1"/>
-    <col min="13" max="13" width="6.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="2.5546875" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" customWidth="1"/>
+    <col min="6" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" customWidth="1"/>
     <col min="14" max="14" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="37.5" customHeight="1">
-      <c r="A2" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="A1" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="38.25" customHeight="1">
+      <c r="A2" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="17"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="13" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -2824,17 +2841,17 @@
       <c r="N3" s="20"/>
     </row>
     <row r="4" spans="1:18" ht="24.6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="35"/>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="34" t="s">
@@ -14279,82 +14296,230 @@
       </c>
       <c r="N361" s="29"/>
     </row>
-    <row r="362" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A362" s="47" t="s">
+    <row r="362" spans="1:14">
+      <c r="A362" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B362" s="4">
+        <v>44876</v>
+      </c>
+      <c r="C362" s="30">
+        <v>44881</v>
+      </c>
+      <c r="D362" s="24"/>
+      <c r="E362" s="4">
+        <v>44939</v>
+      </c>
+      <c r="F362" s="31" t="s">
+        <v>601</v>
+      </c>
+      <c r="G362" s="26"/>
+      <c r="H362" s="24"/>
+      <c r="I362" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J362" s="24"/>
+      <c r="K362" s="32">
+        <v>162</v>
+      </c>
+      <c r="L362" s="24"/>
+      <c r="M362" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="N362" s="29"/>
+    </row>
+    <row r="363" spans="1:14">
+      <c r="A363" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B363" s="2">
+        <v>44826</v>
+      </c>
+      <c r="C363" s="23">
+        <v>44881</v>
+      </c>
+      <c r="D363" s="24"/>
+      <c r="E363" s="2">
+        <v>44883</v>
+      </c>
+      <c r="F363" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="G363" s="26"/>
+      <c r="H363" s="24"/>
+      <c r="I363" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J363" s="24"/>
+      <c r="K363" s="27">
+        <v>1755</v>
+      </c>
+      <c r="L363" s="24"/>
+      <c r="M363" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="N363" s="29"/>
+    </row>
+    <row r="364" spans="1:14">
+      <c r="A364" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B364" s="4">
+        <v>44826</v>
+      </c>
+      <c r="C364" s="30">
+        <v>44881</v>
+      </c>
+      <c r="D364" s="24"/>
+      <c r="E364" s="4">
+        <v>44883</v>
+      </c>
+      <c r="F364" s="31" t="s">
+        <v>603</v>
+      </c>
+      <c r="G364" s="26"/>
+      <c r="H364" s="24"/>
+      <c r="I364" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J364" s="24"/>
+      <c r="K364" s="32">
+        <v>121</v>
+      </c>
+      <c r="L364" s="24"/>
+      <c r="M364" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="N364" s="29"/>
+    </row>
+    <row r="365" spans="1:14">
+      <c r="A365" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B365" s="2">
+        <v>44876</v>
+      </c>
+      <c r="C365" s="23">
+        <v>44881</v>
+      </c>
+      <c r="D365" s="24"/>
+      <c r="E365" s="2">
+        <v>44939</v>
+      </c>
+      <c r="F365" s="25" t="s">
+        <v>601</v>
+      </c>
+      <c r="G365" s="26"/>
+      <c r="H365" s="24"/>
+      <c r="I365" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J365" s="24"/>
+      <c r="K365" s="27">
+        <v>362</v>
+      </c>
+      <c r="L365" s="24"/>
+      <c r="M365" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="N365" s="29"/>
+    </row>
+    <row r="366" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A366" s="47" t="s">
+        <v>617</v>
+      </c>
+      <c r="B366" s="48"/>
+      <c r="C366" s="44" t="s">
+        <v>607</v>
+      </c>
+      <c r="D366" s="45"/>
+      <c r="E366" s="46"/>
+      <c r="F366" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="G366" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="H366" s="44" t="s">
+        <v>610</v>
+      </c>
+      <c r="I366" s="46"/>
+      <c r="J366" s="44" t="s">
         <v>611</v>
       </c>
-      <c r="B362" s="48"/>
-      <c r="C362" s="44" t="s">
-        <v>601</v>
-      </c>
-      <c r="D362" s="45"/>
-      <c r="E362" s="46"/>
-      <c r="F362" s="14" t="s">
-        <v>602</v>
-      </c>
-      <c r="G362" s="14" t="s">
-        <v>603</v>
-      </c>
-      <c r="H362" s="44" t="s">
-        <v>604</v>
-      </c>
-      <c r="I362" s="46"/>
-      <c r="J362" s="44" t="s">
-        <v>605</v>
-      </c>
-      <c r="K362" s="46"/>
-      <c r="L362" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="M362" s="46"/>
-      <c r="N362" s="15" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="363" spans="1:14" s="13" customFormat="1">
-      <c r="A363" s="42" t="s">
-        <v>608</v>
-      </c>
-      <c r="B363" s="43"/>
-      <c r="C363" s="39">
-        <v>25423</v>
-      </c>
-      <c r="D363" s="40"/>
-      <c r="E363" s="41"/>
-      <c r="F363" s="11">
-        <v>215</v>
-      </c>
-      <c r="G363" s="11">
+      <c r="K366" s="46"/>
+      <c r="L366" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="M366" s="46"/>
+      <c r="N366" s="11" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" s="9" customFormat="1">
+      <c r="A367" s="42" t="s">
+        <v>614</v>
+      </c>
+      <c r="B367" s="43"/>
+      <c r="C367" s="39">
+        <v>27823</v>
+      </c>
+      <c r="D367" s="40"/>
+      <c r="E367" s="41"/>
+      <c r="F367" s="7">
+        <v>217</v>
+      </c>
+      <c r="G367" s="7">
         <v>8</v>
       </c>
-      <c r="H363" s="39">
+      <c r="H367" s="39">
         <v>1</v>
       </c>
-      <c r="I363" s="41"/>
-      <c r="J363" s="39">
-        <v>124</v>
-      </c>
-      <c r="K363" s="41"/>
-      <c r="L363" s="39">
+      <c r="I367" s="41"/>
+      <c r="J367" s="39">
+        <v>126</v>
+      </c>
+      <c r="K367" s="41"/>
+      <c r="L367" s="39">
         <v>9</v>
       </c>
-      <c r="M363" s="41"/>
-      <c r="N363" s="12">
+      <c r="M367" s="41"/>
+      <c r="N367" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1807">
-    <mergeCell ref="C363:E363"/>
-    <mergeCell ref="H363:I363"/>
-    <mergeCell ref="J363:K363"/>
-    <mergeCell ref="L363:M363"/>
-    <mergeCell ref="A363:B363"/>
-    <mergeCell ref="C362:E362"/>
-    <mergeCell ref="H362:I362"/>
-    <mergeCell ref="J362:K362"/>
-    <mergeCell ref="L362:M362"/>
-    <mergeCell ref="A362:B362"/>
+  <mergeCells count="1827">
+    <mergeCell ref="C367:E367"/>
+    <mergeCell ref="H367:I367"/>
+    <mergeCell ref="J367:K367"/>
+    <mergeCell ref="L367:M367"/>
+    <mergeCell ref="A367:B367"/>
+    <mergeCell ref="C366:E366"/>
+    <mergeCell ref="H366:I366"/>
+    <mergeCell ref="J366:K366"/>
+    <mergeCell ref="L366:M366"/>
+    <mergeCell ref="A366:B366"/>
+    <mergeCell ref="C365:D365"/>
+    <mergeCell ref="F365:H365"/>
+    <mergeCell ref="I365:J365"/>
+    <mergeCell ref="K365:L365"/>
+    <mergeCell ref="M365:N365"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:H364"/>
+    <mergeCell ref="I364:J364"/>
+    <mergeCell ref="K364:L364"/>
+    <mergeCell ref="M364:N364"/>
+    <mergeCell ref="C363:D363"/>
+    <mergeCell ref="F363:H363"/>
+    <mergeCell ref="I363:J363"/>
+    <mergeCell ref="K363:L363"/>
+    <mergeCell ref="M363:N363"/>
+    <mergeCell ref="C362:D362"/>
+    <mergeCell ref="F362:H362"/>
+    <mergeCell ref="I362:J362"/>
+    <mergeCell ref="K362:L362"/>
+    <mergeCell ref="M362:N362"/>
     <mergeCell ref="C361:D361"/>
     <mergeCell ref="F361:H361"/>
     <mergeCell ref="I361:J361"/>
@@ -16130,8 +16295,8 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="I7:J7"/>

--- a/data/warn-scraper/cache/ca/warn_report.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19692" windowHeight="10860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16860" windowHeight="10608"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="657">
   <si>
     <t/>
   </si>
@@ -1883,6 +1883,123 @@
     <t>250 Howard St.  San Francisco CA 94105</t>
   </si>
   <si>
+    <t>3446 W. Ball Rd.  Anaheim CA 92804</t>
+  </si>
+  <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
+    <t>951 SanDisk Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>Aerotek at Flex LTD</t>
+  </si>
+  <si>
+    <t>1177 Gibraltar Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>12001 Euclid St.  Garden Grove CA 92840</t>
+  </si>
+  <si>
+    <t>1538 E. Chapman Ave.  Orange CA 92866</t>
+  </si>
+  <si>
+    <t>13052 Newport Ave.  Tustin CA 92780</t>
+  </si>
+  <si>
+    <t>1575 S. Harbor Blvd. Suite 48  Fullerton CA 92832</t>
+  </si>
+  <si>
+    <t>17585 Harvard Ave. Suite D  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>25612 Crown Valley Pkwy, Suite L-5  Ladera Ranch CA 92694</t>
+  </si>
+  <si>
+    <t>26012 Marguerite Pkwy Suite H  Mission Viejo CA 92692</t>
+  </si>
+  <si>
+    <t>600 Newport Center Drive  Newport Beach CA 92660</t>
+  </si>
+  <si>
+    <t>2500 E. Imperial Hwy, Suite 110  Brea CA 92821</t>
+  </si>
+  <si>
+    <t>24833 Del Prado  Dana Point CA 92629</t>
+  </si>
+  <si>
+    <t>57 Prism  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>3355 Michelson Drive  Irvine CA 92612</t>
+  </si>
+  <si>
+    <t>Sodexo Inc. at PHH Hemet Valley Medical Center</t>
+  </si>
+  <si>
+    <t>1117 E. Devonshire Avenue  Hemet CA 92543</t>
+  </si>
+  <si>
+    <t>Sodexo Inc. at PHH Hemet Valley Recovery Center</t>
+  </si>
+  <si>
+    <t>371 N. Weston Avenue  Hemet CA 92543</t>
+  </si>
+  <si>
+    <t>Sodexo Inc. at PHH Menifee Valley Medical Center</t>
+  </si>
+  <si>
+    <t>28400 McCall Blvd.  Sun City CA 92586</t>
+  </si>
+  <si>
+    <t>6375 San Ignacio Avenue  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>5601 Great Oaks Parkway  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>GoFundMe, Inc.</t>
+  </si>
+  <si>
+    <t>767 S. Alameda St. Ste 400  Los Angeles CA 90021</t>
+  </si>
+  <si>
+    <t>Synthego Corporation</t>
+  </si>
+  <si>
+    <t>600 Saginaw Dr  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>350 Tenth Ave  San Diego CA 92101</t>
+  </si>
+  <si>
+    <t>GoFundMe, Inc</t>
+  </si>
+  <si>
+    <t>4650 Overland Avenue  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>600 California Ave Office# 13-000  San Francisco CA 94108</t>
+  </si>
+  <si>
+    <t>Coursera, Inc.</t>
+  </si>
+  <si>
+    <t>381 E Evelyn Ave  Mountain View CA 94041</t>
+  </si>
+  <si>
+    <t>Asana, Inc.</t>
+  </si>
+  <si>
+    <t>633 Folsom Street, Suite 100  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Wilhelm L.L.C.</t>
+  </si>
+  <si>
+    <t>181 Lynch Creek Way  Petaluma CA 94954</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Employees Affected</t>
   </si>
   <si>
@@ -1907,16 +2024,16 @@
     <t>Total</t>
   </si>
   <si>
+    <t xml:space="preserve"> Filter By Date: Received Date
+ Start Date: 7/1/2022
+ End Date: 11/21/2022
+</t>
+  </si>
+  <si>
     <t>WARN Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Filter By Date: Received Date
- Start Date: 7/1/2022
- End Date: 11/16/2022
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report Summary </t>
+    <t>Report Summary</t>
   </si>
 </sst>
 </file>
@@ -1985,6 +2102,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFDCDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1998,12 +2121,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFDCDCDC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2292,6 +2409,19 @@
         <color rgb="FFA9A9A9"/>
       </top>
       <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -2306,19 +2436,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9A9A9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9A9A9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2351,37 +2468,37 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2423,19 +2540,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2447,25 +2564,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2748,25 +2865,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R367"/>
+  <dimension ref="A1:R395"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="2.5546875" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" customWidth="1"/>
-    <col min="6" max="7" width="11.33203125" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" customWidth="1"/>
-    <col min="10" max="10" width="7.5546875" customWidth="1"/>
-    <col min="11" max="11" width="5.33203125" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="3" max="3" width="2.44140625" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" customWidth="1"/>
     <col min="14" max="14" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="21" t="s">
-        <v>615</v>
+        <v>655</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -2781,14 +2899,14 @@
       <c r="L1" s="21"/>
       <c r="M1" s="21"/>
       <c r="N1" s="21"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="38.25" customHeight="1">
       <c r="A2" s="22" t="s">
-        <v>616</v>
+        <v>654</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -2803,23 +2921,23 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="17"/>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -2841,17 +2959,17 @@
       <c r="N3" s="20"/>
     </row>
     <row r="4" spans="1:18" ht="24.6">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="35"/>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="34" t="s">
@@ -14424,82 +14542,1118 @@
       </c>
       <c r="N365" s="29"/>
     </row>
-    <row r="366" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A366" s="47" t="s">
+    <row r="366" spans="1:14">
+      <c r="A366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B366" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C366" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D366" s="24"/>
+      <c r="E366" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F366" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G366" s="26"/>
+      <c r="H366" s="24"/>
+      <c r="I366" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J366" s="24"/>
+      <c r="K366" s="32">
+        <v>2</v>
+      </c>
+      <c r="L366" s="24"/>
+      <c r="M366" s="33" t="s">
+        <v>607</v>
+      </c>
+      <c r="N366" s="29"/>
+    </row>
+    <row r="367" spans="1:14">
+      <c r="A367" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B367" s="2">
+        <v>44874</v>
+      </c>
+      <c r="C367" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D367" s="24"/>
+      <c r="E367" s="2">
+        <v>44939</v>
+      </c>
+      <c r="F367" s="25" t="s">
+        <v>608</v>
+      </c>
+      <c r="G367" s="26"/>
+      <c r="H367" s="24"/>
+      <c r="I367" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J367" s="24"/>
+      <c r="K367" s="27">
+        <v>86</v>
+      </c>
+      <c r="L367" s="24"/>
+      <c r="M367" s="28" t="s">
+        <v>609</v>
+      </c>
+      <c r="N367" s="29"/>
+    </row>
+    <row r="368" spans="1:14">
+      <c r="A368" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B368" s="4">
+        <v>44876</v>
+      </c>
+      <c r="C368" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D368" s="24"/>
+      <c r="E368" s="4">
+        <v>44875</v>
+      </c>
+      <c r="F368" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="G368" s="26"/>
+      <c r="H368" s="24"/>
+      <c r="I368" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J368" s="24"/>
+      <c r="K368" s="32">
+        <v>48</v>
+      </c>
+      <c r="L368" s="24"/>
+      <c r="M368" s="33" t="s">
+        <v>611</v>
+      </c>
+      <c r="N368" s="29"/>
+    </row>
+    <row r="369" spans="1:14">
+      <c r="A369" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B369" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C369" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D369" s="24"/>
+      <c r="E369" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F369" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G369" s="26"/>
+      <c r="H369" s="24"/>
+      <c r="I369" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J369" s="24"/>
+      <c r="K369" s="27">
+        <v>2</v>
+      </c>
+      <c r="L369" s="24"/>
+      <c r="M369" s="28" t="s">
+        <v>612</v>
+      </c>
+      <c r="N369" s="29"/>
+    </row>
+    <row r="370" spans="1:14">
+      <c r="A370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B370" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C370" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D370" s="24"/>
+      <c r="E370" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F370" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G370" s="26"/>
+      <c r="H370" s="24"/>
+      <c r="I370" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J370" s="24"/>
+      <c r="K370" s="32">
+        <v>6</v>
+      </c>
+      <c r="L370" s="24"/>
+      <c r="M370" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="N370" s="29"/>
+    </row>
+    <row r="371" spans="1:14">
+      <c r="A371" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B371" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C371" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D371" s="24"/>
+      <c r="E371" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F371" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G371" s="26"/>
+      <c r="H371" s="24"/>
+      <c r="I371" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J371" s="24"/>
+      <c r="K371" s="27">
+        <v>3</v>
+      </c>
+      <c r="L371" s="24"/>
+      <c r="M371" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="N371" s="29"/>
+    </row>
+    <row r="372" spans="1:14">
+      <c r="A372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B372" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C372" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D372" s="24"/>
+      <c r="E372" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F372" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G372" s="26"/>
+      <c r="H372" s="24"/>
+      <c r="I372" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J372" s="24"/>
+      <c r="K372" s="32">
+        <v>12</v>
+      </c>
+      <c r="L372" s="24"/>
+      <c r="M372" s="33" t="s">
+        <v>615</v>
+      </c>
+      <c r="N372" s="29"/>
+    </row>
+    <row r="373" spans="1:14">
+      <c r="A373" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B373" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C373" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D373" s="24"/>
+      <c r="E373" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F373" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G373" s="26"/>
+      <c r="H373" s="24"/>
+      <c r="I373" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J373" s="24"/>
+      <c r="K373" s="27">
+        <v>12</v>
+      </c>
+      <c r="L373" s="24"/>
+      <c r="M373" s="28" t="s">
+        <v>616</v>
+      </c>
+      <c r="N373" s="29"/>
+    </row>
+    <row r="374" spans="1:14">
+      <c r="A374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B374" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C374" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D374" s="24"/>
+      <c r="E374" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F374" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G374" s="26"/>
+      <c r="H374" s="24"/>
+      <c r="I374" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J374" s="24"/>
+      <c r="K374" s="32">
+        <v>4</v>
+      </c>
+      <c r="L374" s="24"/>
+      <c r="M374" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="B366" s="48"/>
-      <c r="C366" s="44" t="s">
-        <v>607</v>
-      </c>
-      <c r="D366" s="45"/>
-      <c r="E366" s="46"/>
-      <c r="F366" s="10" t="s">
+      <c r="N374" s="29"/>
+    </row>
+    <row r="375" spans="1:14">
+      <c r="A375" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B375" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C375" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D375" s="24"/>
+      <c r="E375" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F375" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G375" s="26"/>
+      <c r="H375" s="24"/>
+      <c r="I375" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J375" s="24"/>
+      <c r="K375" s="27">
+        <v>10</v>
+      </c>
+      <c r="L375" s="24"/>
+      <c r="M375" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="N375" s="29"/>
+    </row>
+    <row r="376" spans="1:14">
+      <c r="A376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B376" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C376" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D376" s="24"/>
+      <c r="E376" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F376" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G376" s="26"/>
+      <c r="H376" s="24"/>
+      <c r="I376" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J376" s="24"/>
+      <c r="K376" s="32">
+        <v>4</v>
+      </c>
+      <c r="L376" s="24"/>
+      <c r="M376" s="33" t="s">
+        <v>619</v>
+      </c>
+      <c r="N376" s="29"/>
+    </row>
+    <row r="377" spans="1:14">
+      <c r="A377" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B377" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C377" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D377" s="24"/>
+      <c r="E377" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F377" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G377" s="26"/>
+      <c r="H377" s="24"/>
+      <c r="I377" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J377" s="24"/>
+      <c r="K377" s="27">
+        <v>4</v>
+      </c>
+      <c r="L377" s="24"/>
+      <c r="M377" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="N377" s="29"/>
+    </row>
+    <row r="378" spans="1:14">
+      <c r="A378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B378" s="4">
+        <v>44866</v>
+      </c>
+      <c r="C378" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D378" s="24"/>
+      <c r="E378" s="4">
+        <v>44929</v>
+      </c>
+      <c r="F378" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="G378" s="26"/>
+      <c r="H378" s="24"/>
+      <c r="I378" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J378" s="24"/>
+      <c r="K378" s="32">
+        <v>1</v>
+      </c>
+      <c r="L378" s="24"/>
+      <c r="M378" s="33" t="s">
+        <v>621</v>
+      </c>
+      <c r="N378" s="29"/>
+    </row>
+    <row r="379" spans="1:14">
+      <c r="A379" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B379" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C379" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D379" s="24"/>
+      <c r="E379" s="2">
+        <v>44929</v>
+      </c>
+      <c r="F379" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="G379" s="26"/>
+      <c r="H379" s="24"/>
+      <c r="I379" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J379" s="24"/>
+      <c r="K379" s="27">
+        <v>5</v>
+      </c>
+      <c r="L379" s="24"/>
+      <c r="M379" s="28" t="s">
+        <v>622</v>
+      </c>
+      <c r="N379" s="29"/>
+    </row>
+    <row r="380" spans="1:14">
+      <c r="A380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B380" s="4">
+        <v>44874</v>
+      </c>
+      <c r="C380" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D380" s="24"/>
+      <c r="E380" s="4">
+        <v>44939</v>
+      </c>
+      <c r="F380" s="31" t="s">
         <v>608</v>
       </c>
-      <c r="G366" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="H366" s="44" t="s">
-        <v>610</v>
-      </c>
-      <c r="I366" s="46"/>
-      <c r="J366" s="44" t="s">
-        <v>611</v>
-      </c>
-      <c r="K366" s="46"/>
-      <c r="L366" s="44" t="s">
-        <v>612</v>
-      </c>
-      <c r="M366" s="46"/>
-      <c r="N366" s="11" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="367" spans="1:14" s="9" customFormat="1">
-      <c r="A367" s="42" t="s">
-        <v>614</v>
-      </c>
-      <c r="B367" s="43"/>
-      <c r="C367" s="39">
-        <v>27823</v>
-      </c>
-      <c r="D367" s="40"/>
-      <c r="E367" s="41"/>
-      <c r="F367" s="7">
-        <v>217</v>
-      </c>
-      <c r="G367" s="7">
-        <v>8</v>
-      </c>
-      <c r="H367" s="39">
+      <c r="G380" s="26"/>
+      <c r="H380" s="24"/>
+      <c r="I380" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J380" s="24"/>
+      <c r="K380" s="32">
+        <v>62</v>
+      </c>
+      <c r="L380" s="24"/>
+      <c r="M380" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="N380" s="29"/>
+    </row>
+    <row r="381" spans="1:14">
+      <c r="A381" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B381" s="2">
+        <v>44879</v>
+      </c>
+      <c r="C381" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D381" s="24"/>
+      <c r="E381" s="2">
+        <v>44939</v>
+      </c>
+      <c r="F381" s="25" t="s">
+        <v>624</v>
+      </c>
+      <c r="G381" s="26"/>
+      <c r="H381" s="24"/>
+      <c r="I381" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J381" s="24"/>
+      <c r="K381" s="27">
+        <v>83</v>
+      </c>
+      <c r="L381" s="24"/>
+      <c r="M381" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="N381" s="29"/>
+    </row>
+    <row r="382" spans="1:14">
+      <c r="A382" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B382" s="4">
+        <v>44879</v>
+      </c>
+      <c r="C382" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D382" s="24"/>
+      <c r="E382" s="4">
+        <v>44939</v>
+      </c>
+      <c r="F382" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G382" s="26"/>
+      <c r="H382" s="24"/>
+      <c r="I382" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="J382" s="24"/>
+      <c r="K382" s="32">
+        <v>14</v>
+      </c>
+      <c r="L382" s="24"/>
+      <c r="M382" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="N382" s="29"/>
+    </row>
+    <row r="383" spans="1:14">
+      <c r="A383" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B383" s="2">
+        <v>44879</v>
+      </c>
+      <c r="C383" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D383" s="24"/>
+      <c r="E383" s="2">
+        <v>44939</v>
+      </c>
+      <c r="F383" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="G383" s="26"/>
+      <c r="H383" s="24"/>
+      <c r="I383" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J383" s="24"/>
+      <c r="K383" s="27">
+        <v>32</v>
+      </c>
+      <c r="L383" s="24"/>
+      <c r="M383" s="28" t="s">
+        <v>629</v>
+      </c>
+      <c r="N383" s="29"/>
+    </row>
+    <row r="384" spans="1:14">
+      <c r="A384" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B384" s="4">
+        <v>44869</v>
+      </c>
+      <c r="C384" s="30">
+        <v>44882</v>
+      </c>
+      <c r="D384" s="24"/>
+      <c r="E384" s="4">
+        <v>44917</v>
+      </c>
+      <c r="F384" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="G384" s="26"/>
+      <c r="H384" s="24"/>
+      <c r="I384" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="J384" s="24"/>
+      <c r="K384" s="32">
+        <v>93</v>
+      </c>
+      <c r="L384" s="24"/>
+      <c r="M384" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="N384" s="29"/>
+    </row>
+    <row r="385" spans="1:14">
+      <c r="A385" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B385" s="2">
+        <v>44874</v>
+      </c>
+      <c r="C385" s="23">
+        <v>44882</v>
+      </c>
+      <c r="D385" s="24"/>
+      <c r="E385" s="2">
+        <v>44939</v>
+      </c>
+      <c r="F385" s="25" t="s">
+        <v>608</v>
+      </c>
+      <c r="G385" s="26"/>
+      <c r="H385" s="24"/>
+      <c r="I385" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J385" s="24"/>
+      <c r="K385" s="27">
+        <v>103</v>
+      </c>
+      <c r="L385" s="24"/>
+      <c r="M385" s="28" t="s">
+        <v>631</v>
+      </c>
+      <c r="N385" s="29"/>
+    </row>
+    <row r="386" spans="1:14">
+      <c r="A386" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B386" s="4">
+        <v>44862</v>
+      </c>
+      <c r="C386" s="30">
+        <v>44883</v>
+      </c>
+      <c r="D386" s="24"/>
+      <c r="E386" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F386" s="31" t="s">
+        <v>632</v>
+      </c>
+      <c r="G386" s="26"/>
+      <c r="H386" s="24"/>
+      <c r="I386" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J386" s="24"/>
+      <c r="K386" s="32">
+        <v>27</v>
+      </c>
+      <c r="L386" s="24"/>
+      <c r="M386" s="33" t="s">
+        <v>633</v>
+      </c>
+      <c r="N386" s="29"/>
+    </row>
+    <row r="387" spans="1:14">
+      <c r="A387" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B387" s="2">
+        <v>44880</v>
+      </c>
+      <c r="C387" s="23">
+        <v>44883</v>
+      </c>
+      <c r="D387" s="24"/>
+      <c r="E387" s="2">
+        <v>44883</v>
+      </c>
+      <c r="F387" s="25" t="s">
+        <v>634</v>
+      </c>
+      <c r="G387" s="26"/>
+      <c r="H387" s="24"/>
+      <c r="I387" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J387" s="24"/>
+      <c r="K387" s="27">
+        <v>105</v>
+      </c>
+      <c r="L387" s="24"/>
+      <c r="M387" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="N387" s="29"/>
+    </row>
+    <row r="388" spans="1:14">
+      <c r="A388" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B388" s="4">
+        <v>44862</v>
+      </c>
+      <c r="C388" s="30">
+        <v>44883</v>
+      </c>
+      <c r="D388" s="24"/>
+      <c r="E388" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F388" s="31" t="s">
+        <v>632</v>
+      </c>
+      <c r="G388" s="26"/>
+      <c r="H388" s="24"/>
+      <c r="I388" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J388" s="24"/>
+      <c r="K388" s="32">
+        <v>11</v>
+      </c>
+      <c r="L388" s="24"/>
+      <c r="M388" s="33" t="s">
+        <v>636</v>
+      </c>
+      <c r="N388" s="29"/>
+    </row>
+    <row r="389" spans="1:14">
+      <c r="A389" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B389" s="2">
+        <v>44862</v>
+      </c>
+      <c r="C389" s="23">
+        <v>44883</v>
+      </c>
+      <c r="D389" s="24"/>
+      <c r="E389" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F389" s="25" t="s">
+        <v>637</v>
+      </c>
+      <c r="G389" s="26"/>
+      <c r="H389" s="24"/>
+      <c r="I389" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J389" s="24"/>
+      <c r="K389" s="27">
+        <v>23</v>
+      </c>
+      <c r="L389" s="24"/>
+      <c r="M389" s="28" t="s">
+        <v>638</v>
+      </c>
+      <c r="N389" s="29"/>
+    </row>
+    <row r="390" spans="1:14">
+      <c r="A390" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B390" s="4">
+        <v>44862</v>
+      </c>
+      <c r="C390" s="30">
+        <v>44883</v>
+      </c>
+      <c r="D390" s="24"/>
+      <c r="E390" s="4">
+        <v>44926</v>
+      </c>
+      <c r="F390" s="31" t="s">
+        <v>632</v>
+      </c>
+      <c r="G390" s="26"/>
+      <c r="H390" s="24"/>
+      <c r="I390" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J390" s="24"/>
+      <c r="K390" s="32">
+        <v>11</v>
+      </c>
+      <c r="L390" s="24"/>
+      <c r="M390" s="33" t="s">
+        <v>639</v>
+      </c>
+      <c r="N390" s="29"/>
+    </row>
+    <row r="391" spans="1:14">
+      <c r="A391" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B391" s="2">
+        <v>44876</v>
+      </c>
+      <c r="C391" s="23">
+        <v>44886</v>
+      </c>
+      <c r="D391" s="24"/>
+      <c r="E391" s="2">
+        <v>44874</v>
+      </c>
+      <c r="F391" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="G391" s="26"/>
+      <c r="H391" s="24"/>
+      <c r="I391" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J391" s="24"/>
+      <c r="K391" s="27">
+        <v>77</v>
+      </c>
+      <c r="L391" s="24"/>
+      <c r="M391" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="N391" s="29"/>
+    </row>
+    <row r="392" spans="1:14">
+      <c r="A392" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B392" s="4">
+        <v>44880</v>
+      </c>
+      <c r="C392" s="30">
+        <v>44886</v>
+      </c>
+      <c r="D392" s="24"/>
+      <c r="E392" s="4">
+        <v>44880</v>
+      </c>
+      <c r="F392" s="31" t="s">
+        <v>642</v>
+      </c>
+      <c r="G392" s="26"/>
+      <c r="H392" s="24"/>
+      <c r="I392" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J392" s="24"/>
+      <c r="K392" s="32">
+        <v>97</v>
+      </c>
+      <c r="L392" s="24"/>
+      <c r="M392" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="N392" s="29"/>
+    </row>
+    <row r="393" spans="1:14">
+      <c r="A393" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B393" s="2">
+        <v>44874</v>
+      </c>
+      <c r="C393" s="23">
+        <v>44886</v>
+      </c>
+      <c r="D393" s="24"/>
+      <c r="E393" s="2">
+        <v>44934</v>
+      </c>
+      <c r="F393" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="G393" s="26"/>
+      <c r="H393" s="24"/>
+      <c r="I393" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J393" s="24"/>
+      <c r="K393" s="27">
+        <v>274</v>
+      </c>
+      <c r="L393" s="24"/>
+      <c r="M393" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="N393" s="29"/>
+    </row>
+    <row r="394" spans="1:14" ht="30.75" customHeight="1">
+      <c r="A394" s="47" t="s">
+        <v>656</v>
+      </c>
+      <c r="B394" s="48"/>
+      <c r="C394" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="D394" s="45"/>
+      <c r="E394" s="46"/>
+      <c r="F394" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="G394" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="H394" s="44" t="s">
+        <v>649</v>
+      </c>
+      <c r="I394" s="46"/>
+      <c r="J394" s="44" t="s">
+        <v>650</v>
+      </c>
+      <c r="K394" s="46"/>
+      <c r="L394" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="M394" s="46"/>
+      <c r="N394" s="12" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" s="9" customFormat="1">
+      <c r="A395" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="B395" s="43"/>
+      <c r="C395" s="39">
+        <v>29034</v>
+      </c>
+      <c r="D395" s="40"/>
+      <c r="E395" s="41"/>
+      <c r="F395" s="7">
+        <v>229</v>
+      </c>
+      <c r="G395" s="7">
+        <v>9</v>
+      </c>
+      <c r="H395" s="39">
         <v>1</v>
       </c>
-      <c r="I367" s="41"/>
-      <c r="J367" s="39">
-        <v>126</v>
-      </c>
-      <c r="K367" s="41"/>
-      <c r="L367" s="39">
+      <c r="I395" s="41"/>
+      <c r="J395" s="39">
+        <v>141</v>
+      </c>
+      <c r="K395" s="41"/>
+      <c r="L395" s="39">
         <v>9</v>
       </c>
-      <c r="M367" s="41"/>
-      <c r="N367" s="8">
+      <c r="M395" s="41"/>
+      <c r="N395" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1827">
-    <mergeCell ref="C367:E367"/>
-    <mergeCell ref="H367:I367"/>
-    <mergeCell ref="J367:K367"/>
-    <mergeCell ref="L367:M367"/>
-    <mergeCell ref="A367:B367"/>
-    <mergeCell ref="C366:E366"/>
-    <mergeCell ref="H366:I366"/>
-    <mergeCell ref="J366:K366"/>
-    <mergeCell ref="L366:M366"/>
-    <mergeCell ref="A366:B366"/>
+  <mergeCells count="1967">
+    <mergeCell ref="C395:E395"/>
+    <mergeCell ref="H395:I395"/>
+    <mergeCell ref="J395:K395"/>
+    <mergeCell ref="L395:M395"/>
+    <mergeCell ref="A395:B395"/>
+    <mergeCell ref="C394:E394"/>
+    <mergeCell ref="H394:I394"/>
+    <mergeCell ref="J394:K394"/>
+    <mergeCell ref="L394:M394"/>
+    <mergeCell ref="A394:B394"/>
+    <mergeCell ref="C393:D393"/>
+    <mergeCell ref="F393:H393"/>
+    <mergeCell ref="I393:J393"/>
+    <mergeCell ref="K393:L393"/>
+    <mergeCell ref="M3